--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="629">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES FRANÇAIS CONTEMPORAINS — Données source</t>
   </si>
@@ -1365,6 +1365,25 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe français promoteur de la philosophie sociale en France &amp;amp; de l'épistémologie hégélienne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franck FISCHBACH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Franck_Fischbach"  style="color:#6A142A"  title=" Wikipedia"&gt;Franck FISCHBACH&lt;/a&gt; est un philosophe franço-suisse  spécialiste de la philosophie allemande et de la philosophie sociale. Ses recherches portent sur l’idéalisme allemand (particulièrement Fichte, Hegel et Schelling), la réception de Marx et la philosophie sociale contemporaine. Il s’intéresse notamment à la reconnaissance, à l’aliénation, au travail, au socialisme, et à la &lt;a href="https://www.philomag.com/articles/franck-fischbach-le-capitalisme-fabrique-des-etres-qui-netant-plus-vraiment-sociaux-ne" style="color:#88A1E9" title=" Franck Fischbach : “Le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains” par philosophie magazine"&gt;critique du capitalisme&lt;/a&gt;. Il contribue activement à redonner à la philosophie sociale une légitimité intellectuelle en France. &lt;/p&gt; &lt;p&gt; Il relie la tradition de la théorie critique (Adorno, Honneth) et celle du matérialisme marxien pour repenser les conditions de la vie sociale et du « vivre ensemble ». Il analyse le capitalisme contemporain comme un processus de désocialisation et de perte du monde commun, considérant que "le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains".​ &lt;/p&gt; &lt;p&gt; Il  a reçu le Prix des Rencontres philosophiques de Monaco pour &lt;a href="https://www.youtube.com/watch?v=i16BcDagxns&amp;t=73s" style="color:#88A1E9" title=" Franck Fischbach → Faire ensemble. Reconstruction sociale et sortie du capitalisme par Librairie Ombre Blanche"&gt;"Faire ensemble"&lt;/a&gt;, ouvrage dans lequel il propose une refondation du lien social et une sortie éthique du capitalisme et il est aujourd’hui reconnu comme l’un des penseurs français majeurs de la philosophie sociale, prolongeant la critique marxienne à la lumière des défis écologiques et politiques contemporains.​ &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Qu'est-ce que la philosophie sociale? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11188-25.03.2010-ITEMA_20221135-2010C14987S0084-NET_B0358179-5AB7-42B6-8D32-144EADE35F65_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QetmJoRDpY0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franck Fischbach, L’aliénation : un concept encore utile aujourd’hui ? par Departement Philosophie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/fischbach-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe franco-suisse spécialiste de la philosophie sociale.</t>
   </si>
   <si>
     <t xml:space="preserve">Camille FROIDEVAUX-METTERIE</t>
@@ -1829,6 +1848,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julia_de_Fun%C3%A8s"  title=" Wikipedia"&gt;Julia DE-FUNÈS&lt;/a&gt; est une philosophe, essayiste et conférencière française, également spécialiste des ressources humaines et du monde de l’entreprise. Après avoir travaillé plusieurs années comme chasseuse de têtes, elle a créé en 2010 un cabinet de conseil mobilisant la philosophie dans les organisations. Elle a ensuite soutenu en 2017 une thèse consacrée au passage de l’identité personnelle à l’authenticité, à travers les notions de représentation et de mimétisme. &lt;/p&gt; &lt;p&gt;</t>
     </r>
@@ -1838,6 +1858,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">&lt;a href="https://www.youtube.com/watch?v=OaDbpC3azdQ"  title="julia de Funès, philosophe par 21 News"&gt;</t>
     </r>
@@ -1847,6 +1868,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Sa démarche consiste &lt;/a&gt;  à faire sortir la philosophie du cadre purement universitaire pour la confronter aux situations ordinaires : travail, management, bonheur, relations professionnelles ou développement personnel. Elle considère la philosophie comme un exercice de mise à distance, destiné à interroger les évidences et à examiner le sens réel des mots que nous employons. Dans cette perspective, philosopher revient à ne pas accepter mécaniquement les discours dominants, les slogans ou les habitudes de pensée. &lt;/p&gt; &lt;p&gt; Une de ses principales critiques vise l’entreprise contemporaine et la multiplication des procédures, des indicateurs et des discours managériaux. Dans Socrate au pays des process ou La Vie de bureau, elle dénonce ce qu’elle perçoit comme une perte de sens : les salariés peuvent être soumis à des injonctions contradictoires et à un langage abstrait qui transforme parfois l’être humain en simple fonction. Elle oppose à cette logique la nécessité de retrouver du jugement, de l’autonomie et une réflexion véritable sur les finalités du travail. &lt;/p&gt; &lt;p&gt; Elle critique également le développement personnel lorsqu’il promet le bonheur, la réussite ou la confiance en soi au moyen de recettes standardisées. Dans </t>
     </r>
@@ -1856,6 +1878,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">&lt;a href="https://www.youtube.com/watch?v=dV5r46P6yUU"  title="le développement personnel est la plus grosse arnaque par Clique Tv"&gt;</t>
     </r>
@@ -1865,6 +1888,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Le Développement (im)personnel &lt;/a&gt;, elle soutient que certaines formes de psychologie positive peuvent transformer des problèmes sociaux ou professionnels en responsabilités purement individuelles : si l’on échoue, ce serait parce que l’on n’est pas assez motivé ou « positif ». Sa critique ne consiste donc pas à refuser toute recherche de bien-être, mais à dénoncer les méthodes qui imposent une conformité sous l’apparence de l’épanouissement. &lt;/p&gt; &lt;p&gt; Sa philosophie peut être caractérisée par trois exigences : l’esprit critique, le discernement et l’authenticité. Elle invite chacun à se méfier des formules toutes faites, à ne pas confondre adaptation sociale et vérité personnelle, et à rechercher un rapport plus lucide à soi-même et aux autres. Son originalité tient ainsi à la rencontre entre la tradition philosophique — notamment Socrate, Aristote ou Kant — et les problèmes très concrets de la vie professionnelle et sociale. &lt;/p&gt; </t>
     </r>
@@ -1874,6 +1898,7 @@
         <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> &lt;audio controls title="Un nouvel ordre identitaire avec Julia Dez Funès par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.11.2022-ITEMA_23186791-2022F30378S0309-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
     </r>
@@ -2046,7 +2071,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2160,29 +2185,34 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2273,96 +2303,108 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2618,7 +2660,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -4568,86 +4610,87 @@
         <v>426</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="n">
+    <row r="59" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="18" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="G59" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="H59" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="I59" s="21"/>
+      <c r="J59" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="K59" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="L59" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8" t="n">
         <v>1968</v>
       </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8" t="n">
+      <c r="B60" s="8"/>
+      <c r="C60" s="8" t="n">
         <v>1968</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>431</v>
-      </c>
-      <c r="I59" s="10"/>
-      <c r="J59" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="L59" s="18" t="s">
+      <c r="D60" s="2" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="n">
-        <v>1969</v>
-      </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8" t="s">
+      <c r="E60" s="10" t="s">
         <v>434</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="F60" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="G60" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="H60" s="11" t="s">
         <v>437</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>439</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="2" t="s">
-        <v>286</v>
+        <v>121</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>438</v>
+      </c>
+      <c r="L60" s="23" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
         <v>1969</v>
       </c>
       <c r="B61" s="8"/>
       <c r="C61" s="8" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="13" t="s">
         <v>442</v>
       </c>
       <c r="F61" s="8" t="s">
@@ -4664,58 +4707,58 @@
         <v>286</v>
       </c>
       <c r="K61" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="L61" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="L61" s="16" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="62" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E62" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="F62" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="G62" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="F62" s="8" t="s">
+      <c r="H62" s="10" t="s">
         <v>451</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>453</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="2" t="s">
-        <v>166</v>
+        <v>286</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>452</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
         <v>1970</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="8" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="10" t="s">
         <v>456</v>
       </c>
       <c r="F63" s="8" t="s">
@@ -4729,124 +4772,124 @@
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="2" t="s">
-        <v>317</v>
+        <v>166</v>
       </c>
       <c r="K63" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="L63" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="L63" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="64" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B64" s="8"/>
       <c r="C64" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="D64" s="9" t="s">
+      <c r="F64" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="G64" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="H64" s="10" t="s">
         <v>465</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="H64" s="11" t="s">
-        <v>467</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="2" t="s">
-        <v>112</v>
+        <v>317</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>175</v>
+        <v>466</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="142.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B65" s="8"/>
       <c r="C65" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="D65" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="D65" s="9" t="s">
+      <c r="E65" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="F65" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="F65" s="8" t="s">
+      <c r="G65" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="H65" s="11" t="s">
         <v>473</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>474</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="2" t="s">
-        <v>234</v>
+        <v>112</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>446</v>
+        <v>175</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="174.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B66" s="8"/>
       <c r="C66" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="E66" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="F66" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="F66" s="8" t="s">
+      <c r="G66" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="G66" s="10" t="s">
+      <c r="H66" s="10" t="s">
         <v>480</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>481</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="2" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>122</v>
+        <v>452</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="174.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
         <v>1973</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>483</v>
@@ -4865,61 +4908,61 @@
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="2" t="s">
-        <v>317</v>
+        <v>166</v>
       </c>
       <c r="K67" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L67" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="L67" s="2" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="68" customFormat="false" ht="154.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
         <v>1973</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D68" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="E68" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="F68" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="G68" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="G68" s="10" t="s">
+      <c r="H68" s="10" t="s">
         <v>493</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>494</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="2" t="s">
-        <v>234</v>
+        <v>317</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>220</v>
+        <v>494</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
         <v>1973</v>
       </c>
       <c r="B69" s="8"/>
       <c r="C69" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="11" t="s">
         <v>497</v>
       </c>
       <c r="F69" s="8" t="s">
@@ -4933,61 +4976,61 @@
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="L69" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="K69" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="192" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="70" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="E70" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="D70" s="9" t="s">
+      <c r="F70" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="G70" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="H70" s="10" t="s">
         <v>506</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>508</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="2" t="s">
-        <v>112</v>
+        <v>507</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="141" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="192" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
         <v>1974</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="8" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="11" t="s">
         <v>511</v>
       </c>
       <c r="F71" s="8" t="s">
@@ -5001,22 +5044,22 @@
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="141" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
         <v>1974</v>
       </c>
       <c r="B72" s="8"/>
       <c r="C72" s="8" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>516</v>
@@ -5035,27 +5078,27 @@
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
         <v>1974</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="8" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="E73" s="19" t="s">
+      <c r="E73" s="10" t="s">
         <v>523</v>
       </c>
       <c r="F73" s="8" t="s">
@@ -5069,27 +5112,27 @@
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="2" t="s">
-        <v>234</v>
+        <v>112</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
         <v>1974</v>
       </c>
       <c r="B74" s="8"/>
       <c r="C74" s="8" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D74" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="E74" s="13" t="s">
+      <c r="E74" s="24" t="s">
         <v>529</v>
       </c>
       <c r="F74" s="8" t="s">
@@ -5103,163 +5146,163 @@
       </c>
       <c r="I74" s="10"/>
       <c r="J74" s="2" t="s">
-        <v>317</v>
+        <v>234</v>
       </c>
       <c r="K74" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L74" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="L74" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="75" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="E75" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="D75" s="9" t="s">
+      <c r="F75" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="G75" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="H75" s="10" t="s">
         <v>538</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>539</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>540</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="2" t="s">
-        <v>151</v>
+        <v>317</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>167</v>
+        <v>539</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="D76" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="D76" s="9" t="s">
+      <c r="E76" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="F76" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="G76" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="G76" s="10" t="s">
+      <c r="H76" s="10" t="s">
         <v>546</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>547</v>
       </c>
       <c r="I76" s="10"/>
       <c r="J76" s="2" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>548</v>
+        <v>167</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
         <v>1977</v>
       </c>
       <c r="B77" s="8"/>
       <c r="C77" s="8" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D77" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="E77" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="F77" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="G77" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="H77" s="10" t="s">
         <v>553</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>554</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="2" t="s">
-        <v>324</v>
+        <v>112</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>302</v>
+        <v>554</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="180.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="D78" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="D78" s="9" t="s">
+      <c r="E78" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="F78" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="G78" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="G78" s="10" t="s">
+      <c r="H78" s="10" t="s">
         <v>560</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>561</v>
       </c>
       <c r="I78" s="10"/>
       <c r="J78" s="2" t="s">
-        <v>121</v>
+        <v>324</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>198</v>
+        <v>302</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="283.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="180.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
         <v>1978</v>
       </c>
       <c r="B79" s="8"/>
-      <c r="C79" s="8" t="n">
-        <v>1978</v>
-      </c>
-      <c r="D79" s="2" t="s">
+      <c r="C79" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="D79" s="9" t="s">
         <v>563</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E79" s="11" t="s">
         <v>564</v>
       </c>
       <c r="F79" s="8" t="s">
@@ -5268,168 +5311,168 @@
       <c r="G79" s="10" t="s">
         <v>566</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="10" t="s">
         <v>567</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K79" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="L79" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="L79" s="2" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="395.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="80" customFormat="false" ht="283.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B80" s="8"/>
       <c r="C80" s="8" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E80" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="E80" s="20" t="s">
+      <c r="F80" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="F80" s="8" t="s">
+      <c r="G80" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="G80" s="10" t="s">
+      <c r="H80" s="11" t="s">
         <v>573</v>
-      </c>
-      <c r="H80" s="11" t="s">
-        <v>574</v>
       </c>
       <c r="I80" s="10"/>
       <c r="J80" s="2" t="s">
-        <v>234</v>
+        <v>112</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L80" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="L80" s="2" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="395.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B81" s="8"/>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="8" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="E81" s="25" t="s">
         <v>577</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="F81" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="F81" s="8" t="s">
+      <c r="G81" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="G81" s="10" t="s">
+      <c r="H81" s="11" t="s">
         <v>580</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>581</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="2" t="s">
-        <v>582</v>
+        <v>234</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>220</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B82" s="8"/>
       <c r="C82" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="E82" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="F82" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="G82" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="F82" s="8" t="s">
+      <c r="H82" s="10" t="s">
         <v>587</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>589</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="2" t="s">
-        <v>112</v>
+        <v>588</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>113</v>
+        <v>399</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="202.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B83" s="8"/>
       <c r="C83" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="D83" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="E83" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="F83" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="F83" s="8" t="s">
+      <c r="G83" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="G83" s="10" t="s">
+      <c r="H83" s="10" t="s">
         <v>595</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>596</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="n">
         <v>1983</v>
       </c>
       <c r="B84" s="8"/>
       <c r="C84" s="8" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="E84" s="10" t="s">
         <v>599</v>
       </c>
       <c r="F84" s="8" t="s">
@@ -5443,7 +5486,7 @@
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="2" t="s">
-        <v>234</v>
+        <v>121</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>129</v>
@@ -5452,18 +5495,18 @@
         <v>603</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="237.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B85" s="8"/>
-      <c r="C85" s="8" t="n">
-        <v>1985</v>
+      <c r="C85" s="8" t="s">
+        <v>597</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="E85" s="22" t="s">
+      <c r="E85" s="12" t="s">
         <v>605</v>
       </c>
       <c r="F85" s="8" t="s">
@@ -5472,7 +5515,7 @@
       <c r="G85" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H85" s="10" t="s">
         <v>608</v>
       </c>
       <c r="I85" s="10"/>
@@ -5480,76 +5523,110 @@
         <v>234</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="L85" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="L85" s="2" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="237.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B86" s="8"/>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="8" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>610</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="E86" s="25" t="s">
         <v>611</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="F86" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="F86" s="8" t="s">
+      <c r="G86" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="H86" s="11" t="s">
         <v>614</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>615</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="E87" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="I87" s="10"/>
+      <c r="J87" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="219.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
-        <v>1988</v>
-      </c>
-      <c r="C87" s="1" t="n">
-        <v>1988</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="E87" s="17" t="s">
-        <v>618</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="K87" s="2" t="s">
-        <v>113</v>
+        <v>574</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>622</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="219.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="n">
+        <v>1988</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E88" s="17" t="s">
+        <v>624</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>628</v>
       </c>
     </row>
   </sheetData>
@@ -5582,23 +5659,23 @@
     <hyperlink ref="H47" r:id="rId22" display="https://www.laphilo.fr/pho/paudi-mini.webp"/>
     <hyperlink ref="H48" r:id="rId23" display="https://www.laphilo.fr/pho/cmichon-mini.webp"/>
     <hyperlink ref="E55" r:id="rId24" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Corine_Pelluchon&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href=&quot;https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s&quot; title=&quot;NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco&quot;&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &#10;&lt;p&gt; - Manifeste animaliste. Politiser la cause animale ( 2017 )  - Éthique de la considération ( 2018) - Réparons le monde. Humains, animaux, nature (2020)  &#10; - Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &#10;&lt;p&gt; -   &lt;a href=&quot;https://www.youtube.com/watch?v=zpzzDqYhF-8&quot; title=&quot;Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat&quot;&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href=&quot;https://www.youtube.com/watch?v=tmk-UzN1j70&quot;  title=&quot;Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media&quot;&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title=&quot;Corine Pelluchon par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="H59" r:id="rId25" display="https://www.laphilo.fr/pho/cfmetterie-mini.webp"/>
-    <hyperlink ref="E61" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vincent_Delecroix&quot;  title=&quot; Wikipedia&quot;&gt;Vincent DELECROIX&lt;/a&gt;  est un philosophe français spécialiste de Kierkegaard et de la philosophie de la religion. Il enseigne à l’EPHE, où il travaille sur la vérité, la croyance et les liens entre religion et pensée contemporaine. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse d’abord à la manière dont la foi peut exister dans un monde moderne où les certitudes absolues se  &lt;a href=&quot;https://www.youtube.com/watch?v=2ZHOpP5GMwI&quot; title=&quot;Vincent DELECROIX,la nécessité d’apprendre par TV5 monde&quot;&gt;sont affaiblies. &lt;/a&gt; Il ne traite pas la religion comme un simple héritage figé, mais comme une expérience intérieure, fragile et exigeante.  &lt;/p&gt; &lt;p&gt; Un autre axe important chez lui est la révolte. À travers des livres comme Tombeau d’Achille et Non ! De l’esprit de révolte, il réfléchit à la colère, au refus et à la parole &lt;a href=&quot;https://www.youtube.com/watch?v=OiUgp6wLpCA&quot; title=&quot;Vincent DELECROIX il faut sortir du oui non par France Culture&quot;&gt;qui dit non, &lt;/a&gt; non comme de simples réactions, mais comme des forces qui révèlent une vérité humaine et morale. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il  est un philosophe de la tension entre vérité, foi et révolte. Sa pensée cherche à comprendre comment l’être humain peut garder une voix, une conscience et une exigence spirituelle dans un monde désorienté. &lt;/p&gt;  &lt;audio controls title=&quot;Vincent DELECROIX  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;"/>
-    <hyperlink ref="E63" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89douard_Mehl&quot;  title=&quot; Wikipedia&quot;&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href=&quot;https://www.youtube.com/watch?v=NT0n7tKNb3w&quot; title=&quot;qu’est ce que la verité par Le forum Veritas&quot;&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E64" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Barbara_Stiegler&quot; title=&quot; Wikipedia&quot;&gt;Barbara STEIGLER&lt;/a&gt;  est une philosophe française, fille du philosophe Bernard Stiegler, spécialiste de Nietzsche, de philosophie politique et critique du néolibéralisme. Agrégée de philosophie, elle soutient sa thèse en 2003 à Paris-Sorbonne sous la direction de Jean-Luc Marion sur Nietzsche et la biologie. Maître de conférences puis professeure à l'université Bordeaux-Montaigne depuis 2006, elle y dirige le master  &lt;a href=&quot;https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf&quot; title=&quot;Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne&quot;&gt;&quot;Soin, éthique et santé&quot;. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Engagée politiquement, elle analyse les Gilets Jaunes dans &quot;Du cap aux grèves&quot; paru en 2021 et critique l’adaptationnisme comme fondement du néolibéralisme, opposant une intelligence collective à l’élitisme technocratique. &lt;/p&gt; &lt;p&gt; Ses ouvrages sur Nietzsche explorent le corps et la vie (Nietzsche et la biologie, 2001 ; Nietzsche et la critique de la chair, 2005 ; Nietzsche et la vie, 2021). &lt;/p&gt; &lt;p&gt;  Elle étend ses recherches au politique avec  &lt;a href=&quot;https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/&quot; title=&quot;Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit&quot;&gt;&quot;Il faut s’adapter&quot; &lt;/a&gt; paru en  2019, dénonçant les racines évolutionnistes (Spencer, Lippmann) du &lt;a href=&quot;https://www.youtube.com/watch?v=oQQ4xqRvYTk&quot; style=&quot;color:#88A1E9&quot; title=&quot;LA LENTE AGONIE DU NÉOLIBÉRALISME  par &#10;TheSwissBox Conversation&quot;&gt;néolibéralisme &lt;/a&gt; face au pragmatisme démocratique de Dewey. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   "/>
-    <hyperlink ref="H64" r:id="rId29" display="https://www.laphilo.fr/pho/bastiegler-mini.webp"/>
-    <hyperlink ref="E66" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89ric_Sadin&quot;  title=&quot; Wikipedia&quot;&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href=&quot;https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur&quot; style=&quot;color:#88A1E9&quot;   title=&quot; Éric SADIN contre ChatGPT par Senseur&quot;&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;&#10;Sadin s'est fait connaître grâce à son livre &quot;La société de l'anticipation &quot; publié en 2011, dans lequel il examine l'émergence de la société de la surveillance et des technologies de prévision qui cherchent à anticiper les comportements et les désirs des individus. Il y aborde notamment les thèmes de la surveillance généralisée, de la collecte de données personnelles et des risques de manipulation. &lt;/p&gt; &lt;p&gt;&#10;Dans son ouvrage &lt;a href=&quot;https://christian-biales.fr/wp-content/uploads/2020/12/Sadin.pdf&quot;  title=&quot;Extrait du livre par Christian Bialès&quot;&gt; &quot;L'Ère de l'individu tyran : la fin d'un monde commun&quot;&lt;/a&gt; paru en 2013, Sadin explore les conséquences de la numérisation de la société sur les notions de vie privée, de liberté individuelle et de démocratie. Il met en garde contre le pouvoir croissant des grandes plateformes technologiques et la manière dont elles peuvent influencer et contrôler nos comportements et nos choix. &lt;/p&gt; &lt;p&gt;&#10;Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre &quot;La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique&quot; publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href=&quot;https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008&quot;  title=&quot;Dataïsme par lebigdata&quot;&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title=&quot;Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E67" r:id="rId31" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau&quot; title=&quot; Wikipedia&quot;&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href=&quot;https://www.youtube.com/watch?v=PNMZHr3L_Ws&quot; title=&quot; Vivons nous dans un multivers par Aurelien Barrau&quot;&gt; concept de multivers&lt;/a&gt; , et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage &quot;Chaos multiples&quot; et &quot;De la vérité dans les sciences&quot;  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé &quot;Météorites&quot;. &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de &quot;sauver le climat&quot; plutôt &quot;qu’agir pour la vie&quot;. &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  &quot;habiter la science en poète&quot; en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href=&quot;https://www.youtube.com/watch?v=94IxSYo5wtM&quot; title=&quot;Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter&quot;&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href=&quot;https://www.youtube.com/watch?v=g3Z_LsXD7DU&quot; title=&quot; L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac&quot;&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un &quot;faire monde&quot; éthique et conscient. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Aurelien BARRAU par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E68" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin&quot; title=&quot; Wikipedia&quot;&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href=&quot;https://charlespepin.fr/&quot;  title=&quot; Site officiel Charles Pépin &quot;&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href=&quot;https://www.youtube.com/watch?v=WExeoL6qVmc&quot; title=&quot; Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori&quot;&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href=&quot;https://www.youtube.com/watch?v=orOxuIHT_vc&quot; title=&quot;Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal&quot;&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt; - &quot;Les Vertus de l’échec&quot; publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt; - &quot;La Confiance en soi &quot; paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt; - &quot;La Rencontre&quot;  en 2021 et &quot;Vivre avec son passé&quot; en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href=&quot;https://www.youtube.com/watch?v=M09YmUzDwO8&quot; title=&quot; Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs&quot;&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; La philosophie selon Charles Pépin par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;"/>
-    <hyperlink ref="E70" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel&quot;  title=&quot; Wikipedia&quot;&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un &quot;philosophe de la liberté&quot;. Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que &quot;être de gauche&quot; signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;La privation de l’intime&quot; paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href=&quot;https://www.youtube.com/watch?v=HcDfUGypNvA&quot; style=&quot;color:#88A1E9&quot; title=&quot;Michaël Fœssel - Récidive, 1938 par Librairie mollat&quot;&gt;&quot;Récidive. 1938&quot;&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme &quot;laboratoire&quot; pour comprendre les fragilités  &lt;a href=&quot;https://www.youtube.com/watch?v=wdeS7SFEz7Y&quot;  title=&quot;Démocratie illibérale par Michaël Foessel par France Culture&quot;&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 &quot;Quartier rouge. Le plaisir et la gauche&quot;, il interroge le rapport de  &lt;a href=&quot;https://www.youtube.com/watch?v=MDubXJZox34&quot; title=&quot;Michaël Foessel : &quot;La question du plaisir est aujourd'hui centrale en politique&quot; par France Inter&quot;&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment &quot;Vers la paix perpétuelle&quot; et &quot;La religion dans les limites de la simple raison&quot;, tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title=&quot;La gauche : état des lieux  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E78" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Baptiste_Jeang%C3%A8ne_Vilmer&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Baptiste JEANGENE VILMER&lt;/a&gt;  est un philosophe, politologue et juriste français spécialiste de l’éthique de la guerre, du droit international et des relations internationales, et également diplomate (ambassadeur de France au Vanuatu depuis 2022). Il est formé dans trois disciplines : philosophie (licence, master, doctorat), droit (licence, LLM, postdoctorat) et science politique (doctorat). &lt;/p&gt; &lt;p&gt; Sa thèse porte sur &quot;l’intervention militaire justifiée par des raisons humanitaires&quot;, à la croisée de philosophie politique, droit international et théorie des relations internationales. Il défend en théorie des relations internationales un &quot;réalisme libéral&quot; inspiré de Raymond Aron, Stanley Hoffmann et Pierre Hassner : reconnaissance du tragique et des &lt;a href=&quot;https://www.youtube.com/watch?v=4EECHNFvt4Q&quot;  title=&quot; J-B. Jeangène Vilmer - Synthèse par Institut Guerre et Paix&quot;&gt;rapports de force, &lt;/a&gt;  mais attachée au droit international, aux droits humains et aux institutions. &lt;/p&gt; &lt;p&gt; Il se situe à l’intersection de philosophie morale, droit international et stratégie : penser les guerres et interventions non seulement en termes juridiques ou militaires, mais surtout en termes de responsabilité morale (tuer, laisser mourir, protéger). Son &lt;a href=&quot;https://www.jbjv.com/IMG/pdf/JB_Jeangene_Vilmer_2013_-_Pour_un_realisme_liberal_en_relations_internationales.pdf&quot;  title=&quot;Pour un réalisme libéral en relations internationales par jbjv&quot;&gt;&quot;réalisme libéral&quot; &lt;/a&gt; refuse à la fois le cynisme réaliste pur et l’idéalisme naïf, il cherche des critères prudents mais exigeants pour juger les interventions, la justice pénale, ou la responsabilité des États. &lt;/p&gt; &lt;p&gt; Il insiste sur les dilemmes : parfois, intervenir violemment peut sauver des vies, mais peut aussi aggraver le conflit ; parfois, poursuivre les criminels peut fragiliser la paix. Sa pensée explore ces tensions plutôt que de proposer des solutions simplistes. &lt;/p&gt; &#10;&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   &#10;"/>
-    <hyperlink ref="H79" r:id="rId35" display="https://www.laphilo.fr/pho/nykisukidi-mini.webp"/>
-    <hyperlink ref="H80" r:id="rId36" display="https://www.laphilo.fr/pho/jdfunes-mini.webp"/>
-    <hyperlink ref="E81" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tristan_Garcia&quot; title=&quot; Wikipedia&quot;&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. &lt;/p&gt; &lt;p&gt; Son œuvre majeure &quot;Forme et objet. Un traité des choses&quot; paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie &quot;plate&quot; qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans &quot;Nous&quot; ou &quot;La Vie intense&quot; paru en 2016, il explore l’appartenance à des collectifs variables &quot;nous humains&quot;, &quot;nous animaux&quot; et critique l’obsession moderne pour  &lt;a href=&quot;https://www.youtube.com/watch?v=JTLVzryyyEg&quot; title=&quot;Tristan Garcia, INTENSITÉ par abc penser&quot;&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (La Meilleure part des hommes, sur le sida) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href=&quot;https://www.youtube.com/watch?v=K_wxi5xTYz8&quot; title=&quot;Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace&quot;&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; &#10; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Tristan Garcia, &quot;La vie intense : une obsession moderne&quot; par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10; "/>
-    <hyperlink ref="E84" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Baptiste_Morizot&quot;  title=&quot; Wikipedia&quot;&gt;Baptiste MORIZOT&lt;/a&gt;  est un philosophe français,  maître de conférences à l'université d'Aix-Marseille, dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle. Son approche se distingue par une pratique de terrain ancrée dans l'expérience, notamment le pistage des grands prédateurs comme les loups, ce qui lui permet de nourrir sa pensée philosophique par une observation directe et sensible du vivant.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve l'idée que la crise écologique contemporaine est avant tout une « crise de la sensibilité » et de nos relations avec le reste du monde vivant. Il soutient que la pensée moderne, marquée par un dualisme qui sépare strictement l'humain de la nature, nous a &lt;a href=&quot;https://www.youtube.com/watch?v=bAnXnPnnHCk&quot; title=&quot;Baptiste Morizot, meme penseur on est un animal par France Inter&quot;&gt;rendus aveugles et sourds &lt;/a&gt; aux autres espèces, qu'il préfère considérer comme d'autres « manières d'être vivant » plutôt que comme des êtres inférieurs. &lt;/p&gt; &lt;p&gt; Il propose ainsi de remplacer le modèle classique de la « maîtrise de la nature » par une « diplomatie des interdépendances ». Cette approche invite les humains à se concevoir comme des partenaires au sein d'un réseau complexe d'interdépendances, où il s'agit de tisser des alliances concrètes, de prêter attention aux signaux émis par les autres espèces et d'apprendre à cohabiter avec elles dans un esprit de respect et de responsabilité partagée. &lt;/p&gt; &lt;p&gt; Son travail, qui mêle récit, enquête éthologique et essai théorique, cherche à réenchanter &lt;a href=&quot;https://www.youtube.com/watch?v=uQZcktq_W3E&quot; title=&quot;Baptiste Morizot, remet l’humain à sa place par La Grande Librairie&quot;&gt;notre rapport au monde &lt;/a&gt; en réactivant nos capacités d'attention et d'intelligence sensible. En invitant à une forme de sagesse pragmatique et ancrée, il s'efforce de refonder notre culture environnementale, non pas pour dominer ou sanctuariser la nature, mais pour s'ajuster avec humilité à la diversité des formes de vie qui partagent la Terre avec nous. &lt;/p&gt;  &lt;audio controls title=&quot;Liberté, dignité, habitalité avec baptiste MORIZOT par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18558-25.04.2026-ITEMA_24488881-2026F30378S0115-NET_MFI_D6CADDF4-ADD5-4D3F-AA1D-625272E9CD3C-22-b98aedea0426383b486dc3819cb77a8e.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;"/>
-    <hyperlink ref="H85" r:id="rId39" display="https://www.laphilo.fr/pho/ydallaglio-mini.webp"/>
-    <hyperlink ref="E86" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Norman_Ajari&quot;  title=&quot; Wikipedia&quot;&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href=&quot;https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari&quot;  title=&quot;Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse&quot;&gt;&quot;études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href=&quot;https://www.youtube.com/watch?v=IMUBi9oi2WM&quot; title=&quot;Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche&quot;&gt;&quot;colonialité de l’être&quot; &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=ECSmpOXY8kg&quot; title=&quot;NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS&quot;&gt;&quot;La Dignité ou la mort&quot;, &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de &quot;philosophe militant&quot; : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. &lt;/p&gt; &lt;audio controls title=&quot;où commence et où finit le racisme? par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;"/>
-    <hyperlink ref="H87" r:id="rId41" display="https://www.laphilo.fr/pho/mmaeso-mini.webp"/>
+    <hyperlink ref="H60" r:id="rId25" display="https://www.laphilo.fr/pho/cfmetterie-mini.webp"/>
+    <hyperlink ref="E62" r:id="rId26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vincent_Delecroix&quot;  title=&quot; Wikipedia&quot;&gt;Vincent DELECROIX&lt;/a&gt;  est un philosophe français spécialiste de Kierkegaard et de la philosophie de la religion. Il enseigne à l’EPHE, où il travaille sur la vérité, la croyance et les liens entre religion et pensée contemporaine. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse d’abord à la manière dont la foi peut exister dans un monde moderne où les certitudes absolues se  &lt;a href=&quot;https://www.youtube.com/watch?v=2ZHOpP5GMwI&quot; title=&quot;Vincent DELECROIX,la nécessité d’apprendre par TV5 monde&quot;&gt;sont affaiblies. &lt;/a&gt; Il ne traite pas la religion comme un simple héritage figé, mais comme une expérience intérieure, fragile et exigeante.  &lt;/p&gt; &lt;p&gt; Un autre axe important chez lui est la révolte. À travers des livres comme Tombeau d’Achille et Non ! De l’esprit de révolte, il réfléchit à la colère, au refus et à la parole &lt;a href=&quot;https://www.youtube.com/watch?v=OiUgp6wLpCA&quot; title=&quot;Vincent DELECROIX il faut sortir du oui non par France Culture&quot;&gt;qui dit non, &lt;/a&gt; non comme de simples réactions, mais comme des forces qui révèlent une vérité humaine et morale. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il  est un philosophe de la tension entre vérité, foi et révolte. Sa pensée cherche à comprendre comment l’être humain peut garder une voix, une conscience et une exigence spirituelle dans un monde désorienté. &lt;/p&gt;  &lt;audio controls title=&quot;Vincent DELECROIX  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;"/>
+    <hyperlink ref="E64" r:id="rId27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89douard_Mehl&quot;  title=&quot; Wikipedia&quot;&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href=&quot;https://www.youtube.com/watch?v=NT0n7tKNb3w&quot; title=&quot;qu’est ce que la verité par Le forum Veritas&quot;&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E65" r:id="rId28" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Barbara_Stiegler&quot; title=&quot; Wikipedia&quot;&gt;Barbara STEIGLER&lt;/a&gt;  est une philosophe française, fille du philosophe Bernard Stiegler, spécialiste de Nietzsche, de philosophie politique et critique du néolibéralisme. Agrégée de philosophie, elle soutient sa thèse en 2003 à Paris-Sorbonne sous la direction de Jean-Luc Marion sur Nietzsche et la biologie. Maître de conférences puis professeure à l'université Bordeaux-Montaigne depuis 2006, elle y dirige le master  &lt;a href=&quot;https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf&quot; title=&quot;Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne&quot;&gt;&quot;Soin, éthique et santé&quot;. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Engagée politiquement, elle analyse les Gilets Jaunes dans &quot;Du cap aux grèves&quot; paru en 2021 et critique l’adaptationnisme comme fondement du néolibéralisme, opposant une intelligence collective à l’élitisme technocratique. &lt;/p&gt; &lt;p&gt; Ses ouvrages sur Nietzsche explorent le corps et la vie (Nietzsche et la biologie, 2001 ; Nietzsche et la critique de la chair, 2005 ; Nietzsche et la vie, 2021). &lt;/p&gt; &lt;p&gt;  Elle étend ses recherches au politique avec  &lt;a href=&quot;https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/&quot; title=&quot;Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit&quot;&gt;&quot;Il faut s’adapter&quot; &lt;/a&gt; paru en  2019, dénonçant les racines évolutionnistes (Spencer, Lippmann) du &lt;a href=&quot;https://www.youtube.com/watch?v=oQQ4xqRvYTk&quot; style=&quot;color:#88A1E9&quot; title=&quot;LA LENTE AGONIE DU NÉOLIBÉRALISME  par &#10;TheSwissBox Conversation&quot;&gt;néolibéralisme &lt;/a&gt; face au pragmatisme démocratique de Dewey. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   "/>
+    <hyperlink ref="H65" r:id="rId29" display="https://www.laphilo.fr/pho/bastiegler-mini.webp"/>
+    <hyperlink ref="E67" r:id="rId30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89ric_Sadin&quot;  title=&quot; Wikipedia&quot;&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href=&quot;https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur&quot; style=&quot;color:#88A1E9&quot;   title=&quot; Éric SADIN contre ChatGPT par Senseur&quot;&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;&#10;Sadin s'est fait connaître grâce à son livre &quot;La société de l'anticipation &quot; publié en 2011, dans lequel il examine l'émergence de la société de la surveillance et des technologies de prévision qui cherchent à anticiper les comportements et les désirs des individus. Il y aborde notamment les thèmes de la surveillance généralisée, de la collecte de données personnelles et des risques de manipulation. &lt;/p&gt; &lt;p&gt;&#10;Dans son ouvrage &lt;a href=&quot;https://christian-biales.fr/wp-content/uploads/2020/12/Sadin.pdf&quot;  title=&quot;Extrait du livre par Christian Bialès&quot;&gt; &quot;L'Ère de l'individu tyran : la fin d'un monde commun&quot;&lt;/a&gt; paru en 2013, Sadin explore les conséquences de la numérisation de la société sur les notions de vie privée, de liberté individuelle et de démocratie. Il met en garde contre le pouvoir croissant des grandes plateformes technologiques et la manière dont elles peuvent influencer et contrôler nos comportements et nos choix. &lt;/p&gt; &lt;p&gt;&#10;Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre &quot;La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique&quot; publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href=&quot;https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008&quot;  title=&quot;Dataïsme par lebigdata&quot;&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title=&quot;Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E68" r:id="rId31" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau&quot; title=&quot; Wikipedia&quot;&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href=&quot;https://www.youtube.com/watch?v=PNMZHr3L_Ws&quot; title=&quot; Vivons nous dans un multivers par Aurelien Barrau&quot;&gt; concept de multivers&lt;/a&gt; , et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage &quot;Chaos multiples&quot; et &quot;De la vérité dans les sciences&quot;  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé &quot;Météorites&quot;. &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de &quot;sauver le climat&quot; plutôt &quot;qu’agir pour la vie&quot;. &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  &quot;habiter la science en poète&quot; en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href=&quot;https://www.youtube.com/watch?v=94IxSYo5wtM&quot; title=&quot;Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter&quot;&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href=&quot;https://www.youtube.com/watch?v=g3Z_LsXD7DU&quot; title=&quot; L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac&quot;&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un &quot;faire monde&quot; éthique et conscient. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Aurelien BARRAU par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E69" r:id="rId32" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin&quot; title=&quot; Wikipedia&quot;&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href=&quot;https://charlespepin.fr/&quot;  title=&quot; Site officiel Charles Pépin &quot;&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href=&quot;https://www.youtube.com/watch?v=WExeoL6qVmc&quot; title=&quot; Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori&quot;&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href=&quot;https://www.youtube.com/watch?v=orOxuIHT_vc&quot; title=&quot;Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal&quot;&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt; - &quot;Les Vertus de l’échec&quot; publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt; - &quot;La Confiance en soi &quot; paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt; - &quot;La Rencontre&quot;  en 2021 et &quot;Vivre avec son passé&quot; en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href=&quot;https://www.youtube.com/watch?v=M09YmUzDwO8&quot; title=&quot; Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs&quot;&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; La philosophie selon Charles Pépin par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;"/>
+    <hyperlink ref="E71" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel&quot;  title=&quot; Wikipedia&quot;&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un &quot;philosophe de la liberté&quot;. Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que &quot;être de gauche&quot; signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;La privation de l’intime&quot; paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href=&quot;https://www.youtube.com/watch?v=HcDfUGypNvA&quot; style=&quot;color:#88A1E9&quot; title=&quot;Michaël Fœssel - Récidive, 1938 par Librairie mollat&quot;&gt;&quot;Récidive. 1938&quot;&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme &quot;laboratoire&quot; pour comprendre les fragilités  &lt;a href=&quot;https://www.youtube.com/watch?v=wdeS7SFEz7Y&quot;  title=&quot;Démocratie illibérale par Michaël Foessel par France Culture&quot;&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 &quot;Quartier rouge. Le plaisir et la gauche&quot;, il interroge le rapport de  &lt;a href=&quot;https://www.youtube.com/watch?v=MDubXJZox34&quot; title=&quot;Michaël Foessel : &quot;La question du plaisir est aujourd'hui centrale en politique&quot; par France Inter&quot;&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment &quot;Vers la paix perpétuelle&quot; et &quot;La religion dans les limites de la simple raison&quot;, tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title=&quot;La gauche : état des lieux  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E79" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Baptiste_Jeang%C3%A8ne_Vilmer&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Baptiste JEANGENE VILMER&lt;/a&gt;  est un philosophe, politologue et juriste français spécialiste de l’éthique de la guerre, du droit international et des relations internationales, et également diplomate (ambassadeur de France au Vanuatu depuis 2022). Il est formé dans trois disciplines : philosophie (licence, master, doctorat), droit (licence, LLM, postdoctorat) et science politique (doctorat). &lt;/p&gt; &lt;p&gt; Sa thèse porte sur &quot;l’intervention militaire justifiée par des raisons humanitaires&quot;, à la croisée de philosophie politique, droit international et théorie des relations internationales. Il défend en théorie des relations internationales un &quot;réalisme libéral&quot; inspiré de Raymond Aron, Stanley Hoffmann et Pierre Hassner : reconnaissance du tragique et des &lt;a href=&quot;https://www.youtube.com/watch?v=4EECHNFvt4Q&quot;  title=&quot; J-B. Jeangène Vilmer - Synthèse par Institut Guerre et Paix&quot;&gt;rapports de force, &lt;/a&gt;  mais attachée au droit international, aux droits humains et aux institutions. &lt;/p&gt; &lt;p&gt; Il se situe à l’intersection de philosophie morale, droit international et stratégie : penser les guerres et interventions non seulement en termes juridiques ou militaires, mais surtout en termes de responsabilité morale (tuer, laisser mourir, protéger). Son &lt;a href=&quot;https://www.jbjv.com/IMG/pdf/JB_Jeangene_Vilmer_2013_-_Pour_un_realisme_liberal_en_relations_internationales.pdf&quot;  title=&quot;Pour un réalisme libéral en relations internationales par jbjv&quot;&gt;&quot;réalisme libéral&quot; &lt;/a&gt; refuse à la fois le cynisme réaliste pur et l’idéalisme naïf, il cherche des critères prudents mais exigeants pour juger les interventions, la justice pénale, ou la responsabilité des États. &lt;/p&gt; &lt;p&gt; Il insiste sur les dilemmes : parfois, intervenir violemment peut sauver des vies, mais peut aussi aggraver le conflit ; parfois, poursuivre les criminels peut fragiliser la paix. Sa pensée explore ces tensions plutôt que de proposer des solutions simplistes. &lt;/p&gt; &#10;&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   &#10;"/>
+    <hyperlink ref="H80" r:id="rId35" display="https://www.laphilo.fr/pho/nykisukidi-mini.webp"/>
+    <hyperlink ref="H81" r:id="rId36" display="https://www.laphilo.fr/pho/jdfunes-mini.webp"/>
+    <hyperlink ref="E82" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tristan_Garcia&quot; title=&quot; Wikipedia&quot;&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. &lt;/p&gt; &lt;p&gt; Son œuvre majeure &quot;Forme et objet. Un traité des choses&quot; paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie &quot;plate&quot; qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans &quot;Nous&quot; ou &quot;La Vie intense&quot; paru en 2016, il explore l’appartenance à des collectifs variables &quot;nous humains&quot;, &quot;nous animaux&quot; et critique l’obsession moderne pour  &lt;a href=&quot;https://www.youtube.com/watch?v=JTLVzryyyEg&quot; title=&quot;Tristan Garcia, INTENSITÉ par abc penser&quot;&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (La Meilleure part des hommes, sur le sida) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href=&quot;https://www.youtube.com/watch?v=K_wxi5xTYz8&quot; title=&quot;Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace&quot;&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; &#10; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Tristan Garcia, &quot;La vie intense : une obsession moderne&quot; par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10; "/>
+    <hyperlink ref="E85" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Baptiste_Morizot&quot;  title=&quot; Wikipedia&quot;&gt;Baptiste MORIZOT&lt;/a&gt;  est un philosophe français,  maître de conférences à l'université d'Aix-Marseille, dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle. Son approche se distingue par une pratique de terrain ancrée dans l'expérience, notamment le pistage des grands prédateurs comme les loups, ce qui lui permet de nourrir sa pensée philosophique par une observation directe et sensible du vivant.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve l'idée que la crise écologique contemporaine est avant tout une « crise de la sensibilité » et de nos relations avec le reste du monde vivant. Il soutient que la pensée moderne, marquée par un dualisme qui sépare strictement l'humain de la nature, nous a &lt;a href=&quot;https://www.youtube.com/watch?v=bAnXnPnnHCk&quot; title=&quot;Baptiste Morizot, meme penseur on est un animal par France Inter&quot;&gt;rendus aveugles et sourds &lt;/a&gt; aux autres espèces, qu'il préfère considérer comme d'autres « manières d'être vivant » plutôt que comme des êtres inférieurs. &lt;/p&gt; &lt;p&gt; Il propose ainsi de remplacer le modèle classique de la « maîtrise de la nature » par une « diplomatie des interdépendances ». Cette approche invite les humains à se concevoir comme des partenaires au sein d'un réseau complexe d'interdépendances, où il s'agit de tisser des alliances concrètes, de prêter attention aux signaux émis par les autres espèces et d'apprendre à cohabiter avec elles dans un esprit de respect et de responsabilité partagée. &lt;/p&gt; &lt;p&gt; Son travail, qui mêle récit, enquête éthologique et essai théorique, cherche à réenchanter &lt;a href=&quot;https://www.youtube.com/watch?v=uQZcktq_W3E&quot; title=&quot;Baptiste Morizot, remet l’humain à sa place par La Grande Librairie&quot;&gt;notre rapport au monde &lt;/a&gt; en réactivant nos capacités d'attention et d'intelligence sensible. En invitant à une forme de sagesse pragmatique et ancrée, il s'efforce de refonder notre culture environnementale, non pas pour dominer ou sanctuariser la nature, mais pour s'ajuster avec humilité à la diversité des formes de vie qui partagent la Terre avec nous. &lt;/p&gt;  &lt;audio controls title=&quot;Liberté, dignité, habitalité avec baptiste MORIZOT par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18558-25.04.2026-ITEMA_24488881-2026F30378S0115-NET_MFI_D6CADDF4-ADD5-4D3F-AA1D-625272E9CD3C-22-b98aedea0426383b486dc3819cb77a8e.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;"/>
+    <hyperlink ref="H86" r:id="rId39" display="https://www.laphilo.fr/pho/ydallaglio-mini.webp"/>
+    <hyperlink ref="E87" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Norman_Ajari&quot;  title=&quot; Wikipedia&quot;&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href=&quot;https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari&quot;  title=&quot;Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse&quot;&gt;&quot;études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href=&quot;https://www.youtube.com/watch?v=IMUBi9oi2WM&quot; title=&quot;Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche&quot;&gt;&quot;colonialité de l’être&quot; &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=ECSmpOXY8kg&quot; title=&quot;NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS&quot;&gt;&quot;La Dignité ou la mort&quot;, &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de &quot;philosophe militant&quot; : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. &lt;/p&gt; &lt;audio controls title=&quot;où commence et où finit le racisme? par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;"/>
+    <hyperlink ref="H88" r:id="rId41" display="https://www.laphilo.fr/pho/mmaeso-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -735,6 +735,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="M3" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="221.25" customHeight="1" s="28">
       <c r="A4" s="34" t="n">
@@ -898,6 +903,11 @@
           <t>philosophe française spécialiste de la philosophie juive médiévale.</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="157.5" customHeight="1" s="28">
       <c r="A7" s="34" t="n">
@@ -1363,6 +1373,11 @@
       <c r="L15" s="27" t="inlineStr">
         <is>
           <t>philosophe française spécialisée en philosophie politique et en histoire des idées.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>
@@ -2159,6 +2174,11 @@
       <c r="L30" s="27" t="inlineStr">
         <is>
           <t>philosophe juif français qui enseigna avant de se consacrer à l'écriture et aux médias.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -740,6 +740,16 @@
           <t xml:space="preserve">Traditions</t>
         </is>
       </c>
+      <c r="N3" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Groupe</t>
+        </is>
+      </c>
+      <c r="O3" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importance</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="221.25" customHeight="1" s="28">
       <c r="A4" s="34" t="n">
@@ -793,6 +803,11 @@
       <c r="L4" s="27" t="inlineStr">
         <is>
           <t>philosophe français lauréat du grand prix de philosophie de l'Académie française en 2001.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -851,6 +866,11 @@
           <t>philosophe français spécialiste du symbolisme religieux, la gnose, l'ésotérisme.</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="126.75" customHeight="1" s="28">
       <c r="A6" s="34" t="n">
@@ -908,6 +928,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="157.5" customHeight="1" s="28">
       <c r="A7" s="34" t="n">
@@ -960,6 +985,11 @@
           <t>philosophe français d'inspiration Marxiste.</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="159" customHeight="1" s="28">
       <c r="A8" s="34" t="n">
@@ -1009,6 +1039,11 @@
           <t>philosophe française, historienne de la philosophie et traductrice.</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="152.25" customHeight="1" s="28">
       <c r="A9" s="34" t="n">
@@ -1061,6 +1096,11 @@
           <t>philosophe français figure du marxisme structuraliste et de la théorie littéraire.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="165.75" customHeight="1" s="28">
       <c r="A10" s="34" t="n">
@@ -1113,6 +1153,11 @@
           <t>philosophe française à la croisée de la médecine, la philosophie et les sciences du vivant.</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="147.75" customHeight="1" s="28">
       <c r="A11" s="34" t="n">
@@ -1166,6 +1211,11 @@
           <t>philosophe français travaillant principalement sur l'émancipation intellectuelle des dominés.</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="147.75" customHeight="1" s="28">
       <c r="A12" s="34" t="n">
@@ -1217,6 +1267,11 @@
           <t>philosophe et écrivain français dont le parcours a été marqué par l’engagement politique.</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="199.5" customHeight="1" s="28">
       <c r="A13" s="34" t="n">
@@ -1270,6 +1325,11 @@
           <t>philosophe française figure du post‑structuralisme français à partir des années 1960.</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="178.5" customHeight="1" s="28">
       <c r="A14" s="34" t="n">
@@ -1322,6 +1382,11 @@
           <t>philosophe français connu pour ses positions sur les frontières et les droits de l'homme.</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="147.75" customHeight="1" s="28">
       <c r="A15" s="34" t="n">
@@ -1378,6 +1443,11 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -1436,6 +1506,11 @@
           <t>philosophe français qui fait partie du mouvement post-modernisme.</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="168" customHeight="1" s="28">
       <c r="A17" s="34" t="n">
@@ -1489,6 +1564,11 @@
           <t>philosophe française spécialiste de Montesquieu &amp;amp; de l'éthique de l'environnement.</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="157.5" customHeight="1" s="28">
       <c r="A18" s="34" t="n">
@@ -1542,6 +1622,11 @@
           <t>philosophe français engagé pour la cause écologique, la cause des femmes &amp;amp; de l'immigration.</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="178.5" customHeight="1" s="28">
       <c r="A19" s="34" t="n">
@@ -1595,6 +1680,11 @@
           <t>philosophe français spécialiste de l'empirisme britannique &amp;amp; théoricien de la culture contemporaine.</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="156.75" customHeight="1" s="28">
       <c r="A20" s="34" t="n">
@@ -1647,6 +1737,11 @@
           <t>philosophe français spécialiste de la philosophie moderne.</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="147.75" customHeight="1" s="28">
       <c r="A21" s="34" t="n">
@@ -1699,6 +1794,11 @@
           <t>philosophe français qui se définit comme le "phénoménologiste de la donation".</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="168" customHeight="1" s="28">
       <c r="A22" s="34" t="n">
@@ -1753,6 +1853,11 @@
           <t>philosophe français connu pour ses travaux sur la religion, les droits de l'homme &amp;amp; la démocratie.</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="193.5" customHeight="1" s="28">
       <c r="A23" s="34" t="n">
@@ -1806,6 +1911,11 @@
           <t>philosophe français du langage, de la sémiologie et de la philosophie politique.</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="189" customHeight="1" s="28">
       <c r="A24" s="34" t="n">
@@ -1859,6 +1969,11 @@
           <t>philosophe française spécialiste des Grecs anciens.</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="147.75" customHeight="1" s="28">
       <c r="A25" s="34" t="n">
@@ -1911,6 +2026,14 @@
           <t>philosophe français critique de l'auto-flagellation occidentale et du tiers-mondisme culpabilisant.</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O25">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" ht="178.5" customHeight="1" s="28">
       <c r="A26" s="34" t="n">
@@ -1965,6 +2088,11 @@
           <t>philosophe française auteure d'essais sur la morale et la politique contemporaines.</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="210.75" customHeight="1" s="28">
       <c r="A27" s="34" t="n">
@@ -2017,6 +2145,11 @@
           <t>philosophe français spécialiste de la pensée islamique et en particulier le chiisme.</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="158.25" customHeight="1" s="28">
       <c r="A28" s="34" t="n">
@@ -2070,6 +2203,11 @@
           <t>philosophe française et historienne des sciences.</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="188.25" customHeight="1" s="28">
       <c r="A29" s="34" t="n">
@@ -2123,6 +2261,11 @@
           <t>philosophe français connu pour son monumental travail "La Totalité" en sept volumes.</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="157.5" customHeight="1" s="28">
       <c r="A30" s="34" t="n">
@@ -2181,6 +2324,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="222" customHeight="1" s="28">
       <c r="A31" s="34" t="n">
@@ -2233,6 +2381,11 @@
           <t>philosophe français qui cherche par ses livres à rendre la philosophie accessible à un large public.</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="245.25" customHeight="1" s="28">
       <c r="A32" s="34" t="n">
@@ -2284,6 +2437,11 @@
           <t xml:space="preserve"> anthropologue français spécialiste de l’Amazonie.</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="210" customHeight="1" s="28">
       <c r="A33" s="34" t="n">
@@ -2337,6 +2495,11 @@
           <t>philosophe français socialiste libertaire connu pour ses positions engagées.</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="147.75" customHeight="1" s="28">
       <c r="A34" s="34" t="n">
@@ -2391,6 +2554,11 @@
           <t>philosophe français du droit &amp;amp; de la politique en réflexion de Kant &amp;amp; Hegel.</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="126.75" customHeight="1" s="28">
       <c r="A35" s="34" t="n">
@@ -2446,6 +2614,11 @@
           <t>philosophe français qui analyse la philosophie à partir des langues &amp;amp; pensées grecque et chinoise.</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="137.25" customHeight="1" s="28">
       <c r="A36" s="34" t="n">
@@ -2500,6 +2673,14 @@
           <t>philosophe français matérialiste, rationaliste et humaniste.</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O36">
+        <v>2</v>
+      </c>
     </row>
     <row r="37" ht="95.25" customHeight="1" s="28">
       <c r="A37" s="34" t="n">
@@ -2554,6 +2735,11 @@
           <t>philosophe &amp;amp; historien de l'art français auteur de plus de cinquante ouvrages.</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="157.5" customHeight="1" s="28">
       <c r="A38" s="34" t="n">
@@ -2607,6 +2793,11 @@
           <t>philosophe français spécialiste en éthique et philosophie morale.</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="126.75" customHeight="1" s="28">
       <c r="A39" s="34" t="n">
@@ -2660,6 +2851,14 @@
           <t>philosophe français spécialiste de la philosophie du langage, de la logique et la connaissance.</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O39">
+        <v>3</v>
+      </c>
     </row>
     <row r="40" ht="162" customHeight="1" s="28">
       <c r="A40" s="34" t="n">
@@ -2710,6 +2909,11 @@
       <c r="L40" s="27" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de Derrida et de Spinoza.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -2767,6 +2971,11 @@
           <t>philosophe français connu pour son engagement pour l'Athéisme et l'Anarchisme.</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="126.75" customHeight="1" s="28">
       <c r="A42" s="34" t="n">
@@ -2819,6 +3028,11 @@
           <t>philosophe français travaillant sur l'idéalisme allemand &amp;amp; la philosophie française du XXème.</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="191" customHeight="1" s="28">
       <c r="A43" s="34" t="n">
@@ -2870,6 +3084,11 @@
           <t>philosophe française spécialiste du langage, de la morale et de philosophie politique.</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="202.95" customHeight="1" s="28">
       <c r="A44" s="34" t="n">
@@ -2924,6 +3143,11 @@
           <t>philosophe française menant une réflexion philosophique et sociologique sur la place du travail.</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="189.75" customHeight="1" s="28">
       <c r="A45" s="34" t="n">
@@ -2976,6 +3200,11 @@
           <t>philosophe française spécialiste de la cause animale et des droits des animaux.</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="147.75" customHeight="1" s="28">
       <c r="A46" s="34" t="n">
@@ -3029,6 +3258,11 @@
           <t>philosophe français de la morale et de la politique, notamment de la violence, des langues et des communautés.</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="261.75" customHeight="1" s="28">
       <c r="A47" s="34" t="n">
@@ -3081,6 +3315,11 @@
           <t>philosophe français  centré sur les relations entre l'éthique et l'esthétique en Occident.</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="261.75" customHeight="1" s="28">
       <c r="A48" s="34" t="n">
@@ -3132,6 +3371,11 @@
           <t>philosophe français spécialiste de la philosophie médiévale, de la métaphysique et la philosophie de l’action.</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="207.75" customHeight="1" s="28">
       <c r="A49" s="34" t="n">
@@ -3185,6 +3429,11 @@
           <t>philosophe français historien de la philosophie &amp;amp; spécialiste de l'œuvre d'Henri Bergson.</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="116.25" customHeight="1" s="28">
       <c r="A50" s="34" t="n">
@@ -3239,6 +3488,11 @@
           <t>philosophe française spécialisée en esthétique, philosophie morale et politique et théorie féministe.</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="126.75" customHeight="1" s="28">
       <c r="A51" s="34" t="n">
@@ -3292,6 +3546,11 @@
           <t>philosophe français connu pour ses travaux en philosophie politique et en histoire des idées.</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="147.75" customHeight="1" s="28">
       <c r="A52" s="34" t="n">
@@ -3343,6 +3602,11 @@
       <c r="L52" s="27" t="inlineStr">
         <is>
           <t>philosophe française spécialiste des pensées française &amp;amp; italienne contemporaines.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -3400,6 +3664,11 @@
           <t>philosophe français qui s'interroge sur les normes dans leur dimension vitale et sociale.</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="219.75" customHeight="1" s="28">
       <c r="A54" s="34" t="n">
@@ -3450,6 +3719,11 @@
       <c r="L54" s="27" t="inlineStr">
         <is>
           <t>philosophe français qui a contribué à la formation du réalisme spéculatif.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -3507,6 +3781,11 @@
           <t>philosophe française qui s'intéresse aux questions d'éthique et de philosophie morale et politique.</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="162" customHeight="1" s="28">
       <c r="A56" s="34" t="n">
@@ -3559,6 +3838,11 @@
           <t>philosophe français spécialiste du cartésianisme et de la philosophie des religions.</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="126.75" customHeight="1" s="28">
       <c r="A57" s="34" t="n">
@@ -3611,6 +3895,11 @@
           <t>philosophe français spécialiste de la philosophie sociale &amp;amp; politique.</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="150" customHeight="1" s="28">
       <c r="A58" s="34" t="n">
@@ -3663,6 +3952,11 @@
           <t>philosophe français promoteur de la philosophie sociale en France &amp;amp; de l'épistémologie hégélienne.</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="150" customHeight="1" s="28">
       <c r="A59" s="44" t="n">
@@ -3717,6 +4011,11 @@
         </is>
       </c>
       <c r="M59" s="27" t="n"/>
+      <c r="N59" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="167.25" customHeight="1" s="28">
       <c r="A60" s="34" t="n">
@@ -3769,6 +4068,11 @@
 </t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="123.75" customHeight="1" s="28">
       <c r="A61" s="34" t="n">
@@ -3822,6 +4126,11 @@
           <t>philosophe française spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle.</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="126.75" customHeight="1" s="28">
       <c r="A62" s="34" t="n">
@@ -3873,6 +4182,11 @@
       <c r="L62" s="42" t="inlineStr">
         <is>
           <t>philosophe et écrivain français, spécialiste de Kierkegaard et de philosophie de la religion.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -3930,6 +4244,11 @@
           <t>philosophe français spécialiste de philosophie allemande contemporaine et de philosophie politique.</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="116.25" customHeight="1" s="28">
       <c r="A64" s="34" t="n">
@@ -3983,6 +4302,11 @@
           <t>philosophe français spécialiste de la philosophie moderne et de l’histoire des sciences.</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="142.5" customHeight="1" s="28">
       <c r="A65" s="34" t="n">
@@ -4036,6 +4360,11 @@
           <t>philosophe française spécialiste de Nietzsche, de philosophie politique &amp;amp; critique du néolibéralisme.</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="131.25" customHeight="1" s="28">
       <c r="A66" s="34" t="n">
@@ -4088,6 +4417,11 @@
       <c r="L66" s="27" t="inlineStr">
         <is>
           <t>philosophe français connu pour ses relations avec l'institution de l'être-en-commun.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -4145,6 +4479,11 @@
           <t>philosophe français critique des enjeux liés à la technologie et du Dataïsme.</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="154.5" customHeight="1" s="28">
       <c r="A68" s="34" t="n">
@@ -4197,6 +4536,11 @@
           <t>philosophe et astrophysicien français nous invitant à repenser notre rapport au vivant.</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="168.75" customHeight="1" s="28">
       <c r="A69" s="34" t="n">
@@ -4250,6 +4594,11 @@
           <t>philosophe français qui fait de la philosophie une force de vie quotidienne.</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="146.25" customHeight="1" s="28">
       <c r="A70" s="34" t="n">
@@ -4303,6 +4652,11 @@
           <t>philosophe franco-tunisien auteur du Système du pléonectique.</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="192" customHeight="1" s="28">
       <c r="A71" s="34" t="n">
@@ -4355,6 +4709,11 @@
           <t>philosophe français spécialiste de la philosophie politique &amp;amp; philosophie allemande.</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="141" customHeight="1" s="28">
       <c r="A72" s="34" t="n">
@@ -4407,6 +4766,11 @@
           <t>philosophe et psychanalyste française auteure d'une thèse sur "la métaphysique de l'imagination".</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="132.75" customHeight="1" s="28">
       <c r="A73" s="34" t="n">
@@ -4459,6 +4823,11 @@
           <t>philosophe française spécialiste des épistémologies féministes &amp;amp; des intersections race/genre.</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="173.25" customHeight="1" s="28">
       <c r="A74" s="34" t="n">
@@ -4512,6 +4881,11 @@
           <t>philosophe française au style narratif qui transforme la philo en journal existentiel.</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="162" customHeight="1" s="28">
       <c r="A75" s="34" t="n">
@@ -4565,6 +4939,11 @@
           <t>philosophe français spécialiste de la philosophie française du XXe siècle.</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="144.75" customHeight="1" s="28">
       <c r="A76" s="34" t="n">
@@ -4618,6 +4997,11 @@
           <t>philosophe français penseur contre les évidences, les dogmes et le conformisme.</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="146.25" customHeight="1" s="28">
       <c r="A77" s="34" t="n">
@@ -4671,6 +5055,16 @@
           <t>philosophe française spécialiste des philosophies africaines.</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="147.75" customHeight="1" s="28">
       <c r="A78" s="34" t="n">
@@ -4724,6 +5118,11 @@
           <t>philosophe français spécialiste de Spinoza et créateur d'une "philosophie interactionnelle".</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="180.55" customHeight="1" s="28">
       <c r="A79" s="34" t="n">
@@ -4778,6 +5177,11 @@
           <t>philosophe français spécialiste de l'éthique de la guerre &amp;amp; du droit international.</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="283.55" customHeight="1" s="28">
       <c r="A80" s="34" t="n">
@@ -4829,6 +5233,16 @@
           <t>philosophe française spécialiste de la pensée de Bergson et des études postcoloniales.</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="395.5" customHeight="1" s="28">
       <c r="A81" s="34" t="n">
@@ -4879,6 +5293,11 @@
           <t xml:space="preserve"> philosophe, essayiste et conférencière française, spécialiste des ressources humaines et du monde de l’entreprise.</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="145.5" customHeight="1" s="28">
       <c r="A82" s="34" t="n">
@@ -4933,6 +5352,11 @@
           <t>philosophe &amp;amp; romancier français figure montante d'une métaphysique contemporaine ambitieuse.</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="202.5" customHeight="1" s="28">
       <c r="A83" s="34" t="n">
@@ -4987,6 +5411,11 @@
           <t>philosophe français défenseur du libéralisme classique moderne axé sur la liberté individuelle.</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="124.5" customHeight="1" s="28">
       <c r="A84" s="34" t="n">
@@ -5039,6 +5468,11 @@
           <t>philosophe français principalement orienté sur l'environnement.</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="167.25" customHeight="1" s="28">
       <c r="A85" s="34" t="n">
@@ -5092,6 +5526,11 @@
           <t>philosophe français dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle.</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="237.75" customHeight="1" s="28">
       <c r="A86" s="34" t="n">
@@ -5142,6 +5581,11 @@
           <t xml:space="preserve"> philosophe et essayiste français, drôle et provocateur, qui traite des problèmes existentiels contemporains.</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="115.5" customHeight="1" s="28">
       <c r="A87" s="34" t="n">
@@ -5195,6 +5639,16 @@
           <t>philosophe franco-américain spécialiste des études noires francophones &amp;amp; décoloniales.</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="219.75" customHeight="1" s="28">
       <c r="A88" s="26" t="n">
@@ -5242,6 +5696,11 @@
       <c r="L88" s="27" t="inlineStr">
         <is>
           <t>philosophe politique française, de l’humanisme aux dynamiques de la déshumanisation.</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -2031,9 +2031,7 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O25">
-        <v>3</v>
-      </c>
+      <c r="O25"/>
     </row>
     <row r="26" ht="178.5" customHeight="1" s="28">
       <c r="A26" s="34" t="n">
@@ -2856,9 +2854,7 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O39">
-        <v>3</v>
-      </c>
+      <c r="O39"/>
     </row>
     <row r="40" ht="162" customHeight="1" s="28">
       <c r="A40" s="34" t="n">

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -925,7 +925,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;femme</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1039,6 +1039,11 @@
           <t>philosophe française, historienne de la philosophie et traductrice.</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -1153,6 +1158,11 @@
           <t>philosophe française à la croisée de la médecine, la philosophie et les sciences du vivant.</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -1325,6 +1335,11 @@
           <t>philosophe française figure du post‑structuralisme français à partir des années 1960.</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -1442,7 +1457,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;femme</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1564,6 +1579,11 @@
           <t>philosophe française spécialiste de Montesquieu &amp;amp; de l'éthique de l'environnement.</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -1969,6 +1989,11 @@
           <t>philosophe française spécialiste des Grecs anciens.</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -2086,6 +2111,11 @@
           <t>philosophe française auteure d'essais sur la morale et la politique contemporaines.</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -2199,6 +2229,11 @@
       <c r="L28" s="27" t="inlineStr">
         <is>
           <t>philosophe française et historienne des sciences.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3080,6 +3115,11 @@
           <t>philosophe française spécialiste du langage, de la morale et de philosophie politique.</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3139,6 +3179,11 @@
           <t>philosophe française menant une réflexion philosophique et sociologique sur la place du travail.</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3196,6 +3241,11 @@
           <t>philosophe française spécialiste de la cause animale et des droits des animaux.</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3484,6 +3534,11 @@
           <t>philosophe française spécialisée en esthétique, philosophie morale et politique et théorie féministe.</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -3598,6 +3653,11 @@
       <c r="L52" s="27" t="inlineStr">
         <is>
           <t>philosophe française spécialiste des pensées française &amp;amp; italienne contemporaines.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3777,6 +3837,11 @@
           <t>philosophe française qui s'intéresse aux questions d'éthique et de philosophie morale et politique.</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -4064,6 +4129,11 @@
 </t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -4120,6 +4190,11 @@
       <c r="L61" s="27" t="inlineStr">
         <is>
           <t>philosophe française spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4356,6 +4431,11 @@
           <t>philosophe française spécialiste de Nietzsche, de philosophie politique &amp;amp; critique du néolibéralisme.</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -4762,6 +4842,11 @@
           <t>philosophe et psychanalyste française auteure d'une thèse sur "la métaphysique de l'imagination".</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -4819,6 +4904,11 @@
           <t>philosophe française spécialiste des épistémologies féministes &amp;amp; des intersections race/genre.</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -4877,6 +4967,11 @@
           <t>philosophe française au style narratif qui transforme la philo en journal existentiel.</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -5053,7 +5148,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">sud;femme</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5231,7 +5326,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">sud;femme</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5289,6 +5384,11 @@
           <t xml:space="preserve"> philosophe, essayiste et conférencière française, spécialiste des ressources humaines et du monde de l’entreprise.</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -5692,6 +5792,11 @@
       <c r="L88" s="27" t="inlineStr">
         <is>
           <t>philosophe politique française, de l’humanisme aux dynamiques de la déshumanisation.</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="26" min="1" max="1"/>
@@ -750,6 +750,11 @@
           <t xml:space="preserve">Importance</t>
         </is>
       </c>
+      <c r="P3" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thèmes</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="221.25" customHeight="1" s="28">
       <c r="A4" s="34" t="n">
@@ -808,6 +813,11 @@
       <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
         </is>
       </c>
     </row>
@@ -871,6 +881,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="126.75" customHeight="1" s="28">
       <c r="A6" s="34" t="n">
@@ -933,6 +948,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="157.5" customHeight="1" s="28">
       <c r="A7" s="34" t="n">
@@ -990,6 +1010,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; reel</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="159" customHeight="1" s="28">
       <c r="A8" s="34" t="n">
@@ -1049,6 +1074,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="152.25" customHeight="1" s="28">
       <c r="A9" s="34" t="n">
@@ -1106,6 +1136,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental ; justice</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="165.75" customHeight="1" s="28">
       <c r="A10" s="34" t="n">
@@ -1168,6 +1203,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="147.75" customHeight="1" s="28">
       <c r="A11" s="34" t="n">
@@ -1181,7 +1221,7 @@
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>Jacques RANCIÉRE</t>
+          <t xml:space="preserve">Jacques RANCIÈRE</t>
         </is>
       </c>
       <c r="E11" s="36" t="inlineStr">
@@ -1224,6 +1264,11 @@
       <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; continental</t>
         </is>
       </c>
     </row>
@@ -1282,6 +1327,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="199.5" customHeight="1" s="28">
       <c r="A13" s="34" t="n">
@@ -1345,6 +1395,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; continental</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="178.5" customHeight="1" s="28">
       <c r="A14" s="34" t="n">
@@ -1402,6 +1457,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="147.75" customHeight="1" s="28">
       <c r="A15" s="34" t="n">
@@ -1463,6 +1523,11 @@
       <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
@@ -1526,6 +1591,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="168" customHeight="1" s="28">
       <c r="A17" s="34" t="n">
@@ -1589,6 +1659,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="157.5" customHeight="1" s="28">
       <c r="A18" s="34" t="n">
@@ -1647,6 +1722,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="178.5" customHeight="1" s="28">
       <c r="A19" s="34" t="n">
@@ -1705,6 +1785,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="156.75" customHeight="1" s="28">
       <c r="A20" s="34" t="n">
@@ -1762,6 +1847,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="147.75" customHeight="1" s="28">
       <c r="A21" s="34" t="n">
@@ -1819,6 +1909,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens ; continental</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="168" customHeight="1" s="28">
       <c r="A22" s="34" t="n">
@@ -1878,6 +1973,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="193.5" customHeight="1" s="28">
       <c r="A23" s="34" t="n">
@@ -1936,6 +2036,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice ; continental</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="189" customHeight="1" s="28">
       <c r="A24" s="34" t="n">
@@ -1999,6 +2104,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="147.75" customHeight="1" s="28">
       <c r="A25" s="34" t="n">
@@ -2057,6 +2167,11 @@
         </is>
       </c>
       <c r="O25"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="178.5" customHeight="1" s="28">
       <c r="A26" s="34" t="n">
@@ -2121,6 +2236,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="210.75" customHeight="1" s="28">
       <c r="A27" s="34" t="n">
@@ -2178,6 +2298,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="158.25" customHeight="1" s="28">
       <c r="A28" s="34" t="n">
@@ -2241,6 +2366,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="188.25" customHeight="1" s="28">
       <c r="A29" s="34" t="n">
@@ -2299,6 +2429,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="157.5" customHeight="1" s="28">
       <c r="A30" s="34" t="n">
@@ -2362,6 +2497,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="222" customHeight="1" s="28">
       <c r="A31" s="34" t="n">
@@ -2419,6 +2559,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="245.25" customHeight="1" s="28">
       <c r="A32" s="34" t="n">
@@ -2475,6 +2620,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="210" customHeight="1" s="28">
       <c r="A33" s="34" t="n">
@@ -2533,6 +2683,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="147.75" customHeight="1" s="28">
       <c r="A34" s="34" t="n">
@@ -2592,6 +2747,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="126.75" customHeight="1" s="28">
       <c r="A35" s="34" t="n">
@@ -2652,6 +2812,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="137.25" customHeight="1" s="28">
       <c r="A36" s="34" t="n">
@@ -2714,6 +2879,11 @@
       <c r="O36">
         <v>2</v>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="95.25" customHeight="1" s="28">
       <c r="A37" s="34" t="n">
@@ -2773,6 +2943,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="157.5" customHeight="1" s="28">
       <c r="A38" s="34" t="n">
@@ -2831,6 +3006,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens ; continental</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="126.75" customHeight="1" s="28">
       <c r="A39" s="34" t="n">
@@ -2890,6 +3070,11 @@
         </is>
       </c>
       <c r="O39"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="162" customHeight="1" s="28">
       <c r="A40" s="34" t="n">
@@ -2945,6 +3130,11 @@
       <c r="N40" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
         </is>
       </c>
     </row>
@@ -3007,6 +3197,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="126.75" customHeight="1" s="28">
       <c r="A42" s="34" t="n">
@@ -3064,6 +3259,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental ; decolonial</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="191" customHeight="1" s="28">
       <c r="A43" s="34" t="n">
@@ -3125,6 +3325,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; reel</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="202.95" customHeight="1" s="28">
       <c r="A44" s="34" t="n">
@@ -3189,6 +3394,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="189.75" customHeight="1" s="28">
       <c r="A45" s="34" t="n">
@@ -3251,6 +3461,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="147.75" customHeight="1" s="28">
       <c r="A46" s="34" t="n">
@@ -3309,6 +3524,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="261.75" customHeight="1" s="28">
       <c r="A47" s="34" t="n">
@@ -3366,6 +3586,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="261.75" customHeight="1" s="28">
       <c r="A48" s="34" t="n">
@@ -3422,6 +3647,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens ; reel</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="207.75" customHeight="1" s="28">
       <c r="A49" s="34" t="n">
@@ -3480,6 +3710,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="116.25" customHeight="1" s="28">
       <c r="A50" s="34" t="n">
@@ -3544,6 +3779,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; justice</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="126.75" customHeight="1" s="28">
       <c r="A51" s="34" t="n">
@@ -3602,6 +3842,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="147.75" customHeight="1" s="28">
       <c r="A52" s="34" t="n">
@@ -3663,6 +3908,11 @@
       <c r="N52" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental ; justice</t>
         </is>
       </c>
     </row>
@@ -3725,6 +3975,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="219.75" customHeight="1" s="28">
       <c r="A54" s="34" t="n">
@@ -3780,6 +4035,11 @@
       <c r="N54" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
         </is>
       </c>
     </row>
@@ -3847,6 +4107,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie ; justice</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="162" customHeight="1" s="28">
       <c r="A56" s="34" t="n">
@@ -3904,6 +4169,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="126.75" customHeight="1" s="28">
       <c r="A57" s="34" t="n">
@@ -3917,12 +4187,12 @@
       </c>
       <c r="D57" s="35" t="inlineStr">
         <is>
-          <t>Stéphanne HABER</t>
+          <t xml:space="preserve">Stéphane HABER</t>
         </is>
       </c>
       <c r="E57" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/St%C3%A9phane_Haber" title=" Wikipedia"&gt;Stéphanne HABER&lt;/a&gt;  est un philosophe français spécialiste de la philosophie sociale et politique, ainsi que de l'épistémologie des sciences humaines. Son doctorat obtenu en 1996 à l'université de Besançon portait sur les formes de connaissance du présent dans les sciences sociales, sous la direction de Robert Damien. &lt;/p&gt; &lt;p&gt; Professeur à l'université Paris Nanterre, il est directeur adjoint du laboratoire Sophiapol. Ses enseignements couvrent l'histoire et l'épistémologie des sciences humaines, la philosophie contemporaine et les problèmes de théorie sociale et politique.&lt;/p&gt; &lt;p&gt;  Ses livres incluent Les Sciences humaines (1995), Habermas et la sociologie (1998), Freud et la théorie sociale (2012), Penser le néocapitalisme (2013). Il a dirigé des ouvrages comme L’Action en philosophie contemporaine (2005) et contribué à des revues sur Marx, l'aliénation et le capitalisme. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur  &lt;a href="https://www.youtube.com/watch?v=ZxECyRcOzFY&amp;t=11s"  title=". Haber : Exploitation du travail, appropriation de la nature, crise climatique. par Penser la Transformation"&gt; les interactions philosophie&lt;/a&gt;/sciences sociales, les marxismes contemporains, le néocapitalisme, l'aliénation subjective et objective, ainsi que les pathologies sociales et la théorie critique.</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/St%C3%A9phane_Haber" title=" Wikipedia"&gt;Stéphane HABER&lt;/a&gt;  est un philosophe français spécialiste de la philosophie sociale et politique, ainsi que de l'épistémologie des sciences humaines. Son doctorat obtenu en 1996 à l'université de Besançon portait sur les formes de connaissance du présent dans les sciences sociales, sous la direction de Robert Damien. &lt;/p&gt; &lt;p&gt; Professeur à l'université Paris Nanterre, il est directeur adjoint du laboratoire Sophiapol. Ses enseignements couvrent l'histoire et l'épistémologie des sciences humaines, la philosophie contemporaine et les problèmes de théorie sociale et politique.&lt;/p&gt; &lt;p&gt;  Ses livres incluent Les Sciences humaines (1995), Habermas et la sociologie (1998), Freud et la théorie sociale (2012), Penser le néocapitalisme (2013). Il a dirigé des ouvrages comme L’Action en philosophie contemporaine (2005) et contribué à des revues sur Marx, l'aliénation et le capitalisme. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur  &lt;a href="https://www.youtube.com/watch?v=ZxECyRcOzFY&amp;t=11s"  title=". Haber : Exploitation du travail, appropriation de la nature, crise climatique. par Penser la Transformation"&gt; les interactions philosophie&lt;/a&gt;/sciences sociales, les marxismes contemporains, le néocapitalisme, l'aliénation subjective et objective, ainsi que les pathologies sociales et la théorie critique.</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
@@ -3959,6 +4229,11 @@
       <c r="N57" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
@@ -4018,6 +4293,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="150" customHeight="1" s="28">
       <c r="A59" s="44" t="n">
@@ -4077,6 +4357,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="167.25" customHeight="1" s="28">
       <c r="A60" s="34" t="n">
@@ -4139,6 +4424,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="123.75" customHeight="1" s="28">
       <c r="A61" s="34" t="n">
@@ -4202,6 +4492,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="126.75" customHeight="1" s="28">
       <c r="A62" s="34" t="n">
@@ -4258,6 +4553,11 @@
       <c r="N62" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
         </is>
       </c>
     </row>
@@ -4320,6 +4620,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="116.25" customHeight="1" s="28">
       <c r="A64" s="34" t="n">
@@ -4378,6 +4683,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="142.5" customHeight="1" s="28">
       <c r="A65" s="34" t="n">
@@ -4396,7 +4706,7 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Stiegler" title=" Wikipedia"&gt;Barbara STEIGLER&lt;/a&gt;  est une philosophe française, fille du philosophe Bernard Stiegler, spécialiste de Nietzsche, de philosophie politique et critique du néolibéralisme. Agrégée de philosophie, elle soutient sa thèse en 2003 à Paris-Sorbonne sous la direction de Jean-Luc Marion sur Nietzsche et la biologie. Maître de conférences puis professeure à l'université Bordeaux-Montaigne depuis 2006, elle y dirige le master  &lt;a href="https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf" title="Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne"&gt;"Soin, éthique et santé". &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Engagée politiquement, elle analyse les Gilets Jaunes dans "Du cap aux grèves" paru en 2021 et critique l’adaptationnisme comme fondement du néolibéralisme, opposant une intelligence collective à l’élitisme technocratique. &lt;/p&gt; &lt;p&gt; Ses ouvrages sur Nietzsche explorent le corps et la vie (Nietzsche et la biologie, 2001 ; Nietzsche et la critique de la chair, 2005 ; Nietzsche et la vie, 2021). &lt;/p&gt; &lt;p&gt;  Elle étend ses recherches au politique avec  &lt;a href="https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/" title="Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit"&gt;"Il faut s’adapter" &lt;/a&gt; paru en  2019, dénonçant les racines évolutionnistes (Spencer, Lippmann) du &lt;a href="https://www.youtube.com/watch?v=oQQ4xqRvYTk" style="color:#88A1E9" title="LA LENTE AGONIE DU NÉOLIBÉRALISME  par 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Stiegler" title=" Wikipedia"&gt;Barbara STIEGLER&lt;/a&gt;  est une philosophe française, fille du philosophe Bernard Stiegler, spécialiste de Nietzsche, de philosophie politique et critique du néolibéralisme. Agrégée de philosophie, elle soutient sa thèse en 2003 à Paris-Sorbonne sous la direction de Jean-Luc Marion sur Nietzsche et la biologie. Maître de conférences puis professeure à l'université Bordeaux-Montaigne depuis 2006, elle y dirige le master  &lt;a href="https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf" title="Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne"&gt;"Soin, éthique et santé". &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Engagée politiquement, elle analyse les Gilets Jaunes dans "Du cap aux grèves" paru en 2021 et critique l’adaptationnisme comme fondement du néolibéralisme, opposant une intelligence collective à l’élitisme technocratique. &lt;/p&gt; &lt;p&gt; Ses ouvrages sur Nietzsche explorent le corps et la vie (Nietzsche et la biologie, 2001 ; Nietzsche et la critique de la chair, 2005 ; Nietzsche et la vie, 2021). &lt;/p&gt; &lt;p&gt;  Elle étend ses recherches au politique avec  &lt;a href="https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/" title="Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit"&gt;"Il faut s’adapter" &lt;/a&gt; paru en  2019, dénonçant les racines évolutionnistes (Spencer, Lippmann) du &lt;a href="https://www.youtube.com/watch?v=oQQ4xqRvYTk" style="color:#88A1E9" title="LA LENTE AGONIE DU NÉOLIBÉRALISME  par 
 TheSwissBox Conversation"&gt;néolibéralisme &lt;/a&gt; face au pragmatisme démocratique de Dewey. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
@@ -4439,6 +4749,11 @@
       <c r="N65" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
@@ -4498,6 +4813,11 @@
       <c r="N66" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
@@ -4560,6 +4880,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="154.5" customHeight="1" s="28">
       <c r="A68" s="34" t="n">
@@ -4617,6 +4942,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie ; reel</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="168.75" customHeight="1" s="28">
       <c r="A69" s="34" t="n">
@@ -4675,6 +5005,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="146.25" customHeight="1" s="28">
       <c r="A70" s="34" t="n">
@@ -4733,6 +5068,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="192" customHeight="1" s="28">
       <c r="A71" s="34" t="n">
@@ -4790,6 +5130,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="141" customHeight="1" s="28">
       <c r="A72" s="34" t="n">
@@ -4852,6 +5197,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="132.75" customHeight="1" s="28">
       <c r="A73" s="34" t="n">
@@ -4914,6 +5264,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; justice</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="173.25" customHeight="1" s="28">
       <c r="A74" s="34" t="n">
@@ -4977,6 +5332,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="162" customHeight="1" s="28">
       <c r="A75" s="34" t="n">
@@ -5035,6 +5395,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="144.75" customHeight="1" s="28">
       <c r="A76" s="34" t="n">
@@ -5093,6 +5458,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="146.25" customHeight="1" s="28">
       <c r="A77" s="34" t="n">
@@ -5156,6 +5526,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="147.75" customHeight="1" s="28">
       <c r="A78" s="34" t="n">
@@ -5214,6 +5589,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="180.55" customHeight="1" s="28">
       <c r="A79" s="34" t="n">
@@ -5273,6 +5653,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="283.55" customHeight="1" s="28">
       <c r="A80" s="34" t="n">
@@ -5334,6 +5719,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="395.5" customHeight="1" s="28">
       <c r="A81" s="34" t="n">
@@ -5394,6 +5784,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="145.5" customHeight="1" s="28">
       <c r="A82" s="34" t="n">
@@ -5453,6 +5848,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="202.5" customHeight="1" s="28">
       <c r="A83" s="34" t="n">
@@ -5512,6 +5912,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="124.5" customHeight="1" s="28">
       <c r="A84" s="34" t="n">
@@ -5569,6 +5974,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie ; justice</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="167.25" customHeight="1" s="28">
       <c r="A85" s="34" t="n">
@@ -5627,6 +6037,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="237.75" customHeight="1" s="28">
       <c r="A86" s="34" t="n">
@@ -5682,6 +6097,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="115.5" customHeight="1" s="28">
       <c r="A87" s="34" t="n">
@@ -5745,6 +6165,11 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="219.75" customHeight="1" s="28">
       <c r="A88" s="26" t="n">
@@ -5802,6 +6227,11 @@
       <c r="N88" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice ; reel</t>
+          <t xml:space="preserve">critique ; reel</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
+          <t xml:space="preserve">art</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental ; justice</t>
+          <t xml:space="preserve">continental ; critique</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice ; continental</t>
+          <t xml:space="preserve">critique ; continental ; art</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre ; continental</t>
+          <t xml:space="preserve">genre ; continental ; art</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique ; art</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice ; continental</t>
+          <t xml:space="preserve">critique ; continental</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
+          <t xml:space="preserve">art</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
+          <t xml:space="preserve">art</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre ; justice</t>
+          <t xml:space="preserve">genre ; justice ; art</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental ; justice</t>
+          <t xml:space="preserve">continental ; critique</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
+          <t xml:space="preserve">continental ; art</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre ; justice</t>
+          <t xml:space="preserve">genre ; critique</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -6147,7 +6147,7 @@
       </c>
       <c r="K87" s="27" t="inlineStr">
         <is>
-          <t>Tiers-mondisme</t>
+          <t xml:space="preserve">Tiers-mondisme ; Pensée décoloniale</t>
         </is>
       </c>
       <c r="L87" s="27" t="inlineStr">

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -852,7 +852,7 @@
       </c>
       <c r="G5" s="36" t="inlineStr">
         <is>
-          <t>"Jean Borella - philosophie – les guenoniens " par Baglis tv</t>
+          <t xml:space="preserve">"Jean Borella - philosophie – les guenoniens " par Baglis Tv</t>
         </is>
       </c>
       <c r="H5" s="36" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G13" s="36" t="inlineStr">
         <is>
-          <t>"Julia Kristeva - Prélude à une éthique du féminin" par librairie mollat</t>
+          <t xml:space="preserve">"Julia Kristeva - Prélude à une éthique du féminin" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H13" s="34" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G16" s="36" t="inlineStr">
         <is>
-          <t>"l'authenticité est le new cool" par le Point</t>
+          <t xml:space="preserve">"l'authenticité est le new cool" par Le Point</t>
         </is>
       </c>
       <c r="H16" s="36" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G19" s="36" t="inlineStr">
         <is>
-          <t>"Yves Michaud - L'art, c'est bien fini : essai sur l'hyper-esthétique et les atmosphères" par librairie mollat</t>
+          <t xml:space="preserve">"Yves Michaud - L'art, c'est bien fini : essai sur l'hyper-esthétique et les atmosphères" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H19" s="36" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G27" s="36" t="inlineStr">
         <is>
-          <t>"Exotérisme et ésotérisme" par BAGLIS TV</t>
+          <t xml:space="preserve">"Exotérisme et ésotérisme" par Baglis Tv</t>
         </is>
       </c>
       <c r="H27" s="36" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="G29" s="36" t="inlineStr">
         <is>
-          <t>"Christian Godin - Le soupir de la créature accablée : la religion aujourd’hui" par librairie mollat</t>
+          <t xml:space="preserve">"Christian Godin - Le soupir de la créature accablée : la religion aujourd’hui" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H29" s="36" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="G31" s="36" t="inlineStr">
         <is>
-          <t>Roger-Pol DROIT si je n’avais plus qu’une heure à vivre par librairie Mollat</t>
+          <t xml:space="preserve">Roger-Pol DROIT si je n’avais plus qu’une heure à vivre par Librairie Mollat</t>
         </is>
       </c>
       <c r="H31" s="37" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="G32" s="36" t="inlineStr">
         <is>
-          <t>qui a inventé la nature par arte</t>
+          <t xml:space="preserve">qui a inventé la nature par Arte</t>
         </is>
       </c>
       <c r="H32" s="37" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="G33" s="36" t="inlineStr">
         <is>
-          <t>"Le Libéralisme par le Précepteur"</t>
+          <t xml:space="preserve">"Le Libéralisme par Le Précepteur</t>
         </is>
       </c>
       <c r="H33" s="36" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G37" s="36" t="inlineStr">
         <is>
-          <t>"Qui êtes-vous Georges Didi-Huberman ?" par abc penser</t>
+          <t xml:space="preserve">"Qui êtes-vous Georges Didi-Huberman ?" par ABC Penser</t>
         </is>
       </c>
       <c r="H37" s="36" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="G40" s="36" t="inlineStr">
         <is>
-          <t>"Peut-on se fier au sentiment d'injustice ? - Charles RAMOND" par MSH alpes</t>
+          <t xml:space="preserve">"Peut-on se fier au sentiment d'injustice ? - Charles RAMOND" par MSH Alpes</t>
         </is>
       </c>
       <c r="H40" s="36" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="G43" s="36" t="inlineStr">
         <is>
-          <t>qui êtes vous Sandra LAUGIER par abc penser</t>
+          <t xml:space="preserve">qui êtes vous Sandra LAUGIER par ABC Penser</t>
         </is>
       </c>
       <c r="H43" s="37" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="G50" s="36" t="inlineStr">
         <is>
-          <t>"Fabienne Brugère - Désaimer : manuel d'un retour à la vie" par librairie mollat</t>
+          <t xml:space="preserve">"Fabienne Brugère - Désaimer : manuel d'un retour à la vie" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H50" s="36" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="G53" s="36" t="inlineStr">
         <is>
-          <t>"Guillaume le Blanc - Que faire de notre vulnérabilité ?" par librairie mollat</t>
+          <t xml:space="preserve">"Guillaume le Blanc - Que faire de notre vulnérabilité ?" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H53" s="36" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="G60" s="36" t="inlineStr">
         <is>
-          <t>Camille Froidevaux-Metterie philosophie du genre par Collège de france</t>
+          <t xml:space="preserve">Camille Froidevaux-Metterie philosophie du genre par Collège de France</t>
         </is>
       </c>
       <c r="H60" s="37" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G61" s="36" t="inlineStr">
         <is>
-          <t>"Laurence Devillairs - La splendeur du monde : aller à la rencontre de la beauté" par Librairie mollat</t>
+          <t xml:space="preserve">"Laurence Devillairs - La splendeur du monde : aller à la rencontre de la beauté" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H61" s="36" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="G62" s="36" t="inlineStr">
         <is>
-          <t>"Vincent Delecroix - Naufrage" par librairie mollat</t>
+          <t xml:space="preserve">"Vincent Delecroix - Naufrage" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H62" s="36" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G67" s="36" t="inlineStr">
         <is>
-          <t>"Pourquoi ChatGPT accélère la marchandisation de nos existences" par le Figaro</t>
+          <t xml:space="preserve">"Pourquoi ChatGPT accélère la marchandisation de nos existences" par Le Figaro</t>
         </is>
       </c>
       <c r="H67" s="36" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G71" s="36" t="inlineStr">
         <is>
-          <t>"Qui êtes-vous Michaël Fœssel ?" par abc penser</t>
+          <t xml:space="preserve">"Qui êtes-vous Michaël Fœssel ?" par ABC Penser</t>
         </is>
       </c>
       <c r="H71" s="36" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="G74" s="36" t="inlineStr">
         <is>
-          <t>"Les débuts - Claire Marin" par librairie mollat</t>
+          <t xml:space="preserve">"Les débuts - Claire Marin" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H74" s="36" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G75" s="36" t="inlineStr">
         <is>
-          <t>"Philosophie ou spiritualités : avons-nous besoin d'un supplément d'âme ?" par le point</t>
+          <t xml:space="preserve">"Philosophie ou spiritualités : avons-nous besoin d'un supplément d'âme ?" par Le Point</t>
         </is>
       </c>
       <c r="H75" s="36" t="inlineStr">

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -1097,7 +1097,7 @@
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Macherey"   title=" Wikipedia"&gt;Pierre MACHEREY&lt;/a&gt;  est un philosophe français  proche de Louis Althusser, et l’une des figures importantes du .  &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_1977_num_41_1_1858" title="marxisme et structuralisme par persée"&gt;marxisme structuraliste &lt;/a&gt; et de la théorie littéraire en France. Son travail a beaucoup compté pour la philosophie continentale, surtout à travers ses lectures de Spinoza et ses analyses du lien .  &lt;a href="https://www.youtube.com/watch?v=DjawaCnhaps" title="Pierre Macherey Proust , entre littérature et philosophie par Virginie Chretien"&gt; entre philosophie, littérature &lt;/a&gt; et idéologie. &lt;/p&gt; &lt;p&gt;   Sa philosophie part d’une idée simple mais exigeante : on ne pense jamais hors des conditions historiques et sociales dans lesquelles on vit. Il voit la philosophie comme une pratique conjoncturelle, c’est-à-dire capable d’éclairer une situation pour mieux intervenir sur elle et, à terme, contribuer à sa transformation. Cette approche le distingue d’une philosophie qui prétendrait atteindre des vérités abstraites, détachées du réel. &lt;/p&gt; &lt;p&gt; Un autre axe central de son œuvre est Spinoza. Il s’est servi de Spinoza pour penser la nécessité, la puissance, les affects et la liberté autrement qu’en termes de sujet souverain ou de conscience transparente. Chez lui, la liberté ne consiste pas à échapper aux déterminations, mais à comprendre les conditions qui nous traversent afin d’agir plus lucidement dans le monde. &lt;/p&gt; &lt;p&gt; Il  a renouvelé la  &lt;a href="https://www.persee.fr/doc/roman_0048-8593_1991_num_21_72_5776" title="Pierre Macherey a quoi pense la littérature par persée"&gt; critique littéraire &lt;/a&gt; en refusant de faire de la littérature une simple illustration d’idées philosophiques. Il montre que les œuvres produisent leur propre pensée, à travers leurs formes, leurs silences et leurs écarts, et qu’il faut lire ces structures plutôt que chercher un “message” caché. En ce sens, sa philosophie est à la fois politique, littéraire et rigoureusement attentive aux textes, ce qui en fait un penseur discret mais très influent. &lt;/p&gt;     &lt;audio controls title="Actualité philo : Pierre Macherey par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-07.02.2014-ITEMA_20585549-2014C12410E0044-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Macherey"   title=" Wikipedia"&gt;Pierre MACHEREY&lt;/a&gt;  est un philosophe français  proche de Louis Althusser, et l’une des figures importantes du &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_1977_num_41_1_1858" title="marxisme et structuralisme par persée"&gt;marxisme structuraliste &lt;/a&gt; et de la théorie littéraire en France. Son travail a beaucoup compté pour la philosophie continentale, surtout à travers ses lectures de Spinoza et ses analyses du lien &lt;a href="https://www.youtube.com/watch?v=DjawaCnhaps" title="Pierre Macherey Proust , entre littérature et philosophie par Virginie Chretien"&gt; entre philosophie, littérature &lt;/a&gt; et idéologie. &lt;/p&gt; &lt;p&gt;   Sa philosophie part d’une idée simple mais exigeante : on ne pense jamais hors des conditions historiques et sociales dans lesquelles on vit. Il voit la philosophie comme une pratique conjoncturelle, c’est-à-dire capable d’éclairer une situation pour mieux intervenir sur elle et, à terme, contribuer à sa transformation. Cette approche le distingue d’une philosophie qui prétendrait atteindre des vérités abstraites, détachées du réel. &lt;/p&gt; &lt;p&gt; Un autre axe central de son œuvre est Spinoza. Il s’est servi de Spinoza pour penser la nécessité, la puissance, les affects et la liberté autrement qu’en termes de sujet souverain ou de conscience transparente. Chez lui, la liberté ne consiste pas à échapper aux déterminations, mais à comprendre les conditions qui nous traversent afin d’agir plus lucidement dans le monde. &lt;/p&gt; &lt;p&gt; Il  a renouvelé la  &lt;a href="https://www.persee.fr/doc/roman_0048-8593_1991_num_21_72_5776" title="Pierre Macherey a quoi pense la littérature par persée"&gt; critique littéraire &lt;/a&gt; en refusant de faire de la littérature une simple illustration d’idées philosophiques. Il montre que les œuvres produisent leur propre pensée, à travers leurs formes, leurs silences et leurs écarts, et qu’il faut lire ces structures plutôt que chercher un “message” caché. En ce sens, sa philosophie est à la fois politique, littéraire et rigoureusement attentive aux textes, ce qui en fait un penseur discret mais très influent. &lt;/p&gt;     &lt;audio controls title="Actualité philo : Pierre Macherey par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-07.02.2014-ITEMA_20585549-2014C12410E0044-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F9" s="34" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E10" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Fagot-Largeault"  title=" Wikipedia"&gt;Anne FAGOT-LARGEAULT&lt;/a&gt;  est une une philosophe et psychiatre française, élève de l’École normale supérieure de jeunes filles, agrégée de philosophie en 1961, elle a combiné une carrière académique brillante – professeur à Paris 1 Panthéon-Sorbonne puis au Collège de France (chaire de philosophie des sciences biologiques et médicales de 2000 à 2009) – avec une pratique hospitalière en psychiatrie à l’hôpital Henri-Mondor de Créteil. Membre de l’Académie des sciences depuis 2002, elle incarne une figure rare à la croisée de la médecine, de la philosophie et des sciences du vivant. &lt;/p&gt; &lt;p&gt;  Sa philosophie se déploie dans trois &lt;a href="https://www.youtube.com/watch?v=LYwHBFs7elQ" title=" Philosophie des sciences biologiques et médicales et philosophie par Collège de France"&gt; directions principales, &lt;/a&gt; toutes liées à l’épistémologie et à l’ontologie des sciences biologiques et médicales. D’abord, elle analyse le raisonnement diagnostique : logique inductive, probabilités, heuristiques, en soulignant les limites de la certitude dans un domaine probabiliste par nature. Ensuite, elle interroge la causalité : distinction entre causalité mécanique et téléologique, preuves épidémiologiques, rôle des modèles explicatifs dans la compréhension du vivant. Enfin, elle s’attache à l’éthique : méthodologie des essais cliniques, dilemmes bioéthiques, responsabilité dans un univers contingent où l’humain influence activement l’avenir. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages comme Ontologie du devenir ou Médecine et philosophie, elle revisite les thèmes du temps, de l’évolution et du vivant en dialogue avec Héraclite, Bergson ou les sciences modernes. Elle défend une science du devenir contre l’immobilisme parmnénidien : le flux permanent du réel exige des concepts fluides, une intuition intellectuelle capable de saisir l’instabilité des êtres vivants sans les figer en essences. L’évolution darwinienne, loin d’être une téléologie, révèle un univers de contingences où l’action humaine porte une responsabilité prospective . &lt;/p&gt; &lt;p&gt;     &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2016_hos_114_1_8513" title=" laudatio de la professeure par persée"&gt; Son apport &lt;/a&gt; le plus original réside dans une anthropologie bio-médicale qui refuse le réductionnisme : la médecine suppose une métaphysique du mal, une épistémologie du normal/pathologique et une éthique équilibrant l’autonomie individuelle, le bien du patient et l’intérêt collectif. Professeure honoraire influente, elle a formé des générations à penser la vie non comme un donné stable, mais comme un processus à comprendre et à orienter éthiquement.&lt;/p&gt;                                                                      &lt;audio controls title="Médecine et philosophie avec Anne Fagot-Largeault par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10201-08.03.2010-ITEMA_20218761-2010C10593E0008-NET_01E69962-F316-4C45-826B-43707F9BD385_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Fagot-Largeault"  title=" Wikipedia"&gt;Anne FAGOT-LARGEAULT&lt;/a&gt;  est une philosophe et psychiatre française, élève de l’École normale supérieure de jeunes filles, agrégée de philosophie en 1961, elle a combiné une carrière académique brillante – professeur à Paris 1 Panthéon-Sorbonne puis au Collège de France (chaire de philosophie des sciences biologiques et médicales de 2000 à 2009) – avec une pratique hospitalière en psychiatrie à l’hôpital Henri-Mondor de Créteil. Membre de l’Académie des sciences depuis 2002, elle incarne une figure rare à la croisée de la médecine, de la philosophie et des sciences du vivant. &lt;/p&gt; &lt;p&gt;  Sa philosophie se déploie dans trois &lt;a href="https://www.youtube.com/watch?v=LYwHBFs7elQ" title=" Philosophie des sciences biologiques et médicales et philosophie par Collège de France"&gt; directions principales, &lt;/a&gt; toutes liées à l’épistémologie et à l’ontologie des sciences biologiques et médicales. D’abord, elle analyse le raisonnement diagnostique : logique inductive, probabilités, heuristiques, en soulignant les limites de la certitude dans un domaine probabiliste par nature. Ensuite, elle interroge la causalité : distinction entre causalité mécanique et téléologique, preuves épidémiologiques, rôle des modèles explicatifs dans la compréhension du vivant. Enfin, elle s’attache à l’éthique : méthodologie des essais cliniques, dilemmes bioéthiques, responsabilité dans un univers contingent où l’humain influence activement l’avenir. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages comme Ontologie du devenir ou Médecine et philosophie, elle revisite les thèmes du temps, de l’évolution et du vivant en dialogue avec Héraclite, Bergson ou les sciences modernes. Elle défend une science du devenir contre l’immobilisme parmnénidien : le flux permanent du réel exige des concepts fluides, une intuition intellectuelle capable de saisir l’instabilité des êtres vivants sans les figer en essences. L’évolution darwinienne, loin d’être une téléologie, révèle un univers de contingences où l’action humaine porte une responsabilité prospective. &lt;/p&gt; &lt;p&gt;     &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2016_hos_114_1_8513" title=" laudatio de la professeure par persée"&gt; Son apport &lt;/a&gt; le plus original réside dans une anthropologie bio-médicale qui refuse le réductionnisme : la médecine suppose une métaphysique du mal, une épistémologie du normal/pathologique et une éthique équilibrant l’autonomie individuelle, le bien du patient et l’intérêt collectif. Professeure honoraire influente, elle a formé des générations à penser la vie non comme un donné stable, mais comme un processus à comprendre et à orienter éthiquement.&lt;/p&gt;                                                                      &lt;audio controls title="Médecine et philosophie avec Anne Fagot-Largeault par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10201-08.03.2010-ITEMA_20218761-2010C10593E0008-NET_01E69962-F316-4C45-826B-43707F9BD385_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F10" s="34" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="E16" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Gilles_Lipovetsky"  title=" Wikipedia"&gt;Gilles LIPOVETSKY&lt;/a&gt; est un philosophe Français majeur de l’hypermodernité &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_postmoderne"  title="Le post modernisme par Wikipedia"&gt;  (post modernisme) &lt;/a&gt;, une époque marquée par l’individualisme exacerbé, l’accélération du temps et la domination de la consommation. Il analyse comment les valeurs traditionnelles s’effacent, laissant place à une quête de sens personnelle, souvent empreinte de contradictions. L’individu contemporain recherche l’épanouissement et le bonheur, mais se heurte à un vide existentiel et à une insatisfaction chronique. &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Gilles_Lipovetsky"  title=" Wikipedia"&gt;Gilles LIPOVETSKY&lt;/a&gt; est un philosophe Français majeur de l’hypermodernité &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_postmoderne"  title="Le post modernisme par Wikipedia"&gt;  (post modernisme)&lt;/a&gt;, une époque marquée par l’individualisme exacerbé, l’accélération du temps et la domination de la consommation. Il analyse comment les valeurs traditionnelles s’effacent, laissant place à une quête de sens personnelle, souvent empreinte de contradictions. L’individu contemporain recherche l’épanouissement et le bonheur, mais se heurte à un vide existentiel et à une insatisfaction chronique. &lt;/p&gt;
 &lt;p&gt; Il met en lumière, dans son livre &lt;a href="https://www.youtube.com/watch?v=n3sv-0Hdr2I" title="L'ère du vide' par Kosmos"&gt;  ' l'ère du vite'  &lt;/a&gt; paru en 1983, l’importance de la consommation et de la séduction dans nos sociétés, où les objets et services ne répondent plus seulement à des besoins, mais deviennent des moyens d’expression identitaire. Ce consumérisme est associé à un hédonisme qui, bien qu’omniprésent, ne parvient pas à combler le désenchantement de l’individu. &lt;/p&gt;
 &lt;p&gt; La mode, selon lui, symbolise parfaitement cette époque : elle incarne le culte de l’éphémère, le changement constant et la tension entre originalité et conformisme. Dans un monde saturé par les médias et le marketing, la quête d’authenticité devient paradoxale, oscillant entre sincérité et mise en scène. &lt;/p&gt;
 &lt;p&gt; Il invite à repenser l’éthique dans une société où les repères traditionnels s’effacent. Il appelle à une responsabilité individuelle face aux défis contemporains, notamment écologiques, tout en valorisant une philosophie de la légèreté et du détachement pour mieux vivre les tensions de la modernité.. &lt;/p&gt;                     &lt;audio controls title="Le règne de la séduction par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/12360-05.12.2017-ITEMA_21514533-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E17" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Catherine_Larr%C3%A8re"  style="color:#6A142A"  title=" Wikipedia"&gt;Catherine LARRÈRE&lt;/a&gt; est une philosophe française   professeure émérite de philosophie à Paris 1 Panthéon-Sorbonne et spécialisée en philosophie morale et politique, avec une attention particulière à l’éthique de l’environnement.&lt;/p&gt; &lt;p&gt; Elle a aporté une contribution majeure à l’essor de la philosophie environnementale en France, abordant des thèmes comme  &lt;a href="https://www.youtube.com/watch?v=YNxj0SXoNSo" style="color:#88A1E9" title="Qu'est-ce que la nature ? par Editions M-Editer"&gt;la protection de la nature &lt;/a&gt;, la prévention des risques et la justice environnementale. Engagement et leadership: présidente de la Fondation de l’écologie politique (2013-2016), un think-tank lié à &lt;a href="https://www.persee.fr/doc/ecoru_0013-0559_1999_num_249_1_5068_t1_0091_0000_2 " style="color:#88A1E9" title="Catherine Larrère Les philosophies de l'environnement  par Persée"&gt;Europe Écologie &lt;/a&gt; Les Verts, et commissaire scientifique de l’exposition Nature vive au Muséum national d’histoire naturelle (2001). &lt;/p&gt; &lt;p&gt; Ellle a publié largement sur Montesquieu, la philosophie morale et politique. Elle a aussi travaillé sur le rôle des femmes dans la société selon Rousseau et a collaboré étroitement avec son mari, Raphaël Larrère, agronome et écologue, sur des questions liées à l’environnement. Sa productivité académique est importante: articles, livres et chapitres, avec une présence notable dans les ressources bibliographiques et les bases de données spécialisées. Sa collaboration avec des chercheurs anglophones et ses traductions ont contribué à diffuser des idées clés de l’éthique de l’environnement en milieu francophone. &lt;/p&gt; &lt;p&gt; Elle continue d’être présente dans les débats publics et intellectuels sur l’environnement et l’éthique, notamment à travers des articles dans des revues et des plateformes spécialisées. &lt;/p&gt;   &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Catherine Larrère : "Ne pas s'occuper du social, c'est bloquer les solutions environnementales" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-07.02.2017-ITEMA_21221850-2017C19327S0038-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Catherine_Larr%C3%A8re"  style="color:#6A142A"  title=" Wikipedia"&gt;Catherine LARRÈRE&lt;/a&gt; est une philosophe française   professeure émérite de philosophie à Paris 1 Panthéon-Sorbonne et spécialisée en philosophie morale et politique, avec une attention particulière à l’éthique de l’environnement.&lt;/p&gt; &lt;p&gt; Elle a aporté une contribution majeure à l’essor de la philosophie environnementale en France, abordant des thèmes comme  &lt;a href="https://www.youtube.com/watch?v=YNxj0SXoNSo" style="color:#88A1E9" title="Qu'est-ce que la nature ? par Editions M-Editer"&gt;la protection de la nature&lt;/a&gt;, la prévention des risques et la justice environnementale. Engagement et leadership: présidente de la Fondation de l’écologie politique (2013-2016), un think-tank lié à &lt;a href="https://www.persee.fr/doc/ecoru_0013-0559_1999_num_249_1_5068_t1_0091_0000_2 " style="color:#88A1E9" title="Catherine Larrère Les philosophies de l'environnement  par Persée"&gt;Europe Écologie &lt;/a&gt; Les Verts, et commissaire scientifique de l’exposition Nature vive au Muséum national d’histoire naturelle (2001). &lt;/p&gt; &lt;p&gt; Ellle a publié largement sur Montesquieu, la philosophie morale et politique. Elle a aussi travaillé sur le rôle des femmes dans la société selon Rousseau et a collaboré étroitement avec son mari, Raphaël Larrère, agronome et écologue, sur des questions liées à l’environnement. Sa productivité académique est importante: articles, livres et chapitres, avec une présence notable dans les ressources bibliographiques et les bases de données spécialisées. Sa collaboration avec des chercheurs anglophones et ses traductions ont contribué à diffuser des idées clés de l’éthique de l’environnement en milieu francophone. &lt;/p&gt; &lt;p&gt; Elle continue d’être présente dans les débats publics et intellectuels sur l’environnement et l’éthique, notamment à travers des articles dans des revues et des plateformes spécialisées. &lt;/p&gt;   &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Catherine Larrère : "Ne pas s'occuper du social, c'est bloquer les solutions environnementales" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-07.02.2017-ITEMA_21221850-2017C19327S0038-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
  </t>
         </is>
       </c>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E21" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Marion"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean Luc MARION&lt;/a&gt; est un philosophe, phénoménologue et Membre de l’Académie française depuis 2008, il est reconnu pour sa tentative d’articuler la phénoménologie et la théologie dans ce qu’on a appelé le "tournant théologique de la phénoménologie française". &lt;/p&gt; &lt;p&gt; Il se revendique de la phénoménologie de Husserl et Heidegger, tout en l’orientant vers une réflexion sur la donation (le don). Pour lui, la phénoménologie doit s’intéresser non à l’être, mais à &lt;a href="https://www.youtube.com/watch?v=oS1vVjgKJOQ"  title=" Rencontre avec Jean-Luc Marion par KTO TV"&gt;ce qui se donne&lt;/a&gt;, et même à l’excès de ce don dans ce qu’il appelle les "phénomènes saturés".​  Cette approche déplace la question classique de l’être vers celle du don, où la subjectivité se laisse surprendre par ce qui se manifeste avant toute maîtrise conceptuelle. &lt;/p&gt; &lt;p&gt; Il développe cette idée dans des ouvrages majeurs comme "Réduction et donation" (1989), "Étant donné" (1998) et "De surcroît" (2001) ou la donation devient pour lui la condition de toute phénoménalité : les phénomènes les plus profonds (amour, art, révélation divine) excèdent la capacité de la conscience à les comprendre.​ Il renouvelle également la réflexion sur l’amour. Dans "Le Phénomène érotique" (2003), il propose que le sujet ne se fonde pas sur la conscience cartésienne mais sur "l’amour reçu et donné" qui devient ainsi le lieu de la véritable certitude de soi, en continuité critique avec Descartes et sous influence de Levinas. &lt;/p&gt; &lt;p&gt; Sa philosophie conjugue trois fils essentiels : &lt;/p&gt; &lt;p&gt;- une phénoménologie du don et de la révélation, où le monde se manifeste comme excès reçu. &lt;/p&gt; &lt;p&gt; -  une théologie philosophique, cherchant à penser Dieu hors du cadre métaphysique traditionnel. &lt;/p&gt; &lt;p&gt; - une éthique de l’amour, où autrui et la relation constituent la source du sens existentiel. &lt;/p&gt; &lt;p&gt; Spécialiste éminent de Descartes (notamment Sur la théologie blanche de Descartes et Sur la métaphysique grise de Descartes), il a aussi écrit des livres plus théologiques tels que "Dieu sans l’être" , "D’ailleurs, la Révélation" et a reçu de nombreuses distinctions, dont le Grand Prix de l’Académie française en 1992 et le Prix de la Principauté de Monaco en 2018. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Jean-Luc Marion : "La philosophie c’est de la course de fond, il faut en faire tous les jours, plusieurs heures" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-22.01.2021-ITEMA_22550575-2021C12410S0022.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Marion"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean Luc MARION&lt;/a&gt; est un philosophe, phénoménologue et Membre de l’Académie française depuis 2008, il est reconnu pour sa tentative d’articuler la phénoménologie et la théologie dans ce qu’on a appelé le "tournant théologique de la phénoménologie française". &lt;/p&gt; &lt;p&gt; Il se revendique de la phénoménologie de Husserl et Heidegger, tout en l’orientant vers une réflexion sur la donation (le don). Pour lui, la phénoménologie doit s’intéresser non à l’être, mais à &lt;a href="https://www.youtube.com/watch?v=oS1vVjgKJOQ"  title=" Rencontre avec Jean-Luc Marion par KTO TV"&gt;ce qui se donne&lt;/a&gt;, et même à l’excès de ce don dans ce qu’il appelle les "phénomènes saturés".​  Cette approche déplace la question classique de l’être vers celle du don, où la subjectivité se laisse surprendre par ce qui se manifeste avant toute maîtrise conceptuelle. &lt;/p&gt; &lt;p&gt; Il développe cette idée dans des ouvrages majeurs comme "Réduction et donation" (1989), "Étant donné" (1998) et "De surcroît" (2001) ou la donation devient pour lui la condition de toute phénoménalité : les phénomènes les plus profonds (amour, art, révélation divine) excèdent la capacité de la conscience à les comprendre.​ Il renouvelle également la réflexion sur l’amour. Dans "Le Phénomène érotique" (2003), il propose que le sujet ne se fonde pas sur la conscience cartésienne mais sur "l’amour reçu et donné" qui devient ainsi le lieu de la véritable certitude de soi, en continuité critique avec Descartes et sous influence de Levinas. &lt;/p&gt; &lt;p&gt; Sa philosophie conjugue trois fils essentiels : &lt;/p&gt; &lt;p&gt;- une phénoménologie du don et de la révélation, où le monde se manifeste comme excès reçu. &lt;/p&gt; &lt;p&gt; -  une théologie philosophique, cherchant à penser Dieu hors du cadre métaphysique traditionnel. &lt;/p&gt; &lt;p&gt; - une éthique de l’amour, où autrui et la relation constituent la source du sens existentiel. &lt;/p&gt; &lt;p&gt; Spécialiste éminent de Descartes (notamment Sur la théologie blanche de Descartes et Sur la métaphysique grise de Descartes), il a aussi écrit des livres plus théologiques tels que "Dieu sans l’être", "D’ailleurs, la Révélation" et a reçu de nombreuses distinctions, dont le Grand Prix de l’Académie française en 1992 et le Prix de la Principauté de Monaco en 2018. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Jean-Luc Marion : "La philosophie c’est de la course de fond, il faut en faire tous les jours, plusieurs heures" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-22.01.2021-ITEMA_22550575-2021C12410S0022.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="E22" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcel_Gauchet"  title=" Wikipedia"&gt;Marcel GAUCHET&lt;/a&gt;  est un philosophe, historien et sociologue  français connu pour ses travaux sur , &lt;a href="https://www.youtube.com/watch?v=48xW06Mm7JM&amp;t=4s "  title="Comment expliquer la crise de nos démocraties ? L'analyse de Marcel Gauchet par Le figaro"&gt;la démocratie &lt;/a&gt; , la religion et la sécularisation de l’Occident. Son œuvre cherche à comprendre les conditions politiques et culturelles qui permettent l’émergence et le fonctionnement des démocraties modernes, en particulier à partir du passage d’une société organique et religieuse à une société démocratique laïque. &lt;/p&gt; &lt;p&gt;  Il est une figure centrale du , &lt;a href="https://www.youtube.com/watch?v=Stn5k6P-uI8"  title="Marcel Gauchet, une pensée qui fâche ? par France Culture"&gt;paysage intellectuel &lt;/a&gt; français, dont les positions sur la “fin de la religion” et la démocratie ont suscité des débats et parfois des critiques, notamment autour de son oriention perçue par certains comme néoréactionnaire, qu’il réfute. Une de ses oeuvres marquantes est :  - "Le Désenchantement du monde" paru en 1985 – ouvrage majeur sur la sécularisation et le déclin de l’emprise de la religion dans les sociétés occidentales. &lt;/p&gt; &lt;p&gt; La démocratie moderne naît dans le cadre d’un processus historique complexe où l’émergence de l’individu et la réduction du rôle monopoly de la religion transforment les bases de l’autorité et de la légitimité politique. La religion, loin d’être annihilée, se transforme en une “religion de la sortie de la religion” qui structure encore les attentes morales et citoyennes, même lorsque l’emprise institutionnelle recule. &lt;/p&gt; &lt;p&gt; L’équilibre entre autonomie de l’individu et cohésion sociale demeure un défi central de la démocratie contemporaine, d’où l’attention soutenue de Gauchet pour les “fratures” et les tensions entre pluralisme démocratique et exigences communautaires.
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcel_Gauchet"  title=" Wikipedia"&gt;Marcel GAUCHET&lt;/a&gt;  est un philosophe, historien et sociologue  français connu pour ses travaux sur, &lt;a href="https://www.youtube.com/watch?v=48xW06Mm7JM&amp;t=4s "  title="Comment expliquer la crise de nos démocraties ? L'analyse de Marcel Gauchet par Le figaro"&gt;la démocratie&lt;/a&gt;, la religion et la sécularisation de l’Occident. Son œuvre cherche à comprendre les conditions politiques et culturelles qui permettent l’émergence et le fonctionnement des démocraties modernes, en particulier à partir du passage d’une société organique et religieuse à une société démocratique laïque. &lt;/p&gt; &lt;p&gt;  Il est une figure centrale du, &lt;a href="https://www.youtube.com/watch?v=Stn5k6P-uI8"  title="Marcel Gauchet, une pensée qui fâche ? par France Culture"&gt;paysage intellectuel &lt;/a&gt; français, dont les positions sur la “fin de la religion” et la démocratie ont suscité des débats et parfois des critiques, notamment autour de son oriention perçue par certains comme néoréactionnaire, qu’il réfute. Une de ses oeuvres marquantes est :  - "Le Désenchantement du monde" paru en 1985 – ouvrage majeur sur la sécularisation et le déclin de l’emprise de la religion dans les sociétés occidentales. &lt;/p&gt; &lt;p&gt; La démocratie moderne naît dans le cadre d’un processus historique complexe où l’émergence de l’individu et la réduction du rôle monopoly de la religion transforment les bases de l’autorité et de la légitimité politique. La religion, loin d’être annihilée, se transforme en une “religion de la sortie de la religion” qui structure encore les attentes morales et citoyennes, même lorsque l’emprise institutionnelle recule. &lt;/p&gt; &lt;p&gt; L’équilibre entre autonomie de l’individu et cohésion sociale demeure un défi central de la démocratie contemporaine, d’où l’attention soutenue de Gauchet pour les “fratures” et les tensions entre pluralisme démocratique et exigences communautaires.
  &lt;/p&gt;   &lt;audio controls title="Marcel Gauchet : "C'est l'exigence de comprendre mon temps qui m'a conduit à une réflexion sur l'histoire, en philosophe" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11189-30.05.2011-ITEMA_20288351-2011C15000E0083-ITE_00042075_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
@@ -1997,7 +1997,7 @@
       <c r="E23" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dany-Robert_Dufour"  title=" Wikipedia"&gt;Dany-Robert DUFOUR&lt;/a&gt; est un philosophe français  principalement connu pour ses analyses critiques du  &lt;a href="https://www.youtube.com/watch?v=P7_LuqNO0Zg"  title=" CAPITALISME, Dany-Robert Dufour par abc penser"&gt;capitalisme néolibéral&lt;/a&gt; et ses réflexions sur les systèmes symboliques, à l’intersection de la philosophie politique, du langage et de la psychanalyse. Il travaille à l'Université de Paris et dans d'autres pays tels que le Brésil, le Mexique et la Colombie. &lt;/p&gt; &lt;p&gt; 
-Le thème principal de ses œuvres est le sujet de la société postmoderne et les problèmes auxquels il est confronté. Dans &lt;a href="http://www.dany-robert-dufour.fr/" title="Robert Dufour "&gt;ses œuvres&lt;/a&gt; "Le Divin Marché" ,  "La révolution culturelle libérale" et  "La cité perverse - libéralisme et pornographie", le philosophe défend que la société contemporaine est basée sur des &lt;a href="https://www.youtube.com/watch?v=xUT0q2sk3lc" title=" Le phénomène trans I Dany Robert Dufour par Cercle Aristote"&gt; principes amoraux&lt;/a&gt; et que la crise culturelle a rendu possible des crises économiques comme celle de 2008. La société moderne a évolué de manière alarmante et le sujet n’a pas de modèles ou de leaders. Il propose une lecture radicale et engagée de l’évolution culturelle et politique contemporaine, interrogeant la place des symboles et la crise du sens à l’ère du capitalisme mondialisé.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.actu-philosophia.com/entretien-avec-dany-robert-dufour/"  title="Entretien avec Dany-Robert Dufour par actu philosopphia"&gt;  Sa réflexion&lt;/a&gt; s’inscrit dans une critique du structuralisme et du post-structuralisme, qu’il analyse comme favorisant la désymbolisation et un affaiblissement des repères pour la société.​ Il développe une pensée du "Tiers symbolique", considérant que toute relation entre deux termes (ex : sujet/objet) suppose un tiers pour garantir sens et cohésion, contrairement à la logique binaire des systèmes et des algorithmes contemporains.​​ &lt;/p&gt; &lt;p&gt;  Il propose une lecture critique du néolibéralisme, en montrant comment il affecte les subjectivités et les structures symboliques collectives, par une "illimitation du désir" et une apologie de l’individualisme sans limite.​ Il explore l’histoire de la philosophie et ses incidences sur l’époque contemporaine, avec un intérêt pour l’économie, la linguistique, la psychanalyse et la politique. &lt;/p&gt; &lt;audio controls title=" De la transgression à la perversion par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-10.01.2024-ITEMA_23609669-2024C48904S0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+Le thème principal de ses œuvres est le sujet de la société postmoderne et les problèmes auxquels il est confronté. Dans &lt;a href="http://www.dany-robert-dufour.fr/" title="Robert Dufour "&gt;ses œuvres&lt;/a&gt; "Le Divin Marché",  "La révolution culturelle libérale" et  "La cité perverse - libéralisme et pornographie", le philosophe défend que la société contemporaine est basée sur des &lt;a href="https://www.youtube.com/watch?v=xUT0q2sk3lc" title=" Le phénomène trans I Dany Robert Dufour par Cercle Aristote"&gt; principes amoraux&lt;/a&gt; et que la crise culturelle a rendu possible des crises économiques comme celle de 2008. La société moderne a évolué de manière alarmante et le sujet n’a pas de modèles ou de leaders. Il propose une lecture radicale et engagée de l’évolution culturelle et politique contemporaine, interrogeant la place des symboles et la crise du sens à l’ère du capitalisme mondialisé.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.actu-philosophia.com/entretien-avec-dany-robert-dufour/"  title="Entretien avec Dany-Robert Dufour par actu philosopphia"&gt;  Sa réflexion&lt;/a&gt; s’inscrit dans une critique du structuralisme et du post-structuralisme, qu’il analyse comme favorisant la désymbolisation et un affaiblissement des repères pour la société.​ Il développe une pensée du "Tiers symbolique", considérant que toute relation entre deux termes (ex : sujet/objet) suppose un tiers pour garantir sens et cohésion, contrairement à la logique binaire des systèmes et des algorithmes contemporains.​​ &lt;/p&gt; &lt;p&gt;  Il propose une lecture critique du néolibéralisme, en montrant comment il affecte les subjectivités et les structures symboliques collectives, par une "illimitation du désir" et une apologie de l’individualisme sans limite.​ Il explore l’histoire de la philosophie et ses incidences sur l’époque contemporaine, avec un intérêt pour l’économie, la linguistique, la psychanalyse et la politique. &lt;/p&gt; &lt;audio controls title=" De la transgression à la perversion par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-10.01.2024-ITEMA_23609669-2024C48904S0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E25" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Bruckner"  title=" Wikipedia"&gt;Pascal BRUCKNER&lt;/a&gt;  est un philosophe , essayiste et romancier français figure des "nouveaux philosophes" des années 1970 et membre de l’Académie Goncourt depuis 2019. Il fustige la "tyrannie de la culpabilité" occidentale, le victimarisme contemporain et les excès du wokisme. &lt;/p&gt; &lt;p&gt; Il est un philosophe critique de &lt;a href="https://www.revuedesdeuxmondes.fr/pascal-bruckner-declinisme-et-catastrophisme-provoquent-des-ravages-dans-nos-esprits/" title="Pascal Bruckner : Déclinisme et catastrophisme provoquent des ravages dans nos esprits par Revue des deux mondes"&gt;l’auto-flagellation occidentale, &lt;/a&gt; défendant une forme de libéralisme éclairé qui rejette à la fois le tiers-mondisme culpabilisant, le victimarisme contemporain et les excès anticapitalistes. Pro-israélien et atlantiste, il défend l’héritage des Lumières contre les &lt;a href="https://www.youtube.com/watch?v=wNrAmA6zIQU"  title="L’homme blanc, de l’intouchable au bouc émissaire avec Pascal Bruckner par France Culture"&gt;idéologies déconstructrices, &lt;/a&gt;  tout en explorant paradoxalement les mythologies sexuelles post-68. Dès 1977, avec Finkielkraut, il publie "Le Nouveau Désordre amoureux", critique des utopies amoureuses post-68, qui le propulse dans le paysage intellectuel. &lt;/p&gt; &lt;p&gt; Son essai "Le Sanglot de l’homme blanc" paru en 1983 dénonce le tiers-mondisme culpabilisant de l’Occident, marquant son éloignement de la gauche libertaire pour un positionnement néoconservateur. Il critique ensuite l’auto-flagellation occidentale dans "La Tyrannie de la pénitence" paru en  2006 et l’anticapitalisme dans "Misère de la prospérité" paru en 2002. &lt;/p&gt;  &lt;audio controls title="Pascal Bruckner, au fil de la plume par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-06.06.2021-ITEMA_22685386-2021C3500E0081.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Bruckner"  title=" Wikipedia"&gt;Pascal BRUCKNER&lt;/a&gt;  est un philosophe, essayiste et romancier français figure des "nouveaux philosophes" des années 1970 et membre de l’Académie Goncourt depuis 2019. Il fustige la "tyrannie de la culpabilité" occidentale, le victimarisme contemporain et les excès du wokisme. &lt;/p&gt; &lt;p&gt; Il est un philosophe critique de &lt;a href="https://www.revuedesdeuxmondes.fr/pascal-bruckner-declinisme-et-catastrophisme-provoquent-des-ravages-dans-nos-esprits/" title="Pascal Bruckner : Déclinisme et catastrophisme provoquent des ravages dans nos esprits par Revue des deux mondes"&gt;l’auto-flagellation occidentale, &lt;/a&gt; défendant une forme de libéralisme éclairé qui rejette à la fois le tiers-mondisme culpabilisant, le victimarisme contemporain et les excès anticapitalistes. Pro-israélien et atlantiste, il défend l’héritage des Lumières contre les &lt;a href="https://www.youtube.com/watch?v=wNrAmA6zIQU"  title="L’homme blanc, de l’intouchable au bouc émissaire avec Pascal Bruckner par France Culture"&gt;idéologies déconstructrices, &lt;/a&gt;  tout en explorant paradoxalement les mythologies sexuelles post-68. Dès 1977, avec Finkielkraut, il publie "Le Nouveau Désordre amoureux", critique des utopies amoureuses post-68, qui le propulse dans le paysage intellectuel. &lt;/p&gt; &lt;p&gt; Son essai "Le Sanglot de l’homme blanc" paru en 1983 dénonce le tiers-mondisme culpabilisant de l’Occident, marquant son éloignement de la gauche libertaire pour un positionnement néoconservateur. Il critique ensuite l’auto-flagellation occidentale dans "La Tyrannie de la pénitence" paru en  2006 et l’anticapitalisme dans "Misère de la prospérité" paru en 2002. &lt;/p&gt;  &lt;audio controls title="Pascal Bruckner, au fil de la plume par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-06.06.2021-ITEMA_22685386-2021C3500E0081.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F25" s="34" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E27" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Jambet"  title=" Wikipedia"&gt;Christian JAMBET&lt;/a&gt; est un philosophe et islamologue  français reconnu pour ses travaux qui font le pont entre la philosophie occidentale et la pensée islamique, en particulier le chiisme. Agrégé de philosophie et ancien élève d'Henry Corbin, un spécialiste de &lt;a href="https://fr.wikipedia.org/wiki/Islam_en_Iran"  title=" Islam en Iran par Wikipedia"&gt;l'islam iranien&lt;/a&gt;, il a consacré sa carrière à l'étude des traditions philosophiques et spirituelles de l'Islam, notamment celles de l'Iran. Il est devenu membre de l'Académie française en 2024. Son travail se distingue par sa profondeur et son caractère interdisciplinaire. Ses contributions majeures portent sur :&lt;/p&gt; &lt;p&gt; - La philosophie islamique : Il a montré qu'il existe une tradition philosophique riche et autonome en terre d'Islam, souvent mal comprise ou négligée en Occident. Il a mis en lumière les liens, mais aussi les spécificités, entre la pensée grecque (notamment platonicienne) et les penseurs islamiques. Son ouvrage Qu'est-ce que la philosophie islamique ? est une référence dans ce domaine. &lt;/p&gt; &lt;p&gt; - Le chiisme et le soufisme : il est un expert du chiisme, qu'il étudie non seulement sous son aspect politique et théologique, mais aussi dans sa dimension philosophique et spirituelle. Il a beaucoup travaillé sur la figure du  &lt;a href="https://www.youtube.com/watch?v=kQzLVldS4PU"  title="L'immortalité de l'âme selon Mulla Sadra, Christian Jambet Les vivants et les dieux par Facteur"&gt; philosophe iranien Mullâ Sadrâ Shîrâzî&lt;/a&gt; , qu'il considère comme un des plus grands métaphysiciens de l'histoire. Il explore les concepts de l'ésotérisme (bātin) et de l'exotérisme (zahir), montrant comment la philosophie chiite a développé une pensée de la liberté et de l'intériorité face à l'orthodoxie religieuse. &lt;/p&gt; &lt;p&gt; - La philosophie politique : Il s'intéresse aux conceptions du pouvoir et du droit dans l'Islam. Dans son livre Le gouvernement divin, il analyse la relation entre la théologie et le politique, et les différentes manières dont le pouvoir a été conceptualisé dans le chiisme. &lt;/p&gt; &lt;p&gt; - Les concepts de l'« Ange » et de l'« imagination créatrice » : Reprenant les travaux d'Henry Corbin, il a exploré le rôle central de l'imagination dans la connaissance et l'expérience religieuse. Pour Jambet, l'imagination n'est pas une simple faculté de fiction, mais un organe de perception capable d'accéder à un monde intermédiaire, peuplé d'êtres spirituels comme les Anges. &lt;/p&gt; &lt;p&gt;  Il a publié différents ouvrages dont "L'Ange" paru en 1976 co-écrit avec Guy Lardreau ainsi que "La Logique des Orientaux"  paru en 1983  sans oublié "La Grande Résurrection d'Alamût"  paru en 1990, sur les formes de la liberté dans le shî'isme ismaélien. &lt;/p&gt;  &lt;audio controls title=" La philosophie islamique avec Christian Jambet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-12.02.2012-ITEMA_20344279-2012C14958E0004-ITE_00049063_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Jambet"  title=" Wikipedia"&gt;Christian JAMBET&lt;/a&gt; est un philosophe et islamologue  français reconnu pour ses travaux qui font le pont entre la philosophie occidentale et la pensée islamique, en particulier le chiisme. Agrégé de philosophie et ancien élève d'Henry Corbin, un spécialiste de &lt;a href="https://fr.wikipedia.org/wiki/Islam_en_Iran"  title=" Islam en Iran par Wikipedia"&gt;l'islam iranien&lt;/a&gt;, il a consacré sa carrière à l'étude des traditions philosophiques et spirituelles de l'Islam, notamment celles de l'Iran. Il est devenu membre de l'Académie française en 2024. Son travail se distingue par sa profondeur et son caractère interdisciplinaire. Ses contributions majeures portent sur :&lt;/p&gt; &lt;p&gt; - La philosophie islamique : Il a montré qu'il existe une tradition philosophique riche et autonome en terre d'Islam, souvent mal comprise ou négligée en Occident. Il a mis en lumière les liens, mais aussi les spécificités, entre la pensée grecque (notamment platonicienne) et les penseurs islamiques. Son ouvrage Qu'est-ce que la philosophie islamique ? est une référence dans ce domaine. &lt;/p&gt; &lt;p&gt; - Le chiisme et le soufisme : il est un expert du chiisme, qu'il étudie non seulement sous son aspect politique et théologique, mais aussi dans sa dimension philosophique et spirituelle. Il a beaucoup travaillé sur la figure du  &lt;a href="https://www.youtube.com/watch?v=kQzLVldS4PU"  title="L'immortalité de l'âme selon Mulla Sadra, Christian Jambet Les vivants et les dieux par Facteur"&gt; philosophe iranien Mullâ Sadrâ Shîrâzî&lt;/a&gt;, qu'il considère comme un des plus grands métaphysiciens de l'histoire. Il explore les concepts de l'ésotérisme (bātin) et de l'exotérisme (zahir), montrant comment la philosophie chiite a développé une pensée de la liberté et de l'intériorité face à l'orthodoxie religieuse. &lt;/p&gt; &lt;p&gt; - La philosophie politique : Il s'intéresse aux conceptions du pouvoir et du droit dans l'Islam. Dans son livre Le gouvernement divin, il analyse la relation entre la théologie et le politique, et les différentes manières dont le pouvoir a été conceptualisé dans le chiisme. &lt;/p&gt; &lt;p&gt; - Les concepts de l'« Ange » et de l'« imagination créatrice » : Reprenant les travaux d'Henry Corbin, il a exploré le rôle central de l'imagination dans la connaissance et l'expérience religieuse. Pour Jambet, l'imagination n'est pas une simple faculté de fiction, mais un organe de perception capable d'accéder à un monde intermédiaire, peuplé d'êtres spirituels comme les Anges. &lt;/p&gt; &lt;p&gt;  Il a publié différents ouvrages dont "L'Ange" paru en 1976 co-écrit avec Guy Lardreau ainsi que "La Logique des Orientaux"  paru en 1983  sans oublié "La Grande Résurrection d'Alamût"  paru en 1990, sur les formes de la liberté dans le shî'isme ismaélien. &lt;/p&gt;  &lt;audio controls title=" La philosophie islamique avec Christian Jambet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-12.02.2012-ITEMA_20344279-2012C14958E0004-ITE_00049063_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="E31" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Roger-Pol_Droit"   title=" Wikipedia"&gt;Roger-Pol DROIT&lt;/a&gt; est un philosophe et écrivain français connu à la fois pour ses travaux de recherche et pour ses livres de vulgarisation qui  &lt;a href="https://rpdroit.com/"   title="Roger-Pol DROIT"&gt; rendent la philosophie accessible &lt;/a&gt; à un large public. Sa philosophie ne se présente pas comme un système fermé, mais comme une manière d’ouvrir les questions, de faire dialoguer les idées et de montrer que penser est une activité vivante. Dans ses ouvrages d’initiation, il cherche à expliquer la pensée sans jargon, avec clarté et souvent avec pédagogie, comme dans La philosophie expliquée à ma fille ou &lt;a href="https://www.youtube.com/watch?v=I-GcL40sLGg"   title="Il nous parle de philosophie par Bibliothèque de poche"&gt; Une brève histoire de la philosophie &lt;/a&gt; . Pour lui, la philosophie n’est pas réservée aux spécialistes : elle commence par l’étonnement, la curiosité et le besoin de comprendre. &lt;/p&gt; &lt;p&gt; Il insiste sur le dialogue et l’exercice de l’objection et il voit la pensée comme une conversation intérieure et extérieure, où l’on apprend à examiner une idée, à la contredire, puis à la reformuler. Cette approche apparaît aussi dans ses récits philosophiques, qui mêlent réflexion, humour et narration pour faire sentir que penser engage toute la vie intérieure. &lt;/p&gt; &lt;p&gt; Un autre axe important de son travail est l’ouverture aux philosophies du monde. Il s’est intéressé aux rapports entre la pensée occidentale et les traditions venues d’ailleurs, notamment aux représentations des philosophies non occidentales dans la culture européenne. Son livre &lt;a href="https://www.youtube.com/watch?v=NF9rLrveAbI"   title="Roger-Pol DROIT par editions albin michel"&gt; Un voyage dans les philosophies du monde &lt;/a&gt; va dans ce sens : il montre que la philosophie ne se limite pas à l’Europe et qu’elle prend des formes multiples selon les cultures. &lt;/p&gt; &lt;p&gt; Sa démarche est profondément humaniste. Il relie la philosophie aux inquiétudes concrètes du présent, à la liberté, à la vie commune, aux limites de l’action et aux questions morales. Chez lui, philosopher ne consiste pas seulement à produire des concepts, mais à apprendre à mieux vivre, à mieux juger et à mieux habiter le monde. &lt;/&gt; 
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Roger-Pol_Droit"   title=" Wikipedia"&gt;Roger-Pol DROIT&lt;/a&gt; est un philosophe et écrivain français connu à la fois pour ses travaux de recherche et pour ses livres de vulgarisation qui  &lt;a href="https://rpdroit.com/"   title="Roger-Pol DROIT"&gt; rendent la philosophie accessible &lt;/a&gt; à un large public. Sa philosophie ne se présente pas comme un système fermé, mais comme une manière d’ouvrir les questions, de faire dialoguer les idées et de montrer que penser est une activité vivante. Dans ses ouvrages d’initiation, il cherche à expliquer la pensée sans jargon, avec clarté et souvent avec pédagogie, comme dans La philosophie expliquée à ma fille ou &lt;a href="https://www.youtube.com/watch?v=I-GcL40sLGg"   title="Il nous parle de philosophie par Bibliothèque de poche"&gt; Une brève histoire de la philosophie&lt;/a&gt;. Pour lui, la philosophie n’est pas réservée aux spécialistes : elle commence par l’étonnement, la curiosité et le besoin de comprendre. &lt;/p&gt; &lt;p&gt; Il insiste sur le dialogue et l’exercice de l’objection et il voit la pensée comme une conversation intérieure et extérieure, où l’on apprend à examiner une idée, à la contredire, puis à la reformuler. Cette approche apparaît aussi dans ses récits philosophiques, qui mêlent réflexion, humour et narration pour faire sentir que penser engage toute la vie intérieure. &lt;/p&gt; &lt;p&gt; Un autre axe important de son travail est l’ouverture aux philosophies du monde. Il s’est intéressé aux rapports entre la pensée occidentale et les traditions venues d’ailleurs, notamment aux représentations des philosophies non occidentales dans la culture européenne. Son livre &lt;a href="https://www.youtube.com/watch?v=NF9rLrveAbI"   title="Roger-Pol DROIT par editions albin michel"&gt; Un voyage dans les philosophies du monde &lt;/a&gt; va dans ce sens : il montre que la philosophie ne se limite pas à l’Europe et qu’elle prend des formes multiples selon les cultures. &lt;/p&gt; &lt;p&gt; Sa démarche est profondément humaniste. Il relie la philosophie aux inquiétudes concrètes du présent, à la liberté, à la vie commune, aux limites de l’action et aux questions morales. Chez lui, philosopher ne consiste pas seulement à produire des concepts, mais à apprendre à mieux vivre, à mieux juger et à mieux habiter le monde. &lt;/&gt; 
  &lt;audio controls title="un équilibre instable entre la négatif et le positif par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16173-20.05.2025-ITEMA_24141042-2025F26104S0140-NET_MFI_83506534-46B8-430C-8970-C247B9C3C4C4-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E33" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Mich%C3%A9a"   title=" Wikipedia"&gt;Jean-Claude MICHEA&lt;/a&gt; est un philosophe français issus d'un milieu ouvrier qui se décrit comme un "démocrate radical". Il est connu pour ses analyses critiques de la société contemporaine, de la politique et de l'économie. Considéré comme un penseur de gauche, bien qu'il se distingue souvent des courants dominants de la gauche.&lt;/p&gt; &lt;p&gt; Il s'est intéressé dès ses débuts à la pensée marxiste et à la critique du capitalisme. Cependant, il s'est également inspiré d'autres courants de pensée, tels que l'anarchisme, pour développer sa propre vision politique. Il a écrit &lt;a href="https://www.youtube.com/watch?v=XnfQVE-8K-E"   title="L'enseignement de l'ignorance par Eveilleur de conscience"&gt; "L'enseignement de l'ignorance" &lt;/a&gt; et ses conditions modernes (1999), dans lequel il critique le système éducatif moderne et les politiques néolibérales qui selon lui contribuent à l'ignorance et à l'aliénation des individus ainsi que &lt;a href="https://www.youtube.com/watch?v=igU_2VY3wSQ&amp;ab_channel=MichelDrac"  style="color:#88A1E9"  title="Notre ennemi le capital par Michel Drac"&gt; "Notre ennemi, le capital" &lt;/a&gt; , "La double pensée" qui sont des écrits critiques sur la gauche et la société moderne.&lt;/p&gt; &lt;p&gt;  Pour lui, le libéralisme en tant que doctrine politique et économique est une idéologie qui vante les mérites de la liberté individuelle, du marché et de la concurrence, mais qui  aboutit à une société de plus en plus individualiste, désocialisée et inégalitaire, c'est  &lt;a href="https://www.youtube.com/watch?v=xMM8pw5p6Ms&amp;t=1192s&amp;ab_channel=LePr%C3%A9cepteur"  title="La religion du progrès par le Précepteur"&gt; " La religion du progrès " &lt;/a&gt;. &lt;/p&gt; &lt;p&gt;  Michéa met souvent l'accent sur la défense de la culture populaire et de la tradition, qu'il considère comme des valeurs essentielles pour la préservation des communautés locales et de la diversité culturelle. Il s'oppose à la mondialisation et à l'homogénéisation culturelle qui en découle, ainsi qu'à l'idée du progrès linéaire et de la croissance économique illimitée.&lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Mich%C3%A9a"   title=" Wikipedia"&gt;Jean-Claude MICHEA&lt;/a&gt; est un philosophe français issus d'un milieu ouvrier qui se décrit comme un "démocrate radical". Il est connu pour ses analyses critiques de la société contemporaine, de la politique et de l'économie. Considéré comme un penseur de gauche, bien qu'il se distingue souvent des courants dominants de la gauche.&lt;/p&gt; &lt;p&gt; Il s'est intéressé dès ses débuts à la pensée marxiste et à la critique du capitalisme. Cependant, il s'est également inspiré d'autres courants de pensée, tels que l'anarchisme, pour développer sa propre vision politique. Il a écrit &lt;a href="https://www.youtube.com/watch?v=XnfQVE-8K-E"   title="L'enseignement de l'ignorance par Eveilleur de conscience"&gt; "L'enseignement de l'ignorance" &lt;/a&gt; et ses conditions modernes (1999), dans lequel il critique le système éducatif moderne et les politiques néolibérales qui selon lui contribuent à l'ignorance et à l'aliénation des individus ainsi que &lt;a href="https://www.youtube.com/watch?v=igU_2VY3wSQ&amp;ab_channel=MichelDrac"  style="color:#88A1E9"  title="Notre ennemi le capital par Michel Drac"&gt; "Notre ennemi, le capital"&lt;/a&gt;, "La double pensée" qui sont des écrits critiques sur la gauche et la société moderne.&lt;/p&gt; &lt;p&gt;  Pour lui, le libéralisme en tant que doctrine politique et économique est une idéologie qui vante les mérites de la liberté individuelle, du marché et de la concurrence, mais qui  aboutit à une société de plus en plus individualiste, désocialisée et inégalitaire, c'est  &lt;a href="https://www.youtube.com/watch?v=xMM8pw5p6Ms&amp;t=1192s&amp;ab_channel=LePr%C3%A9cepteur"  title="La religion du progrès par le Précepteur"&gt; " La religion du progrès "&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;  Michéa met souvent l'accent sur la défense de la culture populaire et de la tradition, qu'il considère comme des valeurs essentielles pour la préservation des communautés locales et de la diversité culturelle. Il s'oppose à la mondialisation et à l'homogénéisation culturelle qui en découle, ainsi qu'à l'idée du progrès linéaire et de la croissance économique illimitée.&lt;/p&gt;
   &lt;audio controls title="La chance d'avoir des parents communistes par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-07.01.2019-ITEMA_21943913-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
@@ -2903,7 +2903,7 @@
       <c r="E37" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Didi-Huberman" style="color:#6A142A"  title=" Wikipedia"&gt;Georges DIDI-HUBERMAN&lt;/a&gt; est un philosophe &amp; historien de l'art français spécialiste de la théorie des images et figure majeure de la pensée contemporaine sur le visuel. Il est aujourd’hui considéré comme l’un des théoriciens de l’image les plus importants en France, avec une reconnaissance internationale. &lt;/p&gt; &lt;p&gt; Ses travaux portent sur l’histoire et la théorie des images, de la Renaissance à l’art contemporain, avec une attention aux liens entre images, savoir et pouvoir. Sa démarche relève d’une "archéologie du savoir visuel"  car il cherche à comprendre comment les images construisent une mémoire, une sensibilité et des formes de pensée. &lt;/p&gt; &lt;p&gt; Pour lui, les images ne sont pas seulement des objets à regarder, mais des actes qui engagent le corps, la mémoire,&lt;a href="https://www.youtube.com/watch?v=DUNo6xZkaCo" style="color:#88A1E9" title="
-L'historien de l'art Georges Didi-Huberman explique la fabrique de nos affects par les images par France Culture"&gt; l’affect et l’histoire &lt;/a&gt;. Il insiste sur leu profondeur car il ne s’agit pas seulement de ce qui est visible en surface, mais de ce qui travaille en dessous, dans les couches de sens, de mémoire, de trauma. Il réfléchit aussi à une éthique du regard, comment voir sans réduire, sans consommer l’image, en respectant ce qu’elle expose de vulnérable, de politique, ou de souffrant. &lt;/p&gt; &lt;p&gt;De nombreux ouvrages sur Warburg, Fra Angelico, le Baroque, la mémoire de la Shoah, les images de catastrophes et de survivants, etc. Une série de livres et de projets sur les ,&lt;a href="https://www.youtube.com/watch?v=vKMAHj_kvY8" style="color:#88A1E9" title="Georges Didi-Huberman, SOULÈVEMENT par ABC Penser"&gt; "soulèvements", &lt;/a&gt; où il s’intéresse aux gestes de révolte, aux mouvements collectifs, et à la manière dont les images peuvent porter la voix des sans-voix et lutter contre l’amnésie historique. &lt;/p&gt; &lt;p&gt; Sa réflexion sur les "soulèvements" l’amène à articuler philosophie de l’image et engagement politique : comment des images peuvent accompagner des luttes, préserver des mémoires, donner forme à des désirs de transformation sociale. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Dans la bibliothèque de Georges Didi-Huberman par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23875-11.10.2024-ITEMA_23889638-2024C49162E0034-NET_MFC_8E518A6F-A0BF-49D3-BFEA-B88C4BE3FE7F-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+L'historien de l'art Georges Didi-Huberman explique la fabrique de nos affects par les images par France Culture"&gt; l’affect et l’histoire&lt;/a&gt;. Il insiste sur leu profondeur car il ne s’agit pas seulement de ce qui est visible en surface, mais de ce qui travaille en dessous, dans les couches de sens, de mémoire, de trauma. Il réfléchit aussi à une éthique du regard, comment voir sans réduire, sans consommer l’image, en respectant ce qu’elle expose de vulnérable, de politique, ou de souffrant. &lt;/p&gt; &lt;p&gt;De nombreux ouvrages sur Warburg, Fra Angelico, le Baroque, la mémoire de la Shoah, les images de catastrophes et de survivants, etc. Une série de livres et de projets sur les,&lt;a href="https://www.youtube.com/watch?v=vKMAHj_kvY8" style="color:#88A1E9" title="Georges Didi-Huberman, SOULÈVEMENT par ABC Penser"&gt; "soulèvements", &lt;/a&gt; où il s’intéresse aux gestes de révolte, aux mouvements collectifs, et à la manière dont les images peuvent porter la voix des sans-voix et lutter contre l’amnésie historique. &lt;/p&gt; &lt;p&gt; Sa réflexion sur les "soulèvements" l’amène à articuler philosophie de l’image et engagement politique : comment des images peuvent accompagner des luttes, préserver des mémoires, donner forme à des désirs de transformation sociale. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Dans la bibliothèque de Georges Didi-Huberman par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23875-11.10.2024-ITEMA_23889638-2024C49162E0034-NET_MFC_8E518A6F-A0BF-49D3-BFEA-B88C4BE3FE7F-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="E44" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_M%C3%A9da" title=" Wikipedia"&gt;Dominique MÉDA&lt;/a&gt;  est une philosophe française  reconnue pour ses analyses critiques sur le travail, les politiques sociales et la  &lt;a href="https://www.youtube.com/watch?v=jzyFjl0_QQE" title="La vraie révolution, c'est de désintensifier le travail ! Dominique Méda par Metabolism of Cities"&gt;transition écologique &lt;/a&gt;, elle combine une formation d'élite avec un engagement intellectuel profond sur les inégalités et la mesure de la richesse sociétale.  Elle est professeure de &lt;a href="https://www.youtube.com/watch?v=vKGU1tCOW90"  title="Dominique Méda, une sociologie contemporaine par Anthropologiques"&gt; sociologie &lt;/a&gt; à l'université Paris Dauphine-PSL, dirige l'IRISSO et a occupé la chaire "Reconversion écologique, travail et emploi" au Collège d'études mondiales. Elle fonde en 2010 le Laboratoire de l'égalité professionnelle entre femmes et hommes. &lt;/p&gt; &lt;p&gt; Ses travaux interrogent la centralité du travail dans les sociétés modernes, critiquant son rôle comme norme sociale totale et plaidant pour sa réduction au profit d'autres activités. Elle dénonce les limites du PIB comme indicateur de richesse, proposant des alternatives incluant le travail domestique, familial et écologique. Depuis les années 2010, elle se focalise sur la transition écologique, les inégalités de genre dans l'emploi et les réformes du travail  comme la flexisécurité. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"Le travail, une valeur en voie de disparition ?" paru en  1995 : histoire philosophique du concept de travail et plaidoyer pour sa redéfinition. - "Qu'est-ce que la richesse ?" paru en 1999 : critique des indicateurs économiques traditionnels. - "La reconversion écologique"(ouvrages récents) : lien entre écologie, emploi et justice sociale. &lt;/p&gt; &lt;audio controls title="Sandra LAUGIER par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11189-26.03.2012-ITEMA_20355259-2012C15000E0020-ITE_00049197_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_M%C3%A9da" title=" Wikipedia"&gt;Dominique MÉDA&lt;/a&gt;  est une philosophe française  reconnue pour ses analyses critiques sur le travail, les politiques sociales et la  &lt;a href="https://www.youtube.com/watch?v=jzyFjl0_QQE" title="La vraie révolution, c'est de désintensifier le travail ! Dominique Méda par Metabolism of Cities"&gt;transition écologique&lt;/a&gt;, elle combine une formation d'élite avec un engagement intellectuel profond sur les inégalités et la mesure de la richesse sociétale.  Elle est professeure de &lt;a href="https://www.youtube.com/watch?v=vKGU1tCOW90"  title="Dominique Méda, une sociologie contemporaine par Anthropologiques"&gt; sociologie &lt;/a&gt; à l'université Paris Dauphine-PSL, dirige l'IRISSO et a occupé la chaire "Reconversion écologique, travail et emploi" au Collège d'études mondiales. Elle fonde en 2010 le Laboratoire de l'égalité professionnelle entre femmes et hommes. &lt;/p&gt; &lt;p&gt; Ses travaux interrogent la centralité du travail dans les sociétés modernes, critiquant son rôle comme norme sociale totale et plaidant pour sa réduction au profit d'autres activités. Elle dénonce les limites du PIB comme indicateur de richesse, proposant des alternatives incluant le travail domestique, familial et écologique. Depuis les années 2010, elle se focalise sur la transition écologique, les inégalités de genre dans l'emploi et les réformes du travail  comme la flexisécurité. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"Le travail, une valeur en voie de disparition ?" paru en  1995 : histoire philosophique du concept de travail et plaidoyer pour sa redéfinition. - "Qu'est-ce que la richesse ?" paru en 1999 : critique des indicateurs économiques traditionnels. - "La reconversion écologique"(ouvrages récents) : lien entre écologie, emploi et justice sociale. &lt;/p&gt; &lt;audio controls title="Sandra LAUGIER par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11189-26.03.2012-ITEMA_20355259-2012C15000E0020-ITE_00049197_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 ​
 </t>
         </is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="E45" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Florence_Burgat"  title=" Wikipedia"&gt;Florence BURGAT&lt;/a&gt; est une philosophe française spécialisée dans la phénoménologie de la vie animale et l’éthique animale. Son itinéraire académique comprend une formation en philosophie et une implication dans des laboratoires et équipes de recherche en sciences humaines, avec des décennies d’activité comme directrice de recherche et enseignante dans des institutions françaises de haut niveau. &lt;/p&gt; &lt;p&gt; "Liberté et inquiétude de la vie animale" paru en 2006 et "Une autre existence" paru en 2012 sont parmi ses essais-clés. Ils proposent une phénoménologie de l’animal qui attribue aux animaux une vie vécue, une biographie et un monde propre, en opposition à une conception purement biologique ou fonctionnelle de l’animalité. Son approche met en lumière la distinction entre vivre en première personne et exister biologiquement, et elle s’interroge sur la place des animaux dans les sociétés modernes — notamment dans les pratiques d’élevage, &lt;a href="https://reporterre.net/Florence-Burgat-L-institution-de-l-alimentation-carnee-reflete-un-desir-tres " title="Florence Burgat : « L’institution de l’alimentation carnée reflète un désir très profond de l’humanité  par Reportere"&gt;l’alimentation carnée &lt;/a&gt;, le droit animalier et les enjeux éthiques qui en découlent. Elle a aussi écrit sur la vie végétale et a développé une réflexion sur l’institution de l’alimentation carnée, la notion de sacrifice et les mythes qui entourent l’humanité carnivore, élargissant ainsi la portée philosophique de &lt;a href="https://www.youtube.com/watch?v=AzVErgOotx0" title=" Idées: Carnivore, l'Humanité n'est pas dans son assiette? par TV5Monde"&gt;l’éthique animale &lt;/a&gt; à des domaines comme la nourriture, le droit et la société. &lt;/p&gt; &lt;p&gt; Elle a publié et contribué à des revues et ouvrages dédiés à la philosophie contemporaine et à l’éthique animale. Elle est souvent associée à des discussions sur la manière dont les sociétés humaines reconnaissent ou nüancent l’existence des autres vivants et comment cela influence les pratiques culturelles et juridiques. Son travail est référencé dans des bibliographies universitaires et chez des éditeurs de sciences humaines, ce qui en fait une voix importante pour ceux qui s’interrogent sur la dignité et la vie des êtres non humains dans un cadre éthique et philosophique. &lt;/p&gt;   &lt;audio controls title="L’éthique animale avec Florence Burgat par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Florence_Burgat"  title=" Wikipedia"&gt;Florence BURGAT&lt;/a&gt; est une philosophe française spécialisée dans la phénoménologie de la vie animale et l’éthique animale. Son itinéraire académique comprend une formation en philosophie et une implication dans des laboratoires et équipes de recherche en sciences humaines, avec des décennies d’activité comme directrice de recherche et enseignante dans des institutions françaises de haut niveau. &lt;/p&gt; &lt;p&gt; "Liberté et inquiétude de la vie animale" paru en 2006 et "Une autre existence" paru en 2012 sont parmi ses essais-clés. Ils proposent une phénoménologie de l’animal qui attribue aux animaux une vie vécue, une biographie et un monde propre, en opposition à une conception purement biologique ou fonctionnelle de l’animalité. Son approche met en lumière la distinction entre vivre en première personne et exister biologiquement, et elle s’interroge sur la place des animaux dans les sociétés modernes — notamment dans les pratiques d’élevage, &lt;a href="https://reporterre.net/Florence-Burgat-L-institution-de-l-alimentation-carnee-reflete-un-desir-tres " title="Florence Burgat : « L’institution de l’alimentation carnée reflète un désir très profond de l’humanité  par Reportere"&gt;l’alimentation carnée&lt;/a&gt;, le droit animalier et les enjeux éthiques qui en découlent. Elle a aussi écrit sur la vie végétale et a développé une réflexion sur l’institution de l’alimentation carnée, la notion de sacrifice et les mythes qui entourent l’humanité carnivore, élargissant ainsi la portée philosophique de &lt;a href="https://www.youtube.com/watch?v=AzVErgOotx0" title=" Idées: Carnivore, l'Humanité n'est pas dans son assiette? par TV5Monde"&gt;l’éthique animale &lt;/a&gt; à des domaines comme la nourriture, le droit et la société. &lt;/p&gt; &lt;p&gt; Elle a publié et contribué à des revues et ouvrages dédiés à la philosophie contemporaine et à l’éthique animale. Elle est souvent associée à des discussions sur la manière dont les sociétés humaines reconnaissent ou nüancent l’existence des autres vivants et comment cela influence les pratiques culturelles et juridiques. Son travail est référencé dans des bibliographies universitaires et chez des éditeurs de sciences humaines, ce qui en fait une voix importante pour ceux qui s’interrogent sur la dignité et la vie des êtres non humains dans un cadre éthique et philosophique. &lt;/p&gt;   &lt;audio controls title="L’éthique animale avec Florence Burgat par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E54" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Quentin_Meillassoux"  title=" Wikipedia"&gt;Quentin MEILLASSOUX&lt;/a&gt; est un philosophe français du courant qu'on appelle le  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif" style="color:#88A1E9" title=" Speculative Realism par Wikipedia "&gt;"réalisme spéculatif"&lt;/a&gt;. Le point de départ majeur de sa philosophie est "Le corrélationnisme" qui, selon lui, est la thèse dominante depuis Kant, et qui affirme qu'il est impossible de connaître le monde tel qu'il est en soi, indépendamment de notre rapport à lui (la corrélation entre la pensée et l'être). Cette position rend impossible de penser un "absolu" et nous enferme dans un cercle où nous ne pouvons accéder qu'à ce qui est "pour nous". &lt;a href="https://www.youtube.com/watch?v=29_IhFEWtlc" title="corine-pelluchon"&gt;Il s'interroge &lt;/a&gt;  sur la capacité de la science à parler de réalités "ancestrales", ce qui semble contredire le corrélationnisme. &lt;/p&gt; &lt;p&gt; Face au corrélationnisme, il propose de postuler que la seule chose nécessaire est la &lt;a href="https://www.youtube.com/watch?v=5ECkL9MKDiI" title=" Quentin Meillassoux's "After Finitude" par Five Minute Philosophy "&gt; contingence absolue&lt;/a&gt;. Cela signifie que toutes les lois de la nature, toutes les entités existantes, sont radicalement contingentes et pourraient être différentes, ou même ne pas exister du tout. Il n'y a aucune raison ou fondement nécessaire à l'existence du monde tel qu'il est. Cette absence de raison ultime n'est pas un aveu d'ignorance, mais une vérité ontologique. C'est ce qu'il appelle le "principe de factualité". En affirmant cette contingence radicale, il s'inscrit dans une tradition matérialiste, mais une tradition qui se veut "spéculative" parce qu'elle cherche à penser l'absolu (l'absolu de la contingence) au-delà des limites imposées par le corrélationnisme. Il s'agit de s'affranchir de la dépendance de l'être vis-à-vis de la pensée. Sa pensée est notamment développée dans son ouvrage le plus célèbre,  &lt;a  href="https://fr.wikipedia.org/wiki/Apr%C3%A8s_la_finitude._Essai_sur_la_n%C3%A9cessit%C3%A9_de_la_contingence#:~:text=Quentin%20Meillassoux%20nomme%20cette%20philosophie,la%20pens%C3%A9e%20de%20l'absolu." title=" "Après la finitude. Essai sur la nécessité de la contingence" par Wikipedia "&gt;"Après la finitude. Essai sur la nécessité de la contingence"&lt;/a&gt; .&lt;/p&gt; &lt;p&gt;  Dans sa thèse de doctorat "L'inexistence divine", il explore la possibilité d'un "dieu à venir". Pour lui, si Dieu n'existe pas actuellement, sa non-existence n'est pas une nécessité, mais une contingence. Ainsi, il n'est pas impossible qu'un jour un "Dieu" puisse émerger d'une manière ou d'une autre, à la suite d'un changement radical des lois physiques. &lt;/p&gt; &lt;p&gt; Dans son second livre "Le Nombre et la Sirène", il propose une lecture inédite du célèbre poème de Stéphane Mallarmé, "Un coup de dés jamais n'abolira le hasard". Il y développe une analyse détaillée, y découvrant  &lt;a href="https://www.youtube.com/watch?v=yKwqoW9PxVA" title=" Le code secret de Mallarmé enfin dévoilé?  par De Revolutionibus "&gt;un code numérique&lt;/a&gt;  qui, selon lui, serait intégré au texte par Mallarmé lui-même, en lien avec ses réflexions sur le hasard et la contingence.&lt;/p&gt; &lt;p&gt; En critiquant radicalement le corrélationnisme, il cherche à ouvrir la voie à une nouvelle forme de réalisme et de matérialisme, où la contingence est pensée non pas comme une limite de notre connaissance, mais comme une propriété fondamentale de l'être lui-même. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Quentin Meillassoux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-16.12.2011-ITEMA_20320127-2011C3403E0204-ITE_00047293_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Quentin_Meillassoux"  title=" Wikipedia"&gt;Quentin MEILLASSOUX&lt;/a&gt; est un philosophe français du courant qu'on appelle le  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif" style="color:#88A1E9" title=" Speculative Realism par Wikipedia "&gt;"réalisme spéculatif"&lt;/a&gt;. Le point de départ majeur de sa philosophie est "Le corrélationnisme" qui, selon lui, est la thèse dominante depuis Kant, et qui affirme qu'il est impossible de connaître le monde tel qu'il est en soi, indépendamment de notre rapport à lui (la corrélation entre la pensée et l'être). Cette position rend impossible de penser un "absolu" et nous enferme dans un cercle où nous ne pouvons accéder qu'à ce qui est "pour nous". &lt;a href="https://www.youtube.com/watch?v=29_IhFEWtlc" title="corine-pelluchon"&gt;Il s'interroge &lt;/a&gt;  sur la capacité de la science à parler de réalités "ancestrales", ce qui semble contredire le corrélationnisme. &lt;/p&gt; &lt;p&gt; Face au corrélationnisme, il propose de postuler que la seule chose nécessaire est la &lt;a href="https://www.youtube.com/watch?v=5ECkL9MKDiI" title=" Quentin Meillassoux's "After Finitude" par Five Minute Philosophy "&gt; contingence absolue&lt;/a&gt;. Cela signifie que toutes les lois de la nature, toutes les entités existantes, sont radicalement contingentes et pourraient être différentes, ou même ne pas exister du tout. Il n'y a aucune raison ou fondement nécessaire à l'existence du monde tel qu'il est. Cette absence de raison ultime n'est pas un aveu d'ignorance, mais une vérité ontologique. C'est ce qu'il appelle le "principe de factualité". En affirmant cette contingence radicale, il s'inscrit dans une tradition matérialiste, mais une tradition qui se veut "spéculative" parce qu'elle cherche à penser l'absolu (l'absolu de la contingence) au-delà des limites imposées par le corrélationnisme. Il s'agit de s'affranchir de la dépendance de l'être vis-à-vis de la pensée. Sa pensée est notamment développée dans son ouvrage le plus célèbre,  &lt;a  href="https://fr.wikipedia.org/wiki/Apr%C3%A8s_la_finitude._Essai_sur_la_n%C3%A9cessit%C3%A9_de_la_contingence#:~:text=Quentin%20Meillassoux%20nomme%20cette%20philosophie,la%20pens%C3%A9e%20de%20l'absolu." title=" "Après la finitude. Essai sur la nécessité de la contingence" par Wikipedia "&gt;"Après la finitude. Essai sur la nécessité de la contingence"&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;  Dans sa thèse de doctorat "L'inexistence divine", il explore la possibilité d'un "dieu à venir". Pour lui, si Dieu n'existe pas actuellement, sa non-existence n'est pas une nécessité, mais une contingence. Ainsi, il n'est pas impossible qu'un jour un "Dieu" puisse émerger d'une manière ou d'une autre, à la suite d'un changement radical des lois physiques. &lt;/p&gt; &lt;p&gt; Dans son second livre "Le Nombre et la Sirène", il propose une lecture inédite du célèbre poème de Stéphane Mallarmé, "Un coup de dés jamais n'abolira le hasard". Il y développe une analyse détaillée, y découvrant  &lt;a href="https://www.youtube.com/watch?v=yKwqoW9PxVA" title=" Le code secret de Mallarmé enfin dévoilé?  par De Revolutionibus "&gt;un code numérique&lt;/a&gt;  qui, selon lui, serait intégré au texte par Mallarmé lui-même, en lien avec ses réflexions sur le hasard et la contingence.&lt;/p&gt; &lt;p&gt; En critiquant radicalement le corrélationnisme, il cherche à ouvrir la voie à une nouvelle forme de réalisme et de matérialisme, où la contingence est pensée non pas comme une limite de notre connaissance, mais comme une propriété fondamentale de l'être lui-même. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Quentin Meillassoux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-16.12.2011-ITEMA_20320127-2011C3403E0204-ITE_00047293_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="E58" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Renault"  title=" Wikipedia"&gt;Emmanuel RENAULT&lt;/a&gt; est un philosophe français , spécialisé en théorie critique, philosophie sociale et rapports entre reconnaissance, conflit et domination. Il est largement associé à une approche pragmatiste et pluraliste, cherchant à articuler Hegel, Marx, Honneth et le pragmatisme de Dewey dans une perspective interdisciplinaire. &lt;/p&gt; &lt;p&gt;  Il développe une approche qui croise les traditions marxistes et pragmatistes, et met l’accent sur les questions de travail, de justice, de  &lt;a href="https://www.nonfiction.fr/article-11867-abolir-lexploitation-entretien-avec-emmanuel-renault.htm" title="Abolir l'exploitation : entretien avec Emmanuel Renault. par nonfiction"&gt; souffrance sociale &lt;/a&gt; et de reconnaissance et il analyse comment les conflits sociaux, la reconnaissance et les formes de domination structurent l’injustice moderne.  Il s’inscrit dans une démarche qui remet en question les bases normatives de la justice politique en faveur d’une compréhension de l’injustice comme déni de reconnaissance et comme expérience de souffrance sociale. &lt;/p&gt; &lt;p&gt; Son travail est influent dans les débats sur la philosophie sociale en France et à l’étranger, et il participe à l’extension des cadres marxistes et pragmatistes dans la réflexion sur le travail,  &lt;a href="https://www.youtube.com/watch?v=6DriuHGugCA" title=" l'impensé de l'exploitation par Hors serie"&gt; l’exploitation &lt;/a&gt; et la justice sociale. Ses publications représentatives : - "Le Mépris social" paru en  2000 : exploration des formes de mépris et des dynamiques sociales qui les sous-tendent. - "Souffrances sociales" paru en 2008 : analyse des mécanismes de souffrance dans les sociétés contemporaines et leur lien avec la reconnaissance et la distribution des ressources. - "Reconnaissance, conflit, domination"  en 2017 : thèse centrale sur la relation entre reconnaissance, conflit et domination, et leur rôle dans la configuration des inégalités. &lt;/p&gt;  &lt;audio controls title="Mépris social : comment sortir du dialogue de sourds?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-29.10.2015-ITEMA_20828700-2015C19327S0302-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Renault"  title=" Wikipedia"&gt;Emmanuel RENAULT&lt;/a&gt; est un philosophe français, spécialisé en théorie critique, philosophie sociale et rapports entre reconnaissance, conflit et domination. Il est largement associé à une approche pragmatiste et pluraliste, cherchant à articuler Hegel, Marx, Honneth et le pragmatisme de Dewey dans une perspective interdisciplinaire. &lt;/p&gt; &lt;p&gt;  Il développe une approche qui croise les traditions marxistes et pragmatistes, et met l’accent sur les questions de travail, de justice, de  &lt;a href="https://www.nonfiction.fr/article-11867-abolir-lexploitation-entretien-avec-emmanuel-renault.htm" title="Abolir l'exploitation : entretien avec Emmanuel Renault. par nonfiction"&gt; souffrance sociale &lt;/a&gt; et de reconnaissance et il analyse comment les conflits sociaux, la reconnaissance et les formes de domination structurent l’injustice moderne.  Il s’inscrit dans une démarche qui remet en question les bases normatives de la justice politique en faveur d’une compréhension de l’injustice comme déni de reconnaissance et comme expérience de souffrance sociale. &lt;/p&gt; &lt;p&gt; Son travail est influent dans les débats sur la philosophie sociale en France et à l’étranger, et il participe à l’extension des cadres marxistes et pragmatistes dans la réflexion sur le travail,  &lt;a href="https://www.youtube.com/watch?v=6DriuHGugCA" title=" l'impensé de l'exploitation par Hors serie"&gt; l’exploitation &lt;/a&gt; et la justice sociale. Ses publications représentatives : - "Le Mépris social" paru en  2000 : exploration des formes de mépris et des dynamiques sociales qui les sous-tendent. - "Souffrances sociales" paru en 2008 : analyse des mécanismes de souffrance dans les sociétés contemporaines et leur lien avec la reconnaissance et la distribution des ressources. - "Reconnaissance, conflit, domination"  en 2017 : thèse centrale sur la relation entre reconnaissance, conflit et domination, et leur rôle dans la configuration des inégalités. &lt;/p&gt;  &lt;audio controls title="Mépris social : comment sortir du dialogue de sourds?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-29.10.2015-ITEMA_20828700-2015C19327S0302-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F58" s="34" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="E66" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yves_Cusset"  style="color:#6A142A"  title=" Wikipedia"&gt;Yves CUSSET&lt;/a&gt;  est un philosophe français agrégé et docteur en philosophie, qui allie une réflexion sérieuse sur la philosophie politique à un engagement théâtral et  &lt;a href="https://www.youtube.com/watch?v=uJLmpAgqiWY" style="color:#88A1E9" title="Yves Cusset, Petit manuel d'engagement politique à l'usage des mammifères doués de raison.... par Yves Cusset"&gt;humoristique unique. &lt;/a&gt;  Spécialiste de Habermas et Foucault, il explore les tensions entre raison discussionnelle et pouvoir, ainsi que les apories de l’accueil : comment concilier exigence éthique d’hospitalité et contraintes politiques. &lt;/p&gt; &lt;p&gt; Ses essais interrogent le "bien-mourir", critiquant les normes contemporaines de la mort apaisée, et défendent une politique de l’accueil face à la misère du monde.  Il théorise l’humour comme "bonne humeur pour mourir", un outil philosophique qui désarme les idées fixes et favorise la pensée sans intimidation.  il crée des solos comme Rien ne sert d’exister, Tractatus philo-comicus ou La Philosophie enseignée à ma chouette, joués au festival d’Avignon et ailleurs, mêlant rire, absurdité et métaphysique. &lt;/p&gt; &lt;p&gt; Militant discret, il use de l’humour politique pour dénoncer clichés  &lt;a href="https://www.youtube.com/watch?v=QwVPt_PQE-Q" style="color:#88A1E9" title="Yves Cusset : 100 façons de ne pas accueillir un migrant par TV5Monde"&gt;anti-migrants &lt;/a&gt; ou dérives du "développement personnel".  Son genre hybride, l’"humour philosophique", vise à émerveiller par le rire, suscitant la réflexion sans complexer, comme il l’explique dans Le Monde. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yves_Cusset"  style="color:#6A142A"  title=" Wikipedia"&gt;Yves CUSSET&lt;/a&gt;  est un philosophe français agrégé et docteur en philosophie, qui allie une réflexion sérieuse sur la philosophie politique à un engagement théâtral et  &lt;a href="https://www.youtube.com/watch?v=uJLmpAgqiWY" style="color:#88A1E9" title="Yves Cusset, Petit manuel d'engagement politique à l'usage des mammifères doués de raison.... par Yves Cusset"&gt;humoristique unique. &lt;/a&gt;  Spécialiste de Habermas et Foucault, il explore les tensions entre raison discussionnelle et pouvoir, ainsi que les apories de l’accueil : comment concilier exigence éthique d’hospitalité et contraintes politiques. &lt;/p&gt; &lt;p&gt; Ses essais interrogent le "bien-mourir", critiquant les normes contemporaines de la mort apaisée, et défendent une politique de l’accueil face à la misère du monde.  Il théorise l’humour comme "bonne humeur pour mourir", un outil philosophique qui désarme les idées fixes et favorise la pensée sans intimidation. Il crée des solos comme Rien ne sert d’exister, Tractatus philo-comicus ou La Philosophie enseignée à ma chouette, joués au festival d’Avignon et ailleurs, mêlant rire, absurdité et métaphysique. &lt;/p&gt; &lt;p&gt; Militant discret, il use de l’humour politique pour dénoncer clichés  &lt;a href="https://www.youtube.com/watch?v=QwVPt_PQE-Q" style="color:#88A1E9" title="Yves Cusset : 100 façons de ne pas accueillir un migrant par TV5Monde"&gt;anti-migrants &lt;/a&gt; ou dérives du "développement personnel".  Son genre hybride, l’"humour philosophique", vise à émerveiller par le rire, suscitant la réflexion sans complexer, comme il l’explique dans Le Monde. &lt;/p&gt; 
 &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="L'amour avec Yves Cusset par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-07.06.2024-ITEMA_23765968-2024F45096S0159-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="E68" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau" title=" Wikipedia"&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href="https://www.youtube.com/watch?v=PNMZHr3L_Ws" title=" Vivons nous dans un multivers par Aurelien Barrau"&gt; concept de multivers&lt;/a&gt; , et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage "Chaos multiples" et "De la vérité dans les sciences"  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé "Météorites". &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de "sauver le climat" plutôt "qu’agir pour la vie". &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  "habiter la science en poète" en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href="https://www.youtube.com/watch?v=94IxSYo5wtM" title="Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter"&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href="https://www.youtube.com/watch?v=g3Z_LsXD7DU" title=" L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac"&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un "faire monde" éthique et conscient. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Aurelien BARRAU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau" title=" Wikipedia"&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href="https://www.youtube.com/watch?v=PNMZHr3L_Ws" title=" Vivons nous dans un multivers par Aurelien Barrau"&gt; concept de multivers&lt;/a&gt;, et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage "Chaos multiples" et "De la vérité dans les sciences"  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé "Météorites". &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de "sauver le climat" plutôt "qu’agir pour la vie". &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  "habiter la science en poète" en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href="https://www.youtube.com/watch?v=94IxSYo5wtM" title="Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter"&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href="https://www.youtube.com/watch?v=g3Z_LsXD7DU" title=" L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac"&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un "faire monde" éthique et conscient. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Aurelien BARRAU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="E80" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nadia_Yala_Kisukidi"  title=" Wikipedia"&gt;Nadia Yala KISUKIDI&lt;/a&gt;  est  est une philosophe et écrivaine franco-congolaise née à Bruxelles, professeure à l’université Paris 8, connue pour ses travaux sur Bergson, la philosophie Africaine, le féminisme noir et les effets coloniaux dans la pensée occidentale. Sa philosophie part d’un constat simple : les grands corpus philosophiques ont longtemps été enseignés comme s’ils étaient universels, alors qu’ils reflètent souvent une histoire située, européenne et coloniale. &lt;/p&gt; &lt;p&gt; Elle est d’abord reconnue comme spécialiste de Bergson. Dans son livre Bergson ou l’humanité créatrice, elle relit Bergson à partir de la création, du mouvement et de l’invention de soi, en montrant que la philosophie peut penser la vie comme puissance de transformation plutôt que comme identité figée. &lt;/p&gt; &lt;p&gt; Un autre axe central de son travail est la critique de la « bibliothèque coloniale » : elle montre comment l’idée d’Afrique et l’idée de « Noir » ont été fabriquées dans &lt;a href="https://www.youtube.com/watch?v=smUx6yKHTF4"  title="NY Kisikidi une nouvelle pensée des mondes noirs par RFI"&gt;des cadres intellectuels &lt;/a&gt;  marqués par la domination européenne. Son approche ne consiste pas seulement à dénoncer ces héritages, mais à déplacer le centre du regard pour faire place à des pensées africaines, diasporiques et non occidentales. &lt;/p&gt; &lt;p&gt; Elle développe aussi une réflexion féministe et politique, notamment avec Djamila Ribeiro dans Dialogue transatlantique, où elle met en relation les expériences des femmes noires, les diasporas africaines et les formes contemporaines de résistance. Chez elle, le féminisme n’est pas séparé de la question raciale : il sert à &lt;a href="https://www.youtube.com/watch?v=ECngo81h5v0"  title="NY Kisikidi défendre les vies humaines par Campus AFD par RFI"&gt;penser des solidarités, &lt;/a&gt; des voix minorées et des alliances intellectuelles entre continents. &lt;/p&gt; &lt;p&gt; Sa philosophie vise une forme d’universel décentré : non pas un universel abstrait imposé d’en haut, mais un universel construit à partir des conflits, des pluralités et des expériences historiques concrètes. En ce sens, elle propose une philosophie de la relation, de la circulation et de la restitution, où l’on comprend le monde en écoutant les marges autant que les centres. &lt;/p&gt;  &lt;audio controls title="Nadia Yala Kisukidi le mouvement anti raciste par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-13.06.2020-ITEMA_22360573-3-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nadia_Yala_Kisukidi"  title=" Wikipedia"&gt;Nadia Yala KISUKIDI&lt;/a&gt;  est une philosophe et écrivaine franco-congolaise née à Bruxelles, professeure à l’université Paris 8, connue pour ses travaux sur Bergson, la philosophie Africaine, le féminisme noir et les effets coloniaux dans la pensée occidentale. Sa philosophie part d’un constat simple : les grands corpus philosophiques ont longtemps été enseignés comme s’ils étaient universels, alors qu’ils reflètent souvent une histoire située, européenne et coloniale. &lt;/p&gt; &lt;p&gt; Elle est d’abord reconnue comme spécialiste de Bergson. Dans son livre Bergson ou l’humanité créatrice, elle relit Bergson à partir de la création, du mouvement et de l’invention de soi, en montrant que la philosophie peut penser la vie comme puissance de transformation plutôt que comme identité figée. &lt;/p&gt; &lt;p&gt; Un autre axe central de son travail est la critique de la « bibliothèque coloniale » : elle montre comment l’idée d’Afrique et l’idée de « Noir » ont été fabriquées dans &lt;a href="https://www.youtube.com/watch?v=smUx6yKHTF4"  title="NY Kisikidi une nouvelle pensée des mondes noirs par RFI"&gt;des cadres intellectuels &lt;/a&gt;  marqués par la domination européenne. Son approche ne consiste pas seulement à dénoncer ces héritages, mais à déplacer le centre du regard pour faire place à des pensées africaines, diasporiques et non occidentales. &lt;/p&gt; &lt;p&gt; Elle développe aussi une réflexion féministe et politique, notamment avec Djamila Ribeiro dans Dialogue transatlantique, où elle met en relation les expériences des femmes noires, les diasporas africaines et les formes contemporaines de résistance. Chez elle, le féminisme n’est pas séparé de la question raciale : il sert à &lt;a href="https://www.youtube.com/watch?v=ECngo81h5v0"  title="NY Kisikidi défendre les vies humaines par Campus AFD par RFI"&gt;penser des solidarités, &lt;/a&gt; des voix minorées et des alliances intellectuelles entre continents. &lt;/p&gt; &lt;p&gt; Sa philosophie vise une forme d’universel décentré : non pas un universel abstrait imposé d’en haut, mais un universel construit à partir des conflits, des pluralités et des expériences historiques concrètes. En ce sens, elle propose une philosophie de la relation, de la circulation et de la restitution, où l’on comprend le monde en écoutant les marges autant que les centres. &lt;/p&gt;  &lt;audio controls title="Nadia Yala Kisukidi le mouvement anti raciste par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-13.06.2020-ITEMA_22360573-3-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="E81" s="51" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julia_de_Fun%C3%A8s"  title=" Wikipedia"&gt;Julia DE-FUNÈS&lt;/a&gt; est une philosophe, essayiste et conférencière française, également spécialiste des ressources humaines et du monde de l’entreprise. Après avoir travaillé plusieurs années comme chasseuse de têtes, elle a créé en 2010 un cabinet de conseil mobilisant la philosophie dans les organisations. Elle a ensuite soutenu en 2017 une thèse consacrée au passage de l’identité personnelle à l’authenticité, à travers les notions de représentation et de mimétisme. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=OaDbpC3azdQ"  title="julia de Funès, philosophe par 21 News"&gt; Sa démarche consiste &lt;/a&gt;  à faire sortir la philosophie du cadre purement universitaire pour la confronter aux situations ordinaires : travail, management, bonheur, relations professionnelles ou développement personnel. Elle considère la philosophie comme un exercice de mise à distance, destiné à interroger les évidences et à examiner le sens réel des mots que nous employons. Dans cette perspective, philosopher revient à ne pas accepter mécaniquement les discours dominants, les slogans ou les habitudes de pensée. &lt;/p&gt; &lt;p&gt; Une de ses principales critiques vise l’entreprise contemporaine et la multiplication des procédures, des indicateurs et des discours managériaux. Dans Socrate au pays des process ou La Vie de bureau, elle dénonce ce qu’elle perçoit comme une perte de sens : les salariés peuvent être soumis à des injonctions contradictoires et à un langage abstrait qui transforme parfois l’être humain en simple fonction. Elle oppose à cette logique la nécessité de retrouver du jugement, de l’autonomie et une réflexion véritable sur les finalités du travail. &lt;/p&gt; &lt;p&gt; Elle critique également le développement personnel lorsqu’il promet le bonheur, la réussite ou la confiance en soi au moyen de recettes standardisées. Dans &lt;a href="https://www.youtube.com/watch?v=dV5r46P6yUU"  title="le développement personnel est la plus grosse arnaque par Clique Tv"&gt;Le Développement (im)personnel &lt;/a&gt;, elle soutient que certaines formes de psychologie positive peuvent transformer des problèmes sociaux ou professionnels en responsabilités purement individuelles : si l’on échoue, ce serait parce que l’on n’est pas assez motivé ou « positif ». Sa critique ne consiste donc pas à refuser toute recherche de bien-être, mais à dénoncer les méthodes qui imposent une conformité sous l’apparence de l’épanouissement. &lt;/p&gt; &lt;p&gt; Sa philosophie peut être caractérisée par trois exigences : l’esprit critique, le discernement et l’authenticité. Elle invite chacun à se méfier des formules toutes faites, à ne pas confondre adaptation sociale et vérité personnelle, et à rechercher un rapport plus lucide à soi-même et aux autres. Son originalité tient ainsi à la rencontre entre la tradition philosophique — notamment Socrate, Aristote ou Kant — et les problèmes très concrets de la vie professionnelle et sociale. &lt;/p&gt;  &lt;audio controls title="Un nouvel ordre identitaire avec Julia Dez Funès par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.11.2022-ITEMA_23186791-2022F30378S0309-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julia_de_Fun%C3%A8s"  title=" Wikipedia"&gt;Julia DE-FUNÈS&lt;/a&gt; est une philosophe, essayiste et conférencière française, également spécialiste des ressources humaines et du monde de l’entreprise. Après avoir travaillé plusieurs années comme chasseuse de têtes, elle a créé en 2010 un cabinet de conseil mobilisant la philosophie dans les organisations. Elle a ensuite soutenu en 2017 une thèse consacrée au passage de l’identité personnelle à l’authenticité, à travers les notions de représentation et de mimétisme. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=OaDbpC3azdQ"  title="julia de Funès, philosophe par 21 News"&gt; Sa démarche consiste &lt;/a&gt;  à faire sortir la philosophie du cadre purement universitaire pour la confronter aux situations ordinaires : travail, management, bonheur, relations professionnelles ou développement personnel. Elle considère la philosophie comme un exercice de mise à distance, destiné à interroger les évidences et à examiner le sens réel des mots que nous employons. Dans cette perspective, philosopher revient à ne pas accepter mécaniquement les discours dominants, les slogans ou les habitudes de pensée. &lt;/p&gt; &lt;p&gt; Une de ses principales critiques vise l’entreprise contemporaine et la multiplication des procédures, des indicateurs et des discours managériaux. Dans Socrate au pays des process ou La Vie de bureau, elle dénonce ce qu’elle perçoit comme une perte de sens : les salariés peuvent être soumis à des injonctions contradictoires et à un langage abstrait qui transforme parfois l’être humain en simple fonction. Elle oppose à cette logique la nécessité de retrouver du jugement, de l’autonomie et une réflexion véritable sur les finalités du travail. &lt;/p&gt; &lt;p&gt; Elle critique également le développement personnel lorsqu’il promet le bonheur, la réussite ou la confiance en soi au moyen de recettes standardisées. Dans &lt;a href="https://www.youtube.com/watch?v=dV5r46P6yUU"  title="le développement personnel est la plus grosse arnaque par Clique Tv"&gt;Le Développement (im)personnel&lt;/a&gt;, elle soutient que certaines formes de psychologie positive peuvent transformer des problèmes sociaux ou professionnels en responsabilités purement individuelles : si l’on échoue, ce serait parce que l’on n’est pas assez motivé ou « positif ». Sa critique ne consiste donc pas à refuser toute recherche de bien-être, mais à dénoncer les méthodes qui imposent une conformité sous l’apparence de l’épanouissement. &lt;/p&gt; &lt;p&gt; Sa philosophie peut être caractérisée par trois exigences : l’esprit critique, le discernement et l’authenticité. Elle invite chacun à se méfier des formules toutes faites, à ne pas confondre adaptation sociale et vérité personnelle, et à rechercher un rapport plus lucide à soi-même et aux autres. Son originalité tient ainsi à la rencontre entre la tradition philosophique — notamment Socrate, Aristote ou Kant — et les problèmes très concrets de la vie professionnelle et sociale. &lt;/p&gt;  &lt;audio controls title="Un nouvel ordre identitaire avec Julia Dez Funès par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.11.2022-ITEMA_23186791-2022F30378S0309-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F81" s="34" t="inlineStr">

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -5745,12 +5745,12 @@
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>UKJx1qhdF58</t>
+          <t xml:space="preserve">IbHSzVzGVIM</t>
         </is>
       </c>
       <c r="G81" s="36" t="inlineStr">
         <is>
-          <t>Julia de Funès:Marre de ces débats furieux par l’Invité</t>
+          <t xml:space="preserve">"Julia de Funès, libre de douter" par Public Sénat</t>
         </is>
       </c>
       <c r="H81" s="37" t="inlineStr">

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -1578,7 +1578,7 @@
       </c>
       <c r="K16" s="27" t="inlineStr">
         <is>
-          <t>Post Modernisme</t>
+          <t xml:space="preserve">Post Modernisme ; Individualisme</t>
         </is>
       </c>
       <c r="L16" s="27" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="K25" s="27" t="inlineStr">
         <is>
-          <t>Libéralisme ; Wokisme</t>
+          <t xml:space="preserve">Libéralisme</t>
         </is>
       </c>
       <c r="L25" s="27" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="K36" s="27" t="inlineStr">
         <is>
-          <t>Stoïcisme ; Matérialisme</t>
+          <t xml:space="preserve">Stoïcisme ; Matérialisme ; Athéisme</t>
         </is>
       </c>
       <c r="L36" s="27" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K41" s="27" t="inlineStr">
         <is>
-          <t>Hédonisme ; Anarchisme</t>
+          <t xml:space="preserve">Hédonisme ; Anarchisme ; Athéisme</t>
         </is>
       </c>
       <c r="L41" s="27" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="K43" s="27" t="inlineStr">
         <is>
-          <t>Analytique</t>
+          <t xml:space="preserve">Analytique ; Éthique de la sollicitude</t>
         </is>
       </c>
       <c r="L43" s="27" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K50" s="27" t="inlineStr">
         <is>
-          <t>Libéralisme</t>
+          <t xml:space="preserve">Libéralisme ; Éthique de la sollicitude</t>
         </is>
       </c>
       <c r="L50" s="27" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="K55" s="27" t="inlineStr">
         <is>
-          <t>Phénoménologie</t>
+          <t xml:space="preserve">Phénoménologie ; Éthique de la sollicitude</t>
         </is>
       </c>
       <c r="L55" s="27" t="inlineStr">

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="26" min="1" max="1"/>
@@ -6232,6 +6232,57 @@
       <c r="P88" t="inlineStr">
         <is>
           <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="219.75" customHeight="1" s="28">
+      <c r="A89" s="26">
+        <v>1950</v>
+      </c>
+      <c r="C89" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1950</t>
+        </is>
+      </c>
+      <c r="D89" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jean-Michel BESNIER</t>
+        </is>
+      </c>
+      <c r="E89" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Michel_Besnier" title=" Wikipedia"&gt;Jean-Michel BESNIER&lt;/a&gt; est un philosophe français. Né à Caen en 1950, agrégé de philosophie et docteur en sciences politiques, il enseigne à l’université de technologie de Compiègne de 1988 à 2001, puis à la Sorbonne, dont il est professeur émérite. Ses premiers livres portent sur l’histoire de la philosophie moderne et contemporaine, dont il publie une grande synthèse en 1993, et sur la figure de l’intellectuel, partagé entre la révolte et l’engagement, de Georges Bataille à Maurice Blanchot.&lt;/p&gt; &lt;p&gt;Il se consacre ensuite à l’impact des sciences et des techniques sur nos représentations et nos imaginaires. Dans &lt;em&gt;Demain les posthumains&lt;/em&gt; (2009), il analyse le &lt;a href="https://fr.wikipedia.org/wiki/Transhumanisme" title=" Wikipedia"&gt;transhumanisme&lt;/a&gt;, qui promet de dépasser la condition humaine grâce aux biotechnologies, aux nanotechnologies et à l’intelligence artificielle. Il y voit moins un progrès qu’une fatigue d’être soi, un désir de se débarrasser de la fragilité, de l’incertitude et de la mort, qui sont pourtant ce qui fait notre humanité.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Homme simplifié&lt;/em&gt; (2012), il décrit le « syndrome de la touche étoile » : à force de dialoguer avec des machines, nous simplifions notre langage et nos relations pour nous adapter à elles, au lieu de les rendre plus humaines. Il débat publiquement avec les partisans du transhumanisme, comme Laurent Alexandre, avec qui il publie &lt;em&gt;Les robots font-ils l’amour ?&lt;/em&gt; (2016). Il a siégé dans plusieurs comités d’éthique de la recherche, notamment celui du CNRS, et dirigé le secteur « sciences et société » du ministère de la Recherche de 2008 à 2011.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H89" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/besnier-mini.webp</t>
+        </is>
+      </c>
+      <c r="J89" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K89" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme</t>
+        </is>
+      </c>
+      <c r="L89" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe français des techniques, critique du transhumanisme et de « l’homme simplifié ».</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O89"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -2706,9 +2706,7 @@
       </c>
       <c r="E34" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Fran%C3%A7ois_Kerv%C3%A9gan"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean-François KERVEGAN&lt;/a&gt; est un philosophe français spécialiste de la philosophie allemande classique, de la philosophie politique et du droit. Professeur émérite à l’université Paris 1 Panthéon-Sorbonne depuis 2019, où il a fondé le groupe de recherche NoSoPhi (Normes, Sociétés, Philosophies). &lt;/p&gt; &lt;p&gt; Ses travaux croisent philosophie allemande (Hegel, Kant, Husserl), philosophie politique (État, souveraineté, démocratie, terrorisme) et philosophie du droit (normativité, droits subjectifs).  Dans la philosophie du droit, il explore la "raison des normes" pour éclairer les débats &lt;a href="https://www.youtube.com/watch?v=2uE1rQ84o3E" style="color:#88A1E9" title="Jean-François Kervégan : Le Droit chez Kant par E-Kritik"&gt;post-kelséniens &lt;/a&gt; sur validité et interprétation juridique. &lt;/p&gt; &lt;p&gt; Il défend une normativité juridique ancrée dans la raison pratique, capable de répondre aux apories du positivisme juridique sans tomber dans l’arbitraire moral. 
-Sa pensée interroge les limites de la modernité : comment penser le politique quand l’État souverain est contesté par des acteurs non étatiques ? &lt;/p&gt; 
-&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Qu'est-ce qu'avoir des droits ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/21447-23.04.2025-ITEMA_24112082-2025C27677S0113-NET_MFC_7BBBCBA0-C114-4775-A02F-0D69201542E4-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Fran%C3%A7ois_Kerv%C3%A9gan"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean-François KERVEGAN&lt;/a&gt; (né en 1950) est un philosophe français, spécialiste de la philosophie allemande classique, de la philosophie politique et de la philosophie du droit. Professeur à l’université Paris 1 Panthéon-Sorbonne, dont il est émérite depuis 2019, il y a fondé le groupe de recherche NoSoPhi (Normes, Sociétés, Philosophies).&lt;/p&gt; &lt;p&gt;Spécialiste reconnu de Hegel, il a donné une nouvelle traduction française des &lt;em&gt;Principes de la philosophie du droit&lt;/em&gt; et lui a consacré une grande étude, &lt;em&gt;L’Effectif et le Rationnel&lt;/em&gt; (2007), sur l’« esprit objectif », c’est-à-dire le droit, la morale, la famille, la société civile et l’État. Il y montre que Hegel n’est ni le penseur de l’État autoritaire qu’on a souvent décrit, ni un simple libéral : il pense les institutions comme ce qui rend la liberté réelle. Il a aussi étudié le juriste allemand Carl Schmitt, dont il a confronté la pensée à celle de Hegel, en interrogeant la critique schmittienne du libéralisme et de la démocratie parlementaire tout en en montrant les dangers. Dans &lt;em&gt;La Raison des normes&lt;/em&gt; (2015), consacré à Kant, il interroge le fondement des normes juridiques et morales, et dialogue avec les débats nés du positivisme juridique de Hans Kelsen, que l’on dit &lt;a href="https://www.youtube.com/watch?v=2uE1rQ84o3E" style="color:#88A1E9" title="Jean-François Kervégan : Le Droit chez Kant par E-Kritik"&gt;post-kelséniens&lt;/a&gt;, sur la validité et l’interprétation du droit. Il défend une normativité juridique fondée sur la raison pratique, qui échappe à la fois à l’arbitraire et au simple fait du pouvoir.&lt;/p&gt; &lt;p&gt;Ses travaux récents portent sur les droits subjectifs, la souveraineté et les transformations de l’État face à la mondialisation et aux acteurs non étatiques.&lt;/p&gt;  &lt;audio controls title="Qu'est-ce qu'avoir des droits ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/21447-23.04.2025-ITEMA_24112082-2025C27677S0113-NET_MFC_7BBBCBA0-C114-4775-A02F-0D69201542E4-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F34" s="34" t="inlineStr">
@@ -2966,7 +2964,7 @@
       </c>
       <c r="E38" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olivier_Abel"  style="color:#6A142A"  title=" Wikipedia"&gt;Olivier ABEL&lt;/a&gt;  est un philosophe français spécialiste en éthique et philosophie morale, influencé par Paul Ricœur, Emmanuel Levinas et la tradition protestante. Il soutient en 1983 une thèse sur la rêverie chez Gaston Bachelard sous la direction de Ricœur, puis une habilitation en 2000 sur le temps éthique entre courage et pardon. &lt;/p&gt; &lt;p&gt; Créateur du Fonds Ricœur à Paris, doyen de la Faculté protestante de Paris, il a présidé la Commission d'éthique de la &lt;a href="https://www.lavie.fr/idees/histoire/olivier-abel-avec-le-catholicisme-leffort-fait-partie-du-chemin-pour-acceder-a-la-grace-100952.php"  title="Olivier Abel : Avec le catholicisme, l’effort fait partie du chemin pour accéder à la grâce par la Vie"&gt;Fédération protestante &lt;/a&gt;  de France et est membre de l'Académie de Nîmes depuis 2018. Il est aussi membre du Comité consultatif national d'éthique et contribue à des revues comme Esprit. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'éthique interrogative, le pardon, la conversation, l'Europe et les penseurs protestants comme Calvin ou Bayle. Parmi ses ouvrages : L’éthique interrogative (2000), Le pardon, briser la dette et l’oubli (1991), Le vertige de l’Europe (2019),  &lt;a href="https://www.youtube.com/watch?v=G1_ynk7E7LQ" title="Olivier Abel, philosophe : Le signe de l’humiliation, c’est cette parole rentrée par FRANCE 24"&gt;De l’humiliation &lt;/a&gt; (récent) et La naissance, qu’est-ce que ça change. Il explore la fugacité des liens humains et une critique du sujet délié. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olivier_Abel"  style="color:#6A142A"  title=" Wikipedia"&gt;Olivier ABEL&lt;/a&gt;  est un philosophe français spécialiste en éthique et philosophie morale, influencé par Paul Ricœur, Emmanuel Levinas et la tradition protestante. Il soutient en 1983 une thèse sur la rêverie chez Gaston Bachelard sous la direction de Ricœur, puis une habilitation en 2000 sur le temps éthique entre courage et pardon. &lt;/p&gt; &lt;p&gt; Créateur du Fonds Ricœur à Paris, doyen de la Faculté protestante de Paris, il a présidé la Commission d'éthique de la &lt;a href="https://www.lavie.fr/idees/histoire/olivier-abel-avec-le-catholicisme-leffort-fait-partie-du-chemin-pour-acceder-a-la-grace-100952.php"  title="Olivier Abel : Avec le catholicisme, l’effort fait partie du chemin pour accéder à la grâce par la Vie"&gt;Fédération protestante &lt;/a&gt;  de France et est membre de l'Académie de Nîmes depuis 2018. Il est aussi membre du Comité consultatif national d'éthique et contribue à des revues comme Esprit. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'éthique interrogative, le pardon, la conversation, l'Europe et les penseurs protestants comme Calvin ou Bayle. Parmi ses ouvrages : L’éthique interrogative (2000), Le pardon, briser la dette et l’oubli (1991), Le vertige de l’Europe (2019),  &lt;a href="https://www.youtube.com/watch?v=G1_ynk7E7LQ" title="Olivier Abel, philosophe : Le signe de l’humiliation, c’est cette parole rentrée par FRANCE 24"&gt;De l’humiliation &lt;/a&gt; (récent) et La naissance, qu’est-ce que ça change. Il explore la fugacité des liens humains et une critique du sujet délié. Pour lui, l’éthique n’est pas un système de règles à appliquer, mais un art de poser les bonnes questions dans les situations où plusieurs biens entrent en conflit : c’est ce qu’il appelle une « éthique interrogative ». Il s’intéresse au pardon, qui permet de délier une relation sans l’effacer, et à l’humiliation, qu’il décrit comme une parole empêchée, une manière de priver l’autre de sa place dans la conversation commune. &lt;/p&gt; 
  &lt;audio controls title="Le témoin du vendredi : Olivier Abel, la civilisation européenne par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11739-12.04.2019-ITEMA_22034063-2019F17009S0102-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
@@ -3155,10 +3153,7 @@
       </c>
       <c r="E41" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Michel_Onfray"  title=" Wikipedia"&gt;Michel ONFRAY&lt;/a&gt;  est un philosophe  &lt;a href="https://www.youtube.com/watch?v=wikRuhGQExI&amp;ab_channel=FrontPopulaire"    title="Qu'est ce que le populisme par Front Populaire"&gt;Populiste&lt;/a&gt; et &lt;a href="https://www.youtube.com/watch?v=l4PX2P-KuBE&amp;ab_channel=AlainBajom%C3%A9e"   title="L'hédonisme par Alain Bajomée"&gt; Hédoniste&lt;/a&gt; Français connu pour sa critique de la philosophie traditionnelle et pour son engagement en faveur de l'athéisme et de l'anarchisme. Il rejette l'idée d'une réalité objective et soutient que nos expériences et nos perceptions façonnent notre réalité et que le plaisir est le but ultime de l'existence humaine. &lt;/p&gt; &lt;p&gt; 
-Il a été critiqué par certains philosophes pour avoir simplifié à l'excès des concepts philosophiques complexes et pour avoir promu une vision du monde hédoniste et individualiste. 
- Il a écrit plusieurs ouvrages sur la critique de la religion, en particulier du christianisme mais aussi sur la place de l'Art avec  &lt;a href="https://www.youtube.com/watch?v=MNY2U-T2Xf4&amp;ab_channel=MichelOnfray-Topic"  title="Les Raisons de l'Art par Michel Onfray"&gt;"Les Raisons de l'Art"&lt;/a&gt; où il explore la signification de l'art à travers l'histoire et la philosophie.&lt;/p&gt; &lt;p&gt;  
-Il analyse la conception traditionnelle de l'art, trop souvent associée à la beauté, à la perfection et à l'idéalisme.  C'une vision de l'art qui est profondément ancrée dans la réalité et la condition humaine, plutôt que dans des idéaux inaccessibles ou des constructions sociales artificielles. &lt;/p&gt;  &lt;audio controls title="La philosophie nous permet d'être d'abord vivants et ensuite libres par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19063-03.04.2023-ITEMA_23336345-2023I32164S0093-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Onfray"  title=" Wikipedia"&gt;Michel ONFRAY&lt;/a&gt; (né en 1959) est un philosophe et essayiste français, l’un des auteurs de philosophie les plus lus et les plus discutés de son pays. Né à Argentan, en Normandie, dans une famille modeste, il enseigne pendant vingt ans la philosophie dans un lycée technique de Caen. En 2002, il fonde l’Université populaire de Caen, aux cours gratuits et ouverts à tous, où il donne pendant des années une « contre-histoire de la philosophie », diffusée par France Culture.&lt;/p&gt; &lt;p&gt;Sa pensée se veut &lt;a href="https://www.youtube.com/watch?v=l4PX2P-KuBE&amp;ab_channel=AlainBajom%C3%A9e"   title="L'hédonisme par Alain Bajomée"&gt;hédoniste&lt;/a&gt;, matérialiste et libertaire. Contre la tradition idéaliste et chrétienne, qui méprise le corps et le plaisir, il réhabilite des penseurs qu’il juge oubliés : les atomistes, les cyrénaïques, Épicure, les libertins ou les utilitaristes. Pour lui, la philosophie doit partir de la vie concrète et du corps, et aider chacun à se construire, à faire la « sculpture de soi ». Son &lt;em&gt;Traité d’athéologie&lt;/em&gt; (2005), critique radicale des trois monothéismes, est un grand succès de librairie. Il a écrit aussi sur l’art, sur la morale et sur les grandes figures de la pensée, souvent de manière polémique : son livre contre Freud, en 2010, a suscité de vives controverses. Dans &lt;em&gt;Décadence&lt;/em&gt; (2017), il décrit l’épuisement de la civilisation judéo-chrétienne. Il a enfin fondé en 2020 la revue &lt;em&gt;Front populaire&lt;/em&gt;, souverainiste, et défend un &lt;a href="https://www.youtube.com/watch?v=wikRuhGQExI&amp;ab_channel=FrontPopulaire"    title="Qu'est ce que le populisme par Front Populaire"&gt;populisme&lt;/a&gt; qui oppose le peuple aux élites. &lt;a href="https://www.youtube.com/watch?v=MNY2U-T2Xf4&amp;ab_channel=MichelOnfray-Topic"  title="Les Raisons de l'Art par Michel Onfray"&gt;&lt;em&gt;Les Raisons de l’art&lt;/em&gt;&lt;/a&gt; montrent aussi son intérêt pour la création.&lt;/p&gt; &lt;p&gt;Ses critiques lui reprochent des simplifications et des lectures partiales de l’histoire de la philosophie ; ses lecteurs saluent un passeur qui rend la philosophie vivante et accessible.&lt;/p&gt;  &lt;audio controls title="La philosophie nous permet d'être d'abord vivants et ensuite libres par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19063-03.04.2023-ITEMA_23336345-2023I32164S0093-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F41" s="34" t="inlineStr">
@@ -3733,7 +3728,7 @@
       </c>
       <c r="E50" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fabienne_Brug%C3%A8re" title=" Wikipedia"&gt;Fabienne BRUGÈRE&lt;/a&gt; est une philosophe française   spécialisée en esthétique, philosophie morale et politique, ainsi qu'en théorie féministe. Elle intègre l'École normale supérieure de Fontenay-Saint-Cloud en 1987 et obtient l'agrégation de philosophie en 1991, après un séjour à l'université de Londres. Sa thèse de 1996 porte sur la théorie de l'art chez Shaftesbury et elle a rejoint Paris-VIII en 2014 pour une chaire en philosophie des arts modernes et contemporains. &lt;/p&gt; &lt;p&gt; Elle a été vice-présidente aux relations internationales à Bordeaux-Montaigne et présidente de l'Université Paris Lumières de 2019 à 2023. Elle a aussi présidé le Conseil de développement durable de Bordeaux Métropole et dirige des collections comme "Perspectives du care" aux éditions de l'ENS Lyon. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'esthétique anglo-américaine, &lt;a href="https://www.youtube.com/watch?v=xa1b8Ks6-LM"  title="2050 IA retour vers demain Thierry ménissier par MAIF "  &gt;l'éthique du care  &lt;/a&gt; (notamment son ouvrage "L’éthique du care" paru en 2011), le féminisme et la sociabilité politique. Parmi ses récents essais : Désaimer. Manuel d’un retour à la vie (2024), La vraie histoire de l’impressionnisme (2024) et On ne naît pas femme, on le devient (2019). &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fabienne_Brug%C3%A8re" title=" Wikipedia"&gt;Fabienne BRUGÈRE&lt;/a&gt; est une philosophe française   spécialisée en esthétique, philosophie morale et politique, ainsi qu'en théorie féministe. Elle intègre l'École normale supérieure de Fontenay-Saint-Cloud en 1987 et obtient l'agrégation de philosophie en 1991, après un séjour à l'université de Londres. Sa thèse de 1996 porte sur la théorie de l'art chez Shaftesbury et elle a rejoint Paris-VIII en 2014 pour une chaire en philosophie des arts modernes et contemporains. &lt;/p&gt; &lt;p&gt; Elle a été vice-présidente aux relations internationales à Bordeaux-Montaigne et présidente de l'Université Paris Lumières de 2019 à 2023. Elle a aussi présidé le Conseil de développement durable de Bordeaux Métropole et dirige des collections comme "Perspectives du care" aux éditions de l'ENS Lyon. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'esthétique anglo-américaine, &lt;a href="https://www.youtube.com/watch?v=PmXPfJIOCUw"  title="Fabienne Brugère - L'Éthique du Care par librairie mollat"&gt;l'éthique du care  &lt;/a&gt; (notamment son ouvrage "L’éthique du care" paru en 2011), le féminisme et la sociabilité politique. Parmi ses récents essais : Désaimer. Manuel d’un retour à la vie (2024), La vraie histoire de l’impressionnisme (2024) et On ne naît pas femme, on le devient (2019). Elle montre que le &lt;em&gt;care&lt;/em&gt;, le soin apporté aux autres, n’est pas une affaire privée réservée aux femmes, mais une question politique qui concerne toute la société et la manière dont elle traite les plus vulnérables. Avec Guillaume le Blanc, elle a aussi écrit sur l’hospitalité et l’accueil des étrangers dans &lt;em&gt;La Fin de l’hospitalité&lt;/em&gt; (2017). &lt;/p&gt; 
 &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Le désamour avec Fabienne Brugère par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-03.05.2024-ITEMA_23729943-2024F45096S0124-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
@@ -3802,8 +3797,8 @@
       </c>
       <c r="E51" s="39" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thierry_M%C3%A9nissier"  title=" Wikipedia"&gt;Thierry MÉNISSIER&lt;/a&gt;  est un philosophe français surtout connu pour ses travaux en philosophie politique et en histoire des idées. Il enseigne à l’université Grenoble Alpes et ses recherches s’appuient beaucoup sur Machiavel et la pensée de la Renaissance. &lt;/p&gt; &lt;p&gt;Sa philosophie s’intéresse d’abord à  &lt;a href="https://www.youtube.com/watch?v=KM8r0dQVwvE"  title="Technologie et socéité soutenable par Agence Urbanisme t"&gt;l’éthique publique &lt;/a&gt;  et à la vie démocratique. Il cherche à comprendre comment les sociétés peuvent se gouverner sans réduire la politique à des principes abstraits, mais en partant des situations concrètes et des rapports de pouvoir. &lt;/p&gt; &lt;p&gt;  Un autre axe important de sa pensée concerne l’innovation et les technologies contemporaines. Il ne voit pas l’innovation comme un simple progrès automatique, mais comme un phénomène ambivalent qui oblige à réfléchir à ses effets sur la liberté, la responsabilité, la démocratie et le sens du bien commun. &lt;/p&gt; &lt;p&gt; Il est le philosophe de l’action, de la décision et des transformations du monde contemporain. Sa pensée cherche à construire une éthique capable d’accompagner les mutations politiques,  &lt;a href="https://www.youtube.com/watch?v=PmXPfJIOCUw"  title="Fabienne Brugère - L'Éthique du Care par librairie mollat"&gt;technologiques et sociales &lt;/a&gt; sans perdre de vue la justice. &lt;/p&gt; 
- &lt;audio controls title="Intelligence artificielle : par delà le bien et le mal par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/14312-30.03.2022-ITEMA_22979351-2022C26360S0089-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thierry_M%C3%A9nissier" title=" Wikipedia"&gt;Thierry MÉNISSIER&lt;/a&gt;  est un philosophe français surtout connu pour ses travaux en philosophie politique et en histoire des idées. Il enseigne à l’université Grenoble Alpes et ses recherches s’appuient beaucoup sur Machiavel et la pensée de la Renaissance. &lt;/p&gt; &lt;p&gt;Sa philosophie s’intéresse d’abord à  &lt;a href="https://www.youtube.com/watch?v=KM8r0dQVwvE" title="Technologie et socéité soutenable par Agence Urbanisme t"&gt;l’éthique publique &lt;/a&gt;  et à la vie démocratique. Il cherche à comprendre comment les sociétés peuvent se gouverner sans réduire la politique à des principes abstraits, mais en partant des situations concrètes et des rapports de pouvoir. &lt;/p&gt; &lt;p&gt;  Un autre axe important de sa pensée concerne l’innovation et les technologies contemporaines. Il ne voit pas l’innovation comme un simple progrès automatique, mais comme un phénomène ambivalent qui oblige à réfléchir à ses effets sur la liberté, la responsabilité, la démocratie et le sens du bien commun. &lt;/p&gt; &lt;p&gt; Il est le &lt;a href="https://www.tumultieordini.com/" title="Tumulti e ordini
+Le blog de Thierry Ménissier"&gt;philosophe de l’action&lt;/a&gt;, de la décision et des transformations du monde contemporain. Sa pensée cherche à construire une éthique capable d’accompagner les mutations politiques,  technologiques et sociales  sans perdre de vue la justice. Spécialiste reconnu de Machiavel, auquel il a consacré plusieurs livres, il retient de lui l’idée que la politique se joue dans les circonstances, les conflits et l’occasion, et non dans l’application de règles éternelles. À Grenoble, il a animé des recherches sur l’éthique de l’innovation et sur l’intelligence artificielle, en associant philosophes, ingénieurs et citoyens à la réflexion sur les technologies. &lt;/p&gt;  &lt;audio controls title="Intelligence artificielle : par delà le bien et le mal par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14312-30.03.2022-ITEMA_22979351-2022C26360S0089-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
@@ -3865,8 +3860,7 @@
       </c>
       <c r="E52" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Judith_Revel"  title=" Wikipedia"&gt;Judith REVEL&lt;/a&gt;  est une philosophe française spécialiste de la pensée française et italienne du xxe-XXIe siècle, notamment autour de Michel Foucault, de la philosophy du langage et de l’histoire de la philosophie. Elle a également dirigé des équipes de recherche et occupé des postes universitaires importants en France, notamment à l’Université Paris 1 Panthéon-Sorbonne et à l’Université Paris-Nanterre, et elle est membre de l’Institut Universitaire de France. &lt;/p&gt; &lt;p&gt;  Son travail porte souvent sur le passage de la biopolitique à la subjectivation chez Foucault, la notion de "commun" comme alternative au duo public/privé, et, plus largement, sur la &lt;a href="https://www.youtube.com/watch?v=Y6J6TIET13w&amp;t=15s"  title=" Judith Revel // Suis-je responsable de l'humanité ? par Philomonaco"&gt;philosophie du présent &lt;/a&gt; et l’usage des archives dans l’interprétation historique. &lt;/p&gt; &lt;p&gt; Plusieurs livres et articles consacrés à Foucault, au langage et à la politique, ainsi qu’à l’histoire de la philosophie française et italienne du après-guerre. Pour une bibliographie précise, les pages universitaires et les fiches de profil listent ses ouvrages et ses contributions. &lt;/p&gt; 
-&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="L'hégémonie culturelle : Gramsci pillé de tous côtés par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-21.04.2025-ITEMA_24109706-2025C48904S0111-NET_MFC_47597AB9-4778-4D51-A8A2-7A3D26AD6489-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Judith_Revel"  title=" Wikipedia"&gt;Judith REVEL&lt;/a&gt; (née en 1966) est une philosophe française, spécialiste de Michel Foucault et de la pensée française et italienne contemporaine. Professeure à l’université Paris-Nanterre, après avoir enseigné à Paris 1 Panthéon-Sorbonne, elle a été membre de l’Institut universitaire de France. Elle a aussi traduit en français plusieurs philosophes italiens, en particulier Toni Negri.&lt;/p&gt; &lt;p&gt;Elle est l’une des meilleures connaisseuses de l’œuvre de Foucault, à laquelle elle a consacré plusieurs livres, dont &lt;em&gt;Le Vocabulaire de Foucault&lt;/em&gt; et un &lt;em&gt;Dictionnaire Foucault&lt;/em&gt;, ainsi qu’une étude sur la manière dont Foucault pense le discontinu, la rupture plutôt que la continuité de l’histoire. Elle montre comment, chez lui, l’analyse des pouvoirs qui façonnent les individus, la discipline puis la biopolitique, débouche sur une réflexion sur la « subjectivation » : la manière dont les sujets peuvent se constituer eux-mêmes, résister et inventer d’autres façons de vivre. Elle a aussi confronté Foucault à Merleau-Ponty. Avec d’autres penseurs, elle a développé la notion de « commun », qui désigne ce qui n’appartient ni à l’État ni aux propriétaires privés, mais est produit et géré ensemble par une communauté, et qui offre une alternative au couple du public et du privé. Plus largement, elle s’interroge sur une &lt;a href="https://www.youtube.com/watch?v=Y6J6TIET13w&amp;t=15s"  title=" Judith Revel // Suis-je responsable de l'humanité ? par Philomonaco"&gt;philosophie du présent&lt;/a&gt; : comment penser l’actualité, les luttes sociales et les transformations du travail.&lt;/p&gt; &lt;p&gt;Son travail relie ainsi l’histoire de la philosophie, la politique et les débats contemporains sur la démocratie, l’hégémonie culturelle et les mouvements sociaux.&lt;/p&gt;  &lt;audio controls title="L'hégémonie culturelle : Gramsci pillé de tous côtés par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-21.04.2025-ITEMA_24109706-2025C48904S0111-NET_MFC_47597AB9-4778-4D51-A8A2-7A3D26AD6489-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F52" s="34" t="inlineStr">
@@ -4192,7 +4186,7 @@
       </c>
       <c r="E57" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/St%C3%A9phane_Haber" title=" Wikipedia"&gt;Stéphane HABER&lt;/a&gt;  est un philosophe français spécialiste de la philosophie sociale et politique, ainsi que de l'épistémologie des sciences humaines. Son doctorat obtenu en 1996 à l'université de Besançon portait sur les formes de connaissance du présent dans les sciences sociales, sous la direction de Robert Damien. &lt;/p&gt; &lt;p&gt; Professeur à l'université Paris Nanterre, il est directeur adjoint du laboratoire Sophiapol. Ses enseignements couvrent l'histoire et l'épistémologie des sciences humaines, la philosophie contemporaine et les problèmes de théorie sociale et politique.&lt;/p&gt; &lt;p&gt;  Ses livres incluent Les Sciences humaines (1995), Habermas et la sociologie (1998), Freud et la théorie sociale (2012), Penser le néocapitalisme (2013). Il a dirigé des ouvrages comme L’Action en philosophie contemporaine (2005) et contribué à des revues sur Marx, l'aliénation et le capitalisme. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur  &lt;a href="https://www.youtube.com/watch?v=ZxECyRcOzFY&amp;t=11s"  title=". Haber : Exploitation du travail, appropriation de la nature, crise climatique. par Penser la Transformation"&gt; les interactions philosophie&lt;/a&gt;/sciences sociales, les marxismes contemporains, le néocapitalisme, l'aliénation subjective et objective, ainsi que les pathologies sociales et la théorie critique.</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/St%C3%A9phane_Haber" title=" Wikipedia"&gt;Stéphane HABER&lt;/a&gt;  est un philosophe français spécialiste de la philosophie sociale et politique, ainsi que de l'épistémologie des sciences humaines. Son doctorat obtenu en 1996 à l'université de Besançon portait sur les formes de connaissance du présent dans les sciences sociales, sous la direction de Robert Damien. &lt;/p&gt; &lt;p&gt; Professeur à l'université Paris Nanterre, il est directeur adjoint du laboratoire Sophiapol. Ses enseignements couvrent l'histoire et l'épistémologie des sciences humaines, la philosophie contemporaine et les problèmes de théorie sociale et politique.&lt;/p&gt; &lt;p&gt;  Ses livres incluent Les Sciences humaines (1995), Habermas et la sociologie (1998), Freud et la théorie sociale (2012), Penser le néocapitalisme (2013). Il a dirigé des ouvrages comme L’Action en philosophie contemporaine (2005) et contribué à des revues sur Marx, l'aliénation et le capitalisme. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur  &lt;a href="https://www.youtube.com/watch?v=ZxECyRcOzFY&amp;t=11s"  title=". Haber : Exploitation du travail, appropriation de la nature, crise climatique. par Penser la Transformation"&gt; les interactions philosophie&lt;/a&gt;/sciences sociales, les marxismes contemporains, le néocapitalisme, l'aliénation subjective et objective, ainsi que les pathologies sociales et la théorie critique. Dans &lt;em&gt;L’Aliénation&lt;/em&gt; (2007), il redonne vie à cette notion héritée de Hegel et de Marx : on est aliéné quand on ne se reconnaît plus dans sa propre vie, ses activités ou ses institutions. Il montre que l’idée reste utile pour décrire les souffrances sociales d’aujourd’hui. Dans &lt;em&gt;Penser le néocapitalisme&lt;/em&gt;, il analyse un capitalisme qui s’étend à toutes les dimensions de l’existence, et ses travaux récents relient l’exploitation du travail et celle de la nature.</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
@@ -4447,7 +4441,7 @@
       </c>
       <c r="E61" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://www.philomag.com/philosophes/laurence-devillairs"  title=" Wikipedia"&gt;Laurence DEVILLAIRS&lt;/a&gt;  est une philosophe française, spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle. Elle enseigne à l’université Paris 1 Panthéon-Sorbonne et s’adresse aussi à un large public à travers des essais et des interventions. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse beaucoup à la morale concrète : le bien, le mal, &lt;a href="https://www.youtube.com/watch?v=a5YnPWx7Xw8" title="laurence Devillairs : Eloge de la gentillesse par Brut"&gt; la gentillesse, &lt;/a&gt; le courage, la justice. Elle refuse une vision trop abstraite de l’éthique et cherche plutôt à montrer comment on devient une &lt;a href="https://www.youtube.com/watch?v=T0U2ro8b9Io" title="laurence Devillairs : a quoi reconnaître quelqu’un de bien par TV Monde"&gt; personne meilleure &lt;/a&gt; dans la vie quotidienne. &lt;/p&gt; &lt;p&gt; Elle réfléchit aussi au politique, mais d’une manière très humaine : comment vivre ensemble, comment &lt;a href="https://www.youtube.com/watch?v=p9AaVfIoIPg" title="laurence Devillairs : le pouvoir par Fabrice Midal"&gt; penser le pouvoir, &lt;/a&gt; comment garder une place pour l’utopie et l’espérance sans perdre le sens du réel. Chez elle, le politique n’est pas seulement affaire de règles, mais aussi de désir de transformation. &lt;/p&gt; &lt;p&gt; On peut dire que sa philosophie défend une forme de fermeté douce : être bon ne veut pas dire être faible, et la gentillesse peut être un choix éthique fort. Son travail cherche à rendre la philosophie utile pour mieux vivre, mieux juger et mieux agir. &lt;/p&gt;  &lt;audio controls title="Laurence Devillairs : le désir de vengeance est une libération  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.04.2026-ITEMA_24449483-2026F22640S0095-NET_MFI_BFCBC71B-F523-4D4D-9C0D-E455E058A13C-22-23fd728f6afa552353ce5d4ded4690c9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://www.philomag.com/philosophes/laurence-devillairs"  title=" Wikipedia"&gt;Laurence DEVILLAIRS&lt;/a&gt;  est une philosophe française, spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle. Elle enseigne à l’université Paris 1 Panthéon-Sorbonne et s’adresse aussi à un large public à travers des essais et des interventions. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse beaucoup à la morale concrète : le bien, le mal, &lt;a href="https://www.youtube.com/watch?v=a5YnPWx7Xw8" title="laurence Devillairs : Eloge de la gentillesse par Brut"&gt; la gentillesse, &lt;/a&gt; le courage, la justice. Elle refuse une vision trop abstraite de l’éthique et cherche plutôt à montrer comment on devient une &lt;a href="https://www.youtube.com/watch?v=T0U2ro8b9Io" title="laurence Devillairs : a quoi reconnaître quelqu’un de bien par TV Monde"&gt; personne meilleure &lt;/a&gt; dans la vie quotidienne. &lt;/p&gt; &lt;p&gt; Elle réfléchit aussi au politique, mais d’une manière très humaine : comment vivre ensemble, comment &lt;a href="https://www.youtube.com/watch?v=p9AaVfIoIPg" title="laurence Devillairs : le pouvoir par Fabrice Midal"&gt; penser le pouvoir, &lt;/a&gt; comment garder une place pour l’utopie et l’espérance sans perdre le sens du réel. Chez elle, le politique n’est pas seulement affaire de règles, mais aussi de désir de transformation. &lt;/p&gt; &lt;p&gt; On peut dire que sa philosophie défend une forme de fermeté douce : être bon ne veut pas dire être faible, et la gentillesse peut être un choix éthique fort. Son travail cherche à rendre la philosophie utile pour mieux vivre, mieux juger et mieux agir. Lectrice de Descartes, elle retient de lui le goût de la clarté et de la générosité, cette juste estime de soi qui consiste à bien user de sa liberté. Dans &lt;em&gt;Être quelqu’un de bien&lt;/em&gt; (2019), elle montre que la bonté n’est pas une naïveté, mais une forme de courage, et qu’elle se joue d’abord dans les gestes ordinaires, l’attention, la parole donnée, le refus de l’humiliation. &lt;/p&gt;  &lt;audio controls title="Laurence Devillairs : le désir de vengeance est une libération  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.04.2026-ITEMA_24449483-2026F22640S0095-NET_MFI_BFCBC71B-F523-4D4D-9C0D-E455E058A13C-22-23fd728f6afa552353ce5d4ded4690c9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -4515,8 +4509,7 @@
       </c>
       <c r="E62" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Delecroix"  title=" Wikipedia"&gt;Vincent DELECROIX&lt;/a&gt;  est un philosophe français spécialiste de Kierkegaard et de la philosophie de la religion. Il enseigne à l’EPHE, où il travaille sur la vérité, la croyance et les liens entre religion et pensée contemporaine. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse d’abord à la manière dont la foi peut exister dans un monde moderne où les certitudes absolues se  &lt;a href="https://www.youtube.com/watch?v=2ZHOpP5GMwI" title="Vincent DELECROIX,la nécessité d’apprendre par TV5 monde"&gt;sont affaiblies. &lt;/a&gt; Il ne traite pas la religion comme un simple héritage figé, mais comme une expérience intérieure, fragile et exigeante.  &lt;/p&gt; &lt;p&gt; Un autre axe important chez lui est la révolte. À travers des livres comme Tombeau d’Achille et Non ! De l’esprit de révolte, il réfléchit à la colère, au refus et à la parole &lt;a href="https://www.youtube.com/watch?v=OiUgp6wLpCA" title="Vincent DELECROIX il faut sortir du oui non par France Culture"&gt;qui dit non, &lt;/a&gt; non comme de simples réactions, mais comme des forces qui révèlent une vérité humaine et morale. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il  est un philosophe de la tension entre vérité, foi et révolte. Sa pensée cherche à comprendre comment l’être humain peut garder une voix, une conscience et une exigence spirituelle dans un monde désorienté. &lt;/p&gt;  &lt;audio controls title="Vincent DELECROIX  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Delecroix"  title=" Wikipedia"&gt;Vincent DELECROIX&lt;/a&gt; (né en 1969) est un philosophe et romancier français, spécialiste de Kierkegaard et de la philosophie de la religion. Agrégé de philosophie, il est directeur d’études à l’École pratique des hautes études (EPHE), où il enseigne la philosophie de la religion, et il a dirigé l’édition et la traduction de plusieurs œuvres de Kierkegaard.&lt;/p&gt; &lt;p&gt;Son travail interroge la manière dont la foi peut encore exister dans un monde moderne où les certitudes absolues &lt;a href="https://www.youtube.com/watch?v=2ZHOpP5GMwI" title="Vincent DELECROIX,la nécessité d’apprendre par TV5 monde"&gt;se sont affaiblies&lt;/a&gt;. À la suite de Kierkegaard, il ne traite pas la religion comme un héritage figé ou un ensemble de dogmes, mais comme une expérience intérieure, fragile et exigeante, où l’individu est engagé tout entier. La vérité, dans ce domaine, n’est pas un savoir objectif que l’on possède, mais une manière d’exister. Il réfléchit aussi aux rapports entre religion et politique, et à la façon dont les espérances religieuses se transforment dans les idéologies modernes. Un autre axe important de sa pensée est la révolte. Dans &lt;em&gt;Tombeau d’Achille&lt;/em&gt;, il médite sur la colère du héros d’Homère ; dans &lt;em&gt;Non ! De l’esprit de révolte&lt;/em&gt;, il réfléchit au refus et à la parole &lt;a href="https://www.youtube.com/watch?v=OiUgp6wLpCA" title="Vincent DELECROIX il faut sortir du oui non par France Culture"&gt;qui dit non&lt;/a&gt;, non comme de simples réactions d’humeur, mais comme des actes qui révèlent une exigence morale : refuser l’inacceptable, c’est affirmer qu’il existe quelque chose qui vaut.&lt;/p&gt; &lt;p&gt;Romancier, il a publié plusieurs livres où la fiction devient une autre manière de philosopher. Sa pensée cherche comment l’être humain peut garder une voix et une exigence spirituelle dans un monde désorienté.&lt;/p&gt;  &lt;audio controls title="Vincent DELECROIX  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F62" s="34" t="inlineStr">
@@ -4706,8 +4699,8 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Stiegler" title=" Wikipedia"&gt;Barbara STIEGLER&lt;/a&gt;  est une philosophe française, fille du philosophe Bernard Stiegler, spécialiste de Nietzsche, de philosophie politique et critique du néolibéralisme. Agrégée de philosophie, elle soutient sa thèse en 2003 à Paris-Sorbonne sous la direction de Jean-Luc Marion sur Nietzsche et la biologie. Maître de conférences puis professeure à l'université Bordeaux-Montaigne depuis 2006, elle y dirige le master  &lt;a href="https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf" title="Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne"&gt;"Soin, éthique et santé". &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Engagée politiquement, elle analyse les Gilets Jaunes dans "Du cap aux grèves" paru en 2021 et critique l’adaptationnisme comme fondement du néolibéralisme, opposant une intelligence collective à l’élitisme technocratique. &lt;/p&gt; &lt;p&gt; Ses ouvrages sur Nietzsche explorent le corps et la vie (Nietzsche et la biologie, 2001 ; Nietzsche et la critique de la chair, 2005 ; Nietzsche et la vie, 2021). &lt;/p&gt; &lt;p&gt;  Elle étend ses recherches au politique avec  &lt;a href="https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/" title="Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit"&gt;"Il faut s’adapter" &lt;/a&gt; paru en  2019, dénonçant les racines évolutionnistes (Spencer, Lippmann) du &lt;a href="https://www.youtube.com/watch?v=oQQ4xqRvYTk" style="color:#88A1E9" title="LA LENTE AGONIE DU NÉOLIBÉRALISME  par 
-TheSwissBox Conversation"&gt;néolibéralisme &lt;/a&gt; face au pragmatisme démocratique de Dewey. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Stiegler" title=" Wikipedia"&gt;Barbara STIEGLER&lt;/a&gt; (née en 1971) est une philosophe française, spécialiste de Nietzsche et de philosophie politique, connue pour sa critique du néolibéralisme. Fille du philosophe Bernard Stiegler, agrégée de philosophie, elle est professeure à l’université Bordeaux-Montaigne, où elle a dirigé le master &lt;a href="https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf" title="Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne"&gt;« Soin, éthique et santé »&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Ses premiers travaux portent sur Nietzsche et la biologie de son temps. Dans &lt;em&gt;Nietzsche et la biologie&lt;/em&gt; (2001) et &lt;em&gt;Nietzsche et la critique de la chair&lt;/em&gt; (2005), elle montre que la pensée de Nietzsche dialogue avec les sciences du vivant, et que le corps et la vie y sont des notions centrales. Elle se tourne ensuite vers la philosophie politique. Dans &lt;a href="https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/" title="Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit"&gt;&lt;em&gt;« Il faut s’adapter »&lt;/em&gt;&lt;/a&gt; (2019), elle remonte aux origines du &lt;a href="https://www.youtube.com/watch?v=oQQ4xqRvYTk" style="color:#88A1E9" title="LA LENTE AGONIE DU NÉOLIBÉRALISME  par 
+TheSwissBox Conversation"&gt;néolibéralisme&lt;/a&gt; : au début du XXe siècle, le journaliste américain Walter Lippmann, inspiré par une lecture de la théorie de l’évolution, soutenait que les peuples, en retard sur un monde qui change trop vite, devaient être adaptés par des experts au nouvel environnement mondialisé. Contre lui, le philosophe John Dewey défendait une démocratie fondée sur l’intelligence collective et la participation des citoyens. Barbara Stiegler montre que ce débat oublié éclaire nos sociétés, où l’injonction à s’adapter s’impose à l’école, au travail et dans la santé. Elle a ensuite appliqué ces analyses aux mouvements sociaux, dans &lt;em&gt;Du cap aux grèves&lt;/em&gt; (2020), puis à la crise de la covid, dans &lt;em&gt;De la démocratie en pandémie&lt;/em&gt; (2021).&lt;/p&gt; &lt;p&gt;Engagée dans le débat public, elle plaide pour une démocratie plus participative et pour une autre conception de la santé publique.&lt;/p&gt;  &lt;audio controls title="La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F65" s="34" t="inlineStr">
@@ -5935,7 +5928,7 @@
       </c>
       <c r="E84" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Charbonnier_(philosophe)"  title=" Wikipedia"&gt;Pierre CHARDONNIER&lt;/a&gt; est un philosophe français spécialiste de philosophie politique et de philosophie de l'environnement et de l'écologie. &lt;a href="https://laviedesidees.fr/_Charbonnier-Pierre_" title="ÉCOPO - Pierre Charbonnier par College de France"&gt;Ses travaux&lt;/a&gt; portent sur l'histoire des sciences sociales et de la pensée politique, en particulier sur la manière dont elles abordent la relation entre nature et société et s'intéresse aux systèmes de pensée et d'encadrement du milieu naturel, aux crises politiques et écologiques, et à la place de l'écologie dans le processus de démocratisation. &lt;/p&gt; &lt;p&gt; Son livre &lt;a href="https://www.youtube.com/watch?v=6s54KzHUmRU" title="ÉCOPO - Pierre Charbonnier, Abondance et liberté par Game Of Hearth"&gt;"Abondance et liberté"&lt;/a&gt; : Une histoire environnementale des idées politiques a rencontré un certain succès médiatique et explore l'histoire des idées politiques à travers le prisme des enjeux environnementaux. Il y analyse comment nos conceptions de la liberté et de l'abondance sont historiquement liées à notre rapport à la nature. &lt;/p&gt; &lt;p&gt; Plus récent, son ouvrage   &lt;a href="https://www.youtube.com/watch?v=HslDCTZNq2M"  title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt;"Vers l'écologie de guerre"&lt;/a&gt; : Une histoire environnementale de la paix, il propose une relecture de l'histoire des relations internationales et des conflits à travers le prisme des enjeux écologiques. &lt;/p&gt;  &lt;audio controls title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25343-29.08.2024-ITEMA_23842702-2024C53458S0242-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Charbonnier_(philosophe)"  title=" Wikipedia"&gt;Pierre CHARBONNIER&lt;/a&gt; est un philosophe français spécialiste de philosophie politique et de philosophie de l'environnement et de l'écologie. &lt;a href="https://laviedesidees.fr/_Charbonnier-Pierre_" title="ÉCOPO - Pierre Charbonnier par College de France"&gt;Ses travaux&lt;/a&gt; portent sur l'histoire des sciences sociales et de la pensée politique, en particulier sur la manière dont elles abordent la relation entre nature et société et s'intéresse aux systèmes de pensée et d'encadrement du milieu naturel, aux crises politiques et écologiques, et à la place de l'écologie dans le processus de démocratisation. &lt;/p&gt; &lt;p&gt; Son livre &lt;a href="https://www.youtube.com/watch?v=6s54KzHUmRU" title="ÉCOPO - Pierre Charbonnier, Abondance et liberté par Game Of Hearth"&gt;"Abondance et liberté"&lt;/a&gt; : Une histoire environnementale des idées politiques a rencontré un certain succès médiatique et explore l'histoire des idées politiques à travers le prisme des enjeux environnementaux. Il y analyse comment nos conceptions de la liberté et de l'abondance sont historiquement liées à notre rapport à la nature. &lt;/p&gt; &lt;p&gt; Plus récent, son ouvrage   &lt;a href="https://www.youtube.com/watch?v=HslDCTZNq2M"  title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt;"Vers l'écologie de guerre"&lt;/a&gt; : Une histoire environnementale de la paix, il propose une relecture de l'histoire des relations internationales et des conflits à travers le prisme des enjeux écologiques. Chercheur au CNRS, rattaché à Sciences Po, il montre que la démocratie libérale moderne s’est construite sur une promesse d’abondance rendue possible par l’exploitation de la terre, puis du charbon et du pétrole. La crise climatique oblige donc à repenser ce que nous entendons par liberté, sans renoncer à l’idéal d’émancipation. Il invite ainsi à faire de l’écologie une question centrale de la philosophie politique. &lt;/p&gt;  &lt;audio controls title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25343-29.08.2024-ITEMA_23842702-2024C53458S0242-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
@@ -6120,7 +6113,7 @@
       </c>
       <c r="E87" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Norman_Ajari"  title=" Wikipedia"&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href="https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari"  title="Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse"&gt;"études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href="https://www.youtube.com/watch?v=IMUBi9oi2WM" title="Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche"&gt;"colonialité de l’être" &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=ECSmpOXY8kg" title="NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS"&gt;"La Dignité ou la mort", &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de "philosophe militant" : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. &lt;/p&gt; &lt;audio controls title="où commence et où finit le racisme? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Norman_Ajari"  title=" Wikipedia"&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href="https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari"  title="Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse"&gt;"études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href="https://www.youtube.com/watch?v=IMUBi9oi2WM" title="Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche"&gt;"colonialité de l’être" &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=ECSmpOXY8kg" title="NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS"&gt;"La Dignité ou la mort", &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de "philosophe militant" : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. Né en 1987, formé à l’université de Toulouse, il enseigne aux États-Unis, à l’université Villanova. Dans &lt;em&gt;La Dignité ou la mort. Éthique et politique de la race&lt;/em&gt; (2019), il soutient que l’expérience noire moderne, de l’esclavage aux violences policières, ne peut être comprise par les catégories habituelles de la philosophie morale, et qu’elle appelle une éthique de la dignité face à la mort sociale. Il a aussi fait connaître en France les débats du courant « afro-pessimiste » américain. &lt;/p&gt; &lt;audio controls title="où commence et où finit le racisme? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E25" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Bruckner"  title=" Wikipedia"&gt;Pascal BRUCKNER&lt;/a&gt;  est un philosophe, essayiste et romancier français figure des "nouveaux philosophes" des années 1970 et membre de l’Académie Goncourt depuis 2019. Il fustige la "tyrannie de la culpabilité" occidentale, le victimarisme contemporain et les excès du wokisme. &lt;/p&gt; &lt;p&gt; Il est un philosophe critique de &lt;a href="https://www.revuedesdeuxmondes.fr/pascal-bruckner-declinisme-et-catastrophisme-provoquent-des-ravages-dans-nos-esprits/" title="Pascal Bruckner : Déclinisme et catastrophisme provoquent des ravages dans nos esprits par Revue des deux mondes"&gt;l’auto-flagellation occidentale, &lt;/a&gt; défendant une forme de libéralisme éclairé qui rejette à la fois le tiers-mondisme culpabilisant, le victimarisme contemporain et les excès anticapitalistes. Pro-israélien et atlantiste, il défend l’héritage des Lumières contre les &lt;a href="https://www.youtube.com/watch?v=wNrAmA6zIQU"  title="L’homme blanc, de l’intouchable au bouc émissaire avec Pascal Bruckner par France Culture"&gt;idéologies déconstructrices, &lt;/a&gt;  tout en explorant paradoxalement les mythologies sexuelles post-68. Dès 1977, avec Finkielkraut, il publie "Le Nouveau Désordre amoureux", critique des utopies amoureuses post-68, qui le propulse dans le paysage intellectuel. &lt;/p&gt; &lt;p&gt; Son essai "Le Sanglot de l’homme blanc" paru en 1983 dénonce le tiers-mondisme culpabilisant de l’Occident, marquant son éloignement de la gauche libertaire pour un positionnement néoconservateur. Il critique ensuite l’auto-flagellation occidentale dans "La Tyrannie de la pénitence" paru en  2006 et l’anticapitalisme dans "Misère de la prospérité" paru en 2002. &lt;/p&gt;  &lt;audio controls title="Pascal Bruckner, au fil de la plume par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-06.06.2021-ITEMA_22685386-2021C3500E0081.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Bruckner"  title=" Wikipedia"&gt;Pascal BRUCKNER&lt;/a&gt; (né en 1948) est un philosophe, essayiste et romancier français, membre de l’Académie Goncourt depuis 2019. Il se fait connaître en 1977 avec &lt;em&gt;Le Nouveau Désordre amoureux&lt;/em&gt;, écrit avec Alain Finkielkraut, une critique des utopies sexuelles nées de Mai 68, qui l’associe à la génération des « nouveaux philosophes ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Sanglot de l’homme blanc&lt;/em&gt; (1983), il critique le tiers-mondisme, qui selon lui idéalise les pays du Sud et entretient chez les Occidentaux une culpabilité stérile. Ce thème de la mauvaise conscience occidentale traverse son œuvre : dans &lt;em&gt;La Tyrannie de la pénitence&lt;/em&gt; (2006), il dénonce ce qu’il appelle &lt;a href="https://www.revuedesdeuxmondes.fr/pascal-bruckner-declinisme-et-catastrophisme-provoquent-des-ravages-dans-nos-esprits/" title="Pascal Bruckner : Déclinisme et catastrophisme provoquent des ravages dans nos esprits par Revue des deux mondes"&gt;l’auto-flagellation&lt;/a&gt; de l’Europe, qui l’empêcherait de défendre ses propres valeurs. Il s’en prend aussi à certaines tendances de la société contemporaine. &lt;em&gt;La Tentation de l’innocence&lt;/em&gt; (1995), prix Médicis de l’essai, décrit un individu qui fuit ses responsabilités en se réfugiant dans l’enfance ou dans le statut de victime. &lt;em&gt;L’Euphorie perpétuelle&lt;/em&gt; (2000) critique l’obligation moderne d’être heureux, et &lt;em&gt;Le Fanatisme de l’apocalypse&lt;/em&gt; (2011) le catastrophisme d’une partie de l’écologie. Plus récemment, il a critiqué les &lt;a href="https://www.youtube.com/watch?v=wNrAmA6zIQU"  title="L’homme blanc, de l’intouchable au bouc émissaire avec Pascal Bruckner par France Culture"&gt;idéologies&lt;/a&gt; qui font de « l’homme blanc » un coupable désigné. Défenseur de l’héritage des Lumières, de l’universalisme et de la démocratie libérale, il est souvent classé parmi les intellectuels libéraux et atlantistes, et ses positions suscitent de vifs débats.&lt;/p&gt; &lt;p&gt;Romancier, il est aussi l’auteur de &lt;em&gt;Lunes de fiel&lt;/em&gt; (1981), adapté au cinéma par Roman Polanski.&lt;/p&gt;  &lt;audio controls title="Pascal Bruckner, au fil de la plume par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-06.06.2021-ITEMA_22685386-2021C3500E0081.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F25" s="34" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="E39" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Engel"   title=" Wikipedia"&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent "La Norme du vrai" paru en 1989 sur la philosophie de la logique, &lt;a href="https://www.youtube.com/watch?v=ivsIBYFN6DI" title="*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos"&gt; "Va savoir"&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et "Les vices du savoir" en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il l défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Faut-il faire la morale aux intellectuels ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Engel"   title=" Wikipedia"&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent "La Norme du vrai" paru en 1989 sur la philosophie de la logique, &lt;a href="https://www.youtube.com/watch?v=ivsIBYFN6DI" title="*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos"&gt; "Va savoir"&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et "Les vices du savoir" en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. Pour lui, la croyance a une norme propre : croire, c’est viser la vérité, et l’on ne peut croire à volonté ce que l’on sait faux. Dans &lt;em&gt;Les Vices du savoir&lt;/em&gt;, il montre que l’indifférence à la vérité, le « baratin » et la paresse intellectuelle sont de véritables fautes morales, dont les intellectuels eux-mêmes ne sont pas exempts. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Faut-il faire la morale aux intellectuels ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E46" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon"  title=" Wikipedia"&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href="https://www.youtube.com/watch?v=xOKttB1HgSk"  title="Marc Crépon sur la violence  par France Inter "&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href="https://www.youtube.com/watch?v=kwFC9MSSWcg"  title="Marc Crépon : l’épreuve de la haine   par Librairie mollat "&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; On peut dire qu’il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste.  &lt;/p&gt; &lt;audio controls title="Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon"  title=" Wikipedia"&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href="https://www.youtube.com/watch?v=xOKttB1HgSk"  title="Marc Crépon sur la violence  par France Inter "&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href="https://www.youtube.com/watch?v=kwFC9MSSWcg"  title="Marc Crépon : l’épreuve de la haine   par Librairie mollat "&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; On peut dire qu’il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste. Directeur de recherche au CNRS, il a d’abord étudié la manière dont les philosophes allemands et français pensent les langues et les cultures. Dans &lt;em&gt;Le Consentement meurtrier&lt;/em&gt; (2012), il s’interroge sur la façon dont nous acceptons, souvent sans le voir, la violence faite à d’autres, par la guerre, la misère ou l’indifférence. Dans &lt;em&gt;L’Épreuve de la haine&lt;/em&gt; (2016) il cherche comment résister à la haine sans y répondre par la haine.  &lt;/p&gt; &lt;audio controls title="Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="E59" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Franck_Fischbach"  style="color:#6A142A"  title=" Wikipedia"&gt;Franck FISCHBACH&lt;/a&gt; est un philosophe franço-suisse  spécialiste de la philosophie allemande et de la philosophie sociale. Ses recherches portent sur l’idéalisme allemand (particulièrement Fichte, Hegel et Schelling), la réception de Marx et la philosophie sociale contemporaine. Il s’intéresse notamment à la reconnaissance, à l’aliénation, au travail, au socialisme, et à la &lt;a href="https://www.philomag.com/articles/franck-fischbach-le-capitalisme-fabrique-des-etres-qui-netant-plus-vraiment-sociaux-ne" style="color:#88A1E9" title=" Franck Fischbach : “Le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains” par philosophie magazine"&gt;critique du capitalisme&lt;/a&gt;. Il contribue activement à redonner à la philosophie sociale une légitimité intellectuelle en France. &lt;/p&gt; &lt;p&gt; Il relie la tradition de la théorie critique (Adorno, Honneth) et celle du matérialisme marxien pour repenser les conditions de la vie sociale et du « vivre ensemble ». Il analyse le capitalisme contemporain comme un processus de désocialisation et de perte du monde commun, considérant que "le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains".​ &lt;/p&gt; &lt;p&gt; Il  a reçu le Prix des Rencontres philosophiques de Monaco pour &lt;a href="https://www.youtube.com/watch?v=i16BcDagxns&amp;t=73s" style="color:#88A1E9" title=" Franck Fischbach → Faire ensemble. Reconstruction sociale et sortie du capitalisme par Librairie Ombre Blanche"&gt;"Faire ensemble"&lt;/a&gt;, ouvrage dans lequel il propose une refondation du lien social et une sortie éthique du capitalisme et il est aujourd’hui reconnu comme l’un des penseurs français majeurs de la philosophie sociale, prolongeant la critique marxienne à la lumière des défis écologiques et politiques contemporains.​ &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Qu'est-ce que la philosophie sociale? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11188-25.03.2010-ITEMA_20221135-2010C14987S0084-NET_B0358179-5AB7-42B6-8D32-144EADE35F65_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Franck_Fischbach"  style="color:#6A142A"  title=" Wikipedia"&gt;Franck FISCHBACH&lt;/a&gt; est un philosophe franco-suisse  spécialiste de la philosophie allemande et de la philosophie sociale. Ses recherches portent sur l’idéalisme allemand (particulièrement Fichte, Hegel et Schelling), la réception de Marx et la philosophie sociale contemporaine. Il s’intéresse notamment à la reconnaissance, à l’aliénation, au travail, au socialisme, et à la &lt;a href="https://www.philomag.com/articles/franck-fischbach-le-capitalisme-fabrique-des-etres-qui-netant-plus-vraiment-sociaux-ne" style="color:#88A1E9" title=" Franck Fischbach : “Le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains” par philosophie magazine"&gt;critique du capitalisme&lt;/a&gt;. Il contribue activement à redonner à la philosophie sociale une légitimité intellectuelle en France. &lt;/p&gt; &lt;p&gt; Il relie la tradition de la théorie critique (Adorno, Honneth) et celle du matérialisme marxien pour repenser les conditions de la vie sociale et du « vivre ensemble ». Il analyse le capitalisme contemporain comme un processus de désocialisation et de perte du monde commun, considérant que "le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains".​ &lt;/p&gt; &lt;p&gt; Il  a reçu le Prix des Rencontres philosophiques de Monaco pour &lt;a href="https://www.youtube.com/watch?v=i16BcDagxns&amp;t=73s" style="color:#88A1E9" title=" Franck Fischbach → Faire ensemble. Reconstruction sociale et sortie du capitalisme par Librairie Ombre Blanche"&gt;"Faire ensemble"&lt;/a&gt;, ouvrage dans lequel il propose une refondation du lien social et une sortie éthique du capitalisme et il est aujourd’hui reconnu comme l’un des penseurs français majeurs de la philosophie sociale, prolongeant la critique marxienne à la lumière des défis écologiques et politiques contemporains.​ &lt;/p&gt; Professeur à l’université de Strasbourg, il a publié un &lt;em&gt;Manifeste pour une philosophie sociale&lt;/em&gt; (2009), qui veut redonner à la philosophie la tâche de diagnostiquer les « pathologies » de la société. Dans &lt;em&gt;La Privation de monde&lt;/em&gt; (2011), il décrit l’aliénation contemporaine comme une perte de prise sur le temps, l’espace et le monde commun.  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Qu'est-ce que la philosophie sociale? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11188-25.03.2010-ITEMA_20221135-2010C14987S0084-NET_B0358179-5AB7-42B6-8D32-144EADE35F65_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="E64" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Mehl"  title=" Wikipedia"&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href="https://www.youtube.com/watch?v=NT0n7tKNb3w" title="qu’est ce que la verité par Le forum Veritas"&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Mehl"  title=" Wikipedia"&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href="https://www.youtube.com/watch?v=NT0n7tKNb3w" title="qu’est ce que la verité par Le forum Veritas"&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. Il a notamment étudié le jeune Descartes lors de son séjour en Allemagne, en 1619-1620, au moment de ses célèbres songes et de la naissance de sa méthode, ainsi que ses rapports avec Kepler et les savants de son temps. Il montre que la métaphysique cartésienne est inséparable d’un projet de physique et de cosmologie, qui vise à rendre le monde visible et intelligible tout entier. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="E66" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yves_Cusset"  style="color:#6A142A"  title=" Wikipedia"&gt;Yves CUSSET&lt;/a&gt;  est un philosophe français agrégé et docteur en philosophie, qui allie une réflexion sérieuse sur la philosophie politique à un engagement théâtral et  &lt;a href="https://www.youtube.com/watch?v=uJLmpAgqiWY" style="color:#88A1E9" title="Yves Cusset, Petit manuel d'engagement politique à l'usage des mammifères doués de raison.... par Yves Cusset"&gt;humoristique unique. &lt;/a&gt;  Spécialiste de Habermas et Foucault, il explore les tensions entre raison discussionnelle et pouvoir, ainsi que les apories de l’accueil : comment concilier exigence éthique d’hospitalité et contraintes politiques. &lt;/p&gt; &lt;p&gt; Ses essais interrogent le "bien-mourir", critiquant les normes contemporaines de la mort apaisée, et défendent une politique de l’accueil face à la misère du monde.  Il théorise l’humour comme "bonne humeur pour mourir", un outil philosophique qui désarme les idées fixes et favorise la pensée sans intimidation. Il crée des solos comme Rien ne sert d’exister, Tractatus philo-comicus ou La Philosophie enseignée à ma chouette, joués au festival d’Avignon et ailleurs, mêlant rire, absurdité et métaphysique. &lt;/p&gt; &lt;p&gt; Militant discret, il use de l’humour politique pour dénoncer clichés  &lt;a href="https://www.youtube.com/watch?v=QwVPt_PQE-Q" style="color:#88A1E9" title="Yves Cusset : 100 façons de ne pas accueillir un migrant par TV5Monde"&gt;anti-migrants &lt;/a&gt; ou dérives du "développement personnel".  Son genre hybride, l’"humour philosophique", vise à émerveiller par le rire, suscitant la réflexion sans complexer, comme il l’explique dans Le Monde. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yves_Cusset"  style="color:#6A142A"  title=" Wikipedia"&gt;Yves CUSSET&lt;/a&gt;  est un philosophe français agrégé et docteur en philosophie, qui allie une réflexion sérieuse sur la philosophie politique à un engagement théâtral et  &lt;a href="https://www.youtube.com/watch?v=uJLmpAgqiWY" style="color:#88A1E9" title="Yves Cusset, Petit manuel d'engagement politique à l'usage des mammifères doués de raison.... par Yves Cusset"&gt;humoristique unique. &lt;/a&gt;  Spécialiste de Habermas et Foucault, il explore les tensions entre raison discussionnelle et pouvoir, ainsi que les apories de l’accueil : comment concilier exigence éthique d’hospitalité et contraintes politiques. &lt;/p&gt; &lt;p&gt; Ses essais interrogent le "bien-mourir", critiquant les normes contemporaines de la mort apaisée, et défendent une politique de l’accueil face à la misère du monde.  Il théorise l’humour comme "bonne humeur pour mourir", un outil philosophique qui désarme les idées fixes et favorise la pensée sans intimidation. Il crée des solos comme Rien ne sert d’exister, Tractatus philo-comicus ou La Philosophie enseignée à ma chouette, joués au festival d’Avignon et ailleurs, mêlant rire, absurdité et métaphysique. &lt;/p&gt; &lt;p&gt; Militant discret, il use de l’humour politique pour dénoncer clichés  &lt;a href="https://www.youtube.com/watch?v=QwVPt_PQE-Q" style="color:#88A1E9" title="Yves Cusset : 100 façons de ne pas accueillir un migrant par TV5Monde"&gt;anti-migrants &lt;/a&gt; ou dérives du "développement personnel".  Son genre hybride, l’"humour philosophique", vise à émerveiller par le rire, suscitant la réflexion sans complexer, comme il l’explique dans Le Monde. Ses premiers travaux portent sur Habermas, dont il présente l’« éthique de la discussion » : une norme n’est valable que si tous ceux qu’elle concerne pourraient l’accepter au terme d’une discussion libre. Il en tire une exigence démocratique, mais aussi une attention à ceux qui n’ont pas la parole. Pour lui, le rire n’est pas une fuite hors de la pensée : il oblige à prendre de la distance avec soi-même et avec les certitudes. &lt;/p&gt; 
 &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="L'amour avec Yves Cusset par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-07.06.2024-ITEMA_23765968-2024F45096S0159-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="E70" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mehdi_Belhaj_Kacem"   title=" Wikipedia"&gt;Mehdi BELHAY KACEM&lt;/a&gt;   est un philosophe, écrivain et acteur franco-tunisien, autodidacte radical et figure controversée de la pensée contemporaine, passé par les milieux militants et   &lt;a href="https://blogs.mediapart.fr/olivier-rachet/blog/130525/le-manifeste-conspirationniste-de-mehdi-belhaj-kacem" title="Le manifeste conspirationniste de Mehdi Belhaj Kacempar par mediapart"&gt;littéraires underground &lt;/a&gt; avant de forger une œuvre philosophique exigeante et iconoclaste. Après des expériences communautaires militantes, il découvre Alain Badiou comme maître à penser initial. &lt;/p&gt; &lt;p&gt; Il développe une pensée du nihilisme héritée de Heidegger, Nietzsche et Schürmann, centrée sur le "pléonectique" (désir insatiable de puissance et de transcendance) et une ontologie de l’Histoire comme &lt;a href="https://www.youtube.com/watch?v=YTOzn7dta7k" title="Mehdi Belhaj Kacem : "Un nouveau totalitarisme est en train de se mettre en place" par France Soir"&gt;tragédie irréductible. &lt;/a&gt;  Dans cette période, il écrit ces deux ouvrages :  "L’Antéforme" en 1997 et "Esthétique du chaos" en 2000. Son projet majeur, "L’Esprit du nihilisme" (cinq tomes, 2009-2015), pose Hegel comme "parenthèse" entre Kant et Badiou, avant de rompre violemment avec ce dernier dans "Après Badiou" paru en  2011, accusé d’archaïsme politique et moral. &lt;/p&gt; &lt;p&gt; Positionné à la marge des institutions, il incarne une radicalité post-moderne qui refuse les compromis, liant esthétique, politique et métaphysique dans une critique du présent. Il explore la "sexuation" (être et genre comme inexistant fondamental) et la transgression comme seule voie face au néant. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mehdi_Belhaj_Kacem"   title=" Wikipedia"&gt;Mehdi BELHAJ KACEM&lt;/a&gt;   est un philosophe, écrivain et acteur franco-tunisien, autodidacte radical et figure controversée de la pensée contemporaine, passé par les milieux militants et   &lt;a href="https://blogs.mediapart.fr/olivier-rachet/blog/130525/le-manifeste-conspirationniste-de-mehdi-belhaj-kacem" title="Le manifeste conspirationniste de Mehdi Belhaj Kacempar par mediapart"&gt;littéraires underground &lt;/a&gt; avant de forger une œuvre philosophique exigeante et iconoclaste. Après des expériences communautaires militantes, il découvre Alain Badiou comme maître à penser initial. &lt;/p&gt; &lt;p&gt; Il développe une pensée du nihilisme héritée de Heidegger, Nietzsche et Schürmann, centrée sur le "pléonectique" (désir insatiable de puissance et de transcendance) et une ontologie de l’Histoire comme &lt;a href="https://www.youtube.com/watch?v=YTOzn7dta7k" title="Mehdi Belhaj Kacem : "Un nouveau totalitarisme est en train de se mettre en place" par France Soir"&gt;tragédie irréductible. &lt;/a&gt;  Dans cette période, il écrit ces deux ouvrages :  "L’Antéforme" en 1997 et "Esthétique du chaos" en 2000. Son projet majeur, "L’Esprit du nihilisme" (cinq tomes, 2009-2015), pose Hegel comme "parenthèse" entre Kant et Badiou, avant de rompre violemment avec ce dernier dans "Après Badiou" paru en  2011, accusé d’archaïsme politique et moral. &lt;/p&gt; &lt;p&gt; Positionné à la marge des institutions, il incarne une radicalité post-moderne qui refuse les compromis, liant esthétique, politique et métaphysique dans une critique du présent. Il explore la "sexuation" (être et genre comme inexistant fondamental) et la transgression comme seule voie face au néant. &lt;/p&gt; Né en 1973, il publie très jeune des romans avant de se tourner vers la philosophie. Son œuvre, abondante et difficile, cherche à penser le mal et la démesure humaine, ce désir d’avoir toujours plus qu’il appelle « pléonexie », comme le fond de l’histoire. Ses prises de position récentes, notamment pendant la crise sanitaire, ont suscité de vives critiques. 
  &lt;audio controls title="Le bel âge de Mehdi Belhaj Kacem par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13937-24.01.2017-ITEMA_21206998-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="E83" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gaspard_Koenig" title=" Wikipedia"&gt;Gaspard KONENIG&lt;/a&gt;  est un philosophe français connu pour défendre un libéralisme classique moderne axé sur la liberté individuelle et la réduction des normes administratives. Il étudie initialement Gilles Deleuze avant de découvrir le libéralisme lors d'un séjour à l'université Columbia à New York. Il enseigne comme ATER à Lille-III et travaille comme plume pour Christine Lagarde au ministère de l'Économie, puis à la BERD à Londres. &lt;/p&gt; &lt;p&gt; Fondateur en 2013 du &lt;a href="https://www.youtube.com/watch?v=XmM1deHK-Eo"  title="Génération libre : le think tank, "start-up intellectuelle" par BFM Business"&gt;"think tank Génération Libre", &lt;/a&gt; classé parmi les meilleurs think tanks européens, il en est président et promeut des idées comme le revenu universel (LIBER), la légalisation du cannabis, la propriété des données personnelles et la subsidiarité ascendante. En 2021, il lance le mouvement politique Simple pour  &lt;a href="https://www.youtube.com/watch?v=r6p0dZlUoLQ"  title="Gaspard Koenig : Simplifions radicalement notre administration ! par Contribuables Associés"&gt;diviser par cent les normes &lt;/a&gt; réglementaires ; candidat à la présidentielle 2022, il récolte 107 parrainages. Il se présente aussi aux législatives partielles en 2018. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.gaspardkoenig.com/" title="gaspard koenig - site personnel"&gt;Auteur  d'une quinzaine d'essais &lt;/a&gt; et romans, dont Humus (finaliste Goncourt 2023, prix Interallié), Agrophilosophie (2024) et Time to Philo, il redéfinit la liberté comme "pouvoir sur soi", inspiré par Montaigne, les stoïciens et David Graeber. Ses réflexions touchent l'IA, l'agroécologie, l'éthique et l'économie. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gaspard_Koenig" title=" Wikipedia"&gt;Gaspard KOENIG&lt;/a&gt;  est un philosophe français connu pour défendre un libéralisme classique moderne axé sur la liberté individuelle et la réduction des normes administratives. Il étudie initialement Gilles Deleuze avant de découvrir le libéralisme lors d'un séjour à l'université Columbia à New York. Il enseigne comme ATER à Lille-III et travaille comme plume pour Christine Lagarde au ministère de l'Économie, puis à la BERD à Londres. &lt;/p&gt; &lt;p&gt; Fondateur en 2013 du &lt;a href="https://www.youtube.com/watch?v=XmM1deHK-Eo"  title="Génération libre : le think tank, "start-up intellectuelle" par BFM Business"&gt;"think tank Génération Libre", &lt;/a&gt; classé parmi les meilleurs think tanks européens, il en est président et promeut des idées comme le revenu universel (LIBER), la légalisation du cannabis, la propriété des données personnelles et la subsidiarité ascendante. En 2021, il lance le mouvement politique Simple pour  &lt;a href="https://www.youtube.com/watch?v=r6p0dZlUoLQ"  title="Gaspard Koenig : Simplifions radicalement notre administration ! par Contribuables Associés"&gt;diviser par cent les normes &lt;/a&gt; réglementaires ; candidat à la présidentielle 2022, il récolte 107 parrainages. Il se présente aussi aux législatives partielles en 2018. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.gaspardkoenig.com/" title="gaspard koenig - site personnel"&gt;Auteur  d'une quinzaine d'essais &lt;/a&gt; et romans, dont Humus (finaliste Goncourt 2023, prix Interallié), Agrophilosophie (2024) et Time to Philo, il redéfinit la liberté comme "pouvoir sur soi", inspiré par Montaigne, les stoïciens et David Graeber. Ses réflexions touchent l'IA, l'agroécologie, l'éthique et l'économie. Dans &lt;em&gt;La Fin de l’individu&lt;/em&gt; (2019) il s’inquiète de voir les algorithmes décider à notre place et réduire notre capacité de choisir. Avec &lt;em&gt;Humus&lt;/em&gt;, roman sur deux jeunes agronomes et la vie des vers de terre, puis &lt;em&gt;Agrophilosophie&lt;/em&gt;, il s’intéresse aux sols et à l’agriculture, et cherche à concilier la liberté individuelle avec le respect des équilibres naturels. &lt;/p&gt; 
 &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Gaspard Koenig, un philosophe en liberté par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-30.09.2023-ITEMA_23504378-2023C49326S0273-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E17" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Catherine_Larr%C3%A8re"  style="color:#6A142A"  title=" Wikipedia"&gt;Catherine LARRÈRE&lt;/a&gt; est une philosophe française   professeure émérite de philosophie à Paris 1 Panthéon-Sorbonne et spécialisée en philosophie morale et politique, avec une attention particulière à l’éthique de l’environnement.&lt;/p&gt; &lt;p&gt; Elle a aporté une contribution majeure à l’essor de la philosophie environnementale en France, abordant des thèmes comme  &lt;a href="https://www.youtube.com/watch?v=YNxj0SXoNSo" style="color:#88A1E9" title="Qu'est-ce que la nature ? par Editions M-Editer"&gt;la protection de la nature&lt;/a&gt;, la prévention des risques et la justice environnementale. Engagement et leadership: présidente de la Fondation de l’écologie politique (2013-2016), un think-tank lié à &lt;a href="https://www.persee.fr/doc/ecoru_0013-0559_1999_num_249_1_5068_t1_0091_0000_2 " style="color:#88A1E9" title="Catherine Larrère Les philosophies de l'environnement  par Persée"&gt;Europe Écologie &lt;/a&gt; Les Verts, et commissaire scientifique de l’exposition Nature vive au Muséum national d’histoire naturelle (2001). &lt;/p&gt; &lt;p&gt; Ellle a publié largement sur Montesquieu, la philosophie morale et politique. Elle a aussi travaillé sur le rôle des femmes dans la société selon Rousseau et a collaboré étroitement avec son mari, Raphaël Larrère, agronome et écologue, sur des questions liées à l’environnement. Sa productivité académique est importante: articles, livres et chapitres, avec une présence notable dans les ressources bibliographiques et les bases de données spécialisées. Sa collaboration avec des chercheurs anglophones et ses traductions ont contribué à diffuser des idées clés de l’éthique de l’environnement en milieu francophone. &lt;/p&gt; &lt;p&gt; Elle continue d’être présente dans les débats publics et intellectuels sur l’environnement et l’éthique, notamment à travers des articles dans des revues et des plateformes spécialisées. &lt;/p&gt;   &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Catherine Larrère : "Ne pas s'occuper du social, c'est bloquer les solutions environnementales" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-07.02.2017-ITEMA_21221850-2017C19327S0038-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Catherine_Larr%C3%A8re"  style="color:#6A142A"  title=" Wikipedia"&gt;Catherine LARRÈRE&lt;/a&gt; est une philosophe française   professeure émérite de philosophie à Paris 1 Panthéon-Sorbonne et spécialisée en philosophie morale et politique, avec une attention particulière à l’éthique de l’environnement.&lt;/p&gt; &lt;p&gt; Elle a aporté une contribution majeure à l’essor de la philosophie environnementale en France, abordant des thèmes comme  &lt;a href="https://www.youtube.com/watch?v=YNxj0SXoNSo" style="color:#88A1E9" title="Qu'est-ce que la nature ? par Editions M-Editer"&gt;la protection de la nature&lt;/a&gt;, la prévention des risques et la justice environnementale. Engagement et leadership: présidente de la Fondation de l’écologie politique (2013-2016), un think-tank lié à &lt;a href="https://www.persee.fr/doc/ecoru_0013-0559_1999_num_249_1_5068_t1_0091_0000_2 " style="color:#88A1E9" title="Catherine Larrère Les philosophies de l'environnement  par Persée"&gt;Europe Écologie &lt;/a&gt; Les Verts, et commissaire scientifique de l’exposition Nature vive au Muséum national d’histoire naturelle (2001). &lt;/p&gt; &lt;p&gt; Ellle a publié largement sur Montesquieu, la philosophie morale et politique. Elle a aussi travaillé sur le rôle des femmes dans la société selon Rousseau et a collaboré étroitement avec son mari, Raphaël Larrère, agronome et écologue, sur des questions liées à l’environnement. Sa productivité académique est importante: articles, livres et chapitres, avec une présence notable dans les ressources bibliographiques et les bases de données spécialisées. Sa collaboration avec des chercheurs anglophones et ses traductions ont contribué à diffuser des idées clés de l’éthique de l’environnement en milieu francophone. &lt;/p&gt; &lt;p&gt; Elle continue d’être présente dans les débats publics et intellectuels sur l’environnement et l’éthique, notamment à travers des articles dans des revues et des plateformes spécialisées. &lt;/p&gt;     &lt;audio controls title="Catherine Larrère : "Ne pas s'occuper du social, c'est bloquer les solutions environnementales" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-07.02.2017-ITEMA_21221850-2017C19327S0038-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
  </t>
         </is>
       </c>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E21" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Marion"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean Luc MARION&lt;/a&gt; est un philosophe, phénoménologue et Membre de l’Académie française depuis 2008, il est reconnu pour sa tentative d’articuler la phénoménologie et la théologie dans ce qu’on a appelé le "tournant théologique de la phénoménologie française". &lt;/p&gt; &lt;p&gt; Il se revendique de la phénoménologie de Husserl et Heidegger, tout en l’orientant vers une réflexion sur la donation (le don). Pour lui, la phénoménologie doit s’intéresser non à l’être, mais à &lt;a href="https://www.youtube.com/watch?v=oS1vVjgKJOQ"  title=" Rencontre avec Jean-Luc Marion par KTO TV"&gt;ce qui se donne&lt;/a&gt;, et même à l’excès de ce don dans ce qu’il appelle les "phénomènes saturés".​  Cette approche déplace la question classique de l’être vers celle du don, où la subjectivité se laisse surprendre par ce qui se manifeste avant toute maîtrise conceptuelle. &lt;/p&gt; &lt;p&gt; Il développe cette idée dans des ouvrages majeurs comme "Réduction et donation" (1989), "Étant donné" (1998) et "De surcroît" (2001) ou la donation devient pour lui la condition de toute phénoménalité : les phénomènes les plus profonds (amour, art, révélation divine) excèdent la capacité de la conscience à les comprendre.​ Il renouvelle également la réflexion sur l’amour. Dans "Le Phénomène érotique" (2003), il propose que le sujet ne se fonde pas sur la conscience cartésienne mais sur "l’amour reçu et donné" qui devient ainsi le lieu de la véritable certitude de soi, en continuité critique avec Descartes et sous influence de Levinas. &lt;/p&gt; &lt;p&gt; Sa philosophie conjugue trois fils essentiels : &lt;/p&gt; &lt;p&gt;- une phénoménologie du don et de la révélation, où le monde se manifeste comme excès reçu. &lt;/p&gt; &lt;p&gt; -  une théologie philosophique, cherchant à penser Dieu hors du cadre métaphysique traditionnel. &lt;/p&gt; &lt;p&gt; - une éthique de l’amour, où autrui et la relation constituent la source du sens existentiel. &lt;/p&gt; &lt;p&gt; Spécialiste éminent de Descartes (notamment Sur la théologie blanche de Descartes et Sur la métaphysique grise de Descartes), il a aussi écrit des livres plus théologiques tels que "Dieu sans l’être", "D’ailleurs, la Révélation" et a reçu de nombreuses distinctions, dont le Grand Prix de l’Académie française en 1992 et le Prix de la Principauté de Monaco en 2018. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Jean-Luc Marion : "La philosophie c’est de la course de fond, il faut en faire tous les jours, plusieurs heures" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-22.01.2021-ITEMA_22550575-2021C12410S0022.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Marion"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean Luc MARION&lt;/a&gt; est un philosophe, phénoménologue et Membre de l’Académie française depuis 2008, il est reconnu pour sa tentative d’articuler la phénoménologie et la théologie dans ce qu’on a appelé le "tournant théologique de la phénoménologie française". &lt;/p&gt; &lt;p&gt; Il se revendique de la phénoménologie de Husserl et Heidegger, tout en l’orientant vers une réflexion sur la donation (le don). Pour lui, la phénoménologie doit s’intéresser non à l’être, mais à &lt;a href="https://www.youtube.com/watch?v=oS1vVjgKJOQ"  title=" Rencontre avec Jean-Luc Marion par KTO TV"&gt;ce qui se donne&lt;/a&gt;, et même à l’excès de ce don dans ce qu’il appelle les "phénomènes saturés".​  Cette approche déplace la question classique de l’être vers celle du don, où la subjectivité se laisse surprendre par ce qui se manifeste avant toute maîtrise conceptuelle. &lt;/p&gt; &lt;p&gt; Il développe cette idée dans des ouvrages majeurs comme "Réduction et donation" (1989), "Étant donné" (1998) et "De surcroît" (2001) ou la donation devient pour lui la condition de toute phénoménalité : les phénomènes les plus profonds (amour, art, révélation divine) excèdent la capacité de la conscience à les comprendre.​ Il renouvelle également la réflexion sur l’amour. Dans "Le Phénomène érotique" (2003), il propose que le sujet ne se fonde pas sur la conscience cartésienne mais sur "l’amour reçu et donné" qui devient ainsi le lieu de la véritable certitude de soi, en continuité critique avec Descartes et sous influence de Levinas. &lt;/p&gt; &lt;p&gt; Sa philosophie conjugue trois fils essentiels : &lt;/p&gt; &lt;p&gt;une phénoménologie du don et de la révélation, où le monde se manifeste comme excès reçu. &lt;/p&gt; &lt;p&gt;une théologie philosophique, cherchant à penser Dieu hors du cadre métaphysique traditionnel. &lt;/p&gt; &lt;p&gt;une éthique de l’amour, où autrui et la relation constituent la source du sens existentiel. &lt;/p&gt; &lt;p&gt; Spécialiste éminent de Descartes (notamment Sur la théologie blanche de Descartes et Sur la métaphysique grise de Descartes), il a aussi écrit des livres plus théologiques tels que "Dieu sans l’être", "D’ailleurs, la Révélation" et a reçu de nombreuses distinctions, dont le Grand Prix de l’Académie française en 1992 et le Prix de la Principauté de Monaco en 2018. &lt;/p&gt;    &lt;audio controls title=" Jean-Luc Marion : "La philosophie c’est de la course de fond, il faut en faire tous les jours, plusieurs heures" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-22.01.2021-ITEMA_22550575-2021C12410S0022.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="E22" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcel_Gauchet"  title=" Wikipedia"&gt;Marcel GAUCHET&lt;/a&gt;  est un philosophe, historien et sociologue  français connu pour ses travaux sur, &lt;a href="https://www.youtube.com/watch?v=48xW06Mm7JM&amp;t=4s "  title="Comment expliquer la crise de nos démocraties ? L'analyse de Marcel Gauchet par Le figaro"&gt;la démocratie&lt;/a&gt;, la religion et la sécularisation de l’Occident. Son œuvre cherche à comprendre les conditions politiques et culturelles qui permettent l’émergence et le fonctionnement des démocraties modernes, en particulier à partir du passage d’une société organique et religieuse à une société démocratique laïque. &lt;/p&gt; &lt;p&gt;  Il est une figure centrale du, &lt;a href="https://www.youtube.com/watch?v=Stn5k6P-uI8"  title="Marcel Gauchet, une pensée qui fâche ? par France Culture"&gt;paysage intellectuel &lt;/a&gt; français, dont les positions sur la “fin de la religion” et la démocratie ont suscité des débats et parfois des critiques, notamment autour de son oriention perçue par certains comme néoréactionnaire, qu’il réfute. Une de ses oeuvres marquantes est :  - "Le Désenchantement du monde" paru en 1985 – ouvrage majeur sur la sécularisation et le déclin de l’emprise de la religion dans les sociétés occidentales. &lt;/p&gt; &lt;p&gt; La démocratie moderne naît dans le cadre d’un processus historique complexe où l’émergence de l’individu et la réduction du rôle monopoly de la religion transforment les bases de l’autorité et de la légitimité politique. La religion, loin d’être annihilée, se transforme en une “religion de la sortie de la religion” qui structure encore les attentes morales et citoyennes, même lorsque l’emprise institutionnelle recule. &lt;/p&gt; &lt;p&gt; L’équilibre entre autonomie de l’individu et cohésion sociale demeure un défi central de la démocratie contemporaine, d’où l’attention soutenue de Gauchet pour les “fratures” et les tensions entre pluralisme démocratique et exigences communautaires.
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcel_Gauchet"  title=" Wikipedia"&gt;Marcel GAUCHET&lt;/a&gt;  est un philosophe, historien et sociologue  français connu pour ses travaux sur, &lt;a href="https://www.youtube.com/watch?v=48xW06Mm7JM&amp;t=4s "  title="Comment expliquer la crise de nos démocraties ? L'analyse de Marcel Gauchet par Le figaro"&gt;la démocratie&lt;/a&gt;, la religion et la sécularisation de l’Occident. Son œuvre cherche à comprendre les conditions politiques et culturelles qui permettent l’émergence et le fonctionnement des démocraties modernes, en particulier à partir du passage d’une société organique et religieuse à une société démocratique laïque. &lt;/p&gt; &lt;p&gt;  Il est une figure centrale du, &lt;a href="https://www.youtube.com/watch?v=Stn5k6P-uI8"  title="Marcel Gauchet, une pensée qui fâche ? par France Culture"&gt;paysage intellectuel &lt;/a&gt; français, dont les positions sur la “fin de la religion” et la démocratie ont suscité des débats et parfois des critiques, notamment autour de son oriention perçue par certains comme néoréactionnaire, qu’il réfute. Une de ses oeuvres marquantes est : "Le Désenchantement du monde" paru en 1985 – ouvrage majeur sur la sécularisation et le déclin de l’emprise de la religion dans les sociétés occidentales. &lt;/p&gt; &lt;p&gt; La démocratie moderne naît dans le cadre d’un processus historique complexe où l’émergence de l’individu et la réduction du rôle monopoly de la religion transforment les bases de l’autorité et de la légitimité politique. La religion, loin d’être annihilée, se transforme en une “religion de la sortie de la religion” qui structure encore les attentes morales et citoyennes, même lorsque l’emprise institutionnelle recule. &lt;/p&gt; &lt;p&gt; L’équilibre entre autonomie de l’individu et cohésion sociale demeure un défi central de la démocratie contemporaine, d’où l’attention soutenue de Gauchet pour les “fratures” et les tensions entre pluralisme démocratique et exigences communautaires.
  &lt;/p&gt;   &lt;audio controls title="Marcel Gauchet : "C'est l'exigence de comprendre mon temps qui m'a conduit à une réflexion sur l'histoire, en philosophe" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11189-30.05.2011-ITEMA_20288351-2011C15000E0083-ITE_00042075_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E27" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Jambet"  title=" Wikipedia"&gt;Christian JAMBET&lt;/a&gt; est un philosophe et islamologue  français reconnu pour ses travaux qui font le pont entre la philosophie occidentale et la pensée islamique, en particulier le chiisme. Agrégé de philosophie et ancien élève d'Henry Corbin, un spécialiste de &lt;a href="https://fr.wikipedia.org/wiki/Islam_en_Iran"  title=" Islam en Iran par Wikipedia"&gt;l'islam iranien&lt;/a&gt;, il a consacré sa carrière à l'étude des traditions philosophiques et spirituelles de l'Islam, notamment celles de l'Iran. Il est devenu membre de l'Académie française en 2024. Son travail se distingue par sa profondeur et son caractère interdisciplinaire. Ses contributions majeures portent sur :&lt;/p&gt; &lt;p&gt; - La philosophie islamique : Il a montré qu'il existe une tradition philosophique riche et autonome en terre d'Islam, souvent mal comprise ou négligée en Occident. Il a mis en lumière les liens, mais aussi les spécificités, entre la pensée grecque (notamment platonicienne) et les penseurs islamiques. Son ouvrage Qu'est-ce que la philosophie islamique ? est une référence dans ce domaine. &lt;/p&gt; &lt;p&gt; - Le chiisme et le soufisme : il est un expert du chiisme, qu'il étudie non seulement sous son aspect politique et théologique, mais aussi dans sa dimension philosophique et spirituelle. Il a beaucoup travaillé sur la figure du  &lt;a href="https://www.youtube.com/watch?v=kQzLVldS4PU"  title="L'immortalité de l'âme selon Mulla Sadra, Christian Jambet Les vivants et les dieux par Facteur"&gt; philosophe iranien Mullâ Sadrâ Shîrâzî&lt;/a&gt;, qu'il considère comme un des plus grands métaphysiciens de l'histoire. Il explore les concepts de l'ésotérisme (bātin) et de l'exotérisme (zahir), montrant comment la philosophie chiite a développé une pensée de la liberté et de l'intériorité face à l'orthodoxie religieuse. &lt;/p&gt; &lt;p&gt; - La philosophie politique : Il s'intéresse aux conceptions du pouvoir et du droit dans l'Islam. Dans son livre Le gouvernement divin, il analyse la relation entre la théologie et le politique, et les différentes manières dont le pouvoir a été conceptualisé dans le chiisme. &lt;/p&gt; &lt;p&gt; - Les concepts de l'« Ange » et de l'« imagination créatrice » : Reprenant les travaux d'Henry Corbin, il a exploré le rôle central de l'imagination dans la connaissance et l'expérience religieuse. Pour Jambet, l'imagination n'est pas une simple faculté de fiction, mais un organe de perception capable d'accéder à un monde intermédiaire, peuplé d'êtres spirituels comme les Anges. &lt;/p&gt; &lt;p&gt;  Il a publié différents ouvrages dont "L'Ange" paru en 1976 co-écrit avec Guy Lardreau ainsi que "La Logique des Orientaux"  paru en 1983  sans oublié "La Grande Résurrection d'Alamût"  paru en 1990, sur les formes de la liberté dans le shî'isme ismaélien. &lt;/p&gt;  &lt;audio controls title=" La philosophie islamique avec Christian Jambet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-12.02.2012-ITEMA_20344279-2012C14958E0004-ITE_00049063_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Jambet"  title=" Wikipedia"&gt;Christian JAMBET&lt;/a&gt; est un philosophe et islamologue  français reconnu pour ses travaux qui font le pont entre la philosophie occidentale et la pensée islamique, en particulier le chiisme. Agrégé de philosophie et ancien élève d'Henry Corbin, un spécialiste de &lt;a href="https://fr.wikipedia.org/wiki/Islam_en_Iran"  title=" Islam en Iran par Wikipedia"&gt;l'islam iranien&lt;/a&gt;, il a consacré sa carrière à l'étude des traditions philosophiques et spirituelles de l'Islam, notamment celles de l'Iran. Il est devenu membre de l'Académie française en 2024. Son travail se distingue par sa profondeur et son caractère interdisciplinaire. Ses contributions majeures portent sur :&lt;/p&gt; &lt;p&gt;La philosophie islamique : Il a montré qu'il existe une tradition philosophique riche et autonome en terre d'Islam, souvent mal comprise ou négligée en Occident. Il a mis en lumière les liens, mais aussi les spécificités, entre la pensée grecque (notamment platonicienne) et les penseurs islamiques. Son ouvrage Qu'est-ce que la philosophie islamique ? est une référence dans ce domaine. &lt;/p&gt; &lt;p&gt;Le chiisme et le soufisme : il est un expert du chiisme, qu'il étudie non seulement sous son aspect politique et théologique, mais aussi dans sa dimension philosophique et spirituelle. Il a beaucoup travaillé sur la figure du  &lt;a href="https://www.youtube.com/watch?v=kQzLVldS4PU"  title="L'immortalité de l'âme selon Mulla Sadra, Christian Jambet Les vivants et les dieux par Facteur"&gt; philosophe iranien Mullâ Sadrâ Shîrâzî&lt;/a&gt;, qu'il considère comme un des plus grands métaphysiciens de l'histoire. Il explore les concepts de l'ésotérisme (bātin) et de l'exotérisme (zahir), montrant comment la philosophie chiite a développé une pensée de la liberté et de l'intériorité face à l'orthodoxie religieuse. &lt;/p&gt; &lt;p&gt;La philosophie politique : Il s'intéresse aux conceptions du pouvoir et du droit dans l'Islam. Dans son livre Le gouvernement divin, il analyse la relation entre la théologie et le politique, et les différentes manières dont le pouvoir a été conceptualisé dans le chiisme. &lt;/p&gt; &lt;p&gt;Les concepts de l'« Ange » et de l'« imagination créatrice » : Reprenant les travaux d'Henry Corbin, il a exploré le rôle central de l'imagination dans la connaissance et l'expérience religieuse. Pour Jambet, l'imagination n'est pas une simple faculté de fiction, mais un organe de perception capable d'accéder à un monde intermédiaire, peuplé d'êtres spirituels comme les Anges. &lt;/p&gt; &lt;p&gt;  Il a publié différents ouvrages dont "L'Ange" paru en 1976 co-écrit avec Guy Lardreau ainsi que "La Logique des Orientaux"  paru en 1983  sans oublié "La Grande Résurrection d'Alamût"  paru en 1990, sur les formes de la liberté dans le shî'isme ismaélien. &lt;/p&gt;  &lt;audio controls title=" La philosophie islamique avec Christian Jambet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-12.02.2012-ITEMA_20344279-2012C14958E0004-ITE_00049063_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
@@ -2834,7 +2834,7 @@
       <c r="E36" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Andr%C3%A9_Comte-Sponville"  style="color:#6A142A"  title=" Wikipedia"&gt;André COMTE-SPONVILLE&lt;/a&gt;  est un philosophe français, agrégé de philosophie et docteur de troisième cycle. Matérialiste, rationaliste et humaniste, il s'est fait connaître par des ouvrages accessibles popularisant la sagesse antique adaptée au monde contemporain avec "Le Petit Traité des grandes vertus" paru en  1995, best-seller vendu à plus de 500 000 exemplaires. &lt;/p&gt; &lt;p&gt; Issu d'un milieu catholique, il se convertit à l'athéisme adolescent, adhère au Parti communiste français, puis enseigne la philosophie à l'université Paris-I Panthéon-Sorbonne jusqu'en 1998, date à laquelle il se consacre à l'écriture, aux conférences et aux essais médiatiques.  &lt;/p&gt; &lt;p&gt; Influencé par Épicure, les stoïciens, Montaigne, Spinoza, ainsi que des contemporains comme Claude Lévi-Strauss ou Marcel Conche, il forge   &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_2000_num_135_1_3634_t1_0139_0000_2" style="color:#88A1E9" title="André Comte-Sponville, L'être-temps : quelques réflexions sur le temps de la conscience, coll. Perspectives critiques par Persée"&gt;l'insistantialisme : &lt;/a&gt; une métaphysique matérialiste du temps où l'existence persiste sans finalité divine ni sens transcendant, opposée à l'existentialisme. Il propose une spiritualité athée, une éthique humaniste sans Dieu, centrée sur l'ici-maintenant et l'acceptation joyeuse de la finitude humaine. &lt;/p&gt; &lt;p&gt; Ses vertus cardinales (courage, tempérance, justice, etc.) visent une &lt;a href="https://www.youtube.com/watch?v=OYRMlwYByfA" style="color:#88A1E9" title="André Comte-Sponville, L'amou est joie par Hopitaux Universitaires de Genève"&gt;vie heureuse &lt;/a&gt; malgré la souffrance et la mort, sans illusions religieuses ou morales kantiennes. Dans des essais comme "L'Inconsolable" paru en 2018, il explore l'ennui, la joie, la solitude et les animaux, plaidant tolérance, liberté et sagesse laïque face aux populismes et au déclin écologique. &lt;/p&gt; 
-&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="André Comte-Sponville, homme mélancolique, philosophe heureux par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-04.01.2026-ITEMA_24362243-2025C3500E0181-NET_MFC_54DA91F6-96EA-4790-BDB7-6EA3C744B706-21-8ab3772763c1198b47c221812723e2fa.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
+  &lt;audio controls title="André Comte-Sponville, homme mélancolique, philosophe heureux par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-04.01.2026-ITEMA_24362243-2025C3500E0181-NET_MFC_54DA91F6-96EA-4790-BDB7-6EA3C744B706-21-8ab3772763c1198b47c221812723e2fa.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
@@ -2901,7 +2901,7 @@
       <c r="E37" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Didi-Huberman" style="color:#6A142A"  title=" Wikipedia"&gt;Georges DIDI-HUBERMAN&lt;/a&gt; est un philosophe &amp; historien de l'art français spécialiste de la théorie des images et figure majeure de la pensée contemporaine sur le visuel. Il est aujourd’hui considéré comme l’un des théoriciens de l’image les plus importants en France, avec une reconnaissance internationale. &lt;/p&gt; &lt;p&gt; Ses travaux portent sur l’histoire et la théorie des images, de la Renaissance à l’art contemporain, avec une attention aux liens entre images, savoir et pouvoir. Sa démarche relève d’une "archéologie du savoir visuel"  car il cherche à comprendre comment les images construisent une mémoire, une sensibilité et des formes de pensée. &lt;/p&gt; &lt;p&gt; Pour lui, les images ne sont pas seulement des objets à regarder, mais des actes qui engagent le corps, la mémoire,&lt;a href="https://www.youtube.com/watch?v=DUNo6xZkaCo" style="color:#88A1E9" title="
-L'historien de l'art Georges Didi-Huberman explique la fabrique de nos affects par les images par France Culture"&gt; l’affect et l’histoire&lt;/a&gt;. Il insiste sur leu profondeur car il ne s’agit pas seulement de ce qui est visible en surface, mais de ce qui travaille en dessous, dans les couches de sens, de mémoire, de trauma. Il réfléchit aussi à une éthique du regard, comment voir sans réduire, sans consommer l’image, en respectant ce qu’elle expose de vulnérable, de politique, ou de souffrant. &lt;/p&gt; &lt;p&gt;De nombreux ouvrages sur Warburg, Fra Angelico, le Baroque, la mémoire de la Shoah, les images de catastrophes et de survivants, etc. Une série de livres et de projets sur les,&lt;a href="https://www.youtube.com/watch?v=vKMAHj_kvY8" style="color:#88A1E9" title="Georges Didi-Huberman, SOULÈVEMENT par ABC Penser"&gt; "soulèvements", &lt;/a&gt; où il s’intéresse aux gestes de révolte, aux mouvements collectifs, et à la manière dont les images peuvent porter la voix des sans-voix et lutter contre l’amnésie historique. &lt;/p&gt; &lt;p&gt; Sa réflexion sur les "soulèvements" l’amène à articuler philosophie de l’image et engagement politique : comment des images peuvent accompagner des luttes, préserver des mémoires, donner forme à des désirs de transformation sociale. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Dans la bibliothèque de Georges Didi-Huberman par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23875-11.10.2024-ITEMA_23889638-2024C49162E0034-NET_MFC_8E518A6F-A0BF-49D3-BFEA-B88C4BE3FE7F-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+L'historien de l'art Georges Didi-Huberman explique la fabrique de nos affects par les images par France Culture"&gt; l’affect et l’histoire&lt;/a&gt;. Il insiste sur leu profondeur car il ne s’agit pas seulement de ce qui est visible en surface, mais de ce qui travaille en dessous, dans les couches de sens, de mémoire, de trauma. Il réfléchit aussi à une éthique du regard, comment voir sans réduire, sans consommer l’image, en respectant ce qu’elle expose de vulnérable, de politique, ou de souffrant. &lt;/p&gt; &lt;p&gt;De nombreux ouvrages sur Warburg, Fra Angelico, le Baroque, la mémoire de la Shoah, les images de catastrophes et de survivants, etc. Une série de livres et de projets sur les,&lt;a href="https://www.youtube.com/watch?v=vKMAHj_kvY8" style="color:#88A1E9" title="Georges Didi-Huberman, SOULÈVEMENT par ABC Penser"&gt; "soulèvements", &lt;/a&gt; où il s’intéresse aux gestes de révolte, aux mouvements collectifs, et à la manière dont les images peuvent porter la voix des sans-voix et lutter contre l’amnésie historique. &lt;/p&gt; &lt;p&gt; Sa réflexion sur les "soulèvements" l’amène à articuler philosophie de l’image et engagement politique : comment des images peuvent accompagner des luttes, préserver des mémoires, donner forme à des désirs de transformation sociale. &lt;/p&gt;   &lt;audio controls title="Dans la bibliothèque de Georges Didi-Huberman par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23875-11.10.2024-ITEMA_23889638-2024C49162E0034-NET_MFC_8E518A6F-A0BF-49D3-BFEA-B88C4BE3FE7F-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="E39" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Engel"   title=" Wikipedia"&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent "La Norme du vrai" paru en 1989 sur la philosophie de la logique, &lt;a href="https://www.youtube.com/watch?v=ivsIBYFN6DI" title="*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos"&gt; "Va savoir"&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et "Les vices du savoir" en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. Pour lui, la croyance a une norme propre : croire, c’est viser la vérité, et l’on ne peut croire à volonté ce que l’on sait faux. Dans &lt;em&gt;Les Vices du savoir&lt;/em&gt;, il montre que l’indifférence à la vérité, le « baratin » et la paresse intellectuelle sont de véritables fautes morales, dont les intellectuels eux-mêmes ne sont pas exempts. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Faut-il faire la morale aux intellectuels ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Engel"   title=" Wikipedia"&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent "La Norme du vrai" paru en 1989 sur la philosophie de la logique, &lt;a href="https://www.youtube.com/watch?v=ivsIBYFN6DI" title="*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos"&gt; "Va savoir"&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et "Les vices du savoir" en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. Pour lui, la croyance a une norme propre : croire, c’est viser la vérité, et l’on ne peut croire à volonté ce que l’on sait faux. Dans &lt;em&gt;Les Vices du savoir&lt;/em&gt;, il montre que l’indifférence à la vérité, le « baratin » et la paresse intellectuelle sont de véritables fautes morales, dont les intellectuels eux-mêmes ne sont pas exempts. &lt;/p&gt;   &lt;audio controls title="Faut-il faire la morale aux intellectuels ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="E42" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard"  title=" Wikipedia"&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J.G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime un séminaire sur les décolonisations avec l'Université de Louvain-la-Neuve. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href="https://www.youtube.com/watch?v=vEQWmSo67B4" style="color:#88A1E9" title="Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches"&gt;"Ce sont d'autres gens" &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la "qualité de la vie" sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href="https://www.youtube.com/watch?v=ZDpbSRrWIhU" title="Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées"&gt;"autre monde" &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard"  title=" Wikipedia"&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J.G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime un séminaire sur les décolonisations avec l'Université de Louvain-la-Neuve. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href="https://www.youtube.com/watch?v=vEQWmSo67B4" style="color:#88A1E9" title="Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches"&gt;"Ce sont d'autres gens" &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la "qualité de la vie" sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href="https://www.youtube.com/watch?v=ZDpbSRrWIhU" title="Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées"&gt;"autre monde" &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;    &lt;audio controls title="Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F42" s="34" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="E44" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_M%C3%A9da" title=" Wikipedia"&gt;Dominique MÉDA&lt;/a&gt;  est une philosophe française  reconnue pour ses analyses critiques sur le travail, les politiques sociales et la  &lt;a href="https://www.youtube.com/watch?v=jzyFjl0_QQE" title="La vraie révolution, c'est de désintensifier le travail ! Dominique Méda par Metabolism of Cities"&gt;transition écologique&lt;/a&gt;, elle combine une formation d'élite avec un engagement intellectuel profond sur les inégalités et la mesure de la richesse sociétale.  Elle est professeure de &lt;a href="https://www.youtube.com/watch?v=vKGU1tCOW90"  title="Dominique Méda, une sociologie contemporaine par Anthropologiques"&gt; sociologie &lt;/a&gt; à l'université Paris Dauphine-PSL, dirige l'IRISSO et a occupé la chaire "Reconversion écologique, travail et emploi" au Collège d'études mondiales. Elle fonde en 2010 le Laboratoire de l'égalité professionnelle entre femmes et hommes. &lt;/p&gt; &lt;p&gt; Ses travaux interrogent la centralité du travail dans les sociétés modernes, critiquant son rôle comme norme sociale totale et plaidant pour sa réduction au profit d'autres activités. Elle dénonce les limites du PIB comme indicateur de richesse, proposant des alternatives incluant le travail domestique, familial et écologique. Depuis les années 2010, elle se focalise sur la transition écologique, les inégalités de genre dans l'emploi et les réformes du travail  comme la flexisécurité. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"Le travail, une valeur en voie de disparition ?" paru en  1995 : histoire philosophique du concept de travail et plaidoyer pour sa redéfinition. - "Qu'est-ce que la richesse ?" paru en 1999 : critique des indicateurs économiques traditionnels. - "La reconversion écologique"(ouvrages récents) : lien entre écologie, emploi et justice sociale. &lt;/p&gt; &lt;audio controls title="Sandra LAUGIER par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11189-26.03.2012-ITEMA_20355259-2012C15000E0020-ITE_00049197_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_M%C3%A9da" title=" Wikipedia"&gt;Dominique MÉDA&lt;/a&gt;  est une philosophe française  reconnue pour ses analyses critiques sur le travail, les politiques sociales et la  &lt;a href="https://www.youtube.com/watch?v=jzyFjl0_QQE" title="La vraie révolution, c'est de désintensifier le travail ! Dominique Méda par Metabolism of Cities"&gt;transition écologique&lt;/a&gt;, elle combine une formation d'élite avec un engagement intellectuel profond sur les inégalités et la mesure de la richesse sociétale.  Elle est professeure de &lt;a href="https://www.youtube.com/watch?v=vKGU1tCOW90"  title="Dominique Méda, une sociologie contemporaine par Anthropologiques"&gt; sociologie &lt;/a&gt; à l'université Paris Dauphine-PSL, dirige l'IRISSO et a occupé la chaire "Reconversion écologique, travail et emploi" au Collège d'études mondiales. Elle fonde en 2010 le Laboratoire de l'égalité professionnelle entre femmes et hommes. &lt;/p&gt; &lt;p&gt; Ses travaux interrogent la centralité du travail dans les sociétés modernes, critiquant son rôle comme norme sociale totale et plaidant pour sa réduction au profit d'autres activités. Elle dénonce les limites du PIB comme indicateur de richesse, proposant des alternatives incluant le travail domestique, familial et écologique. Depuis les années 2010, elle se focalise sur la transition écologique, les inégalités de genre dans l'emploi et les réformes du travail  comme la flexisécurité. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"Le travail, une valeur en voie de disparition ?" paru en  1995 : histoire philosophique du concept de travail et plaidoyer pour sa redéfinition. "Qu'est-ce que la richesse ?" paru en 1999 : critique des indicateurs économiques traditionnels. "La reconversion écologique"(ouvrages récents) : lien entre écologie, emploi et justice sociale. &lt;/p&gt; &lt;audio controls title="Sandra LAUGIER par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11189-26.03.2012-ITEMA_20355259-2012C15000E0020-ITE_00049197_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 ​
 </t>
         </is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E46" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon"  title=" Wikipedia"&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href="https://www.youtube.com/watch?v=xOKttB1HgSk"  title="Marc Crépon sur la violence  par France Inter "&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href="https://www.youtube.com/watch?v=kwFC9MSSWcg"  title="Marc Crépon : l’épreuve de la haine   par Librairie mollat "&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; On peut dire qu’il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste. Directeur de recherche au CNRS, il a d’abord étudié la manière dont les philosophes allemands et français pensent les langues et les cultures. Dans &lt;em&gt;Le Consentement meurtrier&lt;/em&gt; (2012), il s’interroge sur la façon dont nous acceptons, souvent sans le voir, la violence faite à d’autres, par la guerre, la misère ou l’indifférence. Dans &lt;em&gt;L’Épreuve de la haine&lt;/em&gt; (2016) il cherche comment résister à la haine sans y répondre par la haine.  &lt;/p&gt; &lt;audio controls title="Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon"  title=" Wikipedia"&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href="https://www.youtube.com/watch?v=xOKttB1HgSk"  title="Marc Crépon sur la violence  par France Inter "&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href="https://www.youtube.com/watch?v=kwFC9MSSWcg"  title="Marc Crépon : l’épreuve de la haine   par Librairie mollat "&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; Il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste. Directeur de recherche au CNRS, il a d’abord étudié la manière dont les philosophes allemands et français pensent les langues et les cultures. Dans &lt;em&gt;Le Consentement meurtrier&lt;/em&gt; (2012), il s’interroge sur la façon dont nous acceptons, souvent sans le voir, la violence faite à d’autres, par la guerre, la misère ou l’indifférence. Dans &lt;em&gt;L’Épreuve de la haine&lt;/em&gt; (2016) il cherche comment résister à la haine sans y répondre par la haine.  &lt;/p&gt; &lt;audio controls title="Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -3729,7 +3729,7 @@
       <c r="E50" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fabienne_Brug%C3%A8re" title=" Wikipedia"&gt;Fabienne BRUGÈRE&lt;/a&gt; est une philosophe française   spécialisée en esthétique, philosophie morale et politique, ainsi qu'en théorie féministe. Elle intègre l'École normale supérieure de Fontenay-Saint-Cloud en 1987 et obtient l'agrégation de philosophie en 1991, après un séjour à l'université de Londres. Sa thèse de 1996 porte sur la théorie de l'art chez Shaftesbury et elle a rejoint Paris-VIII en 2014 pour une chaire en philosophie des arts modernes et contemporains. &lt;/p&gt; &lt;p&gt; Elle a été vice-présidente aux relations internationales à Bordeaux-Montaigne et présidente de l'Université Paris Lumières de 2019 à 2023. Elle a aussi présidé le Conseil de développement durable de Bordeaux Métropole et dirige des collections comme "Perspectives du care" aux éditions de l'ENS Lyon. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'esthétique anglo-américaine, &lt;a href="https://www.youtube.com/watch?v=PmXPfJIOCUw"  title="Fabienne Brugère - L'Éthique du Care par librairie mollat"&gt;l'éthique du care  &lt;/a&gt; (notamment son ouvrage "L’éthique du care" paru en 2011), le féminisme et la sociabilité politique. Parmi ses récents essais : Désaimer. Manuel d’un retour à la vie (2024), La vraie histoire de l’impressionnisme (2024) et On ne naît pas femme, on le devient (2019). Elle montre que le &lt;em&gt;care&lt;/em&gt;, le soin apporté aux autres, n’est pas une affaire privée réservée aux femmes, mais une question politique qui concerne toute la société et la manière dont elle traite les plus vulnérables. Avec Guillaume le Blanc, elle a aussi écrit sur l’hospitalité et l’accueil des étrangers dans &lt;em&gt;La Fin de l’hospitalité&lt;/em&gt; (2017). &lt;/p&gt; 
-&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Le désamour avec Fabienne Brugère par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-03.05.2024-ITEMA_23729943-2024F45096S0124-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
+  &lt;audio controls title="Le désamour avec Fabienne Brugère par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-03.05.2024-ITEMA_23729943-2024F45096S0124-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
@@ -3927,9 +3927,9 @@
       </c>
       <c r="E53" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_Le_Blanc_(%C3%A9crivain_fran%C3%A7ais)"  title=" Wikipedia"&gt;Guillaume LE BLANC&lt;/a&gt;  est un philosophe français spécialiste de philosophie sociale et politique, connu pour ses travaux sur la précarité, l’invisibilité sociale et les vies ordinaires. Il est professeur de philosophie sociale et politique à l’université Paris Cité et membre senior de l’Institut universitaire de France depuis 2022. &lt;/p&gt; &lt;p&gt; Il propose une philosophie des vies ordinaires qui prend au sérieux les expériences de précarité et de marginalisation. La précarité n’est pas une condition naturelle, mais une situation socialement produite qui  &lt;a href="https://www.lavie.fr/idees/debats/guillaume-le-blanc-nous-avons-bascule-dans-lage-de-la-tristesse-detre-soi-98208.php" style=" title=" Guillaume Le Blanc :  Nous avons basculé dans l’âge de la tristesse d’être soi  par lavie.fr"&gt;empêche les individus &lt;/a&gt; de se constituer comme autonomes dans leur rapport aux normes. Il montre comment les chômeurs, les "surnuméraires" et les "sans-voix" inventent de nouveaux langages et formes de vie, que la philosophie doit traduire pour contribuer à une &lt;a href="https://www.youtube.com/watch?v=2wtaG_uD8pQ" title=" L'hospitalité comme leçon de fraternité ? par Guillaume Le Blanc  par Espace Ethique"&gt;"société décente" &lt;/a&gt; et à une critique sociale des normes. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : - "Canguilhem et les normes" paru en 1999, Canguilhem et la vie humaine / La vie humaine. Anthropologie et biologie en 2002. - " Les maladies de l’homme normal" paru en 2004, "Vies ordinaires, vies précaires" en 2007, "L’invisibilité sociale" en 2009, "Que faire de notre vulnérabilité ?" en 2011 et  "L’insurrection des vies minuscules" en  2013. &lt;/p&gt; &lt;p&gt; Il hérite de Canguilhem et Foucault pour analyser la normalité, la santé, le pouvoir et les dispositifs d’invisibilisation, tout en les prolongeant vers une philosophie sociale de la vulnérabilité.
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_Le_Blanc_(%C3%A9crivain_fran%C3%A7ais)"  title=" Wikipedia"&gt;Guillaume LE BLANC&lt;/a&gt;  est un philosophe français spécialiste de philosophie sociale et politique, connu pour ses travaux sur la précarité, l’invisibilité sociale et les vies ordinaires. Il est professeur de philosophie sociale et politique à l’université Paris Cité et membre senior de l’Institut universitaire de France depuis 2022. &lt;/p&gt; &lt;p&gt; Il propose une philosophie des vies ordinaires qui prend au sérieux les expériences de précarité et de marginalisation. La précarité n’est pas une condition naturelle, mais une situation socialement produite qui  &lt;a href="https://www.lavie.fr/idees/debats/guillaume-le-blanc-nous-avons-bascule-dans-lage-de-la-tristesse-detre-soi-98208.php" style=" title=" Guillaume Le Blanc :  Nous avons basculé dans l’âge de la tristesse d’être soi  par lavie.fr"&gt;empêche les individus &lt;/a&gt; de se constituer comme autonomes dans leur rapport aux normes. Il montre comment les chômeurs, les "surnuméraires" et les "sans-voix" inventent de nouveaux langages et formes de vie, que la philosophie doit traduire pour contribuer à une &lt;a href="https://www.youtube.com/watch?v=2wtaG_uD8pQ" title=" L'hospitalité comme leçon de fraternité ? par Guillaume Le Blanc  par Espace Ethique"&gt;"société décente" &lt;/a&gt; et à une critique sociale des normes. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : "Canguilhem et les normes" paru en 1999, Canguilhem et la vie humaine / La vie humaine. Anthropologie et biologie en 2002. " Les maladies de l’homme normal" paru en 2004, "Vies ordinaires, vies précaires" en 2007, "L’invisibilité sociale" en 2009, "Que faire de notre vulnérabilité ?" en 2011 et  "L’insurrection des vies minuscules" en  2013. &lt;/p&gt; &lt;p&gt; Il hérite de Canguilhem et Foucault pour analyser la normalité, la santé, le pouvoir et les dispositifs d’invisibilisation, tout en les prolongeant vers une philosophie sociale de la vulnérabilité.
 Il défend une idée de la philosophie comme contre-culture, capable d’amplifier les voix marginalisées, d’explorer la créativité des vies ordinaires et de questionner les évidences de la normalité sociales. &lt;/p&gt; 
-&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Jalousie, haine, lâcheté, ressentiment : comment lutter contre nos passions dévastatrices ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16173-25.03.2025-ITEMA_24070758-2025F26104S0084-NET_MFI_BAF471BF-9E79-4E46-9F6C-F914E7D3FE60-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+  &lt;audio controls title="Jalousie, haine, lâcheté, ressentiment : comment lutter contre nos passions dévastatrices ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16173-25.03.2025-ITEMA_24070758-2025F26104S0084-NET_MFI_BAF471BF-9E79-4E46-9F6C-F914E7D3FE60-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="E54" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Quentin_Meillassoux"  title=" Wikipedia"&gt;Quentin MEILLASSOUX&lt;/a&gt; est un philosophe français du courant qu'on appelle le  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif" style="color:#88A1E9" title=" Speculative Realism par Wikipedia "&gt;"réalisme spéculatif"&lt;/a&gt;. Le point de départ majeur de sa philosophie est "Le corrélationnisme" qui, selon lui, est la thèse dominante depuis Kant, et qui affirme qu'il est impossible de connaître le monde tel qu'il est en soi, indépendamment de notre rapport à lui (la corrélation entre la pensée et l'être). Cette position rend impossible de penser un "absolu" et nous enferme dans un cercle où nous ne pouvons accéder qu'à ce qui est "pour nous". &lt;a href="https://www.youtube.com/watch?v=29_IhFEWtlc" title="corine-pelluchon"&gt;Il s'interroge &lt;/a&gt;  sur la capacité de la science à parler de réalités "ancestrales", ce qui semble contredire le corrélationnisme. &lt;/p&gt; &lt;p&gt; Face au corrélationnisme, il propose de postuler que la seule chose nécessaire est la &lt;a href="https://www.youtube.com/watch?v=5ECkL9MKDiI" title=" Quentin Meillassoux's "After Finitude" par Five Minute Philosophy "&gt; contingence absolue&lt;/a&gt;. Cela signifie que toutes les lois de la nature, toutes les entités existantes, sont radicalement contingentes et pourraient être différentes, ou même ne pas exister du tout. Il n'y a aucune raison ou fondement nécessaire à l'existence du monde tel qu'il est. Cette absence de raison ultime n'est pas un aveu d'ignorance, mais une vérité ontologique. C'est ce qu'il appelle le "principe de factualité". En affirmant cette contingence radicale, il s'inscrit dans une tradition matérialiste, mais une tradition qui se veut "spéculative" parce qu'elle cherche à penser l'absolu (l'absolu de la contingence) au-delà des limites imposées par le corrélationnisme. Il s'agit de s'affranchir de la dépendance de l'être vis-à-vis de la pensée. Sa pensée est notamment développée dans son ouvrage le plus célèbre,  &lt;a  href="https://fr.wikipedia.org/wiki/Apr%C3%A8s_la_finitude._Essai_sur_la_n%C3%A9cessit%C3%A9_de_la_contingence#:~:text=Quentin%20Meillassoux%20nomme%20cette%20philosophie,la%20pens%C3%A9e%20de%20l'absolu." title=" "Après la finitude. Essai sur la nécessité de la contingence" par Wikipedia "&gt;"Après la finitude. Essai sur la nécessité de la contingence"&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;  Dans sa thèse de doctorat "L'inexistence divine", il explore la possibilité d'un "dieu à venir". Pour lui, si Dieu n'existe pas actuellement, sa non-existence n'est pas une nécessité, mais une contingence. Ainsi, il n'est pas impossible qu'un jour un "Dieu" puisse émerger d'une manière ou d'une autre, à la suite d'un changement radical des lois physiques. &lt;/p&gt; &lt;p&gt; Dans son second livre "Le Nombre et la Sirène", il propose une lecture inédite du célèbre poème de Stéphane Mallarmé, "Un coup de dés jamais n'abolira le hasard". Il y développe une analyse détaillée, y découvrant  &lt;a href="https://www.youtube.com/watch?v=yKwqoW9PxVA" title=" Le code secret de Mallarmé enfin dévoilé?  par De Revolutionibus "&gt;un code numérique&lt;/a&gt;  qui, selon lui, serait intégré au texte par Mallarmé lui-même, en lien avec ses réflexions sur le hasard et la contingence.&lt;/p&gt; &lt;p&gt; En critiquant radicalement le corrélationnisme, il cherche à ouvrir la voie à une nouvelle forme de réalisme et de matérialisme, où la contingence est pensée non pas comme une limite de notre connaissance, mais comme une propriété fondamentale de l'être lui-même. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Quentin Meillassoux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-16.12.2011-ITEMA_20320127-2011C3403E0204-ITE_00047293_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Quentin_Meillassoux"  title=" Wikipedia"&gt;Quentin MEILLASSOUX&lt;/a&gt; est un philosophe français du courant qu'on appelle le  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif" style="color:#88A1E9" title=" Speculative Realism par Wikipedia "&gt;"réalisme spéculatif"&lt;/a&gt;. Le point de départ majeur de sa philosophie est "Le corrélationnisme" qui, selon lui, est la thèse dominante depuis Kant, et qui affirme qu'il est impossible de connaître le monde tel qu'il est en soi, indépendamment de notre rapport à lui (la corrélation entre la pensée et l'être). Cette position rend impossible de penser un "absolu" et nous enferme dans un cercle où nous ne pouvons accéder qu'à ce qui est "pour nous". &lt;a href="https://www.youtube.com/watch?v=29_IhFEWtlc" title="corine-pelluchon"&gt;Il s'interroge &lt;/a&gt;  sur la capacité de la science à parler de réalités "ancestrales", ce qui semble contredire le corrélationnisme. &lt;/p&gt; &lt;p&gt; Face au corrélationnisme, il propose de postuler que la seule chose nécessaire est la &lt;a href="https://www.youtube.com/watch?v=5ECkL9MKDiI" title=" Quentin Meillassoux's "After Finitude" par Five Minute Philosophy "&gt; contingence absolue&lt;/a&gt;. Cela signifie que toutes les lois de la nature, toutes les entités existantes, sont radicalement contingentes et pourraient être différentes, ou même ne pas exister du tout. Il n'y a aucune raison ou fondement nécessaire à l'existence du monde tel qu'il est. Cette absence de raison ultime n'est pas un aveu d'ignorance, mais une vérité ontologique. C'est ce qu'il appelle le "principe de factualité". En affirmant cette contingence radicale, il s'inscrit dans une tradition matérialiste, mais une tradition qui se veut "spéculative" parce qu'elle cherche à penser l'absolu (l'absolu de la contingence) au-delà des limites imposées par le corrélationnisme. Il s'agit de s'affranchir de la dépendance de l'être vis-à-vis de la pensée. Sa pensée est notamment développée dans son ouvrage le plus célèbre,  &lt;a  href="https://fr.wikipedia.org/wiki/Apr%C3%A8s_la_finitude._Essai_sur_la_n%C3%A9cessit%C3%A9_de_la_contingence#:~:text=Quentin%20Meillassoux%20nomme%20cette%20philosophie,la%20pens%C3%A9e%20de%20l'absolu." title=" "Après la finitude. Essai sur la nécessité de la contingence" par Wikipedia "&gt;"Après la finitude. Essai sur la nécessité de la contingence"&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;  Dans sa thèse de doctorat "L'inexistence divine", il explore la possibilité d'un "dieu à venir". Pour lui, si Dieu n'existe pas actuellement, sa non-existence n'est pas une nécessité, mais une contingence. Ainsi, il n'est pas impossible qu'un jour un "Dieu" puisse émerger d'une manière ou d'une autre, à la suite d'un changement radical des lois physiques. &lt;/p&gt; &lt;p&gt; Dans son second livre "Le Nombre et la Sirène", il propose une lecture inédite du célèbre poème de Stéphane Mallarmé, "Un coup de dés jamais n'abolira le hasard". Il y développe une analyse détaillée, y découvrant  &lt;a href="https://www.youtube.com/watch?v=yKwqoW9PxVA" title=" Le code secret de Mallarmé enfin dévoilé?  par De Revolutionibus "&gt;un code numérique&lt;/a&gt;  qui, selon lui, serait intégré au texte par Mallarmé lui-même, en lien avec ses réflexions sur le hasard et la contingence.&lt;/p&gt; &lt;p&gt; En critiquant radicalement le corrélationnisme, il cherche à ouvrir la voie à une nouvelle forme de réalisme et de matérialisme, où la contingence est pensée non pas comme une limite de notre connaissance, mais comme une propriété fondamentale de l'être lui-même. &lt;/p&gt;   &lt;audio controls title="Quentin Meillassoux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-16.12.2011-ITEMA_20320127-2011C3403E0204-ITE_00047293_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
@@ -4054,10 +4054,7 @@
       </c>
       <c r="E55" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Corine_Pelluchon"  style="color:#6A142A"  title=" Wikipedia"&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href="https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s" title="NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco"&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; 
-&lt;p&gt; - Manifeste animaliste. Politiser la cause animale ( 2017 )  - Éthique de la considération ( 2018) - Réparons le monde. Humains, animaux, nature (2020)  
- - Les Lumières à l’âge du vivant (2021) &lt;/p&gt; 
-&lt;p&gt; -   &lt;a href="https://www.youtube.com/watch?v=zpzzDqYhF-8" title="Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat"&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href="https://www.youtube.com/watch?v=tmk-UzN1j70"  title="Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media"&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title="Corine Pelluchon par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Corine_Pelluchon"  style="color:#6A142A"  title=" Wikipedia"&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href="https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s" title="NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco"&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &lt;p&gt;Manifeste animaliste. Politiser la cause animale ( 2017 ) Éthique de la considération ( 2018) Réparons le monde. Humains, animaux, nature (2020) Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=zpzzDqYhF-8" title="Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat"&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href="https://www.youtube.com/watch?v=tmk-UzN1j70"  title="Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media"&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title="Corine Pelluchon par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F55" s="34" t="inlineStr">
@@ -4124,7 +4121,7 @@
       </c>
       <c r="E56" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Denis_Moreau"  title=" Wikipedia"&gt;Denis MOREAU&lt;/a&gt; est un philosophe français spécialiste de la philosophie moderne et de la philosophie de la religion. . Docteur en philosophie (1996) et habilité à diriger des recherches (2008), il a été membre junior de l'Institut universitaire de France dès 2004. &lt;/p&gt; &lt;p&gt; Ses travaux portent principalement sur le XVIIe siècle, avec un focus sur Descartes, le cartésianisme, Malebranche et Spinoza. En philosophie de la religion, il explore le christianisme sous un angle rationaliste, s'inscrivant dans une tradition qu'il nomme "rationalisme chrétien" incluant Augustin, Thomas d'Aquin, Descartes ou encore Benoît XVI. Il aborde des thèmes comme le salut, le mariage, la résurrection et la foi, en articulant justification rationnelle et impact existentiel. &lt;/p&gt; &lt;p&gt; Il a publié plusieurs ouvrages marquants qui allient philosophie moderne, histoire de la philosophie et réflexion sur le christianisme rationalisé. Ses travaux les plus importants se divisent entre essais académiques sur le XVIIe siècle et livres grand public sur la foi. Voici les principaux : &lt;/p&gt; &lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=sglQGZawGWA&amp;list=PL2d4vA4vfs79mlFW_Mo0iP8anxf1F0XXG" title=" DESCARTES - Une expérience philosophique de la vérité, Denis Moreau par Editions M-Editer"&gt;Deux cartésiens&lt;/a&gt;. La polémique entre Descartes et Gassendi (2000), qui analyse les débats entre ces deux penseurs sur la connaissance et la méthode. &lt;/p&gt; &lt;p&gt; -  Mort où est ta victoire ? (2017), une réflexion sur la mort et la résurrection vue sous l'angle philosophique&lt;/p&gt; &lt;p&gt; - Les voies du salut (2015), qui explore les conceptions chrétiennes du salut de manière accessible et rationnelle. &lt;/p&gt; &lt;p&gt; -  &lt;a href="https://www.youtube.com/watch?v=AMv4Quma6t0"title=" Denis Moreau - Résurrections : traverser les nuits de nos vies par Librairie La Procure"&gt;Résurrections. Traverser les nuits de nos vies&lt;/a&gt; (2022), qui applique des thèmes chrétiens à l'existence contemporaine.&lt;/p&gt; &lt;p&gt; - Comment peut-on être catholique ? (2019), un plaidoyer rationnel pour la foi catholique dans un monde sécularisé. &lt;/p&gt;  &lt;audio controls title=" Cogito ergo sum : Descartes l'a-t-il réellement écrit ainsi ? Entretien avec Denis Moreau par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-08.09.2023-ITEMA_23480427-2023F45096S0251-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Denis_Moreau"  title=" Wikipedia"&gt;Denis MOREAU&lt;/a&gt; est un philosophe français spécialiste de la philosophie moderne et de la philosophie de la religion. . Docteur en philosophie (1996) et habilité à diriger des recherches (2008), il a été membre junior de l'Institut universitaire de France dès 2004. &lt;/p&gt; &lt;p&gt; Ses travaux portent principalement sur le XVIIe siècle, avec un focus sur Descartes, le cartésianisme, Malebranche et Spinoza. En philosophie de la religion, il explore le christianisme sous un angle rationaliste, s'inscrivant dans une tradition qu'il nomme "rationalisme chrétien" incluant Augustin, Thomas d'Aquin, Descartes ou encore Benoît XVI. Il aborde des thèmes comme le salut, le mariage, la résurrection et la foi, en articulant justification rationnelle et impact existentiel. &lt;/p&gt; &lt;p&gt; Il a publié plusieurs ouvrages marquants qui allient philosophie moderne, histoire de la philosophie et réflexion sur le christianisme rationalisé. Ses travaux les plus importants se divisent entre essais académiques sur le XVIIe siècle et livres grand public sur la foi. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=sglQGZawGWA&amp;list=PL2d4vA4vfs79mlFW_Mo0iP8anxf1F0XXG" title=" DESCARTES - Une expérience philosophique de la vérité, Denis Moreau par Editions M-Editer"&gt;Deux cartésiens&lt;/a&gt;. La polémique entre Descartes et Gassendi (2000), qui analyse les débats entre ces deux penseurs sur la connaissance et la méthode. &lt;/p&gt; &lt;p&gt;Mort où est ta victoire ? (2017), une réflexion sur la mort et la résurrection vue sous l'angle philosophique&lt;/p&gt; &lt;p&gt;Les voies du salut (2015), qui explore les conceptions chrétiennes du salut de manière accessible et rationnelle. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=AMv4Quma6t0"title=" Denis Moreau - Résurrections : traverser les nuits de nos vies par Librairie La Procure"&gt;Résurrections. Traverser les nuits de nos vies&lt;/a&gt; (2022), qui applique des thèmes chrétiens à l'existence contemporaine.&lt;/p&gt; &lt;p&gt;Comment peut-on être catholique ? (2019), un plaidoyer rationnel pour la foi catholique dans un monde sécularisé. &lt;/p&gt;  &lt;audio controls title=" Cogito ergo sum : Descartes l'a-t-il réellement écrit ainsi ? Entretien avec Denis Moreau par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-08.09.2023-ITEMA_23480427-2023F45096S0251-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
@@ -4248,7 +4245,7 @@
       </c>
       <c r="E58" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Renault"  title=" Wikipedia"&gt;Emmanuel RENAULT&lt;/a&gt; est un philosophe français, spécialisé en théorie critique, philosophie sociale et rapports entre reconnaissance, conflit et domination. Il est largement associé à une approche pragmatiste et pluraliste, cherchant à articuler Hegel, Marx, Honneth et le pragmatisme de Dewey dans une perspective interdisciplinaire. &lt;/p&gt; &lt;p&gt;  Il développe une approche qui croise les traditions marxistes et pragmatistes, et met l’accent sur les questions de travail, de justice, de  &lt;a href="https://www.nonfiction.fr/article-11867-abolir-lexploitation-entretien-avec-emmanuel-renault.htm" title="Abolir l'exploitation : entretien avec Emmanuel Renault. par nonfiction"&gt; souffrance sociale &lt;/a&gt; et de reconnaissance et il analyse comment les conflits sociaux, la reconnaissance et les formes de domination structurent l’injustice moderne.  Il s’inscrit dans une démarche qui remet en question les bases normatives de la justice politique en faveur d’une compréhension de l’injustice comme déni de reconnaissance et comme expérience de souffrance sociale. &lt;/p&gt; &lt;p&gt; Son travail est influent dans les débats sur la philosophie sociale en France et à l’étranger, et il participe à l’extension des cadres marxistes et pragmatistes dans la réflexion sur le travail,  &lt;a href="https://www.youtube.com/watch?v=6DriuHGugCA" title=" l'impensé de l'exploitation par Hors serie"&gt; l’exploitation &lt;/a&gt; et la justice sociale. Ses publications représentatives : - "Le Mépris social" paru en  2000 : exploration des formes de mépris et des dynamiques sociales qui les sous-tendent. - "Souffrances sociales" paru en 2008 : analyse des mécanismes de souffrance dans les sociétés contemporaines et leur lien avec la reconnaissance et la distribution des ressources. - "Reconnaissance, conflit, domination"  en 2017 : thèse centrale sur la relation entre reconnaissance, conflit et domination, et leur rôle dans la configuration des inégalités. &lt;/p&gt;  &lt;audio controls title="Mépris social : comment sortir du dialogue de sourds?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-29.10.2015-ITEMA_20828700-2015C19327S0302-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Renault"  title=" Wikipedia"&gt;Emmanuel RENAULT&lt;/a&gt; est un philosophe français, spécialisé en théorie critique, philosophie sociale et rapports entre reconnaissance, conflit et domination. Il est largement associé à une approche pragmatiste et pluraliste, cherchant à articuler Hegel, Marx, Honneth et le pragmatisme de Dewey dans une perspective interdisciplinaire. &lt;/p&gt; &lt;p&gt;  Il développe une approche qui croise les traditions marxistes et pragmatistes, et met l’accent sur les questions de travail, de justice, de  &lt;a href="https://www.nonfiction.fr/article-11867-abolir-lexploitation-entretien-avec-emmanuel-renault.htm" title="Abolir l'exploitation : entretien avec Emmanuel Renault. par nonfiction"&gt; souffrance sociale &lt;/a&gt; et de reconnaissance et il analyse comment les conflits sociaux, la reconnaissance et les formes de domination structurent l’injustice moderne.  Il s’inscrit dans une démarche qui remet en question les bases normatives de la justice politique en faveur d’une compréhension de l’injustice comme déni de reconnaissance et comme expérience de souffrance sociale. &lt;/p&gt; &lt;p&gt; Son travail est influent dans les débats sur la philosophie sociale en France et à l’étranger, et il participe à l’extension des cadres marxistes et pragmatistes dans la réflexion sur le travail,  &lt;a href="https://www.youtube.com/watch?v=6DriuHGugCA" title=" l'impensé de l'exploitation par Hors serie"&gt; l’exploitation &lt;/a&gt; et la justice sociale. Ses publications représentatives : "Le Mépris social" paru en  2000 : exploration des formes de mépris et des dynamiques sociales qui les sous-tendent. "Souffrances sociales" paru en 2008 : analyse des mécanismes de souffrance dans les sociétés contemporaines et leur lien avec la reconnaissance et la distribution des ressources. "Reconnaissance, conflit, domination"  en 2017 : thèse centrale sur la relation entre reconnaissance, conflit et domination, et leur rôle dans la configuration des inégalités. &lt;/p&gt;  &lt;audio controls title="Mépris social : comment sortir du dialogue de sourds?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-29.10.2015-ITEMA_20828700-2015C19327S0302-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F58" s="34" t="inlineStr">
@@ -4310,7 +4307,7 @@
       </c>
       <c r="E59" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Franck_Fischbach"  style="color:#6A142A"  title=" Wikipedia"&gt;Franck FISCHBACH&lt;/a&gt; est un philosophe franco-suisse  spécialiste de la philosophie allemande et de la philosophie sociale. Ses recherches portent sur l’idéalisme allemand (particulièrement Fichte, Hegel et Schelling), la réception de Marx et la philosophie sociale contemporaine. Il s’intéresse notamment à la reconnaissance, à l’aliénation, au travail, au socialisme, et à la &lt;a href="https://www.philomag.com/articles/franck-fischbach-le-capitalisme-fabrique-des-etres-qui-netant-plus-vraiment-sociaux-ne" style="color:#88A1E9" title=" Franck Fischbach : “Le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains” par philosophie magazine"&gt;critique du capitalisme&lt;/a&gt;. Il contribue activement à redonner à la philosophie sociale une légitimité intellectuelle en France. &lt;/p&gt; &lt;p&gt; Il relie la tradition de la théorie critique (Adorno, Honneth) et celle du matérialisme marxien pour repenser les conditions de la vie sociale et du « vivre ensemble ». Il analyse le capitalisme contemporain comme un processus de désocialisation et de perte du monde commun, considérant que "le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains".​ &lt;/p&gt; &lt;p&gt; Il  a reçu le Prix des Rencontres philosophiques de Monaco pour &lt;a href="https://www.youtube.com/watch?v=i16BcDagxns&amp;t=73s" style="color:#88A1E9" title=" Franck Fischbach → Faire ensemble. Reconstruction sociale et sortie du capitalisme par Librairie Ombre Blanche"&gt;"Faire ensemble"&lt;/a&gt;, ouvrage dans lequel il propose une refondation du lien social et une sortie éthique du capitalisme et il est aujourd’hui reconnu comme l’un des penseurs français majeurs de la philosophie sociale, prolongeant la critique marxienne à la lumière des défis écologiques et politiques contemporains.​ &lt;/p&gt; Professeur à l’université de Strasbourg, il a publié un &lt;em&gt;Manifeste pour une philosophie sociale&lt;/em&gt; (2009), qui veut redonner à la philosophie la tâche de diagnostiquer les « pathologies » de la société. Dans &lt;em&gt;La Privation de monde&lt;/em&gt; (2011), il décrit l’aliénation contemporaine comme une perte de prise sur le temps, l’espace et le monde commun.  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Qu'est-ce que la philosophie sociale? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11188-25.03.2010-ITEMA_20221135-2010C14987S0084-NET_B0358179-5AB7-42B6-8D32-144EADE35F65_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Franck_Fischbach"  style="color:#6A142A"  title=" Wikipedia"&gt;Franck FISCHBACH&lt;/a&gt; est un philosophe franco-suisse  spécialiste de la philosophie allemande et de la philosophie sociale. Ses recherches portent sur l’idéalisme allemand (particulièrement Fichte, Hegel et Schelling), la réception de Marx et la philosophie sociale contemporaine. Il s’intéresse notamment à la reconnaissance, à l’aliénation, au travail, au socialisme, et à la &lt;a href="https://www.philomag.com/articles/franck-fischbach-le-capitalisme-fabrique-des-etres-qui-netant-plus-vraiment-sociaux-ne" style="color:#88A1E9" title=" Franck Fischbach : “Le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains” par philosophie magazine"&gt;critique du capitalisme&lt;/a&gt;. Il contribue activement à redonner à la philosophie sociale une légitimité intellectuelle en France. &lt;/p&gt; &lt;p&gt; Il relie la tradition de la théorie critique (Adorno, Honneth) et celle du matérialisme marxien pour repenser les conditions de la vie sociale et du « vivre ensemble ». Il analyse le capitalisme contemporain comme un processus de désocialisation et de perte du monde commun, considérant que "le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains".​ &lt;/p&gt; &lt;p&gt; Il  a reçu le Prix des Rencontres philosophiques de Monaco pour &lt;a href="https://www.youtube.com/watch?v=i16BcDagxns&amp;t=73s" style="color:#88A1E9" title=" Franck Fischbach → Faire ensemble. Reconstruction sociale et sortie du capitalisme par Librairie Ombre Blanche"&gt;"Faire ensemble"&lt;/a&gt;, ouvrage dans lequel il propose une refondation du lien social et une sortie éthique du capitalisme et il est aujourd’hui reconnu comme l’un des penseurs français majeurs de la philosophie sociale, prolongeant la critique marxienne à la lumière des défis écologiques et politiques contemporains.​ &lt;/p&gt; Professeur à l’université de Strasbourg, il a publié un &lt;em&gt;Manifeste pour une philosophie sociale&lt;/em&gt; (2009), qui veut redonner à la philosophie la tâche de diagnostiquer les « pathologies » de la société. Dans &lt;em&gt;La Privation de monde&lt;/em&gt; (2011), il décrit l’aliénation contemporaine comme une perte de prise sur le temps, l’espace et le monde commun.    &lt;audio controls title=" Qu'est-ce que la philosophie sociale? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11188-25.03.2010-ITEMA_20221135-2010C14987S0084-NET_B0358179-5AB7-42B6-8D32-144EADE35F65_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -4441,7 +4438,7 @@
       </c>
       <c r="E61" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://www.philomag.com/philosophes/laurence-devillairs"  title=" Wikipedia"&gt;Laurence DEVILLAIRS&lt;/a&gt;  est une philosophe française, spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle. Elle enseigne à l’université Paris 1 Panthéon-Sorbonne et s’adresse aussi à un large public à travers des essais et des interventions. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse beaucoup à la morale concrète : le bien, le mal, &lt;a href="https://www.youtube.com/watch?v=a5YnPWx7Xw8" title="laurence Devillairs : Eloge de la gentillesse par Brut"&gt; la gentillesse, &lt;/a&gt; le courage, la justice. Elle refuse une vision trop abstraite de l’éthique et cherche plutôt à montrer comment on devient une &lt;a href="https://www.youtube.com/watch?v=T0U2ro8b9Io" title="laurence Devillairs : a quoi reconnaître quelqu’un de bien par TV Monde"&gt; personne meilleure &lt;/a&gt; dans la vie quotidienne. &lt;/p&gt; &lt;p&gt; Elle réfléchit aussi au politique, mais d’une manière très humaine : comment vivre ensemble, comment &lt;a href="https://www.youtube.com/watch?v=p9AaVfIoIPg" title="laurence Devillairs : le pouvoir par Fabrice Midal"&gt; penser le pouvoir, &lt;/a&gt; comment garder une place pour l’utopie et l’espérance sans perdre le sens du réel. Chez elle, le politique n’est pas seulement affaire de règles, mais aussi de désir de transformation. &lt;/p&gt; &lt;p&gt; On peut dire que sa philosophie défend une forme de fermeté douce : être bon ne veut pas dire être faible, et la gentillesse peut être un choix éthique fort. Son travail cherche à rendre la philosophie utile pour mieux vivre, mieux juger et mieux agir. Lectrice de Descartes, elle retient de lui le goût de la clarté et de la générosité, cette juste estime de soi qui consiste à bien user de sa liberté. Dans &lt;em&gt;Être quelqu’un de bien&lt;/em&gt; (2019), elle montre que la bonté n’est pas une naïveté, mais une forme de courage, et qu’elle se joue d’abord dans les gestes ordinaires, l’attention, la parole donnée, le refus de l’humiliation. &lt;/p&gt;  &lt;audio controls title="Laurence Devillairs : le désir de vengeance est une libération  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.04.2026-ITEMA_24449483-2026F22640S0095-NET_MFI_BFCBC71B-F523-4D4D-9C0D-E455E058A13C-22-23fd728f6afa552353ce5d4ded4690c9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://www.philomag.com/philosophes/laurence-devillairs"  title=" Wikipedia"&gt;Laurence DEVILLAIRS&lt;/a&gt;  est une philosophe française, spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle. Elle enseigne à l’université Paris 1 Panthéon-Sorbonne et s’adresse aussi à un large public à travers des essais et des interventions. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse beaucoup à la morale concrète : le bien, le mal, &lt;a href="https://www.youtube.com/watch?v=a5YnPWx7Xw8" title="laurence Devillairs : Eloge de la gentillesse par Brut"&gt; la gentillesse, &lt;/a&gt; le courage, la justice. Elle refuse une vision trop abstraite de l’éthique et cherche plutôt à montrer comment on devient une &lt;a href="https://www.youtube.com/watch?v=T0U2ro8b9Io" title="laurence Devillairs : a quoi reconnaître quelqu’un de bien par TV Monde"&gt; personne meilleure &lt;/a&gt; dans la vie quotidienne. &lt;/p&gt; &lt;p&gt; Elle réfléchit aussi au politique, mais d’une manière très humaine : comment vivre ensemble, comment &lt;a href="https://www.youtube.com/watch?v=p9AaVfIoIPg" title="laurence Devillairs : le pouvoir par Fabrice Midal"&gt; penser le pouvoir, &lt;/a&gt; comment garder une place pour l’utopie et l’espérance sans perdre le sens du réel. Chez elle, le politique n’est pas seulement affaire de règles, mais aussi de désir de transformation. &lt;/p&gt; &lt;p&gt; Sa philosophie défend une forme de fermeté douce : être bon ne veut pas dire être faible, et la gentillesse peut être un choix éthique fort. Son travail cherche à rendre la philosophie utile pour mieux vivre, mieux juger et mieux agir. Lectrice de Descartes, elle retient de lui le goût de la clarté et de la générosité, cette juste estime de soi qui consiste à bien user de sa liberté. Dans &lt;em&gt;Être quelqu’un de bien&lt;/em&gt; (2019), elle montre que la bonté n’est pas une naïveté, mais une forme de courage, et qu’elle se joue d’abord dans les gestes ordinaires, l’attention, la parole donnée, le refus de l’humiliation. &lt;/p&gt;  &lt;audio controls title="Laurence Devillairs : le désir de vengeance est une libération  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.04.2026-ITEMA_24449483-2026F22640S0095-NET_MFI_BFCBC71B-F523-4D4D-9C0D-E455E058A13C-22-23fd728f6afa552353ce5d4ded4690c9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -4571,9 +4568,9 @@
       </c>
       <c r="E63" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Monod"  title=" Wikipedia"&gt;Jean Claude MONOD&lt;/a&gt; est un philosophe français  contemporain, spécialiste de philosophie politique et de philosophie allemande des XIXe et XXe siècles, en particulier de la question de la sécularisation et des rapports entre religion, modernité et démocratie. &lt;/p&gt; &lt;p&gt;  Un axe central de sa réflexion est de comment comprendre la modernité sans la réduire à une simple transposition de catégories religieuses, et comment penser  &lt;a href="https://www.youtube.com/watch?v=E111pSvCT8g"  title="
-Jean-Claude Monod - L'art de ne pas être trop gouverné par librairie mollat"&gt;le théologico-politique&lt;/a&gt;  aujourd’hui. Il s’intéresse aussi aux formes contemporaines du pouvoir (crises de l’État libéral, charisme politique, crises de gouvernementalité, néolibéralisme autoritaire) et aux tensions entre démocratie, vérité et fake news. &lt;/p&gt; &lt;p&gt; Dans son ouvrage : - &lt;a href="https://www.gregoiredetours.fr/thematiques/religions/jean-claude-monod-secularisation-et-laicite/"  title="
-Jean-Claude Monod -  "La Querelle de la sécularisation" par gregoire de tours"&gt; "La Querelle de la sécularisation"&lt;/a&gt; : Théologies politiques et philosophies de l’Histoire, de Hegel à Blumenberg (Vrin) : analyse des grands débats sur la sécularisation et la modernité, avec une attention particulière à Blumenberg. &lt;/p&gt; &lt;p&gt; - "Penser l’ennemi, affronter l’exception" : Réflexions critiques sur l’actualité de Carl Schmitt (La Découverte) : lecture critique de Schmitt et de la notion d’exception dans les démocraties contemporaines.&lt;/p&gt; &lt;p&gt; Il intervient régulièrement dans les médias et dans des conférences sur la démocratie, l’extrême droite, la crise de l’État et les transformations du néolibéralisme, où il défend une analyse fine des liens entre pouvoir, autorité et contestation. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Monod"  title=" Wikipedia"&gt;Jean Claude MONOD&lt;/a&gt; est un philosophe français  contemporain, spécialiste de philosophie politique et de philosophie allemande des XIXe et XXe siècles, en particulier de la question de la sécularisation et des rapports entre religion, modernité et démocratie. &lt;/p&gt; &lt;p&gt;  Un axe central de sa réflexion est de comment comprendre la modernité sans la réduire à une simple transposition de catégories religieuses, et comment penser  &lt;a href="https://www.youtube.com/watch?v=E111pSvCT8g"  title="
+Jean-Claude Monod - L'art de ne pas être trop gouverné par librairie mollat"&gt;le théologico-politique&lt;/a&gt;  aujourd’hui. Il s’intéresse aussi aux formes contemporaines du pouvoir (crises de l’État libéral, charisme politique, crises de gouvernementalité, néolibéralisme autoritaire) et aux tensions entre démocratie, vérité et fake news. &lt;/p&gt; &lt;p&gt; Dans son ouvrage : &lt;a href="https://www.gregoiredetours.fr/thematiques/religions/jean-claude-monod-secularisation-et-laicite/"  title="
+Jean-Claude Monod -  "La Querelle de la sécularisation" par gregoire de tours"&gt; "La Querelle de la sécularisation"&lt;/a&gt; : Théologies politiques et philosophies de l’Histoire, de Hegel à Blumenberg (Vrin) : analyse des grands débats sur la sécularisation et la modernité, avec une attention particulière à Blumenberg. &lt;/p&gt; &lt;p&gt;"Penser l’ennemi, affronter l’exception" : Réflexions critiques sur l’actualité de Carl Schmitt (La Découverte) : lecture critique de Schmitt et de la notion d’exception dans les démocraties contemporaines.&lt;/p&gt; &lt;p&gt; Il intervient régulièrement dans les médias et dans des conférences sur la démocratie, l’extrême droite, la crise de l’État et les transformations du néolibéralisme, où il défend une analyse fine des liens entre pouvoir, autorité et contestation. &lt;/p&gt; 
   &lt;audio controls title="L'intellectuel peut-il encore exister au XXIe siècle ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/25951-29.11.2025-ITEMA_24326903-2025C54596S0333-NET_MFC_C2F18604-F792-44E5-803E-E62225C653B4-25-bf7dbc88816a940ebe2dc58d15ae6341.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
@@ -4636,7 +4633,7 @@
       </c>
       <c r="E64" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Mehl"  title=" Wikipedia"&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href="https://www.youtube.com/watch?v=NT0n7tKNb3w" title="qu’est ce que la verité par Le forum Veritas"&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. Il a notamment étudié le jeune Descartes lors de son séjour en Allemagne, en 1619-1620, au moment de ses célèbres songes et de la naissance de sa méthode, ainsi que ses rapports avec Kepler et les savants de son temps. Il montre que la métaphysique cartésienne est inséparable d’un projet de physique et de cosmologie, qui vise à rendre le monde visible et intelligible tout entier. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Mehl"  title=" Wikipedia"&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href="https://www.youtube.com/watch?v=NT0n7tKNb3w" title="qu’est ce que la verité par Le forum Veritas"&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; Il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. Il a notamment étudié le jeune Descartes lors de son séjour en Allemagne, en 1619-1620, au moment de ses célèbres songes et de la naissance de sa méthode, ainsi que ses rapports avec Kepler et les savants de son temps. Il montre que la métaphysique cartésienne est inséparable d’un projet de physique et de cosmologie, qui vise à rendre le monde visible et intelligible tout entier. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4768,7 +4765,7 @@
       <c r="E66" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yves_Cusset"  style="color:#6A142A"  title=" Wikipedia"&gt;Yves CUSSET&lt;/a&gt;  est un philosophe français agrégé et docteur en philosophie, qui allie une réflexion sérieuse sur la philosophie politique à un engagement théâtral et  &lt;a href="https://www.youtube.com/watch?v=uJLmpAgqiWY" style="color:#88A1E9" title="Yves Cusset, Petit manuel d'engagement politique à l'usage des mammifères doués de raison.... par Yves Cusset"&gt;humoristique unique. &lt;/a&gt;  Spécialiste de Habermas et Foucault, il explore les tensions entre raison discussionnelle et pouvoir, ainsi que les apories de l’accueil : comment concilier exigence éthique d’hospitalité et contraintes politiques. &lt;/p&gt; &lt;p&gt; Ses essais interrogent le "bien-mourir", critiquant les normes contemporaines de la mort apaisée, et défendent une politique de l’accueil face à la misère du monde.  Il théorise l’humour comme "bonne humeur pour mourir", un outil philosophique qui désarme les idées fixes et favorise la pensée sans intimidation. Il crée des solos comme Rien ne sert d’exister, Tractatus philo-comicus ou La Philosophie enseignée à ma chouette, joués au festival d’Avignon et ailleurs, mêlant rire, absurdité et métaphysique. &lt;/p&gt; &lt;p&gt; Militant discret, il use de l’humour politique pour dénoncer clichés  &lt;a href="https://www.youtube.com/watch?v=QwVPt_PQE-Q" style="color:#88A1E9" title="Yves Cusset : 100 façons de ne pas accueillir un migrant par TV5Monde"&gt;anti-migrants &lt;/a&gt; ou dérives du "développement personnel".  Son genre hybride, l’"humour philosophique", vise à émerveiller par le rire, suscitant la réflexion sans complexer, comme il l’explique dans Le Monde. Ses premiers travaux portent sur Habermas, dont il présente l’« éthique de la discussion » : une norme n’est valable que si tous ceux qu’elle concerne pourraient l’accepter au terme d’une discussion libre. Il en tire une exigence démocratique, mais aussi une attention à ceux qui n’ont pas la parole. Pour lui, le rire n’est pas une fuite hors de la pensée : il oblige à prendre de la distance avec soi-même et avec les certitudes. &lt;/p&gt; 
-&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="L'amour avec Yves Cusset par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-07.06.2024-ITEMA_23765968-2024F45096S0159-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+  &lt;audio controls title="L'amour avec Yves Cusset par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-07.06.2024-ITEMA_23765968-2024F45096S0159-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -4831,10 +4828,10 @@
       </c>
       <c r="E67" s="37" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89ric_Sadin"  title=" Wikipedia"&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href="https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur" style="color:#88A1E9"   title=" Éric SADIN contre ChatGPT par Senseur"&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89ric_Sadin"  title=" Wikipedia"&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href="https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur" style="color:#88A1E9"   title=" Éric SADIN contre ChatGPT par Senseur"&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;
 Sadin s'est fait connaître grâce à son livre "La société de l'anticipation " publié en 2011, dans lequel il examine l'émergence de la société de la surveillance et des technologies de prévision qui cherchent à anticiper les comportements et les désirs des individus. Il y aborde notamment les thèmes de la surveillance généralisée, de la collecte de données personnelles et des risques de manipulation. &lt;/p&gt; &lt;p&gt;
 Dans son ouvrage &lt;a href="https://christian-biales.fr/wp-content/uploads/2020/12/Sadin.pdf"  title="Extrait du livre par Christian Bialès"&gt; "L'Ère de l'individu tyran : la fin d'un monde commun"&lt;/a&gt; paru en 2013, Sadin explore les conséquences de la numérisation de la société sur les notions de vie privée, de liberté individuelle et de démocratie. Il met en garde contre le pouvoir croissant des grandes plateformes technologiques et la manière dont elles peuvent influencer et contrôler nos comportements et nos choix. &lt;/p&gt; &lt;p&gt;
-Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre "La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique" publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href="https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008"  title="Dataïsme par lebigdata"&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title="Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre "La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique" publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href="https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008"  title="Dataïsme par lebigdata"&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title="Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F67" s="34" t="inlineStr">
@@ -4896,7 +4893,7 @@
       </c>
       <c r="E68" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau" title=" Wikipedia"&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href="https://www.youtube.com/watch?v=PNMZHr3L_Ws" title=" Vivons nous dans un multivers par Aurelien Barrau"&gt; concept de multivers&lt;/a&gt;, et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage "Chaos multiples" et "De la vérité dans les sciences"  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé "Météorites". &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de "sauver le climat" plutôt "qu’agir pour la vie". &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  "habiter la science en poète" en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href="https://www.youtube.com/watch?v=94IxSYo5wtM" title="Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter"&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href="https://www.youtube.com/watch?v=g3Z_LsXD7DU" title=" L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac"&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un "faire monde" éthique et conscient. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" Aurelien BARRAU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau" title=" Wikipedia"&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href="https://www.youtube.com/watch?v=PNMZHr3L_Ws" title=" Vivons nous dans un multivers par Aurelien Barrau"&gt; concept de multivers&lt;/a&gt;, et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage "Chaos multiples" et "De la vérité dans les sciences"  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé "Météorites". &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de "sauver le climat" plutôt "qu’agir pour la vie". &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  "habiter la science en poète" en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href="https://www.youtube.com/watch?v=94IxSYo5wtM" title="Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter"&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href="https://www.youtube.com/watch?v=g3Z_LsXD7DU" title=" L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac"&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un "faire monde" éthique et conscient. &lt;/p&gt;   &lt;audio controls title=" Aurelien BARRAU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
@@ -4958,7 +4955,7 @@
       </c>
       <c r="E69" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin" title=" Wikipedia"&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href="https://charlespepin.fr/"  title=" Site officiel Charles Pépin "&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href="https://www.youtube.com/watch?v=WExeoL6qVmc" title=" Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori"&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href="https://www.youtube.com/watch?v=orOxuIHT_vc" title="Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal"&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt; - "Les Vertus de l’échec" publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt; - "La Confiance en soi " paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt; - "La Rencontre"  en 2021 et "Vivre avec son passé" en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href="https://www.youtube.com/watch?v=M09YmUzDwO8" title=" Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs"&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=" La philosophie selon Charles Pépin par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin" title=" Wikipedia"&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href="https://charlespepin.fr/"  title=" Site officiel Charles Pépin "&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href="https://www.youtube.com/watch?v=WExeoL6qVmc" title=" Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori"&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href="https://www.youtube.com/watch?v=orOxuIHT_vc" title="Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal"&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt;"Les Vertus de l’échec" publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt;"La Confiance en soi " paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt;"La Rencontre"  en 2021 et "Vivre avec son passé" en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href="https://www.youtube.com/watch?v=M09YmUzDwO8" title=" Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs"&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt;   &lt;audio controls title=" La philosophie selon Charles Pépin par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -5146,7 +5143,7 @@
       </c>
       <c r="E72" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cynthia_Fleury"  style="color:#6A142A"  title=" Wikipedia"&gt;Cynthia FLEURY&lt;/a&gt;  est une philosophe française connue pour son travail sur la démocratie, la vulnérabilité et l’éthique du soin. Elle  s’intéresse aux "outils de la &lt;a href="https://www.youtube.com/watch?v=rlmteYHuBsc" style="color:#88A1E9" title="DÉMOCRATIE, Cynthia Fleury (ABC Penser) "&gt;régulation démocratique" &lt;/a&gt; et au principe d’individuation en État social de droit, c’est‑à‑dire à la manière dont un État permet à chacun de devenir un sujet autonome tout en restant inséré dans le collectif. &lt;/p&gt; &lt;p&gt; Elle insiste sur l’importance d’un État social qui ne vise pas seulement la croissance économique, mais l’émancipation et l’autonomie des individus, notamment via les biens communs comme la santé et l’éducation et défend l’idée que la démocratie se joue aussi dans la façon dont nous prenons soin des plus vulnérables, à la fois sur le plan institutionnel et dans les relations ordinaires. &lt;/p&gt; &lt;p&gt;Pour elle, la vulnérabilité n’est pas l’inverse de l’autonomie, mais ce qui la traverse et la rend possible, à condition que la société permette de rendre les épreuves vécues "réversibles".&lt;/p&gt; &lt;p&gt;  Elle insiste sur l’éthique du soin : l’éthique n’est pas un "supplément d’âme" mais une condition pour éviter l’épuisement des soignants et mieux soigner les patients dans des institutions très gestionnaires. &lt;/p&gt; &lt;p&gt;Elle  défend un humanisme renouvelé et affirme l’urgence de remettre l’humanisme au cœur du système, face à l’hyper‑compétition, à la productivité sans fin et à l’aliénation qu’elles produisent. Sa réflexion propose une articulation entre transformation personnelle (travailler sa  &lt;a href="https://www.youtube.com/watch?v=8raeMytwQ8U" style="color:#88A1E9" title="Conférence de Cynthia Fleury sur la vulnérabilité  par  Faculté de Santé Sorbonne"&gt;propre vulnérabilité, &lt;/a&gt;  son courage, sa responsabilité) et transformation sociale (institutions plus justes, protection des biens communs, attention à la dignité de tous). &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Cynthia Fleury : comment refaire société ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22259-09.07.2024-ITEMA_23798171-2024F44116S0191-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cynthia_Fleury"  style="color:#6A142A"  title=" Wikipedia"&gt;Cynthia FLEURY&lt;/a&gt;  est une philosophe française connue pour son travail sur la démocratie, la vulnérabilité et l’éthique du soin. Elle  s’intéresse aux "outils de la &lt;a href="https://www.youtube.com/watch?v=rlmteYHuBsc" style="color:#88A1E9" title="DÉMOCRATIE, Cynthia Fleury (ABC Penser) "&gt;régulation démocratique" &lt;/a&gt; et au principe d’individuation en État social de droit, c’est‑à‑dire à la manière dont un État permet à chacun de devenir un sujet autonome tout en restant inséré dans le collectif. &lt;/p&gt; &lt;p&gt; Elle insiste sur l’importance d’un État social qui ne vise pas seulement la croissance économique, mais l’émancipation et l’autonomie des individus, notamment via les biens communs comme la santé et l’éducation et défend l’idée que la démocratie se joue aussi dans la façon dont nous prenons soin des plus vulnérables, à la fois sur le plan institutionnel et dans les relations ordinaires. &lt;/p&gt; &lt;p&gt;Pour elle, la vulnérabilité n’est pas l’inverse de l’autonomie, mais ce qui la traverse et la rend possible, à condition que la société permette de rendre les épreuves vécues "réversibles".&lt;/p&gt; &lt;p&gt;  Elle insiste sur l’éthique du soin : l’éthique n’est pas un "supplément d’âme" mais une condition pour éviter l’épuisement des soignants et mieux soigner les patients dans des institutions très gestionnaires. &lt;/p&gt; &lt;p&gt;Elle  défend un humanisme renouvelé et affirme l’urgence de remettre l’humanisme au cœur du système, face à l’hyper‑compétition, à la productivité sans fin et à l’aliénation qu’elles produisent. Sa réflexion propose une articulation entre transformation personnelle (travailler sa  &lt;a href="https://www.youtube.com/watch?v=8raeMytwQ8U" style="color:#88A1E9" title="Conférence de Cynthia Fleury sur la vulnérabilité  par  Faculté de Santé Sorbonne"&gt;propre vulnérabilité, &lt;/a&gt;  son courage, sa responsabilité) et transformation sociale (institutions plus justes, protection des biens communs, attention à la dignité de tous). &lt;/p&gt;   &lt;audio controls title="Cynthia Fleury : comment refaire société ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22259-09.07.2024-ITEMA_23798171-2024F44116S0191-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
@@ -5411,7 +5408,7 @@
       </c>
       <c r="E76" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Citot"  title=" Wikipedia"&gt;Vincent CITOT&lt;/a&gt; est un philosophe  français, directeur de la revue Le Philosophoire et auteur de travaux sur la philosophie générale, les rapports entre philosophie et science, ainsi que sur la modernité et l’histoire des idées.   &lt;a href="http://www.vincentcitot.com" title="Vincent CITOT"&gt;Son parcours &lt;/a&gt; mêle aussi l’écriture et la photographie, ce qui lui donne une pratique intellectuelle assez large.https://fr.wikipedia.org/wiki/Vincent_Citot &lt;/p&gt; &lt;p&gt; Sa philosophie insiste d’abord sur l’exigence de penser contre les évidences, les dogmes et le conformisme. Chez lui, philosopher n’est pas simplement enchaîner des idées, mais faire un effort critique, une vigilance de l’esprit qui commence par le doute et la mise à distance des fausses certitudes. Cette dimension critique fait de la réflexion une forme d’ascèse intellectuelle, au service de la liberté. &lt;/p&gt; &lt;p&gt; Il défend aussi une conception exigeante mais non réductrice de la philosophie : elle n’est pas une science au sens strict, mais elle dialogue avec la science tout en gardant sa propre portée de sagesse, de valeurs et de pratique existentielle. Dans cette perspective, la philosophie doit examiner ses limites, ses présupposés et ses méthodes, sans se prendre pour un savoir absolu. Il accorde également une grande place à l’universalisme, notamment dans les questions existentielles, qu’il juge plus stables et plus universelles que les cadres purement historiques ou culturels. &lt;/p&gt; &lt;p&gt; Enfin, son ouvrage Histoire mondiale de la philosophie élargit le regard au-delà du seul modèle grec : il propose de penser la philosophie comme une forme de pensée qui cherche à se justifier par divers moyens, dans plusieurs civilisations et au sein de cycles intellectuels plus vastes. Cela fait de lui  &lt;a href="https://www.les-philosophes.fr/agora/vincent-citot.html" title="Vincent CITOT par lesphiulosophes,fr"&gt;un philosophe du comparatisme &lt;/a&gt;  et de la pluralité des traditions, attentif à la modernité, à la liberté individuelle et à la diversité des formes de rationalité. &lt;/p&gt; &lt;audio controls title="Histoire mondiale de la philosophie avec Vincent CITOT  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-14.10.2022-ITEMA_23166024-2022F45096S0287-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Citot"  title=" Wikipedia"&gt;Vincent CITOT&lt;/a&gt; est un philosophe  français, directeur de la revue Le Philosophoire et auteur de travaux sur la philosophie générale, les rapports entre philosophie et science, ainsi que sur la modernité et l’histoire des idées.   &lt;a href="http://www.vincentcitot.com" title="Vincent CITOT"&gt;Son parcours &lt;/a&gt; mêle aussi l’écriture et la photographie, ce qui lui donne une pratique intellectuelle assez large. &lt;/p&gt; &lt;p&gt; Sa philosophie insiste d’abord sur l’exigence de penser contre les évidences, les dogmes et le conformisme. Chez lui, philosopher n’est pas simplement enchaîner des idées, mais faire un effort critique, une vigilance de l’esprit qui commence par le doute et la mise à distance des fausses certitudes. Cette dimension critique fait de la réflexion une forme d’ascèse intellectuelle, au service de la liberté. &lt;/p&gt; &lt;p&gt; Il défend aussi une conception exigeante mais non réductrice de la philosophie : elle n’est pas une science au sens strict, mais elle dialogue avec la science tout en gardant sa propre portée de sagesse, de valeurs et de pratique existentielle. Dans cette perspective, la philosophie doit examiner ses limites, ses présupposés et ses méthodes, sans se prendre pour un savoir absolu. Il accorde également une grande place à l’universalisme, notamment dans les questions existentielles, qu’il juge plus stables et plus universelles que les cadres purement historiques ou culturels. &lt;/p&gt; &lt;p&gt; Enfin, son ouvrage Histoire mondiale de la philosophie élargit le regard au-delà du seul modèle grec : il propose de penser la philosophie comme une forme de pensée qui cherche à se justifier par divers moyens, dans plusieurs civilisations et au sein de cycles intellectuels plus vastes. Cela fait de lui  &lt;a href="https://www.les-philosophes.fr/agora/vincent-citot.html" title="Vincent CITOT par lesphiulosophes,fr"&gt;un philosophe du comparatisme &lt;/a&gt;  et de la pluralité des traditions, attentif à la modernité, à la liberté individuelle et à la diversité des formes de rationalité. &lt;/p&gt; &lt;audio controls title="Histoire mondiale de la philosophie avec Vincent CITOT  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-14.10.2022-ITEMA_23166024-2022F45096S0287-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
 </t>
         </is>
       </c>
@@ -5474,8 +5471,8 @@
       </c>
       <c r="E77" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9verine_Kodjo-Grandvaux"  title=" Wikipedia"&gt;Séverine KODJO-GRANDVAUX&lt;/a&gt; est une philosophe, journaliste, programmatrice littéraire et  &lt;a href="https://www.jeuneafrique.com/auteurs/s-kodjo-grandvaux/"  title="Ses dernières publications par jeuneafrique"&gt;éditrice française &lt;/a&gt; principalement reconnue pour ses travaux sur les philosophies africaines contemporaines et les études postcoloniales. Elle occupe une position de chercheure associée au Laboratoire des logiques contemporaines de la philosophie à l’Université Paris 8, et elle est impliquée dans des initiatives autour des humanités africaines et des échanges intellectuels entre l’Afrique et le monde francophone. &lt;/p&gt; &lt;p&gt; En 2013, elle publie &lt;a href="https://www.youtube.com/watch?v=w8pfqdnej-o" title="African Philosophies I Lecture by philosopher Séverine Kodjo-Grandvaux par Radboud Reflects"&gt;"Philosophies africaines", &lt;/a&gt; ouvrage qui est considéré comme une référence majeure dans le domaine et qui analyse en profondeur les courants et les enjeux de la philosophie africaine contemporaine. Elle publie ensuite  &lt;a href="https://www.youtube.com/watch?v=AJAz1OmcVbI" title=""Devenir Vivants" avec Séverine Kodjo-Grandvaux. Extrait du podcast Afrotopiques par Génération Afrotopia"&gt;"Devenir vivants" &lt;/a&gt; et "Droit et colonisation"  — œuvre collective sur les rapports entre droit et colonialisme, témoignant d’un engagement dans les études postcoloniales et juridiques. &lt;/p&gt; &lt;p&gt; Ce qui la distingue dans le paysage philosophique français, c'est sa capacité à faire dialoguer les philosophies africaines avec les enjeux contemporains globaux, notamment écologiques et postcoloniaux. Elle contribue à décentrer la pensée philosophique de son eurocentrisme traditionnel tout en proposant des outils conceptuels originaux pour penser notre relation au vivant et au cosmos.&lt;/p&gt;
- &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Philosophie Africaine par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12016-15.04.2013-ITEMA_20470144-2013C18044S0105-NET_FC_590A75DA-F57B-40F9-88DF-1D448D87542C-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9verine_Kodjo-Grandvaux"  title=" Wikipedia"&gt;Séverine KODJO-GRANDVAUX&lt;/a&gt; est une philosophe, journaliste, programmatrice littéraire et  &lt;a href="https://www.jeuneafrique.com/auteurs/s-kodjo-grandvaux/"  title="Ses dernières publications par jeuneafrique"&gt;éditrice française &lt;/a&gt; principalement reconnue pour ses travaux sur les philosophies africaines contemporaines et les études postcoloniales. Elle occupe une position de chercheure associée au Laboratoire des logiques contemporaines de la philosophie à l’Université Paris 8, et elle est impliquée dans des initiatives autour des humanités africaines et des échanges intellectuels entre l’Afrique et le monde francophone. &lt;/p&gt; &lt;p&gt; En 2013, elle publie &lt;a href="https://www.youtube.com/watch?v=w8pfqdnej-o" title="African Philosophies I Lecture by philosopher Séverine Kodjo-Grandvaux par Radboud Reflects"&gt;"Philosophies africaines", &lt;/a&gt; ouvrage qui est considéré comme une référence majeure dans le domaine et qui analyse en profondeur les courants et les enjeux de la philosophie africaine contemporaine. Elle publie ensuite  &lt;a href="https://www.youtube.com/watch?v=AJAz1OmcVbI" title=""Devenir Vivants" avec Séverine Kodjo-Grandvaux. Extrait du podcast Afrotopiques par Génération Afrotopia"&gt;"Devenir vivants" &lt;/a&gt; et "Droit et colonisation"  — œuvre collective sur les rapports entre droit et colonialisme, témoignant d’un engagement dans les études postcoloniales et juridiques. &lt;/p&gt; &lt;p&gt; Ce qui la distingue dans le paysage philosophique français, c'est sa capacité à faire dialoguer les philosophies africaines avec les enjeux contemporains globaux, notamment écologiques et postcoloniaux. Elle contribue à décentrer la pensée philosophique de son eurocentrisme traditionnel tout en proposant des outils conceptuels originaux pour penser notre relation au vivant et au cosmos.&lt;/p&gt;
+   &lt;audio controls title="Philosophie Africaine par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12016-15.04.2013-ITEMA_20470144-2013C18044S0105-NET_FC_590A75DA-F57B-40F9-88DF-1D448D87542C-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F77" s="34" t="inlineStr">
@@ -5542,7 +5539,7 @@
       </c>
       <c r="E78" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maxime_Rov%C3%A8re"  title=" Wikipedia"&gt;Maxime ROVÈRE&lt;/a&gt;  est un philosophe, écrivain et traducteur français, spécialiste de Spinoza et créateur d’une -&lt;a href="https://www.youtube.com/watch?v=A_4XSOHakEY" title="À l'école des interactions - Maxime Rovere par Revue Esprit"&gt;"philosophie interactionnelle" &lt;/a&gt; qui met l’accent sur les relations humaines dynamiques plutôt que sur des systèmes abstraits. Chercheur associé à l’IHRIM et Fellow au Netherlands Institute for Advanced Study, il mêle recherche universitaire, traductions et écrits grand public. &lt;/p&gt; &lt;p&gt; Ses travaux sur Spinoza insistent sur des "méthodes pour exister" plutôt qu’un système rigide : la théorie des trois genres de connaissance (expérience, raison, intuition) comme outils pratiques de vérification, et une intelligence partagée plutôt que solitaire. Ses différents écrits sont "Le Clan Spinoza" paru en 2017 qui retrace la vie du philosophe et de son entourage comme invention collective de la liberté ; il a retraduit  "l’Éthique" en 2021 avec un millier de notes contextualisées. &lt;/p&gt; &lt;p&gt; Sa pensée originale, inspirée de l’interactionnisme symbolique (Goffman) et étendue à la métaphysique, voit les relations comme circulations multiples et incontrôlables d’attention, d’affects et de tensions. &lt;/p&gt; &lt;p&gt;  Ses ouvrages : -&lt;a href="https://www.youtube.com/watch?v=oApu_IVn7p4"  title="Maxime Rovere - Se vouloir du bien et se faire du mal : philosophie de la dispute par librairie mollat"&gt;"Se vouloir du bien et se faire du mal" &lt;/a&gt; paru en 2021 : philosophie des disputes comme opportunités éthiques. - "Que faire des cons ?"  best-seller de 2019 : guide argotique pour naviguer les conflits sans violence et - &lt;a href="https://www.youtube.com/watch?v=2IGKNQB4bRo" title="Maxime Rovere : "Parler avec sa mère" "est un défi exigeant" par France Inter"&gt;"Parler avec sa mère"  &lt;/a&gt; paru en 2025 est une réflexion cosmique et pythagoricienne sur les liens familiaux. &lt;/p&gt; &lt;audio controls title="Maxime Rovere nous donne les clés de l'amour infini par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/24295-10.05.2024-ITEMA_23737128-2024F51733S0089-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maxime_Rov%C3%A8re"  title=" Wikipedia"&gt;Maxime ROVÈRE&lt;/a&gt;  est un philosophe, écrivain et traducteur français, spécialiste de Spinoza et créateur d’une -&lt;a href="https://www.youtube.com/watch?v=A_4XSOHakEY" title="À l'école des interactions - Maxime Rovere par Revue Esprit"&gt;"philosophie interactionnelle" &lt;/a&gt; qui met l’accent sur les relations humaines dynamiques plutôt que sur des systèmes abstraits. Chercheur associé à l’IHRIM et Fellow au Netherlands Institute for Advanced Study, il mêle recherche universitaire, traductions et écrits grand public. &lt;/p&gt; &lt;p&gt; Ses travaux sur Spinoza insistent sur des "méthodes pour exister" plutôt qu’un système rigide : la théorie des trois genres de connaissance (expérience, raison, intuition) comme outils pratiques de vérification, et une intelligence partagée plutôt que solitaire. Ses différents écrits sont "Le Clan Spinoza" paru en 2017 qui retrace la vie du philosophe et de son entourage comme invention collective de la liberté ; il a retraduit  "l’Éthique" en 2021 avec un millier de notes contextualisées. &lt;/p&gt; &lt;p&gt; Sa pensée originale, inspirée de l’interactionnisme symbolique (Goffman) et étendue à la métaphysique, voit les relations comme circulations multiples et incontrôlables d’attention, d’affects et de tensions. &lt;/p&gt; &lt;p&gt;  Ses ouvrages : &lt;a href="https://www.youtube.com/watch?v=oApu_IVn7p4"  title="Maxime Rovere - Se vouloir du bien et se faire du mal : philosophie de la dispute par librairie mollat"&gt;"Se vouloir du bien et se faire du mal" &lt;/a&gt; paru en 2021 : philosophie des disputes comme opportunités éthiques. "Que faire des cons ?"  best-seller de 2019 : guide argotique pour naviguer les conflits sans violence et &lt;a href="https://www.youtube.com/watch?v=2IGKNQB4bRo" title="Maxime Rovere : "Parler avec sa mère" "est un défi exigeant" par France Inter"&gt;"Parler avec sa mère"  &lt;/a&gt; paru en 2025 est une réflexion cosmique et pythagoricienne sur les liens familiaux. &lt;/p&gt; &lt;audio controls title="Maxime Rovere nous donne les clés de l'amour infini par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/24295-10.05.2024-ITEMA_23737128-2024F51733S0089-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
@@ -5606,7 +5603,7 @@
       <c r="E79" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Baptiste_Jeang%C3%A8ne_Vilmer"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean-Baptiste JEANGENE VILMER&lt;/a&gt;  est un philosophe, politologue et juriste français spécialiste de l’éthique de la guerre, du droit international et des relations internationales, et également diplomate (ambassadeur de France au Vanuatu depuis 2022). Il est formé dans trois disciplines : philosophie (licence, master, doctorat), droit (licence, LLM, postdoctorat) et science politique (doctorat). &lt;/p&gt; &lt;p&gt; Sa thèse porte sur "l’intervention militaire justifiée par des raisons humanitaires", à la croisée de philosophie politique, droit international et théorie des relations internationales. Il défend en théorie des relations internationales un "réalisme libéral" inspiré de Raymond Aron, Stanley Hoffmann et Pierre Hassner : reconnaissance du tragique et des &lt;a href="https://www.youtube.com/watch?v=4EECHNFvt4Q"  title=" J-B. Jeangène Vilmer - Synthèse par Institut Guerre et Paix"&gt;rapports de force, &lt;/a&gt;  mais attachée au droit international, aux droits humains et aux institutions. &lt;/p&gt; &lt;p&gt; Il se situe à l’intersection de philosophie morale, droit international et stratégie : penser les guerres et interventions non seulement en termes juridiques ou militaires, mais surtout en termes de responsabilité morale (tuer, laisser mourir, protéger). Son &lt;a href="https://www.jbjv.com/IMG/pdf/JB_Jeangene_Vilmer_2013_-_Pour_un_realisme_liberal_en_relations_internationales.pdf"  title="Pour un réalisme libéral en relations internationales par jbjv"&gt;"réalisme libéral" &lt;/a&gt; refuse à la fois le cynisme réaliste pur et l’idéalisme naïf, il cherche des critères prudents mais exigeants pour juger les interventions, la justice pénale, ou la responsabilité des États. &lt;/p&gt; &lt;p&gt; Il insiste sur les dilemmes : parfois, intervenir violemment peut sauver des vies, mais peut aussi aggraver le conflit ; parfois, poursuivre les criminels peut fragiliser la paix. Sa pensée explore ces tensions plutôt que de proposer des solutions simplistes. &lt;/p&gt; 
-&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
+  &lt;audio controls title="Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
@@ -5801,7 +5798,7 @@
       <c r="E82" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tristan_Garcia" title=" Wikipedia"&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. &lt;/p&gt; &lt;p&gt; Son œuvre majeure "Forme et objet. Un traité des choses" paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie "plate" qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans "Nous" ou "La Vie intense" paru en 2016, il explore l’appartenance à des collectifs variables "nous humains", "nous animaux" et critique l’obsession moderne pour  &lt;a href="https://www.youtube.com/watch?v=JTLVzryyyEg" title="Tristan Garcia, INTENSITÉ par abc penser"&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (La Meilleure part des hommes, sur le sida) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href="https://www.youtube.com/watch?v=K_wxi5xTYz8" title="Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace"&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; 
- &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Tristan Garcia, "La vie intense : une obsession moderne" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+   &lt;audio controls title="Tristan Garcia, "La vie intense : une obsession moderne" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
  </t>
         </is>
       </c>
@@ -5865,7 +5862,7 @@
       <c r="E83" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gaspard_Koenig" title=" Wikipedia"&gt;Gaspard KOENIG&lt;/a&gt;  est un philosophe français connu pour défendre un libéralisme classique moderne axé sur la liberté individuelle et la réduction des normes administratives. Il étudie initialement Gilles Deleuze avant de découvrir le libéralisme lors d'un séjour à l'université Columbia à New York. Il enseigne comme ATER à Lille-III et travaille comme plume pour Christine Lagarde au ministère de l'Économie, puis à la BERD à Londres. &lt;/p&gt; &lt;p&gt; Fondateur en 2013 du &lt;a href="https://www.youtube.com/watch?v=XmM1deHK-Eo"  title="Génération libre : le think tank, "start-up intellectuelle" par BFM Business"&gt;"think tank Génération Libre", &lt;/a&gt; classé parmi les meilleurs think tanks européens, il en est président et promeut des idées comme le revenu universel (LIBER), la légalisation du cannabis, la propriété des données personnelles et la subsidiarité ascendante. En 2021, il lance le mouvement politique Simple pour  &lt;a href="https://www.youtube.com/watch?v=r6p0dZlUoLQ"  title="Gaspard Koenig : Simplifions radicalement notre administration ! par Contribuables Associés"&gt;diviser par cent les normes &lt;/a&gt; réglementaires ; candidat à la présidentielle 2022, il récolte 107 parrainages. Il se présente aussi aux législatives partielles en 2018. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.gaspardkoenig.com/" title="gaspard koenig - site personnel"&gt;Auteur  d'une quinzaine d'essais &lt;/a&gt; et romans, dont Humus (finaliste Goncourt 2023, prix Interallié), Agrophilosophie (2024) et Time to Philo, il redéfinit la liberté comme "pouvoir sur soi", inspiré par Montaigne, les stoïciens et David Graeber. Ses réflexions touchent l'IA, l'agroécologie, l'éthique et l'économie. Dans &lt;em&gt;La Fin de l’individu&lt;/em&gt; (2019) il s’inquiète de voir les algorithmes décider à notre place et réduire notre capacité de choisir. Avec &lt;em&gt;Humus&lt;/em&gt;, roman sur deux jeunes agronomes et la vie des vers de terre, puis &lt;em&gt;Agrophilosophie&lt;/em&gt;, il s’intéresse aux sols et à l’agriculture, et cherche à concilier la liberté individuelle avec le respect des équilibres naturels. &lt;/p&gt; 
-&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title="Gaspard Koenig, un philosophe en liberté par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-30.09.2023-ITEMA_23504378-2023C49326S0273-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
+  &lt;audio controls title="Gaspard Koenig, un philosophe en liberté par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-30.09.2023-ITEMA_23504378-2023C49326S0273-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -1287,7 +1287,7 @@
       </c>
       <c r="E12" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9gis_Debray" title=" Wikipedia"&gt;Régis DEBRAY&lt;/a&gt; est un  philosophe, écrivain et essayiste, dont le parcours a été marqué par l’engagement politique autant que par la réflexion théorique. Il s’est formé à l’École normale supérieure puis à l’agrégation de philosophie, avant de s’impliquer dans les mouvements révolutionnaires latino-américains, ce qui a durablement orienté sa pensée. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.regisdebray.com/" title="regisdebray"&gt;Sa philosophie &lt;/a&gt; ne se réduit pas à des idées abstraites : elle part souvent du réel, de l’histoire et des formes concrètes de transmission des croyances, des images et des institutions. Il a notamment développé la médiologie, une approche qui étudie comment les messages circulent grâce à des supports matériels et sociaux, et comment ces supports transforment le sens même des idées. &lt;/p&gt; &lt;p&gt; Une autre dimension importante de sa pensée concerne la République, la laïcité et le sacré. Il s’intéresse à ce qui maintient une communauté politique et symbolique, en montrant que les sociétés ont besoin de rites, de frontières, d’institutions et de formes de &lt;a href="https://www.youtube.com/watch?v=YtqETo-7w9g/" title="regis debray par France Inter"&gt;transmission pour durer. &lt;/a&gt;  Il ne pense donc pas la modernité comme une simple libération des cadres anciens, mais comme une transformation de leurs médiations. &lt;/p&gt; &lt;p&gt; Il  est un philosophe du passage entre les idées et leurs conditions matérielles d’existence, entre la politique et la culture, entre le &lt;a href="https://www.youtube.com/watch?v=vKM_P0HCbUs" title="regis debray analyse le pouvoir de l’image par INA Culture"&gt;spirituel et l’institutionnel. &lt;/a&gt; Son œuvre est traversée par une question centrale : comment une société transmet-elle ce qui la fonde, sans perdre ce qu’elle a de commun ? &lt;/p&gt;  &lt;audio controls title=" Régis DEBRAY invité  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22076-10.04.2026-ITEMA_24472004-2026C16450S0100-NET_MFC_C09BCD10-D8F0-42EC-8B3D-61F3DE131622-21-e22a266a3abc5abf79c18e3abcc532cf.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9gis_Debray" title=" Wikipedia"&gt;Régis DEBRAY&lt;/a&gt; est un  philosophe, écrivain et essayiste, dont le parcours a été marqué par l’engagement politique autant que par la réflexion théorique. Il s’est formé à l’École normale supérieure puis à l’agrégation de philosophie, avant de s’impliquer dans les mouvements révolutionnaires latino-américains, ce qui a durablement orienté sa pensée. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.regisdebray.com/" title="regisdebray"&gt;Sa philosophie &lt;/a&gt; ne se réduit pas à des idées abstraites : elle part souvent du réel, de l’histoire et des formes concrètes de transmission des croyances, des images et des institutions. Il a notamment développé la médiologie, une approche qui étudie comment les messages circulent grâce à des supports matériels et sociaux, et comment ces supports transforment le sens même des idées. &lt;/p&gt; &lt;p&gt; Une autre dimension importante de sa pensée concerne la République, la laïcité et le sacré. Il s’intéresse à ce qui maintient une communauté politique et symbolique, en montrant que les sociétés ont besoin de rites, de frontières, d’institutions et de formes de &lt;a href="https://www.youtube.com/watch?v=YtqETo-7w9g" title="regis debray par France Inter"&gt;transmission pour durer. &lt;/a&gt;  Il ne pense donc pas la modernité comme une simple libération des cadres anciens, mais comme une transformation de leurs médiations. &lt;/p&gt; &lt;p&gt; Il  est un philosophe du passage entre les idées et leurs conditions matérielles d’existence, entre la politique et la culture, entre le &lt;a href="https://www.youtube.com/watch?v=vKM_P0HCbUs" title="regis debray analyse le pouvoir de l’image par INA Culture"&gt;spirituel et l’institutionnel. &lt;/a&gt; Son œuvre est traversée par une question centrale : comment une société transmet-elle ce qui la fonde, sans perdre ce qu’elle a de commun ? &lt;/p&gt;  &lt;audio controls title=" Régis DEBRAY invité  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22076-10.04.2026-ITEMA_24472004-2026C16450S0100-NET_MFC_C09BCD10-D8F0-42EC-8B3D-61F3DE131622-21-e22a266a3abc5abf79c18e3abcc532cf.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="E29" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Godin"   title=" Wikipedia"&gt;Christian GODIN&lt;/a&gt;  est un philosophe français qui a enseigné la philosophie à l’université Blaise-Pascal de Clermont-Ferrand, où il est devenu professeur émérite, et collabore régulièrement à des revues comme Marianne, Le Magazine littéraire et Sciences et Avenir. Il dirige également la revue Cités aux PUF et s’est imposé comme  &lt;a href="http://www.christian-godin.com/biographie.html"  title="autobiographie par c godin"&gt; un auteur prolifique, &lt;/a&gt; avec plus d’une cinquantaine d’ouvrages à caractère pédagogique et érudit. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour son monumental travail « La Totalité en sept volumes » (1997-2003), fruit de sa thèse de doctorat, qui explore la notion philosophique de totalité à travers l’histoire de la pensée. Parmi ses autres travaux phares figurent des ouvrages de vulgarisation comme  &lt;a href="https://www.youtube.com/watch?v=nJga6GYNLUw"  title="Ephilosophie pour les nuls par Google payer livres"&gt; La Philosophie pour les nuls &lt;/a&gt; (2006), des dictionnaires philosophiques et des essais contemporains tels que La crise de la réalité (2021), où il analyse la destitution du réel par le numérique et les idéologies modernes. Il a aussi réalisé des entretiens avec des penseurs comme Axel Kahn ou Malek Chebel.  &lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est avant tout « un désir de comprendre le monde, de donner du sens, d’expliquer les choses », et elle doit rester ancrée dans le concret pour éviter l’abstraction stérile. Il insiste sur son rôle pédagogique et accessible à tous, invitant à dialoguer avec les grands penseurs comme Platon, Nietzsche ou Hannah Arendt pour aborder des thèmes universels : le sens de la vie, l’amour, la mort. Contrairement à la science focalisée sur la vérité, la philosophie cherche le sens via la critique, le débat intérieur et l’examen des  &lt;a href="https://www.youtube.com/watch?v=8KzIKZimPSIl"  title="Etre humain par Philomonaco"&gt; problèmes humains. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il aborde des enjeux actuels comme la crise de la réalité (présentisme, simulationnisme, prédictionnisme), la synchronicité comme signe d’unité divine échappant à la raison, ou la démoralisation contemporaine. Il critique le subjectivisme relativiste, le narcissisme numérique et la technoscience totalitaire qui substitue un monde artificiel à la nature, plaidant pour une pensée multidimensionnelle du réel. Ses analyses, souvent pessimistes sur la virtualité et la post-vérité, défendent une objectivité ancrée dans le monde physique. &lt;/p&gt;     &lt;audio controls title="Le philosophe Christian Godin tire les leçons du Grand Débat " par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15343-18.03.2019-ITEMA_22011803-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Godin"   title=" Wikipedia"&gt;Christian GODIN&lt;/a&gt;  est un philosophe français qui a enseigné la philosophie à l’université Blaise-Pascal de Clermont-Ferrand, où il est devenu professeur émérite, et collabore régulièrement à des revues comme Marianne, Le Magazine littéraire et Sciences et Avenir. Il dirige également la revue Cités aux PUF et s’est imposé comme  &lt;a href="http://www.christian-godin.com/biographie.html"  title="autobiographie par c godin"&gt; un auteur prolifique, &lt;/a&gt; avec plus d’une cinquantaine d’ouvrages à caractère pédagogique et érudit. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour son monumental travail « La Totalité en sept volumes » (1997-2003), fruit de sa thèse de doctorat, qui explore la notion philosophique de totalité à travers l’histoire de la pensée. Parmi ses autres travaux phares figurent des ouvrages de vulgarisation comme  &lt;a href="https://www.youtube.com/watch?v=nJga6GYNLUw"  title="Ephilosophie pour les nuls par Google payer livres"&gt; La Philosophie pour les nuls &lt;/a&gt; (2006), des dictionnaires philosophiques et des essais contemporains tels que La crise de la réalité (2021), où il analyse la destitution du réel par le numérique et les idéologies modernes. Il a aussi réalisé des entretiens avec des penseurs comme Axel Kahn ou Malek Chebel.  &lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est avant tout « un désir de comprendre le monde, de donner du sens, d’expliquer les choses », et elle doit rester ancrée dans le concret pour éviter l’abstraction stérile. Il insiste sur son rôle pédagogique et accessible à tous, invitant à dialoguer avec les grands penseurs comme Platon, Nietzsche ou Hannah Arendt pour aborder des thèmes universels : le sens de la vie, l’amour, la mort. Contrairement à la science focalisée sur la vérité, la philosophie cherche le sens via la critique, le débat intérieur et l’examen des  &lt;a href="https://www.youtube.com/watch?v=8KzIKZimPSI"  title="Etre humain par Philomonaco"&gt; problèmes humains. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il aborde des enjeux actuels comme la crise de la réalité (présentisme, simulationnisme, prédictionnisme), la synchronicité comme signe d’unité divine échappant à la raison, ou la démoralisation contemporaine. Il critique le subjectivisme relativiste, le narcissisme numérique et la technoscience totalitaire qui substitue un monde artificiel à la nature, plaidant pour une pensée multidimensionnelle du réel. Ses analyses, souvent pessimistes sur la virtualité et la post-vérité, défendent une objectivité ancrée dans le monde physique. &lt;/p&gt;     &lt;audio controls title="Le philosophe Christian Godin tire les leçons du Grand Débat " par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15343-18.03.2019-ITEMA_22011803-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -3215,7 +3215,7 @@
       </c>
       <c r="E42" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard"  title=" Wikipedia"&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J.G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime un séminaire sur les décolonisations avec l'Université de Louvain-la-Neuve. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href="https://www.youtube.com/watch?v=vEQWmSo67B4" style="color:#88A1E9" title="Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches"&gt;"Ce sont d'autres gens" &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la "qualité de la vie" sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href="https://www.youtube.com/watch?v=ZDpbSRrWIhU" title="Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées"&gt;"autre monde" &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;    &lt;audio controls title="Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard"  title=" Wikipedia"&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J. G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime avec Marc Maesschalck le séminaire « Penser les décolonisations », commun aux universités de Toulouse et de Louvain-la-Neuve. Il organise aussi, avec le chorégraphe James Carlès, le festival Corpus Africana de Toulouse, et participe depuis 2019 à un séminaire d’anthropologie décoloniale à l’université nationale de Séoul. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href="https://www.youtube.com/watch?v=vEQWmSo67B4" style="color:#88A1E9" title="Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches"&gt;"Ce sont d'autres gens" &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la "qualité de la vie" sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href="https://www.youtube.com/watch?v=ZDpbSRrWIhU" title="Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées"&gt;"autre monde" &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;    &lt;audio controls title="Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F42" s="34" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="E77" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9verine_Kodjo-Grandvaux"  title=" Wikipedia"&gt;Séverine KODJO-GRANDVAUX&lt;/a&gt; est une philosophe, journaliste, programmatrice littéraire et  &lt;a href="https://www.jeuneafrique.com/auteurs/s-kodjo-grandvaux/"  title="Ses dernières publications par jeuneafrique"&gt;éditrice française &lt;/a&gt; principalement reconnue pour ses travaux sur les philosophies africaines contemporaines et les études postcoloniales. Elle occupe une position de chercheure associée au Laboratoire des logiques contemporaines de la philosophie à l’Université Paris 8, et elle est impliquée dans des initiatives autour des humanités africaines et des échanges intellectuels entre l’Afrique et le monde francophone. &lt;/p&gt; &lt;p&gt; En 2013, elle publie &lt;a href="https://www.youtube.com/watch?v=w8pfqdnej-o" title="African Philosophies I Lecture by philosopher Séverine Kodjo-Grandvaux par Radboud Reflects"&gt;"Philosophies africaines", &lt;/a&gt; ouvrage qui est considéré comme une référence majeure dans le domaine et qui analyse en profondeur les courants et les enjeux de la philosophie africaine contemporaine. Elle publie ensuite  &lt;a href="https://www.youtube.com/watch?v=AJAz1OmcVbI" title=""Devenir Vivants" avec Séverine Kodjo-Grandvaux. Extrait du podcast Afrotopiques par Génération Afrotopia"&gt;"Devenir vivants" &lt;/a&gt; et "Droit et colonisation"  — œuvre collective sur les rapports entre droit et colonialisme, témoignant d’un engagement dans les études postcoloniales et juridiques. &lt;/p&gt; &lt;p&gt; Ce qui la distingue dans le paysage philosophique français, c'est sa capacité à faire dialoguer les philosophies africaines avec les enjeux contemporains globaux, notamment écologiques et postcoloniaux. Elle contribue à décentrer la pensée philosophique de son eurocentrisme traditionnel tout en proposant des outils conceptuels originaux pour penser notre relation au vivant et au cosmos.&lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9verine_Kodjo-Grandvaux"  title=" Wikipedia"&gt;Séverine KODJO-GRANDVAUX&lt;/a&gt; est une philosophe, journaliste, programmatrice littéraire et  &lt;a href="https://www.jeuneafrique.com/auteurs/s-kodjo-grandvaux/"  title="Ses dernières publications par jeuneafrique"&gt;éditrice française &lt;/a&gt; principalement reconnue pour ses travaux sur les philosophies africaines contemporaines et les études postcoloniales. Elle occupe une position de chercheure associée au Laboratoire des logiques contemporaines de la philosophie à l’Université Paris 8, et elle est impliquée dans des initiatives autour des humanités africaines et des échanges intellectuels entre l’Afrique et le monde francophone. Née à Besançon en 1977, elle a consacré sa thèse (2006) à l’idée de « philosophie africaine » chez Jean-Godefroy Bidima, Souleymane Bachir Diagne, Henry Odera Oruka et Kwasi Wiredu. Journaliste pour &lt;em&gt;Le Monde&lt;/em&gt;, elle dirige aussi la collection « Essais » des éditions Jimsaan. &lt;/p&gt; &lt;p&gt; En 2013, elle publie &lt;a href="https://www.youtube.com/watch?v=w8pfqdnej-o" title="African Philosophies I Lecture by philosopher Séverine Kodjo-Grandvaux par Radboud Reflects"&gt;"Philosophies africaines", &lt;/a&gt; ouvrage qui est considéré comme une référence majeure dans le domaine et qui analyse en profondeur les courants et les enjeux de la philosophie africaine contemporaine. Elle publie ensuite  &lt;a href="https://www.youtube.com/watch?v=AJAz1OmcVbI" title=""Devenir Vivants" avec Séverine Kodjo-Grandvaux. Extrait du podcast Afrotopiques par Génération Afrotopia"&gt;"Devenir vivants" &lt;/a&gt; et "Droit et colonisation"  — œuvre collective sur les rapports entre droit et colonialisme, témoignant d’un engagement dans les études postcoloniales et juridiques. &lt;/p&gt; &lt;p&gt; Ce qui la distingue dans le paysage philosophique français, c'est sa capacité à faire dialoguer les philosophies africaines avec les enjeux contemporains globaux, notamment écologiques et postcoloniaux. Elle contribue à décentrer la pensée philosophique de son eurocentrisme traditionnel tout en proposant des outils conceptuels originaux pour penser notre relation au vivant et au cosmos.&lt;/p&gt;
    &lt;audio controls title="Philosophie Africaine par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12016-15.04.2013-ITEMA_20470144-2013C18044S0105-NET_FC_590A75DA-F57B-40F9-88DF-1D448D87542C-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -4568,7 +4568,7 @@
       </c>
       <c r="E63" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Monod"  title=" Wikipedia"&gt;Jean Claude MONOD&lt;/a&gt; est un philosophe français  contemporain, spécialiste de philosophie politique et de philosophie allemande des XIXe et XXe siècles, en particulier de la question de la sécularisation et des rapports entre religion, modernité et démocratie. &lt;/p&gt; &lt;p&gt;  Un axe central de sa réflexion est de comment comprendre la modernité sans la réduire à une simple transposition de catégories religieuses, et comment penser  &lt;a href="https://www.youtube.com/watch?v=E111pSvCT8g"  title="
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Monod"  title=" Wikipedia"&gt;Jean Claude MONOD&lt;/a&gt; est un philosophe français  contemporain, spécialiste de philosophie politique et de philosophie allemande des XIXe et XXe siècles, en particulier de la question de la sécularisation et des rapports entre religion, modernité et démocratie. Ancien élève de l’École normale supérieure, chercheur au CNRS aux Archives Husserl, il a aussi publié &lt;em&gt;Qu’est-ce qu’un chef en démocratie ?&lt;/em&gt; (2012), sur le charisme politique. &lt;/p&gt; &lt;p&gt;  Un axe central de sa réflexion est de comprendre la modernité sans la réduire à une simple transposition de catégories religieuses, et de penser  &lt;a href="https://www.youtube.com/watch?v=E111pSvCT8g"  title="
 Jean-Claude Monod - L'art de ne pas être trop gouverné par librairie mollat"&gt;le théologico-politique&lt;/a&gt;  aujourd’hui. Il s’intéresse aussi aux formes contemporaines du pouvoir (crises de l’État libéral, charisme politique, crises de gouvernementalité, néolibéralisme autoritaire) et aux tensions entre démocratie, vérité et fake news. &lt;/p&gt; &lt;p&gt; Dans son ouvrage : &lt;a href="https://www.gregoiredetours.fr/thematiques/religions/jean-claude-monod-secularisation-et-laicite/"  title="
 Jean-Claude Monod -  "La Querelle de la sécularisation" par gregoire de tours"&gt; "La Querelle de la sécularisation"&lt;/a&gt; : Théologies politiques et philosophies de l’Histoire, de Hegel à Blumenberg (Vrin) : analyse des grands débats sur la sécularisation et la modernité, avec une attention particulière à Blumenberg. &lt;/p&gt; &lt;p&gt;"Penser l’ennemi, affronter l’exception" : Réflexions critiques sur l’actualité de Carl Schmitt (La Découverte) : lecture critique de Schmitt et de la notion d’exception dans les démocraties contemporaines.&lt;/p&gt; &lt;p&gt; Il intervient régulièrement dans les médias et dans des conférences sur la démocratie, l’extrême droite, la crise de l’État et les transformations du néolibéralisme, où il défend une analyse fine des liens entre pouvoir, autorité et contestation. &lt;/p&gt; 
   &lt;audio controls title="L'intellectuel peut-il encore exister au XXIe siècle ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/25951-29.11.2025-ITEMA_24326903-2025C54596S0333-NET_MFC_C2F18604-F792-44E5-803E-E62225C653B4-25-bf7dbc88816a940ebe2dc58d15ae6341.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="E82" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tristan_Garcia" title=" Wikipedia"&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. &lt;/p&gt; &lt;p&gt; Son œuvre majeure "Forme et objet. Un traité des choses" paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie "plate" qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans "Nous" ou "La Vie intense" paru en 2016, il explore l’appartenance à des collectifs variables "nous humains", "nous animaux" et critique l’obsession moderne pour  &lt;a href="https://www.youtube.com/watch?v=JTLVzryyyEg" title="Tristan Garcia, INTENSITÉ par abc penser"&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (La Meilleure part des hommes, sur le sida) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href="https://www.youtube.com/watch?v=K_wxi5xTYz8" title="Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace"&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tristan_Garcia" title=" Wikipedia"&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. Ancien élève de l’École normale supérieure, il enseigne la philosophie à l’université Jean-Moulin-Lyon-3. &lt;/p&gt; &lt;p&gt; Son œuvre majeure "Forme et objet. Un traité des choses" paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie "plate" qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans "Nous" ou "La Vie intense" paru en 2016, il explore l’appartenance à des collectifs variables "nous humains", "nous animaux" et critique l’obsession moderne pour  &lt;a href="https://www.youtube.com/watch?v=JTLVzryyyEg" title="Tristan Garcia, INTENSITÉ par abc penser"&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. Son roman &lt;em&gt;7&lt;/em&gt; reçoit en 2016 le prix du Livre Inter. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (&lt;em&gt;La Meilleure Part des hommes&lt;/em&gt;, sur les années sida, prix de Flore 2008) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href="https://www.youtube.com/watch?v=K_wxi5xTYz8" title="Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace"&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; 
    &lt;audio controls title="Tristan Garcia, "La vie intense : une obsession moderne" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
  </t>
         </is>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -4696,7 +4696,7 @@
       </c>
       <c r="E65" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Stiegler" title=" Wikipedia"&gt;Barbara STIEGLER&lt;/a&gt; (née en 1971) est une philosophe française, spécialiste de Nietzsche et de philosophie politique, connue pour sa critique du néolibéralisme. Fille du philosophe Bernard Stiegler, agrégée de philosophie, elle est professeure à l’université Bordeaux-Montaigne, où elle a dirigé le master &lt;a href="https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf" title="Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne"&gt;« Soin, éthique et santé »&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Ses premiers travaux portent sur Nietzsche et la biologie de son temps. Dans &lt;em&gt;Nietzsche et la biologie&lt;/em&gt; (2001) et &lt;em&gt;Nietzsche et la critique de la chair&lt;/em&gt; (2005), elle montre que la pensée de Nietzsche dialogue avec les sciences du vivant, et que le corps et la vie y sont des notions centrales. Elle se tourne ensuite vers la philosophie politique. Dans &lt;a href="https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/" title="Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit"&gt;&lt;em&gt;« Il faut s’adapter »&lt;/em&gt;&lt;/a&gt; (2019), elle remonte aux origines du &lt;a href="https://www.youtube.com/watch?v=oQQ4xqRvYTk" style="color:#88A1E9" title="LA LENTE AGONIE DU NÉOLIBÉRALISME  par 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Stiegler" title=" Wikipedia"&gt;Barbara STIEGLER&lt;/a&gt; (née en 1971) est une philosophe française, spécialiste de Nietzsche et de philosophie politique, connue pour sa critique du néolibéralisme. Fille du philosophe Bernard Stiegler, agrégée de philosophie, elle est professeure à l’université Bordeaux-Montaigne, où elle a dirigé le master « Soin, éthique et santé ».&lt;/p&gt; &lt;p&gt;Ses premiers travaux portent sur Nietzsche et la biologie de son temps. Dans &lt;em&gt;Nietzsche et la biologie&lt;/em&gt; (2001) et &lt;em&gt;Nietzsche et la critique de la chair&lt;/em&gt; (2005), elle montre que la pensée de Nietzsche dialogue avec les sciences du vivant, et que le corps et la vie y sont des notions centrales. Elle se tourne ensuite vers la philosophie politique. Dans &lt;a href="https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/" title="Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit"&gt;&lt;em&gt;« Il faut s’adapter »&lt;/em&gt;&lt;/a&gt; (2019), elle remonte aux origines du &lt;a href="https://www.youtube.com/watch?v=oQQ4xqRvYTk" style="color:#88A1E9" title="LA LENTE AGONIE DU NÉOLIBÉRALISME  par 
 TheSwissBox Conversation"&gt;néolibéralisme&lt;/a&gt; : au début du XXe siècle, le journaliste américain Walter Lippmann, inspiré par une lecture de la théorie de l’évolution, soutenait que les peuples, en retard sur un monde qui change trop vite, devaient être adaptés par des experts au nouvel environnement mondialisé. Contre lui, le philosophe John Dewey défendait une démocratie fondée sur l’intelligence collective et la participation des citoyens. Barbara Stiegler montre que ce débat oublié éclaire nos sociétés, où l’injonction à s’adapter s’impose à l’école, au travail et dans la santé. Elle a ensuite appliqué ces analyses aux mouvements sociaux, dans &lt;em&gt;Du cap aux grèves&lt;/em&gt; (2020), puis à la crise de la covid, dans &lt;em&gt;De la démocratie en pandémie&lt;/em&gt; (2021).&lt;/p&gt; &lt;p&gt;Engagée dans le débat public, elle plaide pour une démocratie plus participative et pour une autre conception de la santé publique.&lt;/p&gt;  &lt;audio controls title="La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -1016,57 +1016,55 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="159" customHeight="1" s="28">
+    <row r="8" ht="152.25" customHeight="1" s="28">
       <c r="A8" s="34" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B8" s="34" t="n"/>
       <c r="C8" s="34" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>Éliane ESCOUBAS</t>
-        </is>
-      </c>
-      <c r="E8" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89liane_Escoubas"  style="color:#6A142A"  title=" Wikipedia"&gt;Éliane ESCOUBAS&lt;/a&gt;  est une philosophe française, historienne de la philosophie et traductrice. Elle qui se rattache à l’école phénoménologique et travaille principalement sur la philosophie allemande, la phénoménologie de l’art et la psychiatrie phénoménologique, dite Daseinsanalyse. Après une formation marquée par les cours de Gérard Granel sur Husserl, Kant et Hegel à Toulouse, elle enseigne dans le secondaire puis devient maître de conférences, puis professeur de philosophie, tout en menant des recherches au CNRS et en participant à la création du Collège international de Philosophie. &lt;/p&gt; &lt;p&gt; Elle met au centre la phénoménologie de l’expérience sensible, en particulier la manière dont le monde et le sujet adviennent à travers le sentir, l’affect et la perception. Elle montre que la phénoménologie fournit un prisme particulièrement adapté pour penser l’esthétique, car l’œuvre d’art apparaît comme un mode privilégié pour saisir comment le sujet et le monde se co‑constituent dans une expérience sensible et existentielle. &lt;/p&gt; &lt;p&gt; Une grande partie de son œuvre est consacrée à une « esthétique du sentir » où l’art n’est pas seulement une illustration de la philosophie, mais un mode de connaissance autonome. Dans ses travaux comme Imago mundi. Topologie de l’art ou L’invention de l’art, elle montre que l’image et l’œuvre picturale ne se réduisent pas à « représentation » ou « signe », mais relèvent d’une apparition du monde lui‑même, d’une spatialité et d’une temporalité qui précèdent les catégories classiques de l’objet. &lt;/p&gt; &lt;p&gt; Sa philosophie s’ouvre aussi à la phénoménologie clinique et à la psychiatrie, notamment à travers la Daseinsanalyse et la place de l’affect et de l’affectivité dans la constitution du sujet. En explorant les affectivités dans la modernité et la phénoménologie, Escoubas prolonge ainsi une réflexion sur la manière dont le vécu, le corps et la subjectivité forment un champ de savoir propre, à la fois esthétique, analytique et existentiel. &lt;/p&gt;  &lt;audio controls title="Alain BADIOU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-25.11.2011-ITEMA_20320112-2011C3403E0190-ITE_00047070_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
-        </is>
-      </c>
-      <c r="F8" s="34" t="n"/>
-      <c r="G8" s="36" t="n"/>
+          <t>Pierre MACHEREY</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Macherey"   title=" Wikipedia"&gt;Pierre MACHEREY&lt;/a&gt;  est un philosophe français  proche de Louis Althusser, et l’une des figures importantes du &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_1977_num_41_1_1858" title="marxisme et structuralisme par persée"&gt;marxisme structuraliste &lt;/a&gt; et de la théorie littéraire en France. Son travail a beaucoup compté pour la philosophie continentale, surtout à travers ses lectures de Spinoza et ses analyses du lien &lt;a href="https://www.youtube.com/watch?v=DjawaCnhaps" title="Pierre Macherey Proust , entre littérature et philosophie par Virginie Chretien"&gt; entre philosophie, littérature &lt;/a&gt; et idéologie. &lt;/p&gt; &lt;p&gt;   Sa philosophie part d’une idée simple mais exigeante : on ne pense jamais hors des conditions historiques et sociales dans lesquelles on vit. Il voit la philosophie comme une pratique conjoncturelle, c’est-à-dire capable d’éclairer une situation pour mieux intervenir sur elle et, à terme, contribuer à sa transformation. Cette approche le distingue d’une philosophie qui prétendrait atteindre des vérités abstraites, détachées du réel. &lt;/p&gt; &lt;p&gt; Un autre axe central de son œuvre est Spinoza. Il s’est servi de Spinoza pour penser la nécessité, la puissance, les affects et la liberté autrement qu’en termes de sujet souverain ou de conscience transparente. Chez lui, la liberté ne consiste pas à échapper aux déterminations, mais à comprendre les conditions qui nous traversent afin d’agir plus lucidement dans le monde. &lt;/p&gt; &lt;p&gt; Il  a renouvelé la  &lt;a href="https://www.persee.fr/doc/roman_0048-8593_1991_num_21_72_5776" title="Pierre Macherey a quoi pense la littérature par persée"&gt; critique littéraire &lt;/a&gt; en refusant de faire de la littérature une simple illustration d’idées philosophiques. Il montre que les œuvres produisent leur propre pensée, à travers leurs formes, leurs silences et leurs écarts, et qu’il faut lire ces structures plutôt que chercher un “message” caché. En ce sens, sa philosophie est à la fois politique, littéraire et rigoureusement attentive aux textes, ce qui en fait un penseur discret mais très influent. &lt;/p&gt;     &lt;audio controls title="Actualité philo : Pierre Macherey par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-07.02.2014-ITEMA_20585549-2014C12410E0044-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>gGldhco-JcY</t>
+        </is>
+      </c>
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>"La raison et les normes - conférence Pierre Macherey" par NormezMoi</t>
+        </is>
+      </c>
       <c r="H8" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/eescoubas-mini.webp</t>
-        </is>
-      </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t>https://laphilo.fr/photo/escoubas.webp</t>
-        </is>
-      </c>
+          <t>https://www.laphilo.fr/pho/pmacherey-mini.webp</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="n"/>
       <c r="J8" s="27" t="inlineStr">
         <is>
-          <t>esthetique ; epistemologie</t>
+          <t>epistemologie ; politique</t>
         </is>
       </c>
       <c r="K8" s="27" t="inlineStr">
         <is>
-          <t>Phénoménologie</t>
+          <t>Marxisme ; Structuralisme</t>
         </is>
       </c>
       <c r="L8" s="27" t="inlineStr">
         <is>
-          <t>philosophe française, historienne de la philosophie et traductrice.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français figure du marxisme structuraliste et de la théorie littéraire.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1076,11 +1074,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">art</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="152.25" customHeight="1" s="28">
+          <t xml:space="preserve">continental ; critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="165.75" customHeight="1" s="28">
       <c r="A9" s="34" t="n">
         <v>1938</v>
       </c>
@@ -1092,43 +1090,48 @@
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>Pierre MACHEREY</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Macherey"   title=" Wikipedia"&gt;Pierre MACHEREY&lt;/a&gt;  est un philosophe français  proche de Louis Althusser, et l’une des figures importantes du &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_1977_num_41_1_1858" title="marxisme et structuralisme par persée"&gt;marxisme structuraliste &lt;/a&gt; et de la théorie littéraire en France. Son travail a beaucoup compté pour la philosophie continentale, surtout à travers ses lectures de Spinoza et ses analyses du lien &lt;a href="https://www.youtube.com/watch?v=DjawaCnhaps" title="Pierre Macherey Proust , entre littérature et philosophie par Virginie Chretien"&gt; entre philosophie, littérature &lt;/a&gt; et idéologie. &lt;/p&gt; &lt;p&gt;   Sa philosophie part d’une idée simple mais exigeante : on ne pense jamais hors des conditions historiques et sociales dans lesquelles on vit. Il voit la philosophie comme une pratique conjoncturelle, c’est-à-dire capable d’éclairer une situation pour mieux intervenir sur elle et, à terme, contribuer à sa transformation. Cette approche le distingue d’une philosophie qui prétendrait atteindre des vérités abstraites, détachées du réel. &lt;/p&gt; &lt;p&gt; Un autre axe central de son œuvre est Spinoza. Il s’est servi de Spinoza pour penser la nécessité, la puissance, les affects et la liberté autrement qu’en termes de sujet souverain ou de conscience transparente. Chez lui, la liberté ne consiste pas à échapper aux déterminations, mais à comprendre les conditions qui nous traversent afin d’agir plus lucidement dans le monde. &lt;/p&gt; &lt;p&gt; Il  a renouvelé la  &lt;a href="https://www.persee.fr/doc/roman_0048-8593_1991_num_21_72_5776" title="Pierre Macherey a quoi pense la littérature par persée"&gt; critique littéraire &lt;/a&gt; en refusant de faire de la littérature une simple illustration d’idées philosophiques. Il montre que les œuvres produisent leur propre pensée, à travers leurs formes, leurs silences et leurs écarts, et qu’il faut lire ces structures plutôt que chercher un “message” caché. En ce sens, sa philosophie est à la fois politique, littéraire et rigoureusement attentive aux textes, ce qui en fait un penseur discret mais très influent. &lt;/p&gt;     &lt;audio controls title="Actualité philo : Pierre Macherey par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-07.02.2014-ITEMA_20585549-2014C12410E0044-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t>Anne FAGOT-LARGEAULT</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Fagot-Largeault"  title=" Wikipedia"&gt;Anne FAGOT-LARGEAULT&lt;/a&gt;  est une philosophe et psychiatre française, élève de l’École normale supérieure de jeunes filles, agrégée de philosophie en 1961, elle a combiné une carrière académique brillante – professeur à Paris 1 Panthéon-Sorbonne puis au Collège de France (chaire de philosophie des sciences biologiques et médicales de 2000 à 2009) – avec une pratique hospitalière en psychiatrie à l’hôpital Henri-Mondor de Créteil. Membre de l’Académie des sciences depuis 2002, elle incarne une figure rare à la croisée de la médecine, de la philosophie et des sciences du vivant. &lt;/p&gt; &lt;p&gt;  Sa philosophie se déploie dans trois &lt;a href="https://www.youtube.com/watch?v=LYwHBFs7elQ" title=" Philosophie des sciences biologiques et médicales et philosophie par Collège de France"&gt; directions principales, &lt;/a&gt; toutes liées à l’épistémologie et à l’ontologie des sciences biologiques et médicales. D’abord, elle analyse le raisonnement diagnostique : logique inductive, probabilités, heuristiques, en soulignant les limites de la certitude dans un domaine probabiliste par nature. Ensuite, elle interroge la causalité : distinction entre causalité mécanique et téléologique, preuves épidémiologiques, rôle des modèles explicatifs dans la compréhension du vivant. Enfin, elle s’attache à l’éthique : méthodologie des essais cliniques, dilemmes bioéthiques, responsabilité dans un univers contingent où l’humain influence activement l’avenir. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages comme Ontologie du devenir ou Médecine et philosophie, elle revisite les thèmes du temps, de l’évolution et du vivant en dialogue avec Héraclite, Bergson ou les sciences modernes. Elle défend une science du devenir contre l’immobilisme parmnénidien : le flux permanent du réel exige des concepts fluides, une intuition intellectuelle capable de saisir l’instabilité des êtres vivants sans les figer en essences. L’évolution darwinienne, loin d’être une téléologie, révèle un univers de contingences où l’action humaine porte une responsabilité prospective. &lt;/p&gt; &lt;p&gt;     &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2016_hos_114_1_8513" title=" laudatio de la professeure par persée"&gt; Son apport &lt;/a&gt; le plus original réside dans une anthropologie bio-médicale qui refuse le réductionnisme : la médecine suppose une métaphysique du mal, une épistémologie du normal/pathologique et une éthique équilibrant l’autonomie individuelle, le bien du patient et l’intérêt collectif. Professeure honoraire influente, elle a formé des générations à penser la vie non comme un donné stable, mais comme un processus à comprendre et à orienter éthiquement.&lt;/p&gt;                                                                      &lt;audio controls title="Médecine et philosophie avec Anne Fagot-Largeault par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10201-08.03.2010-ITEMA_20218761-2010C10593E0008-NET_01E69962-F316-4C45-826B-43707F9BD385_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>gGldhco-JcY</t>
+          <t>XBD5SuIsnIg</t>
         </is>
       </c>
       <c r="G9" s="36" t="inlineStr">
         <is>
-          <t>"La raison et les normes - conférence Pierre Macherey" par NormezMoi</t>
+          <t>"Anne Fagot Largeault Médecine et Philosophie" par Socohade</t>
         </is>
       </c>
       <c r="H9" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/pmacherey-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/aflargault-mini.webp</t>
         </is>
       </c>
       <c r="I9" s="36" t="n"/>
       <c r="J9" s="27" t="inlineStr">
         <is>
-          <t>epistemologie ; politique</t>
+          <t>epistemologie ; ethique</t>
         </is>
       </c>
       <c r="K9" s="27" t="inlineStr">
         <is>
-          <t>Marxisme ; Structuralisme</t>
+          <t>Analytique ; Positivisme Logique</t>
         </is>
       </c>
       <c r="L9" s="27" t="inlineStr">
         <is>
-          <t>philosophe français figure du marxisme structuraliste et de la théorie littéraire.</t>
+          <t>philosophe française à la croisée de la médecine, la philosophie et les sciences du vivant.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1138,64 +1141,60 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental ; critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="165.75" customHeight="1" s="28">
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="147.75" customHeight="1" s="28">
       <c r="A10" s="34" t="n">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="B10" s="34" t="n"/>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
-          <t>Anne FAGOT-LARGEAULT</t>
-        </is>
-      </c>
-      <c r="E10" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Fagot-Largeault"  title=" Wikipedia"&gt;Anne FAGOT-LARGEAULT&lt;/a&gt;  est une philosophe et psychiatre française, élève de l’École normale supérieure de jeunes filles, agrégée de philosophie en 1961, elle a combiné une carrière académique brillante – professeur à Paris 1 Panthéon-Sorbonne puis au Collège de France (chaire de philosophie des sciences biologiques et médicales de 2000 à 2009) – avec une pratique hospitalière en psychiatrie à l’hôpital Henri-Mondor de Créteil. Membre de l’Académie des sciences depuis 2002, elle incarne une figure rare à la croisée de la médecine, de la philosophie et des sciences du vivant. &lt;/p&gt; &lt;p&gt;  Sa philosophie se déploie dans trois &lt;a href="https://www.youtube.com/watch?v=LYwHBFs7elQ" title=" Philosophie des sciences biologiques et médicales et philosophie par Collège de France"&gt; directions principales, &lt;/a&gt; toutes liées à l’épistémologie et à l’ontologie des sciences biologiques et médicales. D’abord, elle analyse le raisonnement diagnostique : logique inductive, probabilités, heuristiques, en soulignant les limites de la certitude dans un domaine probabiliste par nature. Ensuite, elle interroge la causalité : distinction entre causalité mécanique et téléologique, preuves épidémiologiques, rôle des modèles explicatifs dans la compréhension du vivant. Enfin, elle s’attache à l’éthique : méthodologie des essais cliniques, dilemmes bioéthiques, responsabilité dans un univers contingent où l’humain influence activement l’avenir. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages comme Ontologie du devenir ou Médecine et philosophie, elle revisite les thèmes du temps, de l’évolution et du vivant en dialogue avec Héraclite, Bergson ou les sciences modernes. Elle défend une science du devenir contre l’immobilisme parmnénidien : le flux permanent du réel exige des concepts fluides, une intuition intellectuelle capable de saisir l’instabilité des êtres vivants sans les figer en essences. L’évolution darwinienne, loin d’être une téléologie, révèle un univers de contingences où l’action humaine porte une responsabilité prospective. &lt;/p&gt; &lt;p&gt;     &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2016_hos_114_1_8513" title=" laudatio de la professeure par persée"&gt; Son apport &lt;/a&gt; le plus original réside dans une anthropologie bio-médicale qui refuse le réductionnisme : la médecine suppose une métaphysique du mal, une épistémologie du normal/pathologique et une éthique équilibrant l’autonomie individuelle, le bien du patient et l’intérêt collectif. Professeure honoraire influente, elle a formé des générations à penser la vie non comme un donné stable, mais comme un processus à comprendre et à orienter éthiquement.&lt;/p&gt;                                                                      &lt;audio controls title="Médecine et philosophie avec Anne Fagot-Largeault par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10201-08.03.2010-ITEMA_20218761-2010C10593E0008-NET_01E69962-F316-4C45-826B-43707F9BD385_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">Jacques RANCIÈRE</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Ranci%C3%A8re" title=" Wikipedia"&gt;Jacques RANCIERE&lt;/a&gt; est un philosophe français connu pour une pensée qui articule politique, histoire, esthétique et éducation autour de l’idée d’émancipation de n’importe qui. Il est aujourd’hui l’une des grandes références de la philosophie politique dite "radicale" et des études sur la démocratie et l’art. Il fait ses études à l’École normale supérieure à Paris, où il est l’élève de Louis Althusser et participe en 1965 au livre collectif Lire le Capital, qui relit Marx dans une perspective structuraliste. Après Mai 68, il rompt progressivement avec l’althussérisme, auquel il reproche de confisquer la parole politique au profit des théoriciens. &lt;/p&gt; &lt;p&gt; Le fil conducteur de sa pensée est l’affirmation d’une égalité fondamentale de tous quant à ​ &lt;a href="https://www.youtube.com/watch?v=A9kl3_vnXjI" title="Et si on arrêtait de prendre les gens pour des cons ? par ARTE"&gt;l’intelligence &lt;/a&gt; et à la capacité de penser et de parler. Pour lui, la politique authentique commence quand ceux qui sont considérés comme "incapables" (ouvriers, sans-part, exclus) se mettent à parler et à agir comme des égaux, contestant l’ordre qui les tient à l’écart.​
+Cette égalité n’est pas un but lointain mais un point de départ : toute pratique émancipatrice suppose de présupposer l’égalité, non de l’attendre d’une pédagogie ou d’un progrès historique garantis par des experts. C’est pourquoi il critique les formes de domination qui passent par le savoir, les explications savantes, les discours des intellectuels qui se posent en porte‑parole des autres. &lt;/p&gt; &lt;p&gt; Il a aussi profondément marqué la philosophie de l’art. Dans "Le Partage du sensible" paru en 2000 et d’autres ouvrages, il parle de « régimes esthétiques » pour désigner des manières historiques d’organiser ce qui se voit, se dit et se pense comme art.​   Le  &lt;a href="https://www.youtube.com/watch?v=kWB3YzyjsJs" title="Jacques Rancière : les temporalités de la fiction par France Culture"&gt;"partage du sensible"&lt;/a&gt; est la trame commune à l’art et à la politique : ce qui est perceptible, ce qui a droit de cité, la frontière entre bruit et parole. Un geste artistique peut être politique quand il reconfigure ce partage, par exemple en rendant visibles des vies ou des voix jusque‑là tenues pour insignifiantes. &lt;/p&gt; &lt;audio controls title=" La politique selon Jacques Rancière par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-16.01.2023-ITEMA_23257742-2023C48904E0001-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F10" s="34" t="inlineStr">
         <is>
-          <t>XBD5SuIsnIg</t>
+          <t>ESi6O0B6H10</t>
         </is>
       </c>
       <c r="G10" s="36" t="inlineStr">
         <is>
-          <t>"Anne Fagot Largeault Médecine et Philosophie" par Socohade</t>
+          <t>"Les Trente Inglorieuses" selon le philosophe Jacques Rancière par France Culture</t>
         </is>
       </c>
       <c r="H10" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/aflargault-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/ranciere-mini.webp</t>
         </is>
       </c>
       <c r="I10" s="36" t="n"/>
       <c r="J10" s="27" t="inlineStr">
         <is>
-          <t>epistemologie ; ethique</t>
+          <t>politique ; esthetique</t>
         </is>
       </c>
       <c r="K10" s="27" t="inlineStr">
         <is>
-          <t>Analytique ; Positivisme Logique</t>
+          <t>Post-structuralisme</t>
         </is>
       </c>
       <c r="L10" s="27" t="inlineStr">
         <is>
-          <t>philosophe française à la croisée de la médecine, la philosophie et les sciences du vivant.</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français travaillant principalement sur l'émancipation intellectuelle des dominés.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1205,7 +1204,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">reel</t>
+          <t xml:space="preserve">critique ; continental ; art</t>
         </is>
       </c>
     </row>
@@ -1214,51 +1213,49 @@
         <v>1940</v>
       </c>
       <c r="B11" s="34" t="n"/>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
+      <c r="C11" s="34" t="n">
+        <v>1940</v>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacques RANCIÈRE</t>
+          <t>Régis DEBRAY</t>
         </is>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_Ranci%C3%A8re" title=" Wikipedia"&gt;Jacques RANCIERE&lt;/a&gt; est un philosophe français connu pour une pensée qui articule politique, histoire, esthétique et éducation autour de l’idée d’émancipation de n’importe qui. Il est aujourd’hui l’une des grandes références de la philosophie politique dite "radicale" et des études sur la démocratie et l’art. Il fait ses études à l’École normale supérieure à Paris, où il est l’élève de Louis Althusser et participe en 1965 au livre collectif Lire le Capital, qui relit Marx dans une perspective structuraliste. Après Mai 68, il rompt progressivement avec l’althussérisme, auquel il reproche de confisquer la parole politique au profit des théoriciens. &lt;/p&gt; &lt;p&gt; Le fil conducteur de sa pensée est l’affirmation d’une égalité fondamentale de tous quant à ​ &lt;a href="https://www.youtube.com/watch?v=A9kl3_vnXjI" title="Et si on arrêtait de prendre les gens pour des cons ? par ARTE"&gt;l’intelligence &lt;/a&gt; et à la capacité de penser et de parler. Pour lui, la politique authentique commence quand ceux qui sont considérés comme "incapables" (ouvriers, sans-part, exclus) se mettent à parler et à agir comme des égaux, contestant l’ordre qui les tient à l’écart.​
-Cette égalité n’est pas un but lointain mais un point de départ : toute pratique émancipatrice suppose de présupposer l’égalité, non de l’attendre d’une pédagogie ou d’un progrès historique garantis par des experts. C’est pourquoi il critique les formes de domination qui passent par le savoir, les explications savantes, les discours des intellectuels qui se posent en porte‑parole des autres. &lt;/p&gt; &lt;p&gt; Il a aussi profondément marqué la philosophie de l’art. Dans "Le Partage du sensible" paru en 2000 et d’autres ouvrages, il parle de « régimes esthétiques » pour désigner des manières historiques d’organiser ce qui se voit, se dit et se pense comme art.​   Le  &lt;a href="https://www.youtube.com/watch?v=kWB3YzyjsJs" title="Jacques Rancière : les temporalités de la fiction par France Culture"&gt;"partage du sensible"&lt;/a&gt; est la trame commune à l’art et à la politique : ce qui est perceptible, ce qui a droit de cité, la frontière entre bruit et parole. Un geste artistique peut être politique quand il reconfigure ce partage, par exemple en rendant visibles des vies ou des voix jusque‑là tenues pour insignifiantes. &lt;/p&gt; &lt;audio controls title=" La politique selon Jacques Rancière par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-16.01.2023-ITEMA_23257742-2023C48904E0001-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9gis_Debray" title=" Wikipedia"&gt;Régis DEBRAY&lt;/a&gt; est un  philosophe, écrivain et essayiste, dont le parcours a été marqué par l’engagement politique autant que par la réflexion théorique. Il s’est formé à l’École normale supérieure puis à l’agrégation de philosophie, avant de s’impliquer dans les mouvements révolutionnaires latino-américains, ce qui a durablement orienté sa pensée. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.regisdebray.com/" title="regisdebray"&gt;Sa philosophie &lt;/a&gt; ne se réduit pas à des idées abstraites : elle part souvent du réel, de l’histoire et des formes concrètes de transmission des croyances, des images et des institutions. Il a notamment développé la médiologie, une approche qui étudie comment les messages circulent grâce à des supports matériels et sociaux, et comment ces supports transforment le sens même des idées. &lt;/p&gt; &lt;p&gt; Une autre dimension importante de sa pensée concerne la République, la laïcité et le sacré. Il s’intéresse à ce qui maintient une communauté politique et symbolique, en montrant que les sociétés ont besoin de rites, de frontières, d’institutions et de formes de &lt;a href="https://www.youtube.com/watch?v=YtqETo-7w9g" title="regis debray par France Inter"&gt;transmission pour durer. &lt;/a&gt;  Il ne pense donc pas la modernité comme une simple libération des cadres anciens, mais comme une transformation de leurs médiations. &lt;/p&gt; &lt;p&gt; Il  est un philosophe du passage entre les idées et leurs conditions matérielles d’existence, entre la politique et la culture, entre le &lt;a href="https://www.youtube.com/watch?v=vKM_P0HCbUs" title="regis debray analyse le pouvoir de l’image par INA Culture"&gt;spirituel et l’institutionnel. &lt;/a&gt; Son œuvre est traversée par une question centrale : comment une société transmet-elle ce qui la fonde, sans perdre ce qu’elle a de commun ? &lt;/p&gt;  &lt;audio controls title=" Régis DEBRAY invité  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22076-10.04.2026-ITEMA_24472004-2026C16450S0100-NET_MFC_C09BCD10-D8F0-42EC-8B3D-61F3DE131622-21-e22a266a3abc5abf79c18e3abcc532cf.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+</t>
         </is>
       </c>
       <c r="F11" s="34" t="inlineStr">
         <is>
-          <t>ESi6O0B6H10</t>
+          <t>QjR4j6vMzmk</t>
         </is>
       </c>
       <c r="G11" s="36" t="inlineStr">
         <is>
-          <t>"Les Trente Inglorieuses" selon le philosophe Jacques Rancière par France Culture</t>
-        </is>
-      </c>
-      <c r="H11" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/ranciere-mini.webp</t>
+          <t>Régis Debray : nous sommes tous devenus Américains par Polinium</t>
+        </is>
+      </c>
+      <c r="H11" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/rdebray-mini.webp</t>
         </is>
       </c>
       <c r="I11" s="36" t="n"/>
       <c r="J11" s="27" t="inlineStr">
         <is>
-          <t>politique ; esthetique</t>
+          <t>politique</t>
         </is>
       </c>
       <c r="K11" s="27" t="inlineStr">
         <is>
-          <t>Post-structuralisme</t>
+          <t>Marxisme</t>
         </is>
       </c>
       <c r="L11" s="27" t="inlineStr">
         <is>
-          <t>philosophe français travaillant principalement sur l'émancipation intellectuelle des dominés.</t>
+          <t>philosophe et écrivain français dont le parcours a été marqué par l’engagement politique.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1268,58 +1265,65 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">critique ; continental ; art</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="147.75" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="199.5" customHeight="1" s="28">
       <c r="A12" s="34" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B12" s="34" t="n"/>
-      <c r="C12" s="34" t="n">
-        <v>1940</v>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>Régis DEBRAY</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9gis_Debray" title=" Wikipedia"&gt;Régis DEBRAY&lt;/a&gt; est un  philosophe, écrivain et essayiste, dont le parcours a été marqué par l’engagement politique autant que par la réflexion théorique. Il s’est formé à l’École normale supérieure puis à l’agrégation de philosophie, avant de s’impliquer dans les mouvements révolutionnaires latino-américains, ce qui a durablement orienté sa pensée. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.regisdebray.com/" title="regisdebray"&gt;Sa philosophie &lt;/a&gt; ne se réduit pas à des idées abstraites : elle part souvent du réel, de l’histoire et des formes concrètes de transmission des croyances, des images et des institutions. Il a notamment développé la médiologie, une approche qui étudie comment les messages circulent grâce à des supports matériels et sociaux, et comment ces supports transforment le sens même des idées. &lt;/p&gt; &lt;p&gt; Une autre dimension importante de sa pensée concerne la République, la laïcité et le sacré. Il s’intéresse à ce qui maintient une communauté politique et symbolique, en montrant que les sociétés ont besoin de rites, de frontières, d’institutions et de formes de &lt;a href="https://www.youtube.com/watch?v=YtqETo-7w9g" title="regis debray par France Inter"&gt;transmission pour durer. &lt;/a&gt;  Il ne pense donc pas la modernité comme une simple libération des cadres anciens, mais comme une transformation de leurs médiations. &lt;/p&gt; &lt;p&gt; Il  est un philosophe du passage entre les idées et leurs conditions matérielles d’existence, entre la politique et la culture, entre le &lt;a href="https://www.youtube.com/watch?v=vKM_P0HCbUs" title="regis debray analyse le pouvoir de l’image par INA Culture"&gt;spirituel et l’institutionnel. &lt;/a&gt; Son œuvre est traversée par une question centrale : comment une société transmet-elle ce qui la fonde, sans perdre ce qu’elle a de commun ? &lt;/p&gt;  &lt;audio controls title=" Régis DEBRAY invité  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22076-10.04.2026-ITEMA_24472004-2026C16450S0100-NET_MFC_C09BCD10-D8F0-42EC-8B3D-61F3DE131622-21-e22a266a3abc5abf79c18e3abcc532cf.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t>Julia KRISTEVA</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julia_Kristeva"  title=" Wikipedia"&gt;Julia KRISTEVA&lt;/a&gt;  est une philosophe, psychanalyste et écrivaine franco‑bulgare devenue l’une des figures centrales du &lt;a href="https://fr.wikipedia.org/wiki/Post-structuralisme"  title="post structuralisme par Wikipedia"&gt;post‑structuralisme &lt;/a&gt; français à partir des années 1960. D’abord formée en linguistique à Sofia, elle s’installe à Paris où elle fréquente les cercles de la &lt;a href="https://fr.wikipedia.org/wiki/French_Theory"  title="french théory par Wikipedia"&gt;« French theory » &lt;/a&gt; et côtoie des penseurs comme Roland Barthes, Philippe Sollers et Jacques Lacan, ce qui fera de son œuvre un croisement entre linguistique, psychanalyse et esthétique. &lt;/p&gt; &lt;p&gt; Elle est notamment connue pour avoir introduit en 1966 la notion d’« intertextualité », en définissant le texte comme une « mosaïque de citations » où chaque écriture absorbe et transforme d’autres textes. Elle distingue aussi un niveau « sémiotique » du langage, lié aux pulsions et au corps, d’un niveau « symbolique » plus structuré par la loi et la syntaxe, ce qui permet de penser la poésie comme un espace où la parole déborde les codes ordinaires. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Pouvoirs de l’horreur (1980), elle développe la notion d’« abject », désignant ce qui est à la fois rejeté (le sang, le corps, la mort, la merde) et intrinsèquement lié à l’identité du sujet. L’abject apparaît comme un  &lt;a href="https://www.youtube.com/watch?v=ZnYtTJ83u5c"  title="Julia Kristeva, étrange étrangère par patrick Sandrin"&gt; seuil instable &lt;/a&gt; entre propre et impur, entre moi et non‑moi, et elle l’utilise pour analyser la formation de la subjectivité, la face « sombre » de la culture et les limites de l’ordre symbolique. &lt;/p&gt; &lt;p&gt; Sans défendre une essence prédéfinie de la « femme », elle interroge la place du féminin dans la culture et la psychanalyse, en explorant le rapport entre sexualité, désir maternel et création artistique. Ses travaux s’ouvrent aussi à la question de la croyance et de la quête spirituelle, notamment dans ses réflexions sur la dépression, la mélancolie et les « nouvelles maladies de l’âme », où elle articule psychanalyse, littérature et rapport à la foi. &lt;/p&gt;  &lt;audio controls title="Julia Kristeva par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13954-06.03.2017-ITEMA_21250146-2017C26722S0065-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>QjR4j6vMzmk</t>
+          <t>YtmBu6SJOSQ</t>
         </is>
       </c>
       <c r="G12" s="36" t="inlineStr">
         <is>
-          <t>Régis Debray : nous sommes tous devenus Américains par Polinium</t>
-        </is>
-      </c>
-      <c r="H12" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/rdebray-mini.webp</t>
+          <t xml:space="preserve">"Julia Kristeva - Prélude à une éthique du féminin" par Librairie Mollat</t>
+        </is>
+      </c>
+      <c r="H12" s="34" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/jkristeva-mini.webp</t>
         </is>
       </c>
       <c r="I12" s="36" t="n"/>
       <c r="J12" s="27" t="inlineStr">
         <is>
-          <t>politique</t>
+          <t>epistemologie ; esthetique</t>
         </is>
       </c>
       <c r="K12" s="27" t="inlineStr">
         <is>
-          <t>Marxisme</t>
+          <t>Post-structuralisme ; Structuralisme ; French Theory</t>
         </is>
       </c>
       <c r="L12" s="27" t="inlineStr">
         <is>
-          <t>philosophe et écrivain français dont le parcours a été marqué par l’engagement politique.</t>
+          <t>philosophe française figure du post‑structuralisme français à partir des années 1960.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1329,65 +1333,59 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="199.5" customHeight="1" s="28">
+          <t xml:space="preserve">genre ; continental ; art</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="178.5" customHeight="1" s="28">
       <c r="A13" s="34" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B13" s="34" t="n"/>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>Julia KRISTEVA</t>
-        </is>
-      </c>
-      <c r="E13" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julia_Kristeva"  title=" Wikipedia"&gt;Julia KRISTEVA&lt;/a&gt;  est une philosophe, psychanalyste et écrivaine franco‑bulgare devenue l’une des figures centrales du &lt;a href="https://fr.wikipedia.org/wiki/Post-structuralisme"  title="post structuralisme par Wikipedia"&gt;post‑structuralisme &lt;/a&gt; français à partir des années 1960. D’abord formée en linguistique à Sofia, elle s’installe à Paris où elle fréquente les cercles de la &lt;a href="https://fr.wikipedia.org/wiki/French_Theory"  title="french théory par Wikipedia"&gt;« French theory » &lt;/a&gt; et côtoie des penseurs comme Roland Barthes, Philippe Sollers et Jacques Lacan, ce qui fera de son œuvre un croisement entre linguistique, psychanalyse et esthétique. &lt;/p&gt; &lt;p&gt; Elle est notamment connue pour avoir introduit en 1966 la notion d’« intertextualité », en définissant le texte comme une « mosaïque de citations » où chaque écriture absorbe et transforme d’autres textes. Elle distingue aussi un niveau « sémiotique » du langage, lié aux pulsions et au corps, d’un niveau « symbolique » plus structuré par la loi et la syntaxe, ce qui permet de penser la poésie comme un espace où la parole déborde les codes ordinaires. &lt;/p&gt; &lt;p&gt; Dans son ouvrage Pouvoirs de l’horreur (1980), elle développe la notion d’« abject », désignant ce qui est à la fois rejeté (le sang, le corps, la mort, la merde) et intrinsèquement lié à l’identité du sujet. L’abject apparaît comme un  &lt;a href="https://www.youtube.com/watch?v=ZnYtTJ83u5c"  title="Julia Kristeva, étrange étrangère par patrick Sandrin"&gt; seuil instable &lt;/a&gt; entre propre et impur, entre moi et non‑moi, et elle l’utilise pour analyser la formation de la subjectivité, la face « sombre » de la culture et les limites de l’ordre symbolique. &lt;/p&gt; &lt;p&gt; Sans défendre une essence prédéfinie de la « femme », elle interroge la place du féminin dans la culture et la psychanalyse, en explorant le rapport entre sexualité, désir maternel et création artistique. Ses travaux s’ouvrent aussi à la question de la croyance et de la quête spirituelle, notamment dans ses réflexions sur la dépression, la mélancolie et les « nouvelles maladies de l’âme », où elle articule psychanalyse, littérature et rapport à la foi. &lt;/p&gt;  &lt;audio controls title="Julia Kristeva par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13954-06.03.2017-ITEMA_21250146-2017C26722S0065-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
+          <t>Etienne BALIBAR</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Balibar" title=" Wikipedia"&gt;Etienne BALIBAR&lt;/a&gt; est un philosophe français connu pour ses travaux au croisement du marxisme, de la philosophie politique et des questions comme les frontières et les droits de l'homme.&lt;/p&gt; &lt;p&gt; Ses réflexions portent sur le racisme, la citoyenneté, le cosmopolitisme et l'universalisme, critiquant &lt;a href="https://www.youtube.com/watch?v=oNZFlnOn4JA"  title="Etienne Balibar, l’Histoire toujours en mouvement par France Culture"&gt; le capitalisme néolibéral&lt;/a&gt; et défendant une politique émancipatrice. Il interroge les États-nations, les violences contemporaines et l'Europe dans un cadre marxiste revisité. Il promeut "l'égaliberté", liant égalité et liberté dans une anthropologie philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses livres influents figurent "La Philosophie de Marx, Spinoza et la politique" ainsi que "Les Frontières de la démocratie et Droit de Cité". Récemment, "Histoire interminable et Passions du concept" synthétisent sa pensée sur l'histoire, l'épistémologie et la politique. &lt;/p&gt; &lt;p&gt; Il conçoit les frontières comme des institutions dynamiques, polysémiques et hétérogènes, qui ne séparent pas simplement nationaux et étrangers mais produisent des altérités et des exclusions sociales ayant une épaisseur spatiale et temporelle formant des zones de conflits, d'hybridations et de subjectivations inédites surtout  en Europe. Il rejette la fusion stricte entre citoyenneté et nationalité, plaidant pour une citoyenneté transnationale ou un "droit de cité" en France ou en Europe, dissocié de la nationalité, incluant libre circulation et vote local. Il propose une &lt;a href="https://www.youtube.com/watch?v=Vw8wzfRZJUs"  title="Étienne Balibar : « La seule solution, c’est une souveraineté européenne. » par Regards"&gt;"constitution citoyenne"&lt;/a&gt; européenne pour contrer un risque d'apartheid, via l'extension des droits civiques aux immigrés et sans-papiers. &lt;/p&gt; &lt;p&gt; La notion &lt;a href="https://www.youtube.com/watch?v=Hq5frARZZDg" title="Égaux avec nos différences - Etienne Balibar par A gauche"&gt;"d'égaliberté"&lt;/a&gt; unit indissolublement égalité et liberté comme principe révolutionnaire, posant un droit positif à la citoyenneté pour tous, conquis par insurrection contre les privilèges. Elle implique une réciprocité constitutive entre co-citoyens, rendant impossible l'exclusion du "peuple" politique, et vise une démocratisation horizontale des droits. &lt;/p&gt;  &lt;audio controls title="Etienne Balibar, philosophe à la frontière par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-06.06.2016-ITEMA_21002759-2016C3500E0051-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>YtmBu6SJOSQ</t>
+          <t>SbYAWEajtrg</t>
         </is>
       </c>
       <c r="G13" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Julia Kristeva - Prélude à une éthique du féminin" par Librairie Mollat</t>
-        </is>
-      </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/jkristeva-mini.webp</t>
+          <t>"Etienne Balibar - Penser et repenser l’humanité comme espèce" par Le Mans Université Conférences</t>
+        </is>
+      </c>
+      <c r="H13" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/balibar-mini.webp</t>
         </is>
       </c>
       <c r="I13" s="36" t="n"/>
       <c r="J13" s="27" t="inlineStr">
         <is>
-          <t>epistemologie ; esthetique</t>
+          <t>politique</t>
         </is>
       </c>
       <c r="K13" s="27" t="inlineStr">
         <is>
-          <t>Post-structuralisme ; Structuralisme ; French Theory</t>
+          <t>Marxisme</t>
         </is>
       </c>
       <c r="L13" s="27" t="inlineStr">
         <is>
-          <t>philosophe française figure du post‑structuralisme français à partir des années 1960.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français connu pour ses positions sur les frontières et les droits de l'homme.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1397,59 +1395,65 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre ; continental ; art</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="178.5" customHeight="1" s="28">
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="147.75" customHeight="1" s="28">
       <c r="A14" s="34" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B14" s="34" t="n"/>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>Etienne BALIBAR</t>
-        </is>
-      </c>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Balibar" title=" Wikipedia"&gt;Etienne BALIBAR&lt;/a&gt; est un philosophe français connu pour ses travaux au croisement du marxisme, de la philosophie politique et des questions comme les frontières et les droits de l'homme.&lt;/p&gt; &lt;p&gt; Ses réflexions portent sur le racisme, la citoyenneté, le cosmopolitisme et l'universalisme, critiquant &lt;a href="https://www.youtube.com/watch?v=oNZFlnOn4JA"  title="Etienne Balibar, l’Histoire toujours en mouvement par France Culture"&gt; le capitalisme néolibéral&lt;/a&gt; et défendant une politique émancipatrice. Il interroge les États-nations, les violences contemporaines et l'Europe dans un cadre marxiste revisité. Il promeut "l'égaliberté", liant égalité et liberté dans une anthropologie philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses livres influents figurent "La Philosophie de Marx, Spinoza et la politique" ainsi que "Les Frontières de la démocratie et Droit de Cité". Récemment, "Histoire interminable et Passions du concept" synthétisent sa pensée sur l'histoire, l'épistémologie et la politique. &lt;/p&gt; &lt;p&gt; Il conçoit les frontières comme des institutions dynamiques, polysémiques et hétérogènes, qui ne séparent pas simplement nationaux et étrangers mais produisent des altérités et des exclusions sociales ayant une épaisseur spatiale et temporelle formant des zones de conflits, d'hybridations et de subjectivations inédites surtout  en Europe. Il rejette la fusion stricte entre citoyenneté et nationalité, plaidant pour une citoyenneté transnationale ou un "droit de cité" en France ou en Europe, dissocié de la nationalité, incluant libre circulation et vote local. Il propose une &lt;a href="https://www.youtube.com/watch?v=Vw8wzfRZJUs"  title="Étienne Balibar : « La seule solution, c’est une souveraineté européenne. » par Regards"&gt;"constitution citoyenne"&lt;/a&gt; européenne pour contrer un risque d'apartheid, via l'extension des droits civiques aux immigrés et sans-papiers. &lt;/p&gt; &lt;p&gt; La notion &lt;a href="https://www.youtube.com/watch?v=Hq5frARZZDg" title="Égaux avec nos différences - Etienne Balibar par A gauche"&gt;"d'égaliberté"&lt;/a&gt; unit indissolublement égalité et liberté comme principe révolutionnaire, posant un droit positif à la citoyenneté pour tous, conquis par insurrection contre les privilèges. Elle implique une réciprocité constitutive entre co-citoyens, rendant impossible l'exclusion du "peuple" politique, et vise une démocratisation horizontale des droits. &lt;/p&gt;  &lt;audio controls title="Etienne Balibar, philosophe à la frontière par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-06.06.2016-ITEMA_21002759-2016C3500E0051-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Blandine KRIEGEL</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Blandine_Kriegel"  title=" Wikipedia"&gt;Blandine KRIEGEL&lt;/a&gt;  est une philosophe française spécialisée en philosophie politique et en histoire des idées. Elle a travaillé comme professeure, chercheuse au CNRS, conseillère du président de la République et présidente du Haut Conseil à l’intégration, tout en développant une œuvre importante sur l’État de droit, les droits de l’homme et la démocratie. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.blandinekriegel.com/" title="Blandine Kriegel"&gt;  Sa pensée s’est construite &lt;/a&gt; contre plusieurs courants dominants du XXe siècle, notamment le marxisme dogmatique et certaines formes de philosophie allemande qu’elle juge trop centrées sur la volonté, le sujet ou l’historicisme. Elle a remis au premier plan la question du droit politique, en défendant l’idée que la liberté ne se réduit pas à un élan abstrait, mais s’inscrit dans des institutions, des lois et un cadre républicain. &lt;/p&gt; &lt;p&gt; Un des traits les plus marquants de son œuvre est son insistance sur la notion d’État de droit. Dans L’État et les esclaves, puis dans ses travaux ultérieurs, elle montre que la domination politique ne doit pas être pensée seulement comme un rapport de force, mais aussi comme une question de légalité, de protection des corps et des consciences, et de fondement rationnel des institutions. Elle relit ainsi l’histoire moderne du politique à travers Bodin, Hobbes, Spinoza, Locke et &lt;a href="https://www.youtube.com/watch?v=UE77MDWOFnw" title="Locke et la loi naturelle' par Radio J"&gt;  la tradition des droits naturels. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  propose une philosophie de la République qui valorise les droits de l’homme, la citoyenneté et la souveraineté populaire, tout en restant attentive aux formes concrètes du pouvoir. Sa démarche est à la fois historique et normative : elle cherche à comprendre comment les institutions se sont formées, mais aussi comment elles peuvent garantir la liberté dans des sociétés modernes traversées par les conflits, les appartenances collectives et les tensions entre individu et État. &lt;/p&gt;  &lt;audio controls title="La République Imaginaire avec blandine Kriegel à la frontière par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-30.09.2022-ITEMA_23151281-2022F45096S0273-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+</t>
         </is>
       </c>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>SbYAWEajtrg</t>
+          <t>qcmrtkAdhx0</t>
         </is>
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
-          <t>"Etienne Balibar - Penser et repenser l’humanité comme espèce" par Le Mans Université Conférences</t>
+          <t>"Philosophies - Le juste et l’injuste avec Blandine Kriegel" par Radio J</t>
         </is>
       </c>
       <c r="H14" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/balibar-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/bkriegel-mini.webp</t>
         </is>
       </c>
       <c r="I14" s="36" t="n"/>
       <c r="J14" s="27" t="inlineStr">
         <is>
-          <t>politique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K14" s="27" t="inlineStr">
         <is>
-          <t>Marxisme</t>
+          <t>Libéralisme</t>
         </is>
       </c>
       <c r="L14" s="27" t="inlineStr">
         <is>
-          <t>philosophe français connu pour ses positions sur les frontières et les droits de l'homme.</t>
+          <t>philosophe française spécialisée en philosophie politique et en histoire des idées.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive;femme</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1459,94 +1463,26 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="147.75" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="189" customHeight="1" s="28">
       <c r="A15" s="34" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B15" s="34" t="n"/>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>Blandine KRIEGEL</t>
-        </is>
-      </c>
-      <c r="E15" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Blandine_Kriegel"  title=" Wikipedia"&gt;Blandine KRIEGEL&lt;/a&gt;  est une philosophe française spécialisée en philosophie politique et en histoire des idées. Elle a travaillé comme professeure, chercheuse au CNRS, conseillère du président de la République et présidente du Haut Conseil à l’intégration, tout en développant une œuvre importante sur l’État de droit, les droits de l’homme et la démocratie. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.blandinekriegel.com/" title="Blandine Kriegel"&gt;  Sa pensée s’est construite &lt;/a&gt; contre plusieurs courants dominants du XXe siècle, notamment le marxisme dogmatique et certaines formes de philosophie allemande qu’elle juge trop centrées sur la volonté, le sujet ou l’historicisme. Elle a remis au premier plan la question du droit politique, en défendant l’idée que la liberté ne se réduit pas à un élan abstrait, mais s’inscrit dans des institutions, des lois et un cadre républicain. &lt;/p&gt; &lt;p&gt; Un des traits les plus marquants de son œuvre est son insistance sur la notion d’État de droit. Dans L’État et les esclaves, puis dans ses travaux ultérieurs, elle montre que la domination politique ne doit pas être pensée seulement comme un rapport de force, mais aussi comme une question de légalité, de protection des corps et des consciences, et de fondement rationnel des institutions. Elle relit ainsi l’histoire moderne du politique à travers Bodin, Hobbes, Spinoza, Locke et &lt;a href="https://www.youtube.com/watch?v=UE77MDWOFnw" title="Locke et la loi naturelle' par Radio J"&gt;  la tradition des droits naturels. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il  propose une philosophie de la République qui valorise les droits de l’homme, la citoyenneté et la souveraineté populaire, tout en restant attentive aux formes concrètes du pouvoir. Sa démarche est à la fois historique et normative : elle cherche à comprendre comment les institutions se sont formées, mais aussi comment elles peuvent garantir la liberté dans des sociétés modernes traversées par les conflits, les appartenances collectives et les tensions entre individu et État. &lt;/p&gt;  &lt;audio controls title="La République Imaginaire avec blandine Kriegel à la frontière par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-30.09.2022-ITEMA_23151281-2022F45096S0273-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
-        </is>
-      </c>
-      <c r="F15" s="34" t="inlineStr">
-        <is>
-          <t>qcmrtkAdhx0</t>
-        </is>
-      </c>
-      <c r="G15" s="36" t="inlineStr">
-        <is>
-          <t>"Philosophies - Le juste et l’injuste avec Blandine Kriegel" par Radio J</t>
-        </is>
-      </c>
-      <c r="H15" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/bkriegel-mini.webp</t>
-        </is>
-      </c>
-      <c r="I15" s="36" t="n"/>
-      <c r="J15" s="27" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="K15" s="27" t="inlineStr">
-        <is>
-          <t>Libéralisme</t>
-        </is>
-      </c>
-      <c r="L15" s="27" t="inlineStr">
-        <is>
-          <t>philosophe française spécialisée en philosophie politique et en histoire des idées.</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive;femme</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="189" customHeight="1" s="28">
-      <c r="A16" s="34" t="n">
-        <v>1944</v>
-      </c>
-      <c r="B16" s="34" t="n"/>
-      <c r="C16" s="34" t="inlineStr">
-        <is>
-          <t>1944</t>
-        </is>
-      </c>
-      <c r="D16" s="35" t="inlineStr">
-        <is>
           <t>Gilles LIPOVETSKY</t>
         </is>
       </c>
-      <c r="E16" s="36" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Gilles_Lipovetsky"  title=" Wikipedia"&gt;Gilles LIPOVETSKY&lt;/a&gt; est un philosophe Français majeur de l’hypermodernité &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_postmoderne"  title="Le post modernisme par Wikipedia"&gt;  (post modernisme)&lt;/a&gt;, une époque marquée par l’individualisme exacerbé, l’accélération du temps et la domination de la consommation. Il analyse comment les valeurs traditionnelles s’effacent, laissant place à une quête de sens personnelle, souvent empreinte de contradictions. L’individu contemporain recherche l’épanouissement et le bonheur, mais se heurte à un vide existentiel et à une insatisfaction chronique. &lt;/p&gt;
 &lt;p&gt; Il met en lumière, dans son livre &lt;a href="https://www.youtube.com/watch?v=n3sv-0Hdr2I" title="L'ère du vide' par Kosmos"&gt;  ' l'ère du vite'  &lt;/a&gt; paru en 1983, l’importance de la consommation et de la séduction dans nos sociétés, où les objets et services ne répondent plus seulement à des besoins, mais deviennent des moyens d’expression identitaire. Ce consumérisme est associé à un hédonisme qui, bien qu’omniprésent, ne parvient pas à combler le désenchantement de l’individu. &lt;/p&gt;
@@ -1555,19 +1491,82 @@
 </t>
         </is>
       </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>2BYEpTuSpOc</t>
+        </is>
+      </c>
+      <c r="G15" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"l'authenticité est le new cool" par Le Point</t>
+        </is>
+      </c>
+      <c r="H15" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/lipovetsky-mini.webp</t>
+        </is>
+      </c>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="27" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K15" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post Modernisme ; Individualisme</t>
+        </is>
+      </c>
+      <c r="L15" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français qui fait partie du mouvement post-modernisme.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="168" customHeight="1" s="28">
+      <c r="A16" s="34" t="n">
+        <v>1944</v>
+      </c>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>1944</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Catherine LARRÈRE</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Catherine_Larr%C3%A8re"  style="color:#6A142A"  title=" Wikipedia"&gt;Catherine LARRÈRE&lt;/a&gt; est une philosophe française   professeure émérite de philosophie à Paris 1 Panthéon-Sorbonne et spécialisée en philosophie morale et politique, avec une attention particulière à l’éthique de l’environnement.&lt;/p&gt; &lt;p&gt; Elle a aporté une contribution majeure à l’essor de la philosophie environnementale en France, abordant des thèmes comme  &lt;a href="https://www.youtube.com/watch?v=YNxj0SXoNSo" style="color:#88A1E9" title="Qu'est-ce que la nature ? par Editions M-Editer"&gt;la protection de la nature&lt;/a&gt;, la prévention des risques et la justice environnementale. Engagement et leadership: présidente de la Fondation de l’écologie politique (2013-2016), un think-tank lié à &lt;a href="https://www.persee.fr/doc/ecoru_0013-0559_1999_num_249_1_5068_t1_0091_0000_2 " style="color:#88A1E9" title="Catherine Larrère Les philosophies de l'environnement  par Persée"&gt;Europe Écologie &lt;/a&gt; Les Verts, et commissaire scientifique de l’exposition Nature vive au Muséum national d’histoire naturelle (2001). &lt;/p&gt; &lt;p&gt; Ellle a publié largement sur Montesquieu, la philosophie morale et politique. Elle a aussi travaillé sur le rôle des femmes dans la société selon Rousseau et a collaboré étroitement avec son mari, Raphaël Larrère, agronome et écologue, sur des questions liées à l’environnement. Sa productivité académique est importante: articles, livres et chapitres, avec une présence notable dans les ressources bibliographiques et les bases de données spécialisées. Sa collaboration avec des chercheurs anglophones et ses traductions ont contribué à diffuser des idées clés de l’éthique de l’environnement en milieu francophone. &lt;/p&gt; &lt;p&gt; Elle continue d’être présente dans les débats publics et intellectuels sur l’environnement et l’éthique, notamment à travers des articles dans des revues et des plateformes spécialisées. &lt;/p&gt;     &lt;audio controls title="Catherine Larrère : "Ne pas s'occuper du social, c'est bloquer les solutions environnementales" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-07.02.2017-ITEMA_21221850-2017C19327S0038-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+ </t>
+        </is>
+      </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>2BYEpTuSpOc</t>
+          <t>SbTcnfMgm7E</t>
         </is>
       </c>
       <c r="G16" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"l'authenticité est le new cool" par Le Point</t>
+          <t>"C’est quoi la vie ? #2 - Catherine Larrère : « Ça n’est pas la nature ! »" par Le Blob</t>
         </is>
       </c>
       <c r="H16" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/lipovetsky-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/larrere-mini.webp</t>
         </is>
       </c>
       <c r="I16" s="36" t="n"/>
@@ -1578,12 +1577,17 @@
       </c>
       <c r="K16" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post Modernisme ; Individualisme</t>
+          <t>Ecologisme</t>
         </is>
       </c>
       <c r="L16" s="27" t="inlineStr">
         <is>
-          <t>philosophe français qui fait partie du mouvement post-modernisme.</t>
+          <t>philosophe française spécialiste de Montesquieu &amp;amp; de l'éthique de l'environnement.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1593,11 +1597,11 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="168" customHeight="1" s="28">
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="157.5" customHeight="1" s="28">
       <c r="A17" s="34" t="n">
         <v>1944</v>
       </c>
@@ -1609,49 +1613,44 @@
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>Catherine LARRÈRE</t>
+          <t>François GUÉRY</t>
         </is>
       </c>
       <c r="E17" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Catherine_Larr%C3%A8re"  style="color:#6A142A"  title=" Wikipedia"&gt;Catherine LARRÈRE&lt;/a&gt; est une philosophe française   professeure émérite de philosophie à Paris 1 Panthéon-Sorbonne et spécialisée en philosophie morale et politique, avec une attention particulière à l’éthique de l’environnement.&lt;/p&gt; &lt;p&gt; Elle a aporté une contribution majeure à l’essor de la philosophie environnementale en France, abordant des thèmes comme  &lt;a href="https://www.youtube.com/watch?v=YNxj0SXoNSo" style="color:#88A1E9" title="Qu'est-ce que la nature ? par Editions M-Editer"&gt;la protection de la nature&lt;/a&gt;, la prévention des risques et la justice environnementale. Engagement et leadership: présidente de la Fondation de l’écologie politique (2013-2016), un think-tank lié à &lt;a href="https://www.persee.fr/doc/ecoru_0013-0559_1999_num_249_1_5068_t1_0091_0000_2 " style="color:#88A1E9" title="Catherine Larrère Les philosophies de l'environnement  par Persée"&gt;Europe Écologie &lt;/a&gt; Les Verts, et commissaire scientifique de l’exposition Nature vive au Muséum national d’histoire naturelle (2001). &lt;/p&gt; &lt;p&gt; Ellle a publié largement sur Montesquieu, la philosophie morale et politique. Elle a aussi travaillé sur le rôle des femmes dans la société selon Rousseau et a collaboré étroitement avec son mari, Raphaël Larrère, agronome et écologue, sur des questions liées à l’environnement. Sa productivité académique est importante: articles, livres et chapitres, avec une présence notable dans les ressources bibliographiques et les bases de données spécialisées. Sa collaboration avec des chercheurs anglophones et ses traductions ont contribué à diffuser des idées clés de l’éthique de l’environnement en milieu francophone. &lt;/p&gt; &lt;p&gt; Elle continue d’être présente dans les débats publics et intellectuels sur l’environnement et l’éthique, notamment à travers des articles dans des revues et des plateformes spécialisées. &lt;/p&gt;     &lt;audio controls title="Catherine Larrère : "Ne pas s'occuper du social, c'est bloquer les solutions environnementales" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-07.02.2017-ITEMA_21221850-2017C19327S0038-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
- </t>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Gu%C3%A9ry" style="color:#6A142A"  title=" Wikipedia"&gt;François GUÉRY&lt;/a&gt; est un philosophe français,  normalien, professeur émérite, connu pour ses travaux sur le corps, l’industrialisation, le nihilisme et les formes modernes de violence politique. Il a été professeur de philosophie puis doyen de la Faculté de philosophie de l’université Lyon‑III, ainsi que professeur émérite après sa retraite. &lt;/p&gt; &lt;p&gt; Il s’est intéressé à Heidegger (notamment la question de la technique) et à Nietzsche, dont il a traduit et commenté certains textes, dont des passages d’"Ainsi parla Zarathoustra". Il travaille sur des "problèmes de civilisation" : société industrielle, écologie, architecture et urbanisme, matériaux et développement soutenable, cause des femmes, immigration.
+Une partie importante de sa réflexion porte sur la violence et la destruction (haine, terrorisme, nihilisme politique), ainsi que sur la manière dont les sociétés modernes organisent le ravage du monde et du vivant. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=gZOnq9siTAM" style="color:#88A1E9" title="L'expérience. Le faire ou l'avoir par Cité de l'architecture et du patrimoine"&gt;Son travail &lt;/a&gt; montre comment la société industrielle et technicienne transforme les corps, les paysages, les villes et les rapports de pouvoir, en posant la question et qui paie le prix du progrès et du développement. &lt;/p&gt; &lt;p&gt; Dans son "Archéologie du nihilisme", il relie le mouvement des "nihilistes" russes du XIXᵉ siècle, la critique nietzschéenne des valeurs et les régimes totalitaires, jusqu’aux formes contemporaines de négation de l’histoire et de fascination pour la destruction. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=y2IW6iOQOwk" style="color:#88A1E9" title="La Loi du plus faible de François Guery par Les editions du Cerf"&gt;"La loi du plus faible" &lt;/a&gt; paru en 2022 est une réflexion éthique et politique sur la situation géopolitique actuelle, à partir de la fragilité des plus vulnérables et du renversement de la logique du "plus fort".  Il met en lumière des formes actuelles d"amnésie" ou de négation du passé (productivisme, mode, scientisme)  lorsqu’elles rompent avec toute mémoire historique ou limite, et ouvrent à des logiques de ravage. ​&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
         <is>
-          <t>SbTcnfMgm7E</t>
+          <t>0nRT7O11pDQ</t>
         </is>
       </c>
       <c r="G17" s="36" t="inlineStr">
         <is>
-          <t>"C’est quoi la vie ? #2 - Catherine Larrère : « Ça n’est pas la nature ! »" par Le Blob</t>
+          <t>"Youth Pride 2012 Interview François Guery Philosophe" par youthpridrfrance</t>
         </is>
       </c>
       <c r="H17" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/larrere-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/guery-mini.webp</t>
         </is>
       </c>
       <c r="I17" s="36" t="n"/>
       <c r="J17" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K17" s="27" t="inlineStr">
         <is>
-          <t>Ecologisme</t>
+          <t>Marxisme ; Libéralisme</t>
         </is>
       </c>
       <c r="L17" s="27" t="inlineStr">
         <is>
-          <t>philosophe française spécialiste de Montesquieu &amp;amp; de l'éthique de l'environnement.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français engagé pour la cause écologique, la cause des femmes &amp;amp; de l'immigration.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1661,11 +1660,11 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="157.5" customHeight="1" s="28">
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="178.5" customHeight="1" s="28">
       <c r="A18" s="34" t="n">
         <v>1944</v>
       </c>
@@ -1677,44 +1676,44 @@
       </c>
       <c r="D18" s="35" t="inlineStr">
         <is>
-          <t>François GUÉRY</t>
+          <t>Yves MICHAUD</t>
         </is>
       </c>
       <c r="E18" s="36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Gu%C3%A9ry" style="color:#6A142A"  title=" Wikipedia"&gt;François GUÉRY&lt;/a&gt; est un philosophe français,  normalien, professeur émérite, connu pour ses travaux sur le corps, l’industrialisation, le nihilisme et les formes modernes de violence politique. Il a été professeur de philosophie puis doyen de la Faculté de philosophie de l’université Lyon‑III, ainsi que professeur émérite après sa retraite. &lt;/p&gt; &lt;p&gt; Il s’est intéressé à Heidegger (notamment la question de la technique) et à Nietzsche, dont il a traduit et commenté certains textes, dont des passages d’"Ainsi parla Zarathoustra". Il travaille sur des "problèmes de civilisation" : société industrielle, écologie, architecture et urbanisme, matériaux et développement soutenable, cause des femmes, immigration.
-Une partie importante de sa réflexion porte sur la violence et la destruction (haine, terrorisme, nihilisme politique), ainsi que sur la manière dont les sociétés modernes organisent le ravage du monde et du vivant. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=gZOnq9siTAM" style="color:#88A1E9" title="L'expérience. Le faire ou l'avoir par Cité de l'architecture et du patrimoine"&gt;Son travail &lt;/a&gt; montre comment la société industrielle et technicienne transforme les corps, les paysages, les villes et les rapports de pouvoir, en posant la question et qui paie le prix du progrès et du développement. &lt;/p&gt; &lt;p&gt; Dans son "Archéologie du nihilisme", il relie le mouvement des "nihilistes" russes du XIXᵉ siècle, la critique nietzschéenne des valeurs et les régimes totalitaires, jusqu’aux formes contemporaines de négation de l’histoire et de fascination pour la destruction. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=y2IW6iOQOwk" style="color:#88A1E9" title="La Loi du plus faible de François Guery par Les editions du Cerf"&gt;"La loi du plus faible" &lt;/a&gt; paru en 2022 est une réflexion éthique et politique sur la situation géopolitique actuelle, à partir de la fragilité des plus vulnérables et du renversement de la logique du "plus fort".  Il met en lumière des formes actuelles d"amnésie" ou de négation du passé (productivisme, mode, scientisme)  lorsqu’elles rompent avec toute mémoire historique ou limite, et ouvrent à des logiques de ravage. ​&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yves_Michaud_(philosophe)"  title=" Wikipedia"&gt;Yves MICHAUD&lt;/a&gt; est un philosophe français spécialiste de l'empirisme britannique, critique d'art et théoricien de la culture contemporaine. Il a dirigé l'École nationale supérieure des Beaux-Arts de 1989 à 1997 et fondé l'Université de tous les savoirs en 2000 pour démocratiser les avancées scientifiques. Professeur à Paris-I et Rouen, il s'est engagé dans l'enseignement supérieur et les institutions culturelles, mêlant philosophie politique, esthétique et actualité. &lt;/p&gt; &lt;p&gt; Influencé par Hume et Locke, il prône un empirisme sceptique anti-cartésien, privilégiant l'enquête empirique sur les systèmes dogmatiques pour appréhender la réalité dans sa complexité.  &lt;a href="https://www.canal-u.tv/intervenants/michaud-yves-027027678"  title="Yves Michaud par Canal U TV"&gt;Il analyse la violence politique &lt;/a&gt; dans son ouvrage "Violence et Politique" paru en 1978, explorant conflits, normes et institutions sans illusions morales. &lt;/p&gt; &lt;p&gt; Théoricien de l'art contemporain, il diagnostique dans "L'Art, c'est bien fini" paru en 2007 la fin du "Grand Art" au profit d'une hyper-esthétique diffuse et atmosphérique, comme le clubbing ou le tourisme de masse. Il dénonce le fondamentalisme moral et la "bienveillance" compassionnelle qui affaiblit l'État de droit face aux populismes et intégrismes. &lt;/p&gt; &lt;p&gt; Dans "Citoyenneté et loyauté" paru en 2017 et &lt;a href="https://www.youtube.com/watch?v=IBLebcxLbIo" title="
+Yves Michaud - Contre la bienveillance par librairie mollat"&gt;"Contre la bienveillance" &lt;/a&gt; en 2016, il critique l'accueil inconditionnel des migrants, les largesses de l'État-providence et la protection excessive des hors-la-loi, plaidant un retour radical aux Lumières pour une communauté souveraine. &lt;/p&gt;  &lt;audio controls title="Ceci n'est pas une tulipe, Yves Michaud par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-09.03.2020-ITEMA_22302575-2020F26101S0069-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>0nRT7O11pDQ</t>
+          <t>H4TB-9giO_I</t>
         </is>
       </c>
       <c r="G18" s="36" t="inlineStr">
         <is>
-          <t>"Youth Pride 2012 Interview François Guery Philosophe" par youthpridrfrance</t>
+          <t xml:space="preserve">"Yves Michaud - L'art, c'est bien fini : essai sur l'hyper-esthétique et les atmosphères" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H18" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/guery-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/ymichaud-mini.webp</t>
         </is>
       </c>
       <c r="I18" s="36" t="n"/>
       <c r="J18" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>esthetique ; politique</t>
         </is>
       </c>
       <c r="K18" s="27" t="inlineStr">
         <is>
-          <t>Marxisme ; Libéralisme</t>
+          <t>Post Modernisme</t>
         </is>
       </c>
       <c r="L18" s="27" t="inlineStr">
         <is>
-          <t>philosophe français engagé pour la cause écologique, la cause des femmes &amp;amp; de l'immigration.</t>
+          <t>philosophe français spécialiste de l'empirisme britannique &amp;amp; théoricien de la culture contemporaine.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1724,60 +1723,59 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="178.5" customHeight="1" s="28">
+          <t xml:space="preserve">critique ; art</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="156.75" customHeight="1" s="28">
       <c r="A19" s="34" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B19" s="34" t="n"/>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="D19" s="35" t="inlineStr">
         <is>
-          <t>Yves MICHAUD</t>
-        </is>
-      </c>
-      <c r="E19" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yves_Michaud_(philosophe)"  title=" Wikipedia"&gt;Yves MICHAUD&lt;/a&gt; est un philosophe français spécialiste de l'empirisme britannique, critique d'art et théoricien de la culture contemporaine. Il a dirigé l'École nationale supérieure des Beaux-Arts de 1989 à 1997 et fondé l'Université de tous les savoirs en 2000 pour démocratiser les avancées scientifiques. Professeur à Paris-I et Rouen, il s'est engagé dans l'enseignement supérieur et les institutions culturelles, mêlant philosophie politique, esthétique et actualité. &lt;/p&gt; &lt;p&gt; Influencé par Hume et Locke, il prône un empirisme sceptique anti-cartésien, privilégiant l'enquête empirique sur les systèmes dogmatiques pour appréhender la réalité dans sa complexité.  &lt;a href="https://www.canal-u.tv/intervenants/michaud-yves-027027678"  title="Yves Michaud par Canal U TV"&gt;Il analyse la violence politique &lt;/a&gt; dans son ouvrage "Violence et Politique" paru en 1978, explorant conflits, normes et institutions sans illusions morales. &lt;/p&gt; &lt;p&gt; Théoricien de l'art contemporain, il diagnostique dans "L'Art, c'est bien fini" paru en 2007 la fin du "Grand Art" au profit d'une hyper-esthétique diffuse et atmosphérique, comme le clubbing ou le tourisme de masse. Il dénonce le fondamentalisme moral et la "bienveillance" compassionnelle qui affaiblit l'État de droit face aux populismes et intégrismes. &lt;/p&gt; &lt;p&gt; Dans "Citoyenneté et loyauté" paru en 2017 et &lt;a href="https://www.youtube.com/watch?v=IBLebcxLbIo" title="
-Yves Michaud - Contre la bienveillance par librairie mollat"&gt;"Contre la bienveillance" &lt;/a&gt; en 2016, il critique l'accueil inconditionnel des migrants, les largesses de l'État-providence et la protection excessive des hors-la-loi, plaidant un retour radical aux Lumières pour une communauté souveraine. &lt;/p&gt;  &lt;audio controls title="Ceci n'est pas une tulipe, Yves Michaud par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-09.03.2020-ITEMA_22302575-2020F26101S0069-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t>François AZOUVI</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Azouvi"   title=" Wikipedia"&gt;François AZOUVI&lt;/a&gt;  est un philosophe français né au Mexique, directeur de recherches honoraire au CNRS et directeur d’études à l’EHESS. Spécialiste de la philosophie moderne (notamment Descartes et l’existence corporelle), il s’est orienté vers l’histoire culturelle et politique de la France contemporaine, en particulier la mémoire de la Seconde Guerre mondiale et les mutations anthropologiques de nos sociétés. &lt;/p&gt; &lt;p&gt; Sa philosophie s’articule autour de deux axes : une réflexion sur la réception des idées philosophiques dans la culture française, et une analyse critique des récits mémoriels. Proche de Paul Ricœur (avec qui il a réalisé un livre d’entretiens), il explore comment les doctrines se diffusent et se transforment dans l’espace public, en lien avec les événements historiques. &lt;/p&gt; &lt;p&gt; Un de ses apports majeurs est sa déconstruction du &lt;a href="https://www.youtube.com/watch?v=B5DErti_ksQ"  title="le myhte du grand silence par fondation Auschwitz"&gt;« mythe du grand silence » &lt;/a&gt; sur la Shoah en France d’après-guerre. Contre l’idée d’une occultation collective d’Auschwitz, il démontre, à travers romans, films et discours publics dès 1944-1954, que &lt;a href="https://laviedesidees.fr/Francois-Azouvi-Du-heros-a-la-victime"  title=" l’ère victimaire par la vie des idees"&gt;la mémoire juive  &lt;/a&gt; et la tragédie ont été précocement assumées, bien avant les années 1970. Dans Français, on ne vous a rien caché, il prolonge cette enquête sur la Résistance et Vichy, montrant un « mille-feuille » de récits qui forge l’identité nationale sans mensonge ni embellissement. &lt;/p&gt; &lt;p&gt; Plus récemment, dans Du héros à la victime, il diagnostique une « métamorphose contemporaine du sacré » : le déclin de l’héroïsme patriotique et judéo-chrétien (héritier de 1914 et du martyre) laisse place à une logique victimaire, où la reconnaissance de l’opprimé sacralise l’individu et engendre une « concurrence des victimes ». Il y voit, avec Bergson, une « loi de double frénésie » propre à l’ère des individus, où le sacré se réinvente en immanence, loin de toute transcendance héroïque. &lt;/p&gt;  &lt;audio controls title="La figure du héros a laissé place à celle de la victime par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/19489-19.05.2024-ITEMA_23746057-2024C33085E0003-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>H4TB-9giO_I</t>
+          <t>4ds4L9nLD9k</t>
         </is>
       </c>
       <c r="G19" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Yves Michaud - L'art, c'est bien fini : essai sur l'hyper-esthétique et les atmosphères" par Librairie Mollat</t>
+          <t>"François Azouvi "Francais, on ne vous a rien caché, la résistance, Vichy, notre mémoire" par Radio J</t>
         </is>
       </c>
       <c r="H19" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/ymichaud-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/fazouvi-mini.webp</t>
         </is>
       </c>
       <c r="I19" s="36" t="n"/>
       <c r="J19" s="27" t="inlineStr">
         <is>
-          <t>esthetique ; politique</t>
+          <t>epistemologie</t>
         </is>
       </c>
       <c r="K19" s="27" t="inlineStr">
         <is>
-          <t>Post Modernisme</t>
+          <t>Herméneutique</t>
         </is>
       </c>
       <c r="L19" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de l'empirisme britannique &amp;amp; théoricien de la culture contemporaine.</t>
+          <t>philosophe français spécialiste de la philosophie moderne.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1787,59 +1785,59 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">critique ; art</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="156.75" customHeight="1" s="28">
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="147.75" customHeight="1" s="28">
       <c r="A20" s="34" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="B20" s="34" t="n"/>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="D20" s="35" t="inlineStr">
         <is>
-          <t>François AZOUVI</t>
-        </is>
-      </c>
-      <c r="E20" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Azouvi"   title=" Wikipedia"&gt;François AZOUVI&lt;/a&gt;  est un philosophe français né au Mexique, directeur de recherches honoraire au CNRS et directeur d’études à l’EHESS. Spécialiste de la philosophie moderne (notamment Descartes et l’existence corporelle), il s’est orienté vers l’histoire culturelle et politique de la France contemporaine, en particulier la mémoire de la Seconde Guerre mondiale et les mutations anthropologiques de nos sociétés. &lt;/p&gt; &lt;p&gt; Sa philosophie s’articule autour de deux axes : une réflexion sur la réception des idées philosophiques dans la culture française, et une analyse critique des récits mémoriels. Proche de Paul Ricœur (avec qui il a réalisé un livre d’entretiens), il explore comment les doctrines se diffusent et se transforment dans l’espace public, en lien avec les événements historiques. &lt;/p&gt; &lt;p&gt; Un de ses apports majeurs est sa déconstruction du &lt;a href="https://www.youtube.com/watch?v=B5DErti_ksQ"  title="le myhte du grand silence par fondation Auschwitz"&gt;« mythe du grand silence » &lt;/a&gt; sur la Shoah en France d’après-guerre. Contre l’idée d’une occultation collective d’Auschwitz, il démontre, à travers romans, films et discours publics dès 1944-1954, que &lt;a href="https://laviedesidees.fr/Francois-Azouvi-Du-heros-a-la-victime"  title=" l’ère victimaire par la vie des idees"&gt;la mémoire juive  &lt;/a&gt; et la tragédie ont été précocement assumées, bien avant les années 1970. Dans Français, on ne vous a rien caché, il prolonge cette enquête sur la Résistance et Vichy, montrant un « mille-feuille » de récits qui forge l’identité nationale sans mensonge ni embellissement. &lt;/p&gt; &lt;p&gt; Plus récemment, dans Du héros à la victime, il diagnostique une « métamorphose contemporaine du sacré » : le déclin de l’héroïsme patriotique et judéo-chrétien (héritier de 1914 et du martyre) laisse place à une logique victimaire, où la reconnaissance de l’opprimé sacralise l’individu et engendre une « concurrence des victimes ». Il y voit, avec Bergson, une « loi de double frénésie » propre à l’ère des individus, où le sacré se réinvente en immanence, loin de toute transcendance héroïque. &lt;/p&gt;  &lt;audio controls title="La figure du héros a laissé place à celle de la victime par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/19489-19.05.2024-ITEMA_23746057-2024C33085E0003-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t>Jean-Luc MARION</t>
+        </is>
+      </c>
+      <c r="E20" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Marion"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean Luc MARION&lt;/a&gt; est un philosophe, phénoménologue et Membre de l’Académie française depuis 2008, il est reconnu pour sa tentative d’articuler la phénoménologie et la théologie dans ce qu’on a appelé le "tournant théologique de la phénoménologie française". &lt;/p&gt; &lt;p&gt; Il se revendique de la phénoménologie de Husserl et Heidegger, tout en l’orientant vers une réflexion sur la donation (le don). Pour lui, la phénoménologie doit s’intéresser non à l’être, mais à &lt;a href="https://www.youtube.com/watch?v=oS1vVjgKJOQ"  title=" Rencontre avec Jean-Luc Marion par KTO TV"&gt;ce qui se donne&lt;/a&gt;, et même à l’excès de ce don dans ce qu’il appelle les "phénomènes saturés".​  Cette approche déplace la question classique de l’être vers celle du don, où la subjectivité se laisse surprendre par ce qui se manifeste avant toute maîtrise conceptuelle. &lt;/p&gt; &lt;p&gt; Il développe cette idée dans des ouvrages majeurs comme "Réduction et donation" (1989), "Étant donné" (1998) et "De surcroît" (2001) ou la donation devient pour lui la condition de toute phénoménalité : les phénomènes les plus profonds (amour, art, révélation divine) excèdent la capacité de la conscience à les comprendre.​ Il renouvelle également la réflexion sur l’amour. Dans "Le Phénomène érotique" (2003), il propose que le sujet ne se fonde pas sur la conscience cartésienne mais sur "l’amour reçu et donné" qui devient ainsi le lieu de la véritable certitude de soi, en continuité critique avec Descartes et sous influence de Levinas. &lt;/p&gt; &lt;p&gt; Sa philosophie conjugue trois fils essentiels : &lt;/p&gt; &lt;p&gt;une phénoménologie du don et de la révélation, où le monde se manifeste comme excès reçu. &lt;/p&gt; &lt;p&gt;une théologie philosophique, cherchant à penser Dieu hors du cadre métaphysique traditionnel. &lt;/p&gt; &lt;p&gt;une éthique de l’amour, où autrui et la relation constituent la source du sens existentiel. &lt;/p&gt; &lt;p&gt; Spécialiste éminent de Descartes (notamment Sur la théologie blanche de Descartes et Sur la métaphysique grise de Descartes), il a aussi écrit des livres plus théologiques tels que "Dieu sans l’être", "D’ailleurs, la Révélation" et a reçu de nombreuses distinctions, dont le Grand Prix de l’Académie française en 1992 et le Prix de la Principauté de Monaco en 2018. &lt;/p&gt;    &lt;audio controls title=" Jean-Luc Marion : "La philosophie c’est de la course de fond, il faut en faire tous les jours, plusieurs heures" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-22.01.2021-ITEMA_22550575-2021C12410S0022.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>4ds4L9nLD9k</t>
+          <t>EAy1UbvGTe8</t>
         </is>
       </c>
       <c r="G20" s="36" t="inlineStr">
         <is>
-          <t>"François Azouvi "Francais, on ne vous a rien caché, la résistance, Vichy, notre mémoire" par Radio J</t>
+          <t>"Jean-Luc Marion, qui est mon corps ?" par MonacoInfo</t>
         </is>
       </c>
       <c r="H20" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/fazouvi-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/marion-mini.webp</t>
         </is>
       </c>
       <c r="I20" s="36" t="n"/>
       <c r="J20" s="27" t="inlineStr">
         <is>
-          <t>epistemologie</t>
+          <t>metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K20" s="27" t="inlineStr">
         <is>
-          <t>Herméneutique</t>
+          <t>Phénoménologie ; Spiritualisme</t>
         </is>
       </c>
       <c r="L20" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la philosophie moderne.</t>
+          <t>philosophe français qui se définit comme le "phénoménologiste de la donation".</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1849,11 +1847,11 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="147.75" customHeight="1" s="28">
+          <t xml:space="preserve">sens ; continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="168" customHeight="1" s="28">
       <c r="A21" s="34" t="n">
         <v>1946</v>
       </c>
@@ -1865,107 +1863,108 @@
       </c>
       <c r="D21" s="35" t="inlineStr">
         <is>
-          <t>Jean-Luc MARION</t>
+          <t>Marcel GAUCHET</t>
         </is>
       </c>
       <c r="E21" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Luc_Marion"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean Luc MARION&lt;/a&gt; est un philosophe, phénoménologue et Membre de l’Académie française depuis 2008, il est reconnu pour sa tentative d’articuler la phénoménologie et la théologie dans ce qu’on a appelé le "tournant théologique de la phénoménologie française". &lt;/p&gt; &lt;p&gt; Il se revendique de la phénoménologie de Husserl et Heidegger, tout en l’orientant vers une réflexion sur la donation (le don). Pour lui, la phénoménologie doit s’intéresser non à l’être, mais à &lt;a href="https://www.youtube.com/watch?v=oS1vVjgKJOQ"  title=" Rencontre avec Jean-Luc Marion par KTO TV"&gt;ce qui se donne&lt;/a&gt;, et même à l’excès de ce don dans ce qu’il appelle les "phénomènes saturés".​  Cette approche déplace la question classique de l’être vers celle du don, où la subjectivité se laisse surprendre par ce qui se manifeste avant toute maîtrise conceptuelle. &lt;/p&gt; &lt;p&gt; Il développe cette idée dans des ouvrages majeurs comme "Réduction et donation" (1989), "Étant donné" (1998) et "De surcroît" (2001) ou la donation devient pour lui la condition de toute phénoménalité : les phénomènes les plus profonds (amour, art, révélation divine) excèdent la capacité de la conscience à les comprendre.​ Il renouvelle également la réflexion sur l’amour. Dans "Le Phénomène érotique" (2003), il propose que le sujet ne se fonde pas sur la conscience cartésienne mais sur "l’amour reçu et donné" qui devient ainsi le lieu de la véritable certitude de soi, en continuité critique avec Descartes et sous influence de Levinas. &lt;/p&gt; &lt;p&gt; Sa philosophie conjugue trois fils essentiels : &lt;/p&gt; &lt;p&gt;une phénoménologie du don et de la révélation, où le monde se manifeste comme excès reçu. &lt;/p&gt; &lt;p&gt;une théologie philosophique, cherchant à penser Dieu hors du cadre métaphysique traditionnel. &lt;/p&gt; &lt;p&gt;une éthique de l’amour, où autrui et la relation constituent la source du sens existentiel. &lt;/p&gt; &lt;p&gt; Spécialiste éminent de Descartes (notamment Sur la théologie blanche de Descartes et Sur la métaphysique grise de Descartes), il a aussi écrit des livres plus théologiques tels que "Dieu sans l’être", "D’ailleurs, la Révélation" et a reçu de nombreuses distinctions, dont le Grand Prix de l’Académie française en 1992 et le Prix de la Principauté de Monaco en 2018. &lt;/p&gt;    &lt;audio controls title=" Jean-Luc Marion : "La philosophie c’est de la course de fond, il faut en faire tous les jours, plusieurs heures" par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-22.01.2021-ITEMA_22550575-2021C12410S0022.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F21" s="34" t="inlineStr">
-        <is>
-          <t>EAy1UbvGTe8</t>
-        </is>
-      </c>
-      <c r="G21" s="36" t="inlineStr">
-        <is>
-          <t>"Jean-Luc Marion, qui est mon corps ?" par MonacoInfo</t>
-        </is>
-      </c>
-      <c r="H21" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/marion-mini.webp</t>
-        </is>
-      </c>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="27" t="inlineStr">
-        <is>
-          <t>metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="K21" s="27" t="inlineStr">
-        <is>
-          <t>Phénoménologie ; Spiritualisme</t>
-        </is>
-      </c>
-      <c r="L21" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français qui se définit comme le "phénoménologiste de la donation".</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sens ; continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="168" customHeight="1" s="28">
-      <c r="A22" s="34" t="n">
-        <v>1946</v>
-      </c>
-      <c r="B22" s="34" t="n"/>
-      <c r="C22" s="34" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
-      </c>
-      <c r="D22" s="35" t="inlineStr">
-        <is>
-          <t>Marcel GAUCHET</t>
-        </is>
-      </c>
-      <c r="E22" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcel_Gauchet"  title=" Wikipedia"&gt;Marcel GAUCHET&lt;/a&gt;  est un philosophe, historien et sociologue  français connu pour ses travaux sur, &lt;a href="https://www.youtube.com/watch?v=48xW06Mm7JM&amp;t=4s "  title="Comment expliquer la crise de nos démocraties ? L'analyse de Marcel Gauchet par Le figaro"&gt;la démocratie&lt;/a&gt;, la religion et la sécularisation de l’Occident. Son œuvre cherche à comprendre les conditions politiques et culturelles qui permettent l’émergence et le fonctionnement des démocraties modernes, en particulier à partir du passage d’une société organique et religieuse à une société démocratique laïque. &lt;/p&gt; &lt;p&gt;  Il est une figure centrale du, &lt;a href="https://www.youtube.com/watch?v=Stn5k6P-uI8"  title="Marcel Gauchet, une pensée qui fâche ? par France Culture"&gt;paysage intellectuel &lt;/a&gt; français, dont les positions sur la “fin de la religion” et la démocratie ont suscité des débats et parfois des critiques, notamment autour de son oriention perçue par certains comme néoréactionnaire, qu’il réfute. Une de ses oeuvres marquantes est : "Le Désenchantement du monde" paru en 1985 – ouvrage majeur sur la sécularisation et le déclin de l’emprise de la religion dans les sociétés occidentales. &lt;/p&gt; &lt;p&gt; La démocratie moderne naît dans le cadre d’un processus historique complexe où l’émergence de l’individu et la réduction du rôle monopoly de la religion transforment les bases de l’autorité et de la légitimité politique. La religion, loin d’être annihilée, se transforme en une “religion de la sortie de la religion” qui structure encore les attentes morales et citoyennes, même lorsque l’emprise institutionnelle recule. &lt;/p&gt; &lt;p&gt; L’équilibre entre autonomie de l’individu et cohésion sociale demeure un défi central de la démocratie contemporaine, d’où l’attention soutenue de Gauchet pour les “fratures” et les tensions entre pluralisme démocratique et exigences communautaires.
  &lt;/p&gt;   &lt;audio controls title="Marcel Gauchet : "C'est l'exigence de comprendre mon temps qui m'a conduit à une réflexion sur l'histoire, en philosophe" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11189-30.05.2011-ITEMA_20288351-2011C15000E0083-ITE_00042075_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>x4-aqLQFgns</t>
+        </is>
+      </c>
+      <c r="G21" s="36" t="inlineStr">
+        <is>
+          <t>"Pourquoi la société S’EFFONDRE ? - Marcel Gauchet" par Penser c'est chouette Extraits</t>
+        </is>
+      </c>
+      <c r="H21" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/gauchet-mini.webp</t>
+        </is>
+      </c>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="27" t="inlineStr">
+        <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K21" s="27" t="inlineStr">
+        <is>
+          <t>Constructivisme</t>
+        </is>
+      </c>
+      <c r="L21" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français connu pour ses travaux sur la religion, les droits de l'homme &amp;amp; la démocratie.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="193.5" customHeight="1" s="28">
+      <c r="A22" s="34" t="n">
+        <v>1947</v>
+      </c>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>Dany-Robert DUFOUR</t>
+        </is>
+      </c>
+      <c r="E22" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dany-Robert_Dufour"  title=" Wikipedia"&gt;Dany-Robert DUFOUR&lt;/a&gt; est un philosophe français  principalement connu pour ses analyses critiques du  &lt;a href="https://www.youtube.com/watch?v=P7_LuqNO0Zg"  title=" CAPITALISME, Dany-Robert Dufour par abc penser"&gt;capitalisme néolibéral&lt;/a&gt; et ses réflexions sur les systèmes symboliques, à l’intersection de la philosophie politique, du langage et de la psychanalyse. Il travaille à l'Université de Paris et dans d'autres pays tels que le Brésil, le Mexique et la Colombie. &lt;/p&gt; &lt;p&gt; 
+Le thème principal de ses œuvres est le sujet de la société postmoderne et les problèmes auxquels il est confronté. Dans &lt;a href="http://www.dany-robert-dufour.fr/" title="Robert Dufour "&gt;ses œuvres&lt;/a&gt; "Le Divin Marché",  "La révolution culturelle libérale" et  "La cité perverse - libéralisme et pornographie", le philosophe défend que la société contemporaine est basée sur des &lt;a href="https://www.youtube.com/watch?v=xUT0q2sk3lc" title=" Le phénomène trans I Dany Robert Dufour par Cercle Aristote"&gt; principes amoraux&lt;/a&gt; et que la crise culturelle a rendu possible des crises économiques comme celle de 2008. La société moderne a évolué de manière alarmante et le sujet n’a pas de modèles ou de leaders. Il propose une lecture radicale et engagée de l’évolution culturelle et politique contemporaine, interrogeant la place des symboles et la crise du sens à l’ère du capitalisme mondialisé.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.actu-philosophia.com/entretien-avec-dany-robert-dufour/"  title="Entretien avec Dany-Robert Dufour par actu philosopphia"&gt;  Sa réflexion&lt;/a&gt; s’inscrit dans une critique du structuralisme et du post-structuralisme, qu’il analyse comme favorisant la désymbolisation et un affaiblissement des repères pour la société.​ Il développe une pensée du "Tiers symbolique", considérant que toute relation entre deux termes (ex : sujet/objet) suppose un tiers pour garantir sens et cohésion, contrairement à la logique binaire des systèmes et des algorithmes contemporains.​​ &lt;/p&gt; &lt;p&gt;  Il propose une lecture critique du néolibéralisme, en montrant comment il affecte les subjectivités et les structures symboliques collectives, par une "illimitation du désir" et une apologie de l’individualisme sans limite.​ Il explore l’histoire de la philosophie et ses incidences sur l’époque contemporaine, avec un intérêt pour l’économie, la linguistique, la psychanalyse et la politique. &lt;/p&gt; &lt;audio controls title=" De la transgression à la perversion par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-10.01.2024-ITEMA_23609669-2024C48904S0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>x4-aqLQFgns</t>
+          <t>-C0vlfEIXgw</t>
         </is>
       </c>
       <c r="G22" s="36" t="inlineStr">
         <is>
-          <t>"Pourquoi la société S’EFFONDRE ? - Marcel Gauchet" par Penser c'est chouette Extraits</t>
+          <t>"ON A CONFIÉ LE DESTIN DU MONDE AUX PERVERS - Dany-Robert Dufour" par ECLUCID</t>
         </is>
       </c>
       <c r="H22" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/gauchet-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/dufour-mini.webp</t>
         </is>
       </c>
       <c r="I22" s="36" t="n"/>
       <c r="J22" s="27" t="inlineStr">
         <is>
-          <t>politique ; epistemologie</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K22" s="27" t="inlineStr">
         <is>
-          <t>Constructivisme</t>
+          <t>Théorie Critique</t>
         </is>
       </c>
       <c r="L22" s="27" t="inlineStr">
         <is>
-          <t>philosophe français connu pour ses travaux sur la religion, les droits de l'homme &amp;amp; la démocratie.</t>
+          <t>philosophe français du langage, de la sémiologie et de la philosophie politique.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1975,11 +1974,11 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="193.5" customHeight="1" s="28">
+          <t xml:space="preserve">critique ; continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="189" customHeight="1" s="28">
       <c r="A23" s="34" t="n">
         <v>1947</v>
       </c>
@@ -1991,44 +1990,49 @@
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>Dany-Robert DUFOUR</t>
-        </is>
-      </c>
-      <c r="E23" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dany-Robert_Dufour"  title=" Wikipedia"&gt;Dany-Robert DUFOUR&lt;/a&gt; est un philosophe français  principalement connu pour ses analyses critiques du  &lt;a href="https://www.youtube.com/watch?v=P7_LuqNO0Zg"  title=" CAPITALISME, Dany-Robert Dufour par abc penser"&gt;capitalisme néolibéral&lt;/a&gt; et ses réflexions sur les systèmes symboliques, à l’intersection de la philosophie politique, du langage et de la psychanalyse. Il travaille à l'Université de Paris et dans d'autres pays tels que le Brésil, le Mexique et la Colombie. &lt;/p&gt; &lt;p&gt; 
-Le thème principal de ses œuvres est le sujet de la société postmoderne et les problèmes auxquels il est confronté. Dans &lt;a href="http://www.dany-robert-dufour.fr/" title="Robert Dufour "&gt;ses œuvres&lt;/a&gt; "Le Divin Marché",  "La révolution culturelle libérale" et  "La cité perverse - libéralisme et pornographie", le philosophe défend que la société contemporaine est basée sur des &lt;a href="https://www.youtube.com/watch?v=xUT0q2sk3lc" title=" Le phénomène trans I Dany Robert Dufour par Cercle Aristote"&gt; principes amoraux&lt;/a&gt; et que la crise culturelle a rendu possible des crises économiques comme celle de 2008. La société moderne a évolué de manière alarmante et le sujet n’a pas de modèles ou de leaders. Il propose une lecture radicale et engagée de l’évolution culturelle et politique contemporaine, interrogeant la place des symboles et la crise du sens à l’ère du capitalisme mondialisé.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.actu-philosophia.com/entretien-avec-dany-robert-dufour/"  title="Entretien avec Dany-Robert Dufour par actu philosopphia"&gt;  Sa réflexion&lt;/a&gt; s’inscrit dans une critique du structuralisme et du post-structuralisme, qu’il analyse comme favorisant la désymbolisation et un affaiblissement des repères pour la société.​ Il développe une pensée du "Tiers symbolique", considérant que toute relation entre deux termes (ex : sujet/objet) suppose un tiers pour garantir sens et cohésion, contrairement à la logique binaire des systèmes et des algorithmes contemporains.​​ &lt;/p&gt; &lt;p&gt;  Il propose une lecture critique du néolibéralisme, en montrant comment il affecte les subjectivités et les structures symboliques collectives, par une "illimitation du désir" et une apologie de l’individualisme sans limite.​ Il explore l’histoire de la philosophie et ses incidences sur l’époque contemporaine, avec un intérêt pour l’économie, la linguistique, la psychanalyse et la politique. &lt;/p&gt; &lt;audio controls title=" De la transgression à la perversion par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-10.01.2024-ITEMA_23609669-2024C48904S0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t>Barbara CASSIN</t>
+        </is>
+      </c>
+      <c r="E23" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Cassin"  title=" Wikipedia"&gt;Barbara CASSIN&lt;/a&gt;  est une philosophe française spécialiste des Grecs anciens, elle a dirigé le Centre Léon Robin et a été élue à l'Académie française en 2018 au fauteuil 36. Marquée par Heidegger, Jean Beaufret et Pierre Aubenque, elle a aussi exploré la psychanalyse avec Jacques-Alain Miller avant de se consacrer à la philosophie grecque, à la rhétorique et à la traduction.&lt;/p&gt; &lt;p&gt; Sa philosophie met au centre le &lt;a href="https://www.youtube.com/watch?v=lUyWiyTs0fQ"  title="Barbara Cassin et la performativité du langage par France Culture"&gt;  pouvoir du langage &lt;/a&gt;  et des mots comme actes performatifs. Contre l’universalisme abstrait, elle défend les sophistes contre Platon, montrant que la vérité philosophique est un « effet sophistique » produit par le discours, et non une essence immobile. Chez elle, la sophistique n’est pas une ruse relativiste, mais une mesure du vrai qui reconnaît la pluralité des logoi et refuse l’exclusion de la différence. &lt;/p&gt; &lt;p&gt; Un pilier de son œuvre est la traduction comme philosophie pratique : directrice du Vocabulaire européen des philosophies (ou Dictionnaire des intraduisibles), elle révèle comment les mots philosophiques portent des « intraduisibles » qui forcent à penser les singularités culturelles sans les réduire à un sens unique. Cette approche culmine dans des projets comme l’exposition Après Babel, traduire, où elle propose la traduction comme « savoir-faire avec les différences », base d’une citoyenneté plurielle et hospitalière. &lt;/p&gt; &lt;p&gt; Engagée pour les humanités et le féminisme, elle critique l’universel masculin et prône une philosophie « autrement présocratique », ancrée dans le multiple et l’aventure du sens. Ses livres comme L’Effet sophistique, Éloge de la traduction ou Quand dire, c’est vraiment faire articulent Antiquité et contemporanéité, du plurilinguisme à la post-vérité. Médaille d’or du CNRS en 2018, elle incarne &lt;a href="https://www.youtube.com/watch?v=ajoe7wbg8nM"  title="Barbara Cassin  par le mans Université"&gt; une pensée vivante, &lt;/a&gt;  ouverte aux autres savoirs et aux défis du monde global.&lt;/p&gt;                       &lt;audio controls title=" barbara cassin, reconstruire autour de l’Odysée par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13983-16.05.2025-ITEMA_24136893-2025C16450S0136-NET_MFC_1B916F0B-9492-4EAD-9A15-47D5E0E4646C-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>-C0vlfEIXgw</t>
+          <t>ZAP3Ygbh_40</t>
         </is>
       </c>
       <c r="G23" s="36" t="inlineStr">
         <is>
-          <t>"ON A CONFIÉ LE DESTIN DU MONDE AUX PERVERS - Dany-Robert Dufour" par ECLUCID</t>
+          <t>"La philologue Barbara Cassin panse le monde avec le langage - La Terre au carré" par France Inter</t>
         </is>
       </c>
       <c r="H23" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/dufour-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/bcassin-mini.webp</t>
         </is>
       </c>
       <c r="I23" s="36" t="n"/>
       <c r="J23" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>epistemologie ; langage</t>
         </is>
       </c>
       <c r="K23" s="27" t="inlineStr">
         <is>
-          <t>Théorie Critique</t>
+          <t>Analytique ; Herméneutique</t>
         </is>
       </c>
       <c r="L23" s="27" t="inlineStr">
         <is>
-          <t>philosophe français du langage, de la sémiologie et de la philosophie politique.</t>
+          <t>philosophe française spécialiste des Grecs anciens.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2038,65 +2042,59 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">critique ; continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="189" customHeight="1" s="28">
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="147.75" customHeight="1" s="28">
       <c r="A24" s="34" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B24" s="34" t="n"/>
       <c r="C24" s="34" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>Barbara CASSIN</t>
-        </is>
-      </c>
-      <c r="E24" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Cassin"  title=" Wikipedia"&gt;Barbara CASSIN&lt;/a&gt;  est une philosophe française spécialiste des Grecs anciens, elle a dirigé le Centre Léon Robin et a été élue à l'Académie française en 2018 au fauteuil 36. Marquée par Heidegger, Jean Beaufret et Pierre Aubenque, elle a aussi exploré la psychanalyse avec Jacques-Alain Miller avant de se consacrer à la philosophie grecque, à la rhétorique et à la traduction.&lt;/p&gt; &lt;p&gt; Sa philosophie met au centre le &lt;a href="https://www.youtube.com/watch?v=lUyWiyTs0fQ"  title="Barbara Cassin et la performativité du langage par France Culture"&gt;  pouvoir du langage &lt;/a&gt;  et des mots comme actes performatifs. Contre l’universalisme abstrait, elle défend les sophistes contre Platon, montrant que la vérité philosophique est un « effet sophistique » produit par le discours, et non une essence immobile. Chez elle, la sophistique n’est pas une ruse relativiste, mais une mesure du vrai qui reconnaît la pluralité des logoi et refuse l’exclusion de la différence. &lt;/p&gt; &lt;p&gt; Un pilier de son œuvre est la traduction comme philosophie pratique : directrice du Vocabulaire européen des philosophies (ou Dictionnaire des intraduisibles), elle révèle comment les mots philosophiques portent des « intraduisibles » qui forcent à penser les singularités culturelles sans les réduire à un sens unique. Cette approche culmine dans des projets comme l’exposition Après Babel, traduire, où elle propose la traduction comme « savoir-faire avec les différences », base d’une citoyenneté plurielle et hospitalière. &lt;/p&gt; &lt;p&gt; Engagée pour les humanités et le féminisme, elle critique l’universel masculin et prône une philosophie « autrement présocratique », ancrée dans le multiple et l’aventure du sens. Ses livres comme L’Effet sophistique, Éloge de la traduction ou Quand dire, c’est vraiment faire articulent Antiquité et contemporanéité, du plurilinguisme à la post-vérité. Médaille d’or du CNRS en 2018, elle incarne &lt;a href="https://www.youtube.com/watch?v=ajoe7wbg8nM"  title="Barbara Cassin  par le mans Université"&gt; une pensée vivante, &lt;/a&gt;  ouverte aux autres savoirs et aux défis du monde global.&lt;/p&gt;                       &lt;audio controls title=" barbara cassin, reconstruire autour de l’Odysée par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13983-16.05.2025-ITEMA_24136893-2025C16450S0136-NET_MFC_1B916F0B-9492-4EAD-9A15-47D5E0E4646C-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t>Pascal BRUCKNER</t>
+        </is>
+      </c>
+      <c r="E24" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Bruckner"  title=" Wikipedia"&gt;Pascal BRUCKNER&lt;/a&gt; (né en 1948) est un philosophe, essayiste et romancier français, membre de l’Académie Goncourt depuis 2019. Il se fait connaître en 1977 avec &lt;em&gt;Le Nouveau Désordre amoureux&lt;/em&gt;, écrit avec Alain Finkielkraut, une critique des utopies sexuelles nées de Mai 68, qui l’associe à la génération des « nouveaux philosophes ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Sanglot de l’homme blanc&lt;/em&gt; (1983), il critique le tiers-mondisme, qui selon lui idéalise les pays du Sud et entretient chez les Occidentaux une culpabilité stérile. Ce thème de la mauvaise conscience occidentale traverse son œuvre : dans &lt;em&gt;La Tyrannie de la pénitence&lt;/em&gt; (2006), il dénonce ce qu’il appelle &lt;a href="https://www.revuedesdeuxmondes.fr/pascal-bruckner-declinisme-et-catastrophisme-provoquent-des-ravages-dans-nos-esprits/" title="Pascal Bruckner : Déclinisme et catastrophisme provoquent des ravages dans nos esprits par Revue des deux mondes"&gt;l’auto-flagellation&lt;/a&gt; de l’Europe, qui l’empêcherait de défendre ses propres valeurs. Il s’en prend aussi à certaines tendances de la société contemporaine. &lt;em&gt;La Tentation de l’innocence&lt;/em&gt; (1995), prix Médicis de l’essai, décrit un individu qui fuit ses responsabilités en se réfugiant dans l’enfance ou dans le statut de victime. &lt;em&gt;L’Euphorie perpétuelle&lt;/em&gt; (2000) critique l’obligation moderne d’être heureux, et &lt;em&gt;Le Fanatisme de l’apocalypse&lt;/em&gt; (2011) le catastrophisme d’une partie de l’écologie. Plus récemment, il a critiqué les &lt;a href="https://www.youtube.com/watch?v=wNrAmA6zIQU"  title="L’homme blanc, de l’intouchable au bouc émissaire avec Pascal Bruckner par France Culture"&gt;idéologies&lt;/a&gt; qui font de « l’homme blanc » un coupable désigné. Défenseur de l’héritage des Lumières, de l’universalisme et de la démocratie libérale, il est souvent classé parmi les intellectuels libéraux et atlantistes, et ses positions suscitent de vifs débats.&lt;/p&gt; &lt;p&gt;Romancier, il est aussi l’auteur de &lt;em&gt;Lunes de fiel&lt;/em&gt; (1981), adapté au cinéma par Roman Polanski.&lt;/p&gt;  &lt;audio controls title="Pascal Bruckner, au fil de la plume par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-06.06.2021-ITEMA_22685386-2021C3500E0081.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>ZAP3Ygbh_40</t>
+          <t>NryZ_QEqLTc</t>
         </is>
       </c>
       <c r="G24" s="36" t="inlineStr">
         <is>
-          <t>"La philologue Barbara Cassin panse le monde avec le langage - La Terre au carré" par France Inter</t>
+          <t>"Pascal Bruckner, La sagesse de l'argent" par La Grande Librairie</t>
         </is>
       </c>
       <c r="H24" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/bcassin-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/bruckner-mini.webp</t>
         </is>
       </c>
       <c r="I24" s="36" t="n"/>
       <c r="J24" s="27" t="inlineStr">
         <is>
-          <t>epistemologie ; langage</t>
+          <t>ethique ; politique</t>
         </is>
       </c>
       <c r="K24" s="27" t="inlineStr">
         <is>
-          <t>Analytique ; Herméneutique</t>
+          <t xml:space="preserve">Libéralisme</t>
         </is>
       </c>
       <c r="L24" s="27" t="inlineStr">
         <is>
-          <t>philosophe française spécialiste des Grecs anciens.</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français critique de l'auto-flagellation occidentale et du tiers-mondisme culpabilisant.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2104,13 +2102,14 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="O24"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="147.75" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="178.5" customHeight="1" s="28">
       <c r="A25" s="34" t="n">
         <v>1948</v>
       </c>
@@ -2122,113 +2121,112 @@
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>Pascal BRUCKNER</t>
-        </is>
-      </c>
-      <c r="E25" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Bruckner"  title=" Wikipedia"&gt;Pascal BRUCKNER&lt;/a&gt; (né en 1948) est un philosophe, essayiste et romancier français, membre de l’Académie Goncourt depuis 2019. Il se fait connaître en 1977 avec &lt;em&gt;Le Nouveau Désordre amoureux&lt;/em&gt;, écrit avec Alain Finkielkraut, une critique des utopies sexuelles nées de Mai 68, qui l’associe à la génération des « nouveaux philosophes ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Le Sanglot de l’homme blanc&lt;/em&gt; (1983), il critique le tiers-mondisme, qui selon lui idéalise les pays du Sud et entretient chez les Occidentaux une culpabilité stérile. Ce thème de la mauvaise conscience occidentale traverse son œuvre : dans &lt;em&gt;La Tyrannie de la pénitence&lt;/em&gt; (2006), il dénonce ce qu’il appelle &lt;a href="https://www.revuedesdeuxmondes.fr/pascal-bruckner-declinisme-et-catastrophisme-provoquent-des-ravages-dans-nos-esprits/" title="Pascal Bruckner : Déclinisme et catastrophisme provoquent des ravages dans nos esprits par Revue des deux mondes"&gt;l’auto-flagellation&lt;/a&gt; de l’Europe, qui l’empêcherait de défendre ses propres valeurs. Il s’en prend aussi à certaines tendances de la société contemporaine. &lt;em&gt;La Tentation de l’innocence&lt;/em&gt; (1995), prix Médicis de l’essai, décrit un individu qui fuit ses responsabilités en se réfugiant dans l’enfance ou dans le statut de victime. &lt;em&gt;L’Euphorie perpétuelle&lt;/em&gt; (2000) critique l’obligation moderne d’être heureux, et &lt;em&gt;Le Fanatisme de l’apocalypse&lt;/em&gt; (2011) le catastrophisme d’une partie de l’écologie. Plus récemment, il a critiqué les &lt;a href="https://www.youtube.com/watch?v=wNrAmA6zIQU"  title="L’homme blanc, de l’intouchable au bouc émissaire avec Pascal Bruckner par France Culture"&gt;idéologies&lt;/a&gt; qui font de « l’homme blanc » un coupable désigné. Défenseur de l’héritage des Lumières, de l’universalisme et de la démocratie libérale, il est souvent classé parmi les intellectuels libéraux et atlantistes, et ses positions suscitent de vifs débats.&lt;/p&gt; &lt;p&gt;Romancier, il est aussi l’auteur de &lt;em&gt;Lunes de fiel&lt;/em&gt; (1981), adapté au cinéma par Roman Polanski.&lt;/p&gt;  &lt;audio controls title="Pascal Bruckner, au fil de la plume par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-06.06.2021-ITEMA_22685386-2021C3500E0081.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F25" s="34" t="inlineStr">
-        <is>
-          <t>NryZ_QEqLTc</t>
-        </is>
-      </c>
-      <c r="G25" s="36" t="inlineStr">
-        <is>
-          <t>"Pascal Bruckner, La sagesse de l'argent" par La Grande Librairie</t>
-        </is>
-      </c>
-      <c r="H25" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/bruckner-mini.webp</t>
-        </is>
-      </c>
-      <c r="I25" s="36" t="n"/>
-      <c r="J25" s="27" t="inlineStr">
-        <is>
-          <t>ethique ; politique</t>
-        </is>
-      </c>
-      <c r="K25" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme</t>
-        </is>
-      </c>
-      <c r="L25" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français critique de l'auto-flagellation occidentale et du tiers-mondisme culpabilisant.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O25"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="178.5" customHeight="1" s="28">
-      <c r="A26" s="34" t="n">
-        <v>1948</v>
-      </c>
-      <c r="B26" s="34" t="n"/>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
           <t>Laurence HANSEN-LOVE</t>
         </is>
       </c>
-      <c r="E26" s="41" t="inlineStr">
+      <c r="E25" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Laurence_Hansen-L%C3%B8ve"  title=" Wikipedia"&gt;Laurence HANSEN-LOVE&lt;/a&gt;  est une philosophe française  auteure d'essais sur la morale et la politique contemporaines. Diplômée de la Sorbonne, elle a enseigné en classes préparatoires et à Sciences Po Paris, avant de devenir chargée de cours à l'IPESUP. Mère de la cinéaste Mia Hansen-Løve et du musicien Sven Løve, elle est reconnue pour ses ouvrages accessibles destinés aux lycéens et étudiants, comme la direction de La Philosophie de A à Z. &lt;/p&gt; &lt;p&gt; Sa carrière éditoriale est riche : elle a co-dirigé Ce que la philosophie doit aux femmes (2024) avec Laurence Devillairs, mettant en lumière les contributions oubliées des penseuses comme Hypatie ou Hannah Arendt. Elle a publié des manuels tels que Cours particulier de philosophie (2006) et La philosophie comme un roman (2014), ainsi que des essais comme Oublier le bien, nommer le mal (2016) et Planète en ébullition (2022), qui explorent l'éthique face aux crises actuelles. &lt;/p&gt; &lt;p&gt; &lt;a href="https://hansenlove.over-blog.com/"  title=" Hansen-Love" &gt;Sa  philosophie &lt;/a&gt; porte sur l'éthique politique, où elle argue qu'un consensus universel sur le "bien" est impossible, mais que "nommer le mal" – via des valeurs et interdits partagés – permet d'agir collectivement. Elle critique la violence humaine sans désespérer de l'humanité, prônant une recherche d'un "monde commun" contre les excès. &lt;/p&gt; &lt;p&gt; Ses travaux récents intègrent l'écologie philosophique, relisant l'histoire de la pensée occidentale (de l'Antiquité à aujourd'hui) pour questionner la séparation nature/culture et l'hubris humaine. Dans Planète en ébullition, elle défend &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cof%C3%A9minisme"  title=" écofeminisme par Wikipedia&gt;l'écoféminisme, &lt;/a&gt;  une éthique du respect de la phusis grecque comme processus vital, et lie protection environnementale à une critique du capitalisme, sans séparer humain et nature. &lt;/p&gt;
  &lt;audio controls title="Laurence Hansen-Love; le mal , ce n’est pas satan, c’est le coeur des hommes par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16602-16.12.2016-ITEMA_21167806-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>jSeAjRmNIOo</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>"La société doit-elle compter sur les philosophes pour lutter contre le mal ?" par joel landry mvoa</t>
+        </is>
+      </c>
+      <c r="H25" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/llove-mini.webp</t>
+        </is>
+      </c>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="27" t="inlineStr">
+        <is>
+          <t>epistemologie ; ethique</t>
+        </is>
+      </c>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>Analytique</t>
+        </is>
+      </c>
+      <c r="L25" s="27" t="inlineStr">
+        <is>
+          <t>philosophe française auteure d'essais sur la morale et la politique contemporaines.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="210.75" customHeight="1" s="28">
+      <c r="A26" s="34" t="n">
+        <v>1949</v>
+      </c>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>Christian JAMBET</t>
+        </is>
+      </c>
+      <c r="E26" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Jambet"  title=" Wikipedia"&gt;Christian JAMBET&lt;/a&gt; est un philosophe et islamologue  français reconnu pour ses travaux qui font le pont entre la philosophie occidentale et la pensée islamique, en particulier le chiisme. Agrégé de philosophie et ancien élève d'Henry Corbin, un spécialiste de &lt;a href="https://fr.wikipedia.org/wiki/Islam_en_Iran"  title=" Islam en Iran par Wikipedia"&gt;l'islam iranien&lt;/a&gt;, il a consacré sa carrière à l'étude des traditions philosophiques et spirituelles de l'Islam, notamment celles de l'Iran. Il est devenu membre de l'Académie française en 2024. Son travail se distingue par sa profondeur et son caractère interdisciplinaire. Ses contributions majeures portent sur :&lt;/p&gt; &lt;p&gt;La philosophie islamique : Il a montré qu'il existe une tradition philosophique riche et autonome en terre d'Islam, souvent mal comprise ou négligée en Occident. Il a mis en lumière les liens, mais aussi les spécificités, entre la pensée grecque (notamment platonicienne) et les penseurs islamiques. Son ouvrage Qu'est-ce que la philosophie islamique ? est une référence dans ce domaine. &lt;/p&gt; &lt;p&gt;Le chiisme et le soufisme : il est un expert du chiisme, qu'il étudie non seulement sous son aspect politique et théologique, mais aussi dans sa dimension philosophique et spirituelle. Il a beaucoup travaillé sur la figure du  &lt;a href="https://www.youtube.com/watch?v=kQzLVldS4PU"  title="L'immortalité de l'âme selon Mulla Sadra, Christian Jambet Les vivants et les dieux par Facteur"&gt; philosophe iranien Mullâ Sadrâ Shîrâzî&lt;/a&gt;, qu'il considère comme un des plus grands métaphysiciens de l'histoire. Il explore les concepts de l'ésotérisme (bātin) et de l'exotérisme (zahir), montrant comment la philosophie chiite a développé une pensée de la liberté et de l'intériorité face à l'orthodoxie religieuse. &lt;/p&gt; &lt;p&gt;La philosophie politique : Il s'intéresse aux conceptions du pouvoir et du droit dans l'Islam. Dans son livre Le gouvernement divin, il analyse la relation entre la théologie et le politique, et les différentes manières dont le pouvoir a été conceptualisé dans le chiisme. &lt;/p&gt; &lt;p&gt;Les concepts de l'« Ange » et de l'« imagination créatrice » : Reprenant les travaux d'Henry Corbin, il a exploré le rôle central de l'imagination dans la connaissance et l'expérience religieuse. Pour Jambet, l'imagination n'est pas une simple faculté de fiction, mais un organe de perception capable d'accéder à un monde intermédiaire, peuplé d'êtres spirituels comme les Anges. &lt;/p&gt; &lt;p&gt;  Il a publié différents ouvrages dont "L'Ange" paru en 1976 co-écrit avec Guy Lardreau ainsi que "La Logique des Orientaux"  paru en 1983  sans oublié "La Grande Résurrection d'Alamût"  paru en 1990, sur les formes de la liberté dans le shî'isme ismaélien. &lt;/p&gt;  &lt;audio controls title=" La philosophie islamique avec Christian Jambet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-12.02.2012-ITEMA_20344279-2012C14958E0004-ITE_00049063_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>jSeAjRmNIOo</t>
+          <t>bWd541tiPqU</t>
         </is>
       </c>
       <c r="G26" s="36" t="inlineStr">
         <is>
-          <t>"La société doit-elle compter sur les philosophes pour lutter contre le mal ?" par joel landry mvoa</t>
+          <t xml:space="preserve">"Exotérisme et ésotérisme" par Baglis Tv</t>
         </is>
       </c>
       <c r="H26" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/llove-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/jambet-mini.webp</t>
         </is>
       </c>
       <c r="I26" s="36" t="n"/>
       <c r="J26" s="27" t="inlineStr">
         <is>
-          <t>epistemologie ; ethique</t>
+          <t>spiritualite ; metaphysique</t>
         </is>
       </c>
       <c r="K26" s="27" t="inlineStr">
         <is>
-          <t>Analytique</t>
+          <t>Ishraqisme ; Soufisme</t>
         </is>
       </c>
       <c r="L26" s="27" t="inlineStr">
         <is>
-          <t>philosophe française auteure d'essais sur la morale et la politique contemporaines.</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français spécialiste de la pensée islamique et en particulier le chiisme.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2238,11 +2236,11 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="210.75" customHeight="1" s="28">
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="158.25" customHeight="1" s="28">
       <c r="A27" s="34" t="n">
         <v>1949</v>
       </c>
@@ -2254,43 +2252,49 @@
       </c>
       <c r="D27" s="35" t="inlineStr">
         <is>
-          <t>Christian JAMBET</t>
-        </is>
-      </c>
-      <c r="E27" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Jambet"  title=" Wikipedia"&gt;Christian JAMBET&lt;/a&gt; est un philosophe et islamologue  français reconnu pour ses travaux qui font le pont entre la philosophie occidentale et la pensée islamique, en particulier le chiisme. Agrégé de philosophie et ancien élève d'Henry Corbin, un spécialiste de &lt;a href="https://fr.wikipedia.org/wiki/Islam_en_Iran"  title=" Islam en Iran par Wikipedia"&gt;l'islam iranien&lt;/a&gt;, il a consacré sa carrière à l'étude des traditions philosophiques et spirituelles de l'Islam, notamment celles de l'Iran. Il est devenu membre de l'Académie française en 2024. Son travail se distingue par sa profondeur et son caractère interdisciplinaire. Ses contributions majeures portent sur :&lt;/p&gt; &lt;p&gt;La philosophie islamique : Il a montré qu'il existe une tradition philosophique riche et autonome en terre d'Islam, souvent mal comprise ou négligée en Occident. Il a mis en lumière les liens, mais aussi les spécificités, entre la pensée grecque (notamment platonicienne) et les penseurs islamiques. Son ouvrage Qu'est-ce que la philosophie islamique ? est une référence dans ce domaine. &lt;/p&gt; &lt;p&gt;Le chiisme et le soufisme : il est un expert du chiisme, qu'il étudie non seulement sous son aspect politique et théologique, mais aussi dans sa dimension philosophique et spirituelle. Il a beaucoup travaillé sur la figure du  &lt;a href="https://www.youtube.com/watch?v=kQzLVldS4PU"  title="L'immortalité de l'âme selon Mulla Sadra, Christian Jambet Les vivants et les dieux par Facteur"&gt; philosophe iranien Mullâ Sadrâ Shîrâzî&lt;/a&gt;, qu'il considère comme un des plus grands métaphysiciens de l'histoire. Il explore les concepts de l'ésotérisme (bātin) et de l'exotérisme (zahir), montrant comment la philosophie chiite a développé une pensée de la liberté et de l'intériorité face à l'orthodoxie religieuse. &lt;/p&gt; &lt;p&gt;La philosophie politique : Il s'intéresse aux conceptions du pouvoir et du droit dans l'Islam. Dans son livre Le gouvernement divin, il analyse la relation entre la théologie et le politique, et les différentes manières dont le pouvoir a été conceptualisé dans le chiisme. &lt;/p&gt; &lt;p&gt;Les concepts de l'« Ange » et de l'« imagination créatrice » : Reprenant les travaux d'Henry Corbin, il a exploré le rôle central de l'imagination dans la connaissance et l'expérience religieuse. Pour Jambet, l'imagination n'est pas une simple faculté de fiction, mais un organe de perception capable d'accéder à un monde intermédiaire, peuplé d'êtres spirituels comme les Anges. &lt;/p&gt; &lt;p&gt;  Il a publié différents ouvrages dont "L'Ange" paru en 1976 co-écrit avec Guy Lardreau ainsi que "La Logique des Orientaux"  paru en 1983  sans oublié "La Grande Résurrection d'Alamût"  paru en 1990, sur les formes de la liberté dans le shî'isme ismaélien. &lt;/p&gt;  &lt;audio controls title=" La philosophie islamique avec Christian Jambet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-12.02.2012-ITEMA_20344279-2012C14958E0004-ITE_00049063_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t>Bernadette BENSAUDE-VINCENT</t>
+        </is>
+      </c>
+      <c r="E27" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernadette_Bensaude-Vincent" title=" Wikipedia"&gt;Bernadette BENSUDE-VINCENT&lt;/a&gt;  est une philosophe française et historienne des sciences. Formée à l'École normale supérieure de Fontenay-aux-Roses, agrégée de philosophie en 1971 et docteure ès lettres en 1981, elle a enseigné à l'université Paris X-Nanterre puis Paris I Panthéon-Sorbonne jusqu'à sa retraite en 2015, où elle est professeure émérite. Elle a dirigé le Centre d'études des techniques, des connaissances et des pratiques (CETCOPRA) et été membre senior de l'Institut universitaire de France. &lt;/p&gt; &lt;p&gt; Elle a occupé des postes invités dans des universités internationales comme Madrid, Vienne ou Bielefeld, et collaboré avec le MIT sur l'histoire des matériaux. Membre de l'Académie des technologies et vice-présidente du comité d'éthique d'organismes comme l'Inrae, elle a contribué à la Cité des sciences et de l'industrie. Auteure d'une centaine d'ouvrages, elle a coordonné des programmes sur l'éthique des nanotechnologies et les technosciences. &lt;/p&gt; &lt;p&gt; Sa pensée critique la rupture bachelardienne entre science et opinion, plaidant pour leur interdépendance dans une "philosophie de terrain". Elle analyse la chimie, les technosciences et les technologies émergentes comme des pratiques sociales façonnant la matière, questionnant le pouvoir des sciences sur le vivant et la société. Elle rejette &lt;a href="https://www.youtube.com/watch?v=MRD0LLrjGG8"  title="bernadette bensaude-vincent : approche philo de la biologie de synthese par Alter Mardis"&gt;les visions réductionnistes &lt;/a&gt; pour souligner les controverses et la pluralité des savoirs. &lt;/p&gt; &lt;p&gt; Dans des essais comme L’Opinion publique et la science ou ses réflexions sur l'Anthropocène, elle promeut une "culture de la défiance" constructive contre la méfiance, favorisant des savoirs robustes. Ses recherches sur les matériaux et la biologie de synthèse interrogent l'hubris humaine, défendant une  &lt;a href="https://www.youtube.com/watch?v=HnEX-2_p3mQ"  title="bernadette bensaude-vincent : fait il changer notre rapport au temps par écologie rationnelle"&gt;approche humaniste &lt;/a&gt; des relations science-société et une histoire des sciences attentive aux marges. &lt;/p&gt;    &lt;audio controls title=" Science et recherche: de l’expertise à la sphère publique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13983-28.04.2021-ITEMA_22649821-2021C16450S0118.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>bWd541tiPqU</t>
+          <t>uBV5yWbIATY</t>
         </is>
       </c>
       <c r="G27" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Exotérisme et ésotérisme" par Baglis Tv</t>
+          <t>"Interview | Plaidoyer pour le carbone / Bernadette Bensaude-Vincent" par Le Blob</t>
         </is>
       </c>
       <c r="H27" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/jambet-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/bensaudevincent-mini.webp</t>
         </is>
       </c>
       <c r="I27" s="36" t="n"/>
       <c r="J27" s="27" t="inlineStr">
         <is>
-          <t>spiritualite ; metaphysique</t>
+          <t>epistemologie</t>
         </is>
       </c>
       <c r="K27" s="27" t="inlineStr">
         <is>
-          <t>Ishraqisme ; Soufisme</t>
+          <t>Constructivisme</t>
         </is>
       </c>
       <c r="L27" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la pensée islamique et en particulier le chiisme.</t>
+          <t>philosophe française et historienne des sciences.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2300,11 +2304,11 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">sens</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="158.25" customHeight="1" s="28">
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="188.25" customHeight="1" s="28">
       <c r="A28" s="34" t="n">
         <v>1949</v>
       </c>
@@ -2316,28 +2320,28 @@
       </c>
       <c r="D28" s="35" t="inlineStr">
         <is>
-          <t>Bernadette BENSAUDE-VINCENT</t>
+          <t>Christian GODIN</t>
         </is>
       </c>
       <c r="E28" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernadette_Bensaude-Vincent" title=" Wikipedia"&gt;Bernadette BENSUDE-VINCENT&lt;/a&gt;  est une philosophe française et historienne des sciences. Formée à l'École normale supérieure de Fontenay-aux-Roses, agrégée de philosophie en 1971 et docteure ès lettres en 1981, elle a enseigné à l'université Paris X-Nanterre puis Paris I Panthéon-Sorbonne jusqu'à sa retraite en 2015, où elle est professeure émérite. Elle a dirigé le Centre d'études des techniques, des connaissances et des pratiques (CETCOPRA) et été membre senior de l'Institut universitaire de France. &lt;/p&gt; &lt;p&gt; Elle a occupé des postes invités dans des universités internationales comme Madrid, Vienne ou Bielefeld, et collaboré avec le MIT sur l'histoire des matériaux. Membre de l'Académie des technologies et vice-présidente du comité d'éthique d'organismes comme l'Inrae, elle a contribué à la Cité des sciences et de l'industrie. Auteure d'une centaine d'ouvrages, elle a coordonné des programmes sur l'éthique des nanotechnologies et les technosciences. &lt;/p&gt; &lt;p&gt; Sa pensée critique la rupture bachelardienne entre science et opinion, plaidant pour leur interdépendance dans une "philosophie de terrain". Elle analyse la chimie, les technosciences et les technologies émergentes comme des pratiques sociales façonnant la matière, questionnant le pouvoir des sciences sur le vivant et la société. Elle rejette &lt;a href="https://www.youtube.com/watch?v=MRD0LLrjGG8"  title="bernadette bensaude-vincent : approche philo de la biologie de synthese par Alter Mardis"&gt;les visions réductionnistes &lt;/a&gt; pour souligner les controverses et la pluralité des savoirs. &lt;/p&gt; &lt;p&gt; Dans des essais comme L’Opinion publique et la science ou ses réflexions sur l'Anthropocène, elle promeut une "culture de la défiance" constructive contre la méfiance, favorisant des savoirs robustes. Ses recherches sur les matériaux et la biologie de synthèse interrogent l'hubris humaine, défendant une  &lt;a href="https://www.youtube.com/watch?v=HnEX-2_p3mQ"  title="bernadette bensaude-vincent : fait il changer notre rapport au temps par écologie rationnelle"&gt;approche humaniste &lt;/a&gt; des relations science-société et une histoire des sciences attentive aux marges. &lt;/p&gt;    &lt;audio controls title=" Science et recherche: de l’expertise à la sphère publique par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13983-28.04.2021-ITEMA_22649821-2021C16450S0118.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Godin"   title=" Wikipedia"&gt;Christian GODIN&lt;/a&gt;  est un philosophe français qui a enseigné la philosophie à l’université Blaise-Pascal de Clermont-Ferrand, où il est devenu professeur émérite, et collabore régulièrement à des revues comme Marianne, Le Magazine littéraire et Sciences et Avenir. Il dirige également la revue Cités aux PUF et s’est imposé comme  &lt;a href="http://www.christian-godin.com/biographie.html"  title="autobiographie par c godin"&gt; un auteur prolifique, &lt;/a&gt; avec plus d’une cinquantaine d’ouvrages à caractère pédagogique et érudit. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour son monumental travail « La Totalité en sept volumes » (1997-2003), fruit de sa thèse de doctorat, qui explore la notion philosophique de totalité à travers l’histoire de la pensée. Parmi ses autres travaux phares figurent des ouvrages de vulgarisation comme  &lt;a href="https://www.youtube.com/watch?v=nJga6GYNLUw"  title="Ephilosophie pour les nuls par Google payer livres"&gt; La Philosophie pour les nuls &lt;/a&gt; (2006), des dictionnaires philosophiques et des essais contemporains tels que La crise de la réalité (2021), où il analyse la destitution du réel par le numérique et les idéologies modernes. Il a aussi réalisé des entretiens avec des penseurs comme Axel Kahn ou Malek Chebel.  &lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est avant tout « un désir de comprendre le monde, de donner du sens, d’expliquer les choses », et elle doit rester ancrée dans le concret pour éviter l’abstraction stérile. Il insiste sur son rôle pédagogique et accessible à tous, invitant à dialoguer avec les grands penseurs comme Platon, Nietzsche ou Hannah Arendt pour aborder des thèmes universels : le sens de la vie, l’amour, la mort. Contrairement à la science focalisée sur la vérité, la philosophie cherche le sens via la critique, le débat intérieur et l’examen des  &lt;a href="https://www.youtube.com/watch?v=8KzIKZimPSI"  title="Etre humain par Philomonaco"&gt; problèmes humains. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il aborde des enjeux actuels comme la crise de la réalité (présentisme, simulationnisme, prédictionnisme), la synchronicité comme signe d’unité divine échappant à la raison, ou la démoralisation contemporaine. Il critique le subjectivisme relativiste, le narcissisme numérique et la technoscience totalitaire qui substitue un monde artificiel à la nature, plaidant pour une pensée multidimensionnelle du réel. Ses analyses, souvent pessimistes sur la virtualité et la post-vérité, défendent une objectivité ancrée dans le monde physique. &lt;/p&gt;     &lt;audio controls title="Le philosophe Christian Godin tire les leçons du Grand Débat " par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15343-18.03.2019-ITEMA_22011803-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>uBV5yWbIATY</t>
+          <t>8ugwtdNriZA</t>
         </is>
       </c>
       <c r="G28" s="36" t="inlineStr">
         <is>
-          <t>"Interview | Plaidoyer pour le carbone / Bernadette Bensaude-Vincent" par Le Blob</t>
+          <t xml:space="preserve">"Christian Godin - Le soupir de la créature accablée : la religion aujourd’hui" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H28" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/bensaudevincent-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/cgodin-mini.webp</t>
         </is>
       </c>
       <c r="I28" s="36" t="n"/>
@@ -2348,17 +2352,12 @@
       </c>
       <c r="K28" s="27" t="inlineStr">
         <is>
-          <t>Constructivisme</t>
+          <t>Humanisme</t>
         </is>
       </c>
       <c r="L28" s="27" t="inlineStr">
         <is>
-          <t>philosophe française et historienne des sciences.</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français connu pour son monumental travail "La Totalité" en sept volumes.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2368,11 +2367,11 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="188.25" customHeight="1" s="28">
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="157.5" customHeight="1" s="28">
       <c r="A29" s="34" t="n">
         <v>1949</v>
       </c>
@@ -2384,44 +2383,49 @@
       </c>
       <c r="D29" s="35" t="inlineStr">
         <is>
-          <t>Christian GODIN</t>
+          <t>Alain FINKIELKRAUT</t>
         </is>
       </c>
       <c r="E29" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Godin"   title=" Wikipedia"&gt;Christian GODIN&lt;/a&gt;  est un philosophe français qui a enseigné la philosophie à l’université Blaise-Pascal de Clermont-Ferrand, où il est devenu professeur émérite, et collabore régulièrement à des revues comme Marianne, Le Magazine littéraire et Sciences et Avenir. Il dirige également la revue Cités aux PUF et s’est imposé comme  &lt;a href="http://www.christian-godin.com/biographie.html"  title="autobiographie par c godin"&gt; un auteur prolifique, &lt;/a&gt; avec plus d’une cinquantaine d’ouvrages à caractère pédagogique et érudit. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour son monumental travail « La Totalité en sept volumes » (1997-2003), fruit de sa thèse de doctorat, qui explore la notion philosophique de totalité à travers l’histoire de la pensée. Parmi ses autres travaux phares figurent des ouvrages de vulgarisation comme  &lt;a href="https://www.youtube.com/watch?v=nJga6GYNLUw"  title="Ephilosophie pour les nuls par Google payer livres"&gt; La Philosophie pour les nuls &lt;/a&gt; (2006), des dictionnaires philosophiques et des essais contemporains tels que La crise de la réalité (2021), où il analyse la destitution du réel par le numérique et les idéologies modernes. Il a aussi réalisé des entretiens avec des penseurs comme Axel Kahn ou Malek Chebel.  &lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est avant tout « un désir de comprendre le monde, de donner du sens, d’expliquer les choses », et elle doit rester ancrée dans le concret pour éviter l’abstraction stérile. Il insiste sur son rôle pédagogique et accessible à tous, invitant à dialoguer avec les grands penseurs comme Platon, Nietzsche ou Hannah Arendt pour aborder des thèmes universels : le sens de la vie, l’amour, la mort. Contrairement à la science focalisée sur la vérité, la philosophie cherche le sens via la critique, le débat intérieur et l’examen des  &lt;a href="https://www.youtube.com/watch?v=8KzIKZimPSI"  title="Etre humain par Philomonaco"&gt; problèmes humains. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il aborde des enjeux actuels comme la crise de la réalité (présentisme, simulationnisme, prédictionnisme), la synchronicité comme signe d’unité divine échappant à la raison, ou la démoralisation contemporaine. Il critique le subjectivisme relativiste, le narcissisme numérique et la technoscience totalitaire qui substitue un monde artificiel à la nature, plaidant pour une pensée multidimensionnelle du réel. Ses analyses, souvent pessimistes sur la virtualité et la post-vérité, défendent une objectivité ancrée dans le monde physique. &lt;/p&gt;     &lt;audio controls title="Le philosophe Christian Godin tire les leçons du Grand Débat " par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15343-18.03.2019-ITEMA_22011803-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alain_Finkielkraut"  title=" Wikipedia"&gt;Alain FINKIELKRAUT&lt;/a&gt;  est un philosophe français  et essayiste français né en 1949 à Paris, fils de juifs polonais rescapés de la Shoah. Agrégé de philosophie, il a enseigné brièvement avant de se consacrer à l'écriture et aux médias, notamment via des chroniques radiophoniques sur France Culture. Membre de l'Académie française depuis 2014, il est associé au mouvement des "nouveaux philosophes" post-Mai 68, rompant avec le marxisme pour critiquer les idéologies totalitaires. &lt;/p&gt; &lt;p&gt; Ses essais majeurs incluent La Défaite de la pensée (1987), qui dénonce le relativisme culturel et &lt;a href="https://www.youtube.com/watch?v=e-uoL-Ve_8c"   title="A Finkierlkraut et ses clachs tv  par France Tv "&gt; l'appauvrissement intellectuel &lt;/a&gt; moderne, et L'Identité malheureuse (2013), où il analyse la crise de l'identité française face à l'immigration et au multiculturalisme. D'autres livres comme Remembering in Vain (1989) explorent la mémoire de la Shoah et les crimes contre l'humanité, tandis que À la première personne (2019) revisite son parcours personnel.  &lt;/p&gt; &lt;p&gt; Il  défend une pensée humaniste ancrée dans la tradition européenne, influencée par Hannah Arendt, Rousseau et les Lumières. Il rejette le "progressisme" idéologique qui, selon lui, nie les différences culturelles et sapent la civilisation occidentale par un relativisme anti-humaniste.  &lt;a href="https://www.youtube.com/watch?v=CLYyy1U_Y2A"   title="A Finkierlkraut le wokisme  par Le Figaro"&gt; La culture et l'éducation &lt;/a&gt; sont pour lui des remparts contre la barbarie moderne, qu'elle soit technologique ou identitaire. &lt;/p&gt; &lt;p&gt;Ses réflexions portent sur l'antisémitisme contemporain, le déclin de la littérature, la nostalgie du passé et les dangers du politiquement correct. Pessimiste sur la "destitution de l'Occident" par la globalisation et le numérique, il prône un retour à la raison critique et à l'universalisme exigeant, loin des illusions du Progrès. &lt;/p&gt;   &lt;audio controls title="La langue française évolue Alain Finkielkraut par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10241-19.01.2026-ITEMA_24378393-2026F10815S0019-NET_MFI_36E8E6AA-9496-4465-B102-85331E19F173-22-d13018db268bb69d47041561b5f2965e.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>8ugwtdNriZA</t>
+          <t>CLYyy1U_Y2A</t>
         </is>
       </c>
       <c r="G29" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Christian Godin - Le soupir de la créature accablée : la religion aujourd’hui" par Librairie Mollat</t>
+          <t>"Le wokisme est-il une religion de substitution? Avec Alain Finkielkraut et Pierre Manent' par Le Figaro</t>
         </is>
       </c>
       <c r="H29" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/cgodin-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/afinkielkraut-mini.webp</t>
         </is>
       </c>
       <c r="I29" s="36" t="n"/>
       <c r="J29" s="27" t="inlineStr">
         <is>
-          <t>epistemologie</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K29" s="27" t="inlineStr">
         <is>
-          <t>Humanisme</t>
+          <t>Conservatisme</t>
         </is>
       </c>
       <c r="L29" s="27" t="inlineStr">
         <is>
-          <t>philosophe français connu pour son monumental travail "La Totalité" en sept volumes.</t>
+          <t>philosophe juif français qui enseigna avant de se consacrer à l'écriture et aux médias.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2431,65 +2435,59 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="157.5" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="222" customHeight="1" s="28">
       <c r="A30" s="34" t="n">
         <v>1949</v>
       </c>
       <c r="B30" s="34" t="n"/>
-      <c r="C30" s="34" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
+      <c r="C30" s="34" t="n">
+        <v>1949</v>
       </c>
       <c r="D30" s="35" t="inlineStr">
         <is>
-          <t>Alain FINKIELKRAUT</t>
+          <t>Roger-Pol DROIT</t>
         </is>
       </c>
       <c r="E30" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alain_Finkielkraut"  title=" Wikipedia"&gt;Alain FINKIELKRAUT&lt;/a&gt;  est un philosophe français  et essayiste français né en 1949 à Paris, fils de juifs polonais rescapés de la Shoah. Agrégé de philosophie, il a enseigné brièvement avant de se consacrer à l'écriture et aux médias, notamment via des chroniques radiophoniques sur France Culture. Membre de l'Académie française depuis 2014, il est associé au mouvement des "nouveaux philosophes" post-Mai 68, rompant avec le marxisme pour critiquer les idéologies totalitaires. &lt;/p&gt; &lt;p&gt; Ses essais majeurs incluent La Défaite de la pensée (1987), qui dénonce le relativisme culturel et &lt;a href="https://www.youtube.com/watch?v=e-uoL-Ve_8c"   title="A Finkierlkraut et ses clachs tv  par France Tv "&gt; l'appauvrissement intellectuel &lt;/a&gt; moderne, et L'Identité malheureuse (2013), où il analyse la crise de l'identité française face à l'immigration et au multiculturalisme. D'autres livres comme Remembering in Vain (1989) explorent la mémoire de la Shoah et les crimes contre l'humanité, tandis que À la première personne (2019) revisite son parcours personnel.  &lt;/p&gt; &lt;p&gt; Il  défend une pensée humaniste ancrée dans la tradition européenne, influencée par Hannah Arendt, Rousseau et les Lumières. Il rejette le "progressisme" idéologique qui, selon lui, nie les différences culturelles et sapent la civilisation occidentale par un relativisme anti-humaniste.  &lt;a href="https://www.youtube.com/watch?v=CLYyy1U_Y2A"   title="A Finkierlkraut le wokisme  par Le Figaro"&gt; La culture et l'éducation &lt;/a&gt; sont pour lui des remparts contre la barbarie moderne, qu'elle soit technologique ou identitaire. &lt;/p&gt; &lt;p&gt;Ses réflexions portent sur l'antisémitisme contemporain, le déclin de la littérature, la nostalgie du passé et les dangers du politiquement correct. Pessimiste sur la "destitution de l'Occident" par la globalisation et le numérique, il prône un retour à la raison critique et à l'universalisme exigeant, loin des illusions du Progrès. &lt;/p&gt;   &lt;audio controls title="La langue française évolue Alain Finkielkraut par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10241-19.01.2026-ITEMA_24378393-2026F10815S0019-NET_MFI_36E8E6AA-9496-4465-B102-85331E19F173-22-d13018db268bb69d47041561b5f2965e.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Roger-Pol_Droit"   title=" Wikipedia"&gt;Roger-Pol DROIT&lt;/a&gt; est un philosophe et écrivain français connu à la fois pour ses travaux de recherche et pour ses livres de vulgarisation qui  &lt;a href="https://rpdroit.com/"   title="Roger-Pol DROIT"&gt; rendent la philosophie accessible &lt;/a&gt; à un large public. Sa philosophie ne se présente pas comme un système fermé, mais comme une manière d’ouvrir les questions, de faire dialoguer les idées et de montrer que penser est une activité vivante. Dans ses ouvrages d’initiation, il cherche à expliquer la pensée sans jargon, avec clarté et souvent avec pédagogie, comme dans La philosophie expliquée à ma fille ou &lt;a href="https://www.youtube.com/watch?v=I-GcL40sLGg"   title="Il nous parle de philosophie par Bibliothèque de poche"&gt; Une brève histoire de la philosophie&lt;/a&gt;. Pour lui, la philosophie n’est pas réservée aux spécialistes : elle commence par l’étonnement, la curiosité et le besoin de comprendre. &lt;/p&gt; &lt;p&gt; Il insiste sur le dialogue et l’exercice de l’objection et il voit la pensée comme une conversation intérieure et extérieure, où l’on apprend à examiner une idée, à la contredire, puis à la reformuler. Cette approche apparaît aussi dans ses récits philosophiques, qui mêlent réflexion, humour et narration pour faire sentir que penser engage toute la vie intérieure. &lt;/p&gt; &lt;p&gt; Un autre axe important de son travail est l’ouverture aux philosophies du monde. Il s’est intéressé aux rapports entre la pensée occidentale et les traditions venues d’ailleurs, notamment aux représentations des philosophies non occidentales dans la culture européenne. Son livre &lt;a href="https://www.youtube.com/watch?v=NF9rLrveAbI"   title="Roger-Pol DROIT par editions albin michel"&gt; Un voyage dans les philosophies du monde &lt;/a&gt; va dans ce sens : il montre que la philosophie ne se limite pas à l’Europe et qu’elle prend des formes multiples selon les cultures. &lt;/p&gt; &lt;p&gt; Sa démarche est profondément humaniste. Il relie la philosophie aux inquiétudes concrètes du présent, à la liberté, à la vie commune, aux limites de l’action et aux questions morales. Chez lui, philosopher ne consiste pas seulement à produire des concepts, mais à apprendre à mieux vivre, à mieux juger et à mieux habiter le monde. &lt;/&gt; 
+ &lt;audio controls title="un équilibre instable entre la négatif et le positif par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16173-20.05.2025-ITEMA_24141042-2025F26104S0140-NET_MFI_83506534-46B8-430C-8970-C247B9C3C4C4-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>CLYyy1U_Y2A</t>
+          <t>2NRy08SQ4Ec</t>
         </is>
       </c>
       <c r="G30" s="36" t="inlineStr">
         <is>
-          <t>"Le wokisme est-il une religion de substitution? Avec Alain Finkielkraut et Pierre Manent' par Le Figaro</t>
-        </is>
-      </c>
-      <c r="H30" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/afinkielkraut-mini.webp</t>
+          <t xml:space="preserve">Roger-Pol DROIT si je n’avais plus qu’une heure à vivre par Librairie Mollat</t>
+        </is>
+      </c>
+      <c r="H30" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/rpdroit-mini.webp</t>
         </is>
       </c>
       <c r="I30" s="36" t="n"/>
       <c r="J30" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>ethique</t>
         </is>
       </c>
       <c r="K30" s="27" t="inlineStr">
         <is>
-          <t>Conservatisme</t>
-        </is>
-      </c>
-      <c r="L30" s="27" t="inlineStr">
-        <is>
-          <t>philosophe juif français qui enseigna avant de se consacrer à l'écriture et aux médias.</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
+          <t>Humanisme</t>
+        </is>
+      </c>
+      <c r="L30" s="42" t="inlineStr">
+        <is>
+          <t>philosophe français qui cherche par ses livres à rendre la philosophie accessible à un large public.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2499,11 +2497,11 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="222" customHeight="1" s="28">
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="245.25" customHeight="1" s="28">
       <c r="A31" s="34" t="n">
         <v>1949</v>
       </c>
@@ -2513,45 +2511,44 @@
       </c>
       <c r="D31" s="35" t="inlineStr">
         <is>
-          <t>Roger-Pol DROIT</t>
+          <t>Philippe DESCOLA</t>
         </is>
       </c>
       <c r="E31" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Roger-Pol_Droit"   title=" Wikipedia"&gt;Roger-Pol DROIT&lt;/a&gt; est un philosophe et écrivain français connu à la fois pour ses travaux de recherche et pour ses livres de vulgarisation qui  &lt;a href="https://rpdroit.com/"   title="Roger-Pol DROIT"&gt; rendent la philosophie accessible &lt;/a&gt; à un large public. Sa philosophie ne se présente pas comme un système fermé, mais comme une manière d’ouvrir les questions, de faire dialoguer les idées et de montrer que penser est une activité vivante. Dans ses ouvrages d’initiation, il cherche à expliquer la pensée sans jargon, avec clarté et souvent avec pédagogie, comme dans La philosophie expliquée à ma fille ou &lt;a href="https://www.youtube.com/watch?v=I-GcL40sLGg"   title="Il nous parle de philosophie par Bibliothèque de poche"&gt; Une brève histoire de la philosophie&lt;/a&gt;. Pour lui, la philosophie n’est pas réservée aux spécialistes : elle commence par l’étonnement, la curiosité et le besoin de comprendre. &lt;/p&gt; &lt;p&gt; Il insiste sur le dialogue et l’exercice de l’objection et il voit la pensée comme une conversation intérieure et extérieure, où l’on apprend à examiner une idée, à la contredire, puis à la reformuler. Cette approche apparaît aussi dans ses récits philosophiques, qui mêlent réflexion, humour et narration pour faire sentir que penser engage toute la vie intérieure. &lt;/p&gt; &lt;p&gt; Un autre axe important de son travail est l’ouverture aux philosophies du monde. Il s’est intéressé aux rapports entre la pensée occidentale et les traditions venues d’ailleurs, notamment aux représentations des philosophies non occidentales dans la culture européenne. Son livre &lt;a href="https://www.youtube.com/watch?v=NF9rLrveAbI"   title="Roger-Pol DROIT par editions albin michel"&gt; Un voyage dans les philosophies du monde &lt;/a&gt; va dans ce sens : il montre que la philosophie ne se limite pas à l’Europe et qu’elle prend des formes multiples selon les cultures. &lt;/p&gt; &lt;p&gt; Sa démarche est profondément humaniste. Il relie la philosophie aux inquiétudes concrètes du présent, à la liberté, à la vie commune, aux limites de l’action et aux questions morales. Chez lui, philosopher ne consiste pas seulement à produire des concepts, mais à apprendre à mieux vivre, à mieux juger et à mieux habiter le monde. &lt;/&gt; 
- &lt;audio controls title="un équilibre instable entre la négatif et le positif par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16173-20.05.2025-ITEMA_24141042-2025F26104S0140-NET_MFI_83506534-46B8-430C-8970-C247B9C3C4C4-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Philippe_Descola"   title=" Wikipedia"&gt;Philippe DESCOLA&lt;/a&gt; est un anthropologue français spécialiste de l’Amazonie, il a consacré une partie importante de ses recherches aux Achuar, un peuple &lt;a href="https://www.youtube.com/watch?v=d4VRtkRg-_o"   title="Etudier les Jivaros Achaur d’amazonie par RFI"&gt; jivaro de Haute-Amazonie.&lt;/a&gt;  Ses travaux cherchent principalement à comprendre comment les différentes sociétés établissent des relations avec les animaux, les plantes, les objets, les esprits et leur environnement. &lt;/p&gt; &lt;p&gt;  Son œuvre la plus connue est Par-delà nature et culture, publiée en 2005. Dans ce livre, il critique la séparation entre la nature et la culture, séparation qui lui paraît caractéristique de la pensée occidentale moderne. Selon lui, cette distinction n’est pas universelle : toutes les sociétés ne considèrent pas les humains comme appartenant à un domaine culturel séparé d’une nature extérieure et objective. Il propose donc d’étudier différentes manières de composer le monde et d’identifier les êtres qui l’habitent. &lt;/p&gt; &lt;p&gt; Pour effectuer cette comparaison, il distingue quatre grandes ontologies : l’animisme, le totémisme, l’analogisme et le naturalisme. L’animisme reconnaît une intériorité semblable aux humains et aux non-humains, mais des corps différents ; le naturalisme, caractéristique des sociétés occidentales modernes, suppose au contraire une même nature physique, mais une intériorité principalement attribuée aux humains. Le totémisme établit une continuité entre certains humains et certains non-humains, tandis que l’analogisme conçoit le monde comme une multiplicité d’êtres différents reliés par des correspondances. &lt;/p&gt; &lt;p&gt; Il ne présente pas ces quatre ontologies comme des étapes successives de l’évolution de l’humanité. Il ne dit pas non plus qu’une société entière correspond toujours parfaitement à un seul modèle. Il s’agit plutôt de grands schèmes permettant de comparer les façons dont les sociétés organisent leurs rapports avec les existants. Son originalité consiste donc à prendre au sérieux les conceptions non occidentales du monde, sans les interpréter automatiquement comme des croyances irrationnelles ou comme des versions incomplètes de la science moderne. &lt;/p&gt; &lt;p&gt; Sa pensée dépasse ainsi l’anthropologie proprement dite et rejoint la philosophie, l’écologie et la réflexion sur la crise environnementale. En montrant que &lt;a href="https://www.youtube.com/watch?v=fV2VqJhxuEE"   title="la nature n’existe pas par blast, le souflle de l’info"&gt; la nature n’est pas partout &lt;/a&gt; conçue comme une réalité extérieure exploitable, il invite à repenser la place de l’être humain dans le monde. Parmi ses autres ouvrages importants figurent La Nature domestique, Les Lances du crépuscule, L’Écologie des autres, La Composition des mondes et Les Formes du visible. &lt;/p&gt; 
+&lt;audio controls title="Nous sommes les hotes de la terre par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/26684-21.05.2026-ITEMA_24520316-2026F49008S0141-NET_MFI_7313D6B1-DF3B-42D0-AD80-7A8884697517-27-c968a5478f57024ca66b57343b59f5c9.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>2NRy08SQ4Ec</t>
+          <t>UD1vw-d8ZJ0</t>
         </is>
       </c>
       <c r="G31" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roger-Pol DROIT si je n’avais plus qu’une heure à vivre par Librairie Mollat</t>
+          <t xml:space="preserve">qui a inventé la nature par Arte</t>
         </is>
       </c>
       <c r="H31" s="37" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/rpdroit-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/pdescola-mini.webp</t>
         </is>
       </c>
       <c r="I31" s="36" t="n"/>
       <c r="J31" s="27" t="inlineStr">
         <is>
-          <t>ethique</t>
+          <t xml:space="preserve">spiritualite </t>
         </is>
       </c>
       <c r="K31" s="27" t="inlineStr">
         <is>
-          <t>Humanisme</t>
-        </is>
-      </c>
-      <c r="L31" s="42" t="inlineStr">
-        <is>
-          <t>philosophe français qui cherche par ses livres à rendre la philosophie accessible à un large public.</t>
+          <t>Animisme ; Totémisme ; Analogisme ; Naturalisme (ontologie)</t>
+        </is>
+      </c>
+      <c r="L31" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> anthropologue français spécialiste de l’Amazonie.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2561,58 +2558,60 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">sens</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="245.25" customHeight="1" s="28">
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="210" customHeight="1" s="28">
       <c r="A32" s="34" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B32" s="34" t="n"/>
-      <c r="C32" s="34" t="n">
-        <v>1949</v>
+      <c r="C32" s="34" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
       </c>
       <c r="D32" s="35" t="inlineStr">
         <is>
-          <t>Philippe DESCOLA</t>
-        </is>
-      </c>
-      <c r="E32" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Philippe_Descola"   title=" Wikipedia"&gt;Philippe DESCOLA&lt;/a&gt; est un anthropologue français spécialiste de l’Amazonie, il a consacré une partie importante de ses recherches aux Achuar, un peuple &lt;a href="https://www.youtube.com/watch?v=d4VRtkRg-_o"   title="Etudier les Jivaros Achaur d’amazonie par RFI"&gt; jivaro de Haute-Amazonie.&lt;/a&gt;  Ses travaux cherchent principalement à comprendre comment les différentes sociétés établissent des relations avec les animaux, les plantes, les objets, les esprits et leur environnement. &lt;/p&gt; &lt;p&gt;  Son œuvre la plus connue est Par-delà nature et culture, publiée en 2005. Dans ce livre, il critique la séparation entre la nature et la culture, séparation qui lui paraît caractéristique de la pensée occidentale moderne. Selon lui, cette distinction n’est pas universelle : toutes les sociétés ne considèrent pas les humains comme appartenant à un domaine culturel séparé d’une nature extérieure et objective. Il propose donc d’étudier différentes manières de composer le monde et d’identifier les êtres qui l’habitent. &lt;/p&gt; &lt;p&gt; Pour effectuer cette comparaison, il distingue quatre grandes ontologies : l’animisme, le totémisme, l’analogisme et le naturalisme. L’animisme reconnaît une intériorité semblable aux humains et aux non-humains, mais des corps différents ; le naturalisme, caractéristique des sociétés occidentales modernes, suppose au contraire une même nature physique, mais une intériorité principalement attribuée aux humains. Le totémisme établit une continuité entre certains humains et certains non-humains, tandis que l’analogisme conçoit le monde comme une multiplicité d’êtres différents reliés par des correspondances. &lt;/p&gt; &lt;p&gt; Il ne présente pas ces quatre ontologies comme des étapes successives de l’évolution de l’humanité. Il ne dit pas non plus qu’une société entière correspond toujours parfaitement à un seul modèle. Il s’agit plutôt de grands schèmes permettant de comparer les façons dont les sociétés organisent leurs rapports avec les existants. Son originalité consiste donc à prendre au sérieux les conceptions non occidentales du monde, sans les interpréter automatiquement comme des croyances irrationnelles ou comme des versions incomplètes de la science moderne. &lt;/p&gt; &lt;p&gt; Sa pensée dépasse ainsi l’anthropologie proprement dite et rejoint la philosophie, l’écologie et la réflexion sur la crise environnementale. En montrant que &lt;a href="https://www.youtube.com/watch?v=fV2VqJhxuEE"   title="la nature n’existe pas par blast, le souflle de l’info"&gt; la nature n’est pas partout &lt;/a&gt; conçue comme une réalité extérieure exploitable, il invite à repenser la place de l’être humain dans le monde. Parmi ses autres ouvrages importants figurent La Nature domestique, Les Lances du crépuscule, L’Écologie des autres, La Composition des mondes et Les Formes du visible. &lt;/p&gt; 
-&lt;audio controls title="Nous sommes les hotes de la terre par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/26684-21.05.2026-ITEMA_24520316-2026F49008S0141-NET_MFI_7313D6B1-DF3B-42D0-AD80-7A8884697517-27-c968a5478f57024ca66b57343b59f5c9.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t>Jean-Claude MICHEA</t>
+        </is>
+      </c>
+      <c r="E32" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Mich%C3%A9a"   title=" Wikipedia"&gt;Jean-Claude MICHEA&lt;/a&gt; est un philosophe français issus d'un milieu ouvrier qui se décrit comme un "démocrate radical". Il est connu pour ses analyses critiques de la société contemporaine, de la politique et de l'économie. Considéré comme un penseur de gauche, bien qu'il se distingue souvent des courants dominants de la gauche.&lt;/p&gt; &lt;p&gt; Il s'est intéressé dès ses débuts à la pensée marxiste et à la critique du capitalisme. Cependant, il s'est également inspiré d'autres courants de pensée, tels que l'anarchisme, pour développer sa propre vision politique. Il a écrit &lt;a href="https://www.youtube.com/watch?v=XnfQVE-8K-E"   title="L'enseignement de l'ignorance par Eveilleur de conscience"&gt; "L'enseignement de l'ignorance" &lt;/a&gt; et ses conditions modernes (1999), dans lequel il critique le système éducatif moderne et les politiques néolibérales qui selon lui contribuent à l'ignorance et à l'aliénation des individus ainsi que &lt;a href="https://www.youtube.com/watch?v=igU_2VY3wSQ&amp;ab_channel=MichelDrac"  style="color:#88A1E9"  title="Notre ennemi le capital par Michel Drac"&gt; "Notre ennemi, le capital"&lt;/a&gt;, "La double pensée" qui sont des écrits critiques sur la gauche et la société moderne.&lt;/p&gt; &lt;p&gt;  Pour lui, le libéralisme en tant que doctrine politique et économique est une idéologie qui vante les mérites de la liberté individuelle, du marché et de la concurrence, mais qui  aboutit à une société de plus en plus individualiste, désocialisée et inégalitaire, c'est  &lt;a href="https://www.youtube.com/watch?v=xMM8pw5p6Ms&amp;t=1192s&amp;ab_channel=LePr%C3%A9cepteur"  title="La religion du progrès par le Précepteur"&gt; " La religion du progrès "&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;  Michéa met souvent l'accent sur la défense de la culture populaire et de la tradition, qu'il considère comme des valeurs essentielles pour la préservation des communautés locales et de la diversité culturelle. Il s'oppose à la mondialisation et à l'homogénéisation culturelle qui en découle, ainsi qu'à l'idée du progrès linéaire et de la croissance économique illimitée.&lt;/p&gt;
+  &lt;audio controls title="La chance d'avoir des parents communistes par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-07.01.2019-ITEMA_21943913-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>UD1vw-d8ZJ0</t>
+          <t>PjCUoMbbS5g</t>
         </is>
       </c>
       <c r="G32" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">qui a inventé la nature par Arte</t>
-        </is>
-      </c>
-      <c r="H32" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/pdescola-mini.webp</t>
+          <t xml:space="preserve">"Le Libéralisme par Le Précepteur</t>
+        </is>
+      </c>
+      <c r="H32" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/michea-mini.webp</t>
         </is>
       </c>
       <c r="I32" s="36" t="n"/>
       <c r="J32" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite </t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K32" s="27" t="inlineStr">
         <is>
-          <t>Animisme ; Totémisme ; Analogisme ; Naturalisme (ontologie)</t>
-        </is>
-      </c>
-      <c r="L32" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> anthropologue français spécialiste de l’Amazonie.</t>
+          <t>Conservatisme</t>
+        </is>
+      </c>
+      <c r="L32" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français socialiste libertaire connu pour ses positions engagées.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2622,11 +2621,11 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="210" customHeight="1" s="28">
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="147.75" customHeight="1" s="28">
       <c r="A33" s="34" t="n">
         <v>1950</v>
       </c>
@@ -2638,44 +2637,43 @@
       </c>
       <c r="D33" s="35" t="inlineStr">
         <is>
-          <t>Jean-Claude MICHEA</t>
+          <t>Jean-François KERVÉGAN</t>
         </is>
       </c>
       <c r="E33" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Mich%C3%A9a"   title=" Wikipedia"&gt;Jean-Claude MICHEA&lt;/a&gt; est un philosophe français issus d'un milieu ouvrier qui se décrit comme un "démocrate radical". Il est connu pour ses analyses critiques de la société contemporaine, de la politique et de l'économie. Considéré comme un penseur de gauche, bien qu'il se distingue souvent des courants dominants de la gauche.&lt;/p&gt; &lt;p&gt; Il s'est intéressé dès ses débuts à la pensée marxiste et à la critique du capitalisme. Cependant, il s'est également inspiré d'autres courants de pensée, tels que l'anarchisme, pour développer sa propre vision politique. Il a écrit &lt;a href="https://www.youtube.com/watch?v=XnfQVE-8K-E"   title="L'enseignement de l'ignorance par Eveilleur de conscience"&gt; "L'enseignement de l'ignorance" &lt;/a&gt; et ses conditions modernes (1999), dans lequel il critique le système éducatif moderne et les politiques néolibérales qui selon lui contribuent à l'ignorance et à l'aliénation des individus ainsi que &lt;a href="https://www.youtube.com/watch?v=igU_2VY3wSQ&amp;ab_channel=MichelDrac"  style="color:#88A1E9"  title="Notre ennemi le capital par Michel Drac"&gt; "Notre ennemi, le capital"&lt;/a&gt;, "La double pensée" qui sont des écrits critiques sur la gauche et la société moderne.&lt;/p&gt; &lt;p&gt;  Pour lui, le libéralisme en tant que doctrine politique et économique est une idéologie qui vante les mérites de la liberté individuelle, du marché et de la concurrence, mais qui  aboutit à une société de plus en plus individualiste, désocialisée et inégalitaire, c'est  &lt;a href="https://www.youtube.com/watch?v=xMM8pw5p6Ms&amp;t=1192s&amp;ab_channel=LePr%C3%A9cepteur"  title="La religion du progrès par le Précepteur"&gt; " La religion du progrès "&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;  Michéa met souvent l'accent sur la défense de la culture populaire et de la tradition, qu'il considère comme des valeurs essentielles pour la préservation des communautés locales et de la diversité culturelle. Il s'oppose à la mondialisation et à l'homogénéisation culturelle qui en découle, ainsi qu'à l'idée du progrès linéaire et de la croissance économique illimitée.&lt;/p&gt;
-  &lt;audio controls title="La chance d'avoir des parents communistes par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10351-07.01.2019-ITEMA_21943913-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Fran%C3%A7ois_Kerv%C3%A9gan"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean-François KERVEGAN&lt;/a&gt; (né en 1950) est un philosophe français, spécialiste de la philosophie allemande classique, de la philosophie politique et de la philosophie du droit. Professeur à l’université Paris 1 Panthéon-Sorbonne, dont il est émérite depuis 2019, il y a fondé le groupe de recherche NoSoPhi (Normes, Sociétés, Philosophies).&lt;/p&gt; &lt;p&gt;Spécialiste reconnu de Hegel, il a donné une nouvelle traduction française des &lt;em&gt;Principes de la philosophie du droit&lt;/em&gt; et lui a consacré une grande étude, &lt;em&gt;L’Effectif et le Rationnel&lt;/em&gt; (2007), sur l’« esprit objectif », c’est-à-dire le droit, la morale, la famille, la société civile et l’État. Il y montre que Hegel n’est ni le penseur de l’État autoritaire qu’on a souvent décrit, ni un simple libéral : il pense les institutions comme ce qui rend la liberté réelle. Il a aussi étudié le juriste allemand Carl Schmitt, dont il a confronté la pensée à celle de Hegel, en interrogeant la critique schmittienne du libéralisme et de la démocratie parlementaire tout en en montrant les dangers. Dans &lt;em&gt;La Raison des normes&lt;/em&gt; (2015), consacré à Kant, il interroge le fondement des normes juridiques et morales, et dialogue avec les débats nés du positivisme juridique de Hans Kelsen, que l’on dit &lt;a href="https://www.youtube.com/watch?v=2uE1rQ84o3E" style="color:#88A1E9" title="Jean-François Kervégan : Le Droit chez Kant par E-Kritik"&gt;post-kelséniens&lt;/a&gt;, sur la validité et l’interprétation du droit. Il défend une normativité juridique fondée sur la raison pratique, qui échappe à la fois à l’arbitraire et au simple fait du pouvoir.&lt;/p&gt; &lt;p&gt;Ses travaux récents portent sur les droits subjectifs, la souveraineté et les transformations de l’État face à la mondialisation et aux acteurs non étatiques.&lt;/p&gt;  &lt;audio controls title="Qu'est-ce qu'avoir des droits ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/21447-23.04.2025-ITEMA_24112082-2025C27677S0113-NET_MFC_7BBBCBA0-C114-4775-A02F-0D69201542E4-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F33" s="34" t="inlineStr">
         <is>
-          <t>PjCUoMbbS5g</t>
+          <t>RXTR1GHF-ow</t>
         </is>
       </c>
       <c r="G33" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Le Libéralisme par Le Précepteur</t>
+          <t>"Jean-François Kervégan - Avons-nous besoin d’ennemis ?" par Le Mans Université Conférences</t>
         </is>
       </c>
       <c r="H33" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/michea-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/kervegan-mini.webp</t>
         </is>
       </c>
       <c r="I33" s="36" t="n"/>
       <c r="J33" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>politique</t>
         </is>
       </c>
       <c r="K33" s="27" t="inlineStr">
         <is>
-          <t>Conservatisme</t>
+          <t>Libéralisme</t>
         </is>
       </c>
       <c r="L33" s="27" t="inlineStr">
         <is>
-          <t>philosophe français socialiste libertaire connu pour ses positions engagées.</t>
+          <t>philosophe français du droit &amp;amp; de la politique en réflexion de Kant &amp;amp; Hegel.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2685,255 +2683,256 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="147.75" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="126.75" customHeight="1" s="28">
       <c r="A34" s="34" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="B34" s="34" t="n"/>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="D34" s="35" t="inlineStr">
         <is>
-          <t>Jean-François KERVÉGAN</t>
-        </is>
-      </c>
-      <c r="E34" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Fran%C3%A7ois_Kerv%C3%A9gan"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean-François KERVEGAN&lt;/a&gt; (né en 1950) est un philosophe français, spécialiste de la philosophie allemande classique, de la philosophie politique et de la philosophie du droit. Professeur à l’université Paris 1 Panthéon-Sorbonne, dont il est émérite depuis 2019, il y a fondé le groupe de recherche NoSoPhi (Normes, Sociétés, Philosophies).&lt;/p&gt; &lt;p&gt;Spécialiste reconnu de Hegel, il a donné une nouvelle traduction française des &lt;em&gt;Principes de la philosophie du droit&lt;/em&gt; et lui a consacré une grande étude, &lt;em&gt;L’Effectif et le Rationnel&lt;/em&gt; (2007), sur l’« esprit objectif », c’est-à-dire le droit, la morale, la famille, la société civile et l’État. Il y montre que Hegel n’est ni le penseur de l’État autoritaire qu’on a souvent décrit, ni un simple libéral : il pense les institutions comme ce qui rend la liberté réelle. Il a aussi étudié le juriste allemand Carl Schmitt, dont il a confronté la pensée à celle de Hegel, en interrogeant la critique schmittienne du libéralisme et de la démocratie parlementaire tout en en montrant les dangers. Dans &lt;em&gt;La Raison des normes&lt;/em&gt; (2015), consacré à Kant, il interroge le fondement des normes juridiques et morales, et dialogue avec les débats nés du positivisme juridique de Hans Kelsen, que l’on dit &lt;a href="https://www.youtube.com/watch?v=2uE1rQ84o3E" style="color:#88A1E9" title="Jean-François Kervégan : Le Droit chez Kant par E-Kritik"&gt;post-kelséniens&lt;/a&gt;, sur la validité et l’interprétation du droit. Il défend une normativité juridique fondée sur la raison pratique, qui échappe à la fois à l’arbitraire et au simple fait du pouvoir.&lt;/p&gt; &lt;p&gt;Ses travaux récents portent sur les droits subjectifs, la souveraineté et les transformations de l’État face à la mondialisation et aux acteurs non étatiques.&lt;/p&gt;  &lt;audio controls title="Qu'est-ce qu'avoir des droits ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/21447-23.04.2025-ITEMA_24112082-2025C27677S0113-NET_MFC_7BBBCBA0-C114-4775-A02F-0D69201542E4-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F34" s="34" t="inlineStr">
-        <is>
-          <t>RXTR1GHF-ow</t>
-        </is>
-      </c>
-      <c r="G34" s="36" t="inlineStr">
-        <is>
-          <t>"Jean-François Kervégan - Avons-nous besoin d’ennemis ?" par Le Mans Université Conférences</t>
-        </is>
-      </c>
-      <c r="H34" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/kervegan-mini.webp</t>
-        </is>
-      </c>
-      <c r="I34" s="36" t="n"/>
-      <c r="J34" s="27" t="inlineStr">
-        <is>
-          <t>politique</t>
-        </is>
-      </c>
-      <c r="K34" s="27" t="inlineStr">
-        <is>
-          <t>Libéralisme</t>
-        </is>
-      </c>
-      <c r="L34" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français du droit &amp;amp; de la politique en réflexion de Kant &amp;amp; Hegel.</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="126.75" customHeight="1" s="28">
-      <c r="A35" s="34" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B35" s="34" t="n"/>
-      <c r="C35" s="34" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="D35" s="35" t="inlineStr">
-        <is>
           <t>François JULLIEN</t>
         </is>
       </c>
-      <c r="E35" s="37" t="inlineStr">
+      <c r="E34" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Jullien"  title=" Wikipedia"&gt;François JULLIEN&lt;/a&gt; est un philosophe français, à la fois helléniste et sinologue, connu pour avoir construit un dialogue suivi entre la pensée européenne (surtout grecque) et la pensée chinoise. Il séjourne longuement en Asie (notamment à Tokyo) et soutient deux thèses, l’une sur l’écrivain chinois Lu Xun, l’autre sur l’interprétation poétique dans la tradition chinoise, ce qui fonde son approche de  &lt;a href="https://www.berlol.net/foire/fle98ju.htm"  title="le détour d'un grec par la chine par berlol.net"&gt;l’altérité culturelle.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Son projet central consiste à "dépayser" la pensée européenne en la confrontant à la Chine, afin de faire apparaître les présupposés cachés de la philosophie occidentale. Il insiste sur le fait que la rencontre des pensées ne doit pas viser l’exotisme, mais ouvrir un espace "entre" les cultures où se travaille un véritable commun, différent de l’uniforme qu’on confond trop vite avec l’universel. &lt;/p&gt; &lt;p&gt; Il travaille la notion d’"écart" : au lieu de chercher ce qui est semblable entre les cultures, il valorise leurs écarts comme lieu de réflexion et de création conceptuelle. De cet écart naît un "entre" : un espace de tension fécond où se construit le commun, sans effacer les différences. Il propose aussi un déplacement majeur : passer de la pensée de l’"être" à une pensée du "vivre", plus attentive aux processus, aux transformations et à l’expérience concrète de l’existence. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme le "Traité de l’efficacité", il oppose la manière occidentale d’agir à une logique chinoise de l’efficience, qui mise sur les tendances de la situation et les transformations continues. L’idée est moins de choisir un camp que de se servir de cet  &lt;a href="https://www.youtube.com/watch?v=RAgmn0mbUnQ"  title="François Jullien, entrer dans la pensée chinoise par deodaTV"&gt;écart Chine/Europe &lt;/a&gt; pour repenser nos pratiques de l’action, de la stratégie et de la décision dans le monde contemporain. &lt;/p&gt; 
   &lt;audio controls title="L’art de « décoïncider » selon François Jullien  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13957-13.02.2021-ITEMA_22573157-2021C22785S0044.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F35" s="34" t="inlineStr">
+      <c r="F34" s="34" t="inlineStr">
         <is>
           <t>ual52L9ejGw</t>
         </is>
       </c>
-      <c r="G35" s="36" t="inlineStr">
+      <c r="G34" s="36" t="inlineStr">
         <is>
           <t>"
 Comment réinventer sa vie ? Interview avec le philosophe François Jullien" par Union des Savoirs</t>
         </is>
       </c>
-      <c r="H35" s="36" t="inlineStr">
+      <c r="H34" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jullien-mini.webp</t>
         </is>
       </c>
-      <c r="I35" s="36" t="n"/>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I34" s="36" t="n"/>
+      <c r="J34" s="27" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K35" s="27" t="inlineStr">
+      <c r="K34" s="27" t="inlineStr">
         <is>
           <t>Herméneutique</t>
         </is>
       </c>
-      <c r="L35" s="27" t="inlineStr">
+      <c r="L34" s="27" t="inlineStr">
         <is>
           <t>philosophe français qui analyse la philosophie à partir des langues &amp;amp; pensées grecque et chinoise.</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t xml:space="preserve">continental</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="137.25" customHeight="1" s="28">
-      <c r="A36" s="34" t="n">
+    <row r="35" ht="137.25" customHeight="1" s="28">
+      <c r="A35" s="34" t="n">
         <v>1952</v>
       </c>
-      <c r="B36" s="34" t="n"/>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>1952</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>André COMTE-SPONVILLE</t>
         </is>
       </c>
-      <c r="E36" s="36" t="inlineStr">
+      <c r="E35" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Andr%C3%A9_Comte-Sponville"  style="color:#6A142A"  title=" Wikipedia"&gt;André COMTE-SPONVILLE&lt;/a&gt;  est un philosophe français, agrégé de philosophie et docteur de troisième cycle. Matérialiste, rationaliste et humaniste, il s'est fait connaître par des ouvrages accessibles popularisant la sagesse antique adaptée au monde contemporain avec "Le Petit Traité des grandes vertus" paru en  1995, best-seller vendu à plus de 500 000 exemplaires. &lt;/p&gt; &lt;p&gt; Issu d'un milieu catholique, il se convertit à l'athéisme adolescent, adhère au Parti communiste français, puis enseigne la philosophie à l'université Paris-I Panthéon-Sorbonne jusqu'en 1998, date à laquelle il se consacre à l'écriture, aux conférences et aux essais médiatiques.  &lt;/p&gt; &lt;p&gt; Influencé par Épicure, les stoïciens, Montaigne, Spinoza, ainsi que des contemporains comme Claude Lévi-Strauss ou Marcel Conche, il forge   &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_2000_num_135_1_3634_t1_0139_0000_2" style="color:#88A1E9" title="André Comte-Sponville, L'être-temps : quelques réflexions sur le temps de la conscience, coll. Perspectives critiques par Persée"&gt;l'insistantialisme : &lt;/a&gt; une métaphysique matérialiste du temps où l'existence persiste sans finalité divine ni sens transcendant, opposée à l'existentialisme. Il propose une spiritualité athée, une éthique humaniste sans Dieu, centrée sur l'ici-maintenant et l'acceptation joyeuse de la finitude humaine. &lt;/p&gt; &lt;p&gt; Ses vertus cardinales (courage, tempérance, justice, etc.) visent une &lt;a href="https://www.youtube.com/watch?v=OYRMlwYByfA" style="color:#88A1E9" title="André Comte-Sponville, L'amou est joie par Hopitaux Universitaires de Genève"&gt;vie heureuse &lt;/a&gt; malgré la souffrance et la mort, sans illusions religieuses ou morales kantiennes. Dans des essais comme "L'Inconsolable" paru en 2018, il explore l'ennui, la joie, la solitude et les animaux, plaidant tolérance, liberté et sagesse laïque face aux populismes et au déclin écologique. &lt;/p&gt; 
   &lt;audio controls title="André Comte-Sponville, homme mélancolique, philosophe heureux par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-04.01.2026-ITEMA_24362243-2025C3500E0181-NET_MFC_54DA91F6-96EA-4790-BDB7-6EA3C744B706-21-8ab3772763c1198b47c221812723e2fa.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
-      <c r="F36" s="34" t="inlineStr">
+      <c r="F35" s="34" t="inlineStr">
         <is>
           <t>ldl-HgnjS4U</t>
         </is>
       </c>
-      <c r="G36" s="36" t="inlineStr">
+      <c r="G35" s="36" t="inlineStr">
         <is>
           <t>"André Comte-Sponville : "On ne peut pas vivre en faisant semblant qu'on ne va pas mourir" par France Inter</t>
         </is>
       </c>
-      <c r="H36" s="36" t="inlineStr">
+      <c r="H35" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/sponville-mini.webp</t>
         </is>
       </c>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="I35" s="36" t="n"/>
+      <c r="J35" s="27" t="inlineStr">
         <is>
           <t>ethique ; metaphysique</t>
         </is>
       </c>
-      <c r="K36" s="27" t="inlineStr">
+      <c r="K35" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Stoïcisme ; Matérialisme ; Athéisme</t>
         </is>
       </c>
-      <c r="L36" s="27" t="inlineStr">
+      <c r="L35" s="27" t="inlineStr">
         <is>
           <t>philosophe français matérialiste, rationaliste et humaniste.</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O36">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O35">
         <v>2</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t xml:space="preserve">sens</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="95.25" customHeight="1" s="28">
-      <c r="A37" s="34" t="n">
+    <row r="36" ht="95.25" customHeight="1" s="28">
+      <c r="A36" s="34" t="n">
         <v>1953</v>
       </c>
-      <c r="B37" s="34" t="n"/>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>1953</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D36" s="35" t="inlineStr">
         <is>
           <t>Georges DIDI-HUBERMAN</t>
         </is>
       </c>
-      <c r="E37" s="36" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Didi-Huberman" style="color:#6A142A"  title=" Wikipedia"&gt;Georges DIDI-HUBERMAN&lt;/a&gt; est un philosophe &amp; historien de l'art français spécialiste de la théorie des images et figure majeure de la pensée contemporaine sur le visuel. Il est aujourd’hui considéré comme l’un des théoriciens de l’image les plus importants en France, avec une reconnaissance internationale. &lt;/p&gt; &lt;p&gt; Ses travaux portent sur l’histoire et la théorie des images, de la Renaissance à l’art contemporain, avec une attention aux liens entre images, savoir et pouvoir. Sa démarche relève d’une "archéologie du savoir visuel"  car il cherche à comprendre comment les images construisent une mémoire, une sensibilité et des formes de pensée. &lt;/p&gt; &lt;p&gt; Pour lui, les images ne sont pas seulement des objets à regarder, mais des actes qui engagent le corps, la mémoire,&lt;a href="https://www.youtube.com/watch?v=DUNo6xZkaCo" style="color:#88A1E9" title="
 L'historien de l'art Georges Didi-Huberman explique la fabrique de nos affects par les images par France Culture"&gt; l’affect et l’histoire&lt;/a&gt;. Il insiste sur leu profondeur car il ne s’agit pas seulement de ce qui est visible en surface, mais de ce qui travaille en dessous, dans les couches de sens, de mémoire, de trauma. Il réfléchit aussi à une éthique du regard, comment voir sans réduire, sans consommer l’image, en respectant ce qu’elle expose de vulnérable, de politique, ou de souffrant. &lt;/p&gt; &lt;p&gt;De nombreux ouvrages sur Warburg, Fra Angelico, le Baroque, la mémoire de la Shoah, les images de catastrophes et de survivants, etc. Une série de livres et de projets sur les,&lt;a href="https://www.youtube.com/watch?v=vKMAHj_kvY8" style="color:#88A1E9" title="Georges Didi-Huberman, SOULÈVEMENT par ABC Penser"&gt; "soulèvements", &lt;/a&gt; où il s’intéresse aux gestes de révolte, aux mouvements collectifs, et à la manière dont les images peuvent porter la voix des sans-voix et lutter contre l’amnésie historique. &lt;/p&gt; &lt;p&gt; Sa réflexion sur les "soulèvements" l’amène à articuler philosophie de l’image et engagement politique : comment des images peuvent accompagner des luttes, préserver des mémoires, donner forme à des désirs de transformation sociale. &lt;/p&gt;   &lt;audio controls title="Dans la bibliothèque de Georges Didi-Huberman par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23875-11.10.2024-ITEMA_23889638-2024C49162E0034-NET_MFC_8E518A6F-A0BF-49D3-BFEA-B88C4BE3FE7F-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
+      <c r="F36" s="34" t="inlineStr">
+        <is>
+          <t>h629a3ItbQI</t>
+        </is>
+      </c>
+      <c r="G36" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Qui êtes-vous Georges Didi-Huberman ?" par ABC Penser</t>
+        </is>
+      </c>
+      <c r="H36" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/huberman-mini.webp</t>
+        </is>
+      </c>
+      <c r="I36" s="36" t="n"/>
+      <c r="J36" s="27" t="inlineStr">
+        <is>
+          <t>esthetique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K36" s="27" t="inlineStr">
+        <is>
+          <t>Herméneutique ; Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L36" s="27" t="inlineStr">
+        <is>
+          <t>philosophe &amp;amp; historien de l'art français auteur de plus de cinquante ouvrages.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">art</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="157.5" customHeight="1" s="28">
+      <c r="A37" s="34" t="n">
+        <v>1953</v>
+      </c>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>Olivier ABEL</t>
+        </is>
+      </c>
+      <c r="E37" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olivier_Abel"  style="color:#6A142A"  title=" Wikipedia"&gt;Olivier ABEL&lt;/a&gt;  est un philosophe français spécialiste en éthique et philosophie morale, influencé par Paul Ricœur, Emmanuel Levinas et la tradition protestante. Il soutient en 1983 une thèse sur la rêverie chez Gaston Bachelard sous la direction de Ricœur, puis une habilitation en 2000 sur le temps éthique entre courage et pardon. &lt;/p&gt; &lt;p&gt; Créateur du Fonds Ricœur à Paris, doyen de la Faculté protestante de Paris, il a présidé la Commission d'éthique de la &lt;a href="https://www.lavie.fr/idees/histoire/olivier-abel-avec-le-catholicisme-leffort-fait-partie-du-chemin-pour-acceder-a-la-grace-100952.php"  title="Olivier Abel : Avec le catholicisme, l’effort fait partie du chemin pour accéder à la grâce par la Vie"&gt;Fédération protestante &lt;/a&gt;  de France et est membre de l'Académie de Nîmes depuis 2018. Il est aussi membre du Comité consultatif national d'éthique et contribue à des revues comme Esprit. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'éthique interrogative, le pardon, la conversation, l'Europe et les penseurs protestants comme Calvin ou Bayle. Parmi ses ouvrages : L’éthique interrogative (2000), Le pardon, briser la dette et l’oubli (1991), Le vertige de l’Europe (2019),  &lt;a href="https://www.youtube.com/watch?v=G1_ynk7E7LQ" title="Olivier Abel, philosophe : Le signe de l’humiliation, c’est cette parole rentrée par FRANCE 24"&gt;De l’humiliation &lt;/a&gt; (récent) et La naissance, qu’est-ce que ça change. Il explore la fugacité des liens humains et une critique du sujet délié. Pour lui, l’éthique n’est pas un système de règles à appliquer, mais un art de poser les bonnes questions dans les situations où plusieurs biens entrent en conflit : c’est ce qu’il appelle une « éthique interrogative ». Il s’intéresse au pardon, qui permet de délier une relation sans l’effacer, et à l’humiliation, qu’il décrit comme une parole empêchée, une manière de priver l’autre de sa place dans la conversation commune. &lt;/p&gt; 
+ &lt;audio controls title="Le témoin du vendredi : Olivier Abel, la civilisation européenne par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11739-12.04.2019-ITEMA_22034063-2019F17009S0102-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+        </is>
+      </c>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>h629a3ItbQI</t>
+          <t>uXvouJ3eFls</t>
         </is>
       </c>
       <c r="G37" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Qui êtes-vous Georges Didi-Huberman ?" par ABC Penser</t>
+          <t>"Olivier Abel, « il faut arrêter le déni de l’humiliation »" par Regards propestants</t>
         </is>
       </c>
       <c r="H37" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/huberman-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/oabel-mini.webp</t>
         </is>
       </c>
       <c r="I37" s="36" t="n"/>
       <c r="J37" s="27" t="inlineStr">
         <is>
-          <t>esthetique ; epistemologie</t>
+          <t>ethique ; spiritualite</t>
         </is>
       </c>
       <c r="K37" s="27" t="inlineStr">
         <is>
-          <t>Herméneutique ; Phénoménologie</t>
+          <t>Herméneutique</t>
         </is>
       </c>
       <c r="L37" s="27" t="inlineStr">
         <is>
-          <t>philosophe &amp;amp; historien de l'art français auteur de plus de cinquante ouvrages.</t>
+          <t>philosophe français spécialiste en éthique et philosophie morale.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2943,60 +2942,60 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">art</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="157.5" customHeight="1" s="28">
+          <t xml:space="preserve">sens ; continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="126.75" customHeight="1" s="28">
       <c r="A38" s="34" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="B38" s="34" t="n"/>
       <c r="C38" s="34" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="D38" s="35" t="inlineStr">
         <is>
-          <t>Olivier ABEL</t>
+          <t>Pascal ENGEL</t>
         </is>
       </c>
       <c r="E38" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olivier_Abel"  style="color:#6A142A"  title=" Wikipedia"&gt;Olivier ABEL&lt;/a&gt;  est un philosophe français spécialiste en éthique et philosophie morale, influencé par Paul Ricœur, Emmanuel Levinas et la tradition protestante. Il soutient en 1983 une thèse sur la rêverie chez Gaston Bachelard sous la direction de Ricœur, puis une habilitation en 2000 sur le temps éthique entre courage et pardon. &lt;/p&gt; &lt;p&gt; Créateur du Fonds Ricœur à Paris, doyen de la Faculté protestante de Paris, il a présidé la Commission d'éthique de la &lt;a href="https://www.lavie.fr/idees/histoire/olivier-abel-avec-le-catholicisme-leffort-fait-partie-du-chemin-pour-acceder-a-la-grace-100952.php"  title="Olivier Abel : Avec le catholicisme, l’effort fait partie du chemin pour accéder à la grâce par la Vie"&gt;Fédération protestante &lt;/a&gt;  de France et est membre de l'Académie de Nîmes depuis 2018. Il est aussi membre du Comité consultatif national d'éthique et contribue à des revues comme Esprit. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'éthique interrogative, le pardon, la conversation, l'Europe et les penseurs protestants comme Calvin ou Bayle. Parmi ses ouvrages : L’éthique interrogative (2000), Le pardon, briser la dette et l’oubli (1991), Le vertige de l’Europe (2019),  &lt;a href="https://www.youtube.com/watch?v=G1_ynk7E7LQ" title="Olivier Abel, philosophe : Le signe de l’humiliation, c’est cette parole rentrée par FRANCE 24"&gt;De l’humiliation &lt;/a&gt; (récent) et La naissance, qu’est-ce que ça change. Il explore la fugacité des liens humains et une critique du sujet délié. Pour lui, l’éthique n’est pas un système de règles à appliquer, mais un art de poser les bonnes questions dans les situations où plusieurs biens entrent en conflit : c’est ce qu’il appelle une « éthique interrogative ». Il s’intéresse au pardon, qui permet de délier une relation sans l’effacer, et à l’humiliation, qu’il décrit comme une parole empêchée, une manière de priver l’autre de sa place dans la conversation commune. &lt;/p&gt; 
- &lt;audio controls title="Le témoin du vendredi : Olivier Abel, la civilisation européenne par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11739-12.04.2019-ITEMA_22034063-2019F17009S0102-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Engel"   title=" Wikipedia"&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent "La Norme du vrai" paru en 1989 sur la philosophie de la logique, &lt;a href="https://www.youtube.com/watch?v=ivsIBYFN6DI" title="*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos"&gt; "Va savoir"&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et "Les vices du savoir" en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. Pour lui, la croyance a une norme propre : croire, c’est viser la vérité, et l’on ne peut croire à volonté ce que l’on sait faux. Dans &lt;em&gt;Les Vices du savoir&lt;/em&gt;, il montre que l’indifférence à la vérité, le « baratin » et la paresse intellectuelle sont de véritables fautes morales, dont les intellectuels eux-mêmes ne sont pas exempts. &lt;/p&gt;   &lt;audio controls title="Faut-il faire la morale aux intellectuels ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+</t>
         </is>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>uXvouJ3eFls</t>
+          <t>iSesDHgeOYM</t>
         </is>
       </c>
       <c r="G38" s="36" t="inlineStr">
         <is>
-          <t>"Olivier Abel, « il faut arrêter le déni de l’humiliation »" par Regards propestants</t>
+          <t>"Pascal Engel - Introduction à l'épistémologie générale" par Bout de sagesse</t>
         </is>
       </c>
       <c r="H38" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/oabel-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/engel-mini.webp</t>
         </is>
       </c>
       <c r="I38" s="36" t="n"/>
       <c r="J38" s="27" t="inlineStr">
         <is>
-          <t>ethique ; spiritualite</t>
+          <t>epistemologie ; logique</t>
         </is>
       </c>
       <c r="K38" s="27" t="inlineStr">
         <is>
-          <t>Herméneutique</t>
+          <t>Analytique</t>
         </is>
       </c>
       <c r="L38" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste en éthique et philosophie morale.</t>
+          <t>philosophe français spécialiste de la philosophie du langage, de la logique et la connaissance.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3004,62 +3003,62 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="O38"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">sens ; continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="126.75" customHeight="1" s="28">
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="162" customHeight="1" s="28">
       <c r="A39" s="34" t="n">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="B39" s="34" t="n"/>
       <c r="C39" s="34" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>Pascal ENGEL</t>
-        </is>
-      </c>
-      <c r="E39" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Engel"   title=" Wikipedia"&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent "La Norme du vrai" paru en 1989 sur la philosophie de la logique, &lt;a href="https://www.youtube.com/watch?v=ivsIBYFN6DI" title="*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos"&gt; "Va savoir"&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et "Les vices du savoir" en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. Pour lui, la croyance a une norme propre : croire, c’est viser la vérité, et l’on ne peut croire à volonté ce que l’on sait faux. Dans &lt;em&gt;Les Vices du savoir&lt;/em&gt;, il montre que l’indifférence à la vérité, le « baratin » et la paresse intellectuelle sont de véritables fautes morales, dont les intellectuels eux-mêmes ne sont pas exempts. &lt;/p&gt;   &lt;audio controls title="Faut-il faire la morale aux intellectuels ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
+          <t>Charles RAMOND</t>
+        </is>
+      </c>
+      <c r="E39" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Ramond"  title=" Wikipedia"&gt;Charles RAMOND&lt;/a&gt;  est un philosophe français, professeur des universités à Paris-VIII Vincennes-Saint-Denis, où il occupe une chaire de philosophie des sciences et épistémologie de la culture. Spécialiste de Spinoza et de Derrida, il anime un séminaire dédié au philosophe néerlandais et explore la philosophie moderne et contemporaine, avec un accent sur l'ontologie, la logique et la politique des rationalismes classiques. Il a publié de nombreux ouvrages, dont une thèse sur la qualité et la quantité chez Spinoza (1995), un Vocabulaire de Spinoza (1999) et un Dictionnaire Spinoza (2007).  &lt;/p&gt; &lt;p&gt; Il présente Spinoza comme le philosophe de la modernité par excellence, avec des analyses du Traité politique soulignant l'antériorité du politique sur le moral et la démocratie comme régime absolu fondé sur le nombre et la puissance. Il a aussi étudié Descartes dans Descartes, Promesses et paradoxes (2011), explorant les paradoxes de la liberté et de l'irrésolution, ainsi que Derrida et la philosophie du langage. Ses conférences, comme celle à Pékin en 2019, relient Spinoza aux lectures marxistes et aux thèmes de justice et de droit.&lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est la « résolution de problèmes théoriques par les moyens du langage ordinaire », mobilisant rhétorique, ironie et subtilités quotidiennes sans sacrifier rigueur ni clarté. Il rejette les degrés de conceptualité : on peut philosophier avec des termes simples comme « chats » ou « marmites », en mettant ce langage au service de la réflexion pour trancher des problèmes purement théoriques. Chez Spinoza, il défend un conservatisme rationnel immanent à la durée, où ce qui dure est rationnel, et une politique démocratique sceptique obéissant à la loi non pour sa bonté morale mais pour sa validité majoritaire. &lt;/p&gt; &lt;p&gt; Ses réflexions insistent sur la politique spinoziste : justice et injustice n'existent qu'en État, le droit se mesure à la puissance collective, et la démocratie privilégie les « préférences » sur les justifications morales ou républicaines. Il critique les morales théologiques résiduelles en politique moderne et valorise une pensée immanente ouverte aux changements, influencée par la raison spinoziste qui priorise la stabilité sur les valeurs transcendantes. Ramond aborde aussi les sentiments moraux comme l'injustice et les enjeux épistémologiques contemporains. &lt;/p&gt;             &lt;audio controls title="Dictionnaire Derrida de charles Ramond par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-10.01.2017-ITEMA_21192290-2017C24269S0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>iSesDHgeOYM</t>
+          <t>M6vSXx4V98w</t>
         </is>
       </c>
       <c r="G39" s="36" t="inlineStr">
         <is>
-          <t>"Pascal Engel - Introduction à l'épistémologie générale" par Bout de sagesse</t>
+          <t xml:space="preserve">"Peut-on se fier au sentiment d'injustice ? - Charles RAMOND" par MSH Alpes</t>
         </is>
       </c>
       <c r="H39" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/engel-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/cramond-mini.webp</t>
         </is>
       </c>
       <c r="I39" s="36" t="n"/>
       <c r="J39" s="27" t="inlineStr">
         <is>
-          <t>epistemologie ; logique</t>
+          <t>epistemologie ; politique</t>
         </is>
       </c>
       <c r="K39" s="27" t="inlineStr">
         <is>
-          <t>Analytique</t>
+          <t>Rationalisme</t>
         </is>
       </c>
       <c r="L39" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la philosophie du langage, de la logique et la connaissance.</t>
+          <t>philosophe français spécialiste de Derrida et de Spinoza.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3067,62 +3066,61 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O39"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="162" customHeight="1" s="28">
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="137.25" customHeight="1" s="28">
       <c r="A40" s="34" t="n">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="B40" s="34" t="n"/>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>Charles RAMOND</t>
+          <t>Michel ONFRAY</t>
         </is>
       </c>
       <c r="E40" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Ramond"  title=" Wikipedia"&gt;Charles RAMOND&lt;/a&gt;  est un philosophe français, professeur des universités à Paris-VIII Vincennes-Saint-Denis, où il occupe une chaire de philosophie des sciences et épistémologie de la culture. Spécialiste de Spinoza et de Derrida, il anime un séminaire dédié au philosophe néerlandais et explore la philosophie moderne et contemporaine, avec un accent sur l'ontologie, la logique et la politique des rationalismes classiques. Il a publié de nombreux ouvrages, dont une thèse sur la qualité et la quantité chez Spinoza (1995), un Vocabulaire de Spinoza (1999) et un Dictionnaire Spinoza (2007).  &lt;/p&gt; &lt;p&gt; Il présente Spinoza comme le philosophe de la modernité par excellence, avec des analyses du Traité politique soulignant l'antériorité du politique sur le moral et la démocratie comme régime absolu fondé sur le nombre et la puissance. Il a aussi étudié Descartes dans Descartes, Promesses et paradoxes (2011), explorant les paradoxes de la liberté et de l'irrésolution, ainsi que Derrida et la philosophie du langage. Ses conférences, comme celle à Pékin en 2019, relient Spinoza aux lectures marxistes et aux thèmes de justice et de droit.&lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est la « résolution de problèmes théoriques par les moyens du langage ordinaire », mobilisant rhétorique, ironie et subtilités quotidiennes sans sacrifier rigueur ni clarté. Il rejette les degrés de conceptualité : on peut philosophier avec des termes simples comme « chats » ou « marmites », en mettant ce langage au service de la réflexion pour trancher des problèmes purement théoriques. Chez Spinoza, il défend un conservatisme rationnel immanent à la durée, où ce qui dure est rationnel, et une politique démocratique sceptique obéissant à la loi non pour sa bonté morale mais pour sa validité majoritaire. &lt;/p&gt; &lt;p&gt; Ses réflexions insistent sur la politique spinoziste : justice et injustice n'existent qu'en État, le droit se mesure à la puissance collective, et la démocratie privilégie les « préférences » sur les justifications morales ou républicaines. Il critique les morales théologiques résiduelles en politique moderne et valorise une pensée immanente ouverte aux changements, influencée par la raison spinoziste qui priorise la stabilité sur les valeurs transcendantes. Ramond aborde aussi les sentiments moraux comme l'injustice et les enjeux épistémologiques contemporains. &lt;/p&gt;             &lt;audio controls title="Dictionnaire Derrida de charles Ramond par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-10.01.2017-ITEMA_21192290-2017C24269S0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Onfray"  title=" Wikipedia"&gt;Michel ONFRAY&lt;/a&gt; (né en 1959) est un philosophe et essayiste français, l’un des auteurs de philosophie les plus lus et les plus discutés de son pays. Né à Argentan, en Normandie, dans une famille modeste, il enseigne pendant vingt ans la philosophie dans un lycée technique de Caen. En 2002, il fonde l’Université populaire de Caen, aux cours gratuits et ouverts à tous, où il donne pendant des années une « contre-histoire de la philosophie », diffusée par France Culture.&lt;/p&gt; &lt;p&gt;Sa pensée se veut &lt;a href="https://www.youtube.com/watch?v=l4PX2P-KuBE&amp;ab_channel=AlainBajom%C3%A9e"   title="L'hédonisme par Alain Bajomée"&gt;hédoniste&lt;/a&gt;, matérialiste et libertaire. Contre la tradition idéaliste et chrétienne, qui méprise le corps et le plaisir, il réhabilite des penseurs qu’il juge oubliés : les atomistes, les cyrénaïques, Épicure, les libertins ou les utilitaristes. Pour lui, la philosophie doit partir de la vie concrète et du corps, et aider chacun à se construire, à faire la « sculpture de soi ». Son &lt;em&gt;Traité d’athéologie&lt;/em&gt; (2005), critique radicale des trois monothéismes, est un grand succès de librairie. Il a écrit aussi sur l’art, sur la morale et sur les grandes figures de la pensée, souvent de manière polémique : son livre contre Freud, en 2010, a suscité de vives controverses. Dans &lt;em&gt;Décadence&lt;/em&gt; (2017), il décrit l’épuisement de la civilisation judéo-chrétienne. Il a enfin fondé en 2020 la revue &lt;em&gt;Front populaire&lt;/em&gt;, souverainiste, et défend un &lt;a href="https://www.youtube.com/watch?v=wikRuhGQExI&amp;ab_channel=FrontPopulaire"    title="Qu'est ce que le populisme par Front Populaire"&gt;populisme&lt;/a&gt; qui oppose le peuple aux élites. &lt;a href="https://www.youtube.com/watch?v=MNY2U-T2Xf4&amp;ab_channel=MichelOnfray-Topic"  title="Les Raisons de l'Art par Michel Onfray"&gt;&lt;em&gt;Les Raisons de l’art&lt;/em&gt;&lt;/a&gt; montrent aussi son intérêt pour la création.&lt;/p&gt; &lt;p&gt;Ses critiques lui reprochent des simplifications et des lectures partiales de l’histoire de la philosophie ; ses lecteurs saluent un passeur qui rend la philosophie vivante et accessible.&lt;/p&gt;  &lt;audio controls title="La philosophie nous permet d'être d'abord vivants et ensuite libres par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19063-03.04.2023-ITEMA_23336345-2023I32164S0093-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>M6vSXx4V98w</t>
+          <t>ZYhgWCvrWJ8</t>
         </is>
       </c>
       <c r="G40" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Peut-on se fier au sentiment d'injustice ? - Charles RAMOND" par MSH Alpes</t>
+          <t>"Les raisons de l'art" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H40" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/cramond-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/onfray-mini.webp</t>
         </is>
       </c>
       <c r="I40" s="36" t="n"/>
       <c r="J40" s="27" t="inlineStr">
         <is>
-          <t>epistemologie ; politique</t>
+          <t>ethique ; politique</t>
         </is>
       </c>
       <c r="K40" s="27" t="inlineStr">
         <is>
-          <t>Rationalisme</t>
+          <t xml:space="preserve">Hédonisme ; Anarchisme ; Athéisme</t>
         </is>
       </c>
       <c r="L40" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de Derrida et de Spinoza.</t>
+          <t>philosophe français connu pour son engagement pour l'Athéisme et l'Anarchisme.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3132,11 +3130,11 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="137.25" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="126.75" customHeight="1" s="28">
       <c r="A41" s="34" t="n">
         <v>1959</v>
       </c>
@@ -3148,43 +3146,43 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>Michel ONFRAY</t>
-        </is>
-      </c>
-      <c r="E41" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Onfray"  title=" Wikipedia"&gt;Michel ONFRAY&lt;/a&gt; (né en 1959) est un philosophe et essayiste français, l’un des auteurs de philosophie les plus lus et les plus discutés de son pays. Né à Argentan, en Normandie, dans une famille modeste, il enseigne pendant vingt ans la philosophie dans un lycée technique de Caen. En 2002, il fonde l’Université populaire de Caen, aux cours gratuits et ouverts à tous, où il donne pendant des années une « contre-histoire de la philosophie », diffusée par France Culture.&lt;/p&gt; &lt;p&gt;Sa pensée se veut &lt;a href="https://www.youtube.com/watch?v=l4PX2P-KuBE&amp;ab_channel=AlainBajom%C3%A9e"   title="L'hédonisme par Alain Bajomée"&gt;hédoniste&lt;/a&gt;, matérialiste et libertaire. Contre la tradition idéaliste et chrétienne, qui méprise le corps et le plaisir, il réhabilite des penseurs qu’il juge oubliés : les atomistes, les cyrénaïques, Épicure, les libertins ou les utilitaristes. Pour lui, la philosophie doit partir de la vie concrète et du corps, et aider chacun à se construire, à faire la « sculpture de soi ». Son &lt;em&gt;Traité d’athéologie&lt;/em&gt; (2005), critique radicale des trois monothéismes, est un grand succès de librairie. Il a écrit aussi sur l’art, sur la morale et sur les grandes figures de la pensée, souvent de manière polémique : son livre contre Freud, en 2010, a suscité de vives controverses. Dans &lt;em&gt;Décadence&lt;/em&gt; (2017), il décrit l’épuisement de la civilisation judéo-chrétienne. Il a enfin fondé en 2020 la revue &lt;em&gt;Front populaire&lt;/em&gt;, souverainiste, et défend un &lt;a href="https://www.youtube.com/watch?v=wikRuhGQExI&amp;ab_channel=FrontPopulaire"    title="Qu'est ce que le populisme par Front Populaire"&gt;populisme&lt;/a&gt; qui oppose le peuple aux élites. &lt;a href="https://www.youtube.com/watch?v=MNY2U-T2Xf4&amp;ab_channel=MichelOnfray-Topic"  title="Les Raisons de l'Art par Michel Onfray"&gt;&lt;em&gt;Les Raisons de l’art&lt;/em&gt;&lt;/a&gt; montrent aussi son intérêt pour la création.&lt;/p&gt; &lt;p&gt;Ses critiques lui reprochent des simplifications et des lectures partiales de l’histoire de la philosophie ; ses lecteurs saluent un passeur qui rend la philosophie vivante et accessible.&lt;/p&gt;  &lt;audio controls title="La philosophie nous permet d'être d'abord vivants et ensuite libres par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19063-03.04.2023-ITEMA_23336345-2023I32164S0093-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Jean-Christophe GODDARD</t>
+        </is>
+      </c>
+      <c r="E41" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard"  title=" Wikipedia"&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J. G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime avec Marc Maesschalck le séminaire « Penser les décolonisations », commun aux universités de Toulouse et de Louvain-la-Neuve. Il organise aussi, avec le chorégraphe James Carlès, le festival Corpus Africana de Toulouse, et participe depuis 2019 à un séminaire d’anthropologie décoloniale à l’université nationale de Séoul. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href="https://www.youtube.com/watch?v=vEQWmSo67B4" style="color:#88A1E9" title="Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches"&gt;"Ce sont d'autres gens" &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la "qualité de la vie" sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href="https://www.youtube.com/watch?v=ZDpbSRrWIhU" title="Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées"&gt;"autre monde" &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;    &lt;audio controls title="Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>ZYhgWCvrWJ8</t>
+          <t>ezZGT5SlWDk</t>
         </is>
       </c>
       <c r="G41" s="36" t="inlineStr">
         <is>
-          <t>"Les raisons de l'art" par Librairie Mollat</t>
+          <t>"Contre-anthropologie du monde blanc - Jean-Christophe Goddard" par lundimatin</t>
         </is>
       </c>
       <c r="H41" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/onfray-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/goddard-mini.webp</t>
         </is>
       </c>
       <c r="I41" s="36" t="n"/>
       <c r="J41" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K41" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hédonisme ; Anarchisme ; Athéisme</t>
+          <t>Post-structuralisme</t>
         </is>
       </c>
       <c r="L41" s="27" t="inlineStr">
         <is>
-          <t>philosophe français connu pour son engagement pour l'Athéisme et l'Anarchisme.</t>
+          <t>philosophe français travaillant sur l'idéalisme allemand &amp;amp; la philosophie française du XXème.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3194,59 +3192,63 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="126.75" customHeight="1" s="28">
+          <t xml:space="preserve">continental ; decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="191" customHeight="1" s="28">
       <c r="A42" s="34" t="n">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="B42" s="34" t="n"/>
-      <c r="C42" s="34" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
+      <c r="C42" s="34" t="n">
+        <v>1961</v>
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>Jean-Christophe GODDARD</t>
-        </is>
-      </c>
-      <c r="E42" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard"  title=" Wikipedia"&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J. G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime avec Marc Maesschalck le séminaire « Penser les décolonisations », commun aux universités de Toulouse et de Louvain-la-Neuve. Il organise aussi, avec le chorégraphe James Carlès, le festival Corpus Africana de Toulouse, et participe depuis 2019 à un séminaire d’anthropologie décoloniale à l’université nationale de Séoul. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href="https://www.youtube.com/watch?v=vEQWmSo67B4" style="color:#88A1E9" title="Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches"&gt;"Ce sont d'autres gens" &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la "qualité de la vie" sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href="https://www.youtube.com/watch?v=ZDpbSRrWIhU" title="Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées"&gt;"autre monde" &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;    &lt;audio controls title="Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t>Sandra LAUGIER</t>
+        </is>
+      </c>
+      <c r="E42" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sandra_Laugier" title=" Wikipedia"&gt;Sandra LAUGIER&lt;/a&gt;  est une philosophe française, professeure à l’université Paris 1 Panthéon-Sorbonne, membre de l’Institut Universitaire de France et spécialiste de philosophie du langage, de philosophie morale et de philosophie politique. Elle a aussi beaucoup travaillé sur Stanley Cavell, qu’elle a traduit en français, ainsi que sur Emerson, Thoreau et le perfectionnisme moral. &lt;/p&gt; &lt;p&gt; Sa philosophie accorde une place centrale à l’ordinaire : les gestes, les paroles, les liens quotidiens et les formes de vie concrètes sont pour elle des lieux essentiels de la pensée. Elle défend l’idée qu’il faut partir de l’expérience vécue plutôt que de grands systèmes abstraits, ce qui l’a conduite à développer une éthique du care, une réflexion sur le langage ordinaire et une attention aux formes discrètes de la vie commune. &lt;/p&gt; &lt;p&gt; Sur le plan politique, elle s’intéresse aux formes contemporaines de démocratie, à &lt;a href="https://www.youtube.com/watch?v=nlM-aPBIRdg" title="Sandra Laugier : reconnaître nos dépendances par France Inter"&gt;la désobéissance civile &lt;/a&gt; et aux mouvements horizontaux comme Nuit debout. Elle y voit une manière de repenser le politique à partir de l’expression des personnes, du souci du commun et de l’égalité effective des droits, plutôt que d’un modèle hiérarchique classique. Cette perspective la conduit à défendre une démocratie plus attentive aux voix singulières et aux pratiques collectives concrètes. &lt;/p&gt; &lt;p&gt; Elle a aussi élargi la philosophie à la culture populaire, notamment &lt;a href="https://www.youtube.com/watch?v=Rjd2XEvkqWc" title="Sandra Laugier : nos vies en séries par librairie mollat"&gt;aux séries télévisées, &lt;/a&gt; qu’elle considère comme un laboratoire d’expériences morales et politiques. Dans des ouvrages récents, elle montre que les séries peuvent aider à penser nos manières de vivre, nos attachements et nos conflits, en révélant des aspects très actuels de la sensibilité démocratique. &lt;/p&gt;  &lt;audio controls title="L’éthique animale avec Florence Burgat par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+</t>
         </is>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>ezZGT5SlWDk</t>
+          <t>fCTQpI27AeM</t>
         </is>
       </c>
       <c r="G42" s="36" t="inlineStr">
         <is>
-          <t>"Contre-anthropologie du monde blanc - Jean-Christophe Goddard" par lundimatin</t>
-        </is>
-      </c>
-      <c r="H42" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/goddard-mini.webp</t>
+          <t xml:space="preserve">qui êtes vous Sandra LAUGIER par ABC Penser</t>
+        </is>
+      </c>
+      <c r="H42" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/slaugier-mini.webp</t>
         </is>
       </c>
       <c r="I42" s="36" t="n"/>
       <c r="J42" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; epistemologie</t>
+          <t>ethique ; epistemologie</t>
         </is>
       </c>
       <c r="K42" s="27" t="inlineStr">
         <is>
-          <t>Post-structuralisme</t>
+          <t xml:space="preserve">Analytique ; Éthique de la sollicitude</t>
         </is>
       </c>
       <c r="L42" s="27" t="inlineStr">
         <is>
-          <t>philosophe français travaillant sur l'idéalisme allemand &amp;amp; la philosophie française du XXème.</t>
+          <t>philosophe française spécialiste du langage, de la morale et de philosophie politique.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3256,127 +3258,128 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental ; decolonial</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="191" customHeight="1" s="28">
+          <t xml:space="preserve">genre ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="202.95" customHeight="1" s="28">
       <c r="A43" s="34" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B43" s="34" t="n"/>
-      <c r="C43" s="34" t="n">
-        <v>1961</v>
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>Sandra LAUGIER</t>
-        </is>
-      </c>
-      <c r="E43" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sandra_Laugier" title=" Wikipedia"&gt;Sandra LAUGIER&lt;/a&gt;  est une philosophe française, professeure à l’université Paris 1 Panthéon-Sorbonne, membre de l’Institut Universitaire de France et spécialiste de philosophie du langage, de philosophie morale et de philosophie politique. Elle a aussi beaucoup travaillé sur Stanley Cavell, qu’elle a traduit en français, ainsi que sur Emerson, Thoreau et le perfectionnisme moral. &lt;/p&gt; &lt;p&gt; Sa philosophie accorde une place centrale à l’ordinaire : les gestes, les paroles, les liens quotidiens et les formes de vie concrètes sont pour elle des lieux essentiels de la pensée. Elle défend l’idée qu’il faut partir de l’expérience vécue plutôt que de grands systèmes abstraits, ce qui l’a conduite à développer une éthique du care, une réflexion sur le langage ordinaire et une attention aux formes discrètes de la vie commune. &lt;/p&gt; &lt;p&gt; Sur le plan politique, elle s’intéresse aux formes contemporaines de démocratie, à &lt;a href="https://www.youtube.com/watch?v=nlM-aPBIRdg" title="Sandra Laugier : reconnaître nos dépendances par France Inter"&gt;la désobéissance civile &lt;/a&gt; et aux mouvements horizontaux comme Nuit debout. Elle y voit une manière de repenser le politique à partir de l’expression des personnes, du souci du commun et de l’égalité effective des droits, plutôt que d’un modèle hiérarchique classique. Cette perspective la conduit à défendre une démocratie plus attentive aux voix singulières et aux pratiques collectives concrètes. &lt;/p&gt; &lt;p&gt; Elle a aussi élargi la philosophie à la culture populaire, notamment &lt;a href="https://www.youtube.com/watch?v=Rjd2XEvkqWc" title="Sandra Laugier : nos vies en séries par librairie mollat"&gt;aux séries télévisées, &lt;/a&gt; qu’elle considère comme un laboratoire d’expériences morales et politiques. Dans des ouvrages récents, elle montre que les séries peuvent aider à penser nos manières de vivre, nos attachements et nos conflits, en révélant des aspects très actuels de la sensibilité démocratique. &lt;/p&gt;  &lt;audio controls title="L’éthique animale avec Florence Burgat par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
-        </is>
-      </c>
-      <c r="F43" s="34" t="inlineStr">
-        <is>
-          <t>fCTQpI27AeM</t>
-        </is>
-      </c>
-      <c r="G43" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">qui êtes vous Sandra LAUGIER par ABC Penser</t>
-        </is>
-      </c>
-      <c r="H43" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/slaugier-mini.webp</t>
-        </is>
-      </c>
-      <c r="I43" s="36" t="n"/>
-      <c r="J43" s="27" t="inlineStr">
-        <is>
-          <t>ethique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K43" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Analytique ; Éthique de la sollicitude</t>
-        </is>
-      </c>
-      <c r="L43" s="27" t="inlineStr">
-        <is>
-          <t>philosophe française spécialiste du langage, de la morale et de philosophie politique.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">genre ; reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="202.95" customHeight="1" s="28">
-      <c r="A44" s="34" t="n">
-        <v>1962</v>
-      </c>
-      <c r="B44" s="34" t="n"/>
-      <c r="C44" s="34" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="D44" s="35" t="inlineStr">
-        <is>
           <t>Dominique MÉDA</t>
         </is>
       </c>
-      <c r="E44" s="36" t="inlineStr">
+      <c r="E43" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_M%C3%A9da" title=" Wikipedia"&gt;Dominique MÉDA&lt;/a&gt;  est une philosophe française  reconnue pour ses analyses critiques sur le travail, les politiques sociales et la  &lt;a href="https://www.youtube.com/watch?v=jzyFjl0_QQE" title="La vraie révolution, c'est de désintensifier le travail ! Dominique Méda par Metabolism of Cities"&gt;transition écologique&lt;/a&gt;, elle combine une formation d'élite avec un engagement intellectuel profond sur les inégalités et la mesure de la richesse sociétale.  Elle est professeure de &lt;a href="https://www.youtube.com/watch?v=vKGU1tCOW90"  title="Dominique Méda, une sociologie contemporaine par Anthropologiques"&gt; sociologie &lt;/a&gt; à l'université Paris Dauphine-PSL, dirige l'IRISSO et a occupé la chaire "Reconversion écologique, travail et emploi" au Collège d'études mondiales. Elle fonde en 2010 le Laboratoire de l'égalité professionnelle entre femmes et hommes. &lt;/p&gt; &lt;p&gt; Ses travaux interrogent la centralité du travail dans les sociétés modernes, critiquant son rôle comme norme sociale totale et plaidant pour sa réduction au profit d'autres activités. Elle dénonce les limites du PIB comme indicateur de richesse, proposant des alternatives incluant le travail domestique, familial et écologique. Depuis les années 2010, elle se focalise sur la transition écologique, les inégalités de genre dans l'emploi et les réformes du travail  comme la flexisécurité. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"Le travail, une valeur en voie de disparition ?" paru en  1995 : histoire philosophique du concept de travail et plaidoyer pour sa redéfinition. "Qu'est-ce que la richesse ?" paru en 1999 : critique des indicateurs économiques traditionnels. "La reconversion écologique"(ouvrages récents) : lien entre écologie, emploi et justice sociale. &lt;/p&gt; &lt;audio controls title="Sandra LAUGIER par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11189-26.03.2012-ITEMA_20355259-2012C15000E0020-ITE_00049197_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 ​
 </t>
         </is>
       </c>
+      <c r="F43" s="34" t="inlineStr">
+        <is>
+          <t>sF6TLJ92amU</t>
+        </is>
+      </c>
+      <c r="G43" s="36" t="inlineStr">
+        <is>
+          <t>"Compétition mondiale, dette, urgence climatique : comment sortir du piège ? - DOMINIQUE MEDA" par Sismique</t>
+        </is>
+      </c>
+      <c r="H43" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/meda-mini.webp</t>
+        </is>
+      </c>
+      <c r="I43" s="36" t="n"/>
+      <c r="J43" s="27" t="inlineStr">
+        <is>
+          <t>politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K43" s="27" t="inlineStr">
+        <is>
+          <t>Ecologisme</t>
+        </is>
+      </c>
+      <c r="L43" s="27" t="inlineStr">
+        <is>
+          <t>philosophe française menant une réflexion philosophique et sociologique sur la place du travail.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="189.75" customHeight="1" s="28">
+      <c r="A44" s="34" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B44" s="34" t="n"/>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>Florence BURGAT</t>
+        </is>
+      </c>
+      <c r="E44" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Florence_Burgat"  title=" Wikipedia"&gt;Florence BURGAT&lt;/a&gt; est une philosophe française spécialisée dans la phénoménologie de la vie animale et l’éthique animale. Son itinéraire académique comprend une formation en philosophie et une implication dans des laboratoires et équipes de recherche en sciences humaines, avec des décennies d’activité comme directrice de recherche et enseignante dans des institutions françaises de haut niveau. &lt;/p&gt; &lt;p&gt; "Liberté et inquiétude de la vie animale" paru en 2006 et "Une autre existence" paru en 2012 sont parmi ses essais-clés. Ils proposent une phénoménologie de l’animal qui attribue aux animaux une vie vécue, une biographie et un monde propre, en opposition à une conception purement biologique ou fonctionnelle de l’animalité. Son approche met en lumière la distinction entre vivre en première personne et exister biologiquement, et elle s’interroge sur la place des animaux dans les sociétés modernes — notamment dans les pratiques d’élevage, &lt;a href="https://reporterre.net/Florence-Burgat-L-institution-de-l-alimentation-carnee-reflete-un-desir-tres " title="Florence Burgat : « L’institution de l’alimentation carnée reflète un désir très profond de l’humanité  par Reportere"&gt;l’alimentation carnée&lt;/a&gt;, le droit animalier et les enjeux éthiques qui en découlent. Elle a aussi écrit sur la vie végétale et a développé une réflexion sur l’institution de l’alimentation carnée, la notion de sacrifice et les mythes qui entourent l’humanité carnivore, élargissant ainsi la portée philosophique de &lt;a href="https://www.youtube.com/watch?v=AzVErgOotx0" title=" Idées: Carnivore, l'Humanité n'est pas dans son assiette? par TV5Monde"&gt;l’éthique animale &lt;/a&gt; à des domaines comme la nourriture, le droit et la société. &lt;/p&gt; &lt;p&gt; Elle a publié et contribué à des revues et ouvrages dédiés à la philosophie contemporaine et à l’éthique animale. Elle est souvent associée à des discussions sur la manière dont les sociétés humaines reconnaissent ou nüancent l’existence des autres vivants et comment cela influence les pratiques culturelles et juridiques. Son travail est référencé dans des bibliographies universitaires et chez des éditeurs de sciences humaines, ce qui en fait une voix importante pour ceux qui s’interrogent sur la dignité et la vie des êtres non humains dans un cadre éthique et philosophique. &lt;/p&gt;   &lt;audio controls title="L’éthique animale avec Florence Burgat par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>sF6TLJ92amU</t>
+          <t>wfuQnGA9izE</t>
         </is>
       </c>
       <c r="G44" s="36" t="inlineStr">
         <is>
-          <t>"Compétition mondiale, dette, urgence climatique : comment sortir du piège ? - DOMINIQUE MEDA" par Sismique</t>
+          <t>"L'humanité carnivore par Florence Burgat" par L214 Ethique &amp; Animaux</t>
         </is>
       </c>
       <c r="H44" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/meda-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/burgat-mini.webp</t>
         </is>
       </c>
       <c r="I44" s="36" t="n"/>
       <c r="J44" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>ethique</t>
         </is>
       </c>
       <c r="K44" s="27" t="inlineStr">
         <is>
-          <t>Ecologisme</t>
+          <t>Phénoménologie</t>
         </is>
       </c>
       <c r="L44" s="27" t="inlineStr">
         <is>
-          <t>philosophe française menant une réflexion philosophique et sociologique sur la place du travail.</t>
+          <t>philosophe française spécialiste de la cause animale et des droits des animaux.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3391,11 +3394,11 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="189.75" customHeight="1" s="28">
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="147.75" customHeight="1" s="28">
       <c r="A45" s="34" t="n">
         <v>1962</v>
       </c>
@@ -3407,48 +3410,44 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>Florence BURGAT</t>
-        </is>
-      </c>
-      <c r="E45" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Florence_Burgat"  title=" Wikipedia"&gt;Florence BURGAT&lt;/a&gt; est une philosophe française spécialisée dans la phénoménologie de la vie animale et l’éthique animale. Son itinéraire académique comprend une formation en philosophie et une implication dans des laboratoires et équipes de recherche en sciences humaines, avec des décennies d’activité comme directrice de recherche et enseignante dans des institutions françaises de haut niveau. &lt;/p&gt; &lt;p&gt; "Liberté et inquiétude de la vie animale" paru en 2006 et "Une autre existence" paru en 2012 sont parmi ses essais-clés. Ils proposent une phénoménologie de l’animal qui attribue aux animaux une vie vécue, une biographie et un monde propre, en opposition à une conception purement biologique ou fonctionnelle de l’animalité. Son approche met en lumière la distinction entre vivre en première personne et exister biologiquement, et elle s’interroge sur la place des animaux dans les sociétés modernes — notamment dans les pratiques d’élevage, &lt;a href="https://reporterre.net/Florence-Burgat-L-institution-de-l-alimentation-carnee-reflete-un-desir-tres " title="Florence Burgat : « L’institution de l’alimentation carnée reflète un désir très profond de l’humanité  par Reportere"&gt;l’alimentation carnée&lt;/a&gt;, le droit animalier et les enjeux éthiques qui en découlent. Elle a aussi écrit sur la vie végétale et a développé une réflexion sur l’institution de l’alimentation carnée, la notion de sacrifice et les mythes qui entourent l’humanité carnivore, élargissant ainsi la portée philosophique de &lt;a href="https://www.youtube.com/watch?v=AzVErgOotx0" title=" Idées: Carnivore, l'Humanité n'est pas dans son assiette? par TV5Monde"&gt;l’éthique animale &lt;/a&gt; à des domaines comme la nourriture, le droit et la société. &lt;/p&gt; &lt;p&gt; Elle a publié et contribué à des revues et ouvrages dédiés à la philosophie contemporaine et à l’éthique animale. Elle est souvent associée à des discussions sur la manière dont les sociétés humaines reconnaissent ou nüancent l’existence des autres vivants et comment cela influence les pratiques culturelles et juridiques. Son travail est référencé dans des bibliographies universitaires et chez des éditeurs de sciences humaines, ce qui en fait une voix importante pour ceux qui s’interrogent sur la dignité et la vie des êtres non humains dans un cadre éthique et philosophique. &lt;/p&gt;   &lt;audio controls title="L’éthique animale avec Florence Burgat par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Marc CRÉPON</t>
+        </is>
+      </c>
+      <c r="E45" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon"  title=" Wikipedia"&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href="https://www.youtube.com/watch?v=xOKttB1HgSk"  title="Marc Crépon sur la violence  par France Inter "&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href="https://www.youtube.com/watch?v=kwFC9MSSWcg"  title="Marc Crépon : l’épreuve de la haine   par Librairie mollat "&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; Il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste. Directeur de recherche au CNRS, il a d’abord étudié la manière dont les philosophes allemands et français pensent les langues et les cultures. Dans &lt;em&gt;Le Consentement meurtrier&lt;/em&gt; (2012), il s’interroge sur la façon dont nous acceptons, souvent sans le voir, la violence faite à d’autres, par la guerre, la misère ou l’indifférence. Dans &lt;em&gt;L’Épreuve de la haine&lt;/em&gt; (2016) il cherche comment résister à la haine sans y répondre par la haine.  &lt;/p&gt; &lt;audio controls title="Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>wfuQnGA9izE</t>
+          <t>zYbMprOKips</t>
         </is>
       </c>
       <c r="G45" s="36" t="inlineStr">
         <is>
-          <t>"L'humanité carnivore par Florence Burgat" par L214 Ethique &amp; Animaux</t>
+          <t>Qui êtes-vous Marc Crépon ?  par ABC Penser</t>
         </is>
       </c>
       <c r="H45" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/burgat-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/mcrepon-mini.webp</t>
         </is>
       </c>
       <c r="I45" s="36" t="n"/>
       <c r="J45" s="27" t="inlineStr">
         <is>
-          <t>ethique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K45" s="27" t="inlineStr">
         <is>
-          <t>Phénoménologie</t>
+          <t>Phénoménologie ; Herméneutique</t>
         </is>
       </c>
       <c r="L45" s="27" t="inlineStr">
         <is>
-          <t>philosophe française spécialiste de la cause animale et des droits des animaux.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français de la morale et de la politique, notamment de la violence, des langues et des communautés.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3458,60 +3457,59 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="147.75" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="261.75" customHeight="1" s="28">
       <c r="A46" s="34" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B46" s="34" t="n"/>
-      <c r="C46" s="34" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
+      <c r="C46" s="34" t="n">
+        <v>1963</v>
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>Marc CRÉPON</t>
+          <t>Paul AUDI</t>
         </is>
       </c>
       <c r="E46" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon"  title=" Wikipedia"&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href="https://www.youtube.com/watch?v=xOKttB1HgSk"  title="Marc Crépon sur la violence  par France Inter "&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href="https://www.youtube.com/watch?v=kwFC9MSSWcg"  title="Marc Crépon : l’épreuve de la haine   par Librairie mollat "&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; Il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste. Directeur de recherche au CNRS, il a d’abord étudié la manière dont les philosophes allemands et français pensent les langues et les cultures. Dans &lt;em&gt;Le Consentement meurtrier&lt;/em&gt; (2012), il s’interroge sur la façon dont nous acceptons, souvent sans le voir, la violence faite à d’autres, par la guerre, la misère ou l’indifférence. Dans &lt;em&gt;L’Épreuve de la haine&lt;/em&gt; (2016) il cherche comment résister à la haine sans y répondre par la haine.  &lt;/p&gt; &lt;audio controls title="Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Audi"  title=" Wikipedia"&gt;Paul AUDI&lt;/a&gt;  est un philosophe et écrivain français né à Beyrouth, au Liban, et ancien élève de l'École normale supérieure. Agrégé de philosophie et docteur en philosophie, il a soutenu une thèse sur Jean-Jacques Rousseau publiée en 1997. Après avoir enseigné à l'université de Paris-XII, il s'est éloigné du champ universitaire pour s'orienter vers l'édition, et aujourd'hui il est professeur invité dans diverses institutions en France et à l'étranger. Il est auteur de plus d'une trentaine d'ouvrages et membre de l'équipe de recherches PHILéPOL à l'université Paris Descartes. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre principalement sur les relations entre l'éthique et l'esthétique en Occident durant les Temps Modernes. Son œuvre explore ces liens à travers des &lt;a href="https://www.youtube.com/watch?v=3GRhkvYGMs0"  title="Paul Audi contrat social par le nouvel Obs"&gt;lectures de Rousseau, &lt;/a&gt;  Nietzsche, Lacan, Schopenhauer et Georges Bataille. Il est considéré comme un philosophe atypique, commençant à être reconnu hors de France. Sa pensée conjugue la vie du corps et la création artistique, l'éthique et la passion, avec un souci d'ancrer la pensée dans la vie physique. &lt;/p&gt; &lt;p&gt; L'idée centrale de sa philosophie est que l'acte de création et le comportement éthique ne forment qu'un seul et même geste, qui naît de la vie elle-même et finalement l'excède. Il nomme cette fusion « esth/éthique », considérant que l'éthique et l'esthétique dans l'acte de créer se confondent ou sont le recto et verso d'une même « explication avec la vie ». Pour lui, créer revient à « s'expliquer avec la vie », à faire de l'énigme que nous sommes une bribe d'un discours neuf. &lt;/p&gt; &lt;p&gt; L'éthique, selon lui, consiste d'abord en un travail sur soi, où « c'est moi-même qui suis la tâche ». La philosophie ne s'accomplit qu'au sein d'un corps à corps avec ce qui, en nous-mêmes, nous dépasse — non pas le monde ou un dehors, mais ce qui nous situe sur le  &lt;a href="https://www.youtube.com/watch?v=FJsDRUR9bYQ"  title="Paul Audi il faut le nuance par France Inter"&gt;« plan de la vie », &lt;/a&gt; qui ne recouvre ni le champ social ni l'espace politique. Cette éthique de la création, qu'il dénomme « esthéthique », n'est pas un code de règles mais une posture existentielle, une manière de se situer face au monde. &lt;/p&gt; &lt;p&gt; Il  s'intéresse également aux conditions permettant à l'être humain d'accéder à sa propre humanité, et interroge profondément la question de l'identité. Dans son ouvrage Troublante identité (2022), il parle pour la première fois de lui-même et de ce qui le hante, résistant à toute réduction de son être à sa provenance libanaise. Il désire en finir avec les clôtures identitaires et trouve son émancipation dans une conception juive d'une identité ouverte, toujours à construire, guidée par un impératif de justice à venir. Son dernier essai Le Vrai du beau (2026) transforme la contemplation d'un tableau en expérience de vérité, éclaircissant ce qui se joue en nous face à un tableau. &lt;/p&gt; 
+  &lt;audio controls title="la verité picturale existe t’elle ?  Par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/26657-24.04.2026-ITEMA_24487813-2026F45096S0114-NET_MFI_F40118A5-5297-4676-86E9-2E9A248FB2F7-27-03023a67ff6f93208a5f302d7d3b8771.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>zYbMprOKips</t>
+          <t>HvdSKzhBQCY</t>
         </is>
       </c>
       <c r="G46" s="36" t="inlineStr">
         <is>
-          <t>Qui êtes-vous Marc Crépon ?  par ABC Penser</t>
-        </is>
-      </c>
-      <c r="H46" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/mcrepon-mini.webp</t>
+          <t>en orient, l’antijudaisme paul AUDI par Akadem</t>
+        </is>
+      </c>
+      <c r="H46" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/paudi-mini.webp</t>
         </is>
       </c>
       <c r="I46" s="36" t="n"/>
       <c r="J46" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>ethique ; esthetique</t>
         </is>
       </c>
       <c r="K46" s="27" t="inlineStr">
         <is>
-          <t>Phénoménologie ; Herméneutique</t>
+          <t>Pessimisme</t>
         </is>
       </c>
       <c r="L46" s="27" t="inlineStr">
         <is>
-          <t>philosophe français de la morale et de la politique, notamment de la violence, des langues et des communautés.</t>
+          <t>philosophe français  centré sur les relations entre l'éthique et l'esthétique en Occident.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3521,7 +3519,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
+          <t xml:space="preserve">art</t>
         </is>
       </c>
     </row>
@@ -3535,45 +3533,44 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>Paul AUDI</t>
+          <t>Cyrille MICHON</t>
         </is>
       </c>
       <c r="E47" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Audi"  title=" Wikipedia"&gt;Paul AUDI&lt;/a&gt;  est un philosophe et écrivain français né à Beyrouth, au Liban, et ancien élève de l'École normale supérieure. Agrégé de philosophie et docteur en philosophie, il a soutenu une thèse sur Jean-Jacques Rousseau publiée en 1997. Après avoir enseigné à l'université de Paris-XII, il s'est éloigné du champ universitaire pour s'orienter vers l'édition, et aujourd'hui il est professeur invité dans diverses institutions en France et à l'étranger. Il est auteur de plus d'une trentaine d'ouvrages et membre de l'équipe de recherches PHILéPOL à l'université Paris Descartes. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre principalement sur les relations entre l'éthique et l'esthétique en Occident durant les Temps Modernes. Son œuvre explore ces liens à travers des &lt;a href="https://www.youtube.com/watch?v=3GRhkvYGMs0"  title="Paul Audi contrat social par le nouvel Obs"&gt;lectures de Rousseau, &lt;/a&gt;  Nietzsche, Lacan, Schopenhauer et Georges Bataille. Il est considéré comme un philosophe atypique, commençant à être reconnu hors de France. Sa pensée conjugue la vie du corps et la création artistique, l'éthique et la passion, avec un souci d'ancrer la pensée dans la vie physique. &lt;/p&gt; &lt;p&gt; L'idée centrale de sa philosophie est que l'acte de création et le comportement éthique ne forment qu'un seul et même geste, qui naît de la vie elle-même et finalement l'excède. Il nomme cette fusion « esth/éthique », considérant que l'éthique et l'esthétique dans l'acte de créer se confondent ou sont le recto et verso d'une même « explication avec la vie ». Pour lui, créer revient à « s'expliquer avec la vie », à faire de l'énigme que nous sommes une bribe d'un discours neuf. &lt;/p&gt; &lt;p&gt; L'éthique, selon lui, consiste d'abord en un travail sur soi, où « c'est moi-même qui suis la tâche ». La philosophie ne s'accomplit qu'au sein d'un corps à corps avec ce qui, en nous-mêmes, nous dépasse — non pas le monde ou un dehors, mais ce qui nous situe sur le  &lt;a href="https://www.youtube.com/watch?v=FJsDRUR9bYQ"  title="Paul Audi il faut le nuance par France Inter"&gt;« plan de la vie », &lt;/a&gt; qui ne recouvre ni le champ social ni l'espace politique. Cette éthique de la création, qu'il dénomme « esthéthique », n'est pas un code de règles mais une posture existentielle, une manière de se situer face au monde. &lt;/p&gt; &lt;p&gt; Il  s'intéresse également aux conditions permettant à l'être humain d'accéder à sa propre humanité, et interroge profondément la question de l'identité. Dans son ouvrage Troublante identité (2022), il parle pour la première fois de lui-même et de ce qui le hante, résistant à toute réduction de son être à sa provenance libanaise. Il désire en finir avec les clôtures identitaires et trouve son émancipation dans une conception juive d'une identité ouverte, toujours à construire, guidée par un impératif de justice à venir. Son dernier essai Le Vrai du beau (2026) transforme la contemplation d'un tableau en expérience de vérité, éclaircissant ce qui se joue en nous face à un tableau. &lt;/p&gt; 
-  &lt;audio controls title="la verité picturale existe t’elle ?  Par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/26657-24.04.2026-ITEMA_24487813-2026F45096S0114-NET_MFI_F40118A5-5297-4676-86E9-2E9A248FB2F7-27-03023a67ff6f93208a5f302d7d3b8771.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cyrille_Michon"  title=" Wikipedia"&gt;Cyrille MICHON&lt;/a&gt; est un philosophe français, professeur de philosophie à l’Université de Nantes. Formé à l’École normale supérieure, agrégé puis docteur en philosophie, il a d’abord consacré ses recherches à la philosophie médiévale, en particulier à Guillaume d’Ockham et à Thomas d’Aquin. Ses domaines de spécialité sont aujourd’hui la métaphysique, la philosophie de l’action, la   &lt;a href="https://www.youtube.com/watch?v=q-1VlvsVTOY"  title="vérité sur le christianisme par angelicum"&gt;philosophie de la religion &lt;/a&gt;  et la philosophie médiévale. &lt;/p&gt; &lt;p&gt; Sa réflexion porte principalement sur la liberté humaine, le libre arbitre et la responsabilité morale. Il pose une question classique mais toujours actuelle : pouvons-nous être véritablement responsables de nos actes si tout ce qui arrive est déterminé par des causes antérieures, par les lois de la nature ou par la providence divine ? Pour lui, comprendre la liberté exige donc d’examiner les rapports entre la volonté, l’action, les raisons de choisir et la responsabilité. &lt;/p&gt; &lt;p&gt; Dans Prescience et liberté, il étudie notamment le problème de la prescience divine : si Dieu sait infailliblement ce que nous allons faire, sommes-nous encore libres de le faire ou de ne pas le faire ? Il s’agit d’un problème central de la théologie philosophique, car il met en tension la connaissance parfaite de Dieu et la liberté humaine. Il cherche à montrer que la connaissance divine ne doit pas être confondue avec une contrainte causale exercée sur nos décisions. &lt;/p&gt; &lt;p&gt; Dans Répondre de soi. Enquête métaphysique sur la liberté humaine, publié en 2022, il défend une conception exigeante de la liberté, proche de ce que l’on appelle le libertarianisme métaphysique. Selon cette position, la liberté authentique n’est pas simplement le fait d’agir conformément à ses désirs, comme le soutiennent certains compatibilistes ; elle suppose que l’agent soit réellement l’auteur de son choix et qu’il puisse, dans un sens pertinent, prendre une autre décision. Il soutient ainsi que la responsabilité morale repose sur une liberté qui ne se réduit pas à l’absence de contrainte. &lt;/p&gt; &lt;p&gt; Sa philosophie se caractérise enfin par la rencontre entre la tradition médiévale, notamment thomiste, et la philosophie analytique contemporaine. Il mobilise une argumentation précise pour discuter le déterminisme, le hasard, les raisons de l’action et la responsabilité. Son œuvre cherche donc à montrer que les problèmes anciens — l’âme, la volonté, la providence ou la liberté — peuvent être reformulés avec les outils conceptuels de la philosophie contemporaine, sans perdre leur portée métaphysique. &lt;/p&gt; 
+&lt;audio controls title="le temps des monothéismes par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13094-29.12.2013-ITEMA_20567993-2013C21364E0017-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>HvdSKzhBQCY</t>
+          <t>-8NCPEbGk1o</t>
         </is>
       </c>
       <c r="G47" s="36" t="inlineStr">
         <is>
-          <t>en orient, l’antijudaisme paul AUDI par Akadem</t>
+          <t>Cyrille Michon – libre arbitre et déterminisme par Nantes Université</t>
         </is>
       </c>
       <c r="H47" s="37" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/paudi-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/cmichon-mini.webp</t>
         </is>
       </c>
       <c r="I47" s="36" t="n"/>
       <c r="J47" s="27" t="inlineStr">
         <is>
-          <t>ethique ; esthetique</t>
+          <t>metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K47" s="27" t="inlineStr">
         <is>
-          <t>Pessimisme</t>
-        </is>
-      </c>
-      <c r="L47" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français  centré sur les relations entre l'éthique et l'esthétique en Occident.</t>
+          <t>Libertarianisme ; Thomisme</t>
+        </is>
+      </c>
+      <c r="L47" s="43" t="inlineStr">
+        <is>
+          <t>philosophe français spécialiste de la philosophie médiévale, de la métaphysique et la philosophie de l’action.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3583,58 +3580,60 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">art</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="261.75" customHeight="1" s="28">
+          <t xml:space="preserve">sens ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="207.75" customHeight="1" s="28">
       <c r="A48" s="34" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B48" s="34" t="n"/>
-      <c r="C48" s="34" t="n">
-        <v>1963</v>
+      <c r="C48" s="34" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>Cyrille MICHON</t>
-        </is>
-      </c>
-      <c r="E48" s="38" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cyrille_Michon"  title=" Wikipedia"&gt;Cyrille MICHON&lt;/a&gt; est un philosophe français, professeur de philosophie à l’Université de Nantes. Formé à l’École normale supérieure, agrégé puis docteur en philosophie, il a d’abord consacré ses recherches à la philosophie médiévale, en particulier à Guillaume d’Ockham et à Thomas d’Aquin. Ses domaines de spécialité sont aujourd’hui la métaphysique, la philosophie de l’action, la   &lt;a href="https://www.youtube.com/watch?v=q-1VlvsVTOY"  title="vérité sur le christianisme par angelicum"&gt;philosophie de la religion &lt;/a&gt;  et la philosophie médiévale. &lt;/p&gt; &lt;p&gt; Sa réflexion porte principalement sur la liberté humaine, le libre arbitre et la responsabilité morale. Il pose une question classique mais toujours actuelle : pouvons-nous être véritablement responsables de nos actes si tout ce qui arrive est déterminé par des causes antérieures, par les lois de la nature ou par la providence divine ? Pour lui, comprendre la liberté exige donc d’examiner les rapports entre la volonté, l’action, les raisons de choisir et la responsabilité. &lt;/p&gt; &lt;p&gt; Dans Prescience et liberté, il étudie notamment le problème de la prescience divine : si Dieu sait infailliblement ce que nous allons faire, sommes-nous encore libres de le faire ou de ne pas le faire ? Il s’agit d’un problème central de la théologie philosophique, car il met en tension la connaissance parfaite de Dieu et la liberté humaine. Il cherche à montrer que la connaissance divine ne doit pas être confondue avec une contrainte causale exercée sur nos décisions. &lt;/p&gt; &lt;p&gt; Dans Répondre de soi. Enquête métaphysique sur la liberté humaine, publié en 2022, il défend une conception exigeante de la liberté, proche de ce que l’on appelle le libertarianisme métaphysique. Selon cette position, la liberté authentique n’est pas simplement le fait d’agir conformément à ses désirs, comme le soutiennent certains compatibilistes ; elle suppose que l’agent soit réellement l’auteur de son choix et qu’il puisse, dans un sens pertinent, prendre une autre décision. Il soutient ainsi que la responsabilité morale repose sur une liberté qui ne se réduit pas à l’absence de contrainte. &lt;/p&gt; &lt;p&gt; Sa philosophie se caractérise enfin par la rencontre entre la tradition médiévale, notamment thomiste, et la philosophie analytique contemporaine. Il mobilise une argumentation précise pour discuter le déterminisme, le hasard, les raisons de l’action et la responsabilité. Son œuvre cherche donc à montrer que les problèmes anciens — l’âme, la volonté, la providence ou la liberté — peuvent être reformulés avec les outils conceptuels de la philosophie contemporaine, sans perdre leur portée métaphysique. &lt;/p&gt; 
-&lt;audio controls title="le temps des monothéismes par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13094-29.12.2013-ITEMA_20567993-2013C21364E0017-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Frédéric WORMS</t>
+        </is>
+      </c>
+      <c r="E48" s="36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fr%C3%A9d%C3%A9ric_Worms"  title=" Wikipedia"&gt;Frédéric WORMS&lt;/a&gt; est un philosophe français  spécialiste de Bergson et des questions du vivant, du soin et de la démocratie. Ancien élève de l’ENS, agrégé de philosophie, il soutient en 1995 une thèse sur "le problème de l’esprit" chez Bergson, puis une habilitation publiée sous le titre "Bergson ou les deux sens de la vie". &lt;/p&gt; &lt;p&gt; Grand spécialiste d’Henri Bergson, il a dirigé l’édition critique ses œuvres complètes aux PUF et les Annales bergsoniennes. Sa lecture de Bergson insiste sur "les deux sens de la vie" : la vie comme simple conservation/instinct et la vie comme ouverture créatrice, tension qu’il prolonge dans sa propre philosophie du vivant. &lt;/p&gt; &lt;p&gt;  Son travail s’organise autour de deux axes : l’histoire de la philosophie et une réflexion propre sur les relations vitales et morales entre les êtres humains.  Il forge l’idée de  &lt;a href="https://www.youtube.com/watch?v=-gqpI3sJ3xQ"  title="Frédéric Worms, MOMENT par abc penser"&gt;"moment" &lt;/a&gt;  philosophique pour penser l’histoire de la philosophie française : chaque moment serait une rupture et un déplacement par rapport au précédent. &lt;/p&gt; &lt;p&gt; Dans ses &lt;a href="https://www.youtube.com/watch?v=dTWnuz7mZV4"  title="Frédéric Worms - Penser à quelqu'un par librairie mollat"&gt;livres récents &lt;/a&gt; (par ex. Pour un humanisme vital), il développe une philosophie du vivant qui articule la vulnérabilité, le refus de la mort sous toutes ses formes, et la nécessité de refonder l’éthique et la politique sur le soin. Le soin n’est pas seulement médical : il désigne pour lui l’ensemble des relations vitales, morales et politiques par lesquelles les humains se soutiennent ou se détruisent. &lt;/p&gt; &lt;p&gt; Membre du CCNE, il intervient sur la fin de vie, les biotechnologies, les neurosciences, la santé, en cherchant un équilibre entre protection des plus vulnérables et exigences démocratiques.  Il parle parfois de "maladies de la démocratie" : formes de fragilisation (inégalités, indifférence, désinformation) auxquelles il oppose l’idée d’une "démocratie vitale", nourrie par le soin et la reconnaissance des personnes. &lt;/p&gt; 
+ &lt;audio controls title="Comment reconnaît-on l’intelligence ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22788-26.01.2026-ITEMA_24386219-2026C45539E0001-NET_MFC_7E5F54FC-88F9-4EAB-A263-ED6928FD46E4-21-b7522d721c0e520ad7f9edd0fee90576.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>-8NCPEbGk1o</t>
+          <t>w8wD5uNhq8Y</t>
         </is>
       </c>
       <c r="G48" s="36" t="inlineStr">
         <is>
-          <t>Cyrille Michon – libre arbitre et déterminisme par Nantes Université</t>
-        </is>
-      </c>
-      <c r="H48" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/cmichon-mini.webp</t>
+          <t>"Frédéric Worms : "Je suis un peu fatigué des intellectuels qui transgressent la bien-pensance" par France Culture</t>
+        </is>
+      </c>
+      <c r="H48" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/worms-mini.webp</t>
         </is>
       </c>
       <c r="I48" s="36" t="n"/>
       <c r="J48" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; spiritualite</t>
+          <t>ethique ; epistemologie</t>
         </is>
       </c>
       <c r="K48" s="27" t="inlineStr">
         <is>
-          <t>Libertarianisme ; Thomisme</t>
-        </is>
-      </c>
-      <c r="L48" s="43" t="inlineStr">
-        <is>
-          <t>philosophe français spécialiste de la philosophie médiévale, de la métaphysique et la philosophie de l’action.</t>
+          <t>Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L48" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français historien de la philosophie &amp;amp; spécialiste de l'œuvre d'Henri Bergson.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3644,11 +3643,11 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">sens ; reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="207.75" customHeight="1" s="28">
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="116.25" customHeight="1" s="28">
       <c r="A49" s="34" t="n">
         <v>1964</v>
       </c>
@@ -3660,113 +3659,113 @@
       </c>
       <c r="D49" s="35" t="inlineStr">
         <is>
-          <t>Frédéric WORMS</t>
+          <t>Fabienne BRUGÈRE</t>
         </is>
       </c>
       <c r="E49" s="36" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fr%C3%A9d%C3%A9ric_Worms"  title=" Wikipedia"&gt;Frédéric WORMS&lt;/a&gt; est un philosophe français  spécialiste de Bergson et des questions du vivant, du soin et de la démocratie. Ancien élève de l’ENS, agrégé de philosophie, il soutient en 1995 une thèse sur "le problème de l’esprit" chez Bergson, puis une habilitation publiée sous le titre "Bergson ou les deux sens de la vie". &lt;/p&gt; &lt;p&gt; Grand spécialiste d’Henri Bergson, il a dirigé l’édition critique ses œuvres complètes aux PUF et les Annales bergsoniennes. Sa lecture de Bergson insiste sur "les deux sens de la vie" : la vie comme simple conservation/instinct et la vie comme ouverture créatrice, tension qu’il prolonge dans sa propre philosophie du vivant. &lt;/p&gt; &lt;p&gt;  Son travail s’organise autour de deux axes : l’histoire de la philosophie et une réflexion propre sur les relations vitales et morales entre les êtres humains.  Il forge l’idée de  &lt;a href="https://www.youtube.com/watch?v=-gqpI3sJ3xQ"  title="Frédéric Worms, MOMENT par abc penser"&gt;"moment" &lt;/a&gt;  philosophique pour penser l’histoire de la philosophie française : chaque moment serait une rupture et un déplacement par rapport au précédent. &lt;/p&gt; &lt;p&gt; Dans ses &lt;a href="https://www.youtube.com/watch?v=dTWnuz7mZV4"  title="Frédéric Worms - Penser à quelqu'un par librairie mollat"&gt;livres récents &lt;/a&gt; (par ex. Pour un humanisme vital), il développe une philosophie du vivant qui articule la vulnérabilité, le refus de la mort sous toutes ses formes, et la nécessité de refonder l’éthique et la politique sur le soin. Le soin n’est pas seulement médical : il désigne pour lui l’ensemble des relations vitales, morales et politiques par lesquelles les humains se soutiennent ou se détruisent. &lt;/p&gt; &lt;p&gt; Membre du CCNE, il intervient sur la fin de vie, les biotechnologies, les neurosciences, la santé, en cherchant un équilibre entre protection des plus vulnérables et exigences démocratiques.  Il parle parfois de "maladies de la démocratie" : formes de fragilisation (inégalités, indifférence, désinformation) auxquelles il oppose l’idée d’une "démocratie vitale", nourrie par le soin et la reconnaissance des personnes. &lt;/p&gt; 
- &lt;audio controls title="Comment reconnaît-on l’intelligence ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22788-26.01.2026-ITEMA_24386219-2026C45539E0001-NET_MFC_7E5F54FC-88F9-4EAB-A263-ED6928FD46E4-21-b7522d721c0e520ad7f9edd0fee90576.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F49" s="34" t="inlineStr">
-        <is>
-          <t>w8wD5uNhq8Y</t>
-        </is>
-      </c>
-      <c r="G49" s="36" t="inlineStr">
-        <is>
-          <t>"Frédéric Worms : "Je suis un peu fatigué des intellectuels qui transgressent la bien-pensance" par France Culture</t>
-        </is>
-      </c>
-      <c r="H49" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/worms-mini.webp</t>
-        </is>
-      </c>
-      <c r="I49" s="36" t="n"/>
-      <c r="J49" s="27" t="inlineStr">
-        <is>
-          <t>ethique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K49" s="27" t="inlineStr">
-        <is>
-          <t>Phénoménologie</t>
-        </is>
-      </c>
-      <c r="L49" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français historien de la philosophie &amp;amp; spécialiste de l'œuvre d'Henri Bergson.</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="116.25" customHeight="1" s="28">
-      <c r="A50" s="34" t="n">
-        <v>1964</v>
-      </c>
-      <c r="B50" s="34" t="n"/>
-      <c r="C50" s="34" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="D50" s="35" t="inlineStr">
-        <is>
-          <t>Fabienne BRUGÈRE</t>
-        </is>
-      </c>
-      <c r="E50" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fabienne_Brug%C3%A8re" title=" Wikipedia"&gt;Fabienne BRUGÈRE&lt;/a&gt; est une philosophe française   spécialisée en esthétique, philosophie morale et politique, ainsi qu'en théorie féministe. Elle intègre l'École normale supérieure de Fontenay-Saint-Cloud en 1987 et obtient l'agrégation de philosophie en 1991, après un séjour à l'université de Londres. Sa thèse de 1996 porte sur la théorie de l'art chez Shaftesbury et elle a rejoint Paris-VIII en 2014 pour une chaire en philosophie des arts modernes et contemporains. &lt;/p&gt; &lt;p&gt; Elle a été vice-présidente aux relations internationales à Bordeaux-Montaigne et présidente de l'Université Paris Lumières de 2019 à 2023. Elle a aussi présidé le Conseil de développement durable de Bordeaux Métropole et dirige des collections comme "Perspectives du care" aux éditions de l'ENS Lyon. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'esthétique anglo-américaine, &lt;a href="https://www.youtube.com/watch?v=PmXPfJIOCUw"  title="Fabienne Brugère - L'Éthique du Care par librairie mollat"&gt;l'éthique du care  &lt;/a&gt; (notamment son ouvrage "L’éthique du care" paru en 2011), le féminisme et la sociabilité politique. Parmi ses récents essais : Désaimer. Manuel d’un retour à la vie (2024), La vraie histoire de l’impressionnisme (2024) et On ne naît pas femme, on le devient (2019). Elle montre que le &lt;em&gt;care&lt;/em&gt;, le soin apporté aux autres, n’est pas une affaire privée réservée aux femmes, mais une question politique qui concerne toute la société et la manière dont elle traite les plus vulnérables. Avec Guillaume le Blanc, elle a aussi écrit sur l’hospitalité et l’accueil des étrangers dans &lt;em&gt;La Fin de l’hospitalité&lt;/em&gt; (2017). &lt;/p&gt; 
   &lt;audio controls title="Le désamour avec Fabienne Brugère par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-03.05.2024-ITEMA_23729943-2024F45096S0124-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
+      <c r="F49" s="34" t="inlineStr">
+        <is>
+          <t>JkVPQiVidJM</t>
+        </is>
+      </c>
+      <c r="G49" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Fabienne Brugère - Désaimer : manuel d'un retour à la vie" par Librairie Mollat</t>
+        </is>
+      </c>
+      <c r="H49" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/brugere-mini.webp</t>
+        </is>
+      </c>
+      <c r="I49" s="36" t="n"/>
+      <c r="J49" s="27" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K49" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Éthique de la sollicitude</t>
+        </is>
+      </c>
+      <c r="L49" s="27" t="inlineStr">
+        <is>
+          <t>philosophe française spécialisée en esthétique, philosophie morale et politique et théorie féministe.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; justice ; art</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="126.75" customHeight="1" s="28">
+      <c r="A50" s="34" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B50" s="34" t="n"/>
+      <c r="C50" s="34" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="D50" s="35" t="inlineStr">
+        <is>
+          <t>Thierry MÉNISSIER</t>
+        </is>
+      </c>
+      <c r="E50" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thierry_M%C3%A9nissier" title=" Wikipedia"&gt;Thierry MÉNISSIER&lt;/a&gt;  est un philosophe français surtout connu pour ses travaux en philosophie politique et en histoire des idées. Il enseigne à l’université Grenoble Alpes et ses recherches s’appuient beaucoup sur Machiavel et la pensée de la Renaissance. &lt;/p&gt; &lt;p&gt;Sa philosophie s’intéresse d’abord à  &lt;a href="https://www.youtube.com/watch?v=KM8r0dQVwvE" title="Technologie et socéité soutenable par Agence Urbanisme t"&gt;l’éthique publique &lt;/a&gt;  et à la vie démocratique. Il cherche à comprendre comment les sociétés peuvent se gouverner sans réduire la politique à des principes abstraits, mais en partant des situations concrètes et des rapports de pouvoir. &lt;/p&gt; &lt;p&gt;  Un autre axe important de sa pensée concerne l’innovation et les technologies contemporaines. Il ne voit pas l’innovation comme un simple progrès automatique, mais comme un phénomène ambivalent qui oblige à réfléchir à ses effets sur la liberté, la responsabilité, la démocratie et le sens du bien commun. &lt;/p&gt; &lt;p&gt; Il est le &lt;a href="https://www.tumultieordini.com/" title="Tumulti e ordini
+Le blog de Thierry Ménissier"&gt;philosophe de l’action&lt;/a&gt;, de la décision et des transformations du monde contemporain. Sa pensée cherche à construire une éthique capable d’accompagner les mutations politiques,  technologiques et sociales  sans perdre de vue la justice. Spécialiste reconnu de Machiavel, auquel il a consacré plusieurs livres, il retient de lui l’idée que la politique se joue dans les circonstances, les conflits et l’occasion, et non dans l’application de règles éternelles. À Grenoble, il a animé des recherches sur l’éthique de l’innovation et sur l’intelligence artificielle, en associant philosophes, ingénieurs et citoyens à la réflexion sur les technologies. &lt;/p&gt;  &lt;audio controls title="Intelligence artificielle : par delà le bien et le mal par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14312-30.03.2022-ITEMA_22979351-2022C26360S0089-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>JkVPQiVidJM</t>
+          <t>2m_2MDcB7h8</t>
         </is>
       </c>
       <c r="G50" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Fabienne Brugère - Désaimer : manuel d'un retour à la vie" par Librairie Mollat</t>
+          <t>"Une philosophie politique de la corruption" par MSH Alpes</t>
         </is>
       </c>
       <c r="H50" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/brugere-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/tmenissier-mini.webp</t>
         </is>
       </c>
       <c r="I50" s="36" t="n"/>
       <c r="J50" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>politique</t>
         </is>
       </c>
       <c r="K50" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libéralisme ; Éthique de la sollicitude</t>
+          <t>Libéralisme</t>
         </is>
       </c>
       <c r="L50" s="27" t="inlineStr">
         <is>
-          <t>philosophe française spécialisée en esthétique, philosophie morale et politique et théorie féministe.</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français connu pour ses travaux en philosophie politique et en histoire des idées.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3776,60 +3775,64 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre ; justice ; art</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="126.75" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="147.75" customHeight="1" s="28">
       <c r="A51" s="34" t="n">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="B51" s="34" t="n"/>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="D51" s="35" t="inlineStr">
         <is>
-          <t>Thierry MÉNISSIER</t>
-        </is>
-      </c>
-      <c r="E51" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thierry_M%C3%A9nissier" title=" Wikipedia"&gt;Thierry MÉNISSIER&lt;/a&gt;  est un philosophe français surtout connu pour ses travaux en philosophie politique et en histoire des idées. Il enseigne à l’université Grenoble Alpes et ses recherches s’appuient beaucoup sur Machiavel et la pensée de la Renaissance. &lt;/p&gt; &lt;p&gt;Sa philosophie s’intéresse d’abord à  &lt;a href="https://www.youtube.com/watch?v=KM8r0dQVwvE" title="Technologie et socéité soutenable par Agence Urbanisme t"&gt;l’éthique publique &lt;/a&gt;  et à la vie démocratique. Il cherche à comprendre comment les sociétés peuvent se gouverner sans réduire la politique à des principes abstraits, mais en partant des situations concrètes et des rapports de pouvoir. &lt;/p&gt; &lt;p&gt;  Un autre axe important de sa pensée concerne l’innovation et les technologies contemporaines. Il ne voit pas l’innovation comme un simple progrès automatique, mais comme un phénomène ambivalent qui oblige à réfléchir à ses effets sur la liberté, la responsabilité, la démocratie et le sens du bien commun. &lt;/p&gt; &lt;p&gt; Il est le &lt;a href="https://www.tumultieordini.com/" title="Tumulti e ordini
-Le blog de Thierry Ménissier"&gt;philosophe de l’action&lt;/a&gt;, de la décision et des transformations du monde contemporain. Sa pensée cherche à construire une éthique capable d’accompagner les mutations politiques,  technologiques et sociales  sans perdre de vue la justice. Spécialiste reconnu de Machiavel, auquel il a consacré plusieurs livres, il retient de lui l’idée que la politique se joue dans les circonstances, les conflits et l’occasion, et non dans l’application de règles éternelles. À Grenoble, il a animé des recherches sur l’éthique de l’innovation et sur l’intelligence artificielle, en associant philosophes, ingénieurs et citoyens à la réflexion sur les technologies. &lt;/p&gt;  &lt;audio controls title="Intelligence artificielle : par delà le bien et le mal par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14312-30.03.2022-ITEMA_22979351-2022C26360S0089-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Judith REVEL</t>
+        </is>
+      </c>
+      <c r="E51" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Judith_Revel"  title=" Wikipedia"&gt;Judith REVEL&lt;/a&gt; (née en 1966) est une philosophe française, spécialiste de Michel Foucault et de la pensée française et italienne contemporaine. Professeure à l’université Paris-Nanterre, après avoir enseigné à Paris 1 Panthéon-Sorbonne, elle a été membre de l’Institut universitaire de France. Elle a aussi traduit en français plusieurs philosophes italiens, en particulier Toni Negri.&lt;/p&gt; &lt;p&gt;Elle est l’une des meilleures connaisseuses de l’œuvre de Foucault, à laquelle elle a consacré plusieurs livres, dont &lt;em&gt;Le Vocabulaire de Foucault&lt;/em&gt; et un &lt;em&gt;Dictionnaire Foucault&lt;/em&gt;, ainsi qu’une étude sur la manière dont Foucault pense le discontinu, la rupture plutôt que la continuité de l’histoire. Elle montre comment, chez lui, l’analyse des pouvoirs qui façonnent les individus, la discipline puis la biopolitique, débouche sur une réflexion sur la « subjectivation » : la manière dont les sujets peuvent se constituer eux-mêmes, résister et inventer d’autres façons de vivre. Elle a aussi confronté Foucault à Merleau-Ponty. Avec d’autres penseurs, elle a développé la notion de « commun », qui désigne ce qui n’appartient ni à l’État ni aux propriétaires privés, mais est produit et géré ensemble par une communauté, et qui offre une alternative au couple du public et du privé. Plus largement, elle s’interroge sur une &lt;a href="https://www.youtube.com/watch?v=Y6J6TIET13w&amp;t=15s"  title=" Judith Revel // Suis-je responsable de l'humanité ? par Philomonaco"&gt;philosophie du présent&lt;/a&gt; : comment penser l’actualité, les luttes sociales et les transformations du travail.&lt;/p&gt; &lt;p&gt;Son travail relie ainsi l’histoire de la philosophie, la politique et les débats contemporains sur la démocratie, l’hégémonie culturelle et les mouvements sociaux.&lt;/p&gt;  &lt;audio controls title="L'hégémonie culturelle : Gramsci pillé de tous côtés par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-21.04.2025-ITEMA_24109706-2025C48904S0111-NET_MFC_47597AB9-4778-4D51-A8A2-7A3D26AD6489-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>2m_2MDcB7h8</t>
+          <t>me9YXsmumHs</t>
         </is>
       </c>
       <c r="G51" s="36" t="inlineStr">
         <is>
-          <t>"Une philosophie politique de la corruption" par MSH Alpes</t>
+          <t>"JUDITH REVEL - Quotidiens fragiles et labiles : le mortel des communs" par Rencontres Orient Occident</t>
         </is>
       </c>
       <c r="H51" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/tmenissier-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/revel-mini.webp</t>
         </is>
       </c>
       <c r="I51" s="36" t="n"/>
       <c r="J51" s="27" t="inlineStr">
         <is>
-          <t>politique</t>
+          <t>politique ; epistemologie</t>
         </is>
       </c>
       <c r="K51" s="27" t="inlineStr">
         <is>
-          <t>Libéralisme</t>
+          <t>Post-structuralisme</t>
         </is>
       </c>
       <c r="L51" s="27" t="inlineStr">
         <is>
-          <t>philosophe français connu pour ses travaux en philosophie politique et en histoire des idées.</t>
+          <t>philosophe française spécialiste des pensées française &amp;amp; italienne contemporaines.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3839,11 +3842,11 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="147.75" customHeight="1" s="28">
+          <t xml:space="preserve">continental ; critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="161.25" customHeight="1" s="28">
       <c r="A52" s="34" t="n">
         <v>1966</v>
       </c>
@@ -3855,77 +3858,10 @@
       </c>
       <c r="D52" s="35" t="inlineStr">
         <is>
-          <t>Judith REVEL</t>
+          <t>Guillaume LE-BLANC</t>
         </is>
       </c>
       <c r="E52" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Judith_Revel"  title=" Wikipedia"&gt;Judith REVEL&lt;/a&gt; (née en 1966) est une philosophe française, spécialiste de Michel Foucault et de la pensée française et italienne contemporaine. Professeure à l’université Paris-Nanterre, après avoir enseigné à Paris 1 Panthéon-Sorbonne, elle a été membre de l’Institut universitaire de France. Elle a aussi traduit en français plusieurs philosophes italiens, en particulier Toni Negri.&lt;/p&gt; &lt;p&gt;Elle est l’une des meilleures connaisseuses de l’œuvre de Foucault, à laquelle elle a consacré plusieurs livres, dont &lt;em&gt;Le Vocabulaire de Foucault&lt;/em&gt; et un &lt;em&gt;Dictionnaire Foucault&lt;/em&gt;, ainsi qu’une étude sur la manière dont Foucault pense le discontinu, la rupture plutôt que la continuité de l’histoire. Elle montre comment, chez lui, l’analyse des pouvoirs qui façonnent les individus, la discipline puis la biopolitique, débouche sur une réflexion sur la « subjectivation » : la manière dont les sujets peuvent se constituer eux-mêmes, résister et inventer d’autres façons de vivre. Elle a aussi confronté Foucault à Merleau-Ponty. Avec d’autres penseurs, elle a développé la notion de « commun », qui désigne ce qui n’appartient ni à l’État ni aux propriétaires privés, mais est produit et géré ensemble par une communauté, et qui offre une alternative au couple du public et du privé. Plus largement, elle s’interroge sur une &lt;a href="https://www.youtube.com/watch?v=Y6J6TIET13w&amp;t=15s"  title=" Judith Revel // Suis-je responsable de l'humanité ? par Philomonaco"&gt;philosophie du présent&lt;/a&gt; : comment penser l’actualité, les luttes sociales et les transformations du travail.&lt;/p&gt; &lt;p&gt;Son travail relie ainsi l’histoire de la philosophie, la politique et les débats contemporains sur la démocratie, l’hégémonie culturelle et les mouvements sociaux.&lt;/p&gt;  &lt;audio controls title="L'hégémonie culturelle : Gramsci pillé de tous côtés par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-21.04.2025-ITEMA_24109706-2025C48904S0111-NET_MFC_47597AB9-4778-4D51-A8A2-7A3D26AD6489-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F52" s="34" t="inlineStr">
-        <is>
-          <t>me9YXsmumHs</t>
-        </is>
-      </c>
-      <c r="G52" s="36" t="inlineStr">
-        <is>
-          <t>"JUDITH REVEL - Quotidiens fragiles et labiles : le mortel des communs" par Rencontres Orient Occident</t>
-        </is>
-      </c>
-      <c r="H52" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/revel-mini.webp</t>
-        </is>
-      </c>
-      <c r="I52" s="36" t="n"/>
-      <c r="J52" s="27" t="inlineStr">
-        <is>
-          <t>politique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K52" s="27" t="inlineStr">
-        <is>
-          <t>Post-structuralisme</t>
-        </is>
-      </c>
-      <c r="L52" s="27" t="inlineStr">
-        <is>
-          <t>philosophe française spécialiste des pensées française &amp;amp; italienne contemporaines.</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">continental ; critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="161.25" customHeight="1" s="28">
-      <c r="A53" s="34" t="n">
-        <v>1966</v>
-      </c>
-      <c r="B53" s="34" t="n"/>
-      <c r="C53" s="34" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="D53" s="35" t="inlineStr">
-        <is>
-          <t>Guillaume LE-BLANC</t>
-        </is>
-      </c>
-      <c r="E53" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_Le_Blanc_(%C3%A9crivain_fran%C3%A7ais)"  title=" Wikipedia"&gt;Guillaume LE BLANC&lt;/a&gt;  est un philosophe français spécialiste de philosophie sociale et politique, connu pour ses travaux sur la précarité, l’invisibilité sociale et les vies ordinaires. Il est professeur de philosophie sociale et politique à l’université Paris Cité et membre senior de l’Institut universitaire de France depuis 2022. &lt;/p&gt; &lt;p&gt; Il propose une philosophie des vies ordinaires qui prend au sérieux les expériences de précarité et de marginalisation. La précarité n’est pas une condition naturelle, mais une situation socialement produite qui  &lt;a href="https://www.lavie.fr/idees/debats/guillaume-le-blanc-nous-avons-bascule-dans-lage-de-la-tristesse-detre-soi-98208.php" style=" title=" Guillaume Le Blanc :  Nous avons basculé dans l’âge de la tristesse d’être soi  par lavie.fr"&gt;empêche les individus &lt;/a&gt; de se constituer comme autonomes dans leur rapport aux normes. Il montre comment les chômeurs, les "surnuméraires" et les "sans-voix" inventent de nouveaux langages et formes de vie, que la philosophie doit traduire pour contribuer à une &lt;a href="https://www.youtube.com/watch?v=2wtaG_uD8pQ" title=" L'hospitalité comme leçon de fraternité ? par Guillaume Le Blanc  par Espace Ethique"&gt;"société décente" &lt;/a&gt; et à une critique sociale des normes. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : "Canguilhem et les normes" paru en 1999, Canguilhem et la vie humaine / La vie humaine. Anthropologie et biologie en 2002. " Les maladies de l’homme normal" paru en 2004, "Vies ordinaires, vies précaires" en 2007, "L’invisibilité sociale" en 2009, "Que faire de notre vulnérabilité ?" en 2011 et  "L’insurrection des vies minuscules" en  2013. &lt;/p&gt; &lt;p&gt; Il hérite de Canguilhem et Foucault pour analyser la normalité, la santé, le pouvoir et les dispositifs d’invisibilisation, tout en les prolongeant vers une philosophie sociale de la vulnérabilité.
 Il défend une idée de la philosophie comme contre-culture, capable d’amplifier les voix marginalisées, d’explorer la créativité des vies ordinaires et de questionner les évidences de la normalité sociales. &lt;/p&gt; 
@@ -3933,35 +3869,97 @@
 </t>
         </is>
       </c>
+      <c r="F52" s="34" t="inlineStr">
+        <is>
+          <t>rT2XTNwqbRs</t>
+        </is>
+      </c>
+      <c r="G52" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Guillaume le Blanc - Que faire de notre vulnérabilité ?" par Librairie Mollat</t>
+        </is>
+      </c>
+      <c r="H52" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/blanc-mini.webp</t>
+        </is>
+      </c>
+      <c r="I52" s="36" t="n"/>
+      <c r="J52" s="27" t="inlineStr">
+        <is>
+          <t>politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K52" s="27" t="inlineStr">
+        <is>
+          <t>Post-structuralisme</t>
+        </is>
+      </c>
+      <c r="L52" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français qui s'interroge sur les normes dans leur dimension vitale et sociale.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="219.75" customHeight="1" s="28">
+      <c r="A53" s="34" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B53" s="34" t="n"/>
+      <c r="C53" s="34" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="D53" s="35" t="inlineStr">
+        <is>
+          <t>Quentin MEILLASSOUX</t>
+        </is>
+      </c>
+      <c r="E53" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Quentin_Meillassoux"  title=" Wikipedia"&gt;Quentin MEILLASSOUX&lt;/a&gt; est un philosophe français du courant qu'on appelle le  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif" style="color:#88A1E9" title=" Speculative Realism par Wikipedia "&gt;"réalisme spéculatif"&lt;/a&gt;. Le point de départ majeur de sa philosophie est "Le corrélationnisme" qui, selon lui, est la thèse dominante depuis Kant, et qui affirme qu'il est impossible de connaître le monde tel qu'il est en soi, indépendamment de notre rapport à lui (la corrélation entre la pensée et l'être). Cette position rend impossible de penser un "absolu" et nous enferme dans un cercle où nous ne pouvons accéder qu'à ce qui est "pour nous". &lt;a href="https://www.youtube.com/watch?v=29_IhFEWtlc" title="corine-pelluchon"&gt;Il s'interroge &lt;/a&gt;  sur la capacité de la science à parler de réalités "ancestrales", ce qui semble contredire le corrélationnisme. &lt;/p&gt; &lt;p&gt; Face au corrélationnisme, il propose de postuler que la seule chose nécessaire est la &lt;a href="https://www.youtube.com/watch?v=5ECkL9MKDiI" title=" Quentin Meillassoux's "After Finitude" par Five Minute Philosophy "&gt; contingence absolue&lt;/a&gt;. Cela signifie que toutes les lois de la nature, toutes les entités existantes, sont radicalement contingentes et pourraient être différentes, ou même ne pas exister du tout. Il n'y a aucune raison ou fondement nécessaire à l'existence du monde tel qu'il est. Cette absence de raison ultime n'est pas un aveu d'ignorance, mais une vérité ontologique. C'est ce qu'il appelle le "principe de factualité". En affirmant cette contingence radicale, il s'inscrit dans une tradition matérialiste, mais une tradition qui se veut "spéculative" parce qu'elle cherche à penser l'absolu (l'absolu de la contingence) au-delà des limites imposées par le corrélationnisme. Il s'agit de s'affranchir de la dépendance de l'être vis-à-vis de la pensée. Sa pensée est notamment développée dans son ouvrage le plus célèbre,  &lt;a  href="https://fr.wikipedia.org/wiki/Apr%C3%A8s_la_finitude._Essai_sur_la_n%C3%A9cessit%C3%A9_de_la_contingence#:~:text=Quentin%20Meillassoux%20nomme%20cette%20philosophie,la%20pens%C3%A9e%20de%20l'absolu." title=" "Après la finitude. Essai sur la nécessité de la contingence" par Wikipedia "&gt;"Après la finitude. Essai sur la nécessité de la contingence"&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;  Dans sa thèse de doctorat "L'inexistence divine", il explore la possibilité d'un "dieu à venir". Pour lui, si Dieu n'existe pas actuellement, sa non-existence n'est pas une nécessité, mais une contingence. Ainsi, il n'est pas impossible qu'un jour un "Dieu" puisse émerger d'une manière ou d'une autre, à la suite d'un changement radical des lois physiques. &lt;/p&gt; &lt;p&gt; Dans son second livre "Le Nombre et la Sirène", il propose une lecture inédite du célèbre poème de Stéphane Mallarmé, "Un coup de dés jamais n'abolira le hasard". Il y développe une analyse détaillée, y découvrant  &lt;a href="https://www.youtube.com/watch?v=yKwqoW9PxVA" title=" Le code secret de Mallarmé enfin dévoilé?  par De Revolutionibus "&gt;un code numérique&lt;/a&gt;  qui, selon lui, serait intégré au texte par Mallarmé lui-même, en lien avec ses réflexions sur le hasard et la contingence.&lt;/p&gt; &lt;p&gt; En critiquant radicalement le corrélationnisme, il cherche à ouvrir la voie à une nouvelle forme de réalisme et de matérialisme, où la contingence est pensée non pas comme une limite de notre connaissance, mais comme une propriété fondamentale de l'être lui-même. &lt;/p&gt;   &lt;audio controls title="Quentin Meillassoux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-16.12.2011-ITEMA_20320127-2011C3403E0204-ITE_00047293_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>rT2XTNwqbRs</t>
+          <t>Ic8h23MNVWU</t>
         </is>
       </c>
       <c r="G53" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Guillaume le Blanc - Que faire de notre vulnérabilité ?" par Librairie Mollat</t>
+          <t>"Quentin Meillassoux : Principes du signe creux" par Ecole Normale superieure</t>
         </is>
       </c>
       <c r="H53" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/blanc-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/meillassoux-mini.webp</t>
         </is>
       </c>
       <c r="I53" s="36" t="n"/>
       <c r="J53" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K53" s="27" t="inlineStr">
         <is>
-          <t>Post-structuralisme</t>
+          <t>Nouveau réalisme</t>
         </is>
       </c>
       <c r="L53" s="27" t="inlineStr">
         <is>
-          <t>philosophe français qui s'interroge sur les normes dans leur dimension vitale et sociale.</t>
+          <t>philosophe français qui a contribué à la formation du réalisme spéculatif.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3971,11 +3969,11 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="219.75" customHeight="1" s="28">
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="198" customHeight="1" s="28">
       <c r="A54" s="34" t="n">
         <v>1967</v>
       </c>
@@ -3987,43 +3985,48 @@
       </c>
       <c r="D54" s="35" t="inlineStr">
         <is>
-          <t>Quentin MEILLASSOUX</t>
-        </is>
-      </c>
-      <c r="E54" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Quentin_Meillassoux"  title=" Wikipedia"&gt;Quentin MEILLASSOUX&lt;/a&gt; est un philosophe français du courant qu'on appelle le  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif" style="color:#88A1E9" title=" Speculative Realism par Wikipedia "&gt;"réalisme spéculatif"&lt;/a&gt;. Le point de départ majeur de sa philosophie est "Le corrélationnisme" qui, selon lui, est la thèse dominante depuis Kant, et qui affirme qu'il est impossible de connaître le monde tel qu'il est en soi, indépendamment de notre rapport à lui (la corrélation entre la pensée et l'être). Cette position rend impossible de penser un "absolu" et nous enferme dans un cercle où nous ne pouvons accéder qu'à ce qui est "pour nous". &lt;a href="https://www.youtube.com/watch?v=29_IhFEWtlc" title="corine-pelluchon"&gt;Il s'interroge &lt;/a&gt;  sur la capacité de la science à parler de réalités "ancestrales", ce qui semble contredire le corrélationnisme. &lt;/p&gt; &lt;p&gt; Face au corrélationnisme, il propose de postuler que la seule chose nécessaire est la &lt;a href="https://www.youtube.com/watch?v=5ECkL9MKDiI" title=" Quentin Meillassoux's "After Finitude" par Five Minute Philosophy "&gt; contingence absolue&lt;/a&gt;. Cela signifie que toutes les lois de la nature, toutes les entités existantes, sont radicalement contingentes et pourraient être différentes, ou même ne pas exister du tout. Il n'y a aucune raison ou fondement nécessaire à l'existence du monde tel qu'il est. Cette absence de raison ultime n'est pas un aveu d'ignorance, mais une vérité ontologique. C'est ce qu'il appelle le "principe de factualité". En affirmant cette contingence radicale, il s'inscrit dans une tradition matérialiste, mais une tradition qui se veut "spéculative" parce qu'elle cherche à penser l'absolu (l'absolu de la contingence) au-delà des limites imposées par le corrélationnisme. Il s'agit de s'affranchir de la dépendance de l'être vis-à-vis de la pensée. Sa pensée est notamment développée dans son ouvrage le plus célèbre,  &lt;a  href="https://fr.wikipedia.org/wiki/Apr%C3%A8s_la_finitude._Essai_sur_la_n%C3%A9cessit%C3%A9_de_la_contingence#:~:text=Quentin%20Meillassoux%20nomme%20cette%20philosophie,la%20pens%C3%A9e%20de%20l'absolu." title=" "Après la finitude. Essai sur la nécessité de la contingence" par Wikipedia "&gt;"Après la finitude. Essai sur la nécessité de la contingence"&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;  Dans sa thèse de doctorat "L'inexistence divine", il explore la possibilité d'un "dieu à venir". Pour lui, si Dieu n'existe pas actuellement, sa non-existence n'est pas une nécessité, mais une contingence. Ainsi, il n'est pas impossible qu'un jour un "Dieu" puisse émerger d'une manière ou d'une autre, à la suite d'un changement radical des lois physiques. &lt;/p&gt; &lt;p&gt; Dans son second livre "Le Nombre et la Sirène", il propose une lecture inédite du célèbre poème de Stéphane Mallarmé, "Un coup de dés jamais n'abolira le hasard". Il y développe une analyse détaillée, y découvrant  &lt;a href="https://www.youtube.com/watch?v=yKwqoW9PxVA" title=" Le code secret de Mallarmé enfin dévoilé?  par De Revolutionibus "&gt;un code numérique&lt;/a&gt;  qui, selon lui, serait intégré au texte par Mallarmé lui-même, en lien avec ses réflexions sur le hasard et la contingence.&lt;/p&gt; &lt;p&gt; En critiquant radicalement le corrélationnisme, il cherche à ouvrir la voie à une nouvelle forme de réalisme et de matérialisme, où la contingence est pensée non pas comme une limite de notre connaissance, mais comme une propriété fondamentale de l'être lui-même. &lt;/p&gt;   &lt;audio controls title="Quentin Meillassoux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-16.12.2011-ITEMA_20320127-2011C3403E0204-ITE_00047293_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t>Corine PELLUCHON</t>
+        </is>
+      </c>
+      <c r="E54" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Corine_Pelluchon"  style="color:#6A142A"  title=" Wikipedia"&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href="https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s" title="NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco"&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &lt;p&gt;Manifeste animaliste. Politiser la cause animale ( 2017 ) Éthique de la considération ( 2018) Réparons le monde. Humains, animaux, nature (2020) Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=zpzzDqYhF-8" title="Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat"&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href="https://www.youtube.com/watch?v=tmk-UzN1j70"  title="Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media"&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title="Corine Pelluchon par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>Ic8h23MNVWU</t>
+          <t>_qZVJll1J2k</t>
         </is>
       </c>
       <c r="G54" s="36" t="inlineStr">
         <is>
-          <t>"Quentin Meillassoux : Principes du signe creux" par Ecole Normale superieure</t>
+          <t>"Corine Pelluchon : réparer le monde des vivants" par La Grande Librairie</t>
         </is>
       </c>
       <c r="H54" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/meillassoux-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/pelluchon-mini.webp</t>
         </is>
       </c>
       <c r="I54" s="36" t="n"/>
       <c r="J54" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; epistemologie</t>
+          <t>ethique ; politique</t>
         </is>
       </c>
       <c r="K54" s="27" t="inlineStr">
         <is>
-          <t>Nouveau réalisme</t>
+          <t xml:space="preserve">Phénoménologie ; Éthique de la sollicitude</t>
         </is>
       </c>
       <c r="L54" s="27" t="inlineStr">
         <is>
-          <t>philosophe français qui a contribué à la formation du réalisme spéculatif.</t>
+          <t>philosophe française qui s'intéresse aux questions d'éthique et de philosophie morale et politique.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4033,11 +4036,11 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="198" customHeight="1" s="28">
+          <t xml:space="preserve">ecologie ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="162" customHeight="1" s="28">
       <c r="A55" s="34" t="n">
         <v>1967</v>
       </c>
@@ -4049,48 +4052,43 @@
       </c>
       <c r="D55" s="35" t="inlineStr">
         <is>
-          <t>Corine PELLUCHON</t>
-        </is>
-      </c>
-      <c r="E55" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Corine_Pelluchon"  style="color:#6A142A"  title=" Wikipedia"&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href="https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s" title="NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco"&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &lt;p&gt;Manifeste animaliste. Politiser la cause animale ( 2017 ) Éthique de la considération ( 2018) Réparons le monde. Humains, animaux, nature (2020) Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=zpzzDqYhF-8" title="Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat"&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href="https://www.youtube.com/watch?v=tmk-UzN1j70"  title="Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media"&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title="Corine Pelluchon par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t>Denis MOREAU</t>
+        </is>
+      </c>
+      <c r="E55" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Denis_Moreau"  title=" Wikipedia"&gt;Denis MOREAU&lt;/a&gt; est un philosophe français spécialiste de la philosophie moderne et de la philosophie de la religion. . Docteur en philosophie (1996) et habilité à diriger des recherches (2008), il a été membre junior de l'Institut universitaire de France dès 2004. &lt;/p&gt; &lt;p&gt; Ses travaux portent principalement sur le XVIIe siècle, avec un focus sur Descartes, le cartésianisme, Malebranche et Spinoza. En philosophie de la religion, il explore le christianisme sous un angle rationaliste, s'inscrivant dans une tradition qu'il nomme "rationalisme chrétien" incluant Augustin, Thomas d'Aquin, Descartes ou encore Benoît XVI. Il aborde des thèmes comme le salut, le mariage, la résurrection et la foi, en articulant justification rationnelle et impact existentiel. &lt;/p&gt; &lt;p&gt; Il a publié plusieurs ouvrages marquants qui allient philosophie moderne, histoire de la philosophie et réflexion sur le christianisme rationalisé. Ses travaux les plus importants se divisent entre essais académiques sur le XVIIe siècle et livres grand public sur la foi. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=sglQGZawGWA&amp;list=PL2d4vA4vfs79mlFW_Mo0iP8anxf1F0XXG" title=" DESCARTES - Une expérience philosophique de la vérité, Denis Moreau par Editions M-Editer"&gt;Deux cartésiens&lt;/a&gt;. La polémique entre Descartes et Gassendi (2000), qui analyse les débats entre ces deux penseurs sur la connaissance et la méthode. &lt;/p&gt; &lt;p&gt;Mort où est ta victoire ? (2017), une réflexion sur la mort et la résurrection vue sous l'angle philosophique&lt;/p&gt; &lt;p&gt;Les voies du salut (2015), qui explore les conceptions chrétiennes du salut de manière accessible et rationnelle. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=AMv4Quma6t0"title=" Denis Moreau - Résurrections : traverser les nuits de nos vies par Librairie La Procure"&gt;Résurrections. Traverser les nuits de nos vies&lt;/a&gt; (2022), qui applique des thèmes chrétiens à l'existence contemporaine.&lt;/p&gt; &lt;p&gt;Comment peut-on être catholique ? (2019), un plaidoyer rationnel pour la foi catholique dans un monde sécularisé. &lt;/p&gt;  &lt;audio controls title=" Cogito ergo sum : Descartes l'a-t-il réellement écrit ainsi ? Entretien avec Denis Moreau par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-08.09.2023-ITEMA_23480427-2023F45096S0251-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>_qZVJll1J2k</t>
+          <t>pMOSVwX5U6Y</t>
         </is>
       </c>
       <c r="G55" s="36" t="inlineStr">
         <is>
-          <t>"Corine Pelluchon : réparer le monde des vivants" par La Grande Librairie</t>
+          <t>"Être CHRÉTIEN est LA MEILLEURE FAÇON de RÉUSSIR SA VIE !" : Denis Moreau, professeur de philosophie par Meditatio</t>
         </is>
       </c>
       <c r="H55" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/pelluchon-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/moreau-mini.webp</t>
         </is>
       </c>
       <c r="I55" s="36" t="n"/>
       <c r="J55" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K55" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phénoménologie ; Éthique de la sollicitude</t>
+          <t>Spiritualisme</t>
         </is>
       </c>
       <c r="L55" s="27" t="inlineStr">
         <is>
-          <t>philosophe française qui s'intéresse aux questions d'éthique et de philosophie morale et politique.</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français spécialiste du cartésianisme et de la philosophie des religions.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4100,11 +4098,11 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie ; justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="162" customHeight="1" s="28">
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="126.75" customHeight="1" s="28">
       <c r="A56" s="34" t="n">
         <v>1967</v>
       </c>
@@ -4116,43 +4114,43 @@
       </c>
       <c r="D56" s="35" t="inlineStr">
         <is>
-          <t>Denis MOREAU</t>
+          <t xml:space="preserve">Stéphane HABER</t>
         </is>
       </c>
       <c r="E56" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Denis_Moreau"  title=" Wikipedia"&gt;Denis MOREAU&lt;/a&gt; est un philosophe français spécialiste de la philosophie moderne et de la philosophie de la religion. . Docteur en philosophie (1996) et habilité à diriger des recherches (2008), il a été membre junior de l'Institut universitaire de France dès 2004. &lt;/p&gt; &lt;p&gt; Ses travaux portent principalement sur le XVIIe siècle, avec un focus sur Descartes, le cartésianisme, Malebranche et Spinoza. En philosophie de la religion, il explore le christianisme sous un angle rationaliste, s'inscrivant dans une tradition qu'il nomme "rationalisme chrétien" incluant Augustin, Thomas d'Aquin, Descartes ou encore Benoît XVI. Il aborde des thèmes comme le salut, le mariage, la résurrection et la foi, en articulant justification rationnelle et impact existentiel. &lt;/p&gt; &lt;p&gt; Il a publié plusieurs ouvrages marquants qui allient philosophie moderne, histoire de la philosophie et réflexion sur le christianisme rationalisé. Ses travaux les plus importants se divisent entre essais académiques sur le XVIIe siècle et livres grand public sur la foi. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=sglQGZawGWA&amp;list=PL2d4vA4vfs79mlFW_Mo0iP8anxf1F0XXG" title=" DESCARTES - Une expérience philosophique de la vérité, Denis Moreau par Editions M-Editer"&gt;Deux cartésiens&lt;/a&gt;. La polémique entre Descartes et Gassendi (2000), qui analyse les débats entre ces deux penseurs sur la connaissance et la méthode. &lt;/p&gt; &lt;p&gt;Mort où est ta victoire ? (2017), une réflexion sur la mort et la résurrection vue sous l'angle philosophique&lt;/p&gt; &lt;p&gt;Les voies du salut (2015), qui explore les conceptions chrétiennes du salut de manière accessible et rationnelle. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=AMv4Quma6t0"title=" Denis Moreau - Résurrections : traverser les nuits de nos vies par Librairie La Procure"&gt;Résurrections. Traverser les nuits de nos vies&lt;/a&gt; (2022), qui applique des thèmes chrétiens à l'existence contemporaine.&lt;/p&gt; &lt;p&gt;Comment peut-on être catholique ? (2019), un plaidoyer rationnel pour la foi catholique dans un monde sécularisé. &lt;/p&gt;  &lt;audio controls title=" Cogito ergo sum : Descartes l'a-t-il réellement écrit ainsi ? Entretien avec Denis Moreau par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-08.09.2023-ITEMA_23480427-2023F45096S0251-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/St%C3%A9phane_Haber" title=" Wikipedia"&gt;Stéphane HABER&lt;/a&gt;  est un philosophe français spécialiste de la philosophie sociale et politique, ainsi que de l'épistémologie des sciences humaines. Son doctorat obtenu en 1996 à l'université de Besançon portait sur les formes de connaissance du présent dans les sciences sociales, sous la direction de Robert Damien. &lt;/p&gt; &lt;p&gt; Professeur à l'université Paris Nanterre, il est directeur adjoint du laboratoire Sophiapol. Ses enseignements couvrent l'histoire et l'épistémologie des sciences humaines, la philosophie contemporaine et les problèmes de théorie sociale et politique.&lt;/p&gt; &lt;p&gt;  Ses livres incluent Les Sciences humaines (1995), Habermas et la sociologie (1998), Freud et la théorie sociale (2012), Penser le néocapitalisme (2013). Il a dirigé des ouvrages comme L’Action en philosophie contemporaine (2005) et contribué à des revues sur Marx, l'aliénation et le capitalisme. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur  &lt;a href="https://www.youtube.com/watch?v=ZxECyRcOzFY&amp;t=11s"  title=". Haber : Exploitation du travail, appropriation de la nature, crise climatique. par Penser la Transformation"&gt; les interactions philosophie&lt;/a&gt;/sciences sociales, les marxismes contemporains, le néocapitalisme, l'aliénation subjective et objective, ainsi que les pathologies sociales et la théorie critique. Dans &lt;em&gt;L’Aliénation&lt;/em&gt; (2007), il redonne vie à cette notion héritée de Hegel et de Marx : on est aliéné quand on ne se reconnaît plus dans sa propre vie, ses activités ou ses institutions. Il montre que l’idée reste utile pour décrire les souffrances sociales d’aujourd’hui. Dans &lt;em&gt;Penser le néocapitalisme&lt;/em&gt;, il analyse un capitalisme qui s’étend à toutes les dimensions de l’existence, et ses travaux récents relient l’exploitation du travail et celle de la nature.</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>pMOSVwX5U6Y</t>
+          <t>vnSkomfLExM</t>
         </is>
       </c>
       <c r="G56" s="36" t="inlineStr">
         <is>
-          <t>"Être CHRÉTIEN est LA MEILLEURE FAÇON de RÉUSSIR SA VIE !" : Denis Moreau, professeur de philosophie par Meditatio</t>
+          <t>"Stephane Haber" par Université de Namur</t>
         </is>
       </c>
       <c r="H56" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/moreau-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/haber-mini.webp</t>
         </is>
       </c>
       <c r="I56" s="36" t="n"/>
       <c r="J56" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; spiritualite</t>
+          <t>politique ; epistemologie</t>
         </is>
       </c>
       <c r="K56" s="27" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
+          <t>Théorie Critique</t>
         </is>
       </c>
       <c r="L56" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste du cartésianisme et de la philosophie des religions.</t>
+          <t>philosophe français spécialiste de la philosophie sociale &amp;amp; politique.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4162,11 +4160,11 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">sens</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="126.75" customHeight="1" s="28">
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="150" customHeight="1" s="28">
       <c r="A57" s="34" t="n">
         <v>1967</v>
       </c>
@@ -4178,43 +4176,43 @@
       </c>
       <c r="D57" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stéphane HABER</t>
+          <t>Emmanuel RENAULT</t>
         </is>
       </c>
       <c r="E57" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/St%C3%A9phane_Haber" title=" Wikipedia"&gt;Stéphane HABER&lt;/a&gt;  est un philosophe français spécialiste de la philosophie sociale et politique, ainsi que de l'épistémologie des sciences humaines. Son doctorat obtenu en 1996 à l'université de Besançon portait sur les formes de connaissance du présent dans les sciences sociales, sous la direction de Robert Damien. &lt;/p&gt; &lt;p&gt; Professeur à l'université Paris Nanterre, il est directeur adjoint du laboratoire Sophiapol. Ses enseignements couvrent l'histoire et l'épistémologie des sciences humaines, la philosophie contemporaine et les problèmes de théorie sociale et politique.&lt;/p&gt; &lt;p&gt;  Ses livres incluent Les Sciences humaines (1995), Habermas et la sociologie (1998), Freud et la théorie sociale (2012), Penser le néocapitalisme (2013). Il a dirigé des ouvrages comme L’Action en philosophie contemporaine (2005) et contribué à des revues sur Marx, l'aliénation et le capitalisme. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur  &lt;a href="https://www.youtube.com/watch?v=ZxECyRcOzFY&amp;t=11s"  title=". Haber : Exploitation du travail, appropriation de la nature, crise climatique. par Penser la Transformation"&gt; les interactions philosophie&lt;/a&gt;/sciences sociales, les marxismes contemporains, le néocapitalisme, l'aliénation subjective et objective, ainsi que les pathologies sociales et la théorie critique. Dans &lt;em&gt;L’Aliénation&lt;/em&gt; (2007), il redonne vie à cette notion héritée de Hegel et de Marx : on est aliéné quand on ne se reconnaît plus dans sa propre vie, ses activités ou ses institutions. Il montre que l’idée reste utile pour décrire les souffrances sociales d’aujourd’hui. Dans &lt;em&gt;Penser le néocapitalisme&lt;/em&gt;, il analyse un capitalisme qui s’étend à toutes les dimensions de l’existence, et ses travaux récents relient l’exploitation du travail et celle de la nature.</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Renault"  title=" Wikipedia"&gt;Emmanuel RENAULT&lt;/a&gt; est un philosophe français, spécialisé en théorie critique, philosophie sociale et rapports entre reconnaissance, conflit et domination. Il est largement associé à une approche pragmatiste et pluraliste, cherchant à articuler Hegel, Marx, Honneth et le pragmatisme de Dewey dans une perspective interdisciplinaire. &lt;/p&gt; &lt;p&gt;  Il développe une approche qui croise les traditions marxistes et pragmatistes, et met l’accent sur les questions de travail, de justice, de  &lt;a href="https://www.nonfiction.fr/article-11867-abolir-lexploitation-entretien-avec-emmanuel-renault.htm" title="Abolir l'exploitation : entretien avec Emmanuel Renault. par nonfiction"&gt; souffrance sociale &lt;/a&gt; et de reconnaissance et il analyse comment les conflits sociaux, la reconnaissance et les formes de domination structurent l’injustice moderne.  Il s’inscrit dans une démarche qui remet en question les bases normatives de la justice politique en faveur d’une compréhension de l’injustice comme déni de reconnaissance et comme expérience de souffrance sociale. &lt;/p&gt; &lt;p&gt; Son travail est influent dans les débats sur la philosophie sociale en France et à l’étranger, et il participe à l’extension des cadres marxistes et pragmatistes dans la réflexion sur le travail,  &lt;a href="https://www.youtube.com/watch?v=6DriuHGugCA" title=" l'impensé de l'exploitation par Hors serie"&gt; l’exploitation &lt;/a&gt; et la justice sociale. Ses publications représentatives : "Le Mépris social" paru en  2000 : exploration des formes de mépris et des dynamiques sociales qui les sous-tendent. "Souffrances sociales" paru en 2008 : analyse des mécanismes de souffrance dans les sociétés contemporaines et leur lien avec la reconnaissance et la distribution des ressources. "Reconnaissance, conflit, domination"  en 2017 : thèse centrale sur la relation entre reconnaissance, conflit et domination, et leur rôle dans la configuration des inégalités. &lt;/p&gt;  &lt;audio controls title="Mépris social : comment sortir du dialogue de sourds?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-29.10.2015-ITEMA_20828700-2015C19327S0302-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>vnSkomfLExM</t>
+          <t>fbovR0UFucs</t>
         </is>
       </c>
       <c r="G57" s="36" t="inlineStr">
         <is>
-          <t>"Stephane Haber" par Université de Namur</t>
+          <t>"E. Renault : l'exploitation comme domination" par Penser la Transformation</t>
         </is>
       </c>
       <c r="H57" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/haber-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/renault-mini.webp</t>
         </is>
       </c>
       <c r="I57" s="36" t="n"/>
       <c r="J57" s="27" t="inlineStr">
         <is>
-          <t>politique ; epistemologie</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K57" s="27" t="inlineStr">
         <is>
-          <t>Théorie Critique</t>
+          <t>Marxisme ; Théorie Critique</t>
         </is>
       </c>
       <c r="L57" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la philosophie sociale &amp;amp; politique.</t>
+          <t>philosophe français promoteur de la philosophie sociale en France &amp;amp; de l'épistémologie hégélienne.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4229,180 +4227,186 @@
       </c>
     </row>
     <row r="58" ht="150" customHeight="1" s="28">
-      <c r="A58" s="34" t="n">
+      <c r="A58" s="44" t="n">
         <v>1967</v>
       </c>
-      <c r="B58" s="34" t="n"/>
-      <c r="C58" s="34" t="inlineStr">
+      <c r="B58" s="44" t="n"/>
+      <c r="C58" s="44" t="inlineStr">
         <is>
           <t>1967</t>
         </is>
       </c>
-      <c r="D58" s="35" t="inlineStr">
-        <is>
-          <t>Emmanuel RENAULT</t>
-        </is>
-      </c>
-      <c r="E58" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Renault"  title=" Wikipedia"&gt;Emmanuel RENAULT&lt;/a&gt; est un philosophe français, spécialisé en théorie critique, philosophie sociale et rapports entre reconnaissance, conflit et domination. Il est largement associé à une approche pragmatiste et pluraliste, cherchant à articuler Hegel, Marx, Honneth et le pragmatisme de Dewey dans une perspective interdisciplinaire. &lt;/p&gt; &lt;p&gt;  Il développe une approche qui croise les traditions marxistes et pragmatistes, et met l’accent sur les questions de travail, de justice, de  &lt;a href="https://www.nonfiction.fr/article-11867-abolir-lexploitation-entretien-avec-emmanuel-renault.htm" title="Abolir l'exploitation : entretien avec Emmanuel Renault. par nonfiction"&gt; souffrance sociale &lt;/a&gt; et de reconnaissance et il analyse comment les conflits sociaux, la reconnaissance et les formes de domination structurent l’injustice moderne.  Il s’inscrit dans une démarche qui remet en question les bases normatives de la justice politique en faveur d’une compréhension de l’injustice comme déni de reconnaissance et comme expérience de souffrance sociale. &lt;/p&gt; &lt;p&gt; Son travail est influent dans les débats sur la philosophie sociale en France et à l’étranger, et il participe à l’extension des cadres marxistes et pragmatistes dans la réflexion sur le travail,  &lt;a href="https://www.youtube.com/watch?v=6DriuHGugCA" title=" l'impensé de l'exploitation par Hors serie"&gt; l’exploitation &lt;/a&gt; et la justice sociale. Ses publications représentatives : "Le Mépris social" paru en  2000 : exploration des formes de mépris et des dynamiques sociales qui les sous-tendent. "Souffrances sociales" paru en 2008 : analyse des mécanismes de souffrance dans les sociétés contemporaines et leur lien avec la reconnaissance et la distribution des ressources. "Reconnaissance, conflit, domination"  en 2017 : thèse centrale sur la relation entre reconnaissance, conflit et domination, et leur rôle dans la configuration des inégalités. &lt;/p&gt;  &lt;audio controls title="Mépris social : comment sortir du dialogue de sourds?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-29.10.2015-ITEMA_20828700-2015C19327S0302-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F58" s="34" t="inlineStr">
-        <is>
-          <t>fbovR0UFucs</t>
-        </is>
-      </c>
-      <c r="G58" s="36" t="inlineStr">
-        <is>
-          <t>"E. Renault : l'exploitation comme domination" par Penser la Transformation</t>
-        </is>
-      </c>
-      <c r="H58" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/renault-mini.webp</t>
-        </is>
-      </c>
-      <c r="I58" s="36" t="n"/>
-      <c r="J58" s="27" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="K58" s="27" t="inlineStr">
-        <is>
-          <t>Marxisme ; Théorie Critique</t>
-        </is>
-      </c>
-      <c r="L58" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français promoteur de la philosophie sociale en France &amp;amp; de l'épistémologie hégélienne.</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="150" customHeight="1" s="28">
-      <c r="A59" s="44" t="n">
-        <v>1967</v>
-      </c>
-      <c r="B59" s="44" t="n"/>
-      <c r="C59" s="44" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="D59" s="45" t="inlineStr">
+      <c r="D58" s="45" t="inlineStr">
         <is>
           <t>Franck FISCHBACH</t>
         </is>
       </c>
-      <c r="E59" s="46" t="inlineStr">
+      <c r="E58" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Franck_Fischbach"  style="color:#6A142A"  title=" Wikipedia"&gt;Franck FISCHBACH&lt;/a&gt; est un philosophe franco-suisse  spécialiste de la philosophie allemande et de la philosophie sociale. Ses recherches portent sur l’idéalisme allemand (particulièrement Fichte, Hegel et Schelling), la réception de Marx et la philosophie sociale contemporaine. Il s’intéresse notamment à la reconnaissance, à l’aliénation, au travail, au socialisme, et à la &lt;a href="https://www.philomag.com/articles/franck-fischbach-le-capitalisme-fabrique-des-etres-qui-netant-plus-vraiment-sociaux-ne" style="color:#88A1E9" title=" Franck Fischbach : “Le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains” par philosophie magazine"&gt;critique du capitalisme&lt;/a&gt;. Il contribue activement à redonner à la philosophie sociale une légitimité intellectuelle en France. &lt;/p&gt; &lt;p&gt; Il relie la tradition de la théorie critique (Adorno, Honneth) et celle du matérialisme marxien pour repenser les conditions de la vie sociale et du « vivre ensemble ». Il analyse le capitalisme contemporain comme un processus de désocialisation et de perte du monde commun, considérant que "le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains".​ &lt;/p&gt; &lt;p&gt; Il  a reçu le Prix des Rencontres philosophiques de Monaco pour &lt;a href="https://www.youtube.com/watch?v=i16BcDagxns&amp;t=73s" style="color:#88A1E9" title=" Franck Fischbach → Faire ensemble. Reconstruction sociale et sortie du capitalisme par Librairie Ombre Blanche"&gt;"Faire ensemble"&lt;/a&gt;, ouvrage dans lequel il propose une refondation du lien social et une sortie éthique du capitalisme et il est aujourd’hui reconnu comme l’un des penseurs français majeurs de la philosophie sociale, prolongeant la critique marxienne à la lumière des défis écologiques et politiques contemporains.​ &lt;/p&gt; Professeur à l’université de Strasbourg, il a publié un &lt;em&gt;Manifeste pour une philosophie sociale&lt;/em&gt; (2009), qui veut redonner à la philosophie la tâche de diagnostiquer les « pathologies » de la société. Dans &lt;em&gt;La Privation de monde&lt;/em&gt; (2011), il décrit l’aliénation contemporaine comme une perte de prise sur le temps, l’espace et le monde commun.    &lt;audio controls title=" Qu'est-ce que la philosophie sociale? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11188-25.03.2010-ITEMA_20221135-2010C14987S0084-NET_B0358179-5AB7-42B6-8D32-144EADE35F65_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F59" s="44" t="inlineStr">
+      <c r="F58" s="44" t="inlineStr">
         <is>
           <t>QetmJoRDpY0</t>
         </is>
       </c>
-      <c r="G59" s="47" t="inlineStr">
+      <c r="G58" s="47" t="inlineStr">
         <is>
           <t>Franck Fischbach, L’aliénation : un concept encore utile aujourd’hui ? par Departement Philosophie</t>
         </is>
       </c>
-      <c r="H59" s="47" t="inlineStr">
+      <c r="H58" s="47" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fischbach-mini.webp</t>
         </is>
       </c>
-      <c r="I59" s="47" t="n"/>
-      <c r="J59" s="48" t="inlineStr">
+      <c r="I58" s="47" t="n"/>
+      <c r="J58" s="48" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K59" s="48" t="inlineStr">
+      <c r="K58" s="48" t="inlineStr">
         <is>
           <t>Marxisme ; Théorie Critique</t>
         </is>
       </c>
-      <c r="L59" s="48" t="inlineStr">
+      <c r="L58" s="48" t="inlineStr">
         <is>
           <t>philosophe franco-suisse spécialiste de la philosophie sociale.</t>
         </is>
       </c>
-      <c r="M59" s="27" t="n"/>
-      <c r="N59" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
+      <c r="M58" s="27" t="n"/>
+      <c r="N58" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="167.25" customHeight="1" s="28">
-      <c r="A60" s="34" t="n">
+    <row r="59" ht="167.25" customHeight="1" s="28">
+      <c r="A59" s="34" t="n">
         <v>1968</v>
       </c>
-      <c r="B60" s="34" t="n"/>
-      <c r="C60" s="34" t="n">
+      <c r="B59" s="34" t="n"/>
+      <c r="C59" s="34" t="n">
         <v>1968</v>
       </c>
-      <c r="D60" s="27" t="inlineStr">
+      <c r="D59" s="27" t="inlineStr">
         <is>
           <t>Camille FROIDEVAUX-METTERIE</t>
         </is>
       </c>
-      <c r="E60" s="36" t="inlineStr">
+      <c r="E59" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Camille_Froidevaux-Metterie"  title=" Wikipedia"&gt;Camille FROIDEVAUX-METTERIE&lt;/a&gt;  est une philosophe et professeure de science politique française, spécialisée dans les questions féministes et la condition féminine contemporaine. Agrégée de science politique et titulaire d’un doctorat de philosophie politique, elle enseigne notamment à l’Université de Reims Champagne-Ardenne et a contribué à renouveler la pensée féministe en France. &lt;/p&gt; &lt;p&gt; Sa philosophie repose sur une phénoménologie du corps des femmes, qu’elle considère comme le &lt;a href="https://www.youtube.com/watch?v=raJW9Ovmpvk" title=" Camille Fridevaux-Metterie un corps à soi par librairie molla"&gt; lieu central de l’expérience &lt;/a&gt; féminine et de l’oppression patriarcale. Elle analyse comment le corps féminin a historiquement été objectivé, contrôlé et réduit à un objet de désir ou de norme sociale, ce qui produit une aliénation profonde pour les femmes. &lt;/p&gt; &lt;p&gt; Elle développe une approche de féminisme incarné, qui cherche à &lt;a href="https://www.youtube.com/watch?v=3omfOctPy48" title=" Camille Fridevaux-Metterie réinventer l’amour par Barbara Carlotti"&gt; dépasser les clivages &lt;/a&gt; traditionnels entre universalisme et différentialisme. Selon elle, le corps n’est pas seulement un lieu d’aliénation, mais aussi une source potentielle d’émancipation : la réappropriation de son propre corps permet aux femmes de se libérer et de transformer les normes sociales. &lt;/p&gt; &lt;p&gt; Elle insiste sur l’importance de l’expérience vécue (le « vécu corporel »), notamment autour de la grossesse, de la vulnérabilité et de la sexualité, qu’elle traite comme des dimensions politiques et non plus seulement intimes. Dans Un si gros ventre (2023), par exemple, elle explore la grossesse comme expérience à la fois intime et socialement structurante. &lt;/p&gt; &lt;p&gt; Elle incarne un féminisme contemporain qui articule philosophie, sciences politiques et récit personnel. Inspirée par Simone de Beauvoir et Iris Marion Young, elle défend un féminisme pluriel, créatif et politiquement engageant, où la libération des femmes passe par la reconnaissance et la réappropriation de leur corporéité.  &lt;/p&gt; &lt;audio controls title="Histoire politique du féménisme avec Camille Froidevaux-Metterie  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-31.10.2025-ITEMA_24296659-2025F45096S0304-NET_MFI_7891A381-183D-44C4-B741-51A4BC4DD2C4-22-2af896bd1e7f8bcd4790879da0a18b3c.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
+      <c r="F59" s="34" t="inlineStr">
+        <is>
+          <t>mprvC9XQUJk</t>
+        </is>
+      </c>
+      <c r="G59" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Camille Froidevaux-Metterie philosophie du genre par Collège de France</t>
+        </is>
+      </c>
+      <c r="H59" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/cfmetterie-mini.webp</t>
+        </is>
+      </c>
+      <c r="I59" s="36" t="n"/>
+      <c r="J59" s="27" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K59" s="27" t="inlineStr">
+        <is>
+          <t>Phénoménologie ; Féminisme</t>
+        </is>
+      </c>
+      <c r="L59" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe féministe française connue pour ses travaux sur le corps des femmes et les transformations du féminisme.
+</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="123.75" customHeight="1" s="28">
+      <c r="A60" s="34" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B60" s="34" t="n"/>
+      <c r="C60" s="34" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="D60" s="35" t="inlineStr">
+        <is>
+          <t>Laurence DEVILLAIRS</t>
+        </is>
+      </c>
+      <c r="E60" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://www.philomag.com/philosophes/laurence-devillairs"  title=" Wikipedia"&gt;Laurence DEVILLAIRS&lt;/a&gt;  est une philosophe française, spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle. Elle enseigne à l’université Paris 1 Panthéon-Sorbonne et s’adresse aussi à un large public à travers des essais et des interventions. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse beaucoup à la morale concrète : le bien, le mal, &lt;a href="https://www.youtube.com/watch?v=a5YnPWx7Xw8" title="laurence Devillairs : Eloge de la gentillesse par Brut"&gt; la gentillesse, &lt;/a&gt; le courage, la justice. Elle refuse une vision trop abstraite de l’éthique et cherche plutôt à montrer comment on devient une &lt;a href="https://www.youtube.com/watch?v=T0U2ro8b9Io" title="laurence Devillairs : a quoi reconnaître quelqu’un de bien par TV Monde"&gt; personne meilleure &lt;/a&gt; dans la vie quotidienne. &lt;/p&gt; &lt;p&gt; Elle réfléchit aussi au politique, mais d’une manière très humaine : comment vivre ensemble, comment &lt;a href="https://www.youtube.com/watch?v=p9AaVfIoIPg" title="laurence Devillairs : le pouvoir par Fabrice Midal"&gt; penser le pouvoir, &lt;/a&gt; comment garder une place pour l’utopie et l’espérance sans perdre le sens du réel. Chez elle, le politique n’est pas seulement affaire de règles, mais aussi de désir de transformation. &lt;/p&gt; &lt;p&gt; Sa philosophie défend une forme de fermeté douce : être bon ne veut pas dire être faible, et la gentillesse peut être un choix éthique fort. Son travail cherche à rendre la philosophie utile pour mieux vivre, mieux juger et mieux agir. Lectrice de Descartes, elle retient de lui le goût de la clarté et de la générosité, cette juste estime de soi qui consiste à bien user de sa liberté. Dans &lt;em&gt;Être quelqu’un de bien&lt;/em&gt; (2019), elle montre que la bonté n’est pas une naïveté, mais une forme de courage, et qu’elle se joue d’abord dans les gestes ordinaires, l’attention, la parole donnée, le refus de l’humiliation. &lt;/p&gt;  &lt;audio controls title="Laurence Devillairs : le désir de vengeance est une libération  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.04.2026-ITEMA_24449483-2026F22640S0095-NET_MFI_BFCBC71B-F523-4D4D-9C0D-E455E058A13C-22-23fd728f6afa552353ce5d4ded4690c9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+</t>
+        </is>
+      </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>mprvC9XQUJk</t>
+          <t>ebQxk90j0NQ</t>
         </is>
       </c>
       <c r="G60" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camille Froidevaux-Metterie philosophie du genre par Collège de France</t>
-        </is>
-      </c>
-      <c r="H60" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/cfmetterie-mini.webp</t>
+          <t xml:space="preserve">"Laurence Devillairs - La splendeur du monde : aller à la rencontre de la beauté" par Librairie Mollat</t>
+        </is>
+      </c>
+      <c r="H60" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/devillairs-mini.webp</t>
         </is>
       </c>
       <c r="I60" s="36" t="n"/>
       <c r="J60" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>ethique ; spiritualite</t>
         </is>
       </c>
       <c r="K60" s="27" t="inlineStr">
         <is>
-          <t>Phénoménologie ; Féminisme</t>
-        </is>
-      </c>
-      <c r="L60" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe féministe française connue pour ses travaux sur le corps des femmes et les transformations du féminisme.
-</t>
+          <t>Spiritualisme</t>
+        </is>
+      </c>
+      <c r="L60" s="27" t="inlineStr">
+        <is>
+          <t>philosophe française spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4417,11 +4421,11 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="123.75" customHeight="1" s="28">
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="126.75" customHeight="1" s="28">
       <c r="A61" s="34" t="n">
         <v>1969</v>
       </c>
@@ -4433,28 +4437,27 @@
       </c>
       <c r="D61" s="35" t="inlineStr">
         <is>
-          <t>Laurence DEVILLAIRS</t>
-        </is>
-      </c>
-      <c r="E61" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://www.philomag.com/philosophes/laurence-devillairs"  title=" Wikipedia"&gt;Laurence DEVILLAIRS&lt;/a&gt;  est une philosophe française, spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle. Elle enseigne à l’université Paris 1 Panthéon-Sorbonne et s’adresse aussi à un large public à travers des essais et des interventions. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse beaucoup à la morale concrète : le bien, le mal, &lt;a href="https://www.youtube.com/watch?v=a5YnPWx7Xw8" title="laurence Devillairs : Eloge de la gentillesse par Brut"&gt; la gentillesse, &lt;/a&gt; le courage, la justice. Elle refuse une vision trop abstraite de l’éthique et cherche plutôt à montrer comment on devient une &lt;a href="https://www.youtube.com/watch?v=T0U2ro8b9Io" title="laurence Devillairs : a quoi reconnaître quelqu’un de bien par TV Monde"&gt; personne meilleure &lt;/a&gt; dans la vie quotidienne. &lt;/p&gt; &lt;p&gt; Elle réfléchit aussi au politique, mais d’une manière très humaine : comment vivre ensemble, comment &lt;a href="https://www.youtube.com/watch?v=p9AaVfIoIPg" title="laurence Devillairs : le pouvoir par Fabrice Midal"&gt; penser le pouvoir, &lt;/a&gt; comment garder une place pour l’utopie et l’espérance sans perdre le sens du réel. Chez elle, le politique n’est pas seulement affaire de règles, mais aussi de désir de transformation. &lt;/p&gt; &lt;p&gt; Sa philosophie défend une forme de fermeté douce : être bon ne veut pas dire être faible, et la gentillesse peut être un choix éthique fort. Son travail cherche à rendre la philosophie utile pour mieux vivre, mieux juger et mieux agir. Lectrice de Descartes, elle retient de lui le goût de la clarté et de la générosité, cette juste estime de soi qui consiste à bien user de sa liberté. Dans &lt;em&gt;Être quelqu’un de bien&lt;/em&gt; (2019), elle montre que la bonté n’est pas une naïveté, mais une forme de courage, et qu’elle se joue d’abord dans les gestes ordinaires, l’attention, la parole donnée, le refus de l’humiliation. &lt;/p&gt;  &lt;audio controls title="Laurence Devillairs : le désir de vengeance est une libération  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.04.2026-ITEMA_24449483-2026F22640S0095-NET_MFI_BFCBC71B-F523-4D4D-9C0D-E455E058A13C-22-23fd728f6afa552353ce5d4ded4690c9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
+          <t>Vincent DELECROIX</t>
+        </is>
+      </c>
+      <c r="E61" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Delecroix"  title=" Wikipedia"&gt;Vincent DELECROIX&lt;/a&gt; (né en 1969) est un philosophe et romancier français, spécialiste de Kierkegaard et de la philosophie de la religion. Agrégé de philosophie, il est directeur d’études à l’École pratique des hautes études (EPHE), où il enseigne la philosophie de la religion, et il a dirigé l’édition et la traduction de plusieurs œuvres de Kierkegaard.&lt;/p&gt; &lt;p&gt;Son travail interroge la manière dont la foi peut encore exister dans un monde moderne où les certitudes absolues &lt;a href="https://www.youtube.com/watch?v=2ZHOpP5GMwI" title="Vincent DELECROIX,la nécessité d’apprendre par TV5 monde"&gt;se sont affaiblies&lt;/a&gt;. À la suite de Kierkegaard, il ne traite pas la religion comme un héritage figé ou un ensemble de dogmes, mais comme une expérience intérieure, fragile et exigeante, où l’individu est engagé tout entier. La vérité, dans ce domaine, n’est pas un savoir objectif que l’on possède, mais une manière d’exister. Il réfléchit aussi aux rapports entre religion et politique, et à la façon dont les espérances religieuses se transforment dans les idéologies modernes. Un autre axe important de sa pensée est la révolte. Dans &lt;em&gt;Tombeau d’Achille&lt;/em&gt;, il médite sur la colère du héros d’Homère ; dans &lt;em&gt;Non ! De l’esprit de révolte&lt;/em&gt;, il réfléchit au refus et à la parole &lt;a href="https://www.youtube.com/watch?v=OiUgp6wLpCA" title="Vincent DELECROIX il faut sortir du oui non par France Culture"&gt;qui dit non&lt;/a&gt;, non comme de simples réactions d’humeur, mais comme des actes qui révèlent une exigence morale : refuser l’inacceptable, c’est affirmer qu’il existe quelque chose qui vaut.&lt;/p&gt; &lt;p&gt;Romancier, il a publié plusieurs livres où la fiction devient une autre manière de philosopher. Sa pensée cherche comment l’être humain peut garder une voix et une exigence spirituelle dans un monde désorienté.&lt;/p&gt;  &lt;audio controls title="Vincent DELECROIX  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>ebQxk90j0NQ</t>
+          <t>sVWokXyL1YE</t>
         </is>
       </c>
       <c r="G61" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Laurence Devillairs - La splendeur du monde : aller à la rencontre de la beauté" par Librairie Mollat</t>
+          <t xml:space="preserve">"Vincent Delecroix - Naufrage" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H61" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/devillairs-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/vdelecroix-mini.webp</t>
         </is>
       </c>
       <c r="I61" s="36" t="n"/>
@@ -4465,17 +4468,12 @@
       </c>
       <c r="K61" s="27" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
-        </is>
-      </c>
-      <c r="L61" s="27" t="inlineStr">
-        <is>
-          <t>philosophe française spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>Existentialisme</t>
+        </is>
+      </c>
+      <c r="L61" s="42" t="inlineStr">
+        <is>
+          <t>philosophe et écrivain français, spécialiste de Kierkegaard et de philosophie de la religion.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4489,84 +4487,22 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="126.75" customHeight="1" s="28">
+    <row r="62" ht="147.75" customHeight="1" s="28">
       <c r="A62" s="34" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B62" s="34" t="n"/>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="D62" s="35" t="inlineStr">
         <is>
-          <t>Vincent DELECROIX</t>
-        </is>
-      </c>
-      <c r="E62" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Delecroix"  title=" Wikipedia"&gt;Vincent DELECROIX&lt;/a&gt; (né en 1969) est un philosophe et romancier français, spécialiste de Kierkegaard et de la philosophie de la religion. Agrégé de philosophie, il est directeur d’études à l’École pratique des hautes études (EPHE), où il enseigne la philosophie de la religion, et il a dirigé l’édition et la traduction de plusieurs œuvres de Kierkegaard.&lt;/p&gt; &lt;p&gt;Son travail interroge la manière dont la foi peut encore exister dans un monde moderne où les certitudes absolues &lt;a href="https://www.youtube.com/watch?v=2ZHOpP5GMwI" title="Vincent DELECROIX,la nécessité d’apprendre par TV5 monde"&gt;se sont affaiblies&lt;/a&gt;. À la suite de Kierkegaard, il ne traite pas la religion comme un héritage figé ou un ensemble de dogmes, mais comme une expérience intérieure, fragile et exigeante, où l’individu est engagé tout entier. La vérité, dans ce domaine, n’est pas un savoir objectif que l’on possède, mais une manière d’exister. Il réfléchit aussi aux rapports entre religion et politique, et à la façon dont les espérances religieuses se transforment dans les idéologies modernes. Un autre axe important de sa pensée est la révolte. Dans &lt;em&gt;Tombeau d’Achille&lt;/em&gt;, il médite sur la colère du héros d’Homère ; dans &lt;em&gt;Non ! De l’esprit de révolte&lt;/em&gt;, il réfléchit au refus et à la parole &lt;a href="https://www.youtube.com/watch?v=OiUgp6wLpCA" title="Vincent DELECROIX il faut sortir du oui non par France Culture"&gt;qui dit non&lt;/a&gt;, non comme de simples réactions d’humeur, mais comme des actes qui révèlent une exigence morale : refuser l’inacceptable, c’est affirmer qu’il existe quelque chose qui vaut.&lt;/p&gt; &lt;p&gt;Romancier, il a publié plusieurs livres où la fiction devient une autre manière de philosopher. Sa pensée cherche comment l’être humain peut garder une voix et une exigence spirituelle dans un monde désorienté.&lt;/p&gt;  &lt;audio controls title="Vincent DELECROIX  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F62" s="34" t="inlineStr">
-        <is>
-          <t>sVWokXyL1YE</t>
-        </is>
-      </c>
-      <c r="G62" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Vincent Delecroix - Naufrage" par Librairie Mollat</t>
-        </is>
-      </c>
-      <c r="H62" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/vdelecroix-mini.webp</t>
-        </is>
-      </c>
-      <c r="I62" s="36" t="n"/>
-      <c r="J62" s="27" t="inlineStr">
-        <is>
-          <t>ethique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="K62" s="27" t="inlineStr">
-        <is>
-          <t>Existentialisme</t>
-        </is>
-      </c>
-      <c r="L62" s="42" t="inlineStr">
-        <is>
-          <t>philosophe et écrivain français, spécialiste de Kierkegaard et de philosophie de la religion.</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sens</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="147.75" customHeight="1" s="28">
-      <c r="A63" s="34" t="n">
-        <v>1970</v>
-      </c>
-      <c r="B63" s="34" t="n"/>
-      <c r="C63" s="34" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="D63" s="35" t="inlineStr">
-        <is>
           <t>Jean Claude MONOD</t>
         </is>
       </c>
-      <c r="E63" s="36" t="inlineStr">
+      <c r="E62" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Monod"  title=" Wikipedia"&gt;Jean Claude MONOD&lt;/a&gt; est un philosophe français  contemporain, spécialiste de philosophie politique et de philosophie allemande des XIXe et XXe siècles, en particulier de la question de la sécularisation et des rapports entre religion, modernité et démocratie. Ancien élève de l’École normale supérieure, chercheur au CNRS aux Archives Husserl, il a aussi publié &lt;em&gt;Qu’est-ce qu’un chef en démocratie ?&lt;/em&gt; (2012), sur le charisme politique. &lt;/p&gt; &lt;p&gt;  Un axe central de sa réflexion est de comprendre la modernité sans la réduire à une simple transposition de catégories religieuses, et de penser  &lt;a href="https://www.youtube.com/watch?v=E111pSvCT8g"  title="
 Jean-Claude Monod - L'art de ne pas être trop gouverné par librairie mollat"&gt;le théologico-politique&lt;/a&gt;  aujourd’hui. Il s’intéresse aussi aux formes contemporaines du pouvoir (crises de l’État libéral, charisme politique, crises de gouvernementalité, néolibéralisme autoritaire) et aux tensions entre démocratie, vérité et fake news. &lt;/p&gt; &lt;p&gt; Dans son ouvrage : &lt;a href="https://www.gregoiredetours.fr/thematiques/religions/jean-claude-monod-secularisation-et-laicite/"  title="
@@ -4574,35 +4510,98 @@
   &lt;audio controls title="L'intellectuel peut-il encore exister au XXIe siècle ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/25951-29.11.2025-ITEMA_24326903-2025C54596S0333-NET_MFC_C2F18604-F792-44E5-803E-E62225C653B4-25-bf7dbc88816a940ebe2dc58d15ae6341.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
+      <c r="F62" s="34" t="inlineStr">
+        <is>
+          <t>v6zl6a4K1Sw</t>
+        </is>
+      </c>
+      <c r="G62" s="36" t="inlineStr">
+        <is>
+          <t>"Gouverner sans dominer, ou le difficile héritage du libéralisme" par France Culture</t>
+        </is>
+      </c>
+      <c r="H62" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/monod-mini.webp</t>
+        </is>
+      </c>
+      <c r="I62" s="36" t="n"/>
+      <c r="J62" s="27" t="inlineStr">
+        <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K62" s="27" t="inlineStr">
+        <is>
+          <t>Herméneutique ; Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L62" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français spécialiste de philosophie allemande contemporaine et de philosophie politique.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="116.25" customHeight="1" s="28">
+      <c r="A63" s="34" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B63" s="34" t="n"/>
+      <c r="C63" s="34" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="D63" s="35" t="inlineStr">
+        <is>
+          <t>Edouard MEHL</t>
+        </is>
+      </c>
+      <c r="E63" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Mehl"  title=" Wikipedia"&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href="https://www.youtube.com/watch?v=NT0n7tKNb3w" title="qu’est ce que la verité par Le forum Veritas"&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; Il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. Il a notamment étudié le jeune Descartes lors de son séjour en Allemagne, en 1619-1620, au moment de ses célèbres songes et de la naissance de sa méthode, ainsi que ses rapports avec Kepler et les savants de son temps. Il montre que la métaphysique cartésienne est inséparable d’un projet de physique et de cosmologie, qui vise à rendre le monde visible et intelligible tout entier. &lt;/p&gt; 
+</t>
+        </is>
+      </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>v6zl6a4K1Sw</t>
+          <t>aBav8Q81MeQ</t>
         </is>
       </c>
       <c r="G63" s="36" t="inlineStr">
         <is>
-          <t>"Gouverner sans dominer, ou le difficile héritage du libéralisme" par France Culture</t>
+          <t>"Pourquoi méditer ? — Edouard Mehl" par Andrea Cirla</t>
         </is>
       </c>
       <c r="H63" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/monod-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/emehl-mini.webp</t>
         </is>
       </c>
       <c r="I63" s="36" t="n"/>
       <c r="J63" s="27" t="inlineStr">
         <is>
-          <t>politique ; epistemologie</t>
+          <t>metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K63" s="27" t="inlineStr">
         <is>
-          <t>Herméneutique ; Phénoménologie</t>
+          <t>Idéalisme</t>
         </is>
       </c>
       <c r="L63" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de philosophie allemande contemporaine et de philosophie politique.</t>
+          <t>philosophe français spécialiste de la philosophie moderne et de l’histoire des sciences.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4612,60 +4611,65 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="116.25" customHeight="1" s="28">
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="142.5" customHeight="1" s="28">
       <c r="A64" s="34" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B64" s="34" t="n"/>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
         <is>
-          <t>Edouard MEHL</t>
-        </is>
-      </c>
-      <c r="E64" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Mehl"  title=" Wikipedia"&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href="https://www.youtube.com/watch?v=NT0n7tKNb3w" title="qu’est ce que la verité par Le forum Veritas"&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; Il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. Il a notamment étudié le jeune Descartes lors de son séjour en Allemagne, en 1619-1620, au moment de ses célèbres songes et de la naissance de sa méthode, ainsi que ses rapports avec Kepler et les savants de son temps. Il montre que la métaphysique cartésienne est inséparable d’un projet de physique et de cosmologie, qui vise à rendre le monde visible et intelligible tout entier. &lt;/p&gt; 
-</t>
+          <t>Barbara STIEGLER</t>
+        </is>
+      </c>
+      <c r="E64" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Stiegler" title=" Wikipedia"&gt;Barbara STIEGLER&lt;/a&gt; (née en 1971) est une philosophe française, spécialiste de Nietzsche et de philosophie politique, connue pour sa critique du néolibéralisme. Fille du philosophe Bernard Stiegler, agrégée de philosophie, elle est professeure à l’université Bordeaux-Montaigne, où elle a dirigé le master « Soin, éthique et santé ».&lt;/p&gt; &lt;p&gt;Ses premiers travaux portent sur Nietzsche et la biologie de son temps. Dans &lt;em&gt;Nietzsche et la biologie&lt;/em&gt; (2001) et &lt;em&gt;Nietzsche et la critique de la chair&lt;/em&gt; (2005), elle montre que la pensée de Nietzsche dialogue avec les sciences du vivant, et que le corps et la vie y sont des notions centrales. Elle se tourne ensuite vers la philosophie politique. Dans &lt;a href="https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/" title="Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit"&gt;&lt;em&gt;« Il faut s’adapter »&lt;/em&gt;&lt;/a&gt; (2019), elle remonte aux origines du &lt;a href="https://www.youtube.com/watch?v=oQQ4xqRvYTk" style="color:#88A1E9" title="LA LENTE AGONIE DU NÉOLIBÉRALISME  par 
+TheSwissBox Conversation"&gt;néolibéralisme&lt;/a&gt; : au début du XXe siècle, le journaliste américain Walter Lippmann, inspiré par une lecture de la théorie de l’évolution, soutenait que les peuples, en retard sur un monde qui change trop vite, devaient être adaptés par des experts au nouvel environnement mondialisé. Contre lui, le philosophe John Dewey défendait une démocratie fondée sur l’intelligence collective et la participation des citoyens. Barbara Stiegler montre que ce débat oublié éclaire nos sociétés, où l’injonction à s’adapter s’impose à l’école, au travail et dans la santé. Elle a ensuite appliqué ces analyses aux mouvements sociaux, dans &lt;em&gt;Du cap aux grèves&lt;/em&gt; (2020), puis à la crise de la covid, dans &lt;em&gt;De la démocratie en pandémie&lt;/em&gt; (2021).&lt;/p&gt; &lt;p&gt;Engagée dans le débat public, elle plaide pour une démocratie plus participative et pour une autre conception de la santé publique.&lt;/p&gt;  &lt;audio controls title="La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>aBav8Q81MeQ</t>
+          <t>bm6KyWYpaQU</t>
         </is>
       </c>
       <c r="G64" s="36" t="inlineStr">
         <is>
-          <t>"Pourquoi méditer ? — Edouard Mehl" par Andrea Cirla</t>
-        </is>
-      </c>
-      <c r="H64" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/emehl-mini.webp</t>
+          <t>"Barbara Stiegler - Les meilleurs moments de QG" par QG TV</t>
+        </is>
+      </c>
+      <c r="H64" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/bastiegler-mini.webp</t>
         </is>
       </c>
       <c r="I64" s="36" t="n"/>
       <c r="J64" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; epistemologie</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K64" s="27" t="inlineStr">
         <is>
-          <t>Idéalisme</t>
+          <t>Théorie Critique</t>
         </is>
       </c>
       <c r="L64" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la philosophie moderne et de l’histoire des sciences.</t>
+          <t>philosophe française spécialiste de Nietzsche, de philosophie politique &amp;amp; critique du néolibéralisme.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4675,158 +4679,90 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t xml:space="preserve">reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="142.5" customHeight="1" s="28">
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="131.25" customHeight="1" s="28">
       <c r="A65" s="34" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B65" s="34" t="n"/>
       <c r="C65" s="34" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="D65" s="35" t="inlineStr">
         <is>
-          <t>Barbara STIEGLER</t>
-        </is>
-      </c>
-      <c r="E65" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Stiegler" title=" Wikipedia"&gt;Barbara STIEGLER&lt;/a&gt; (née en 1971) est une philosophe française, spécialiste de Nietzsche et de philosophie politique, connue pour sa critique du néolibéralisme. Fille du philosophe Bernard Stiegler, agrégée de philosophie, elle est professeure à l’université Bordeaux-Montaigne, où elle a dirigé le master « Soin, éthique et santé ».&lt;/p&gt; &lt;p&gt;Ses premiers travaux portent sur Nietzsche et la biologie de son temps. Dans &lt;em&gt;Nietzsche et la biologie&lt;/em&gt; (2001) et &lt;em&gt;Nietzsche et la critique de la chair&lt;/em&gt; (2005), elle montre que la pensée de Nietzsche dialogue avec les sciences du vivant, et que le corps et la vie y sont des notions centrales. Elle se tourne ensuite vers la philosophie politique. Dans &lt;a href="https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/" title="Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit"&gt;&lt;em&gt;« Il faut s’adapter »&lt;/em&gt;&lt;/a&gt; (2019), elle remonte aux origines du &lt;a href="https://www.youtube.com/watch?v=oQQ4xqRvYTk" style="color:#88A1E9" title="LA LENTE AGONIE DU NÉOLIBÉRALISME  par 
-TheSwissBox Conversation"&gt;néolibéralisme&lt;/a&gt; : au début du XXe siècle, le journaliste américain Walter Lippmann, inspiré par une lecture de la théorie de l’évolution, soutenait que les peuples, en retard sur un monde qui change trop vite, devaient être adaptés par des experts au nouvel environnement mondialisé. Contre lui, le philosophe John Dewey défendait une démocratie fondée sur l’intelligence collective et la participation des citoyens. Barbara Stiegler montre que ce débat oublié éclaire nos sociétés, où l’injonction à s’adapter s’impose à l’école, au travail et dans la santé. Elle a ensuite appliqué ces analyses aux mouvements sociaux, dans &lt;em&gt;Du cap aux grèves&lt;/em&gt; (2020), puis à la crise de la covid, dans &lt;em&gt;De la démocratie en pandémie&lt;/em&gt; (2021).&lt;/p&gt; &lt;p&gt;Engagée dans le débat public, elle plaide pour une démocratie plus participative et pour une autre conception de la santé publique.&lt;/p&gt;  &lt;audio controls title="La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F65" s="34" t="inlineStr">
-        <is>
-          <t>bm6KyWYpaQU</t>
-        </is>
-      </c>
-      <c r="G65" s="36" t="inlineStr">
-        <is>
-          <t>"Barbara Stiegler - Les meilleurs moments de QG" par QG TV</t>
-        </is>
-      </c>
-      <c r="H65" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/bastiegler-mini.webp</t>
-        </is>
-      </c>
-      <c r="I65" s="36" t="n"/>
-      <c r="J65" s="27" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="K65" s="27" t="inlineStr">
-        <is>
-          <t>Théorie Critique</t>
-        </is>
-      </c>
-      <c r="L65" s="27" t="inlineStr">
-        <is>
-          <t>philosophe française spécialiste de Nietzsche, de philosophie politique &amp;amp; critique du néolibéralisme.</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="131.25" customHeight="1" s="28">
-      <c r="A66" s="34" t="n">
-        <v>1972</v>
-      </c>
-      <c r="B66" s="34" t="n"/>
-      <c r="C66" s="34" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="D66" s="35" t="inlineStr">
-        <is>
           <t>Yves CUSSET</t>
         </is>
       </c>
-      <c r="E66" s="36" t="inlineStr">
+      <c r="E65" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yves_Cusset"  style="color:#6A142A"  title=" Wikipedia"&gt;Yves CUSSET&lt;/a&gt;  est un philosophe français agrégé et docteur en philosophie, qui allie une réflexion sérieuse sur la philosophie politique à un engagement théâtral et  &lt;a href="https://www.youtube.com/watch?v=uJLmpAgqiWY" style="color:#88A1E9" title="Yves Cusset, Petit manuel d'engagement politique à l'usage des mammifères doués de raison.... par Yves Cusset"&gt;humoristique unique. &lt;/a&gt;  Spécialiste de Habermas et Foucault, il explore les tensions entre raison discussionnelle et pouvoir, ainsi que les apories de l’accueil : comment concilier exigence éthique d’hospitalité et contraintes politiques. &lt;/p&gt; &lt;p&gt; Ses essais interrogent le "bien-mourir", critiquant les normes contemporaines de la mort apaisée, et défendent une politique de l’accueil face à la misère du monde.  Il théorise l’humour comme "bonne humeur pour mourir", un outil philosophique qui désarme les idées fixes et favorise la pensée sans intimidation. Il crée des solos comme Rien ne sert d’exister, Tractatus philo-comicus ou La Philosophie enseignée à ma chouette, joués au festival d’Avignon et ailleurs, mêlant rire, absurdité et métaphysique. &lt;/p&gt; &lt;p&gt; Militant discret, il use de l’humour politique pour dénoncer clichés  &lt;a href="https://www.youtube.com/watch?v=QwVPt_PQE-Q" style="color:#88A1E9" title="Yves Cusset : 100 façons de ne pas accueillir un migrant par TV5Monde"&gt;anti-migrants &lt;/a&gt; ou dérives du "développement personnel".  Son genre hybride, l’"humour philosophique", vise à émerveiller par le rire, suscitant la réflexion sans complexer, comme il l’explique dans Le Monde. Ses premiers travaux portent sur Habermas, dont il présente l’« éthique de la discussion » : une norme n’est valable que si tous ceux qu’elle concerne pourraient l’accepter au terme d’une discussion libre. Il en tire une exigence démocratique, mais aussi une attention à ceux qui n’ont pas la parole. Pour lui, le rire n’est pas une fuite hors de la pensée : il oblige à prendre de la distance avec soi-même et avec les certitudes. &lt;/p&gt; 
   &lt;audio controls title="L'amour avec Yves Cusset par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-07.06.2024-ITEMA_23765968-2024F45096S0159-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F66" s="34" t="inlineStr">
+      <c r="F65" s="34" t="inlineStr">
         <is>
           <t>3vE-JUIYaPs</t>
         </is>
       </c>
-      <c r="G66" s="36" t="inlineStr">
+      <c r="G65" s="36" t="inlineStr">
         <is>
           <t>"Réussir sa vie du premier coup", Yves Cusset, extrait par Yves Cusset</t>
         </is>
       </c>
-      <c r="H66" s="36" t="inlineStr">
+      <c r="H65" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/cusset-mini.webp</t>
         </is>
       </c>
-      <c r="I66" s="36" t="n"/>
-      <c r="J66" s="27" t="inlineStr">
+      <c r="I65" s="36" t="n"/>
+      <c r="J65" s="27" t="inlineStr">
         <is>
           <t>ethique</t>
         </is>
       </c>
-      <c r="K66" s="27" t="inlineStr">
+      <c r="K65" s="27" t="inlineStr">
         <is>
           <t>Existentialisme</t>
         </is>
       </c>
-      <c r="L66" s="27" t="inlineStr">
+      <c r="L65" s="27" t="inlineStr">
         <is>
           <t>philosophe français connu pour ses relations avec l'institution de l'être-en-commun.</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="174.75" customHeight="1" s="28">
-      <c r="A67" s="34" t="n">
+    <row r="66" ht="174.75" customHeight="1" s="28">
+      <c r="A66" s="34" t="n">
         <v>1973</v>
       </c>
-      <c r="B67" s="34" t="n"/>
-      <c r="C67" s="34" t="inlineStr">
+      <c r="B66" s="34" t="n"/>
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>1973</t>
         </is>
       </c>
-      <c r="D67" s="35" t="inlineStr">
+      <c r="D66" s="35" t="inlineStr">
         <is>
           <t>Eric SADIN</t>
         </is>
       </c>
-      <c r="E67" s="37" t="inlineStr">
+      <c r="E66" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89ric_Sadin"  title=" Wikipedia"&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href="https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur" style="color:#88A1E9"   title=" Éric SADIN contre ChatGPT par Senseur"&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;
 Sadin s'est fait connaître grâce à son livre "La société de l'anticipation " publié en 2011, dans lequel il examine l'émergence de la société de la surveillance et des technologies de prévision qui cherchent à anticiper les comportements et les désirs des individus. Il y aborde notamment les thèmes de la surveillance généralisée, de la collecte de données personnelles et des risques de manipulation. &lt;/p&gt; &lt;p&gt;
@@ -4834,35 +4770,97 @@
 Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre "La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique" publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href="https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008"  title="Dataïsme par lebigdata"&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title="Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
+      <c r="F66" s="34" t="inlineStr">
+        <is>
+          <t>DfLKeExecZc</t>
+        </is>
+      </c>
+      <c r="G66" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Pourquoi ChatGPT accélère la marchandisation de nos existences" par Le Figaro</t>
+        </is>
+      </c>
+      <c r="H66" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/sadin-mini.webp</t>
+        </is>
+      </c>
+      <c r="I66" s="36" t="n"/>
+      <c r="J66" s="27" t="inlineStr">
+        <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K66" s="27" t="inlineStr">
+        <is>
+          <t>Post Modernisme</t>
+        </is>
+      </c>
+      <c r="L66" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français critique des enjeux liés à la technologie et du Dataïsme.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="154.5" customHeight="1" s="28">
+      <c r="A67" s="34" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B67" s="34" t="n"/>
+      <c r="C67" s="34" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="D67" s="35" t="inlineStr">
+        <is>
+          <t>Aurélien BARRAU</t>
+        </is>
+      </c>
+      <c r="E67" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau" title=" Wikipedia"&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href="https://www.youtube.com/watch?v=PNMZHr3L_Ws" title=" Vivons nous dans un multivers par Aurelien Barrau"&gt; concept de multivers&lt;/a&gt;, et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage "Chaos multiples" et "De la vérité dans les sciences"  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé "Météorites". &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de "sauver le climat" plutôt "qu’agir pour la vie". &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  "habiter la science en poète" en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href="https://www.youtube.com/watch?v=94IxSYo5wtM" title="Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter"&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href="https://www.youtube.com/watch?v=g3Z_LsXD7DU" title=" L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac"&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un "faire monde" éthique et conscient. &lt;/p&gt;   &lt;audio controls title=" Aurelien BARRAU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>DfLKeExecZc</t>
+          <t>NXHzt-dnNZY</t>
         </is>
       </c>
       <c r="G67" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Pourquoi ChatGPT accélère la marchandisation de nos existences" par Le Figaro</t>
+          <t>"SORTIR DE NOS ADDICTIONS" par LIMIT</t>
         </is>
       </c>
       <c r="H67" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/sadin-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/barrau-mini.webp</t>
         </is>
       </c>
       <c r="I67" s="36" t="n"/>
       <c r="J67" s="27" t="inlineStr">
         <is>
-          <t>politique ; epistemologie</t>
+          <t>metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K67" s="27" t="inlineStr">
         <is>
-          <t>Post Modernisme</t>
+          <t>Réalisme</t>
         </is>
       </c>
       <c r="L67" s="27" t="inlineStr">
         <is>
-          <t>philosophe français critique des enjeux liés à la technologie et du Dataïsme.</t>
+          <t>philosophe et astrophysicien français nous invitant à repenser notre rapport au vivant.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4872,11 +4870,11 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t xml:space="preserve">esprit-ia</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="154.5" customHeight="1" s="28">
+          <t xml:space="preserve">ecologie ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="168.75" customHeight="1" s="28">
       <c r="A68" s="34" t="n">
         <v>1973</v>
       </c>
@@ -4888,43 +4886,44 @@
       </c>
       <c r="D68" s="35" t="inlineStr">
         <is>
-          <t>Aurélien BARRAU</t>
+          <t>Charles PÉPIN</t>
         </is>
       </c>
       <c r="E68" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau" title=" Wikipedia"&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href="https://www.youtube.com/watch?v=PNMZHr3L_Ws" title=" Vivons nous dans un multivers par Aurelien Barrau"&gt; concept de multivers&lt;/a&gt;, et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage "Chaos multiples" et "De la vérité dans les sciences"  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé "Météorites". &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de "sauver le climat" plutôt "qu’agir pour la vie". &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  "habiter la science en poète" en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href="https://www.youtube.com/watch?v=94IxSYo5wtM" title="Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter"&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href="https://www.youtube.com/watch?v=g3Z_LsXD7DU" title=" L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac"&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un "faire monde" éthique et conscient. &lt;/p&gt;   &lt;audio controls title=" Aurelien BARRAU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin" title=" Wikipedia"&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href="https://charlespepin.fr/"  title=" Site officiel Charles Pépin "&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href="https://www.youtube.com/watch?v=WExeoL6qVmc" title=" Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori"&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href="https://www.youtube.com/watch?v=orOxuIHT_vc" title="Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal"&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt;"Les Vertus de l’échec" publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt;"La Confiance en soi " paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt;"La Rencontre"  en 2021 et "Vivre avec son passé" en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href="https://www.youtube.com/watch?v=M09YmUzDwO8" title=" Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs"&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt;   &lt;audio controls title=" La philosophie selon Charles Pépin par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>NXHzt-dnNZY</t>
+          <t>EvUMFrTWzsQ</t>
         </is>
       </c>
       <c r="G68" s="36" t="inlineStr">
         <is>
-          <t>"SORTIR DE NOS ADDICTIONS" par LIMIT</t>
+          <t>"Mieux vivre grâce la philosophie pratique ! avec le philosophe Charles Pépin" par Métamorphose, éveille ta conscience</t>
         </is>
       </c>
       <c r="H68" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/barrau-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/pepin-mini.webp</t>
         </is>
       </c>
       <c r="I68" s="36" t="n"/>
       <c r="J68" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; epistemologie</t>
+          <t>ethique</t>
         </is>
       </c>
       <c r="K68" s="27" t="inlineStr">
         <is>
-          <t>Réalisme</t>
+          <t>Humanisme</t>
         </is>
       </c>
       <c r="L68" s="27" t="inlineStr">
         <is>
-          <t>philosophe et astrophysicien français nous invitant à repenser notre rapport au vivant.</t>
+          <t>philosophe français qui fait de la philosophie une force de vie quotidienne.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -4934,11 +4933,11 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie ; reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="168.75" customHeight="1" s="28">
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="146.25" customHeight="1" s="28">
       <c r="A69" s="34" t="n">
         <v>1973</v>
       </c>
@@ -4950,44 +4949,44 @@
       </c>
       <c r="D69" s="35" t="inlineStr">
         <is>
-          <t>Charles PÉPIN</t>
-        </is>
-      </c>
-      <c r="E69" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin" title=" Wikipedia"&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href="https://charlespepin.fr/"  title=" Site officiel Charles Pépin "&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href="https://www.youtube.com/watch?v=WExeoL6qVmc" title=" Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori"&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href="https://www.youtube.com/watch?v=orOxuIHT_vc" title="Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal"&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt;"Les Vertus de l’échec" publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt;"La Confiance en soi " paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt;"La Rencontre"  en 2021 et "Vivre avec son passé" en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href="https://www.youtube.com/watch?v=M09YmUzDwO8" title=" Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs"&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt;   &lt;audio controls title=" La philosophie selon Charles Pépin par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
+          <t>Mehdi BELHAJ KACEM</t>
+        </is>
+      </c>
+      <c r="E69" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mehdi_Belhaj_Kacem"   title=" Wikipedia"&gt;Mehdi BELHAJ KACEM&lt;/a&gt;   est un philosophe, écrivain et acteur franco-tunisien, autodidacte radical et figure controversée de la pensée contemporaine, passé par les milieux militants et   &lt;a href="https://blogs.mediapart.fr/olivier-rachet/blog/130525/le-manifeste-conspirationniste-de-mehdi-belhaj-kacem" title="Le manifeste conspirationniste de Mehdi Belhaj Kacempar par mediapart"&gt;littéraires underground &lt;/a&gt; avant de forger une œuvre philosophique exigeante et iconoclaste. Après des expériences communautaires militantes, il découvre Alain Badiou comme maître à penser initial. &lt;/p&gt; &lt;p&gt; Il développe une pensée du nihilisme héritée de Heidegger, Nietzsche et Schürmann, centrée sur le "pléonectique" (désir insatiable de puissance et de transcendance) et une ontologie de l’Histoire comme &lt;a href="https://www.youtube.com/watch?v=YTOzn7dta7k" title="Mehdi Belhaj Kacem : "Un nouveau totalitarisme est en train de se mettre en place" par France Soir"&gt;tragédie irréductible. &lt;/a&gt;  Dans cette période, il écrit ces deux ouvrages :  "L’Antéforme" en 1997 et "Esthétique du chaos" en 2000. Son projet majeur, "L’Esprit du nihilisme" (cinq tomes, 2009-2015), pose Hegel comme "parenthèse" entre Kant et Badiou, avant de rompre violemment avec ce dernier dans "Après Badiou" paru en  2011, accusé d’archaïsme politique et moral. &lt;/p&gt; &lt;p&gt; Positionné à la marge des institutions, il incarne une radicalité post-moderne qui refuse les compromis, liant esthétique, politique et métaphysique dans une critique du présent. Il explore la "sexuation" (être et genre comme inexistant fondamental) et la transgression comme seule voie face au néant. &lt;/p&gt; Né en 1973, il publie très jeune des romans avant de se tourner vers la philosophie. Son œuvre, abondante et difficile, cherche à penser le mal et la démesure humaine, ce désir d’avoir toujours plus qu’il appelle « pléonexie », comme le fond de l’histoire. Ses prises de position récentes, notamment pendant la crise sanitaire, ont suscité de vives critiques. 
+ &lt;audio controls title="Le bel âge de Mehdi Belhaj Kacem par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13937-24.01.2017-ITEMA_21206998-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>EvUMFrTWzsQ</t>
+          <t>0DgQg3UK08E</t>
         </is>
       </c>
       <c r="G69" s="36" t="inlineStr">
         <is>
-          <t>"Mieux vivre grâce la philosophie pratique ! avec le philosophe Charles Pépin" par Métamorphose, éveille ta conscience</t>
+          <t>"MEHDI BELHAJ KACEM - ÊTRE ET SEXUATION" par Nicolas CHOPIN-DESPRES</t>
         </is>
       </c>
       <c r="H69" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/pepin-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/kacem-mini.webp</t>
         </is>
       </c>
       <c r="I69" s="36" t="n"/>
       <c r="J69" s="27" t="inlineStr">
         <is>
-          <t>ethique</t>
+          <t>metaphysique ; esthetique</t>
         </is>
       </c>
       <c r="K69" s="27" t="inlineStr">
         <is>
-          <t>Humanisme</t>
+          <t>Post-structuralisme</t>
         </is>
       </c>
       <c r="L69" s="27" t="inlineStr">
         <is>
-          <t>philosophe français qui fait de la philosophie une force de vie quotidienne.</t>
+          <t>philosophe franco-tunisien auteur du Système du pléonectique.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -4997,60 +4996,59 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">sens</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="146.25" customHeight="1" s="28">
+          <t xml:space="preserve">continental ; art</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="192" customHeight="1" s="28">
       <c r="A70" s="34" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B70" s="34" t="n"/>
       <c r="C70" s="34" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="D70" s="35" t="inlineStr">
         <is>
-          <t>Mehdi BELHAJ KACEM</t>
-        </is>
-      </c>
-      <c r="E70" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mehdi_Belhaj_Kacem"   title=" Wikipedia"&gt;Mehdi BELHAJ KACEM&lt;/a&gt;   est un philosophe, écrivain et acteur franco-tunisien, autodidacte radical et figure controversée de la pensée contemporaine, passé par les milieux militants et   &lt;a href="https://blogs.mediapart.fr/olivier-rachet/blog/130525/le-manifeste-conspirationniste-de-mehdi-belhaj-kacem" title="Le manifeste conspirationniste de Mehdi Belhaj Kacempar par mediapart"&gt;littéraires underground &lt;/a&gt; avant de forger une œuvre philosophique exigeante et iconoclaste. Après des expériences communautaires militantes, il découvre Alain Badiou comme maître à penser initial. &lt;/p&gt; &lt;p&gt; Il développe une pensée du nihilisme héritée de Heidegger, Nietzsche et Schürmann, centrée sur le "pléonectique" (désir insatiable de puissance et de transcendance) et une ontologie de l’Histoire comme &lt;a href="https://www.youtube.com/watch?v=YTOzn7dta7k" title="Mehdi Belhaj Kacem : "Un nouveau totalitarisme est en train de se mettre en place" par France Soir"&gt;tragédie irréductible. &lt;/a&gt;  Dans cette période, il écrit ces deux ouvrages :  "L’Antéforme" en 1997 et "Esthétique du chaos" en 2000. Son projet majeur, "L’Esprit du nihilisme" (cinq tomes, 2009-2015), pose Hegel comme "parenthèse" entre Kant et Badiou, avant de rompre violemment avec ce dernier dans "Après Badiou" paru en  2011, accusé d’archaïsme politique et moral. &lt;/p&gt; &lt;p&gt; Positionné à la marge des institutions, il incarne une radicalité post-moderne qui refuse les compromis, liant esthétique, politique et métaphysique dans une critique du présent. Il explore la "sexuation" (être et genre comme inexistant fondamental) et la transgression comme seule voie face au néant. &lt;/p&gt; Né en 1973, il publie très jeune des romans avant de se tourner vers la philosophie. Son œuvre, abondante et difficile, cherche à penser le mal et la démesure humaine, ce désir d’avoir toujours plus qu’il appelle « pléonexie », comme le fond de l’histoire. Ses prises de position récentes, notamment pendant la crise sanitaire, ont suscité de vives critiques. 
- &lt;audio controls title="Le bel âge de Mehdi Belhaj Kacem par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13937-24.01.2017-ITEMA_21206998-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Michaël FOESSEL</t>
+        </is>
+      </c>
+      <c r="E70" s="37" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel"  title=" Wikipedia"&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un "philosophe de la liberté". Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que "être de gauche" signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage "La privation de l’intime" paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href="https://www.youtube.com/watch?v=HcDfUGypNvA" style="color:#88A1E9" title="Michaël Fœssel - Récidive, 1938 par Librairie mollat"&gt;"Récidive. 1938"&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme "laboratoire" pour comprendre les fragilités  &lt;a href="https://www.youtube.com/watch?v=wdeS7SFEz7Y"  title="Démocratie illibérale par Michaël Foessel par France Culture"&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 "Quartier rouge. Le plaisir et la gauche", il interroge le rapport de  &lt;a href="https://www.youtube.com/watch?v=MDubXJZox34" title="Michaël Foessel : "La question du plaisir est aujourd'hui centrale en politique" par France Inter"&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment "Vers la paix perpétuelle" et "La religion dans les limites de la simple raison", tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title="La gauche : état des lieux  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>0DgQg3UK08E</t>
+          <t>qejnQu7Cubs</t>
         </is>
       </c>
       <c r="G70" s="36" t="inlineStr">
         <is>
-          <t>"MEHDI BELHAJ KACEM - ÊTRE ET SEXUATION" par Nicolas CHOPIN-DESPRES</t>
+          <t xml:space="preserve">"Qui êtes-vous Michaël Fœssel ?" par ABC Penser</t>
         </is>
       </c>
       <c r="H70" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/kacem-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/foessel-mini.webp</t>
         </is>
       </c>
       <c r="I70" s="36" t="n"/>
       <c r="J70" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; esthetique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K70" s="27" t="inlineStr">
         <is>
-          <t>Post-structuralisme</t>
+          <t>Phénoménologie</t>
         </is>
       </c>
       <c r="L70" s="27" t="inlineStr">
         <is>
-          <t>philosophe franco-tunisien auteur du Système du pléonectique.</t>
+          <t>philosophe français spécialiste de la philosophie politique &amp;amp; philosophie allemande.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5060,11 +5058,11 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental ; art</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="192" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="141" customHeight="1" s="28">
       <c r="A71" s="34" t="n">
         <v>1974</v>
       </c>
@@ -5076,43 +5074,48 @@
       </c>
       <c r="D71" s="35" t="inlineStr">
         <is>
-          <t>Michaël FOESSEL</t>
-        </is>
-      </c>
-      <c r="E71" s="37" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel"  title=" Wikipedia"&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un "philosophe de la liberté". Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que "être de gauche" signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage "La privation de l’intime" paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href="https://www.youtube.com/watch?v=HcDfUGypNvA" style="color:#88A1E9" title="Michaël Fœssel - Récidive, 1938 par Librairie mollat"&gt;"Récidive. 1938"&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme "laboratoire" pour comprendre les fragilités  &lt;a href="https://www.youtube.com/watch?v=wdeS7SFEz7Y"  title="Démocratie illibérale par Michaël Foessel par France Culture"&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 "Quartier rouge. Le plaisir et la gauche", il interroge le rapport de  &lt;a href="https://www.youtube.com/watch?v=MDubXJZox34" title="Michaël Foessel : "La question du plaisir est aujourd'hui centrale en politique" par France Inter"&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment "Vers la paix perpétuelle" et "La religion dans les limites de la simple raison", tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title="La gauche : état des lieux  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Cynthia FLEURY</t>
+        </is>
+      </c>
+      <c r="E71" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cynthia_Fleury"  style="color:#6A142A"  title=" Wikipedia"&gt;Cynthia FLEURY&lt;/a&gt;  est une philosophe française connue pour son travail sur la démocratie, la vulnérabilité et l’éthique du soin. Elle  s’intéresse aux "outils de la &lt;a href="https://www.youtube.com/watch?v=rlmteYHuBsc" style="color:#88A1E9" title="DÉMOCRATIE, Cynthia Fleury (ABC Penser) "&gt;régulation démocratique" &lt;/a&gt; et au principe d’individuation en État social de droit, c’est‑à‑dire à la manière dont un État permet à chacun de devenir un sujet autonome tout en restant inséré dans le collectif. &lt;/p&gt; &lt;p&gt; Elle insiste sur l’importance d’un État social qui ne vise pas seulement la croissance économique, mais l’émancipation et l’autonomie des individus, notamment via les biens communs comme la santé et l’éducation et défend l’idée que la démocratie se joue aussi dans la façon dont nous prenons soin des plus vulnérables, à la fois sur le plan institutionnel et dans les relations ordinaires. &lt;/p&gt; &lt;p&gt;Pour elle, la vulnérabilité n’est pas l’inverse de l’autonomie, mais ce qui la traverse et la rend possible, à condition que la société permette de rendre les épreuves vécues "réversibles".&lt;/p&gt; &lt;p&gt;  Elle insiste sur l’éthique du soin : l’éthique n’est pas un "supplément d’âme" mais une condition pour éviter l’épuisement des soignants et mieux soigner les patients dans des institutions très gestionnaires. &lt;/p&gt; &lt;p&gt;Elle  défend un humanisme renouvelé et affirme l’urgence de remettre l’humanisme au cœur du système, face à l’hyper‑compétition, à la productivité sans fin et à l’aliénation qu’elles produisent. Sa réflexion propose une articulation entre transformation personnelle (travailler sa  &lt;a href="https://www.youtube.com/watch?v=8raeMytwQ8U" style="color:#88A1E9" title="Conférence de Cynthia Fleury sur la vulnérabilité  par  Faculté de Santé Sorbonne"&gt;propre vulnérabilité, &lt;/a&gt;  son courage, sa responsabilité) et transformation sociale (institutions plus justes, protection des biens communs, attention à la dignité de tous). &lt;/p&gt;   &lt;audio controls title="Cynthia Fleury : comment refaire société ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22259-09.07.2024-ITEMA_23798171-2024F44116S0191-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>qejnQu7Cubs</t>
+          <t>cwm4rm9brZE</t>
         </is>
       </c>
       <c r="G71" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Qui êtes-vous Michaël Fœssel ?" par ABC Penser</t>
+          <t>" le témoignage de Cynthia Fleury, psychologue" par Ville de Saint-Médard-en-Jalles</t>
         </is>
       </c>
       <c r="H71" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/foessel-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/fleury-mini.webp</t>
         </is>
       </c>
       <c r="I71" s="36" t="n"/>
       <c r="J71" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>ethique ; politique</t>
         </is>
       </c>
       <c r="K71" s="27" t="inlineStr">
         <is>
-          <t>Phénoménologie</t>
+          <t>Herméneutique</t>
         </is>
       </c>
       <c r="L71" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la philosophie politique &amp;amp; philosophie allemande.</t>
+          <t>philosophe et psychanalyste française auteure d'une thèse sur "la métaphysique de l'imagination".</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5126,7 +5129,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="141" customHeight="1" s="28">
+    <row r="72" ht="132.75" customHeight="1" s="28">
       <c r="A72" s="34" t="n">
         <v>1974</v>
       </c>
@@ -5138,43 +5141,43 @@
       </c>
       <c r="D72" s="35" t="inlineStr">
         <is>
-          <t>Cynthia FLEURY</t>
+          <t>Elsa DORLIN</t>
         </is>
       </c>
       <c r="E72" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cynthia_Fleury"  style="color:#6A142A"  title=" Wikipedia"&gt;Cynthia FLEURY&lt;/a&gt;  est une philosophe française connue pour son travail sur la démocratie, la vulnérabilité et l’éthique du soin. Elle  s’intéresse aux "outils de la &lt;a href="https://www.youtube.com/watch?v=rlmteYHuBsc" style="color:#88A1E9" title="DÉMOCRATIE, Cynthia Fleury (ABC Penser) "&gt;régulation démocratique" &lt;/a&gt; et au principe d’individuation en État social de droit, c’est‑à‑dire à la manière dont un État permet à chacun de devenir un sujet autonome tout en restant inséré dans le collectif. &lt;/p&gt; &lt;p&gt; Elle insiste sur l’importance d’un État social qui ne vise pas seulement la croissance économique, mais l’émancipation et l’autonomie des individus, notamment via les biens communs comme la santé et l’éducation et défend l’idée que la démocratie se joue aussi dans la façon dont nous prenons soin des plus vulnérables, à la fois sur le plan institutionnel et dans les relations ordinaires. &lt;/p&gt; &lt;p&gt;Pour elle, la vulnérabilité n’est pas l’inverse de l’autonomie, mais ce qui la traverse et la rend possible, à condition que la société permette de rendre les épreuves vécues "réversibles".&lt;/p&gt; &lt;p&gt;  Elle insiste sur l’éthique du soin : l’éthique n’est pas un "supplément d’âme" mais une condition pour éviter l’épuisement des soignants et mieux soigner les patients dans des institutions très gestionnaires. &lt;/p&gt; &lt;p&gt;Elle  défend un humanisme renouvelé et affirme l’urgence de remettre l’humanisme au cœur du système, face à l’hyper‑compétition, à la productivité sans fin et à l’aliénation qu’elles produisent. Sa réflexion propose une articulation entre transformation personnelle (travailler sa  &lt;a href="https://www.youtube.com/watch?v=8raeMytwQ8U" style="color:#88A1E9" title="Conférence de Cynthia Fleury sur la vulnérabilité  par  Faculté de Santé Sorbonne"&gt;propre vulnérabilité, &lt;/a&gt;  son courage, sa responsabilité) et transformation sociale (institutions plus justes, protection des biens communs, attention à la dignité de tous). &lt;/p&gt;   &lt;audio controls title="Cynthia Fleury : comment refaire société ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22259-09.07.2024-ITEMA_23798171-2024F44116S0191-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Elsa_Dorlin"  title=" Wikipedia"&gt;Elsa DORLIN&lt;/a&gt;  est une philosophe française  professeure de philosophie politique contemporaine à l’université Toulouse Jean Jaurès, spécialiste des épistémologies féministes, des intersections race/genre et de la violence politique. Invitée à Berkeley et chercheuse associée à Columbia, elle a dirigé des programmes comme ANR “Biosex” sur les sciences biomédicales et la différence sexuelle/raciale. &lt;/p&gt; &lt;p&gt; Ses travaux croisent Foucault, Judith Butler, Frantz Fanon et les traditions matérialistes africaines-américaines pour analyser les imbrications de domination (genre, race, classe) via une généalogie des discours médicaux, coloniaux et biopolitiques. Elle explore  &lt;a href="https://www.youtube.com/watch?v=04iiLbmn65w" title="Elsa Dorlin, pour un féminisme qui révolutionne la société par Centre d'Action Laïque. Libres, ensemble"&gt;l’historicité du sexe &lt;/a&gt; comme construction médicale et politique, critiquant l’assignation binaire et l’hétérosexualité reproductive comme outils de contrôle. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"La Matrice de la race" paru en 2006 : généalogie coloniale et sexuelle de la nation française via la médecine et "Sexe, genre et sexualités" en 2008 : introduction aux théories féministes, queer et post-coloniales. -"Une philosophie de la violence"  en 2017 : histoire politique de l’autodéfense des minorités opprimées. &lt;/p&gt; &lt;p&gt; Elle défend une "analytique de la domination" intersectionnelle, où race et genre sont co-constitutifs via biopouvoirs historiques, et une phénoménologie fanonienne des corps opprimés qui légitime la   &lt;a href="https://www.youtube.com/watch?v=Qh0FHzFxZns" title="Se défendre, une philosophie de la violence - Elsa Dorlinr par lundimatin"&gt;violence défensive &lt;/a&gt; comme praxis émancipatrice. &lt;/p&gt; &lt;audio controls title="Se défendre avec Elsa Dorlin par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-03.05.2021-ITEMA_22654753-2021F26101S0123-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>cwm4rm9brZE</t>
+          <t>tGPA-Nv1OBc</t>
         </is>
       </c>
       <c r="G72" s="36" t="inlineStr">
         <is>
-          <t>" le témoignage de Cynthia Fleury, psychologue" par Ville de Saint-Médard-en-Jalles</t>
+          <t>"Mouvements sociaux : violence ou autodéfense  ? " par France 24</t>
         </is>
       </c>
       <c r="H72" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/fleury-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/dorlin-mini.webp</t>
         </is>
       </c>
       <c r="I72" s="36" t="n"/>
       <c r="J72" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K72" s="27" t="inlineStr">
         <is>
-          <t>Herméneutique</t>
+          <t>Post-structuralisme</t>
         </is>
       </c>
       <c r="L72" s="27" t="inlineStr">
         <is>
-          <t>philosophe et psychanalyste française auteure d'une thèse sur "la métaphysique de l'imagination".</t>
+          <t>philosophe française spécialiste des épistémologies féministes &amp;amp; des intersections race/genre.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5189,11 +5192,11 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="132.75" customHeight="1" s="28">
+          <t xml:space="preserve">genre ; critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="173.25" customHeight="1" s="28">
       <c r="A73" s="34" t="n">
         <v>1974</v>
       </c>
@@ -5205,43 +5208,44 @@
       </c>
       <c r="D73" s="35" t="inlineStr">
         <is>
-          <t>Elsa DORLIN</t>
-        </is>
-      </c>
-      <c r="E73" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Elsa_Dorlin"  title=" Wikipedia"&gt;Elsa DORLIN&lt;/a&gt;  est une philosophe française  professeure de philosophie politique contemporaine à l’université Toulouse Jean Jaurès, spécialiste des épistémologies féministes, des intersections race/genre et de la violence politique. Invitée à Berkeley et chercheuse associée à Columbia, elle a dirigé des programmes comme ANR “Biosex” sur les sciences biomédicales et la différence sexuelle/raciale. &lt;/p&gt; &lt;p&gt; Ses travaux croisent Foucault, Judith Butler, Frantz Fanon et les traditions matérialistes africaines-américaines pour analyser les imbrications de domination (genre, race, classe) via une généalogie des discours médicaux, coloniaux et biopolitiques. Elle explore  &lt;a href="https://www.youtube.com/watch?v=04iiLbmn65w" title="Elsa Dorlin, pour un féminisme qui révolutionne la société par Centre d'Action Laïque. Libres, ensemble"&gt;l’historicité du sexe &lt;/a&gt; comme construction médicale et politique, critiquant l’assignation binaire et l’hétérosexualité reproductive comme outils de contrôle. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"La Matrice de la race" paru en 2006 : généalogie coloniale et sexuelle de la nation française via la médecine et "Sexe, genre et sexualités" en 2008 : introduction aux théories féministes, queer et post-coloniales. -"Une philosophie de la violence"  en 2017 : histoire politique de l’autodéfense des minorités opprimées. &lt;/p&gt; &lt;p&gt; Elle défend une "analytique de la domination" intersectionnelle, où race et genre sont co-constitutifs via biopouvoirs historiques, et une phénoménologie fanonienne des corps opprimés qui légitime la   &lt;a href="https://www.youtube.com/watch?v=Qh0FHzFxZns" title="Se défendre, une philosophie de la violence - Elsa Dorlinr par lundimatin"&gt;violence défensive &lt;/a&gt; comme praxis émancipatrice. &lt;/p&gt; &lt;audio controls title="Se défendre avec Elsa Dorlin par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-03.05.2021-ITEMA_22654753-2021F26101S0123-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;                                                                                                                                                                                                                                       </t>
+          <t>Claire MARIN</t>
+        </is>
+      </c>
+      <c r="E73" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claire_Marin"  title=" Wikipedia"&gt;Claire MARIN&lt;/a&gt;  est une philosophe et écrivaine française professeure agrégée de philosophie en classes préparatives aux grandes écoles et membre associée de l'École normale supérieure. Normalienne, elle enseigne des auteurs comme Deleuze ou Bergson tout en menant une œuvre accessible et sensible, mêlant philosophie, littérature et expérience intime. Ses essais,  &lt;a href="https://www.youtube.com/watch?v=189nLvJBfJc" title="Claire MARIN par LCP"&gt;best-sellers récents &lt;/a&gt; comme Rupture(s) (2021) et Être à sa place (2022), explorent les épreuves existentielles sans céder au développement personnel simpliste, en s'appuyant sur un corpus philosophique et littéraire vaste. &lt;/p&gt; &lt;p&gt; Elle excelle à philosophier l'intime : ruptures amoureuses, deuil, maladie, identité plurielle, en les reliant à des penseurs comme Pascal, Hume ou le courant du care (qu'elle étudie au Séminaire international d’études sur le soin à l’ENS). La rupture y est à double visage – blessure irrémédiable mais aussi transformation radicale, plaisir de la dispersion du "moi" fragmenté. Elle rejette l'unité illusoire du sujet pour une existence mouvante, ancrée dans le vécu concret et la narration poétique. &lt;/p&gt; &lt;p&gt; Ses &lt;a href="https://www.youtube.com/watch?v=3L7BK5JN8FM" title="Claire MARIN par Librairie mollat"&gt;réflexions récentes &lt;/a&gt; insistent sur le "vivant" comme mouvement patient, empathique et sensible, contre les abstractions métaphysiques : éducation au rythme biologique, altérité bienveillante, douceur face à la souffrance. Influencée par Bergson, elle reconnecte discours philosophiques au corps et à l'émotion, critiquant le mépris académique pour le care. Philosophe "psylosophe" post-Covid, elle rend la pensée romanesque, ciselant des chapitres incisifs comme des "disserts intimistes".&lt;/p&gt; &lt;p&gt; Enseignante engagée, elle vulgarise la philosophie pour lycéens via des ouvrages thématiques (bonheur, identité, nature/culture), sans manuel rigide mais avec un "pas de côté" concret. Romancière primée (prix Jean-Bernard en 2008), elle mêle esthétique poétique et réflexion sociétale, dialoguant avec la modernité (feminine, technique). Son style narratif transforme la philo en journal existentiel, touchant un large public féminin surtout. &lt;/p&gt; &lt;audio controls title="La philosophie de Claire MARIN par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13942-19.09.2022-ITEMA_23138788-2022F29830S0262-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
+</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>tGPA-Nv1OBc</t>
+          <t>fe6vbibY2CY</t>
         </is>
       </c>
       <c r="G73" s="36" t="inlineStr">
         <is>
-          <t>"Mouvements sociaux : violence ou autodéfense  ? " par France 24</t>
+          <t xml:space="preserve">"Les débuts - Claire Marin" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H73" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/dorlin-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/cmarin-mini.webp</t>
         </is>
       </c>
       <c r="I73" s="36" t="n"/>
       <c r="J73" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>ethique</t>
         </is>
       </c>
       <c r="K73" s="27" t="inlineStr">
         <is>
-          <t>Post-structuralisme</t>
+          <t>Phénoménologie</t>
         </is>
       </c>
       <c r="L73" s="27" t="inlineStr">
         <is>
-          <t>philosophe française spécialiste des épistémologies féministes &amp;amp; des intersections race/genre.</t>
+          <t>philosophe française au style narratif qui transforme la philo en journal existentiel.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5256,11 +5260,11 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre ; critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="173.25" customHeight="1" s="28">
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="162" customHeight="1" s="28">
       <c r="A74" s="34" t="n">
         <v>1974</v>
       </c>
@@ -5272,49 +5276,44 @@
       </c>
       <c r="D74" s="35" t="inlineStr">
         <is>
-          <t>Claire MARIN</t>
-        </is>
-      </c>
-      <c r="E74" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claire_Marin"  title=" Wikipedia"&gt;Claire MARIN&lt;/a&gt;  est une philosophe et écrivaine française professeure agrégée de philosophie en classes préparatives aux grandes écoles et membre associée de l'École normale supérieure. Normalienne, elle enseigne des auteurs comme Deleuze ou Bergson tout en menant une œuvre accessible et sensible, mêlant philosophie, littérature et expérience intime. Ses essais,  &lt;a href="https://www.youtube.com/watch?v=189nLvJBfJc" title="Claire MARIN par LCP"&gt;best-sellers récents &lt;/a&gt; comme Rupture(s) (2021) et Être à sa place (2022), explorent les épreuves existentielles sans céder au développement personnel simpliste, en s'appuyant sur un corpus philosophique et littéraire vaste. &lt;/p&gt; &lt;p&gt; Elle excelle à philosophier l'intime : ruptures amoureuses, deuil, maladie, identité plurielle, en les reliant à des penseurs comme Pascal, Hume ou le courant du care (qu'elle étudie au Séminaire international d’études sur le soin à l’ENS). La rupture y est à double visage – blessure irrémédiable mais aussi transformation radicale, plaisir de la dispersion du "moi" fragmenté. Elle rejette l'unité illusoire du sujet pour une existence mouvante, ancrée dans le vécu concret et la narration poétique. &lt;/p&gt; &lt;p&gt; Ses &lt;a href="https://www.youtube.com/watch?v=3L7BK5JN8FM" title="Claire MARIN par Librairie mollat"&gt;réflexions récentes &lt;/a&gt; insistent sur le "vivant" comme mouvement patient, empathique et sensible, contre les abstractions métaphysiques : éducation au rythme biologique, altérité bienveillante, douceur face à la souffrance. Influencée par Bergson, elle reconnecte discours philosophiques au corps et à l'émotion, critiquant le mépris académique pour le care. Philosophe "psylosophe" post-Covid, elle rend la pensée romanesque, ciselant des chapitres incisifs comme des "disserts intimistes".&lt;/p&gt; &lt;p&gt; Enseignante engagée, elle vulgarise la philosophie pour lycéens via des ouvrages thématiques (bonheur, identité, nature/culture), sans manuel rigide mais avec un "pas de côté" concret. Romancière primée (prix Jean-Bernard en 2008), elle mêle esthétique poétique et réflexion sociétale, dialoguant avec la modernité (feminine, technique). Son style narratif transforme la philo en journal existentiel, touchant un large public féminin surtout. &lt;/p&gt; &lt;audio controls title="La philosophie de Claire MARIN par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13942-19.09.2022-ITEMA_23138788-2022F29830S0262-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
+          <t>Camille RIQUIER</t>
+        </is>
+      </c>
+      <c r="E74" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Camille_Riquier"  title=" Wikipedia"&gt;Camille RIQUIER&lt;/a&gt;  est un philosophe français, spécialiste de la philosophie française du XXe siècle, agrégé de philosophie (2000) et docteur de l'université Paris-Sorbonne (thèse sur « Temps et méthode chez Bergson »). Doyen de la faculté de philosophie de l'Institut catholique de Paris, il est membre de la rédaction des revues Esprit, Philosophie et Alter, et contribue à Libération. Lauréat du prix La Bruyère de l'Académie française en 2010 pour Archéologie de Bergson, il allie rigueur académique et  &lt;a href="https://www.youtube.com/watch?v=URFYj-EZAMc" title="Camille Riquier l’audace du rêve à l’action par TEDx Talks"&gt;réflexion contemporaine &lt;/a&gt; sur foi, temps et existentialisme.&lt;/p&gt; &lt;p&gt; Spécialiste de Bergson, il en propose une "archéologie" dans son ouvrage éponyme, révélant comment le temps bergsonien (durée intuitive) dépasse la métaphysique classique pour une méthode généalogique du changement. Il souligne l'intuition comme outil anti-scientiste, reliant Bergson à Péguy et Sartre : chez Bergson, le temps n'est pas spatialisé mais vivant, fondant une  &lt;a href="https://www.youtube.com/watch?v=dAFK_Quxcms" title="Camille Riquier lire ou quand l’oeil écoute par Banquetdelagrasse"&gt;métaphysique de l'intérieur.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Dans Philosophie de Péguy ou les mémoires d'un imbécile, il  explore la pensée péguyste comme anti-intellectualisme charnel : l'"imbécile" (figure bergsonienne) incarne la mémoire résistante à l'abstraction républicaine. Péguy y réconcilie mystique et révolution, foi et raison, contre le progressisme abstrait ; il y voit une philosophie de la répétition créatrice, proche du corps et de l'histoire vécue. &lt;/p&gt; &lt;p&gt; Ses travaux récents sur Sartre (Métamorphoses de Descartes : Le secret de Sartre, Gallimard, 2022) déconstruisent l'existentialisme sartrien comme héritage cartésien transformé : liberté absolue masquant un vide ontologique. Nous ne savons plus croire diagnostique un nihilisme post-moderne où la crédulité remplace la foi raisonnée, appelant à une "foi des autres" sociale et dubitative face à la désorientation spirituelle. &lt;/p&gt; &lt;audio controls title="Camille RIQUIER, philosophe de la croyance  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-28.08.2020-ITEMA_22411316-2020C12410E0368-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
 </t>
         </is>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>fe6vbibY2CY</t>
+          <t>6IVqKs2fQWE</t>
         </is>
       </c>
       <c r="G74" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Les débuts - Claire Marin" par Librairie Mollat</t>
+          <t xml:space="preserve">"Philosophie ou spiritualités : avons-nous besoin d'un supplément d'âme ?" par Le Point</t>
         </is>
       </c>
       <c r="H74" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/cmarin-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/criquier-mini.webp</t>
         </is>
       </c>
       <c r="I74" s="36" t="n"/>
       <c r="J74" s="27" t="inlineStr">
         <is>
-          <t>ethique</t>
+          <t>metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K74" s="27" t="inlineStr">
         <is>
-          <t>Phénoménologie</t>
+          <t>Spiritualisme ; Réalisme</t>
         </is>
       </c>
       <c r="L74" s="27" t="inlineStr">
         <is>
-          <t>philosophe française au style narratif qui transforme la philo en journal existentiel.</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français spécialiste de la philosophie française du XXe siècle.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5328,56 +5327,56 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="162" customHeight="1" s="28">
+    <row r="75" ht="144.75" customHeight="1" s="28">
       <c r="A75" s="34" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B75" s="34" t="n"/>
       <c r="C75" s="34" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="D75" s="35" t="inlineStr">
         <is>
-          <t>Camille RIQUIER</t>
-        </is>
-      </c>
-      <c r="E75" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Camille_Riquier"  title=" Wikipedia"&gt;Camille RIQUIER&lt;/a&gt;  est un philosophe français, spécialiste de la philosophie française du XXe siècle, agrégé de philosophie (2000) et docteur de l'université Paris-Sorbonne (thèse sur « Temps et méthode chez Bergson »). Doyen de la faculté de philosophie de l'Institut catholique de Paris, il est membre de la rédaction des revues Esprit, Philosophie et Alter, et contribue à Libération. Lauréat du prix La Bruyère de l'Académie française en 2010 pour Archéologie de Bergson, il allie rigueur académique et  &lt;a href="https://www.youtube.com/watch?v=URFYj-EZAMc" title="Camille Riquier l’audace du rêve à l’action par TEDx Talks"&gt;réflexion contemporaine &lt;/a&gt; sur foi, temps et existentialisme.&lt;/p&gt; &lt;p&gt; Spécialiste de Bergson, il en propose une "archéologie" dans son ouvrage éponyme, révélant comment le temps bergsonien (durée intuitive) dépasse la métaphysique classique pour une méthode généalogique du changement. Il souligne l'intuition comme outil anti-scientiste, reliant Bergson à Péguy et Sartre : chez Bergson, le temps n'est pas spatialisé mais vivant, fondant une  &lt;a href="https://www.youtube.com/watch?v=dAFK_Quxcms" title="Camille Riquier lire ou quand l’oeil écoute par Banquetdelagrasse"&gt;métaphysique de l'intérieur.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Dans Philosophie de Péguy ou les mémoires d'un imbécile, il  explore la pensée péguyste comme anti-intellectualisme charnel : l'"imbécile" (figure bergsonienne) incarne la mémoire résistante à l'abstraction républicaine. Péguy y réconcilie mystique et révolution, foi et raison, contre le progressisme abstrait ; il y voit une philosophie de la répétition créatrice, proche du corps et de l'histoire vécue. &lt;/p&gt; &lt;p&gt; Ses travaux récents sur Sartre (Métamorphoses de Descartes : Le secret de Sartre, Gallimard, 2022) déconstruisent l'existentialisme sartrien comme héritage cartésien transformé : liberté absolue masquant un vide ontologique. Nous ne savons plus croire diagnostique un nihilisme post-moderne où la crédulité remplace la foi raisonnée, appelant à une "foi des autres" sociale et dubitative face à la désorientation spirituelle. &lt;/p&gt; &lt;audio controls title="Camille RIQUIER, philosophe de la croyance  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-28.08.2020-ITEMA_22411316-2020C12410E0368-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
+          <t>Vincent CITOT</t>
+        </is>
+      </c>
+      <c r="E75" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Citot"  title=" Wikipedia"&gt;Vincent CITOT&lt;/a&gt; est un philosophe  français, directeur de la revue Le Philosophoire et auteur de travaux sur la philosophie générale, les rapports entre philosophie et science, ainsi que sur la modernité et l’histoire des idées.   &lt;a href="http://www.vincentcitot.com" title="Vincent CITOT"&gt;Son parcours &lt;/a&gt; mêle aussi l’écriture et la photographie, ce qui lui donne une pratique intellectuelle assez large. &lt;/p&gt; &lt;p&gt; Sa philosophie insiste d’abord sur l’exigence de penser contre les évidences, les dogmes et le conformisme. Chez lui, philosopher n’est pas simplement enchaîner des idées, mais faire un effort critique, une vigilance de l’esprit qui commence par le doute et la mise à distance des fausses certitudes. Cette dimension critique fait de la réflexion une forme d’ascèse intellectuelle, au service de la liberté. &lt;/p&gt; &lt;p&gt; Il défend aussi une conception exigeante mais non réductrice de la philosophie : elle n’est pas une science au sens strict, mais elle dialogue avec la science tout en gardant sa propre portée de sagesse, de valeurs et de pratique existentielle. Dans cette perspective, la philosophie doit examiner ses limites, ses présupposés et ses méthodes, sans se prendre pour un savoir absolu. Il accorde également une grande place à l’universalisme, notamment dans les questions existentielles, qu’il juge plus stables et plus universelles que les cadres purement historiques ou culturels. &lt;/p&gt; &lt;p&gt; Enfin, son ouvrage Histoire mondiale de la philosophie élargit le regard au-delà du seul modèle grec : il propose de penser la philosophie comme une forme de pensée qui cherche à se justifier par divers moyens, dans plusieurs civilisations et au sein de cycles intellectuels plus vastes. Cela fait de lui  &lt;a href="https://www.les-philosophes.fr/agora/vincent-citot.html" title="Vincent CITOT par lesphiulosophes,fr"&gt;un philosophe du comparatisme &lt;/a&gt;  et de la pluralité des traditions, attentif à la modernité, à la liberté individuelle et à la diversité des formes de rationalité. &lt;/p&gt; &lt;audio controls title="Histoire mondiale de la philosophie avec Vincent CITOT  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-14.10.2022-ITEMA_23166024-2022F45096S0287-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
 </t>
         </is>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>6IVqKs2fQWE</t>
+          <t>Gt0gT_ORLYs</t>
         </is>
       </c>
       <c r="G75" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Philosophie ou spiritualités : avons-nous besoin d'un supplément d'âme ?" par Le Point</t>
+          <t>"Vincent Citot Exposition Montrond les bains" par Dominique Dozolme</t>
         </is>
       </c>
       <c r="H75" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/criquier-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/vcitot-mini.webp</t>
         </is>
       </c>
       <c r="I75" s="36" t="n"/>
       <c r="J75" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; epistemologie</t>
+          <t>epistemologie</t>
         </is>
       </c>
       <c r="K75" s="27" t="inlineStr">
         <is>
-          <t>Spiritualisme ; Réalisme</t>
+          <t>Constructivisme</t>
         </is>
       </c>
       <c r="L75" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la philosophie française du XXe siècle.</t>
+          <t>philosophe français penseur contre les évidences, les dogmes et le conformisme.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5391,56 +5390,61 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="144.75" customHeight="1" s="28">
+    <row r="76" ht="146.25" customHeight="1" s="28">
       <c r="A76" s="34" t="n">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="B76" s="34" t="n"/>
       <c r="C76" s="34" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="D76" s="35" t="inlineStr">
         <is>
-          <t>Vincent CITOT</t>
-        </is>
-      </c>
-      <c r="E76" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Citot"  title=" Wikipedia"&gt;Vincent CITOT&lt;/a&gt; est un philosophe  français, directeur de la revue Le Philosophoire et auteur de travaux sur la philosophie générale, les rapports entre philosophie et science, ainsi que sur la modernité et l’histoire des idées.   &lt;a href="http://www.vincentcitot.com" title="Vincent CITOT"&gt;Son parcours &lt;/a&gt; mêle aussi l’écriture et la photographie, ce qui lui donne une pratique intellectuelle assez large. &lt;/p&gt; &lt;p&gt; Sa philosophie insiste d’abord sur l’exigence de penser contre les évidences, les dogmes et le conformisme. Chez lui, philosopher n’est pas simplement enchaîner des idées, mais faire un effort critique, une vigilance de l’esprit qui commence par le doute et la mise à distance des fausses certitudes. Cette dimension critique fait de la réflexion une forme d’ascèse intellectuelle, au service de la liberté. &lt;/p&gt; &lt;p&gt; Il défend aussi une conception exigeante mais non réductrice de la philosophie : elle n’est pas une science au sens strict, mais elle dialogue avec la science tout en gardant sa propre portée de sagesse, de valeurs et de pratique existentielle. Dans cette perspective, la philosophie doit examiner ses limites, ses présupposés et ses méthodes, sans se prendre pour un savoir absolu. Il accorde également une grande place à l’universalisme, notamment dans les questions existentielles, qu’il juge plus stables et plus universelles que les cadres purement historiques ou culturels. &lt;/p&gt; &lt;p&gt; Enfin, son ouvrage Histoire mondiale de la philosophie élargit le regard au-delà du seul modèle grec : il propose de penser la philosophie comme une forme de pensée qui cherche à se justifier par divers moyens, dans plusieurs civilisations et au sein de cycles intellectuels plus vastes. Cela fait de lui  &lt;a href="https://www.les-philosophes.fr/agora/vincent-citot.html" title="Vincent CITOT par lesphiulosophes,fr"&gt;un philosophe du comparatisme &lt;/a&gt;  et de la pluralité des traditions, attentif à la modernité, à la liberté individuelle et à la diversité des formes de rationalité. &lt;/p&gt; &lt;audio controls title="Histoire mondiale de la philosophie avec Vincent CITOT  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-14.10.2022-ITEMA_23166024-2022F45096S0287-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
-</t>
+          <t>Séverine KODJO-GRANDVAUX</t>
+        </is>
+      </c>
+      <c r="E76" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9verine_Kodjo-Grandvaux"  title=" Wikipedia"&gt;Séverine KODJO-GRANDVAUX&lt;/a&gt; est une philosophe, journaliste, programmatrice littéraire et  &lt;a href="https://www.jeuneafrique.com/auteurs/s-kodjo-grandvaux/"  title="Ses dernières publications par jeuneafrique"&gt;éditrice française &lt;/a&gt; principalement reconnue pour ses travaux sur les philosophies africaines contemporaines et les études postcoloniales. Elle occupe une position de chercheure associée au Laboratoire des logiques contemporaines de la philosophie à l’Université Paris 8, et elle est impliquée dans des initiatives autour des humanités africaines et des échanges intellectuels entre l’Afrique et le monde francophone. Née à Besançon en 1977, elle a consacré sa thèse (2006) à l’idée de « philosophie africaine » chez Jean-Godefroy Bidima, Souleymane Bachir Diagne, Henry Odera Oruka et Kwasi Wiredu. Journaliste pour &lt;em&gt;Le Monde&lt;/em&gt;, elle dirige aussi la collection « Essais » des éditions Jimsaan. &lt;/p&gt; &lt;p&gt; En 2013, elle publie &lt;a href="https://www.youtube.com/watch?v=w8pfqdnej-o" title="African Philosophies I Lecture by philosopher Séverine Kodjo-Grandvaux par Radboud Reflects"&gt;"Philosophies africaines", &lt;/a&gt; ouvrage qui est considéré comme une référence majeure dans le domaine et qui analyse en profondeur les courants et les enjeux de la philosophie africaine contemporaine. Elle publie ensuite  &lt;a href="https://www.youtube.com/watch?v=AJAz1OmcVbI" title=""Devenir Vivants" avec Séverine Kodjo-Grandvaux. Extrait du podcast Afrotopiques par Génération Afrotopia"&gt;"Devenir vivants" &lt;/a&gt; et "Droit et colonisation"  — œuvre collective sur les rapports entre droit et colonialisme, témoignant d’un engagement dans les études postcoloniales et juridiques. &lt;/p&gt; &lt;p&gt; Ce qui la distingue dans le paysage philosophique français, c'est sa capacité à faire dialoguer les philosophies africaines avec les enjeux contemporains globaux, notamment écologiques et postcoloniaux. Elle contribue à décentrer la pensée philosophique de son eurocentrisme traditionnel tout en proposant des outils conceptuels originaux pour penser notre relation au vivant et au cosmos.&lt;/p&gt;
+   &lt;audio controls title="Philosophie Africaine par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12016-15.04.2013-ITEMA_20470144-2013C18044S0105-NET_FC_590A75DA-F57B-40F9-88DF-1D448D87542C-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>Gt0gT_ORLYs</t>
+          <t>NDaTcUJ5XmY</t>
         </is>
       </c>
       <c r="G76" s="36" t="inlineStr">
         <is>
-          <t>"Vincent Citot Exposition Montrond les bains" par Dominique Dozolme</t>
+          <t>"Séverine Kodjo-Grandvaux : De la domination à la résonance" par AFD</t>
         </is>
       </c>
       <c r="H76" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/vcitot-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/grandvaux-mini.webp</t>
         </is>
       </c>
       <c r="I76" s="36" t="n"/>
       <c r="J76" s="27" t="inlineStr">
         <is>
-          <t>epistemologie</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K76" s="27" t="inlineStr">
         <is>
-          <t>Constructivisme</t>
+          <t>Tiers-mondisme ; Pan-africanisme</t>
         </is>
       </c>
       <c r="L76" s="27" t="inlineStr">
         <is>
-          <t>philosophe français penseur contre les évidences, les dogmes et le conformisme.</t>
+          <t>philosophe française spécialiste des philosophies africaines.</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud;femme</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5450,11 +5454,11 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="146.25" customHeight="1" s="28">
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="147.75" customHeight="1" s="28">
       <c r="A77" s="34" t="n">
         <v>1977</v>
       </c>
@@ -5466,49 +5470,44 @@
       </c>
       <c r="D77" s="35" t="inlineStr">
         <is>
-          <t>Séverine KODJO-GRANDVAUX</t>
+          <t>Maxime ROVÈRE</t>
         </is>
       </c>
       <c r="E77" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9verine_Kodjo-Grandvaux"  title=" Wikipedia"&gt;Séverine KODJO-GRANDVAUX&lt;/a&gt; est une philosophe, journaliste, programmatrice littéraire et  &lt;a href="https://www.jeuneafrique.com/auteurs/s-kodjo-grandvaux/"  title="Ses dernières publications par jeuneafrique"&gt;éditrice française &lt;/a&gt; principalement reconnue pour ses travaux sur les philosophies africaines contemporaines et les études postcoloniales. Elle occupe une position de chercheure associée au Laboratoire des logiques contemporaines de la philosophie à l’Université Paris 8, et elle est impliquée dans des initiatives autour des humanités africaines et des échanges intellectuels entre l’Afrique et le monde francophone. Née à Besançon en 1977, elle a consacré sa thèse (2006) à l’idée de « philosophie africaine » chez Jean-Godefroy Bidima, Souleymane Bachir Diagne, Henry Odera Oruka et Kwasi Wiredu. Journaliste pour &lt;em&gt;Le Monde&lt;/em&gt;, elle dirige aussi la collection « Essais » des éditions Jimsaan. &lt;/p&gt; &lt;p&gt; En 2013, elle publie &lt;a href="https://www.youtube.com/watch?v=w8pfqdnej-o" title="African Philosophies I Lecture by philosopher Séverine Kodjo-Grandvaux par Radboud Reflects"&gt;"Philosophies africaines", &lt;/a&gt; ouvrage qui est considéré comme une référence majeure dans le domaine et qui analyse en profondeur les courants et les enjeux de la philosophie africaine contemporaine. Elle publie ensuite  &lt;a href="https://www.youtube.com/watch?v=AJAz1OmcVbI" title=""Devenir Vivants" avec Séverine Kodjo-Grandvaux. Extrait du podcast Afrotopiques par Génération Afrotopia"&gt;"Devenir vivants" &lt;/a&gt; et "Droit et colonisation"  — œuvre collective sur les rapports entre droit et colonialisme, témoignant d’un engagement dans les études postcoloniales et juridiques. &lt;/p&gt; &lt;p&gt; Ce qui la distingue dans le paysage philosophique français, c'est sa capacité à faire dialoguer les philosophies africaines avec les enjeux contemporains globaux, notamment écologiques et postcoloniaux. Elle contribue à décentrer la pensée philosophique de son eurocentrisme traditionnel tout en proposant des outils conceptuels originaux pour penser notre relation au vivant et au cosmos.&lt;/p&gt;
-   &lt;audio controls title="Philosophie Africaine par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12016-15.04.2013-ITEMA_20470144-2013C18044S0105-NET_FC_590A75DA-F57B-40F9-88DF-1D448D87542C-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maxime_Rov%C3%A8re"  title=" Wikipedia"&gt;Maxime ROVÈRE&lt;/a&gt;  est un philosophe, écrivain et traducteur français, spécialiste de Spinoza et créateur d’une -&lt;a href="https://www.youtube.com/watch?v=A_4XSOHakEY" title="À l'école des interactions - Maxime Rovere par Revue Esprit"&gt;"philosophie interactionnelle" &lt;/a&gt; qui met l’accent sur les relations humaines dynamiques plutôt que sur des systèmes abstraits. Chercheur associé à l’IHRIM et Fellow au Netherlands Institute for Advanced Study, il mêle recherche universitaire, traductions et écrits grand public. &lt;/p&gt; &lt;p&gt; Ses travaux sur Spinoza insistent sur des "méthodes pour exister" plutôt qu’un système rigide : la théorie des trois genres de connaissance (expérience, raison, intuition) comme outils pratiques de vérification, et une intelligence partagée plutôt que solitaire. Ses différents écrits sont "Le Clan Spinoza" paru en 2017 qui retrace la vie du philosophe et de son entourage comme invention collective de la liberté ; il a retraduit  "l’Éthique" en 2021 avec un millier de notes contextualisées. &lt;/p&gt; &lt;p&gt; Sa pensée originale, inspirée de l’interactionnisme symbolique (Goffman) et étendue à la métaphysique, voit les relations comme circulations multiples et incontrôlables d’attention, d’affects et de tensions. &lt;/p&gt; &lt;p&gt;  Ses ouvrages : &lt;a href="https://www.youtube.com/watch?v=oApu_IVn7p4"  title="Maxime Rovere - Se vouloir du bien et se faire du mal : philosophie de la dispute par librairie mollat"&gt;"Se vouloir du bien et se faire du mal" &lt;/a&gt; paru en 2021 : philosophie des disputes comme opportunités éthiques. "Que faire des cons ?"  best-seller de 2019 : guide argotique pour naviguer les conflits sans violence et &lt;a href="https://www.youtube.com/watch?v=2IGKNQB4bRo" title="Maxime Rovere : "Parler avec sa mère" "est un défi exigeant" par France Inter"&gt;"Parler avec sa mère"  &lt;/a&gt; paru en 2025 est une réflexion cosmique et pythagoricienne sur les liens familiaux. &lt;/p&gt; &lt;audio controls title="Maxime Rovere nous donne les clés de l'amour infini par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/24295-10.05.2024-ITEMA_23737128-2024F51733S0089-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
+</t>
         </is>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>NDaTcUJ5XmY</t>
+          <t>ZamutZpubdY</t>
         </is>
       </c>
       <c r="G77" s="36" t="inlineStr">
         <is>
-          <t>"Séverine Kodjo-Grandvaux : De la domination à la résonance" par AFD</t>
+          <t>"Que faire des cons ? | Maxime Rovere | TEDxTours" par TEDx Talks</t>
         </is>
       </c>
       <c r="H77" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/grandvaux-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/rovere-mini.webp</t>
         </is>
       </c>
       <c r="I77" s="36" t="n"/>
       <c r="J77" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>ethique ; epistemologie</t>
         </is>
       </c>
       <c r="K77" s="27" t="inlineStr">
         <is>
-          <t>Tiers-mondisme ; Pan-africanisme</t>
+          <t>Rationalisme</t>
         </is>
       </c>
       <c r="L77" s="27" t="inlineStr">
         <is>
-          <t>philosophe française spécialiste des philosophies africaines.</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud;femme</t>
+          <t>philosophe français spécialiste de Spinoza et créateur d'une "philosophie interactionnelle".</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5518,124 +5517,127 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t xml:space="preserve">decolonial</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="147.75" customHeight="1" s="28">
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="180.55" customHeight="1" s="28">
       <c r="A78" s="34" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B78" s="34" t="n"/>
       <c r="C78" s="34" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="D78" s="35" t="inlineStr">
         <is>
-          <t>Maxime ROVÈRE</t>
-        </is>
-      </c>
-      <c r="E78" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maxime_Rov%C3%A8re"  title=" Wikipedia"&gt;Maxime ROVÈRE&lt;/a&gt;  est un philosophe, écrivain et traducteur français, spécialiste de Spinoza et créateur d’une -&lt;a href="https://www.youtube.com/watch?v=A_4XSOHakEY" title="À l'école des interactions - Maxime Rovere par Revue Esprit"&gt;"philosophie interactionnelle" &lt;/a&gt; qui met l’accent sur les relations humaines dynamiques plutôt que sur des systèmes abstraits. Chercheur associé à l’IHRIM et Fellow au Netherlands Institute for Advanced Study, il mêle recherche universitaire, traductions et écrits grand public. &lt;/p&gt; &lt;p&gt; Ses travaux sur Spinoza insistent sur des "méthodes pour exister" plutôt qu’un système rigide : la théorie des trois genres de connaissance (expérience, raison, intuition) comme outils pratiques de vérification, et une intelligence partagée plutôt que solitaire. Ses différents écrits sont "Le Clan Spinoza" paru en 2017 qui retrace la vie du philosophe et de son entourage comme invention collective de la liberté ; il a retraduit  "l’Éthique" en 2021 avec un millier de notes contextualisées. &lt;/p&gt; &lt;p&gt; Sa pensée originale, inspirée de l’interactionnisme symbolique (Goffman) et étendue à la métaphysique, voit les relations comme circulations multiples et incontrôlables d’attention, d’affects et de tensions. &lt;/p&gt; &lt;p&gt;  Ses ouvrages : &lt;a href="https://www.youtube.com/watch?v=oApu_IVn7p4"  title="Maxime Rovere - Se vouloir du bien et se faire du mal : philosophie de la dispute par librairie mollat"&gt;"Se vouloir du bien et se faire du mal" &lt;/a&gt; paru en 2021 : philosophie des disputes comme opportunités éthiques. "Que faire des cons ?"  best-seller de 2019 : guide argotique pour naviguer les conflits sans violence et &lt;a href="https://www.youtube.com/watch?v=2IGKNQB4bRo" title="Maxime Rovere : "Parler avec sa mère" "est un défi exigeant" par France Inter"&gt;"Parler avec sa mère"  &lt;/a&gt; paru en 2025 est une réflexion cosmique et pythagoricienne sur les liens familiaux. &lt;/p&gt; &lt;audio controls title="Maxime Rovere nous donne les clés de l'amour infini par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/24295-10.05.2024-ITEMA_23737128-2024F51733S0089-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
-</t>
-        </is>
-      </c>
-      <c r="F78" s="34" t="inlineStr">
-        <is>
-          <t>ZamutZpubdY</t>
-        </is>
-      </c>
-      <c r="G78" s="36" t="inlineStr">
-        <is>
-          <t>"Que faire des cons ? | Maxime Rovere | TEDxTours" par TEDx Talks</t>
-        </is>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/rovere-mini.webp</t>
-        </is>
-      </c>
-      <c r="I78" s="36" t="n"/>
-      <c r="J78" s="27" t="inlineStr">
-        <is>
-          <t>ethique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K78" s="27" t="inlineStr">
-        <is>
-          <t>Rationalisme</t>
-        </is>
-      </c>
-      <c r="L78" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français spécialiste de Spinoza et créateur d'une "philosophie interactionnelle".</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="180.55" customHeight="1" s="28">
-      <c r="A79" s="34" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B79" s="34" t="n"/>
-      <c r="C79" s="34" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="D79" s="35" t="inlineStr">
-        <is>
           <t>Jean-Baptiste JEANGENE VILMER</t>
         </is>
       </c>
-      <c r="E79" s="37" t="inlineStr">
+      <c r="E78" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Baptiste_Jeang%C3%A8ne_Vilmer"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean-Baptiste JEANGENE VILMER&lt;/a&gt;  est un philosophe, politologue et juriste français spécialiste de l’éthique de la guerre, du droit international et des relations internationales, et également diplomate (ambassadeur de France au Vanuatu depuis 2022). Il est formé dans trois disciplines : philosophie (licence, master, doctorat), droit (licence, LLM, postdoctorat) et science politique (doctorat). &lt;/p&gt; &lt;p&gt; Sa thèse porte sur "l’intervention militaire justifiée par des raisons humanitaires", à la croisée de philosophie politique, droit international et théorie des relations internationales. Il défend en théorie des relations internationales un "réalisme libéral" inspiré de Raymond Aron, Stanley Hoffmann et Pierre Hassner : reconnaissance du tragique et des &lt;a href="https://www.youtube.com/watch?v=4EECHNFvt4Q"  title=" J-B. Jeangène Vilmer - Synthèse par Institut Guerre et Paix"&gt;rapports de force, &lt;/a&gt;  mais attachée au droit international, aux droits humains et aux institutions. &lt;/p&gt; &lt;p&gt; Il se situe à l’intersection de philosophie morale, droit international et stratégie : penser les guerres et interventions non seulement en termes juridiques ou militaires, mais surtout en termes de responsabilité morale (tuer, laisser mourir, protéger). Son &lt;a href="https://www.jbjv.com/IMG/pdf/JB_Jeangene_Vilmer_2013_-_Pour_un_realisme_liberal_en_relations_internationales.pdf"  title="Pour un réalisme libéral en relations internationales par jbjv"&gt;"réalisme libéral" &lt;/a&gt; refuse à la fois le cynisme réaliste pur et l’idéalisme naïf, il cherche des critères prudents mais exigeants pour juger les interventions, la justice pénale, ou la responsabilité des États. &lt;/p&gt; &lt;p&gt; Il insiste sur les dilemmes : parfois, intervenir violemment peut sauver des vies, mais peut aussi aggraver le conflit ; parfois, poursuivre les criminels peut fragiliser la paix. Sa pensée explore ces tensions plutôt que de proposer des solutions simplistes. &lt;/p&gt; 
   &lt;audio controls title="Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
+      <c r="F78" s="34" t="inlineStr">
+        <is>
+          <t>v_czW-Qh8sg</t>
+        </is>
+      </c>
+      <c r="G78" s="36" t="inlineStr">
+        <is>
+          <t>"Le changement climatique au Vanuatu et l'action de la France (Jean-Baptiste Jeangène Vilmer)" par ambassade fr</t>
+        </is>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/vilmer-mini.webp</t>
+        </is>
+      </c>
+      <c r="I78" s="36" t="n"/>
+      <c r="J78" s="27" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>Analytique</t>
+        </is>
+      </c>
+      <c r="L78" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français spécialiste de l'éthique de la guerre &amp;amp; du droit international.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="283.55" customHeight="1" s="28">
+      <c r="A79" s="34" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B79" s="34" t="n"/>
+      <c r="C79" s="34" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D79" s="27" t="inlineStr">
+        <is>
+          <t>Nadia Yala KISUKIDI</t>
+        </is>
+      </c>
+      <c r="E79" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nadia_Yala_Kisukidi"  title=" Wikipedia"&gt;Nadia Yala KISUKIDI&lt;/a&gt;  est une philosophe et écrivaine franco-congolaise née à Bruxelles, professeure à l’université Paris 8, connue pour ses travaux sur Bergson, la philosophie Africaine, le féminisme noir et les effets coloniaux dans la pensée occidentale. Sa philosophie part d’un constat simple : les grands corpus philosophiques ont longtemps été enseignés comme s’ils étaient universels, alors qu’ils reflètent souvent une histoire située, européenne et coloniale. &lt;/p&gt; &lt;p&gt; Elle est d’abord reconnue comme spécialiste de Bergson. Dans son livre Bergson ou l’humanité créatrice, elle relit Bergson à partir de la création, du mouvement et de l’invention de soi, en montrant que la philosophie peut penser la vie comme puissance de transformation plutôt que comme identité figée. &lt;/p&gt; &lt;p&gt; Un autre axe central de son travail est la critique de la « bibliothèque coloniale » : elle montre comment l’idée d’Afrique et l’idée de « Noir » ont été fabriquées dans &lt;a href="https://www.youtube.com/watch?v=smUx6yKHTF4"  title="NY Kisikidi une nouvelle pensée des mondes noirs par RFI"&gt;des cadres intellectuels &lt;/a&gt;  marqués par la domination européenne. Son approche ne consiste pas seulement à dénoncer ces héritages, mais à déplacer le centre du regard pour faire place à des pensées africaines, diasporiques et non occidentales. &lt;/p&gt; &lt;p&gt; Elle développe aussi une réflexion féministe et politique, notamment avec Djamila Ribeiro dans Dialogue transatlantique, où elle met en relation les expériences des femmes noires, les diasporas africaines et les formes contemporaines de résistance. Chez elle, le féminisme n’est pas séparé de la question raciale : il sert à &lt;a href="https://www.youtube.com/watch?v=ECngo81h5v0"  title="NY Kisikidi défendre les vies humaines par Campus AFD par RFI"&gt;penser des solidarités, &lt;/a&gt; des voix minorées et des alliances intellectuelles entre continents. &lt;/p&gt; &lt;p&gt; Sa philosophie vise une forme d’universel décentré : non pas un universel abstrait imposé d’en haut, mais un universel construit à partir des conflits, des pluralités et des expériences historiques concrètes. En ce sens, elle propose une philosophie de la relation, de la circulation et de la restitution, où l’on comprend le monde en écoutant les marges autant que les centres. &lt;/p&gt;  &lt;audio controls title="Nadia Yala Kisukidi le mouvement anti raciste par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-13.06.2020-ITEMA_22360573-3-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
+</t>
+        </is>
+      </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>v_czW-Qh8sg</t>
+          <t>C6RlugxFljU</t>
         </is>
       </c>
       <c r="G79" s="36" t="inlineStr">
         <is>
-          <t>"Le changement climatique au Vanuatu et l'action de la France (Jean-Baptiste Jeangène Vilmer)" par ambassade fr</t>
-        </is>
-      </c>
-      <c r="H79" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/vilmer-mini.webp</t>
+          <t>Nadia Yala Kisukidi décolonisation et philosophie par TV5 Monde</t>
+        </is>
+      </c>
+      <c r="H79" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/nykisukidi-mini.webp</t>
         </is>
       </c>
       <c r="I79" s="36" t="n"/>
       <c r="J79" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K79" s="27" t="inlineStr">
         <is>
-          <t>Analytique</t>
+          <t>Tiers-mondisme</t>
         </is>
       </c>
       <c r="L79" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de l'éthique de la guerre &amp;amp; du droit international.</t>
+          <t>philosophe française spécialiste de la pensée de Bergson et des études postcoloniales.</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud;femme</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5645,63 +5647,62 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="283.55" customHeight="1" s="28">
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="395.5" customHeight="1" s="28">
       <c r="A80" s="34" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B80" s="34" t="n"/>
       <c r="C80" s="34" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="D80" s="27" t="inlineStr">
         <is>
-          <t>Nadia Yala KISUKIDI</t>
-        </is>
-      </c>
-      <c r="E80" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nadia_Yala_Kisukidi"  title=" Wikipedia"&gt;Nadia Yala KISUKIDI&lt;/a&gt;  est une philosophe et écrivaine franco-congolaise née à Bruxelles, professeure à l’université Paris 8, connue pour ses travaux sur Bergson, la philosophie Africaine, le féminisme noir et les effets coloniaux dans la pensée occidentale. Sa philosophie part d’un constat simple : les grands corpus philosophiques ont longtemps été enseignés comme s’ils étaient universels, alors qu’ils reflètent souvent une histoire située, européenne et coloniale. &lt;/p&gt; &lt;p&gt; Elle est d’abord reconnue comme spécialiste de Bergson. Dans son livre Bergson ou l’humanité créatrice, elle relit Bergson à partir de la création, du mouvement et de l’invention de soi, en montrant que la philosophie peut penser la vie comme puissance de transformation plutôt que comme identité figée. &lt;/p&gt; &lt;p&gt; Un autre axe central de son travail est la critique de la « bibliothèque coloniale » : elle montre comment l’idée d’Afrique et l’idée de « Noir » ont été fabriquées dans &lt;a href="https://www.youtube.com/watch?v=smUx6yKHTF4"  title="NY Kisikidi une nouvelle pensée des mondes noirs par RFI"&gt;des cadres intellectuels &lt;/a&gt;  marqués par la domination européenne. Son approche ne consiste pas seulement à dénoncer ces héritages, mais à déplacer le centre du regard pour faire place à des pensées africaines, diasporiques et non occidentales. &lt;/p&gt; &lt;p&gt; Elle développe aussi une réflexion féministe et politique, notamment avec Djamila Ribeiro dans Dialogue transatlantique, où elle met en relation les expériences des femmes noires, les diasporas africaines et les formes contemporaines de résistance. Chez elle, le féminisme n’est pas séparé de la question raciale : il sert à &lt;a href="https://www.youtube.com/watch?v=ECngo81h5v0"  title="NY Kisikidi défendre les vies humaines par Campus AFD par RFI"&gt;penser des solidarités, &lt;/a&gt; des voix minorées et des alliances intellectuelles entre continents. &lt;/p&gt; &lt;p&gt; Sa philosophie vise une forme d’universel décentré : non pas un universel abstrait imposé d’en haut, mais un universel construit à partir des conflits, des pluralités et des expériences historiques concrètes. En ce sens, elle propose une philosophie de la relation, de la circulation et de la restitution, où l’on comprend le monde en écoutant les marges autant que les centres. &lt;/p&gt;  &lt;audio controls title="Nadia Yala Kisukidi le mouvement anti raciste par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-13.06.2020-ITEMA_22360573-3-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
-</t>
+          <t>Julia DE-FUNÈS</t>
+        </is>
+      </c>
+      <c r="E80" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julia_de_Fun%C3%A8s"  title=" Wikipedia"&gt;Julia DE-FUNÈS&lt;/a&gt; est une philosophe, essayiste et conférencière française, également spécialiste des ressources humaines et du monde de l’entreprise. Après avoir travaillé plusieurs années comme chasseuse de têtes, elle a créé en 2010 un cabinet de conseil mobilisant la philosophie dans les organisations. Elle a ensuite soutenu en 2017 une thèse consacrée au passage de l’identité personnelle à l’authenticité, à travers les notions de représentation et de mimétisme. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=OaDbpC3azdQ"  title="julia de Funès, philosophe par 21 News"&gt; Sa démarche consiste &lt;/a&gt;  à faire sortir la philosophie du cadre purement universitaire pour la confronter aux situations ordinaires : travail, management, bonheur, relations professionnelles ou développement personnel. Elle considère la philosophie comme un exercice de mise à distance, destiné à interroger les évidences et à examiner le sens réel des mots que nous employons. Dans cette perspective, philosopher revient à ne pas accepter mécaniquement les discours dominants, les slogans ou les habitudes de pensée. &lt;/p&gt; &lt;p&gt; Une de ses principales critiques vise l’entreprise contemporaine et la multiplication des procédures, des indicateurs et des discours managériaux. Dans Socrate au pays des process ou La Vie de bureau, elle dénonce ce qu’elle perçoit comme une perte de sens : les salariés peuvent être soumis à des injonctions contradictoires et à un langage abstrait qui transforme parfois l’être humain en simple fonction. Elle oppose à cette logique la nécessité de retrouver du jugement, de l’autonomie et une réflexion véritable sur les finalités du travail. &lt;/p&gt; &lt;p&gt; Elle critique également le développement personnel lorsqu’il promet le bonheur, la réussite ou la confiance en soi au moyen de recettes standardisées. Dans &lt;a href="https://www.youtube.com/watch?v=dV5r46P6yUU"  title="le développement personnel est la plus grosse arnaque par Clique Tv"&gt;Le Développement (im)personnel&lt;/a&gt;, elle soutient que certaines formes de psychologie positive peuvent transformer des problèmes sociaux ou professionnels en responsabilités purement individuelles : si l’on échoue, ce serait parce que l’on n’est pas assez motivé ou « positif ». Sa critique ne consiste donc pas à refuser toute recherche de bien-être, mais à dénoncer les méthodes qui imposent une conformité sous l’apparence de l’épanouissement. &lt;/p&gt; &lt;p&gt; Sa philosophie peut être caractérisée par trois exigences : l’esprit critique, le discernement et l’authenticité. Elle invite chacun à se méfier des formules toutes faites, à ne pas confondre adaptation sociale et vérité personnelle, et à rechercher un rapport plus lucide à soi-même et aux autres. Son originalité tient ainsi à la rencontre entre la tradition philosophique — notamment Socrate, Aristote ou Kant — et les problèmes très concrets de la vie professionnelle et sociale. &lt;/p&gt;  &lt;audio controls title="Un nouvel ordre identitaire avec Julia Dez Funès par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.11.2022-ITEMA_23186791-2022F30378S0309-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>C6RlugxFljU</t>
+          <t xml:space="preserve">IbHSzVzGVIM</t>
         </is>
       </c>
       <c r="G80" s="36" t="inlineStr">
         <is>
-          <t>Nadia Yala Kisukidi décolonisation et philosophie par TV5 Monde</t>
+          <t xml:space="preserve">"Julia de Funès, libre de douter" par Public Sénat</t>
         </is>
       </c>
       <c r="H80" s="37" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/nykisukidi-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/jdfunes-mini.webp</t>
         </is>
       </c>
       <c r="I80" s="36" t="n"/>
       <c r="J80" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>ethique</t>
         </is>
       </c>
       <c r="K80" s="27" t="inlineStr">
         <is>
-          <t>Tiers-mondisme</t>
-        </is>
-      </c>
-      <c r="L80" s="27" t="inlineStr">
-        <is>
-          <t>philosophe française spécialiste de la pensée de Bergson et des études postcoloniales.</t>
+          <t>Humanisme</t>
+        </is>
+      </c>
+      <c r="L80" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> philosophe, essayiste et conférencière française, spécialiste des ressources humaines et du monde de l’entreprise.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud;femme</t>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5711,190 +5712,187 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t xml:space="preserve">decolonial</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="395.5" customHeight="1" s="28">
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="145.5" customHeight="1" s="28">
       <c r="A81" s="34" t="n">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B81" s="34" t="n"/>
-      <c r="C81" s="34" t="n">
-        <v>1979</v>
-      </c>
-      <c r="D81" s="27" t="inlineStr">
-        <is>
-          <t>Julia DE-FUNÈS</t>
-        </is>
-      </c>
-      <c r="E81" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julia_de_Fun%C3%A8s"  title=" Wikipedia"&gt;Julia DE-FUNÈS&lt;/a&gt; est une philosophe, essayiste et conférencière française, également spécialiste des ressources humaines et du monde de l’entreprise. Après avoir travaillé plusieurs années comme chasseuse de têtes, elle a créé en 2010 un cabinet de conseil mobilisant la philosophie dans les organisations. Elle a ensuite soutenu en 2017 une thèse consacrée au passage de l’identité personnelle à l’authenticité, à travers les notions de représentation et de mimétisme. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=OaDbpC3azdQ"  title="julia de Funès, philosophe par 21 News"&gt; Sa démarche consiste &lt;/a&gt;  à faire sortir la philosophie du cadre purement universitaire pour la confronter aux situations ordinaires : travail, management, bonheur, relations professionnelles ou développement personnel. Elle considère la philosophie comme un exercice de mise à distance, destiné à interroger les évidences et à examiner le sens réel des mots que nous employons. Dans cette perspective, philosopher revient à ne pas accepter mécaniquement les discours dominants, les slogans ou les habitudes de pensée. &lt;/p&gt; &lt;p&gt; Une de ses principales critiques vise l’entreprise contemporaine et la multiplication des procédures, des indicateurs et des discours managériaux. Dans Socrate au pays des process ou La Vie de bureau, elle dénonce ce qu’elle perçoit comme une perte de sens : les salariés peuvent être soumis à des injonctions contradictoires et à un langage abstrait qui transforme parfois l’être humain en simple fonction. Elle oppose à cette logique la nécessité de retrouver du jugement, de l’autonomie et une réflexion véritable sur les finalités du travail. &lt;/p&gt; &lt;p&gt; Elle critique également le développement personnel lorsqu’il promet le bonheur, la réussite ou la confiance en soi au moyen de recettes standardisées. Dans &lt;a href="https://www.youtube.com/watch?v=dV5r46P6yUU"  title="le développement personnel est la plus grosse arnaque par Clique Tv"&gt;Le Développement (im)personnel&lt;/a&gt;, elle soutient que certaines formes de psychologie positive peuvent transformer des problèmes sociaux ou professionnels en responsabilités purement individuelles : si l’on échoue, ce serait parce que l’on n’est pas assez motivé ou « positif ». Sa critique ne consiste donc pas à refuser toute recherche de bien-être, mais à dénoncer les méthodes qui imposent une conformité sous l’apparence de l’épanouissement. &lt;/p&gt; &lt;p&gt; Sa philosophie peut être caractérisée par trois exigences : l’esprit critique, le discernement et l’authenticité. Elle invite chacun à se méfier des formules toutes faites, à ne pas confondre adaptation sociale et vérité personnelle, et à rechercher un rapport plus lucide à soi-même et aux autres. Son originalité tient ainsi à la rencontre entre la tradition philosophique — notamment Socrate, Aristote ou Kant — et les problèmes très concrets de la vie professionnelle et sociale. &lt;/p&gt;  &lt;audio controls title="Un nouvel ordre identitaire avec Julia Dez Funès par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.11.2022-ITEMA_23186791-2022F30378S0309-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
-        </is>
-      </c>
-      <c r="F81" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IbHSzVzGVIM</t>
-        </is>
-      </c>
-      <c r="G81" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Julia de Funès, libre de douter" par Public Sénat</t>
-        </is>
-      </c>
-      <c r="H81" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/jdfunes-mini.webp</t>
-        </is>
-      </c>
-      <c r="I81" s="36" t="n"/>
-      <c r="J81" s="27" t="inlineStr">
-        <is>
-          <t>ethique</t>
-        </is>
-      </c>
-      <c r="K81" s="27" t="inlineStr">
-        <is>
-          <t>Humanisme</t>
-        </is>
-      </c>
-      <c r="L81" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> philosophe, essayiste et conférencière française, spécialiste des ressources humaines et du monde de l’entreprise.</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="145.5" customHeight="1" s="28">
-      <c r="A82" s="34" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B82" s="34" t="n"/>
-      <c r="C82" s="34" t="inlineStr">
+      <c r="C81" s="34" t="inlineStr">
         <is>
           <t>1981</t>
         </is>
       </c>
-      <c r="D82" s="35" t="inlineStr">
+      <c r="D81" s="35" t="inlineStr">
         <is>
           <t>Tristan GARCIA</t>
         </is>
       </c>
-      <c r="E82" s="37" t="inlineStr">
+      <c r="E81" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tristan_Garcia" title=" Wikipedia"&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. Ancien élève de l’École normale supérieure, il enseigne la philosophie à l’université Jean-Moulin-Lyon-3. &lt;/p&gt; &lt;p&gt; Son œuvre majeure "Forme et objet. Un traité des choses" paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie "plate" qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans "Nous" ou "La Vie intense" paru en 2016, il explore l’appartenance à des collectifs variables "nous humains", "nous animaux" et critique l’obsession moderne pour  &lt;a href="https://www.youtube.com/watch?v=JTLVzryyyEg" title="Tristan Garcia, INTENSITÉ par abc penser"&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. Son roman &lt;em&gt;7&lt;/em&gt; reçoit en 2016 le prix du Livre Inter. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (&lt;em&gt;La Meilleure Part des hommes&lt;/em&gt;, sur les années sida, prix de Flore 2008) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href="https://www.youtube.com/watch?v=K_wxi5xTYz8" title="Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace"&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; 
    &lt;audio controls title="Tristan Garcia, "La vie intense : une obsession moderne" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
  </t>
         </is>
       </c>
-      <c r="F82" s="34" t="inlineStr">
+      <c r="F81" s="34" t="inlineStr">
         <is>
           <t>CNhfmBxUwdc</t>
         </is>
       </c>
-      <c r="G82" s="36" t="inlineStr">
+      <c r="G81" s="36" t="inlineStr">
         <is>
           <t>"Ecriture inclusive : cinq minutes qui élèvent le débat, par Tristan Garcia" par Le nouvel Obs</t>
         </is>
       </c>
-      <c r="H82" s="36" t="inlineStr">
+      <c r="H81" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/garcia-mini.webp</t>
         </is>
       </c>
-      <c r="I82" s="36" t="n"/>
-      <c r="J82" s="27" t="inlineStr">
+      <c r="I81" s="36" t="n"/>
+      <c r="J81" s="27" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="K82" s="27" t="inlineStr">
+      <c r="K81" s="27" t="inlineStr">
         <is>
           <t>Nouveau réalisme</t>
         </is>
       </c>
-      <c r="L82" s="27" t="inlineStr">
+      <c r="L81" s="27" t="inlineStr">
         <is>
           <t>philosophe &amp;amp; romancier français figure montante d'une métaphysique contemporaine ambitieuse.</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t xml:space="preserve">reel</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="202.5" customHeight="1" s="28">
-      <c r="A83" s="34" t="n">
+    <row r="82" ht="202.5" customHeight="1" s="28">
+      <c r="A82" s="34" t="n">
         <v>1982</v>
       </c>
-      <c r="B83" s="34" t="n"/>
-      <c r="C83" s="34" t="inlineStr">
+      <c r="B82" s="34" t="n"/>
+      <c r="C82" s="34" t="inlineStr">
         <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="D83" s="35" t="inlineStr">
+      <c r="D82" s="35" t="inlineStr">
         <is>
           <t>Gaspard KOENIG</t>
         </is>
       </c>
-      <c r="E83" s="36" t="inlineStr">
+      <c r="E82" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gaspard_Koenig" title=" Wikipedia"&gt;Gaspard KOENIG&lt;/a&gt;  est un philosophe français connu pour défendre un libéralisme classique moderne axé sur la liberté individuelle et la réduction des normes administratives. Il étudie initialement Gilles Deleuze avant de découvrir le libéralisme lors d'un séjour à l'université Columbia à New York. Il enseigne comme ATER à Lille-III et travaille comme plume pour Christine Lagarde au ministère de l'Économie, puis à la BERD à Londres. &lt;/p&gt; &lt;p&gt; Fondateur en 2013 du &lt;a href="https://www.youtube.com/watch?v=XmM1deHK-Eo"  title="Génération libre : le think tank, "start-up intellectuelle" par BFM Business"&gt;"think tank Génération Libre", &lt;/a&gt; classé parmi les meilleurs think tanks européens, il en est président et promeut des idées comme le revenu universel (LIBER), la légalisation du cannabis, la propriété des données personnelles et la subsidiarité ascendante. En 2021, il lance le mouvement politique Simple pour  &lt;a href="https://www.youtube.com/watch?v=r6p0dZlUoLQ"  title="Gaspard Koenig : Simplifions radicalement notre administration ! par Contribuables Associés"&gt;diviser par cent les normes &lt;/a&gt; réglementaires ; candidat à la présidentielle 2022, il récolte 107 parrainages. Il se présente aussi aux législatives partielles en 2018. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.gaspardkoenig.com/" title="gaspard koenig - site personnel"&gt;Auteur  d'une quinzaine d'essais &lt;/a&gt; et romans, dont Humus (finaliste Goncourt 2023, prix Interallié), Agrophilosophie (2024) et Time to Philo, il redéfinit la liberté comme "pouvoir sur soi", inspiré par Montaigne, les stoïciens et David Graeber. Ses réflexions touchent l'IA, l'agroécologie, l'éthique et l'économie. Dans &lt;em&gt;La Fin de l’individu&lt;/em&gt; (2019) il s’inquiète de voir les algorithmes décider à notre place et réduire notre capacité de choisir. Avec &lt;em&gt;Humus&lt;/em&gt;, roman sur deux jeunes agronomes et la vie des vers de terre, puis &lt;em&gt;Agrophilosophie&lt;/em&gt;, il s’intéresse aux sols et à l’agriculture, et cherche à concilier la liberté individuelle avec le respect des équilibres naturels. &lt;/p&gt; 
   &lt;audio controls title="Gaspard Koenig, un philosophe en liberté par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-30.09.2023-ITEMA_23504378-2023C49326S0273-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
+      <c r="F82" s="34" t="inlineStr">
+        <is>
+          <t>4BW1Ch1Dw6I</t>
+        </is>
+      </c>
+      <c r="G82" s="36" t="inlineStr">
+        <is>
+          <t>Gaspard Koenig : "Les panthéonisations sont une façon pour l'État de nationaliser les talents" par France Inter</t>
+        </is>
+      </c>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/koenig-mini.webp</t>
+        </is>
+      </c>
+      <c r="I82" s="36" t="n"/>
+      <c r="J82" s="27" t="inlineStr">
+        <is>
+          <t>politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>Libéralisme</t>
+        </is>
+      </c>
+      <c r="L82" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français défenseur du libéralisme classique moderne axé sur la liberté individuelle.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="124.5" customHeight="1" s="28">
+      <c r="A83" s="34" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B83" s="34" t="n"/>
+      <c r="C83" s="34" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="D83" s="35" t="inlineStr">
+        <is>
+          <t>Pierre CHARBONNIER</t>
+        </is>
+      </c>
+      <c r="E83" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Charbonnier_(philosophe)"  title=" Wikipedia"&gt;Pierre CHARBONNIER&lt;/a&gt; est un philosophe français spécialiste de philosophie politique et de philosophie de l'environnement et de l'écologie. &lt;a href="https://laviedesidees.fr/_Charbonnier-Pierre_" title="ÉCOPO - Pierre Charbonnier par College de France"&gt;Ses travaux&lt;/a&gt; portent sur l'histoire des sciences sociales et de la pensée politique, en particulier sur la manière dont elles abordent la relation entre nature et société et s'intéresse aux systèmes de pensée et d'encadrement du milieu naturel, aux crises politiques et écologiques, et à la place de l'écologie dans le processus de démocratisation. &lt;/p&gt; &lt;p&gt; Son livre &lt;a href="https://www.youtube.com/watch?v=6s54KzHUmRU" title="ÉCOPO - Pierre Charbonnier, Abondance et liberté par Game Of Hearth"&gt;"Abondance et liberté"&lt;/a&gt; : Une histoire environnementale des idées politiques a rencontré un certain succès médiatique et explore l'histoire des idées politiques à travers le prisme des enjeux environnementaux. Il y analyse comment nos conceptions de la liberté et de l'abondance sont historiquement liées à notre rapport à la nature. &lt;/p&gt; &lt;p&gt; Plus récent, son ouvrage   &lt;a href="https://www.youtube.com/watch?v=HslDCTZNq2M"  title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt;"Vers l'écologie de guerre"&lt;/a&gt; : Une histoire environnementale de la paix, il propose une relecture de l'histoire des relations internationales et des conflits à travers le prisme des enjeux écologiques. Chercheur au CNRS, rattaché à Sciences Po, il montre que la démocratie libérale moderne s’est construite sur une promesse d’abondance rendue possible par l’exploitation de la terre, puis du charbon et du pétrole. La crise climatique oblige donc à repenser ce que nous entendons par liberté, sans renoncer à l’idéal d’émancipation. Il invite ainsi à faire de l’écologie une question centrale de la philosophie politique. &lt;/p&gt;  &lt;audio controls title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25343-29.08.2024-ITEMA_23842702-2024C53458S0242-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
+      </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>4BW1Ch1Dw6I</t>
+          <t>GGLZjIzYDnE</t>
         </is>
       </c>
       <c r="G83" s="36" t="inlineStr">
         <is>
-          <t>Gaspard Koenig : "Les panthéonisations sont une façon pour l'État de nationaliser les talents" par France Inter</t>
+          <t>"Le philosophe Pierre Charbonnier: "Beaucoup de choses qui nous semblaient aller de soi ne vont plus"" par France Inter</t>
         </is>
       </c>
       <c r="H83" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/koenig-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/charbonnier-mini.webp</t>
         </is>
       </c>
       <c r="I83" s="36" t="n"/>
       <c r="J83" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>ethique ; politique</t>
         </is>
       </c>
       <c r="K83" s="27" t="inlineStr">
         <is>
-          <t>Libéralisme</t>
+          <t>Ecologisme</t>
         </is>
       </c>
       <c r="L83" s="27" t="inlineStr">
         <is>
-          <t>philosophe français défenseur du libéralisme classique moderne axé sur la liberté individuelle.</t>
+          <t>philosophe français principalement orienté sur l'environnement.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -5904,11 +5902,11 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="124.5" customHeight="1" s="28">
+          <t xml:space="preserve">ecologie ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="167.25" customHeight="1" s="28">
       <c r="A84" s="34" t="n">
         <v>1983</v>
       </c>
@@ -5920,33 +5918,34 @@
       </c>
       <c r="D84" s="35" t="inlineStr">
         <is>
-          <t>Pierre CHARBONNIER</t>
-        </is>
-      </c>
-      <c r="E84" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Charbonnier_(philosophe)"  title=" Wikipedia"&gt;Pierre CHARBONNIER&lt;/a&gt; est un philosophe français spécialiste de philosophie politique et de philosophie de l'environnement et de l'écologie. &lt;a href="https://laviedesidees.fr/_Charbonnier-Pierre_" title="ÉCOPO - Pierre Charbonnier par College de France"&gt;Ses travaux&lt;/a&gt; portent sur l'histoire des sciences sociales et de la pensée politique, en particulier sur la manière dont elles abordent la relation entre nature et société et s'intéresse aux systèmes de pensée et d'encadrement du milieu naturel, aux crises politiques et écologiques, et à la place de l'écologie dans le processus de démocratisation. &lt;/p&gt; &lt;p&gt; Son livre &lt;a href="https://www.youtube.com/watch?v=6s54KzHUmRU" title="ÉCOPO - Pierre Charbonnier, Abondance et liberté par Game Of Hearth"&gt;"Abondance et liberté"&lt;/a&gt; : Une histoire environnementale des idées politiques a rencontré un certain succès médiatique et explore l'histoire des idées politiques à travers le prisme des enjeux environnementaux. Il y analyse comment nos conceptions de la liberté et de l'abondance sont historiquement liées à notre rapport à la nature. &lt;/p&gt; &lt;p&gt; Plus récent, son ouvrage   &lt;a href="https://www.youtube.com/watch?v=HslDCTZNq2M"  title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt;"Vers l'écologie de guerre"&lt;/a&gt; : Une histoire environnementale de la paix, il propose une relecture de l'histoire des relations internationales et des conflits à travers le prisme des enjeux écologiques. Chercheur au CNRS, rattaché à Sciences Po, il montre que la démocratie libérale moderne s’est construite sur une promesse d’abondance rendue possible par l’exploitation de la terre, puis du charbon et du pétrole. La crise climatique oblige donc à repenser ce que nous entendons par liberté, sans renoncer à l’idéal d’émancipation. Il invite ainsi à faire de l’écologie une question centrale de la philosophie politique. &lt;/p&gt;  &lt;audio controls title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25343-29.08.2024-ITEMA_23842702-2024C53458S0242-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t>Baptiste MORIZOT</t>
+        </is>
+      </c>
+      <c r="E84" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baptiste_Morizot"  title=" Wikipedia"&gt;Baptiste MORIZOT&lt;/a&gt;  est un philosophe français,  maître de conférences à l'université d'Aix-Marseille, dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle. Son approche se distingue par une pratique de terrain ancrée dans l'expérience, notamment le pistage des grands prédateurs comme les loups, ce qui lui permet de nourrir sa pensée philosophique par une observation directe et sensible du vivant.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve l'idée que la crise écologique contemporaine est avant tout une « crise de la sensibilité » et de nos relations avec le reste du monde vivant. Il soutient que la pensée moderne, marquée par un dualisme qui sépare strictement l'humain de la nature, nous a &lt;a href="https://www.youtube.com/watch?v=bAnXnPnnHCk" title="Baptiste Morizot, meme penseur on est un animal par France Inter"&gt;rendus aveugles et sourds &lt;/a&gt; aux autres espèces, qu'il préfère considérer comme d'autres « manières d'être vivant » plutôt que comme des êtres inférieurs. &lt;/p&gt; &lt;p&gt; Il propose ainsi de remplacer le modèle classique de la « maîtrise de la nature » par une « diplomatie des interdépendances ». Cette approche invite les humains à se concevoir comme des partenaires au sein d'un réseau complexe d'interdépendances, où il s'agit de tisser des alliances concrètes, de prêter attention aux signaux émis par les autres espèces et d'apprendre à cohabiter avec elles dans un esprit de respect et de responsabilité partagée. &lt;/p&gt; &lt;p&gt; Son travail, qui mêle récit, enquête éthologique et essai théorique, cherche à réenchanter &lt;a href="https://www.youtube.com/watch?v=uQZcktq_W3E" title="Baptiste Morizot, remet l’humain à sa place par La Grande Librairie"&gt;notre rapport au monde &lt;/a&gt; en réactivant nos capacités d'attention et d'intelligence sensible. En invitant à une forme de sagesse pragmatique et ancrée, il s'efforce de refonder notre culture environnementale, non pas pour dominer ou sanctuariser la nature, mais pour s'ajuster avec humilité à la diversité des formes de vie qui partagent la Terre avec nous. &lt;/p&gt;  &lt;audio controls title="Liberté, dignité, habitalité avec baptiste MORIZOT par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18558-25.04.2026-ITEMA_24488881-2026F30378S0115-NET_MFI_D6CADDF4-ADD5-4D3F-AA1D-625272E9CD3C-22-b98aedea0426383b486dc3819cb77a8e.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>GGLZjIzYDnE</t>
+          <t>k8yRIzRzKPw</t>
         </is>
       </c>
       <c r="G84" s="36" t="inlineStr">
         <is>
-          <t>"Le philosophe Pierre Charbonnier: "Beaucoup de choses qui nous semblaient aller de soi ne vont plus"" par France Inter</t>
+          <t>"Masterclass philosophique sur le vivant et la nature" par Ethique et tac</t>
         </is>
       </c>
       <c r="H84" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/charbonnier-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/bmorizot-mini.webp</t>
         </is>
       </c>
       <c r="I84" s="36" t="n"/>
       <c r="J84" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>ethique</t>
         </is>
       </c>
       <c r="K84" s="27" t="inlineStr">
@@ -5956,7 +5955,7 @@
       </c>
       <c r="L84" s="27" t="inlineStr">
         <is>
-          <t>philosophe français principalement orienté sur l'environnement.</t>
+          <t>philosophe français dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle.</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -5966,44 +5965,41 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie ; justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="167.25" customHeight="1" s="28">
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="237.75" customHeight="1" s="28">
       <c r="A85" s="34" t="n">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="B85" s="34" t="n"/>
-      <c r="C85" s="34" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
+      <c r="C85" s="34" t="n">
+        <v>1985</v>
       </c>
       <c r="D85" s="35" t="inlineStr">
         <is>
-          <t>Baptiste MORIZOT</t>
-        </is>
-      </c>
-      <c r="E85" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baptiste_Morizot"  title=" Wikipedia"&gt;Baptiste MORIZOT&lt;/a&gt;  est un philosophe français,  maître de conférences à l'université d'Aix-Marseille, dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle. Son approche se distingue par une pratique de terrain ancrée dans l'expérience, notamment le pistage des grands prédateurs comme les loups, ce qui lui permet de nourrir sa pensée philosophique par une observation directe et sensible du vivant.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve l'idée que la crise écologique contemporaine est avant tout une « crise de la sensibilité » et de nos relations avec le reste du monde vivant. Il soutient que la pensée moderne, marquée par un dualisme qui sépare strictement l'humain de la nature, nous a &lt;a href="https://www.youtube.com/watch?v=bAnXnPnnHCk" title="Baptiste Morizot, meme penseur on est un animal par France Inter"&gt;rendus aveugles et sourds &lt;/a&gt; aux autres espèces, qu'il préfère considérer comme d'autres « manières d'être vivant » plutôt que comme des êtres inférieurs. &lt;/p&gt; &lt;p&gt; Il propose ainsi de remplacer le modèle classique de la « maîtrise de la nature » par une « diplomatie des interdépendances ». Cette approche invite les humains à se concevoir comme des partenaires au sein d'un réseau complexe d'interdépendances, où il s'agit de tisser des alliances concrètes, de prêter attention aux signaux émis par les autres espèces et d'apprendre à cohabiter avec elles dans un esprit de respect et de responsabilité partagée. &lt;/p&gt; &lt;p&gt; Son travail, qui mêle récit, enquête éthologique et essai théorique, cherche à réenchanter &lt;a href="https://www.youtube.com/watch?v=uQZcktq_W3E" title="Baptiste Morizot, remet l’humain à sa place par La Grande Librairie"&gt;notre rapport au monde &lt;/a&gt; en réactivant nos capacités d'attention et d'intelligence sensible. En invitant à une forme de sagesse pragmatique et ancrée, il s'efforce de refonder notre culture environnementale, non pas pour dominer ou sanctuariser la nature, mais pour s'ajuster avec humilité à la diversité des formes de vie qui partagent la Terre avec nous. &lt;/p&gt;  &lt;audio controls title="Liberté, dignité, habitalité avec baptiste MORIZOT par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18558-25.04.2026-ITEMA_24488881-2026F30378S0115-NET_MFI_D6CADDF4-ADD5-4D3F-AA1D-625272E9CD3C-22-b98aedea0426383b486dc3819cb77a8e.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
+          <t>Yann DALL-AGLIO</t>
+        </is>
+      </c>
+      <c r="E85" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;(Son année de naissance n’étant pas connu, il est positionné ici de façon approximative)&lt;/p&gt; &lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Yann_Dall%27Aglio" title=" Wikipedia"&gt;Yamm DALL-AGLIO&lt;/a&gt; est un philosophe et essayiste français, agrégé de philosophie, qui s’est fait connaître par une manière accessible, humoristique et volontiers provocatrice de traiter les problèmes existentiels contemporains. Il a notamment enseigné la philosophie et s’est adressé à un large public à travers ses livres, ses conférences et une intervention TEDx consacrée à l’amour moderne. Son œuvre se situe ainsi à la croisée de la philosophie, de la satire sociale et de la vulgarisation. &lt;/p&gt; &lt;p&gt; Dans Une Rolex à 50 ans : A-t-on le droit de rater sa vie ?, il part d’une formule célèbre de Jacques Séguéla pour interroger l’idée selon laquelle  &lt;a href="https://www.youtube.com/watch?v=nxjf1wb5Rz4" title="reussir sa vie par Vers soi"&gt;la réussite se mesurerait &lt;/a&gt;  à la richesse, au prestige ou aux signes extérieurs de succès. Il montre que « réussir sa vie » n’a rien d’une norme objective : chacun donne un contenu différent au bonheur, à l’accomplissement ou à la réussite. La possession d’une Rolex devient alors le symbole d’une société qui confond la valeur d’une existence avec sa visibilité sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie défend donc le droit à une « vie de traviole », c’est-à-dire une existence qui ne suit pas nécessairement les modèles dominants de la performance, de la productivité et de la consommation. Il ne s’agit pas de glorifier l’échec ou la passivité, mais de refuser l’obligation de transformer sa vie en projet rentable et parfaitement maîtrisé. Dans cette perspective, l’erreur, l’errance, la simplicité et même certaines impasses peuvent avoir une valeur existentielle : une vie n’est pas ratée simplement parce qu’elle ne ressemble pas aux critères sociaux de la réussite. &lt;/p&gt; &lt;p&gt; Dans JTM. L’amour est-il has been ?, il applique cette réflexion au domaine amoureux. Il définit l’amour comme le désir d’être désiré et analyse les difficultés que l’individualisme, la logique de la performance, les rencontres virtuelles et les réseaux sociaux introduisent dans les relations. Puisque chacun cherche à être reconnu comme désirable, la relation amoureuse peut prendre la forme d’un véritable « marché des désirs », où l’on négocie sans cesse sa valeur aux yeux d’autrui. Il ne conclut toutefois pas à la disparition de l’amour : il plaide plutôt pour la tendresse, l’humour, la vulnérabilité et le droit à la maladresse. &lt;/p&gt; &lt;p&gt; Son style est inséparable de sa démarche philosophique : il préfère l’ironie au ton professoral et les exemples ordinaires aux abstractions isolées. Dans Vies, sentences et doctrines des sages imaginaires, il invente même de faux penseurs pour parodier les biographies et les doctrines philosophiques, tout en proposant une réflexion amusée sur notre besoin de fabriquer des autorités et des systèmes. Sa philosophie peut ainsi être comprise comme un scepticisme bienveillant : elle se méfie des recettes du bonheur, des normes de réussite et des discours trop sérieux, mais elle conserve une confiance dans l’amour, la liberté et la possibilité de vivre autrement. &lt;/p&gt;  &lt;audio controls title="L'amour est il ‘has been’?  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14034-12.02.2012-ITEMA_20344223-2012F4034S0043-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
-          <t>k8yRIzRzKPw</t>
+          <t>dJgiYBdD2VA</t>
         </is>
       </c>
       <c r="G85" s="36" t="inlineStr">
         <is>
-          <t>"Masterclass philosophique sur le vivant et la nature" par Ethique et tac</t>
-        </is>
-      </c>
-      <c r="H85" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/bmorizot-mini.webp</t>
+          <t>L’amour – vous le faites mal par TED</t>
+        </is>
+      </c>
+      <c r="H85" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/ydallaglio-mini.webp</t>
         </is>
       </c>
       <c r="I85" s="36" t="n"/>
@@ -6014,12 +6010,12 @@
       </c>
       <c r="K85" s="27" t="inlineStr">
         <is>
-          <t>Ecologisme</t>
-        </is>
-      </c>
-      <c r="L85" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle.</t>
+          <t>Existentialisme</t>
+        </is>
+      </c>
+      <c r="L85" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> philosophe et essayiste français, drôle et provocateur, qui traite des problèmes existentiels contemporains.</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6029,57 +6025,65 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="237.75" customHeight="1" s="28">
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="115.5" customHeight="1" s="28">
       <c r="A86" s="34" t="n">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B86" s="34" t="n"/>
-      <c r="C86" s="34" t="n">
-        <v>1985</v>
+      <c r="C86" s="34" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
       </c>
       <c r="D86" s="35" t="inlineStr">
         <is>
-          <t>Yann DALL-AGLIO</t>
-        </is>
-      </c>
-      <c r="E86" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;(Son année de naissance n’étant pas connu, il est positionné ici de façon approximative)&lt;/p&gt; &lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Yann_Dall%27Aglio" title=" Wikipedia"&gt;Yamm DALL-AGLIO&lt;/a&gt; est un philosophe et essayiste français, agrégé de philosophie, qui s’est fait connaître par une manière accessible, humoristique et volontiers provocatrice de traiter les problèmes existentiels contemporains. Il a notamment enseigné la philosophie et s’est adressé à un large public à travers ses livres, ses conférences et une intervention TEDx consacrée à l’amour moderne. Son œuvre se situe ainsi à la croisée de la philosophie, de la satire sociale et de la vulgarisation. &lt;/p&gt; &lt;p&gt; Dans Une Rolex à 50 ans : A-t-on le droit de rater sa vie ?, il part d’une formule célèbre de Jacques Séguéla pour interroger l’idée selon laquelle  &lt;a href="https://www.youtube.com/watch?v=nxjf1wb5Rz4" title="reussir sa vie par Vers soi"&gt;la réussite se mesurerait &lt;/a&gt;  à la richesse, au prestige ou aux signes extérieurs de succès. Il montre que « réussir sa vie » n’a rien d’une norme objective : chacun donne un contenu différent au bonheur, à l’accomplissement ou à la réussite. La possession d’une Rolex devient alors le symbole d’une société qui confond la valeur d’une existence avec sa visibilité sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie défend donc le droit à une « vie de traviole », c’est-à-dire une existence qui ne suit pas nécessairement les modèles dominants de la performance, de la productivité et de la consommation. Il ne s’agit pas de glorifier l’échec ou la passivité, mais de refuser l’obligation de transformer sa vie en projet rentable et parfaitement maîtrisé. Dans cette perspective, l’erreur, l’errance, la simplicité et même certaines impasses peuvent avoir une valeur existentielle : une vie n’est pas ratée simplement parce qu’elle ne ressemble pas aux critères sociaux de la réussite. &lt;/p&gt; &lt;p&gt; Dans JTM. L’amour est-il has been ?, il applique cette réflexion au domaine amoureux. Il définit l’amour comme le désir d’être désiré et analyse les difficultés que l’individualisme, la logique de la performance, les rencontres virtuelles et les réseaux sociaux introduisent dans les relations. Puisque chacun cherche à être reconnu comme désirable, la relation amoureuse peut prendre la forme d’un véritable « marché des désirs », où l’on négocie sans cesse sa valeur aux yeux d’autrui. Il ne conclut toutefois pas à la disparition de l’amour : il plaide plutôt pour la tendresse, l’humour, la vulnérabilité et le droit à la maladresse. &lt;/p&gt; &lt;p&gt; Son style est inséparable de sa démarche philosophique : il préfère l’ironie au ton professoral et les exemples ordinaires aux abstractions isolées. Dans Vies, sentences et doctrines des sages imaginaires, il invente même de faux penseurs pour parodier les biographies et les doctrines philosophiques, tout en proposant une réflexion amusée sur notre besoin de fabriquer des autorités et des systèmes. Sa philosophie peut ainsi être comprise comme un scepticisme bienveillant : elle se méfie des recettes du bonheur, des normes de réussite et des discours trop sérieux, mais elle conserve une confiance dans l’amour, la liberté et la possibilité de vivre autrement. &lt;/p&gt;  &lt;audio controls title="L'amour est il ‘has been’?  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14034-12.02.2012-ITEMA_20344223-2012F4034S0043-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+          <t>Norman AJARI</t>
+        </is>
+      </c>
+      <c r="E86" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Norman_Ajari"  title=" Wikipedia"&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href="https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari"  title="Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse"&gt;"études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href="https://www.youtube.com/watch?v=IMUBi9oi2WM" title="Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche"&gt;"colonialité de l’être" &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=ECSmpOXY8kg" title="NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS"&gt;"La Dignité ou la mort", &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de "philosophe militant" : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. Né en 1987, formé à l’université de Toulouse, il enseigne aux États-Unis, à l’université Villanova. Dans &lt;em&gt;La Dignité ou la mort. Éthique et politique de la race&lt;/em&gt; (2019), il soutient que l’expérience noire moderne, de l’esclavage aux violences policières, ne peut être comprise par les catégories habituelles de la philosophie morale, et qu’elle appelle une éthique de la dignité face à la mort sociale. Il a aussi fait connaître en France les débats du courant « afro-pessimiste » américain. &lt;/p&gt; &lt;audio controls title="où commence et où finit le racisme? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
+</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>dJgiYBdD2VA</t>
+          <t>8xfdl8Hmbik</t>
         </is>
       </c>
       <c r="G86" s="36" t="inlineStr">
         <is>
-          <t>L’amour – vous le faites mal par TED</t>
-        </is>
-      </c>
-      <c r="H86" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/ydallaglio-mini.webp</t>
+          <t>"Le racisme dans la loi et dans les faits - Norman Ajari" par A gauche</t>
+        </is>
+      </c>
+      <c r="H86" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/ajari-mini.webp</t>
         </is>
       </c>
       <c r="I86" s="36" t="n"/>
       <c r="J86" s="27" t="inlineStr">
         <is>
-          <t>ethique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K86" s="27" t="inlineStr">
         <is>
-          <t>Existentialisme</t>
-        </is>
-      </c>
-      <c r="L86" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> philosophe et essayiste français, drôle et provocateur, qui traite des problèmes existentiels contemporains.</t>
+          <t xml:space="preserve">Tiers-mondisme ; Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="L86" s="27" t="inlineStr">
+        <is>
+          <t>philosophe franco-américain spécialiste des études noires francophones &amp;amp; décoloniales.</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6089,129 +6093,111 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t xml:space="preserve">sens</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="115.5" customHeight="1" s="28">
-      <c r="A87" s="34" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B87" s="34" t="n"/>
-      <c r="C87" s="34" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="D87" s="35" t="inlineStr">
-        <is>
-          <t>Norman AJARI</t>
-        </is>
-      </c>
-      <c r="E87" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Norman_Ajari"  title=" Wikipedia"&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href="https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari"  title="Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse"&gt;"études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href="https://www.youtube.com/watch?v=IMUBi9oi2WM" title="Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche"&gt;"colonialité de l’être" &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=ECSmpOXY8kg" title="NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS"&gt;"La Dignité ou la mort", &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de "philosophe militant" : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. Né en 1987, formé à l’université de Toulouse, il enseigne aux États-Unis, à l’université Villanova. Dans &lt;em&gt;La Dignité ou la mort. Éthique et politique de la race&lt;/em&gt; (2019), il soutient que l’expérience noire moderne, de l’esclavage aux violences policières, ne peut être comprise par les catégories habituelles de la philosophie morale, et qu’elle appelle une éthique de la dignité face à la mort sociale. Il a aussi fait connaître en France les débats du courant « afro-pessimiste » américain. &lt;/p&gt; &lt;audio controls title="où commence et où finit le racisme? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
-</t>
-        </is>
-      </c>
-      <c r="F87" s="34" t="inlineStr">
-        <is>
-          <t>8xfdl8Hmbik</t>
-        </is>
-      </c>
-      <c r="G87" s="36" t="inlineStr">
-        <is>
-          <t>"Le racisme dans la loi et dans les faits - Norman Ajari" par A gauche</t>
-        </is>
-      </c>
-      <c r="H87" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/ajari-mini.webp</t>
-        </is>
-      </c>
-      <c r="I87" s="36" t="n"/>
-      <c r="J87" s="27" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="K87" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiers-mondisme ; Pensée décoloniale</t>
-        </is>
-      </c>
-      <c r="L87" s="27" t="inlineStr">
-        <is>
-          <t>philosophe franco-américain spécialiste des études noires francophones &amp;amp; décoloniales.</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
           <t xml:space="preserve">decolonial</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="219.75" customHeight="1" s="28">
-      <c r="A88" s="26" t="n">
+    <row r="87" ht="219.75" customHeight="1" s="28">
+      <c r="A87" s="26" t="n">
         <v>1988</v>
       </c>
-      <c r="C88" s="26" t="n">
+      <c r="C87" s="26" t="n">
         <v>1988</v>
       </c>
-      <c r="D88" s="26" t="inlineStr">
+      <c r="D87" s="26" t="inlineStr">
         <is>
           <t>Marylin MAESO</t>
         </is>
       </c>
-      <c r="E88" s="43" t="inlineStr">
+      <c r="E87" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marylin_Maeso"  title=" Wikipedia"&gt;Marylin MAESO&lt;/a&gt; est une philosophe  et enseignante française, agrégée de philosophie et ancienne élève de l'École normale supérieure. Spécialiste reconnue de  &lt;a href="https://www.youtube.com/watch?v=UtgptKTW288" title="l’étranger de Camus, une philosophe de l’absurde par France Inter"&gt;l’œuvre d’Albert Camus, &lt;/a&gt; elle consacre une grande partie de ses recherches à la philosophie politique contemporaine, à la question de l’humanisme et aux dynamiques de la déshumanisation dans nos sociétés modernes. &lt;/p&gt;&lt;p&gt; Son travail intellectuel est profondément marqué par une lecture renouvelée de Camus, qu'elle mobilise pour analyser les enjeux éthiques de notre époque. Dans La Petite &lt;a href="https://www.youtube.com/watch?v=YQqfp9iA5ME" title="nous sommes nous habitués à l’inhumain par marianne"&gt;Fabrique de l'inhumain, &lt;/a&gt; elle s'appuie sur le roman La Peste pour explorer comment l'inhumanité s'insinue dans le quotidien, souvent de manière insidieuse, plutôt que par de grands événements spectaculaires. Elle cherche ainsi à éveiller la vigilance citoyenne face aux processus de banalisation du mal. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches, Marylin Maeso défend une éthique du débat public fondée sur la nuance et le dialogue. Dans Les Conspirateurs du silence, elle critique les polémiques stériles et les clivages idéologiques qui empêchent la compréhension mutuelle, plaidant pour un exercice de la pensée qui permette de maintenir un lien social malgré les désaccords. Son engagement se traduit également par des actions concrètes, notamment à travers l'association Tête-à-texte, qu'elle a créée pour promouvoir la lecture et la réflexion comme leviers d'émancipation et de citoyenneté. &lt;/p&gt; &lt;p&gt;  Sa philosophie se veut une « philosophie de terrain » et de transmission, portée par un souci constant de réhabiliter l'humanisme face aux idéologies qui cloisonnent et déshumanisent. En privilégiant la lecture des textes classiques comme guides pour penser les crises actuelles, elle s'efforce de fournir aux citoyens des outils critiques pour naviguer dans un monde complexe tout en préservant leur capacité de jugement et d'empathie.  &lt;/p&gt;  &lt;audio controls title=" Camus, vivre malgré tout par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-30.10.2023-ITEMA_23535378-2023C48904S0303-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F88" s="26" t="inlineStr">
+      <c r="F87" s="26" t="inlineStr">
         <is>
           <t>6VIxXg4eTqw</t>
         </is>
       </c>
-      <c r="G88" s="27" t="inlineStr">
+      <c r="G87" s="27" t="inlineStr">
         <is>
           <t>Marylin Maeso : L ‘antisémitisme est une peste par France 24</t>
         </is>
       </c>
+      <c r="H87" s="27" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/mmaeso-mini.webp</t>
+        </is>
+      </c>
+      <c r="J87" s="27" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K87" s="27" t="inlineStr">
+        <is>
+          <t>Libéralisme</t>
+        </is>
+      </c>
+      <c r="L87" s="27" t="inlineStr">
+        <is>
+          <t>philosophe politique française, de l’humanisme aux dynamiques de la déshumanisation.</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="219.75" customHeight="1" s="28">
+      <c r="A88" s="26">
+        <v>1950</v>
+      </c>
+      <c r="C88" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1950</t>
+        </is>
+      </c>
+      <c r="D88" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jean-Michel BESNIER</t>
+        </is>
+      </c>
+      <c r="E88" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Michel_Besnier" title=" Wikipedia"&gt;Jean-Michel BESNIER&lt;/a&gt; est un philosophe français. Né à Caen en 1950, agrégé de philosophie et docteur en sciences politiques, il enseigne à l’université de technologie de Compiègne de 1988 à 2001, puis à la Sorbonne, dont il est professeur émérite. Ses premiers livres portent sur l’histoire de la philosophie moderne et contemporaine, dont il publie une grande synthèse en 1993, et sur la figure de l’intellectuel, partagé entre la révolte et l’engagement, de Georges Bataille à Maurice Blanchot.&lt;/p&gt; &lt;p&gt;Il se consacre ensuite à l’impact des sciences et des techniques sur nos représentations et nos imaginaires. Dans &lt;em&gt;Demain les posthumains&lt;/em&gt; (2009), il analyse le &lt;a href="https://fr.wikipedia.org/wiki/Transhumanisme" title=" Wikipedia"&gt;transhumanisme&lt;/a&gt;, qui promet de dépasser la condition humaine grâce aux biotechnologies, aux nanotechnologies et à l’intelligence artificielle. Il y voit moins un progrès qu’une fatigue d’être soi, un désir de se débarrasser de la fragilité, de l’incertitude et de la mort, qui sont pourtant ce qui fait notre humanité.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Homme simplifié&lt;/em&gt; (2012), il décrit le « syndrome de la touche étoile » : à force de dialoguer avec des machines, nous simplifions notre langage et nos relations pour nous adapter à elles, au lieu de les rendre plus humaines. Il débat publiquement avec les partisans du transhumanisme, comme Laurent Alexandre, avec qui il publie &lt;em&gt;Les robots font-ils l’amour ?&lt;/em&gt; (2016). Il a siégé dans plusieurs comités d’éthique de la recherche, notamment celui du CNRS, et dirigé le secteur « sciences et société » du ministère de la Recherche de 2008 à 2011.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="H88" s="27" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/mmaeso-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/besnier-mini.webp</t>
         </is>
       </c>
       <c r="J88" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t xml:space="preserve">ethique ; epistemologie</t>
         </is>
       </c>
       <c r="K88" s="27" t="inlineStr">
         <is>
-          <t>Libéralisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="L88" s="27" t="inlineStr">
         <is>
-          <t>philosophe politique française, de l’humanisme aux dynamiques de la déshumanisation.</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t xml:space="preserve">philosophe français des techniques, critique du transhumanisme et de « l’homme simplifié ».</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6219,58 +6205,8 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="O88"/>
       <c r="P88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="219.75" customHeight="1" s="28">
-      <c r="A89" s="26">
-        <v>1950</v>
-      </c>
-      <c r="C89" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1950</t>
-        </is>
-      </c>
-      <c r="D89" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jean-Michel BESNIER</t>
-        </is>
-      </c>
-      <c r="E89" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Michel_Besnier" title=" Wikipedia"&gt;Jean-Michel BESNIER&lt;/a&gt; est un philosophe français. Né à Caen en 1950, agrégé de philosophie et docteur en sciences politiques, il enseigne à l’université de technologie de Compiègne de 1988 à 2001, puis à la Sorbonne, dont il est professeur émérite. Ses premiers livres portent sur l’histoire de la philosophie moderne et contemporaine, dont il publie une grande synthèse en 1993, et sur la figure de l’intellectuel, partagé entre la révolte et l’engagement, de Georges Bataille à Maurice Blanchot.&lt;/p&gt; &lt;p&gt;Il se consacre ensuite à l’impact des sciences et des techniques sur nos représentations et nos imaginaires. Dans &lt;em&gt;Demain les posthumains&lt;/em&gt; (2009), il analyse le &lt;a href="https://fr.wikipedia.org/wiki/Transhumanisme" title=" Wikipedia"&gt;transhumanisme&lt;/a&gt;, qui promet de dépasser la condition humaine grâce aux biotechnologies, aux nanotechnologies et à l’intelligence artificielle. Il y voit moins un progrès qu’une fatigue d’être soi, un désir de se débarrasser de la fragilité, de l’incertitude et de la mort, qui sont pourtant ce qui fait notre humanité.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Homme simplifié&lt;/em&gt; (2012), il décrit le « syndrome de la touche étoile » : à force de dialoguer avec des machines, nous simplifions notre langage et nos relations pour nous adapter à elles, au lieu de les rendre plus humaines. Il débat publiquement avec les partisans du transhumanisme, comme Laurent Alexandre, avec qui il publie &lt;em&gt;Les robots font-ils l’amour ?&lt;/em&gt; (2016). Il a siégé dans plusieurs comités d’éthique de la recherche, notamment celui du CNRS, et dirigé le secteur « sciences et société » du ministère de la Recherche de 2008 à 2011.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H89" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/besnier-mini.webp</t>
-        </is>
-      </c>
-      <c r="J89" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K89" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Humanisme</t>
-        </is>
-      </c>
-      <c r="L89" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe français des techniques, critique du transhumanisme et de « l’homme simplifié ».</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O89"/>
-      <c r="P89" t="inlineStr">
         <is>
           <t xml:space="preserve">esprit-ia</t>
         </is>
@@ -6283,46 +6219,44 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alain_Badiou&quot;  title=&quot; Wikipedia&quot;&gt;Alain BADIOU&lt;/a&gt; est un philosophe, écrivain et dramaturge français dont la pensée se situe au croisement du platonisme, du marxisme et des mathématiques contemporaines.  Son  &lt;a href=&quot;https://www.youtube.com/watch?v=mSLudQ6QxvM&quot; style=&quot;color:#88A1E9&quot; title=&quot;  La Masterclass d'Alain Badiou ! (Amour, Guerres, Identité, Smartphone...)  par Cerveaux Non Disponible &quot;&gt; œuvre philosophique&lt;/a&gt;  repose sur l’idée que la philosophie ne produit pas elle-même de vérités, mais qu’elle se nourrit de quatre domaines — la science ; l'art ; la politique et l'amour —  d'où des vérités universelles peuvent surgir. &lt;/p&gt; &lt;p&gt; Il définit l’être comme ce que les mathématiques, en particulier la théorie des ensembles, permettent de penser l’être en tant que multiple pur. Sa réflexion se concentre sur le concept &quot;d’événement&quot;, rupture imprévisible qui bouleverse une situation donnée et ouvre la possibilité d’une vérité nouvelle. Le sujet, pour lui, n’existe pas avant l’événement, il se constitue par la fidélité à ce qui s’est produit et par le processus de vérité qui en découle. Cette fidélité est ce qui permet à l’événement de durer et de transformer le monde. &lt;/p&gt; &lt;p&gt; Il s’oppose à l’éthique &lt;a href=&quot;https://www.youtube.com/watch?v=Ic-4f03-v3U&quot; title=&quot;  Alain Badiou - Que signifie la démocratie?  par Ce soir ou jamais &quot;&gt; &quot;humanitaire&quot; &lt;/a&gt; dominante, qu’il considère comme une gestion du statu quo, et défend au contraire une éthique des vérités, exigeante et universaliste. &lt;/p&gt; &lt;p&gt;  Parmi ses ouvrages majeurs figurent &lt;a href=&quot;https://rumeurdespace.com/2018/12/18/badiou-1-letre-et-levenement-que-le-vide-est-le-nom-propre-de-letre/&quot;  title=&quot;  Alain Badiou - L'être et l'évènement  par Rumeur d'espace &quot;&gt; &quot;L’Être et l’événement&quot; &lt;/a&gt; (1988), qui expose sa théorie ontologique, &quot;Logiques des mondes&quot; (2006), qui traite des modalités de l’apparaître, et &quot;L’Immanence des vérités&quot; (2018), qui achève sa trilogie sur l’ontologie et la vérité. Il a également écrit &quot;L’Éthique&quot; (1993), où il critique la moralisation contemporaine, et &quot;Conditions&quot; (1992), où il développe sa conception des quatre conditions de la philosophie. &lt;/p&gt; &lt;p&gt; Sa pensée, dense et exigeante, a exercé une influence importante à l’international, autant dans le champ universitaire que dans les milieux artistiques et militants, et reste marquée par une volonté constante de penser l’émancipation au-delà des formes politiques et sociales dominantes. &lt;/p&gt;  &lt;audio controls title=&quot;Alain BADIOU par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10351-12.01.2009-ITEMA_20163782-2008C3500E0127-ITE_00017859_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89liane_Escoubas&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Éliane ESCOUBAS&lt;/a&gt;  est une philosophe française, historienne de la philosophie et traductrice. Elle qui se rattache à l’école phénoménologique et travaille principalement sur la philosophie allemande, la phénoménologie de l’art et la psychiatrie phénoménologique, dite Daseinsanalyse. Après une formation marquée par les cours de Gérard Granel sur Husserl, Kant et Hegel à Toulouse, elle enseigne dans le secondaire puis devient maître de conférences, puis professeur de philosophie, tout en menant des recherches au CNRS et en participant à la création du Collège international de Philosophie. &lt;/p&gt; &lt;p&gt; Elle met au centre la phénoménologie de l’expérience sensible, en particulier la manière dont le monde et le sujet adviennent à travers le sentir, l’affect et la perception. Elle montre que la phénoménologie fournit un prisme particulièrement adapté pour penser l’esthétique, car l’œuvre d’art apparaît comme un mode privilégié pour saisir comment le sujet et le monde se co‑constituent dans une expérience sensible et existentielle. &lt;/p&gt; &lt;p&gt; Une grande partie de son œuvre est consacrée à une « esthétique du sentir » où l’art n’est pas seulement une illustration de la philosophie, mais un mode de connaissance autonome. Dans ses travaux comme Imago mundi. Topologie de l’art ou L’invention de l’art, elle montre que l’image et l’œuvre picturale ne se réduisent pas à « représentation » ou « signe », mais relèvent d’une apparition du monde lui‑même, d’une spatialité et d’une temporalité qui précèdent les catégories classiques de l’objet. &lt;/p&gt; &lt;p&gt; Sa philosophie s’ouvre aussi à la phénoménologie clinique et à la psychiatrie, notamment à travers la Daseinsanalyse et la place de l’affect et de l’affectivité dans la constitution du sujet. En explorant les affectivités dans la modernité et la phénoménologie, Escoubas prolonge ainsi une réflexion sur la manière dont le vécu, le corps et la subjectivité forment un champ de savoir propre, à la fois esthétique, analytique et existentiel. &lt;/p&gt;  &lt;audio controls title=&quot;Alain BADIOU par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10080-25.11.2011-ITEMA_20320112-2011C3403E0190-ITE_00047070_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" display="https://laphilo.fr/photo/escoubas.webp" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anne_Fagot-Largeault&quot;  title=&quot; Wikipedia&quot;&gt;Anne FAGOT-LARGEAULT&lt;/a&gt;  est une une philosophe et psychiatre française, élève de l’École normale supérieure de jeunes filles, agrégée de philosophie en 1961, elle a combiné une carrière académique brillante – professeur à Paris 1 Panthéon-Sorbonne puis au Collège de France (chaire de philosophie des sciences biologiques et médicales de 2000 à 2009) – avec une pratique hospitalière en psychiatrie à l’hôpital Henri-Mondor de Créteil. Membre de l’Académie des sciences depuis 2002, elle incarne une figure rare à la croisée de la médecine, de la philosophie et des sciences du vivant. &lt;/p&gt; &lt;p&gt;  Sa philosophie se déploie dans trois &lt;a href=&quot;https://www.youtube.com/watch?v=LYwHBFs7elQ&quot; title=&quot; Philosophie des sciences biologiques et médicales et philosophie par Collège de France&quot;&gt; directions principales, &lt;/a&gt; toutes liées à l’épistémologie et à l’ontologie des sciences biologiques et médicales. D’abord, elle analyse le raisonnement diagnostique : logique inductive, probabilités, heuristiques, en soulignant les limites de la certitude dans un domaine probabiliste par nature. Ensuite, elle interroge la causalité : distinction entre causalité mécanique et téléologique, preuves épidémiologiques, rôle des modèles explicatifs dans la compréhension du vivant. Enfin, elle s’attache à l’éthique : méthodologie des essais cliniques, dilemmes bioéthiques, responsabilité dans un univers contingent où l’humain influence activement l’avenir. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages comme Ontologie du devenir ou Médecine et philosophie, elle revisite les thèmes du temps, de l’évolution et du vivant en dialogue avec Héraclite, Bergson ou les sciences modernes. Elle défend une science du devenir contre l’immobilisme parmnénidien : le flux permanent du réel exige des concepts fluides, une intuition intellectuelle capable de saisir l’instabilité des êtres vivants sans les figer en essences. L’évolution darwinienne, loin d’être une téléologie, révèle un univers de contingences où l’action humaine porte une responsabilité prospective . &lt;/p&gt; &lt;p&gt;     &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_2016_hos_114_1_8513&quot; title=&quot; laudatio de la professeure par persée&quot;&gt; Son apport &lt;/a&gt; le plus original réside dans une anthropologie bio-médicale qui refuse le réductionnisme : la médecine suppose une métaphysique du mal, une épistémologie du normal/pathologique et une éthique équilibrant l’autonomie individuelle, le bien du patient et l’intérêt collectif. Professeure honoraire influente, elle a formé des générations à penser la vie non comme un donné stable, mais comme un processus à comprendre et à orienter éthiquement.&lt;/p&gt;                                                                      &lt;audio controls title=&quot;Médecine et philosophie avec Anne Fagot-Largeault par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10201-08.03.2010-ITEMA_20218761-2010C10593E0008-NET_01E69962-F316-4C45-826B-43707F9BD385_FC-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" display="https://www.laphilo.fr/pho/rdebray-mini.webp" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christian_Jambet&quot;  title=&quot; Wikipedia&quot;&gt;Christian JAMBET&lt;/a&gt; est un philosophe et islamologue  français reconnu pour ses travaux qui font le pont entre la philosophie occidentale et la pensée islamique, en particulier le chiisme. Agrégé de philosophie et ancien élève d'Henry Corbin, un spécialiste de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Islam_en_Iran&quot;  title=&quot; Islam en Iran par Wikipedia&quot;&gt;l'islam iranien&lt;/a&gt;, il a consacré sa carrière à l'étude des traditions philosophiques et spirituelles de l'Islam, notamment celles de l'Iran. Il est devenu membre de l'Académie française en 2024. Son travail se distingue par sa profondeur et son caractère interdisciplinaire. Ses contributions majeures portent sur :&lt;/p&gt; &lt;p&gt; - La philosophie islamique : Il a montré qu'il existe une tradition philosophique riche et autonome en terre d'Islam, souvent mal comprise ou négligée en Occident. Il a mis en lumière les liens, mais aussi les spécificités, entre la pensée grecque (notamment platonicienne) et les penseurs islamiques. Son ouvrage Qu'est-ce que la philosophie islamique ? est une référence dans ce domaine. &lt;/p&gt; &lt;p&gt; - Le chiisme et le soufisme : il est un expert du chiisme, qu'il étudie non seulement sous son aspect politique et théologique, mais aussi dans sa dimension philosophique et spirituelle. Il a beaucoup travaillé sur la figure du  &lt;a href=&quot;https://www.youtube.com/watch?v=kQzLVldS4PU&quot;  title=&quot;L'immortalité de l'âme selon Mulla Sadra, Christian Jambet Les vivants et les dieux par Facteur&quot;&gt; philosophe iranien Mullâ Sadrâ Shîrâzî&lt;/a&gt; , qu'il considère comme un des plus grands métaphysiciens de l'histoire. Il explore les concepts de l'ésotérisme (bātin) et de l'exotérisme (zahir), montrant comment la philosophie chiite a développé une pensée de la liberté et de l'intériorité face à l'orthodoxie religieuse. &lt;/p&gt; &lt;p&gt; - La philosophie politique : Il s'intéresse aux conceptions du pouvoir et du droit dans l'Islam. Dans son livre Le gouvernement divin, il analyse la relation entre la théologie et le politique, et les différentes manières dont le pouvoir a été conceptualisé dans le chiisme. &lt;/p&gt; &lt;p&gt; - Les concepts de l'« Ange » et de l'« imagination créatrice » : Reprenant les travaux d'Henry Corbin, il a exploré le rôle central de l'imagination dans la connaissance et l'expérience religieuse. Pour Jambet, l'imagination n'est pas une simple faculté de fiction, mais un organe de perception capable d'accéder à un monde intermédiaire, peuplé d'êtres spirituels comme les Anges. &lt;/p&gt; &lt;p&gt;  Il a publié différents ouvrages dont &quot;L'Ange&quot; paru en 1976 co-écrit avec Guy Lardreau ainsi que &quot;La Logique des Orientaux&quot;  paru en 1983  sans oublié &quot;La Grande Résurrection d'Alamût&quot;  paru en 1990, sur les formes de la liberté dans le shî'isme ismaélien. &lt;/p&gt;  &lt;audio controls title=&quot; La philosophie islamique avec Christian Jambet par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11200-12.02.2012-ITEMA_20344279-2012C14958E0004-ITE_00049063_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernadette_Bensaude-Vincent&quot; title=&quot; Wikipedia&quot;&gt;Bernadette BENSUDE-VINCENT&lt;/a&gt;  est une philosophe française et historienne des sciences. Formée à l'École normale supérieure de Fontenay-aux-Roses, agrégée de philosophie en 1971 et docteure ès lettres en 1981, elle a enseigné à l'université Paris X-Nanterre puis Paris I Panthéon-Sorbonne jusqu'à sa retraite en 2015, où elle est professeure émérite. Elle a dirigé le Centre d'études des techniques, des connaissances et des pratiques (CETCOPRA) et été membre senior de l'Institut universitaire de France. &lt;/p&gt; &lt;p&gt; Elle a occupé des postes invités dans des universités internationales comme Madrid, Vienne ou Bielefeld, et collaboré avec le MIT sur l'histoire des matériaux. Membre de l'Académie des technologies et vice-présidente du comité d'éthique d'organismes comme l'Inrae, elle a contribué à la Cité des sciences et de l'industrie. Auteure d'une centaine d'ouvrages, elle a coordonné des programmes sur l'éthique des nanotechnologies et les technosciences. &lt;/p&gt; &lt;p&gt; Sa pensée critique la rupture bachelardienne entre science et opinion, plaidant pour leur interdépendance dans une &quot;philosophie de terrain&quot;. Elle analyse la chimie, les technosciences et les technologies émergentes comme des pratiques sociales façonnant la matière, questionnant le pouvoir des sciences sur le vivant et la société. Elle rejette &lt;a href=&quot;https://www.youtube.com/watch?v=MRD0LLrjGG8&quot;  title=&quot;bernadette bensaude-vincent : approche philo de la biologie de synthese par Alter Mardis&quot;&gt;les visions réductionnistes &lt;/a&gt; pour souligner les controverses et la pluralité des savoirs. &lt;/p&gt; &lt;p&gt; Dans des essais comme L’Opinion publique et la science ou ses réflexions sur l'Anthropocène, elle promeut une &quot;culture de la défiance&quot; constructive contre la méfiance, favorisant des savoirs robustes. Ses recherches sur les matériaux et la biologie de synthèse interrogent l'hubris humaine, défendant une  &lt;a href=&quot;https://www.youtube.com/watch?v=HnEX-2_p3mQ&quot;  title=&quot;bernadette bensaude-vincent : fait il changer notre rapport au temps par écologie rationnelle&quot;&gt;approche humaniste &lt;/a&gt; des relations science-société et une histoire des sciences attentive aux marges. &lt;/p&gt;    &lt;audio controls title=&quot; Science et recherche: de l’expertise à la sphère publique par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13983-28.04.2021-ITEMA_22649821-2021C16450S0118.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christian_Godin&quot;   title=&quot; Wikipedia&quot;&gt;Christian GODIN&lt;/a&gt;  est un philosophe français qui a enseigné la philosophie à l’université Blaise-Pascal de Clermont-Ferrand, où il est devenu professeur émérite, et collabore régulièrement à des revues comme Marianne, Le Magazine littéraire et Sciences et Avenir. Il dirige également la revue Cités aux PUF et s’est imposé comme  &lt;a href=&quot;http://www.christian-godin.com/biographie.html&quot;  title=&quot;autobiographie par c godin&quot;&gt; un auteur prolifique, &lt;/a&gt; avec plus d’une cinquantaine d’ouvrages à caractère pédagogique et érudit. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour son monumental travail « La Totalité en sept volumes » (1997-2003), fruit de sa thèse de doctorat, qui explore la notion philosophique de totalité à travers l’histoire de la pensée. Parmi ses autres travaux phares figurent des ouvrages de vulgarisation comme  &lt;a href=&quot;https://www.youtube.com/watch?v=nJga6GYNLUw&quot;  title=&quot;Ephilosophie pour les nuls par Google payer livres&quot;&gt; La Philosophie pour les nuls &lt;/a&gt; (2006), des dictionnaires philosophiques et des essais contemporains tels que La crise de la réalité (2021), où il analyse la destitution du réel par le numérique et les idéologies modernes. Il a aussi réalisé des entretiens avec des penseurs comme Axel Kahn ou Malek Chebel.  &lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est avant tout « un désir de comprendre le monde, de donner du sens, d’expliquer les choses », et elle doit rester ancrée dans le concret pour éviter l’abstraction stérile. Il insiste sur son rôle pédagogique et accessible à tous, invitant à dialoguer avec les grands penseurs comme Platon, Nietzsche ou Hannah Arendt pour aborder des thèmes universels : le sens de la vie, l’amour, la mort. Contrairement à la science focalisée sur la vérité, la philosophie cherche le sens via la critique, le débat intérieur et l’examen des  &lt;a href=&quot;https://www.youtube.com/watch?v=8KzIKZimPSIl&quot;  title=&quot;Etre humain par Philomonaco&quot;&gt; problèmes humains. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il aborde des enjeux actuels comme la crise de la réalité (présentisme, simulationnisme, prédictionnisme), la synchronicité comme signe d’unité divine échappant à la raison, ou la démoralisation contemporaine. Il critique le subjectivisme relativiste, le narcissisme numérique et la technoscience totalitaire qui substitue un monde artificiel à la nature, plaidant pour une pensée multidimensionnelle du réel. Ses analyses, souvent pessimistes sur la virtualité et la post-vérité, défendent une objectivité ancrée dans le monde physique. &lt;/p&gt;     &lt;audio controls title=&quot;Le philosophe Christian Godin tire les leçons du Grand Débat &quot; par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/15343-18.03.2019-ITEMA_22011803-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alain_Finkielkraut&quot;  title=&quot; Wikipedia&quot;&gt;Alain FINKIELKRAUT&lt;/a&gt;  est un philosophe français  et essayiste français né en 1949 à Paris, fils de juifs polonais rescapés de la Shoah. Agrégé de philosophie, il a enseigné brièvement avant de se consacrer à l'écriture et aux médias, notamment via des chroniques radiophoniques sur France Culture. Membre de l'Académie française depuis 2014, il est associé au mouvement des &quot;nouveaux philosophes&quot; post-Mai 68, rompant avec le marxisme pour critiquer les idéologies totalitaires. &lt;/p&gt; &lt;p&gt; Ses essais majeurs incluent La Défaite de la pensée (1987), qui dénonce le relativisme culturel et &lt;a href=&quot;https://www.youtube.com/watch?v=e-uoL-Ve_8c&quot;   title=&quot;A Finkierlkraut et ses clachs tv  par France Tv &quot;&gt; l'appauvrissement intellectuel &lt;/a&gt; moderne, et L'Identité malheureuse (2013), où il analyse la crise de l'identité française face à l'immigration et au multiculturalisme. D'autres livres comme Remembering in Vain (1989) explorent la mémoire de la Shoah et les crimes contre l'humanité, tandis que À la première personne (2019) revisite son parcours personnel.  &lt;/p&gt; &lt;p&gt; Il  défend une pensée humaniste ancrée dans la tradition européenne, influencée par Hannah Arendt, Rousseau et les Lumières. Il rejette le &quot;progressisme&quot; idéologique qui, selon lui, nie les différences culturelles et sapent la civilisation occidentale par un relativisme anti-humaniste.  &lt;a href=&quot;https://www.youtube.com/watch?v=CLYyy1U_Y2A&quot;   title=&quot;A Finkierlkraut le wokisme  par Le Figaro&quot;&gt; La culture et l'éducation &lt;/a&gt; sont pour lui des remparts contre la barbarie moderne, qu'elle soit technologique ou identitaire. &lt;/p&gt; &lt;p&gt;Ses réflexions portent sur l'antisémitisme contemporain, le déclin de la littérature, la nostalgie du passé et les dangers du politiquement correct. Pessimiste sur la &quot;destitution de l'Occident&quot; par la globalisation et le numérique, il prône un retour à la raison critique et à l'universalisme exigeant, loin des illusions du Progrès. &lt;/p&gt;   &lt;audio controls title=&quot;La langue française évolue Alain Finkielkraut par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10241-19.01.2026-ITEMA_24378393-2026F10815S0019-NET_MFI_36E8E6AA-9496-4465-B102-85331E19F173-22-d13018db268bb69d47041561b5f2965e.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10; &#10;" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Roger-Pol_Droit&quot;   title=&quot; Wikipedia&quot;&gt;Roger-Pol DROIT&lt;/a&gt; est un philosophe et écrivain français connu à la fois pour ses travaux de recherche et pour ses livres de vulgarisation qui  &lt;a href=&quot;https://rpdroit.com/&quot;   title=&quot;Roger-Pol DROIT&quot;&gt; rendent la philosophie accessible &lt;/a&gt; à un large public. Sa philosophie ne se présente pas comme un système fermé, mais comme une manière d’ouvrir les questions, de faire dialoguer les idées et de montrer que penser est une activité vivante. Dans ses ouvrages d’initiation, il cherche à expliquer la pensée sans jargon, avec clarté et souvent avec pédagogie, comme dans La philosophie expliquée à ma fille ou &lt;a href=&quot;https://www.youtube.com/watch?v=I-GcL40sLGg&quot;   title=&quot;Il nous parle de philosophie par Bibliothèque de poche&quot;&gt; Une brève histoire de la philosophie &lt;/a&gt; . Pour lui, la philosophie n’est pas réservée aux spécialistes : elle commence par l’étonnement, la curiosité et le besoin de comprendre. &lt;/p&gt; &lt;p&gt; Il insiste sur le dialogue et l’exercice de l’objection et il voit la pensée comme une conversation intérieure et extérieure, où l’on apprend à examiner une idée, à la contredire, puis à la reformuler. Cette approche apparaît aussi dans ses récits philosophiques, qui mêlent réflexion, humour et narration pour faire sentir que penser engage toute la vie intérieure. &lt;/p&gt; &lt;p&gt; Un autre axe important de son travail est l’ouverture aux philosophies du monde. Il s’est intéressé aux rapports entre la pensée occidentale et les traditions venues d’ailleurs, notamment aux représentations des philosophies non occidentales dans la culture européenne. Son livre &lt;a href=&quot;https://www.youtube.com/watch?v=NF9rLrveAbI&quot;   title=&quot;Roger-Pol DROIT par editions albin michel&quot;&gt; Un voyage dans les philosophies du monde &lt;/a&gt; va dans ce sens : il montre que la philosophie ne se limite pas à l’Europe et qu’elle prend des formes multiples selon les cultures. &lt;/p&gt; &lt;p&gt; Sa démarche est profondément humaniste. Il relie la philosophie aux inquiétudes concrètes du présent, à la liberté, à la vie commune, aux limites de l’action et aux questions morales. Chez lui, philosopher ne consiste pas seulement à produire des concepts, mais à apprendre à mieux vivre, à mieux juger et à mieux habiter le monde. &lt;/&gt; &#10; &lt;audio controls title=&quot;un équilibre instable entre la négatif et le positif par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16173-20.05.2025-ITEMA_24141042-2025F26104S0140-NET_MFI_83506534-46B8-430C-8970-C247B9C3C4C4-27.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" display="https://www.laphilo.fr/pho/rpdroit-mini.webp" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philippe_Descola&quot;   title=&quot; Wikipedia&quot;&gt;Philippe DESCOLA&lt;/a&gt; est un anthropologue français spécialiste de l’Amazonie, il a consacré une partie importante de ses recherches aux Achuar, un peuple &lt;a href=&quot;https://www.youtube.com/watch?v=d4VRtkRg-_o&quot;   title=&quot;Etudier les Jivaros Achaur d’amazonie par RFI&quot;&gt; jivaro de Haute-Amazonie.&lt;/a&gt;  Ses travaux cherchent principalement à comprendre comment les différentes sociétés établissent des relations avec les animaux, les plantes, les objets, les esprits et leur environnement. &lt;/p&gt; &lt;p&gt;  Son œuvre la plus connue est Par-delà nature et culture, publiée en 2005. Dans ce livre, il critique la séparation entre la nature et la culture, séparation qui lui paraît caractéristique de la pensée occidentale moderne. Selon lui, cette distinction n’est pas universelle : toutes les sociétés ne considèrent pas les humains comme appartenant à un domaine culturel séparé d’une nature extérieure et objective. Il propose donc d’étudier différentes manières de composer le monde et d’identifier les êtres qui l’habitent. &lt;/p&gt; &lt;p&gt; Pour effectuer cette comparaison, il distingue quatre grandes ontologies : l’animisme, le totémisme, l’analogisme et le naturalisme. L’animisme reconnaît une intériorité semblable aux humains et aux non-humains, mais des corps différents ; le naturalisme, caractéristique des sociétés occidentales modernes, suppose au contraire une même nature physique, mais une intériorité principalement attribuée aux humains. Le totémisme établit une continuité entre certains humains et certains non-humains, tandis que l’analogisme conçoit le monde comme une multiplicité d’êtres différents reliés par des correspondances. &lt;/p&gt; &lt;p&gt; Il ne présente pas ces quatre ontologies comme des étapes successives de l’évolution de l’humanité. Il ne dit pas non plus qu’une société entière correspond toujours parfaitement à un seul modèle. Il s’agit plutôt de grands schèmes permettant de comparer les façons dont les sociétés organisent leurs rapports avec les existants. Son originalité consiste donc à prendre au sérieux les conceptions non occidentales du monde, sans les interpréter automatiquement comme des croyances irrationnelles ou comme des versions incomplètes de la science moderne. &lt;/p&gt; &lt;p&gt; Sa pensée dépasse ainsi l’anthropologie proprement dite et rejoint la philosophie, l’écologie et la réflexion sur la crise environnementale. En montrant que &lt;a href=&quot;https://www.youtube.com/watch?v=fV2VqJhxuEE&quot;   title=&quot;la nature n’existe pas par blast, le souflle de l’info&quot;&gt; la nature n’est pas partout &lt;/a&gt; conçue comme une réalité extérieure exploitable, il invite à repenser la place de l’être humain dans le monde. Parmi ses autres ouvrages importants figurent La Nature domestique, Les Lances du crépuscule, L’Écologie des autres, La Composition des mondes et Les Formes du visible. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Nous sommes les hotes de la terre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/26684-21.05.2026-ITEMA_24520316-2026F49008S0141-NET_MFI_7313D6B1-DF3B-42D0-AD80-7A8884697517-27-c968a5478f57024ca66b57343b59f5c9.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" display="https://www.laphilo.fr/pho/pdescola-mini.webp" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Jullien&quot;  title=&quot; Wikipedia&quot;&gt;François JULLIEN&lt;/a&gt; est un philosophe français, à la fois helléniste et sinologue, connu pour avoir construit un dialogue suivi entre la pensée européenne (surtout grecque) et la pensée chinoise. Il séjourne longuement en Asie (notamment à Tokyo) et soutient deux thèses, l’une sur l’écrivain chinois Lu Xun, l’autre sur l’interprétation poétique dans la tradition chinoise, ce qui fonde son approche de  &lt;a href=&quot;https://www.berlol.net/foire/fle98ju.htm&quot;  title=&quot;le détour d'un grec par la chine par berlol.net&quot;&gt;l’altérité culturelle.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Son projet central consiste à &quot;dépayser&quot; la pensée européenne en la confrontant à la Chine, afin de faire apparaître les présupposés cachés de la philosophie occidentale. Il insiste sur le fait que la rencontre des pensées ne doit pas viser l’exotisme, mais ouvrir un espace &quot;entre&quot; les cultures où se travaille un véritable commun, différent de l’uniforme qu’on confond trop vite avec l’universel. &lt;/p&gt; &lt;p&gt; Il travaille la notion d’&quot;écart&quot; : au lieu de chercher ce qui est semblable entre les cultures, il valorise leurs écarts comme lieu de réflexion et de création conceptuelle. De cet écart naît un &quot;entre&quot; : un espace de tension fécond où se construit le commun, sans effacer les différences. Il propose aussi un déplacement majeur : passer de la pensée de l’&quot;être&quot; à une pensée du &quot;vivre&quot;, plus attentive aux processus, aux transformations et à l’expérience concrète de l’existence. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme le &quot;Traité de l’efficacité&quot;, il oppose la manière occidentale d’agir à une logique chinoise de l’efficience, qui mise sur les tendances de la situation et les transformations continues. L’idée est moins de choisir un camp que de se servir de cet  &lt;a href=&quot;https://www.youtube.com/watch?v=RAgmn0mbUnQ&quot;  title=&quot;François Jullien, entrer dans la pensée chinoise par deodaTV&quot;&gt;écart Chine/Europe &lt;/a&gt; pour repenser nos pratiques de l’action, de la stratégie et de la décision dans le monde contemporain. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;L’art de « décoïncider » selon François Jullien  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13957-13.02.2021-ITEMA_22573157-2021C22785S0044.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Olivier_Abel&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Olivier ABEL&lt;/a&gt;  est un philosophe français spécialiste en éthique et philosophie morale, influencé par Paul Ricœur, Emmanuel Levinas et la tradition protestante. Il soutient en 1983 une thèse sur la rêverie chez Gaston Bachelard sous la direction de Ricœur, puis une habilitation en 2000 sur le temps éthique entre courage et pardon. &lt;/p&gt; &lt;p&gt; Créateur du Fonds Ricœur à Paris, doyen de la Faculté protestante de Paris, il a présidé la Commission d'éthique de la &lt;a href=&quot;https://www.lavie.fr/idees/histoire/olivier-abel-avec-le-catholicisme-leffort-fait-partie-du-chemin-pour-acceder-a-la-grace-100952.php&quot;  title=&quot;Olivier Abel : Avec le catholicisme, l’effort fait partie du chemin pour accéder à la grâce par la Vie&quot;&gt;Fédération protestante &lt;/a&gt;  de France et est membre de l'Académie de Nîmes depuis 2018. Il est aussi membre du Comité consultatif national d'éthique et contribue à des revues comme Esprit. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'éthique interrogative, le pardon, la conversation, l'Europe et les penseurs protestants comme Calvin ou Bayle. Parmi ses ouvrages : L’éthique interrogative (2000), Le pardon, briser la dette et l’oubli (1991), Le vertige de l’Europe (2019),  &lt;a href=&quot;https://www.youtube.com/watch?v=G1_ynk7E7LQ&quot; title=&quot;Olivier Abel, philosophe : Le signe de l’humiliation, c’est cette parole rentrée par FRANCE 24&quot;&gt;De l’humiliation &lt;/a&gt; (récent) et La naissance, qu’est-ce que ça change. Il explore la fugacité des liens humains et une critique du sujet délié. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Le témoin du vendredi : Olivier Abel, la civilisation européenne par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/11739-12.04.2019-ITEMA_22034063-2019F17009S0102-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pascal_Engel&quot;   title=&quot; Wikipedia&quot;&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent &quot;La Norme du vrai&quot; paru en 1989 sur la philosophie de la logique, &lt;a href=&quot;https://www.youtube.com/watch?v=ivsIBYFN6DI&quot; title=&quot;*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos&quot;&gt; &quot;Va savoir&quot;&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et &quot;Les vices du savoir&quot; en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il l défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Faut-il faire la morale aux intellectuels ?  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J.G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime un séminaire sur les décolonisations avec l'Université de Louvain-la-Neuve. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href=&quot;https://www.youtube.com/watch?v=vEQWmSo67B4&quot; style=&quot;color:#88A1E9&quot; title=&quot;Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches&quot;&gt;&quot;Ce sont d'autres gens&quot; &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la &quot;qualité de la vie&quot; sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href=&quot;https://www.youtube.com/watch?v=ZDpbSRrWIhU&quot; title=&quot;Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées&quot;&gt;&quot;autre monde&quot; &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Sandra_Laugier&quot; title=&quot; Wikipedia&quot;&gt;Sandra LAUGIER&lt;/a&gt;  est une philosophe française, professeure à l’université Paris 1 Panthéon-Sorbonne, membre de l’Institut Universitaire de France et spécialiste de philosophie du langage, de philosophie morale et de philosophie politique. Elle a aussi beaucoup travaillé sur Stanley Cavell, qu’elle a traduit en français, ainsi que sur Emerson, Thoreau et le perfectionnisme moral. &lt;/p&gt; &lt;p&gt; Sa philosophie accorde une place centrale à l’ordinaire : les gestes, les paroles, les liens quotidiens et les formes de vie concrètes sont pour elle des lieux essentiels de la pensée. Elle défend l’idée qu’il faut partir de l’expérience vécue plutôt que de grands systèmes abstraits, ce qui l’a conduite à développer une éthique du care, une réflexion sur le langage ordinaire et une attention aux formes discrètes de la vie commune. &lt;/p&gt; &lt;p&gt; Sur le plan politique, elle s’intéresse aux formes contemporaines de démocratie, à &lt;a href=&quot;https://www.youtube.com/watch?v=nlM-aPBIRdg&quot; title=&quot;Sandra Laugier : reconnaître nos dépendances par France Inter&quot;&gt;la désobéissance civile &lt;/a&gt; et aux mouvements horizontaux comme Nuit debout. Elle y voit une manière de repenser le politique à partir de l’expression des personnes, du souci du commun et de l’égalité effective des droits, plutôt que d’un modèle hiérarchique classique. Cette perspective la conduit à défendre une démocratie plus attentive aux voix singulières et aux pratiques collectives concrètes. &lt;/p&gt; &lt;p&gt; Elle a aussi élargi la philosophie à la culture populaire, notamment &lt;a href=&quot;https://www.youtube.com/watch?v=Rjd2XEvkqWc&quot; title=&quot;Sandra Laugier : nos vies en séries par librairie mollat&quot;&gt;aux séries télévisées, &lt;/a&gt; qu’elle considère comme un laboratoire d’expériences morales et politiques. Dans des ouvrages récents, elle montre que les séries peuvent aider à penser nos manières de vivre, nos attachements et nos conflits, en révélant des aspects très actuels de la sensibilité démocratique. &lt;/p&gt;  &lt;audio controls title=&quot;L’éthique animale avec Florence Burgat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" display="https://www.laphilo.fr/pho/slaugier-mini.webp" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon&quot;  title=&quot; Wikipedia&quot;&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href=&quot;https://www.youtube.com/watch?v=xOKttB1HgSk&quot;  title=&quot;Marc Crépon sur la violence  par France Inter &quot;&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href=&quot;https://www.youtube.com/watch?v=kwFC9MSSWcg&quot;  title=&quot;Marc Crépon : l’épreuve de la haine   par Librairie mollat &quot;&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; On peut dire qu’il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste.  &lt;/p&gt; &lt;audio controls title=&quot;Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Audi&quot;  title=&quot; Wikipedia&quot;&gt;Paul AUDI&lt;/a&gt;  est un philosophe et écrivain français né à Beyrouth, au Liban, et ancien élève de l'École normale supérieure. Agrégé de philosophie et docteur en philosophie, il a soutenu une thèse sur Jean-Jacques Rousseau publiée en 1997. Après avoir enseigné à l'université de Paris-XII, il s'est éloigné du champ universitaire pour s'orienter vers l'édition, et aujourd'hui il est professeur invité dans diverses institutions en France et à l'étranger. Il est auteur de plus d'une trentaine d'ouvrages et membre de l'équipe de recherches PHILéPOL à l'université Paris Descartes. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre principalement sur les relations entre l'éthique et l'esthétique en Occident durant les Temps Modernes. Son œuvre explore ces liens à travers des &lt;a href=&quot;https://www.youtube.com/watch?v=3GRhkvYGMs0&quot;  title=&quot;Paul Audi contrat social par le nouvel Obs&quot;&gt;lectures de Rousseau, &lt;/a&gt;  Nietzsche, Lacan, Schopenhauer et Georges Bataille. Il est considéré comme un philosophe atypique, commençant à être reconnu hors de France. Sa pensée conjugue la vie du corps et la création artistique, l'éthique et la passion, avec un souci d'ancrer la pensée dans la vie physique. &lt;/p&gt; &lt;p&gt; L'idée centrale de sa philosophie est que l'acte de création et le comportement éthique ne forment qu'un seul et même geste, qui naît de la vie elle-même et finalement l'excède. Il nomme cette fusion « esth/éthique », considérant que l'éthique et l'esthétique dans l'acte de créer se confondent ou sont le recto et verso d'une même « explication avec la vie ». Pour lui, créer revient à « s'expliquer avec la vie », à faire de l'énigme que nous sommes une bribe d'un discours neuf. &lt;/p&gt; &lt;p&gt; L'éthique, selon lui, consiste d'abord en un travail sur soi, où « c'est moi-même qui suis la tâche ». La philosophie ne s'accomplit qu'au sein d'un corps à corps avec ce qui, en nous-mêmes, nous dépasse — non pas le monde ou un dehors, mais ce qui nous situe sur le  &lt;a href=&quot;https://www.youtube.com/watch?v=FJsDRUR9bYQ&quot;  title=&quot;Paul Audi il faut le nuance par France Inter&quot;&gt;« plan de la vie », &lt;/a&gt; qui ne recouvre ni le champ social ni l'espace politique. Cette éthique de la création, qu'il dénomme « esthéthique », n'est pas un code de règles mais une posture existentielle, une manière de se situer face au monde. &lt;/p&gt; &lt;p&gt; Il  s'intéresse également aux conditions permettant à l'être humain d'accéder à sa propre humanité, et interroge profondément la question de l'identité. Dans son ouvrage Troublante identité (2022), il parle pour la première fois de lui-même et de ce qui le hante, résistant à toute réduction de son être à sa provenance libanaise. Il désire en finir avec les clôtures identitaires et trouve son émancipation dans une conception juive d'une identité ouverte, toujours à construire, guidée par un impératif de justice à venir. Son dernier essai Le Vrai du beau (2026) transforme la contemplation d'un tableau en expérience de vérité, éclaircissant ce qui se joue en nous face à un tableau. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;la verité picturale existe t’elle ?  Par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/26657-24.04.2026-ITEMA_24487813-2026F45096S0114-NET_MFI_F40118A5-5297-4676-86E9-2E9A248FB2F7-27-03023a67ff6f93208a5f302d7d3b8771.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" display="https://www.laphilo.fr/pho/paudi-mini.webp" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" display="https://www.laphilo.fr/pho/cmichon-mini.webp" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Corine_Pelluchon&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href=&quot;https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s&quot; title=&quot;NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco&quot;&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &#10;&lt;p&gt; - Manifeste animaliste. Politiser la cause animale ( 2017 )  - Éthique de la considération ( 2018) - Réparons le monde. Humains, animaux, nature (2020)  &#10; - Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &#10;&lt;p&gt; -   &lt;a href=&quot;https://www.youtube.com/watch?v=zpzzDqYhF-8&quot; title=&quot;Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat&quot;&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href=&quot;https://www.youtube.com/watch?v=tmk-UzN1j70&quot;  title=&quot;Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media&quot;&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title=&quot;Corine Pelluchon par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" display="https://www.laphilo.fr/pho/cfmetterie-mini.webp" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vincent_Delecroix&quot;  title=&quot; Wikipedia&quot;&gt;Vincent DELECROIX&lt;/a&gt;  est un philosophe français spécialiste de Kierkegaard et de la philosophie de la religion. Il enseigne à l’EPHE, où il travaille sur la vérité, la croyance et les liens entre religion et pensée contemporaine. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse d’abord à la manière dont la foi peut exister dans un monde moderne où les certitudes absolues se  &lt;a href=&quot;https://www.youtube.com/watch?v=2ZHOpP5GMwI&quot; title=&quot;Vincent DELECROIX,la nécessité d’apprendre par TV5 monde&quot;&gt;sont affaiblies. &lt;/a&gt; Il ne traite pas la religion comme un simple héritage figé, mais comme une expérience intérieure, fragile et exigeante.  &lt;/p&gt; &lt;p&gt; Un autre axe important chez lui est la révolte. À travers des livres comme Tombeau d’Achille et Non ! De l’esprit de révolte, il réfléchit à la colère, au refus et à la parole &lt;a href=&quot;https://www.youtube.com/watch?v=OiUgp6wLpCA&quot; title=&quot;Vincent DELECROIX il faut sortir du oui non par France Culture&quot;&gt;qui dit non, &lt;/a&gt; non comme de simples réactions, mais comme des forces qui révèlent une vérité humaine et morale. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il  est un philosophe de la tension entre vérité, foi et révolte. Sa pensée cherche à comprendre comment l’être humain peut garder une voix, une conscience et une exigence spirituelle dans un monde désorienté. &lt;/p&gt;  &lt;audio controls title=&quot;Vincent DELECROIX  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89douard_Mehl&quot;  title=&quot; Wikipedia&quot;&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href=&quot;https://www.youtube.com/watch?v=NT0n7tKNb3w&quot; title=&quot;qu’est ce que la verité par Le forum Veritas&quot;&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. &lt;/p&gt; &#10;&#10;" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Barbara_Stiegler&quot; title=&quot; Wikipedia&quot;&gt;Barbara STEIGLER&lt;/a&gt;  est une philosophe française, fille du philosophe Bernard Stiegler, spécialiste de Nietzsche, de philosophie politique et critique du néolibéralisme. Agrégée de philosophie, elle soutient sa thèse en 2003 à Paris-Sorbonne sous la direction de Jean-Luc Marion sur Nietzsche et la biologie. Maître de conférences puis professeure à l'université Bordeaux-Montaigne depuis 2006, elle y dirige le master  &lt;a href=&quot;https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf&quot; title=&quot;Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne&quot;&gt;&quot;Soin, éthique et santé&quot;. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Engagée politiquement, elle analyse les Gilets Jaunes dans &quot;Du cap aux grèves&quot; paru en 2021 et critique l’adaptationnisme comme fondement du néolibéralisme, opposant une intelligence collective à l’élitisme technocratique. &lt;/p&gt; &lt;p&gt; Ses ouvrages sur Nietzsche explorent le corps et la vie (Nietzsche et la biologie, 2001 ; Nietzsche et la critique de la chair, 2005 ; Nietzsche et la vie, 2021). &lt;/p&gt; &lt;p&gt;  Elle étend ses recherches au politique avec  &lt;a href=&quot;https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/&quot; title=&quot;Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit&quot;&gt;&quot;Il faut s’adapter&quot; &lt;/a&gt; paru en  2019, dénonçant les racines évolutionnistes (Spencer, Lippmann) du &lt;a href=&quot;https://www.youtube.com/watch?v=oQQ4xqRvYTk&quot; style=&quot;color:#88A1E9&quot; title=&quot;LA LENTE AGONIE DU NÉOLIBÉRALISME  par &#10;TheSwissBox Conversation&quot;&gt;néolibéralisme &lt;/a&gt; face au pragmatisme démocratique de Dewey. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" display="https://www.laphilo.fr/pho/bastiegler-mini.webp" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89ric_Sadin&quot;  title=&quot; Wikipedia&quot;&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href=&quot;https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur&quot; style=&quot;color:#88A1E9&quot;   title=&quot; Éric SADIN contre ChatGPT par Senseur&quot;&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;&#10;Sadin s'est fait connaître grâce à son livre &quot;La société de l'anticipation &quot; publié en 2011, dans lequel il examine l'émergence de la société de la surveillance et des technologies de prévision qui cherchent à anticiper les comportements et les désirs des individus. Il y aborde notamment les thèmes de la surveillance généralisée, de la collecte de données personnelles et des risques de manipulation. &lt;/p&gt; &lt;p&gt;&#10;Dans son ouvrage &lt;a href=&quot;https://christian-biales.fr/wp-content/uploads/2020/12/Sadin.pdf&quot;  title=&quot;Extrait du livre par Christian Bialès&quot;&gt; &quot;L'Ère de l'individu tyran : la fin d'un monde commun&quot;&lt;/a&gt; paru en 2013, Sadin explore les conséquences de la numérisation de la société sur les notions de vie privée, de liberté individuelle et de démocratie. Il met en garde contre le pouvoir croissant des grandes plateformes technologiques et la manière dont elles peuvent influencer et contrôler nos comportements et nos choix. &lt;/p&gt; &lt;p&gt;&#10;Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre &quot;La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique&quot; publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href=&quot;https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008&quot;  title=&quot;Dataïsme par lebigdata&quot;&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title=&quot;Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau&quot; title=&quot; Wikipedia&quot;&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href=&quot;https://www.youtube.com/watch?v=PNMZHr3L_Ws&quot; title=&quot; Vivons nous dans un multivers par Aurelien Barrau&quot;&gt; concept de multivers&lt;/a&gt; , et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage &quot;Chaos multiples&quot; et &quot;De la vérité dans les sciences&quot;  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé &quot;Météorites&quot;. &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de &quot;sauver le climat&quot; plutôt &quot;qu’agir pour la vie&quot;. &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  &quot;habiter la science en poète&quot; en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href=&quot;https://www.youtube.com/watch?v=94IxSYo5wtM&quot; title=&quot;Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter&quot;&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href=&quot;https://www.youtube.com/watch?v=g3Z_LsXD7DU&quot; title=&quot; L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac&quot;&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un &quot;faire monde&quot; éthique et conscient. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Aurelien BARRAU par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin&quot; title=&quot; Wikipedia&quot;&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href=&quot;https://charlespepin.fr/&quot;  title=&quot; Site officiel Charles Pépin &quot;&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href=&quot;https://www.youtube.com/watch?v=WExeoL6qVmc&quot; title=&quot; Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori&quot;&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href=&quot;https://www.youtube.com/watch?v=orOxuIHT_vc&quot; title=&quot;Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal&quot;&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt; - &quot;Les Vertus de l’échec&quot; publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt; - &quot;La Confiance en soi &quot; paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt; - &quot;La Rencontre&quot;  en 2021 et &quot;Vivre avec son passé&quot; en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href=&quot;https://www.youtube.com/watch?v=M09YmUzDwO8&quot; title=&quot; Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs&quot;&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; La philosophie selon Charles Pépin par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel&quot;  title=&quot; Wikipedia&quot;&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un &quot;philosophe de la liberté&quot;. Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que &quot;être de gauche&quot; signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;La privation de l’intime&quot; paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href=&quot;https://www.youtube.com/watch?v=HcDfUGypNvA&quot; style=&quot;color:#88A1E9&quot; title=&quot;Michaël Fœssel - Récidive, 1938 par Librairie mollat&quot;&gt;&quot;Récidive. 1938&quot;&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme &quot;laboratoire&quot; pour comprendre les fragilités  &lt;a href=&quot;https://www.youtube.com/watch?v=wdeS7SFEz7Y&quot;  title=&quot;Démocratie illibérale par Michaël Foessel par France Culture&quot;&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 &quot;Quartier rouge. Le plaisir et la gauche&quot;, il interroge le rapport de  &lt;a href=&quot;https://www.youtube.com/watch?v=MDubXJZox34&quot; title=&quot;Michaël Foessel : &quot;La question du plaisir est aujourd'hui centrale en politique&quot; par France Inter&quot;&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment &quot;Vers la paix perpétuelle&quot; et &quot;La religion dans les limites de la simple raison&quot;, tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title=&quot;La gauche : état des lieux  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Baptiste_Jeang%C3%A8ne_Vilmer&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Baptiste JEANGENE VILMER&lt;/a&gt;  est un philosophe, politologue et juriste français spécialiste de l’éthique de la guerre, du droit international et des relations internationales, et également diplomate (ambassadeur de France au Vanuatu depuis 2022). Il est formé dans trois disciplines : philosophie (licence, master, doctorat), droit (licence, LLM, postdoctorat) et science politique (doctorat). &lt;/p&gt; &lt;p&gt; Sa thèse porte sur &quot;l’intervention militaire justifiée par des raisons humanitaires&quot;, à la croisée de philosophie politique, droit international et théorie des relations internationales. Il défend en théorie des relations internationales un &quot;réalisme libéral&quot; inspiré de Raymond Aron, Stanley Hoffmann et Pierre Hassner : reconnaissance du tragique et des &lt;a href=&quot;https://www.youtube.com/watch?v=4EECHNFvt4Q&quot;  title=&quot; J-B. Jeangène Vilmer - Synthèse par Institut Guerre et Paix&quot;&gt;rapports de force, &lt;/a&gt;  mais attachée au droit international, aux droits humains et aux institutions. &lt;/p&gt; &lt;p&gt; Il se situe à l’intersection de philosophie morale, droit international et stratégie : penser les guerres et interventions non seulement en termes juridiques ou militaires, mais surtout en termes de responsabilité morale (tuer, laisser mourir, protéger). Son &lt;a href=&quot;https://www.jbjv.com/IMG/pdf/JB_Jeangene_Vilmer_2013_-_Pour_un_realisme_liberal_en_relations_internationales.pdf&quot;  title=&quot;Pour un réalisme libéral en relations internationales par jbjv&quot;&gt;&quot;réalisme libéral&quot; &lt;/a&gt; refuse à la fois le cynisme réaliste pur et l’idéalisme naïf, il cherche des critères prudents mais exigeants pour juger les interventions, la justice pénale, ou la responsabilité des États. &lt;/p&gt; &lt;p&gt; Il insiste sur les dilemmes : parfois, intervenir violemment peut sauver des vies, mais peut aussi aggraver le conflit ; parfois, poursuivre les criminels peut fragiliser la paix. Sa pensée explore ces tensions plutôt que de proposer des solutions simplistes. &lt;/p&gt; &#10;&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   &#10;" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" display="https://www.laphilo.fr/pho/nykisukidi-mini.webp" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" display="https://www.laphilo.fr/pho/jdfunes-mini.webp" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tristan_Garcia&quot; title=&quot; Wikipedia&quot;&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. &lt;/p&gt; &lt;p&gt; Son œuvre majeure &quot;Forme et objet. Un traité des choses&quot; paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie &quot;plate&quot; qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans &quot;Nous&quot; ou &quot;La Vie intense&quot; paru en 2016, il explore l’appartenance à des collectifs variables &quot;nous humains&quot;, &quot;nous animaux&quot; et critique l’obsession moderne pour  &lt;a href=&quot;https://www.youtube.com/watch?v=JTLVzryyyEg&quot; title=&quot;Tristan Garcia, INTENSITÉ par abc penser&quot;&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (La Meilleure part des hommes, sur le sida) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href=&quot;https://www.youtube.com/watch?v=K_wxi5xTYz8&quot; title=&quot;Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace&quot;&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; &#10; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Tristan Garcia, &quot;La vie intense : une obsession moderne&quot; par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10; " r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Baptiste_Morizot&quot;  title=&quot; Wikipedia&quot;&gt;Baptiste MORIZOT&lt;/a&gt;  est un philosophe français,  maître de conférences à l'université d'Aix-Marseille, dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle. Son approche se distingue par une pratique de terrain ancrée dans l'expérience, notamment le pistage des grands prédateurs comme les loups, ce qui lui permet de nourrir sa pensée philosophique par une observation directe et sensible du vivant.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve l'idée que la crise écologique contemporaine est avant tout une « crise de la sensibilité » et de nos relations avec le reste du monde vivant. Il soutient que la pensée moderne, marquée par un dualisme qui sépare strictement l'humain de la nature, nous a &lt;a href=&quot;https://www.youtube.com/watch?v=bAnXnPnnHCk&quot; title=&quot;Baptiste Morizot, meme penseur on est un animal par France Inter&quot;&gt;rendus aveugles et sourds &lt;/a&gt; aux autres espèces, qu'il préfère considérer comme d'autres « manières d'être vivant » plutôt que comme des êtres inférieurs. &lt;/p&gt; &lt;p&gt; Il propose ainsi de remplacer le modèle classique de la « maîtrise de la nature » par une « diplomatie des interdépendances ». Cette approche invite les humains à se concevoir comme des partenaires au sein d'un réseau complexe d'interdépendances, où il s'agit de tisser des alliances concrètes, de prêter attention aux signaux émis par les autres espèces et d'apprendre à cohabiter avec elles dans un esprit de respect et de responsabilité partagée. &lt;/p&gt; &lt;p&gt; Son travail, qui mêle récit, enquête éthologique et essai théorique, cherche à réenchanter &lt;a href=&quot;https://www.youtube.com/watch?v=uQZcktq_W3E&quot; title=&quot;Baptiste Morizot, remet l’humain à sa place par La Grande Librairie&quot;&gt;notre rapport au monde &lt;/a&gt; en réactivant nos capacités d'attention et d'intelligence sensible. En invitant à une forme de sagesse pragmatique et ancrée, il s'efforce de refonder notre culture environnementale, non pas pour dominer ou sanctuariser la nature, mais pour s'ajuster avec humilité à la diversité des formes de vie qui partagent la Terre avec nous. &lt;/p&gt;  &lt;audio controls title=&quot;Liberté, dignité, habitalité avec baptiste MORIZOT par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18558-25.04.2026-ITEMA_24488881-2026F30378S0115-NET_MFI_D6CADDF4-ADD5-4D3F-AA1D-625272E9CD3C-22-b98aedea0426383b486dc3819cb77a8e.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" display="https://www.laphilo.fr/pho/ydallaglio-mini.webp" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Norman_Ajari&quot;  title=&quot; Wikipedia&quot;&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href=&quot;https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari&quot;  title=&quot;Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse&quot;&gt;&quot;études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href=&quot;https://www.youtube.com/watch?v=IMUBi9oi2WM&quot; title=&quot;Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche&quot;&gt;&quot;colonialité de l’être&quot; &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=ECSmpOXY8kg&quot; title=&quot;NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS&quot;&gt;&quot;La Dignité ou la mort&quot;, &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de &quot;philosophe militant&quot; : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. &lt;/p&gt; &lt;audio controls title=&quot;où commence et où finit le racisme? par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" display="https://www.laphilo.fr/pho/mmaeso-mini.webp" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anne_Fagot-Largeault&quot;  title=&quot; Wikipedia&quot;&gt;Anne FAGOT-LARGEAULT&lt;/a&gt;  est une une philosophe et psychiatre française, élève de l’École normale supérieure de jeunes filles, agrégée de philosophie en 1961, elle a combiné une carrière académique brillante – professeur à Paris 1 Panthéon-Sorbonne puis au Collège de France (chaire de philosophie des sciences biologiques et médicales de 2000 à 2009) – avec une pratique hospitalière en psychiatrie à l’hôpital Henri-Mondor de Créteil. Membre de l’Académie des sciences depuis 2002, elle incarne une figure rare à la croisée de la médecine, de la philosophie et des sciences du vivant. &lt;/p&gt; &lt;p&gt;  Sa philosophie se déploie dans trois &lt;a href=&quot;https://www.youtube.com/watch?v=LYwHBFs7elQ&quot; title=&quot; Philosophie des sciences biologiques et médicales et philosophie par Collège de France&quot;&gt; directions principales, &lt;/a&gt; toutes liées à l’épistémologie et à l’ontologie des sciences biologiques et médicales. D’abord, elle analyse le raisonnement diagnostique : logique inductive, probabilités, heuristiques, en soulignant les limites de la certitude dans un domaine probabiliste par nature. Ensuite, elle interroge la causalité : distinction entre causalité mécanique et téléologique, preuves épidémiologiques, rôle des modèles explicatifs dans la compréhension du vivant. Enfin, elle s’attache à l’éthique : méthodologie des essais cliniques, dilemmes bioéthiques, responsabilité dans un univers contingent où l’humain influence activement l’avenir. &lt;/p&gt; &lt;p&gt; Dans ses ouvrages comme Ontologie du devenir ou Médecine et philosophie, elle revisite les thèmes du temps, de l’évolution et du vivant en dialogue avec Héraclite, Bergson ou les sciences modernes. Elle défend une science du devenir contre l’immobilisme parmnénidien : le flux permanent du réel exige des concepts fluides, une intuition intellectuelle capable de saisir l’instabilité des êtres vivants sans les figer en essences. L’évolution darwinienne, loin d’être une téléologie, révèle un univers de contingences où l’action humaine porte une responsabilité prospective . &lt;/p&gt; &lt;p&gt;     &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_2016_hos_114_1_8513&quot; title=&quot; laudatio de la professeure par persée&quot;&gt; Son apport &lt;/a&gt; le plus original réside dans une anthropologie bio-médicale qui refuse le réductionnisme : la médecine suppose une métaphysique du mal, une épistémologie du normal/pathologique et une éthique équilibrant l’autonomie individuelle, le bien du patient et l’intérêt collectif. Professeure honoraire influente, elle a formé des générations à penser la vie non comme un donné stable, mais comme un processus à comprendre et à orienter éthiquement.&lt;/p&gt;                                                                      &lt;audio controls title=&quot;Médecine et philosophie avec Anne Fagot-Largeault par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10201-08.03.2010-ITEMA_20218761-2010C10593E0008-NET_01E69962-F316-4C45-826B-43707F9BD385_FC-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" display="https://www.laphilo.fr/pho/rdebray-mini.webp" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christian_Jambet&quot;  title=&quot; Wikipedia&quot;&gt;Christian JAMBET&lt;/a&gt; est un philosophe et islamologue  français reconnu pour ses travaux qui font le pont entre la philosophie occidentale et la pensée islamique, en particulier le chiisme. Agrégé de philosophie et ancien élève d'Henry Corbin, un spécialiste de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Islam_en_Iran&quot;  title=&quot; Islam en Iran par Wikipedia&quot;&gt;l'islam iranien&lt;/a&gt;, il a consacré sa carrière à l'étude des traditions philosophiques et spirituelles de l'Islam, notamment celles de l'Iran. Il est devenu membre de l'Académie française en 2024. Son travail se distingue par sa profondeur et son caractère interdisciplinaire. Ses contributions majeures portent sur :&lt;/p&gt; &lt;p&gt; - La philosophie islamique : Il a montré qu'il existe une tradition philosophique riche et autonome en terre d'Islam, souvent mal comprise ou négligée en Occident. Il a mis en lumière les liens, mais aussi les spécificités, entre la pensée grecque (notamment platonicienne) et les penseurs islamiques. Son ouvrage Qu'est-ce que la philosophie islamique ? est une référence dans ce domaine. &lt;/p&gt; &lt;p&gt; - Le chiisme et le soufisme : il est un expert du chiisme, qu'il étudie non seulement sous son aspect politique et théologique, mais aussi dans sa dimension philosophique et spirituelle. Il a beaucoup travaillé sur la figure du  &lt;a href=&quot;https://www.youtube.com/watch?v=kQzLVldS4PU&quot;  title=&quot;L'immortalité de l'âme selon Mulla Sadra, Christian Jambet Les vivants et les dieux par Facteur&quot;&gt; philosophe iranien Mullâ Sadrâ Shîrâzî&lt;/a&gt; , qu'il considère comme un des plus grands métaphysiciens de l'histoire. Il explore les concepts de l'ésotérisme (bātin) et de l'exotérisme (zahir), montrant comment la philosophie chiite a développé une pensée de la liberté et de l'intériorité face à l'orthodoxie religieuse. &lt;/p&gt; &lt;p&gt; - La philosophie politique : Il s'intéresse aux conceptions du pouvoir et du droit dans l'Islam. Dans son livre Le gouvernement divin, il analyse la relation entre la théologie et le politique, et les différentes manières dont le pouvoir a été conceptualisé dans le chiisme. &lt;/p&gt; &lt;p&gt; - Les concepts de l'« Ange » et de l'« imagination créatrice » : Reprenant les travaux d'Henry Corbin, il a exploré le rôle central de l'imagination dans la connaissance et l'expérience religieuse. Pour Jambet, l'imagination n'est pas une simple faculté de fiction, mais un organe de perception capable d'accéder à un monde intermédiaire, peuplé d'êtres spirituels comme les Anges. &lt;/p&gt; &lt;p&gt;  Il a publié différents ouvrages dont &quot;L'Ange&quot; paru en 1976 co-écrit avec Guy Lardreau ainsi que &quot;La Logique des Orientaux&quot;  paru en 1983  sans oublié &quot;La Grande Résurrection d'Alamût&quot;  paru en 1990, sur les formes de la liberté dans le shî'isme ismaélien. &lt;/p&gt;  &lt;audio controls title=&quot; La philosophie islamique avec Christian Jambet par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11200-12.02.2012-ITEMA_20344279-2012C14958E0004-ITE_00049063_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernadette_Bensaude-Vincent&quot; title=&quot; Wikipedia&quot;&gt;Bernadette BENSUDE-VINCENT&lt;/a&gt;  est une philosophe française et historienne des sciences. Formée à l'École normale supérieure de Fontenay-aux-Roses, agrégée de philosophie en 1971 et docteure ès lettres en 1981, elle a enseigné à l'université Paris X-Nanterre puis Paris I Panthéon-Sorbonne jusqu'à sa retraite en 2015, où elle est professeure émérite. Elle a dirigé le Centre d'études des techniques, des connaissances et des pratiques (CETCOPRA) et été membre senior de l'Institut universitaire de France. &lt;/p&gt; &lt;p&gt; Elle a occupé des postes invités dans des universités internationales comme Madrid, Vienne ou Bielefeld, et collaboré avec le MIT sur l'histoire des matériaux. Membre de l'Académie des technologies et vice-présidente du comité d'éthique d'organismes comme l'Inrae, elle a contribué à la Cité des sciences et de l'industrie. Auteure d'une centaine d'ouvrages, elle a coordonné des programmes sur l'éthique des nanotechnologies et les technosciences. &lt;/p&gt; &lt;p&gt; Sa pensée critique la rupture bachelardienne entre science et opinion, plaidant pour leur interdépendance dans une &quot;philosophie de terrain&quot;. Elle analyse la chimie, les technosciences et les technologies émergentes comme des pratiques sociales façonnant la matière, questionnant le pouvoir des sciences sur le vivant et la société. Elle rejette &lt;a href=&quot;https://www.youtube.com/watch?v=MRD0LLrjGG8&quot;  title=&quot;bernadette bensaude-vincent : approche philo de la biologie de synthese par Alter Mardis&quot;&gt;les visions réductionnistes &lt;/a&gt; pour souligner les controverses et la pluralité des savoirs. &lt;/p&gt; &lt;p&gt; Dans des essais comme L’Opinion publique et la science ou ses réflexions sur l'Anthropocène, elle promeut une &quot;culture de la défiance&quot; constructive contre la méfiance, favorisant des savoirs robustes. Ses recherches sur les matériaux et la biologie de synthèse interrogent l'hubris humaine, défendant une  &lt;a href=&quot;https://www.youtube.com/watch?v=HnEX-2_p3mQ&quot;  title=&quot;bernadette bensaude-vincent : fait il changer notre rapport au temps par écologie rationnelle&quot;&gt;approche humaniste &lt;/a&gt; des relations science-société et une histoire des sciences attentive aux marges. &lt;/p&gt;    &lt;audio controls title=&quot; Science et recherche: de l’expertise à la sphère publique par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13983-28.04.2021-ITEMA_22649821-2021C16450S0118.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Christian_Godin&quot;   title=&quot; Wikipedia&quot;&gt;Christian GODIN&lt;/a&gt;  est un philosophe français qui a enseigné la philosophie à l’université Blaise-Pascal de Clermont-Ferrand, où il est devenu professeur émérite, et collabore régulièrement à des revues comme Marianne, Le Magazine littéraire et Sciences et Avenir. Il dirige également la revue Cités aux PUF et s’est imposé comme  &lt;a href=&quot;http://www.christian-godin.com/biographie.html&quot;  title=&quot;autobiographie par c godin&quot;&gt; un auteur prolifique, &lt;/a&gt; avec plus d’une cinquantaine d’ouvrages à caractère pédagogique et érudit. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour son monumental travail « La Totalité en sept volumes » (1997-2003), fruit de sa thèse de doctorat, qui explore la notion philosophique de totalité à travers l’histoire de la pensée. Parmi ses autres travaux phares figurent des ouvrages de vulgarisation comme  &lt;a href=&quot;https://www.youtube.com/watch?v=nJga6GYNLUw&quot;  title=&quot;Ephilosophie pour les nuls par Google payer livres&quot;&gt; La Philosophie pour les nuls &lt;/a&gt; (2006), des dictionnaires philosophiques et des essais contemporains tels que La crise de la réalité (2021), où il analyse la destitution du réel par le numérique et les idéologies modernes. Il a aussi réalisé des entretiens avec des penseurs comme Axel Kahn ou Malek Chebel.  &lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est avant tout « un désir de comprendre le monde, de donner du sens, d’expliquer les choses », et elle doit rester ancrée dans le concret pour éviter l’abstraction stérile. Il insiste sur son rôle pédagogique et accessible à tous, invitant à dialoguer avec les grands penseurs comme Platon, Nietzsche ou Hannah Arendt pour aborder des thèmes universels : le sens de la vie, l’amour, la mort. Contrairement à la science focalisée sur la vérité, la philosophie cherche le sens via la critique, le débat intérieur et l’examen des  &lt;a href=&quot;https://www.youtube.com/watch?v=8KzIKZimPSIl&quot;  title=&quot;Etre humain par Philomonaco&quot;&gt; problèmes humains. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il aborde des enjeux actuels comme la crise de la réalité (présentisme, simulationnisme, prédictionnisme), la synchronicité comme signe d’unité divine échappant à la raison, ou la démoralisation contemporaine. Il critique le subjectivisme relativiste, le narcissisme numérique et la technoscience totalitaire qui substitue un monde artificiel à la nature, plaidant pour une pensée multidimensionnelle du réel. Ses analyses, souvent pessimistes sur la virtualité et la post-vérité, défendent une objectivité ancrée dans le monde physique. &lt;/p&gt;     &lt;audio controls title=&quot;Le philosophe Christian Godin tire les leçons du Grand Débat &quot; par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/15343-18.03.2019-ITEMA_22011803-0.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Alain_Finkielkraut&quot;  title=&quot; Wikipedia&quot;&gt;Alain FINKIELKRAUT&lt;/a&gt;  est un philosophe français  et essayiste français né en 1949 à Paris, fils de juifs polonais rescapés de la Shoah. Agrégé de philosophie, il a enseigné brièvement avant de se consacrer à l'écriture et aux médias, notamment via des chroniques radiophoniques sur France Culture. Membre de l'Académie française depuis 2014, il est associé au mouvement des &quot;nouveaux philosophes&quot; post-Mai 68, rompant avec le marxisme pour critiquer les idéologies totalitaires. &lt;/p&gt; &lt;p&gt; Ses essais majeurs incluent La Défaite de la pensée (1987), qui dénonce le relativisme culturel et &lt;a href=&quot;https://www.youtube.com/watch?v=e-uoL-Ve_8c&quot;   title=&quot;A Finkierlkraut et ses clachs tv  par France Tv &quot;&gt; l'appauvrissement intellectuel &lt;/a&gt; moderne, et L'Identité malheureuse (2013), où il analyse la crise de l'identité française face à l'immigration et au multiculturalisme. D'autres livres comme Remembering in Vain (1989) explorent la mémoire de la Shoah et les crimes contre l'humanité, tandis que À la première personne (2019) revisite son parcours personnel.  &lt;/p&gt; &lt;p&gt; Il  défend une pensée humaniste ancrée dans la tradition européenne, influencée par Hannah Arendt, Rousseau et les Lumières. Il rejette le &quot;progressisme&quot; idéologique qui, selon lui, nie les différences culturelles et sapent la civilisation occidentale par un relativisme anti-humaniste.  &lt;a href=&quot;https://www.youtube.com/watch?v=CLYyy1U_Y2A&quot;   title=&quot;A Finkierlkraut le wokisme  par Le Figaro&quot;&gt; La culture et l'éducation &lt;/a&gt; sont pour lui des remparts contre la barbarie moderne, qu'elle soit technologique ou identitaire. &lt;/p&gt; &lt;p&gt;Ses réflexions portent sur l'antisémitisme contemporain, le déclin de la littérature, la nostalgie du passé et les dangers du politiquement correct. Pessimiste sur la &quot;destitution de l'Occident&quot; par la globalisation et le numérique, il prône un retour à la raison critique et à l'universalisme exigeant, loin des illusions du Progrès. &lt;/p&gt;   &lt;audio controls title=&quot;La langue française évolue Alain Finkielkraut par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10241-19.01.2026-ITEMA_24378393-2026F10815S0019-NET_MFI_36E8E6AA-9496-4465-B102-85331E19F173-22-d13018db268bb69d47041561b5f2965e.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10; &#10;" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Roger-Pol_Droit&quot;   title=&quot; Wikipedia&quot;&gt;Roger-Pol DROIT&lt;/a&gt; est un philosophe et écrivain français connu à la fois pour ses travaux de recherche et pour ses livres de vulgarisation qui  &lt;a href=&quot;https://rpdroit.com/&quot;   title=&quot;Roger-Pol DROIT&quot;&gt; rendent la philosophie accessible &lt;/a&gt; à un large public. Sa philosophie ne se présente pas comme un système fermé, mais comme une manière d’ouvrir les questions, de faire dialoguer les idées et de montrer que penser est une activité vivante. Dans ses ouvrages d’initiation, il cherche à expliquer la pensée sans jargon, avec clarté et souvent avec pédagogie, comme dans La philosophie expliquée à ma fille ou &lt;a href=&quot;https://www.youtube.com/watch?v=I-GcL40sLGg&quot;   title=&quot;Il nous parle de philosophie par Bibliothèque de poche&quot;&gt; Une brève histoire de la philosophie &lt;/a&gt; . Pour lui, la philosophie n’est pas réservée aux spécialistes : elle commence par l’étonnement, la curiosité et le besoin de comprendre. &lt;/p&gt; &lt;p&gt; Il insiste sur le dialogue et l’exercice de l’objection et il voit la pensée comme une conversation intérieure et extérieure, où l’on apprend à examiner une idée, à la contredire, puis à la reformuler. Cette approche apparaît aussi dans ses récits philosophiques, qui mêlent réflexion, humour et narration pour faire sentir que penser engage toute la vie intérieure. &lt;/p&gt; &lt;p&gt; Un autre axe important de son travail est l’ouverture aux philosophies du monde. Il s’est intéressé aux rapports entre la pensée occidentale et les traditions venues d’ailleurs, notamment aux représentations des philosophies non occidentales dans la culture européenne. Son livre &lt;a href=&quot;https://www.youtube.com/watch?v=NF9rLrveAbI&quot;   title=&quot;Roger-Pol DROIT par editions albin michel&quot;&gt; Un voyage dans les philosophies du monde &lt;/a&gt; va dans ce sens : il montre que la philosophie ne se limite pas à l’Europe et qu’elle prend des formes multiples selon les cultures. &lt;/p&gt; &lt;p&gt; Sa démarche est profondément humaniste. Il relie la philosophie aux inquiétudes concrètes du présent, à la liberté, à la vie commune, aux limites de l’action et aux questions morales. Chez lui, philosopher ne consiste pas seulement à produire des concepts, mais à apprendre à mieux vivre, à mieux juger et à mieux habiter le monde. &lt;/&gt; &#10; &lt;audio controls title=&quot;un équilibre instable entre la négatif et le positif par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/16173-20.05.2025-ITEMA_24141042-2025F26104S0140-NET_MFI_83506534-46B8-430C-8970-C247B9C3C4C4-27.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" display="https://www.laphilo.fr/pho/rpdroit-mini.webp" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philippe_Descola&quot;   title=&quot; Wikipedia&quot;&gt;Philippe DESCOLA&lt;/a&gt; est un anthropologue français spécialiste de l’Amazonie, il a consacré une partie importante de ses recherches aux Achuar, un peuple &lt;a href=&quot;https://www.youtube.com/watch?v=d4VRtkRg-_o&quot;   title=&quot;Etudier les Jivaros Achaur d’amazonie par RFI&quot;&gt; jivaro de Haute-Amazonie.&lt;/a&gt;  Ses travaux cherchent principalement à comprendre comment les différentes sociétés établissent des relations avec les animaux, les plantes, les objets, les esprits et leur environnement. &lt;/p&gt; &lt;p&gt;  Son œuvre la plus connue est Par-delà nature et culture, publiée en 2005. Dans ce livre, il critique la séparation entre la nature et la culture, séparation qui lui paraît caractéristique de la pensée occidentale moderne. Selon lui, cette distinction n’est pas universelle : toutes les sociétés ne considèrent pas les humains comme appartenant à un domaine culturel séparé d’une nature extérieure et objective. Il propose donc d’étudier différentes manières de composer le monde et d’identifier les êtres qui l’habitent. &lt;/p&gt; &lt;p&gt; Pour effectuer cette comparaison, il distingue quatre grandes ontologies : l’animisme, le totémisme, l’analogisme et le naturalisme. L’animisme reconnaît une intériorité semblable aux humains et aux non-humains, mais des corps différents ; le naturalisme, caractéristique des sociétés occidentales modernes, suppose au contraire une même nature physique, mais une intériorité principalement attribuée aux humains. Le totémisme établit une continuité entre certains humains et certains non-humains, tandis que l’analogisme conçoit le monde comme une multiplicité d’êtres différents reliés par des correspondances. &lt;/p&gt; &lt;p&gt; Il ne présente pas ces quatre ontologies comme des étapes successives de l’évolution de l’humanité. Il ne dit pas non plus qu’une société entière correspond toujours parfaitement à un seul modèle. Il s’agit plutôt de grands schèmes permettant de comparer les façons dont les sociétés organisent leurs rapports avec les existants. Son originalité consiste donc à prendre au sérieux les conceptions non occidentales du monde, sans les interpréter automatiquement comme des croyances irrationnelles ou comme des versions incomplètes de la science moderne. &lt;/p&gt; &lt;p&gt; Sa pensée dépasse ainsi l’anthropologie proprement dite et rejoint la philosophie, l’écologie et la réflexion sur la crise environnementale. En montrant que &lt;a href=&quot;https://www.youtube.com/watch?v=fV2VqJhxuEE&quot;   title=&quot;la nature n’existe pas par blast, le souflle de l’info&quot;&gt; la nature n’est pas partout &lt;/a&gt; conçue comme une réalité extérieure exploitable, il invite à repenser la place de l’être humain dans le monde. Parmi ses autres ouvrages importants figurent La Nature domestique, Les Lances du crépuscule, L’Écologie des autres, La Composition des mondes et Les Formes du visible. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Nous sommes les hotes de la terre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/26684-21.05.2026-ITEMA_24520316-2026F49008S0141-NET_MFI_7313D6B1-DF3B-42D0-AD80-7A8884697517-27-c968a5478f57024ca66b57343b59f5c9.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" display="https://www.laphilo.fr/pho/pdescola-mini.webp" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Jullien&quot;  title=&quot; Wikipedia&quot;&gt;François JULLIEN&lt;/a&gt; est un philosophe français, à la fois helléniste et sinologue, connu pour avoir construit un dialogue suivi entre la pensée européenne (surtout grecque) et la pensée chinoise. Il séjourne longuement en Asie (notamment à Tokyo) et soutient deux thèses, l’une sur l’écrivain chinois Lu Xun, l’autre sur l’interprétation poétique dans la tradition chinoise, ce qui fonde son approche de  &lt;a href=&quot;https://www.berlol.net/foire/fle98ju.htm&quot;  title=&quot;le détour d'un grec par la chine par berlol.net&quot;&gt;l’altérité culturelle.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Son projet central consiste à &quot;dépayser&quot; la pensée européenne en la confrontant à la Chine, afin de faire apparaître les présupposés cachés de la philosophie occidentale. Il insiste sur le fait que la rencontre des pensées ne doit pas viser l’exotisme, mais ouvrir un espace &quot;entre&quot; les cultures où se travaille un véritable commun, différent de l’uniforme qu’on confond trop vite avec l’universel. &lt;/p&gt; &lt;p&gt; Il travaille la notion d’&quot;écart&quot; : au lieu de chercher ce qui est semblable entre les cultures, il valorise leurs écarts comme lieu de réflexion et de création conceptuelle. De cet écart naît un &quot;entre&quot; : un espace de tension fécond où se construit le commun, sans effacer les différences. Il propose aussi un déplacement majeur : passer de la pensée de l’&quot;être&quot; à une pensée du &quot;vivre&quot;, plus attentive aux processus, aux transformations et à l’expérience concrète de l’existence. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme le &quot;Traité de l’efficacité&quot;, il oppose la manière occidentale d’agir à une logique chinoise de l’efficience, qui mise sur les tendances de la situation et les transformations continues. L’idée est moins de choisir un camp que de se servir de cet  &lt;a href=&quot;https://www.youtube.com/watch?v=RAgmn0mbUnQ&quot;  title=&quot;François Jullien, entrer dans la pensée chinoise par deodaTV&quot;&gt;écart Chine/Europe &lt;/a&gt; pour repenser nos pratiques de l’action, de la stratégie et de la décision dans le monde contemporain. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;L’art de « décoïncider » selon François Jullien  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13957-13.02.2021-ITEMA_22573157-2021C22785S0044.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Olivier_Abel&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Olivier ABEL&lt;/a&gt;  est un philosophe français spécialiste en éthique et philosophie morale, influencé par Paul Ricœur, Emmanuel Levinas et la tradition protestante. Il soutient en 1983 une thèse sur la rêverie chez Gaston Bachelard sous la direction de Ricœur, puis une habilitation en 2000 sur le temps éthique entre courage et pardon. &lt;/p&gt; &lt;p&gt; Créateur du Fonds Ricœur à Paris, doyen de la Faculté protestante de Paris, il a présidé la Commission d'éthique de la &lt;a href=&quot;https://www.lavie.fr/idees/histoire/olivier-abel-avec-le-catholicisme-leffort-fait-partie-du-chemin-pour-acceder-a-la-grace-100952.php&quot;  title=&quot;Olivier Abel : Avec le catholicisme, l’effort fait partie du chemin pour accéder à la grâce par la Vie&quot;&gt;Fédération protestante &lt;/a&gt;  de France et est membre de l'Académie de Nîmes depuis 2018. Il est aussi membre du Comité consultatif national d'éthique et contribue à des revues comme Esprit. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'éthique interrogative, le pardon, la conversation, l'Europe et les penseurs protestants comme Calvin ou Bayle. Parmi ses ouvrages : L’éthique interrogative (2000), Le pardon, briser la dette et l’oubli (1991), Le vertige de l’Europe (2019),  &lt;a href=&quot;https://www.youtube.com/watch?v=G1_ynk7E7LQ&quot; title=&quot;Olivier Abel, philosophe : Le signe de l’humiliation, c’est cette parole rentrée par FRANCE 24&quot;&gt;De l’humiliation &lt;/a&gt; (récent) et La naissance, qu’est-ce que ça change. Il explore la fugacité des liens humains et une critique du sujet délié. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Le témoin du vendredi : Olivier Abel, la civilisation européenne par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/11739-12.04.2019-ITEMA_22034063-2019F17009S0102-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pascal_Engel&quot;   title=&quot; Wikipedia&quot;&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent &quot;La Norme du vrai&quot; paru en 1989 sur la philosophie de la logique, &lt;a href=&quot;https://www.youtube.com/watch?v=ivsIBYFN6DI&quot; title=&quot;*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos&quot;&gt; &quot;Va savoir&quot;&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et &quot;Les vices du savoir&quot; en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il l défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Faut-il faire la morale aux intellectuels ?  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J.G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime un séminaire sur les décolonisations avec l'Université de Louvain-la-Neuve. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href=&quot;https://www.youtube.com/watch?v=vEQWmSo67B4&quot; style=&quot;color:#88A1E9&quot; title=&quot;Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches&quot;&gt;&quot;Ce sont d'autres gens&quot; &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la &quot;qualité de la vie&quot; sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href=&quot;https://www.youtube.com/watch?v=ZDpbSRrWIhU&quot; title=&quot;Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées&quot;&gt;&quot;autre monde&quot; &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Sandra_Laugier&quot; title=&quot; Wikipedia&quot;&gt;Sandra LAUGIER&lt;/a&gt;  est une philosophe française, professeure à l’université Paris 1 Panthéon-Sorbonne, membre de l’Institut Universitaire de France et spécialiste de philosophie du langage, de philosophie morale et de philosophie politique. Elle a aussi beaucoup travaillé sur Stanley Cavell, qu’elle a traduit en français, ainsi que sur Emerson, Thoreau et le perfectionnisme moral. &lt;/p&gt; &lt;p&gt; Sa philosophie accorde une place centrale à l’ordinaire : les gestes, les paroles, les liens quotidiens et les formes de vie concrètes sont pour elle des lieux essentiels de la pensée. Elle défend l’idée qu’il faut partir de l’expérience vécue plutôt que de grands systèmes abstraits, ce qui l’a conduite à développer une éthique du care, une réflexion sur le langage ordinaire et une attention aux formes discrètes de la vie commune. &lt;/p&gt; &lt;p&gt; Sur le plan politique, elle s’intéresse aux formes contemporaines de démocratie, à &lt;a href=&quot;https://www.youtube.com/watch?v=nlM-aPBIRdg&quot; title=&quot;Sandra Laugier : reconnaître nos dépendances par France Inter&quot;&gt;la désobéissance civile &lt;/a&gt; et aux mouvements horizontaux comme Nuit debout. Elle y voit une manière de repenser le politique à partir de l’expression des personnes, du souci du commun et de l’égalité effective des droits, plutôt que d’un modèle hiérarchique classique. Cette perspective la conduit à défendre une démocratie plus attentive aux voix singulières et aux pratiques collectives concrètes. &lt;/p&gt; &lt;p&gt; Elle a aussi élargi la philosophie à la culture populaire, notamment &lt;a href=&quot;https://www.youtube.com/watch?v=Rjd2XEvkqWc&quot; title=&quot;Sandra Laugier : nos vies en séries par librairie mollat&quot;&gt;aux séries télévisées, &lt;/a&gt; qu’elle considère comme un laboratoire d’expériences morales et politiques. Dans des ouvrages récents, elle montre que les séries peuvent aider à penser nos manières de vivre, nos attachements et nos conflits, en révélant des aspects très actuels de la sensibilité démocratique. &lt;/p&gt;  &lt;audio controls title=&quot;L’éthique animale avec Florence Burgat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" display="https://www.laphilo.fr/pho/slaugier-mini.webp" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon&quot;  title=&quot; Wikipedia&quot;&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href=&quot;https://www.youtube.com/watch?v=xOKttB1HgSk&quot;  title=&quot;Marc Crépon sur la violence  par France Inter &quot;&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href=&quot;https://www.youtube.com/watch?v=kwFC9MSSWcg&quot;  title=&quot;Marc Crépon : l’épreuve de la haine   par Librairie mollat &quot;&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; On peut dire qu’il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste.  &lt;/p&gt; &lt;audio controls title=&quot;Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Audi&quot;  title=&quot; Wikipedia&quot;&gt;Paul AUDI&lt;/a&gt;  est un philosophe et écrivain français né à Beyrouth, au Liban, et ancien élève de l'École normale supérieure. Agrégé de philosophie et docteur en philosophie, il a soutenu une thèse sur Jean-Jacques Rousseau publiée en 1997. Après avoir enseigné à l'université de Paris-XII, il s'est éloigné du champ universitaire pour s'orienter vers l'édition, et aujourd'hui il est professeur invité dans diverses institutions en France et à l'étranger. Il est auteur de plus d'une trentaine d'ouvrages et membre de l'équipe de recherches PHILéPOL à l'université Paris Descartes. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre principalement sur les relations entre l'éthique et l'esthétique en Occident durant les Temps Modernes. Son œuvre explore ces liens à travers des &lt;a href=&quot;https://www.youtube.com/watch?v=3GRhkvYGMs0&quot;  title=&quot;Paul Audi contrat social par le nouvel Obs&quot;&gt;lectures de Rousseau, &lt;/a&gt;  Nietzsche, Lacan, Schopenhauer et Georges Bataille. Il est considéré comme un philosophe atypique, commençant à être reconnu hors de France. Sa pensée conjugue la vie du corps et la création artistique, l'éthique et la passion, avec un souci d'ancrer la pensée dans la vie physique. &lt;/p&gt; &lt;p&gt; L'idée centrale de sa philosophie est que l'acte de création et le comportement éthique ne forment qu'un seul et même geste, qui naît de la vie elle-même et finalement l'excède. Il nomme cette fusion « esth/éthique », considérant que l'éthique et l'esthétique dans l'acte de créer se confondent ou sont le recto et verso d'une même « explication avec la vie ». Pour lui, créer revient à « s'expliquer avec la vie », à faire de l'énigme que nous sommes une bribe d'un discours neuf. &lt;/p&gt; &lt;p&gt; L'éthique, selon lui, consiste d'abord en un travail sur soi, où « c'est moi-même qui suis la tâche ». La philosophie ne s'accomplit qu'au sein d'un corps à corps avec ce qui, en nous-mêmes, nous dépasse — non pas le monde ou un dehors, mais ce qui nous situe sur le  &lt;a href=&quot;https://www.youtube.com/watch?v=FJsDRUR9bYQ&quot;  title=&quot;Paul Audi il faut le nuance par France Inter&quot;&gt;« plan de la vie », &lt;/a&gt; qui ne recouvre ni le champ social ni l'espace politique. Cette éthique de la création, qu'il dénomme « esthéthique », n'est pas un code de règles mais une posture existentielle, une manière de se situer face au monde. &lt;/p&gt; &lt;p&gt; Il  s'intéresse également aux conditions permettant à l'être humain d'accéder à sa propre humanité, et interroge profondément la question de l'identité. Dans son ouvrage Troublante identité (2022), il parle pour la première fois de lui-même et de ce qui le hante, résistant à toute réduction de son être à sa provenance libanaise. Il désire en finir avec les clôtures identitaires et trouve son émancipation dans une conception juive d'une identité ouverte, toujours à construire, guidée par un impératif de justice à venir. Son dernier essai Le Vrai du beau (2026) transforme la contemplation d'un tableau en expérience de vérité, éclaircissant ce qui se joue en nous face à un tableau. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;la verité picturale existe t’elle ?  Par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/26657-24.04.2026-ITEMA_24487813-2026F45096S0114-NET_MFI_F40118A5-5297-4676-86E9-2E9A248FB2F7-27-03023a67ff6f93208a5f302d7d3b8771.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" display="https://www.laphilo.fr/pho/paudi-mini.webp" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" display="https://www.laphilo.fr/pho/cmichon-mini.webp" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Corine_Pelluchon&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href=&quot;https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s&quot; title=&quot;NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco&quot;&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &#10;&lt;p&gt; - Manifeste animaliste. Politiser la cause animale ( 2017 )  - Éthique de la considération ( 2018) - Réparons le monde. Humains, animaux, nature (2020)  &#10; - Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &#10;&lt;p&gt; -   &lt;a href=&quot;https://www.youtube.com/watch?v=zpzzDqYhF-8&quot; title=&quot;Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat&quot;&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href=&quot;https://www.youtube.com/watch?v=tmk-UzN1j70&quot;  title=&quot;Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media&quot;&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title=&quot;Corine Pelluchon par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" display="https://www.laphilo.fr/pho/cfmetterie-mini.webp" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vincent_Delecroix&quot;  title=&quot; Wikipedia&quot;&gt;Vincent DELECROIX&lt;/a&gt;  est un philosophe français spécialiste de Kierkegaard et de la philosophie de la religion. Il enseigne à l’EPHE, où il travaille sur la vérité, la croyance et les liens entre religion et pensée contemporaine. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse d’abord à la manière dont la foi peut exister dans un monde moderne où les certitudes absolues se  &lt;a href=&quot;https://www.youtube.com/watch?v=2ZHOpP5GMwI&quot; title=&quot;Vincent DELECROIX,la nécessité d’apprendre par TV5 monde&quot;&gt;sont affaiblies. &lt;/a&gt; Il ne traite pas la religion comme un simple héritage figé, mais comme une expérience intérieure, fragile et exigeante.  &lt;/p&gt; &lt;p&gt; Un autre axe important chez lui est la révolte. À travers des livres comme Tombeau d’Achille et Non ! De l’esprit de révolte, il réfléchit à la colère, au refus et à la parole &lt;a href=&quot;https://www.youtube.com/watch?v=OiUgp6wLpCA&quot; title=&quot;Vincent DELECROIX il faut sortir du oui non par France Culture&quot;&gt;qui dit non, &lt;/a&gt; non comme de simples réactions, mais comme des forces qui révèlent une vérité humaine et morale. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il  est un philosophe de la tension entre vérité, foi et révolte. Sa pensée cherche à comprendre comment l’être humain peut garder une voix, une conscience et une exigence spirituelle dans un monde désorienté. &lt;/p&gt;  &lt;audio controls title=&quot;Vincent DELECROIX  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89douard_Mehl&quot;  title=&quot; Wikipedia&quot;&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href=&quot;https://www.youtube.com/watch?v=NT0n7tKNb3w&quot; title=&quot;qu’est ce que la verité par Le forum Veritas&quot;&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. &lt;/p&gt; &#10;&#10;" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Barbara_Stiegler&quot; title=&quot; Wikipedia&quot;&gt;Barbara STEIGLER&lt;/a&gt;  est une philosophe française, fille du philosophe Bernard Stiegler, spécialiste de Nietzsche, de philosophie politique et critique du néolibéralisme. Agrégée de philosophie, elle soutient sa thèse en 2003 à Paris-Sorbonne sous la direction de Jean-Luc Marion sur Nietzsche et la biologie. Maître de conférences puis professeure à l'université Bordeaux-Montaigne depuis 2006, elle y dirige le master  &lt;a href=&quot;https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf&quot; title=&quot;Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne&quot;&gt;&quot;Soin, éthique et santé&quot;. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Engagée politiquement, elle analyse les Gilets Jaunes dans &quot;Du cap aux grèves&quot; paru en 2021 et critique l’adaptationnisme comme fondement du néolibéralisme, opposant une intelligence collective à l’élitisme technocratique. &lt;/p&gt; &lt;p&gt; Ses ouvrages sur Nietzsche explorent le corps et la vie (Nietzsche et la biologie, 2001 ; Nietzsche et la critique de la chair, 2005 ; Nietzsche et la vie, 2021). &lt;/p&gt; &lt;p&gt;  Elle étend ses recherches au politique avec  &lt;a href=&quot;https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/&quot; title=&quot;Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit&quot;&gt;&quot;Il faut s’adapter&quot; &lt;/a&gt; paru en  2019, dénonçant les racines évolutionnistes (Spencer, Lippmann) du &lt;a href=&quot;https://www.youtube.com/watch?v=oQQ4xqRvYTk&quot; style=&quot;color:#88A1E9&quot; title=&quot;LA LENTE AGONIE DU NÉOLIBÉRALISME  par &#10;TheSwissBox Conversation&quot;&gt;néolibéralisme &lt;/a&gt; face au pragmatisme démocratique de Dewey. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" display="https://www.laphilo.fr/pho/bastiegler-mini.webp" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89ric_Sadin&quot;  title=&quot; Wikipedia&quot;&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href=&quot;https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur&quot; style=&quot;color:#88A1E9&quot;   title=&quot; Éric SADIN contre ChatGPT par Senseur&quot;&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;&#10;Sadin s'est fait connaître grâce à son livre &quot;La société de l'anticipation &quot; publié en 2011, dans lequel il examine l'émergence de la société de la surveillance et des technologies de prévision qui cherchent à anticiper les comportements et les désirs des individus. Il y aborde notamment les thèmes de la surveillance généralisée, de la collecte de données personnelles et des risques de manipulation. &lt;/p&gt; &lt;p&gt;&#10;Dans son ouvrage &lt;a href=&quot;https://christian-biales.fr/wp-content/uploads/2020/12/Sadin.pdf&quot;  title=&quot;Extrait du livre par Christian Bialès&quot;&gt; &quot;L'Ère de l'individu tyran : la fin d'un monde commun&quot;&lt;/a&gt; paru en 2013, Sadin explore les conséquences de la numérisation de la société sur les notions de vie privée, de liberté individuelle et de démocratie. Il met en garde contre le pouvoir croissant des grandes plateformes technologiques et la manière dont elles peuvent influencer et contrôler nos comportements et nos choix. &lt;/p&gt; &lt;p&gt;&#10;Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre &quot;La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique&quot; publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href=&quot;https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008&quot;  title=&quot;Dataïsme par lebigdata&quot;&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title=&quot;Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau&quot; title=&quot; Wikipedia&quot;&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href=&quot;https://www.youtube.com/watch?v=PNMZHr3L_Ws&quot; title=&quot; Vivons nous dans un multivers par Aurelien Barrau&quot;&gt; concept de multivers&lt;/a&gt; , et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage &quot;Chaos multiples&quot; et &quot;De la vérité dans les sciences&quot;  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé &quot;Météorites&quot;. &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de &quot;sauver le climat&quot; plutôt &quot;qu’agir pour la vie&quot;. &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  &quot;habiter la science en poète&quot; en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href=&quot;https://www.youtube.com/watch?v=94IxSYo5wtM&quot; title=&quot;Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter&quot;&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href=&quot;https://www.youtube.com/watch?v=g3Z_LsXD7DU&quot; title=&quot; L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac&quot;&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un &quot;faire monde&quot; éthique et conscient. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Aurelien BARRAU par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin&quot; title=&quot; Wikipedia&quot;&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href=&quot;https://charlespepin.fr/&quot;  title=&quot; Site officiel Charles Pépin &quot;&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href=&quot;https://www.youtube.com/watch?v=WExeoL6qVmc&quot; title=&quot; Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori&quot;&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href=&quot;https://www.youtube.com/watch?v=orOxuIHT_vc&quot; title=&quot;Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal&quot;&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt; - &quot;Les Vertus de l’échec&quot; publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt; - &quot;La Confiance en soi &quot; paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt; - &quot;La Rencontre&quot;  en 2021 et &quot;Vivre avec son passé&quot; en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href=&quot;https://www.youtube.com/watch?v=M09YmUzDwO8&quot; title=&quot; Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs&quot;&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; La philosophie selon Charles Pépin par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel&quot;  title=&quot; Wikipedia&quot;&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un &quot;philosophe de la liberté&quot;. Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que &quot;être de gauche&quot; signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;La privation de l’intime&quot; paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href=&quot;https://www.youtube.com/watch?v=HcDfUGypNvA&quot; style=&quot;color:#88A1E9&quot; title=&quot;Michaël Fœssel - Récidive, 1938 par Librairie mollat&quot;&gt;&quot;Récidive. 1938&quot;&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme &quot;laboratoire&quot; pour comprendre les fragilités  &lt;a href=&quot;https://www.youtube.com/watch?v=wdeS7SFEz7Y&quot;  title=&quot;Démocratie illibérale par Michaël Foessel par France Culture&quot;&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 &quot;Quartier rouge. Le plaisir et la gauche&quot;, il interroge le rapport de  &lt;a href=&quot;https://www.youtube.com/watch?v=MDubXJZox34&quot; title=&quot;Michaël Foessel : &quot;La question du plaisir est aujourd'hui centrale en politique&quot; par France Inter&quot;&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment &quot;Vers la paix perpétuelle&quot; et &quot;La religion dans les limites de la simple raison&quot;, tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title=&quot;La gauche : état des lieux  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Baptiste_Jeang%C3%A8ne_Vilmer&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Baptiste JEANGENE VILMER&lt;/a&gt;  est un philosophe, politologue et juriste français spécialiste de l’éthique de la guerre, du droit international et des relations internationales, et également diplomate (ambassadeur de France au Vanuatu depuis 2022). Il est formé dans trois disciplines : philosophie (licence, master, doctorat), droit (licence, LLM, postdoctorat) et science politique (doctorat). &lt;/p&gt; &lt;p&gt; Sa thèse porte sur &quot;l’intervention militaire justifiée par des raisons humanitaires&quot;, à la croisée de philosophie politique, droit international et théorie des relations internationales. Il défend en théorie des relations internationales un &quot;réalisme libéral&quot; inspiré de Raymond Aron, Stanley Hoffmann et Pierre Hassner : reconnaissance du tragique et des &lt;a href=&quot;https://www.youtube.com/watch?v=4EECHNFvt4Q&quot;  title=&quot; J-B. Jeangène Vilmer - Synthèse par Institut Guerre et Paix&quot;&gt;rapports de force, &lt;/a&gt;  mais attachée au droit international, aux droits humains et aux institutions. &lt;/p&gt; &lt;p&gt; Il se situe à l’intersection de philosophie morale, droit international et stratégie : penser les guerres et interventions non seulement en termes juridiques ou militaires, mais surtout en termes de responsabilité morale (tuer, laisser mourir, protéger). Son &lt;a href=&quot;https://www.jbjv.com/IMG/pdf/JB_Jeangene_Vilmer_2013_-_Pour_un_realisme_liberal_en_relations_internationales.pdf&quot;  title=&quot;Pour un réalisme libéral en relations internationales par jbjv&quot;&gt;&quot;réalisme libéral&quot; &lt;/a&gt; refuse à la fois le cynisme réaliste pur et l’idéalisme naïf, il cherche des critères prudents mais exigeants pour juger les interventions, la justice pénale, ou la responsabilité des États. &lt;/p&gt; &lt;p&gt; Il insiste sur les dilemmes : parfois, intervenir violemment peut sauver des vies, mais peut aussi aggraver le conflit ; parfois, poursuivre les criminels peut fragiliser la paix. Sa pensée explore ces tensions plutôt que de proposer des solutions simplistes. &lt;/p&gt; &#10;&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   &#10;" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" display="https://www.laphilo.fr/pho/nykisukidi-mini.webp" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" display="https://www.laphilo.fr/pho/jdfunes-mini.webp" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tristan_Garcia&quot; title=&quot; Wikipedia&quot;&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. &lt;/p&gt; &lt;p&gt; Son œuvre majeure &quot;Forme et objet. Un traité des choses&quot; paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie &quot;plate&quot; qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans &quot;Nous&quot; ou &quot;La Vie intense&quot; paru en 2016, il explore l’appartenance à des collectifs variables &quot;nous humains&quot;, &quot;nous animaux&quot; et critique l’obsession moderne pour  &lt;a href=&quot;https://www.youtube.com/watch?v=JTLVzryyyEg&quot; title=&quot;Tristan Garcia, INTENSITÉ par abc penser&quot;&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (La Meilleure part des hommes, sur le sida) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href=&quot;https://www.youtube.com/watch?v=K_wxi5xTYz8&quot; title=&quot;Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace&quot;&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; &#10; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Tristan Garcia, &quot;La vie intense : une obsession moderne&quot; par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10; " r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Baptiste_Morizot&quot;  title=&quot; Wikipedia&quot;&gt;Baptiste MORIZOT&lt;/a&gt;  est un philosophe français,  maître de conférences à l'université d'Aix-Marseille, dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle. Son approche se distingue par une pratique de terrain ancrée dans l'expérience, notamment le pistage des grands prédateurs comme les loups, ce qui lui permet de nourrir sa pensée philosophique par une observation directe et sensible du vivant.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve l'idée que la crise écologique contemporaine est avant tout une « crise de la sensibilité » et de nos relations avec le reste du monde vivant. Il soutient que la pensée moderne, marquée par un dualisme qui sépare strictement l'humain de la nature, nous a &lt;a href=&quot;https://www.youtube.com/watch?v=bAnXnPnnHCk&quot; title=&quot;Baptiste Morizot, meme penseur on est un animal par France Inter&quot;&gt;rendus aveugles et sourds &lt;/a&gt; aux autres espèces, qu'il préfère considérer comme d'autres « manières d'être vivant » plutôt que comme des êtres inférieurs. &lt;/p&gt; &lt;p&gt; Il propose ainsi de remplacer le modèle classique de la « maîtrise de la nature » par une « diplomatie des interdépendances ». Cette approche invite les humains à se concevoir comme des partenaires au sein d'un réseau complexe d'interdépendances, où il s'agit de tisser des alliances concrètes, de prêter attention aux signaux émis par les autres espèces et d'apprendre à cohabiter avec elles dans un esprit de respect et de responsabilité partagée. &lt;/p&gt; &lt;p&gt; Son travail, qui mêle récit, enquête éthologique et essai théorique, cherche à réenchanter &lt;a href=&quot;https://www.youtube.com/watch?v=uQZcktq_W3E&quot; title=&quot;Baptiste Morizot, remet l’humain à sa place par La Grande Librairie&quot;&gt;notre rapport au monde &lt;/a&gt; en réactivant nos capacités d'attention et d'intelligence sensible. En invitant à une forme de sagesse pragmatique et ancrée, il s'efforce de refonder notre culture environnementale, non pas pour dominer ou sanctuariser la nature, mais pour s'ajuster avec humilité à la diversité des formes de vie qui partagent la Terre avec nous. &lt;/p&gt;  &lt;audio controls title=&quot;Liberté, dignité, habitalité avec baptiste MORIZOT par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18558-25.04.2026-ITEMA_24488881-2026F30378S0115-NET_MFI_D6CADDF4-ADD5-4D3F-AA1D-625272E9CD3C-22-b98aedea0426383b486dc3819cb77a8e.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" display="https://www.laphilo.fr/pho/ydallaglio-mini.webp" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Norman_Ajari&quot;  title=&quot; Wikipedia&quot;&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href=&quot;https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari&quot;  title=&quot;Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse&quot;&gt;&quot;études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href=&quot;https://www.youtube.com/watch?v=IMUBi9oi2WM&quot; title=&quot;Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche&quot;&gt;&quot;colonialité de l’être&quot; &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=ECSmpOXY8kg&quot; title=&quot;NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS&quot;&gt;&quot;La Dignité ou la mort&quot;, &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de &quot;philosophe militant&quot; : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. &lt;/p&gt; &lt;audio controls title=&quot;où commence et où finit le racisme? par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" display="https://www.laphilo.fr/pho/mmaeso-mini.webp" r:id="rId41"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-france-actif.xlsx
+++ b/data/frise-philosophes-france-actif.xlsx
@@ -2687,378 +2687,376 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="126.75" customHeight="1" s="28">
-      <c r="A34" s="34" t="n">
+    <row r="34" ht="219.75" customHeight="1" s="28">
+      <c r="A34" s="26">
+        <v>1950</v>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1950</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jean-Michel BESNIER</t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Michel_Besnier" title=" Wikipedia"&gt;Jean-Michel BESNIER&lt;/a&gt; est un philosophe français. Né à Caen en 1950, agrégé de philosophie et docteur en sciences politiques, il enseigne à l’université de technologie de Compiègne de 1988 à 2001, puis à la Sorbonne, dont il est professeur émérite. Ses premiers livres portent sur l’histoire de la philosophie moderne et contemporaine, dont il publie une grande synthèse en 1993, et sur la figure de l’intellectuel, partagé entre la révolte et l’engagement, de Georges Bataille à Maurice Blanchot.&lt;/p&gt; &lt;p&gt;Il se consacre ensuite à l’impact des sciences et des techniques sur nos représentations et nos imaginaires. Dans &lt;em&gt;Demain les posthumains&lt;/em&gt; (2009), il analyse le &lt;a href="https://fr.wikipedia.org/wiki/Transhumanisme" title=" Wikipedia"&gt;transhumanisme&lt;/a&gt;, qui promet de dépasser la condition humaine grâce aux biotechnologies, aux nanotechnologies et à l’intelligence artificielle. Il y voit moins un progrès qu’une fatigue d’être soi, un désir de se débarrasser de la fragilité, de l’incertitude et de la mort, qui sont pourtant ce qui fait notre humanité.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Homme simplifié&lt;/em&gt; (2012), il décrit le « syndrome de la touche étoile » : à force de dialoguer avec des machines, nous simplifions notre langage et nos relations pour nous adapter à elles, au lieu de les rendre plus humaines. Il débat publiquement avec les partisans du transhumanisme, comme Laurent Alexandre, avec qui il publie &lt;em&gt;Les robots font-ils l’amour ?&lt;/em&gt; (2016). Il a siégé dans plusieurs comités d’éthique de la recherche, notamment celui du CNRS, et dirigé le secteur « sciences et société » du ministère de la Recherche de 2008 à 2011.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PuO8pLjlWKE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Le sacré, le pouvoir et le mythe - Jean-Michel Besnier" par Les Mardis de la Philo</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/besnier-mini.webp</t>
+        </is>
+      </c>
+      <c r="J34" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K34" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme</t>
+        </is>
+      </c>
+      <c r="L34" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe français des techniques, critique du transhumanisme et de « l’homme simplifié ».</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O34"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="126.75" customHeight="1" s="28">
+      <c r="A35" s="34" t="n">
         <v>1951</v>
       </c>
-      <c r="B34" s="34" t="n"/>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>1951</t>
         </is>
       </c>
-      <c r="D34" s="35" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>François JULLIEN</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
+      <c r="E35" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Jullien"  title=" Wikipedia"&gt;François JULLIEN&lt;/a&gt; est un philosophe français, à la fois helléniste et sinologue, connu pour avoir construit un dialogue suivi entre la pensée européenne (surtout grecque) et la pensée chinoise. Il séjourne longuement en Asie (notamment à Tokyo) et soutient deux thèses, l’une sur l’écrivain chinois Lu Xun, l’autre sur l’interprétation poétique dans la tradition chinoise, ce qui fonde son approche de  &lt;a href="https://www.berlol.net/foire/fle98ju.htm"  title="le détour d'un grec par la chine par berlol.net"&gt;l’altérité culturelle.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Son projet central consiste à "dépayser" la pensée européenne en la confrontant à la Chine, afin de faire apparaître les présupposés cachés de la philosophie occidentale. Il insiste sur le fait que la rencontre des pensées ne doit pas viser l’exotisme, mais ouvrir un espace "entre" les cultures où se travaille un véritable commun, différent de l’uniforme qu’on confond trop vite avec l’universel. &lt;/p&gt; &lt;p&gt; Il travaille la notion d’"écart" : au lieu de chercher ce qui est semblable entre les cultures, il valorise leurs écarts comme lieu de réflexion et de création conceptuelle. De cet écart naît un "entre" : un espace de tension fécond où se construit le commun, sans effacer les différences. Il propose aussi un déplacement majeur : passer de la pensée de l’"être" à une pensée du "vivre", plus attentive aux processus, aux transformations et à l’expérience concrète de l’existence. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme le "Traité de l’efficacité", il oppose la manière occidentale d’agir à une logique chinoise de l’efficience, qui mise sur les tendances de la situation et les transformations continues. L’idée est moins de choisir un camp que de se servir de cet  &lt;a href="https://www.youtube.com/watch?v=RAgmn0mbUnQ"  title="François Jullien, entrer dans la pensée chinoise par deodaTV"&gt;écart Chine/Europe &lt;/a&gt; pour repenser nos pratiques de l’action, de la stratégie et de la décision dans le monde contemporain. &lt;/p&gt; 
   &lt;audio controls title="L’art de « décoïncider » selon François Jullien  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13957-13.02.2021-ITEMA_22573157-2021C22785S0044.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F34" s="34" t="inlineStr">
+      <c r="F35" s="34" t="inlineStr">
         <is>
           <t>ual52L9ejGw</t>
         </is>
       </c>
-      <c r="G34" s="36" t="inlineStr">
+      <c r="G35" s="36" t="inlineStr">
         <is>
           <t>"
 Comment réinventer sa vie ? Interview avec le philosophe François Jullien" par Union des Savoirs</t>
         </is>
       </c>
-      <c r="H34" s="36" t="inlineStr">
+      <c r="H35" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jullien-mini.webp</t>
         </is>
       </c>
-      <c r="I34" s="36" t="n"/>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="I35" s="36" t="n"/>
+      <c r="J35" s="27" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K34" s="27" t="inlineStr">
+      <c r="K35" s="27" t="inlineStr">
         <is>
           <t>Herméneutique</t>
         </is>
       </c>
-      <c r="L34" s="27" t="inlineStr">
+      <c r="L35" s="27" t="inlineStr">
         <is>
           <t>philosophe français qui analyse la philosophie à partir des langues &amp;amp; pensées grecque et chinoise.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t xml:space="preserve">continental</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="137.25" customHeight="1" s="28">
-      <c r="A35" s="34" t="n">
+    <row r="36" ht="137.25" customHeight="1" s="28">
+      <c r="A36" s="34" t="n">
         <v>1952</v>
       </c>
-      <c r="B35" s="34" t="n"/>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>1952</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="D36" s="35" t="inlineStr">
         <is>
           <t>André COMTE-SPONVILLE</t>
         </is>
       </c>
-      <c r="E35" s="36" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Andr%C3%A9_Comte-Sponville"  style="color:#6A142A"  title=" Wikipedia"&gt;André COMTE-SPONVILLE&lt;/a&gt;  est un philosophe français, agrégé de philosophie et docteur de troisième cycle. Matérialiste, rationaliste et humaniste, il s'est fait connaître par des ouvrages accessibles popularisant la sagesse antique adaptée au monde contemporain avec "Le Petit Traité des grandes vertus" paru en  1995, best-seller vendu à plus de 500 000 exemplaires. &lt;/p&gt; &lt;p&gt; Issu d'un milieu catholique, il se convertit à l'athéisme adolescent, adhère au Parti communiste français, puis enseigne la philosophie à l'université Paris-I Panthéon-Sorbonne jusqu'en 1998, date à laquelle il se consacre à l'écriture, aux conférences et aux essais médiatiques.  &lt;/p&gt; &lt;p&gt; Influencé par Épicure, les stoïciens, Montaigne, Spinoza, ainsi que des contemporains comme Claude Lévi-Strauss ou Marcel Conche, il forge   &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_2000_num_135_1_3634_t1_0139_0000_2" style="color:#88A1E9" title="André Comte-Sponville, L'être-temps : quelques réflexions sur le temps de la conscience, coll. Perspectives critiques par Persée"&gt;l'insistantialisme : &lt;/a&gt; une métaphysique matérialiste du temps où l'existence persiste sans finalité divine ni sens transcendant, opposée à l'existentialisme. Il propose une spiritualité athée, une éthique humaniste sans Dieu, centrée sur l'ici-maintenant et l'acceptation joyeuse de la finitude humaine. &lt;/p&gt; &lt;p&gt; Ses vertus cardinales (courage, tempérance, justice, etc.) visent une &lt;a href="https://www.youtube.com/watch?v=OYRMlwYByfA" style="color:#88A1E9" title="André Comte-Sponville, L'amou est joie par Hopitaux Universitaires de Genève"&gt;vie heureuse &lt;/a&gt; malgré la souffrance et la mort, sans illusions religieuses ou morales kantiennes. Dans des essais comme "L'Inconsolable" paru en 2018, il explore l'ennui, la joie, la solitude et les animaux, plaidant tolérance, liberté et sagesse laïque face aux populismes et au déclin écologique. &lt;/p&gt; 
   &lt;audio controls title="André Comte-Sponville, homme mélancolique, philosophe heureux par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10351-04.01.2026-ITEMA_24362243-2025C3500E0181-NET_MFC_54DA91F6-96EA-4790-BDB7-6EA3C744B706-21-8ab3772763c1198b47c221812723e2fa.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
-      <c r="F35" s="34" t="inlineStr">
+      <c r="F36" s="34" t="inlineStr">
         <is>
           <t>ldl-HgnjS4U</t>
         </is>
       </c>
-      <c r="G35" s="36" t="inlineStr">
+      <c r="G36" s="36" t="inlineStr">
         <is>
           <t>"André Comte-Sponville : "On ne peut pas vivre en faisant semblant qu'on ne va pas mourir" par France Inter</t>
         </is>
       </c>
-      <c r="H35" s="36" t="inlineStr">
+      <c r="H36" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/sponville-mini.webp</t>
         </is>
       </c>
-      <c r="I35" s="36" t="n"/>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I36" s="36" t="n"/>
+      <c r="J36" s="27" t="inlineStr">
         <is>
           <t>ethique ; metaphysique</t>
         </is>
       </c>
-      <c r="K35" s="27" t="inlineStr">
+      <c r="K36" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Stoïcisme ; Matérialisme ; Athéisme</t>
         </is>
       </c>
-      <c r="L35" s="27" t="inlineStr">
+      <c r="L36" s="27" t="inlineStr">
         <is>
           <t>philosophe français matérialiste, rationaliste et humaniste.</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O35">
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O36">
         <v>2</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t xml:space="preserve">sens</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="95.25" customHeight="1" s="28">
-      <c r="A36" s="34" t="n">
+    <row r="37" ht="95.25" customHeight="1" s="28">
+      <c r="A37" s="34" t="n">
         <v>1953</v>
       </c>
-      <c r="B36" s="34" t="n"/>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>1953</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr">
+      <c r="D37" s="35" t="inlineStr">
         <is>
           <t>Georges DIDI-HUBERMAN</t>
         </is>
       </c>
-      <c r="E36" s="36" t="inlineStr">
+      <c r="E37" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Georges_Didi-Huberman" style="color:#6A142A"  title=" Wikipedia"&gt;Georges DIDI-HUBERMAN&lt;/a&gt; est un philosophe &amp; historien de l'art français spécialiste de la théorie des images et figure majeure de la pensée contemporaine sur le visuel. Il est aujourd’hui considéré comme l’un des théoriciens de l’image les plus importants en France, avec une reconnaissance internationale. &lt;/p&gt; &lt;p&gt; Ses travaux portent sur l’histoire et la théorie des images, de la Renaissance à l’art contemporain, avec une attention aux liens entre images, savoir et pouvoir. Sa démarche relève d’une "archéologie du savoir visuel"  car il cherche à comprendre comment les images construisent une mémoire, une sensibilité et des formes de pensée. &lt;/p&gt; &lt;p&gt; Pour lui, les images ne sont pas seulement des objets à regarder, mais des actes qui engagent le corps, la mémoire,&lt;a href="https://www.youtube.com/watch?v=DUNo6xZkaCo" style="color:#88A1E9" title="
 L'historien de l'art Georges Didi-Huberman explique la fabrique de nos affects par les images par France Culture"&gt; l’affect et l’histoire&lt;/a&gt;. Il insiste sur leu profondeur car il ne s’agit pas seulement de ce qui est visible en surface, mais de ce qui travaille en dessous, dans les couches de sens, de mémoire, de trauma. Il réfléchit aussi à une éthique du regard, comment voir sans réduire, sans consommer l’image, en respectant ce qu’elle expose de vulnérable, de politique, ou de souffrant. &lt;/p&gt; &lt;p&gt;De nombreux ouvrages sur Warburg, Fra Angelico, le Baroque, la mémoire de la Shoah, les images de catastrophes et de survivants, etc. Une série de livres et de projets sur les,&lt;a href="https://www.youtube.com/watch?v=vKMAHj_kvY8" style="color:#88A1E9" title="Georges Didi-Huberman, SOULÈVEMENT par ABC Penser"&gt; "soulèvements", &lt;/a&gt; où il s’intéresse aux gestes de révolte, aux mouvements collectifs, et à la manière dont les images peuvent porter la voix des sans-voix et lutter contre l’amnésie historique. &lt;/p&gt; &lt;p&gt; Sa réflexion sur les "soulèvements" l’amène à articuler philosophie de l’image et engagement politique : comment des images peuvent accompagner des luttes, préserver des mémoires, donner forme à des désirs de transformation sociale. &lt;/p&gt;   &lt;audio controls title="Dans la bibliothèque de Georges Didi-Huberman par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23875-11.10.2024-ITEMA_23889638-2024C49162E0034-NET_MFC_8E518A6F-A0BF-49D3-BFEA-B88C4BE3FE7F-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F36" s="34" t="inlineStr">
+      <c r="F37" s="34" t="inlineStr">
         <is>
           <t>h629a3ItbQI</t>
         </is>
       </c>
-      <c r="G36" s="36" t="inlineStr">
+      <c r="G37" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">"Qui êtes-vous Georges Didi-Huberman ?" par ABC Penser</t>
         </is>
       </c>
-      <c r="H36" s="36" t="inlineStr">
+      <c r="H37" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/huberman-mini.webp</t>
         </is>
       </c>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="I37" s="36" t="n"/>
+      <c r="J37" s="27" t="inlineStr">
         <is>
           <t>esthetique ; epistemologie</t>
         </is>
       </c>
-      <c r="K36" s="27" t="inlineStr">
+      <c r="K37" s="27" t="inlineStr">
         <is>
           <t>Herméneutique ; Phénoménologie</t>
         </is>
       </c>
-      <c r="L36" s="27" t="inlineStr">
+      <c r="L37" s="27" t="inlineStr">
         <is>
           <t>philosophe &amp;amp; historien de l'art français auteur de plus de cinquante ouvrages.</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t xml:space="preserve">art</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="157.5" customHeight="1" s="28">
-      <c r="A37" s="34" t="n">
+    <row r="38" ht="157.5" customHeight="1" s="28">
+      <c r="A38" s="34" t="n">
         <v>1953</v>
       </c>
-      <c r="B37" s="34" t="n"/>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>1953</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D38" s="35" t="inlineStr">
         <is>
           <t>Olivier ABEL</t>
         </is>
       </c>
-      <c r="E37" s="37" t="inlineStr">
+      <c r="E38" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olivier_Abel"  style="color:#6A142A"  title=" Wikipedia"&gt;Olivier ABEL&lt;/a&gt;  est un philosophe français spécialiste en éthique et philosophie morale, influencé par Paul Ricœur, Emmanuel Levinas et la tradition protestante. Il soutient en 1983 une thèse sur la rêverie chez Gaston Bachelard sous la direction de Ricœur, puis une habilitation en 2000 sur le temps éthique entre courage et pardon. &lt;/p&gt; &lt;p&gt; Créateur du Fonds Ricœur à Paris, doyen de la Faculté protestante de Paris, il a présidé la Commission d'éthique de la &lt;a href="https://www.lavie.fr/idees/histoire/olivier-abel-avec-le-catholicisme-leffort-fait-partie-du-chemin-pour-acceder-a-la-grace-100952.php"  title="Olivier Abel : Avec le catholicisme, l’effort fait partie du chemin pour accéder à la grâce par la Vie"&gt;Fédération protestante &lt;/a&gt;  de France et est membre de l'Académie de Nîmes depuis 2018. Il est aussi membre du Comité consultatif national d'éthique et contribue à des revues comme Esprit. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'éthique interrogative, le pardon, la conversation, l'Europe et les penseurs protestants comme Calvin ou Bayle. Parmi ses ouvrages : L’éthique interrogative (2000), Le pardon, briser la dette et l’oubli (1991), Le vertige de l’Europe (2019),  &lt;a href="https://www.youtube.com/watch?v=G1_ynk7E7LQ" title="Olivier Abel, philosophe : Le signe de l’humiliation, c’est cette parole rentrée par FRANCE 24"&gt;De l’humiliation &lt;/a&gt; (récent) et La naissance, qu’est-ce que ça change. Il explore la fugacité des liens humains et une critique du sujet délié. Pour lui, l’éthique n’est pas un système de règles à appliquer, mais un art de poser les bonnes questions dans les situations où plusieurs biens entrent en conflit : c’est ce qu’il appelle une « éthique interrogative ». Il s’intéresse au pardon, qui permet de délier une relation sans l’effacer, et à l’humiliation, qu’il décrit comme une parole empêchée, une manière de priver l’autre de sa place dans la conversation commune. &lt;/p&gt; 
  &lt;audio controls title="Le témoin du vendredi : Olivier Abel, la civilisation européenne par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11739-12.04.2019-ITEMA_22034063-2019F17009S0102-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
-      <c r="F37" s="34" t="inlineStr">
+      <c r="F38" s="34" t="inlineStr">
         <is>
           <t>uXvouJ3eFls</t>
         </is>
       </c>
-      <c r="G37" s="36" t="inlineStr">
+      <c r="G38" s="36" t="inlineStr">
         <is>
           <t>"Olivier Abel, « il faut arrêter le déni de l’humiliation »" par Regards propestants</t>
         </is>
       </c>
-      <c r="H37" s="36" t="inlineStr">
+      <c r="H38" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/oabel-mini.webp</t>
         </is>
       </c>
-      <c r="I37" s="36" t="n"/>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="I38" s="36" t="n"/>
+      <c r="J38" s="27" t="inlineStr">
         <is>
           <t>ethique ; spiritualite</t>
         </is>
       </c>
-      <c r="K37" s="27" t="inlineStr">
+      <c r="K38" s="27" t="inlineStr">
         <is>
           <t>Herméneutique</t>
         </is>
       </c>
-      <c r="L37" s="27" t="inlineStr">
+      <c r="L38" s="27" t="inlineStr">
         <is>
           <t>philosophe français spécialiste en éthique et philosophie morale.</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t xml:space="preserve">sens ; continental</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="126.75" customHeight="1" s="28">
-      <c r="A38" s="34" t="n">
+    <row r="39" ht="126.75" customHeight="1" s="28">
+      <c r="A39" s="34" t="n">
         <v>1954</v>
       </c>
-      <c r="B38" s="34" t="n"/>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="B39" s="34" t="n"/>
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>1954</t>
         </is>
       </c>
-      <c r="D38" s="35" t="inlineStr">
+      <c r="D39" s="35" t="inlineStr">
         <is>
           <t>Pascal ENGEL</t>
         </is>
       </c>
-      <c r="E38" s="37" t="inlineStr">
+      <c r="E39" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pascal_Engel"   title=" Wikipedia"&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent "La Norme du vrai" paru en 1989 sur la philosophie de la logique, &lt;a href="https://www.youtube.com/watch?v=ivsIBYFN6DI" title="*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos"&gt; "Va savoir"&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et "Les vices du savoir" en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. Pour lui, la croyance a une norme propre : croire, c’est viser la vérité, et l’on ne peut croire à volonté ce que l’on sait faux. Dans &lt;em&gt;Les Vices du savoir&lt;/em&gt;, il montre que l’indifférence à la vérité, le « baratin » et la paresse intellectuelle sont de véritables fautes morales, dont les intellectuels eux-mêmes ne sont pas exempts. &lt;/p&gt;   &lt;audio controls title="Faut-il faire la morale aux intellectuels ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F38" s="34" t="inlineStr">
+      <c r="F39" s="34" t="inlineStr">
         <is>
           <t>iSesDHgeOYM</t>
         </is>
       </c>
-      <c r="G38" s="36" t="inlineStr">
+      <c r="G39" s="36" t="inlineStr">
         <is>
           <t>"Pascal Engel - Introduction à l'épistémologie générale" par Bout de sagesse</t>
         </is>
       </c>
-      <c r="H38" s="36" t="inlineStr">
+      <c r="H39" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/engel-mini.webp</t>
-        </is>
-      </c>
-      <c r="I38" s="36" t="n"/>
-      <c r="J38" s="27" t="inlineStr">
-        <is>
-          <t>epistemologie ; logique</t>
-        </is>
-      </c>
-      <c r="K38" s="27" t="inlineStr">
-        <is>
-          <t>Analytique</t>
-        </is>
-      </c>
-      <c r="L38" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français spécialiste de la philosophie du langage, de la logique et la connaissance.</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O38"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="162" customHeight="1" s="28">
-      <c r="A39" s="34" t="n">
-        <v>1957</v>
-      </c>
-      <c r="B39" s="34" t="n"/>
-      <c r="C39" s="34" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="D39" s="35" t="inlineStr">
-        <is>
-          <t>Charles RAMOND</t>
-        </is>
-      </c>
-      <c r="E39" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Ramond"  title=" Wikipedia"&gt;Charles RAMOND&lt;/a&gt;  est un philosophe français, professeur des universités à Paris-VIII Vincennes-Saint-Denis, où il occupe une chaire de philosophie des sciences et épistémologie de la culture. Spécialiste de Spinoza et de Derrida, il anime un séminaire dédié au philosophe néerlandais et explore la philosophie moderne et contemporaine, avec un accent sur l'ontologie, la logique et la politique des rationalismes classiques. Il a publié de nombreux ouvrages, dont une thèse sur la qualité et la quantité chez Spinoza (1995), un Vocabulaire de Spinoza (1999) et un Dictionnaire Spinoza (2007).  &lt;/p&gt; &lt;p&gt; Il présente Spinoza comme le philosophe de la modernité par excellence, avec des analyses du Traité politique soulignant l'antériorité du politique sur le moral et la démocratie comme régime absolu fondé sur le nombre et la puissance. Il a aussi étudié Descartes dans Descartes, Promesses et paradoxes (2011), explorant les paradoxes de la liberté et de l'irrésolution, ainsi que Derrida et la philosophie du langage. Ses conférences, comme celle à Pékin en 2019, relient Spinoza aux lectures marxistes et aux thèmes de justice et de droit.&lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est la « résolution de problèmes théoriques par les moyens du langage ordinaire », mobilisant rhétorique, ironie et subtilités quotidiennes sans sacrifier rigueur ni clarté. Il rejette les degrés de conceptualité : on peut philosophier avec des termes simples comme « chats » ou « marmites », en mettant ce langage au service de la réflexion pour trancher des problèmes purement théoriques. Chez Spinoza, il défend un conservatisme rationnel immanent à la durée, où ce qui dure est rationnel, et une politique démocratique sceptique obéissant à la loi non pour sa bonté morale mais pour sa validité majoritaire. &lt;/p&gt; &lt;p&gt; Ses réflexions insistent sur la politique spinoziste : justice et injustice n'existent qu'en État, le droit se mesure à la puissance collective, et la démocratie privilégie les « préférences » sur les justifications morales ou républicaines. Il critique les morales théologiques résiduelles en politique moderne et valorise une pensée immanente ouverte aux changements, influencée par la raison spinoziste qui priorise la stabilité sur les valeurs transcendantes. Ramond aborde aussi les sentiments moraux comme l'injustice et les enjeux épistémologiques contemporains. &lt;/p&gt;             &lt;audio controls title="Dictionnaire Derrida de charles Ramond par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-10.01.2017-ITEMA_21192290-2017C24269S0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
-        </is>
-      </c>
-      <c r="F39" s="34" t="inlineStr">
-        <is>
-          <t>M6vSXx4V98w</t>
-        </is>
-      </c>
-      <c r="G39" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Peut-on se fier au sentiment d'injustice ? - Charles RAMOND" par MSH Alpes</t>
-        </is>
-      </c>
-      <c r="H39" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/cramond-mini.webp</t>
         </is>
       </c>
       <c r="I39" s="36" t="n"/>
       <c r="J39" s="27" t="inlineStr">
         <is>
-          <t>epistemologie ; politique</t>
+          <t>epistemologie ; logique</t>
         </is>
       </c>
       <c r="K39" s="27" t="inlineStr">
         <is>
-          <t>Rationalisme</t>
+          <t>Analytique</t>
         </is>
       </c>
       <c r="L39" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de Derrida et de Spinoza.</t>
+          <t>philosophe français spécialiste de la philosophie du langage, de la logique et la connaissance.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3066,61 +3064,62 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="O39"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="137.25" customHeight="1" s="28">
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="162" customHeight="1" s="28">
       <c r="A40" s="34" t="n">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B40" s="34" t="n"/>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>Michel ONFRAY</t>
+          <t>Charles RAMOND</t>
         </is>
       </c>
       <c r="E40" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Onfray"  title=" Wikipedia"&gt;Michel ONFRAY&lt;/a&gt; (né en 1959) est un philosophe et essayiste français, l’un des auteurs de philosophie les plus lus et les plus discutés de son pays. Né à Argentan, en Normandie, dans une famille modeste, il enseigne pendant vingt ans la philosophie dans un lycée technique de Caen. En 2002, il fonde l’Université populaire de Caen, aux cours gratuits et ouverts à tous, où il donne pendant des années une « contre-histoire de la philosophie », diffusée par France Culture.&lt;/p&gt; &lt;p&gt;Sa pensée se veut &lt;a href="https://www.youtube.com/watch?v=l4PX2P-KuBE&amp;ab_channel=AlainBajom%C3%A9e"   title="L'hédonisme par Alain Bajomée"&gt;hédoniste&lt;/a&gt;, matérialiste et libertaire. Contre la tradition idéaliste et chrétienne, qui méprise le corps et le plaisir, il réhabilite des penseurs qu’il juge oubliés : les atomistes, les cyrénaïques, Épicure, les libertins ou les utilitaristes. Pour lui, la philosophie doit partir de la vie concrète et du corps, et aider chacun à se construire, à faire la « sculpture de soi ». Son &lt;em&gt;Traité d’athéologie&lt;/em&gt; (2005), critique radicale des trois monothéismes, est un grand succès de librairie. Il a écrit aussi sur l’art, sur la morale et sur les grandes figures de la pensée, souvent de manière polémique : son livre contre Freud, en 2010, a suscité de vives controverses. Dans &lt;em&gt;Décadence&lt;/em&gt; (2017), il décrit l’épuisement de la civilisation judéo-chrétienne. Il a enfin fondé en 2020 la revue &lt;em&gt;Front populaire&lt;/em&gt;, souverainiste, et défend un &lt;a href="https://www.youtube.com/watch?v=wikRuhGQExI&amp;ab_channel=FrontPopulaire"    title="Qu'est ce que le populisme par Front Populaire"&gt;populisme&lt;/a&gt; qui oppose le peuple aux élites. &lt;a href="https://www.youtube.com/watch?v=MNY2U-T2Xf4&amp;ab_channel=MichelOnfray-Topic"  title="Les Raisons de l'Art par Michel Onfray"&gt;&lt;em&gt;Les Raisons de l’art&lt;/em&gt;&lt;/a&gt; montrent aussi son intérêt pour la création.&lt;/p&gt; &lt;p&gt;Ses critiques lui reprochent des simplifications et des lectures partiales de l’histoire de la philosophie ; ses lecteurs saluent un passeur qui rend la philosophie vivante et accessible.&lt;/p&gt;  &lt;audio controls title="La philosophie nous permet d'être d'abord vivants et ensuite libres par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19063-03.04.2023-ITEMA_23336345-2023I32164S0093-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Ramond"  title=" Wikipedia"&gt;Charles RAMOND&lt;/a&gt;  est un philosophe français, professeur des universités à Paris-VIII Vincennes-Saint-Denis, où il occupe une chaire de philosophie des sciences et épistémologie de la culture. Spécialiste de Spinoza et de Derrida, il anime un séminaire dédié au philosophe néerlandais et explore la philosophie moderne et contemporaine, avec un accent sur l'ontologie, la logique et la politique des rationalismes classiques. Il a publié de nombreux ouvrages, dont une thèse sur la qualité et la quantité chez Spinoza (1995), un Vocabulaire de Spinoza (1999) et un Dictionnaire Spinoza (2007).  &lt;/p&gt; &lt;p&gt; Il présente Spinoza comme le philosophe de la modernité par excellence, avec des analyses du Traité politique soulignant l'antériorité du politique sur le moral et la démocratie comme régime absolu fondé sur le nombre et la puissance. Il a aussi étudié Descartes dans Descartes, Promesses et paradoxes (2011), explorant les paradoxes de la liberté et de l'irrésolution, ainsi que Derrida et la philosophie du langage. Ses conférences, comme celle à Pékin en 2019, relient Spinoza aux lectures marxistes et aux thèmes de justice et de droit.&lt;/p&gt; &lt;p&gt; Pour lui, la philosophie est la « résolution de problèmes théoriques par les moyens du langage ordinaire », mobilisant rhétorique, ironie et subtilités quotidiennes sans sacrifier rigueur ni clarté. Il rejette les degrés de conceptualité : on peut philosophier avec des termes simples comme « chats » ou « marmites », en mettant ce langage au service de la réflexion pour trancher des problèmes purement théoriques. Chez Spinoza, il défend un conservatisme rationnel immanent à la durée, où ce qui dure est rationnel, et une politique démocratique sceptique obéissant à la loi non pour sa bonté morale mais pour sa validité majoritaire. &lt;/p&gt; &lt;p&gt; Ses réflexions insistent sur la politique spinoziste : justice et injustice n'existent qu'en État, le droit se mesure à la puissance collective, et la démocratie privilégie les « préférences » sur les justifications morales ou républicaines. Il critique les morales théologiques résiduelles en politique moderne et valorise une pensée immanente ouverte aux changements, influencée par la raison spinoziste qui priorise la stabilité sur les valeurs transcendantes. Ramond aborde aussi les sentiments moraux comme l'injustice et les enjeux épistémologiques contemporains. &lt;/p&gt;             &lt;audio controls title="Dictionnaire Derrida de charles Ramond par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-10.01.2017-ITEMA_21192290-2017C24269S0010-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>ZYhgWCvrWJ8</t>
+          <t>M6vSXx4V98w</t>
         </is>
       </c>
       <c r="G40" s="36" t="inlineStr">
         <is>
-          <t>"Les raisons de l'art" par Librairie Mollat</t>
+          <t xml:space="preserve">"Peut-on se fier au sentiment d'injustice ? - Charles RAMOND" par MSH Alpes</t>
         </is>
       </c>
       <c r="H40" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/onfray-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/cramond-mini.webp</t>
         </is>
       </c>
       <c r="I40" s="36" t="n"/>
       <c r="J40" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>epistemologie ; politique</t>
         </is>
       </c>
       <c r="K40" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hédonisme ; Anarchisme ; Athéisme</t>
+          <t>Rationalisme</t>
         </is>
       </c>
       <c r="L40" s="27" t="inlineStr">
         <is>
-          <t>philosophe français connu pour son engagement pour l'Athéisme et l'Anarchisme.</t>
+          <t>philosophe français spécialiste de Derrida et de Spinoza.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3130,11 +3129,11 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="126.75" customHeight="1" s="28">
+          <t xml:space="preserve">continental</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="137.25" customHeight="1" s="28">
       <c r="A41" s="34" t="n">
         <v>1959</v>
       </c>
@@ -3146,240 +3145,235 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>Jean-Christophe GODDARD</t>
-        </is>
-      </c>
-      <c r="E41" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard"  title=" Wikipedia"&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J. G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime avec Marc Maesschalck le séminaire « Penser les décolonisations », commun aux universités de Toulouse et de Louvain-la-Neuve. Il organise aussi, avec le chorégraphe James Carlès, le festival Corpus Africana de Toulouse, et participe depuis 2019 à un séminaire d’anthropologie décoloniale à l’université nationale de Séoul. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href="https://www.youtube.com/watch?v=vEQWmSo67B4" style="color:#88A1E9" title="Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches"&gt;"Ce sont d'autres gens" &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la "qualité de la vie" sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href="https://www.youtube.com/watch?v=ZDpbSRrWIhU" title="Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées"&gt;"autre monde" &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;    &lt;audio controls title="Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t>Michel ONFRAY</t>
+        </is>
+      </c>
+      <c r="E41" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Onfray"  title=" Wikipedia"&gt;Michel ONFRAY&lt;/a&gt; (né en 1959) est un philosophe et essayiste français, l’un des auteurs de philosophie les plus lus et les plus discutés de son pays. Né à Argentan, en Normandie, dans une famille modeste, il enseigne pendant vingt ans la philosophie dans un lycée technique de Caen. En 2002, il fonde l’Université populaire de Caen, aux cours gratuits et ouverts à tous, où il donne pendant des années une « contre-histoire de la philosophie », diffusée par France Culture.&lt;/p&gt; &lt;p&gt;Sa pensée se veut &lt;a href="https://www.youtube.com/watch?v=l4PX2P-KuBE&amp;ab_channel=AlainBajom%C3%A9e"   title="L'hédonisme par Alain Bajomée"&gt;hédoniste&lt;/a&gt;, matérialiste et libertaire. Contre la tradition idéaliste et chrétienne, qui méprise le corps et le plaisir, il réhabilite des penseurs qu’il juge oubliés : les atomistes, les cyrénaïques, Épicure, les libertins ou les utilitaristes. Pour lui, la philosophie doit partir de la vie concrète et du corps, et aider chacun à se construire, à faire la « sculpture de soi ». Son &lt;em&gt;Traité d’athéologie&lt;/em&gt; (2005), critique radicale des trois monothéismes, est un grand succès de librairie. Il a écrit aussi sur l’art, sur la morale et sur les grandes figures de la pensée, souvent de manière polémique : son livre contre Freud, en 2010, a suscité de vives controverses. Dans &lt;em&gt;Décadence&lt;/em&gt; (2017), il décrit l’épuisement de la civilisation judéo-chrétienne. Il a enfin fondé en 2020 la revue &lt;em&gt;Front populaire&lt;/em&gt;, souverainiste, et défend un &lt;a href="https://www.youtube.com/watch?v=wikRuhGQExI&amp;ab_channel=FrontPopulaire"    title="Qu'est ce que le populisme par Front Populaire"&gt;populisme&lt;/a&gt; qui oppose le peuple aux élites. &lt;a href="https://www.youtube.com/watch?v=MNY2U-T2Xf4&amp;ab_channel=MichelOnfray-Topic"  title="Les Raisons de l'Art par Michel Onfray"&gt;&lt;em&gt;Les Raisons de l’art&lt;/em&gt;&lt;/a&gt; montrent aussi son intérêt pour la création.&lt;/p&gt; &lt;p&gt;Ses critiques lui reprochent des simplifications et des lectures partiales de l’histoire de la philosophie ; ses lecteurs saluent un passeur qui rend la philosophie vivante et accessible.&lt;/p&gt;  &lt;audio controls title="La philosophie nous permet d'être d'abord vivants et ensuite libres par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19063-03.04.2023-ITEMA_23336345-2023I32164S0093-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>ezZGT5SlWDk</t>
+          <t>ZYhgWCvrWJ8</t>
         </is>
       </c>
       <c r="G41" s="36" t="inlineStr">
         <is>
-          <t>"Contre-anthropologie du monde blanc - Jean-Christophe Goddard" par lundimatin</t>
+          <t>"Les raisons de l'art" par Librairie Mollat</t>
         </is>
       </c>
       <c r="H41" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/goddard-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/onfray-mini.webp</t>
         </is>
       </c>
       <c r="I41" s="36" t="n"/>
       <c r="J41" s="27" t="inlineStr">
         <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K41" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hédonisme ; Anarchisme ; Athéisme</t>
+        </is>
+      </c>
+      <c r="L41" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français connu pour son engagement pour l'Athéisme et l'Anarchisme.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="126.75" customHeight="1" s="28">
+      <c r="A42" s="34" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B42" s="34" t="n"/>
+      <c r="C42" s="34" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>Jean-Christophe GODDARD</t>
+        </is>
+      </c>
+      <c r="E42" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard"  title=" Wikipedia"&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J. G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime avec Marc Maesschalck le séminaire « Penser les décolonisations », commun aux universités de Toulouse et de Louvain-la-Neuve. Il organise aussi, avec le chorégraphe James Carlès, le festival Corpus Africana de Toulouse, et participe depuis 2019 à un séminaire d’anthropologie décoloniale à l’université nationale de Séoul. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href="https://www.youtube.com/watch?v=vEQWmSo67B4" style="color:#88A1E9" title="Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches"&gt;"Ce sont d'autres gens" &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la "qualité de la vie" sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href="https://www.youtube.com/watch?v=ZDpbSRrWIhU" title="Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées"&gt;"autre monde" &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;    &lt;audio controls title="Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+        </is>
+      </c>
+      <c r="F42" s="34" t="inlineStr">
+        <is>
+          <t>ezZGT5SlWDk</t>
+        </is>
+      </c>
+      <c r="G42" s="36" t="inlineStr">
+        <is>
+          <t>"Contre-anthropologie du monde blanc - Jean-Christophe Goddard" par lundimatin</t>
+        </is>
+      </c>
+      <c r="H42" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/goddard-mini.webp</t>
+        </is>
+      </c>
+      <c r="I42" s="36" t="n"/>
+      <c r="J42" s="27" t="inlineStr">
+        <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="K41" s="27" t="inlineStr">
+      <c r="K42" s="27" t="inlineStr">
         <is>
           <t>Post-structuralisme</t>
         </is>
       </c>
-      <c r="L41" s="27" t="inlineStr">
+      <c r="L42" s="27" t="inlineStr">
         <is>
           <t>philosophe français travaillant sur l'idéalisme allemand &amp;amp; la philosophie française du XXème.</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t xml:space="preserve">continental ; decolonial</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="191" customHeight="1" s="28">
-      <c r="A42" s="34" t="n">
+    <row r="43" ht="191" customHeight="1" s="28">
+      <c r="A43" s="34" t="n">
         <v>1961</v>
       </c>
-      <c r="B42" s="34" t="n"/>
-      <c r="C42" s="34" t="n">
+      <c r="B43" s="34" t="n"/>
+      <c r="C43" s="34" t="n">
         <v>1961</v>
       </c>
-      <c r="D42" s="35" t="inlineStr">
+      <c r="D43" s="35" t="inlineStr">
         <is>
           <t>Sandra LAUGIER</t>
         </is>
       </c>
-      <c r="E42" s="38" t="inlineStr">
+      <c r="E43" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sandra_Laugier" title=" Wikipedia"&gt;Sandra LAUGIER&lt;/a&gt;  est une philosophe française, professeure à l’université Paris 1 Panthéon-Sorbonne, membre de l’Institut Universitaire de France et spécialiste de philosophie du langage, de philosophie morale et de philosophie politique. Elle a aussi beaucoup travaillé sur Stanley Cavell, qu’elle a traduit en français, ainsi que sur Emerson, Thoreau et le perfectionnisme moral. &lt;/p&gt; &lt;p&gt; Sa philosophie accorde une place centrale à l’ordinaire : les gestes, les paroles, les liens quotidiens et les formes de vie concrètes sont pour elle des lieux essentiels de la pensée. Elle défend l’idée qu’il faut partir de l’expérience vécue plutôt que de grands systèmes abstraits, ce qui l’a conduite à développer une éthique du care, une réflexion sur le langage ordinaire et une attention aux formes discrètes de la vie commune. &lt;/p&gt; &lt;p&gt; Sur le plan politique, elle s’intéresse aux formes contemporaines de démocratie, à &lt;a href="https://www.youtube.com/watch?v=nlM-aPBIRdg" title="Sandra Laugier : reconnaître nos dépendances par France Inter"&gt;la désobéissance civile &lt;/a&gt; et aux mouvements horizontaux comme Nuit debout. Elle y voit une manière de repenser le politique à partir de l’expression des personnes, du souci du commun et de l’égalité effective des droits, plutôt que d’un modèle hiérarchique classique. Cette perspective la conduit à défendre une démocratie plus attentive aux voix singulières et aux pratiques collectives concrètes. &lt;/p&gt; &lt;p&gt; Elle a aussi élargi la philosophie à la culture populaire, notamment &lt;a href="https://www.youtube.com/watch?v=Rjd2XEvkqWc" title="Sandra Laugier : nos vies en séries par librairie mollat"&gt;aux séries télévisées, &lt;/a&gt; qu’elle considère comme un laboratoire d’expériences morales et politiques. Dans des ouvrages récents, elle montre que les séries peuvent aider à penser nos manières de vivre, nos attachements et nos conflits, en révélant des aspects très actuels de la sensibilité démocratique. &lt;/p&gt;  &lt;audio controls title="L’éthique animale avec Florence Burgat par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F42" s="34" t="inlineStr">
+      <c r="F43" s="34" t="inlineStr">
         <is>
           <t>fCTQpI27AeM</t>
         </is>
       </c>
-      <c r="G42" s="36" t="inlineStr">
+      <c r="G43" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">qui êtes vous Sandra LAUGIER par ABC Penser</t>
         </is>
       </c>
-      <c r="H42" s="37" t="inlineStr">
+      <c r="H43" s="37" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/slaugier-mini.webp</t>
         </is>
       </c>
-      <c r="I42" s="36" t="n"/>
-      <c r="J42" s="27" t="inlineStr">
+      <c r="I43" s="36" t="n"/>
+      <c r="J43" s="27" t="inlineStr">
         <is>
           <t>ethique ; epistemologie</t>
         </is>
       </c>
-      <c r="K42" s="27" t="inlineStr">
+      <c r="K43" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Analytique ; Éthique de la sollicitude</t>
         </is>
       </c>
-      <c r="L42" s="27" t="inlineStr">
+      <c r="L43" s="27" t="inlineStr">
         <is>
           <t>philosophe française spécialiste du langage, de la morale et de philosophie politique.</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t xml:space="preserve">genre ; reel</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="202.95" customHeight="1" s="28">
-      <c r="A43" s="34" t="n">
+    <row r="44" ht="202.95" customHeight="1" s="28">
+      <c r="A44" s="34" t="n">
         <v>1962</v>
       </c>
-      <c r="B43" s="34" t="n"/>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="B44" s="34" t="n"/>
+      <c r="C44" s="34" t="inlineStr">
         <is>
           <t>1962</t>
         </is>
       </c>
-      <c r="D43" s="35" t="inlineStr">
+      <c r="D44" s="35" t="inlineStr">
         <is>
           <t>Dominique MÉDA</t>
         </is>
       </c>
-      <c r="E43" s="36" t="inlineStr">
+      <c r="E44" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dominique_M%C3%A9da" title=" Wikipedia"&gt;Dominique MÉDA&lt;/a&gt;  est une philosophe française  reconnue pour ses analyses critiques sur le travail, les politiques sociales et la  &lt;a href="https://www.youtube.com/watch?v=jzyFjl0_QQE" title="La vraie révolution, c'est de désintensifier le travail ! Dominique Méda par Metabolism of Cities"&gt;transition écologique&lt;/a&gt;, elle combine une formation d'élite avec un engagement intellectuel profond sur les inégalités et la mesure de la richesse sociétale.  Elle est professeure de &lt;a href="https://www.youtube.com/watch?v=vKGU1tCOW90"  title="Dominique Méda, une sociologie contemporaine par Anthropologiques"&gt; sociologie &lt;/a&gt; à l'université Paris Dauphine-PSL, dirige l'IRISSO et a occupé la chaire "Reconversion écologique, travail et emploi" au Collège d'études mondiales. Elle fonde en 2010 le Laboratoire de l'égalité professionnelle entre femmes et hommes. &lt;/p&gt; &lt;p&gt; Ses travaux interrogent la centralité du travail dans les sociétés modernes, critiquant son rôle comme norme sociale totale et plaidant pour sa réduction au profit d'autres activités. Elle dénonce les limites du PIB comme indicateur de richesse, proposant des alternatives incluant le travail domestique, familial et écologique. Depuis les années 2010, elle se focalise sur la transition écologique, les inégalités de genre dans l'emploi et les réformes du travail  comme la flexisécurité. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"Le travail, une valeur en voie de disparition ?" paru en  1995 : histoire philosophique du concept de travail et plaidoyer pour sa redéfinition. "Qu'est-ce que la richesse ?" paru en 1999 : critique des indicateurs économiques traditionnels. "La reconversion écologique"(ouvrages récents) : lien entre écologie, emploi et justice sociale. &lt;/p&gt; &lt;audio controls title="Sandra LAUGIER par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/11189-26.03.2012-ITEMA_20355259-2012C15000E0020-ITE_00049197_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 ​
 </t>
         </is>
       </c>
-      <c r="F43" s="34" t="inlineStr">
+      <c r="F44" s="34" t="inlineStr">
         <is>
           <t>sF6TLJ92amU</t>
         </is>
       </c>
-      <c r="G43" s="36" t="inlineStr">
+      <c r="G44" s="36" t="inlineStr">
         <is>
           <t>"Compétition mondiale, dette, urgence climatique : comment sortir du piège ? - DOMINIQUE MEDA" par Sismique</t>
         </is>
       </c>
-      <c r="H43" s="36" t="inlineStr">
+      <c r="H44" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/meda-mini.webp</t>
-        </is>
-      </c>
-      <c r="I43" s="36" t="n"/>
-      <c r="J43" s="27" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="K43" s="27" t="inlineStr">
-        <is>
-          <t>Ecologisme</t>
-        </is>
-      </c>
-      <c r="L43" s="27" t="inlineStr">
-        <is>
-          <t>philosophe française menant une réflexion philosophique et sociologique sur la place du travail.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="189.75" customHeight="1" s="28">
-      <c r="A44" s="34" t="n">
-        <v>1962</v>
-      </c>
-      <c r="B44" s="34" t="n"/>
-      <c r="C44" s="34" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="D44" s="35" t="inlineStr">
-        <is>
-          <t>Florence BURGAT</t>
-        </is>
-      </c>
-      <c r="E44" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Florence_Burgat"  title=" Wikipedia"&gt;Florence BURGAT&lt;/a&gt; est une philosophe française spécialisée dans la phénoménologie de la vie animale et l’éthique animale. Son itinéraire académique comprend une formation en philosophie et une implication dans des laboratoires et équipes de recherche en sciences humaines, avec des décennies d’activité comme directrice de recherche et enseignante dans des institutions françaises de haut niveau. &lt;/p&gt; &lt;p&gt; "Liberté et inquiétude de la vie animale" paru en 2006 et "Une autre existence" paru en 2012 sont parmi ses essais-clés. Ils proposent une phénoménologie de l’animal qui attribue aux animaux une vie vécue, une biographie et un monde propre, en opposition à une conception purement biologique ou fonctionnelle de l’animalité. Son approche met en lumière la distinction entre vivre en première personne et exister biologiquement, et elle s’interroge sur la place des animaux dans les sociétés modernes — notamment dans les pratiques d’élevage, &lt;a href="https://reporterre.net/Florence-Burgat-L-institution-de-l-alimentation-carnee-reflete-un-desir-tres " title="Florence Burgat : « L’institution de l’alimentation carnée reflète un désir très profond de l’humanité  par Reportere"&gt;l’alimentation carnée&lt;/a&gt;, le droit animalier et les enjeux éthiques qui en découlent. Elle a aussi écrit sur la vie végétale et a développé une réflexion sur l’institution de l’alimentation carnée, la notion de sacrifice et les mythes qui entourent l’humanité carnivore, élargissant ainsi la portée philosophique de &lt;a href="https://www.youtube.com/watch?v=AzVErgOotx0" title=" Idées: Carnivore, l'Humanité n'est pas dans son assiette? par TV5Monde"&gt;l’éthique animale &lt;/a&gt; à des domaines comme la nourriture, le droit et la société. &lt;/p&gt; &lt;p&gt; Elle a publié et contribué à des revues et ouvrages dédiés à la philosophie contemporaine et à l’éthique animale. Elle est souvent associée à des discussions sur la manière dont les sociétés humaines reconnaissent ou nüancent l’existence des autres vivants et comment cela influence les pratiques culturelles et juridiques. Son travail est référencé dans des bibliographies universitaires et chez des éditeurs de sciences humaines, ce qui en fait une voix importante pour ceux qui s’interrogent sur la dignité et la vie des êtres non humains dans un cadre éthique et philosophique. &lt;/p&gt;   &lt;audio controls title="L’éthique animale avec Florence Burgat par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F44" s="34" t="inlineStr">
-        <is>
-          <t>wfuQnGA9izE</t>
-        </is>
-      </c>
-      <c r="G44" s="36" t="inlineStr">
-        <is>
-          <t>"L'humanité carnivore par Florence Burgat" par L214 Ethique &amp; Animaux</t>
-        </is>
-      </c>
-      <c r="H44" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/burgat-mini.webp</t>
         </is>
       </c>
       <c r="I44" s="36" t="n"/>
       <c r="J44" s="27" t="inlineStr">
         <is>
-          <t>ethique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K44" s="27" t="inlineStr">
         <is>
-          <t>Phénoménologie</t>
+          <t>Ecologisme</t>
         </is>
       </c>
       <c r="L44" s="27" t="inlineStr">
         <is>
-          <t>philosophe française spécialiste de la cause animale et des droits des animaux.</t>
+          <t>philosophe française menant une réflexion philosophique et sociologique sur la place du travail.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3394,11 +3388,11 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="147.75" customHeight="1" s="28">
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="189.75" customHeight="1" s="28">
       <c r="A45" s="34" t="n">
         <v>1962</v>
       </c>
@@ -3410,429 +3404,429 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
+          <t>Florence BURGAT</t>
+        </is>
+      </c>
+      <c r="E45" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Florence_Burgat"  title=" Wikipedia"&gt;Florence BURGAT&lt;/a&gt; est une philosophe française spécialisée dans la phénoménologie de la vie animale et l’éthique animale. Son itinéraire académique comprend une formation en philosophie et une implication dans des laboratoires et équipes de recherche en sciences humaines, avec des décennies d’activité comme directrice de recherche et enseignante dans des institutions françaises de haut niveau. &lt;/p&gt; &lt;p&gt; "Liberté et inquiétude de la vie animale" paru en 2006 et "Une autre existence" paru en 2012 sont parmi ses essais-clés. Ils proposent une phénoménologie de l’animal qui attribue aux animaux une vie vécue, une biographie et un monde propre, en opposition à une conception purement biologique ou fonctionnelle de l’animalité. Son approche met en lumière la distinction entre vivre en première personne et exister biologiquement, et elle s’interroge sur la place des animaux dans les sociétés modernes — notamment dans les pratiques d’élevage, &lt;a href="https://reporterre.net/Florence-Burgat-L-institution-de-l-alimentation-carnee-reflete-un-desir-tres " title="Florence Burgat : « L’institution de l’alimentation carnée reflète un désir très profond de l’humanité  par Reportere"&gt;l’alimentation carnée&lt;/a&gt;, le droit animalier et les enjeux éthiques qui en découlent. Elle a aussi écrit sur la vie végétale et a développé une réflexion sur l’institution de l’alimentation carnée, la notion de sacrifice et les mythes qui entourent l’humanité carnivore, élargissant ainsi la portée philosophique de &lt;a href="https://www.youtube.com/watch?v=AzVErgOotx0" title=" Idées: Carnivore, l'Humanité n'est pas dans son assiette? par TV5Monde"&gt;l’éthique animale &lt;/a&gt; à des domaines comme la nourriture, le droit et la société. &lt;/p&gt; &lt;p&gt; Elle a publié et contribué à des revues et ouvrages dédiés à la philosophie contemporaine et à l’éthique animale. Elle est souvent associée à des discussions sur la manière dont les sociétés humaines reconnaissent ou nüancent l’existence des autres vivants et comment cela influence les pratiques culturelles et juridiques. Son travail est référencé dans des bibliographies universitaires et chez des éditeurs de sciences humaines, ce qui en fait une voix importante pour ceux qui s’interrogent sur la dignité et la vie des êtres non humains dans un cadre éthique et philosophique. &lt;/p&gt;   &lt;audio controls title="L’éthique animale avec Florence Burgat par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F45" s="34" t="inlineStr">
+        <is>
+          <t>wfuQnGA9izE</t>
+        </is>
+      </c>
+      <c r="G45" s="36" t="inlineStr">
+        <is>
+          <t>"L'humanité carnivore par Florence Burgat" par L214 Ethique &amp; Animaux</t>
+        </is>
+      </c>
+      <c r="H45" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/burgat-mini.webp</t>
+        </is>
+      </c>
+      <c r="I45" s="36" t="n"/>
+      <c r="J45" s="27" t="inlineStr">
+        <is>
+          <t>ethique</t>
+        </is>
+      </c>
+      <c r="K45" s="27" t="inlineStr">
+        <is>
+          <t>Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L45" s="27" t="inlineStr">
+        <is>
+          <t>philosophe française spécialiste de la cause animale et des droits des animaux.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="147.75" customHeight="1" s="28">
+      <c r="A46" s="34" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B46" s="34" t="n"/>
+      <c r="C46" s="34" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
+        <is>
           <t>Marc CRÉPON</t>
         </is>
       </c>
-      <c r="E45" s="38" t="inlineStr">
+      <c r="E46" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon"  title=" Wikipedia"&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href="https://www.youtube.com/watch?v=xOKttB1HgSk"  title="Marc Crépon sur la violence  par France Inter "&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href="https://www.youtube.com/watch?v=kwFC9MSSWcg"  title="Marc Crépon : l’épreuve de la haine   par Librairie mollat "&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; Il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste. Directeur de recherche au CNRS, il a d’abord étudié la manière dont les philosophes allemands et français pensent les langues et les cultures. Dans &lt;em&gt;Le Consentement meurtrier&lt;/em&gt; (2012), il s’interroge sur la façon dont nous acceptons, souvent sans le voir, la violence faite à d’autres, par la guerre, la misère ou l’indifférence. Dans &lt;em&gt;L’Épreuve de la haine&lt;/em&gt; (2016) il cherche comment résister à la haine sans y répondre par la haine.  &lt;/p&gt; &lt;audio controls title="Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F45" s="34" t="inlineStr">
+      <c r="F46" s="34" t="inlineStr">
         <is>
           <t>zYbMprOKips</t>
         </is>
       </c>
-      <c r="G45" s="36" t="inlineStr">
+      <c r="G46" s="36" t="inlineStr">
         <is>
           <t>Qui êtes-vous Marc Crépon ?  par ABC Penser</t>
         </is>
       </c>
-      <c r="H45" s="36" t="inlineStr">
+      <c r="H46" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mcrepon-mini.webp</t>
         </is>
       </c>
-      <c r="I45" s="36" t="n"/>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="I46" s="36" t="n"/>
+      <c r="J46" s="27" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K45" s="27" t="inlineStr">
+      <c r="K46" s="27" t="inlineStr">
         <is>
           <t>Phénoménologie ; Herméneutique</t>
         </is>
       </c>
-      <c r="L45" s="27" t="inlineStr">
+      <c r="L46" s="27" t="inlineStr">
         <is>
           <t>philosophe français de la morale et de la politique, notamment de la violence, des langues et des communautés.</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="261.75" customHeight="1" s="28">
-      <c r="A46" s="34" t="n">
+    <row r="47" ht="261.75" customHeight="1" s="28">
+      <c r="A47" s="34" t="n">
         <v>1963</v>
       </c>
-      <c r="B46" s="34" t="n"/>
-      <c r="C46" s="34" t="n">
+      <c r="B47" s="34" t="n"/>
+      <c r="C47" s="34" t="n">
         <v>1963</v>
       </c>
-      <c r="D46" s="35" t="inlineStr">
+      <c r="D47" s="35" t="inlineStr">
         <is>
           <t>Paul AUDI</t>
         </is>
       </c>
-      <c r="E46" s="38" t="inlineStr">
+      <c r="E47" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Audi"  title=" Wikipedia"&gt;Paul AUDI&lt;/a&gt;  est un philosophe et écrivain français né à Beyrouth, au Liban, et ancien élève de l'École normale supérieure. Agrégé de philosophie et docteur en philosophie, il a soutenu une thèse sur Jean-Jacques Rousseau publiée en 1997. Après avoir enseigné à l'université de Paris-XII, il s'est éloigné du champ universitaire pour s'orienter vers l'édition, et aujourd'hui il est professeur invité dans diverses institutions en France et à l'étranger. Il est auteur de plus d'une trentaine d'ouvrages et membre de l'équipe de recherches PHILéPOL à l'université Paris Descartes. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre principalement sur les relations entre l'éthique et l'esthétique en Occident durant les Temps Modernes. Son œuvre explore ces liens à travers des &lt;a href="https://www.youtube.com/watch?v=3GRhkvYGMs0"  title="Paul Audi contrat social par le nouvel Obs"&gt;lectures de Rousseau, &lt;/a&gt;  Nietzsche, Lacan, Schopenhauer et Georges Bataille. Il est considéré comme un philosophe atypique, commençant à être reconnu hors de France. Sa pensée conjugue la vie du corps et la création artistique, l'éthique et la passion, avec un souci d'ancrer la pensée dans la vie physique. &lt;/p&gt; &lt;p&gt; L'idée centrale de sa philosophie est que l'acte de création et le comportement éthique ne forment qu'un seul et même geste, qui naît de la vie elle-même et finalement l'excède. Il nomme cette fusion « esth/éthique », considérant que l'éthique et l'esthétique dans l'acte de créer se confondent ou sont le recto et verso d'une même « explication avec la vie ». Pour lui, créer revient à « s'expliquer avec la vie », à faire de l'énigme que nous sommes une bribe d'un discours neuf. &lt;/p&gt; &lt;p&gt; L'éthique, selon lui, consiste d'abord en un travail sur soi, où « c'est moi-même qui suis la tâche ». La philosophie ne s'accomplit qu'au sein d'un corps à corps avec ce qui, en nous-mêmes, nous dépasse — non pas le monde ou un dehors, mais ce qui nous situe sur le  &lt;a href="https://www.youtube.com/watch?v=FJsDRUR9bYQ"  title="Paul Audi il faut le nuance par France Inter"&gt;« plan de la vie », &lt;/a&gt; qui ne recouvre ni le champ social ni l'espace politique. Cette éthique de la création, qu'il dénomme « esthéthique », n'est pas un code de règles mais une posture existentielle, une manière de se situer face au monde. &lt;/p&gt; &lt;p&gt; Il  s'intéresse également aux conditions permettant à l'être humain d'accéder à sa propre humanité, et interroge profondément la question de l'identité. Dans son ouvrage Troublante identité (2022), il parle pour la première fois de lui-même et de ce qui le hante, résistant à toute réduction de son être à sa provenance libanaise. Il désire en finir avec les clôtures identitaires et trouve son émancipation dans une conception juive d'une identité ouverte, toujours à construire, guidée par un impératif de justice à venir. Son dernier essai Le Vrai du beau (2026) transforme la contemplation d'un tableau en expérience de vérité, éclaircissant ce qui se joue en nous face à un tableau. &lt;/p&gt; 
   &lt;audio controls title="la verité picturale existe t’elle ?  Par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/26657-24.04.2026-ITEMA_24487813-2026F45096S0114-NET_MFI_F40118A5-5297-4676-86E9-2E9A248FB2F7-27-03023a67ff6f93208a5f302d7d3b8771.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F46" s="34" t="inlineStr">
+      <c r="F47" s="34" t="inlineStr">
         <is>
           <t>HvdSKzhBQCY</t>
         </is>
       </c>
-      <c r="G46" s="36" t="inlineStr">
+      <c r="G47" s="36" t="inlineStr">
         <is>
           <t>en orient, l’antijudaisme paul AUDI par Akadem</t>
         </is>
       </c>
-      <c r="H46" s="37" t="inlineStr">
+      <c r="H47" s="37" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/paudi-mini.webp</t>
         </is>
       </c>
-      <c r="I46" s="36" t="n"/>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="I47" s="36" t="n"/>
+      <c r="J47" s="27" t="inlineStr">
         <is>
           <t>ethique ; esthetique</t>
         </is>
       </c>
-      <c r="K46" s="27" t="inlineStr">
+      <c r="K47" s="27" t="inlineStr">
         <is>
           <t>Pessimisme</t>
         </is>
       </c>
-      <c r="L46" s="27" t="inlineStr">
+      <c r="L47" s="27" t="inlineStr">
         <is>
           <t>philosophe français  centré sur les relations entre l'éthique et l'esthétique en Occident.</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t xml:space="preserve">art</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="261.75" customHeight="1" s="28">
-      <c r="A47" s="34" t="n">
+    <row r="48" ht="261.75" customHeight="1" s="28">
+      <c r="A48" s="34" t="n">
         <v>1963</v>
       </c>
-      <c r="B47" s="34" t="n"/>
-      <c r="C47" s="34" t="n">
+      <c r="B48" s="34" t="n"/>
+      <c r="C48" s="34" t="n">
         <v>1963</v>
       </c>
-      <c r="D47" s="35" t="inlineStr">
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>Cyrille MICHON</t>
         </is>
       </c>
-      <c r="E47" s="38" t="inlineStr">
+      <c r="E48" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cyrille_Michon"  title=" Wikipedia"&gt;Cyrille MICHON&lt;/a&gt; est un philosophe français, professeur de philosophie à l’Université de Nantes. Formé à l’École normale supérieure, agrégé puis docteur en philosophie, il a d’abord consacré ses recherches à la philosophie médiévale, en particulier à Guillaume d’Ockham et à Thomas d’Aquin. Ses domaines de spécialité sont aujourd’hui la métaphysique, la philosophie de l’action, la   &lt;a href="https://www.youtube.com/watch?v=q-1VlvsVTOY"  title="vérité sur le christianisme par angelicum"&gt;philosophie de la religion &lt;/a&gt;  et la philosophie médiévale. &lt;/p&gt; &lt;p&gt; Sa réflexion porte principalement sur la liberté humaine, le libre arbitre et la responsabilité morale. Il pose une question classique mais toujours actuelle : pouvons-nous être véritablement responsables de nos actes si tout ce qui arrive est déterminé par des causes antérieures, par les lois de la nature ou par la providence divine ? Pour lui, comprendre la liberté exige donc d’examiner les rapports entre la volonté, l’action, les raisons de choisir et la responsabilité. &lt;/p&gt; &lt;p&gt; Dans Prescience et liberté, il étudie notamment le problème de la prescience divine : si Dieu sait infailliblement ce que nous allons faire, sommes-nous encore libres de le faire ou de ne pas le faire ? Il s’agit d’un problème central de la théologie philosophique, car il met en tension la connaissance parfaite de Dieu et la liberté humaine. Il cherche à montrer que la connaissance divine ne doit pas être confondue avec une contrainte causale exercée sur nos décisions. &lt;/p&gt; &lt;p&gt; Dans Répondre de soi. Enquête métaphysique sur la liberté humaine, publié en 2022, il défend une conception exigeante de la liberté, proche de ce que l’on appelle le libertarianisme métaphysique. Selon cette position, la liberté authentique n’est pas simplement le fait d’agir conformément à ses désirs, comme le soutiennent certains compatibilistes ; elle suppose que l’agent soit réellement l’auteur de son choix et qu’il puisse, dans un sens pertinent, prendre une autre décision. Il soutient ainsi que la responsabilité morale repose sur une liberté qui ne se réduit pas à l’absence de contrainte. &lt;/p&gt; &lt;p&gt; Sa philosophie se caractérise enfin par la rencontre entre la tradition médiévale, notamment thomiste, et la philosophie analytique contemporaine. Il mobilise une argumentation précise pour discuter le déterminisme, le hasard, les raisons de l’action et la responsabilité. Son œuvre cherche donc à montrer que les problèmes anciens — l’âme, la volonté, la providence ou la liberté — peuvent être reformulés avec les outils conceptuels de la philosophie contemporaine, sans perdre leur portée métaphysique. &lt;/p&gt; 
 &lt;audio controls title="le temps des monothéismes par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13094-29.12.2013-ITEMA_20567993-2013C21364E0017-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F47" s="34" t="inlineStr">
+      <c r="F48" s="34" t="inlineStr">
         <is>
           <t>-8NCPEbGk1o</t>
         </is>
       </c>
-      <c r="G47" s="36" t="inlineStr">
+      <c r="G48" s="36" t="inlineStr">
         <is>
           <t>Cyrille Michon – libre arbitre et déterminisme par Nantes Université</t>
         </is>
       </c>
-      <c r="H47" s="37" t="inlineStr">
+      <c r="H48" s="37" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/cmichon-mini.webp</t>
         </is>
       </c>
-      <c r="I47" s="36" t="n"/>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="I48" s="36" t="n"/>
+      <c r="J48" s="27" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="K47" s="27" t="inlineStr">
+      <c r="K48" s="27" t="inlineStr">
         <is>
           <t>Libertarianisme ; Thomisme</t>
         </is>
       </c>
-      <c r="L47" s="43" t="inlineStr">
+      <c r="L48" s="43" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de la philosophie médiévale, de la métaphysique et la philosophie de l’action.</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
+      <c r="N48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t xml:space="preserve">sens ; reel</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="207.75" customHeight="1" s="28">
-      <c r="A48" s="34" t="n">
+    <row r="49" ht="207.75" customHeight="1" s="28">
+      <c r="A49" s="34" t="n">
         <v>1964</v>
       </c>
-      <c r="B48" s="34" t="n"/>
-      <c r="C48" s="34" t="inlineStr">
+      <c r="B49" s="34" t="n"/>
+      <c r="C49" s="34" t="inlineStr">
         <is>
           <t>1964</t>
         </is>
       </c>
-      <c r="D48" s="35" t="inlineStr">
+      <c r="D49" s="35" t="inlineStr">
         <is>
           <t>Frédéric WORMS</t>
         </is>
       </c>
-      <c r="E48" s="36" t="inlineStr">
+      <c r="E49" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fr%C3%A9d%C3%A9ric_Worms"  title=" Wikipedia"&gt;Frédéric WORMS&lt;/a&gt; est un philosophe français  spécialiste de Bergson et des questions du vivant, du soin et de la démocratie. Ancien élève de l’ENS, agrégé de philosophie, il soutient en 1995 une thèse sur "le problème de l’esprit" chez Bergson, puis une habilitation publiée sous le titre "Bergson ou les deux sens de la vie". &lt;/p&gt; &lt;p&gt; Grand spécialiste d’Henri Bergson, il a dirigé l’édition critique ses œuvres complètes aux PUF et les Annales bergsoniennes. Sa lecture de Bergson insiste sur "les deux sens de la vie" : la vie comme simple conservation/instinct et la vie comme ouverture créatrice, tension qu’il prolonge dans sa propre philosophie du vivant. &lt;/p&gt; &lt;p&gt;  Son travail s’organise autour de deux axes : l’histoire de la philosophie et une réflexion propre sur les relations vitales et morales entre les êtres humains.  Il forge l’idée de  &lt;a href="https://www.youtube.com/watch?v=-gqpI3sJ3xQ"  title="Frédéric Worms, MOMENT par abc penser"&gt;"moment" &lt;/a&gt;  philosophique pour penser l’histoire de la philosophie française : chaque moment serait une rupture et un déplacement par rapport au précédent. &lt;/p&gt; &lt;p&gt; Dans ses &lt;a href="https://www.youtube.com/watch?v=dTWnuz7mZV4"  title="Frédéric Worms - Penser à quelqu'un par librairie mollat"&gt;livres récents &lt;/a&gt; (par ex. Pour un humanisme vital), il développe une philosophie du vivant qui articule la vulnérabilité, le refus de la mort sous toutes ses formes, et la nécessité de refonder l’éthique et la politique sur le soin. Le soin n’est pas seulement médical : il désigne pour lui l’ensemble des relations vitales, morales et politiques par lesquelles les humains se soutiennent ou se détruisent. &lt;/p&gt; &lt;p&gt; Membre du CCNE, il intervient sur la fin de vie, les biotechnologies, les neurosciences, la santé, en cherchant un équilibre entre protection des plus vulnérables et exigences démocratiques.  Il parle parfois de "maladies de la démocratie" : formes de fragilisation (inégalités, indifférence, désinformation) auxquelles il oppose l’idée d’une "démocratie vitale", nourrie par le soin et la reconnaissance des personnes. &lt;/p&gt; 
  &lt;audio controls title="Comment reconnaît-on l’intelligence ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22788-26.01.2026-ITEMA_24386219-2026C45539E0001-NET_MFC_7E5F54FC-88F9-4EAB-A263-ED6928FD46E4-21-b7522d721c0e520ad7f9edd0fee90576.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F48" s="34" t="inlineStr">
+      <c r="F49" s="34" t="inlineStr">
         <is>
           <t>w8wD5uNhq8Y</t>
         </is>
       </c>
-      <c r="G48" s="36" t="inlineStr">
+      <c r="G49" s="36" t="inlineStr">
         <is>
           <t>"Frédéric Worms : "Je suis un peu fatigué des intellectuels qui transgressent la bien-pensance" par France Culture</t>
         </is>
       </c>
-      <c r="H48" s="36" t="inlineStr">
+      <c r="H49" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/worms-mini.webp</t>
         </is>
       </c>
-      <c r="I48" s="36" t="n"/>
-      <c r="J48" s="27" t="inlineStr">
+      <c r="I49" s="36" t="n"/>
+      <c r="J49" s="27" t="inlineStr">
         <is>
           <t>ethique ; epistemologie</t>
         </is>
       </c>
-      <c r="K48" s="27" t="inlineStr">
+      <c r="K49" s="27" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L48" s="27" t="inlineStr">
+      <c r="L49" s="27" t="inlineStr">
         <is>
           <t>philosophe français historien de la philosophie &amp;amp; spécialiste de l'œuvre d'Henri Bergson.</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
+      <c r="N49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t xml:space="preserve">continental</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="116.25" customHeight="1" s="28">
-      <c r="A49" s="34" t="n">
+    <row r="50" ht="116.25" customHeight="1" s="28">
+      <c r="A50" s="34" t="n">
         <v>1964</v>
       </c>
-      <c r="B49" s="34" t="n"/>
-      <c r="C49" s="34" t="inlineStr">
+      <c r="B50" s="34" t="n"/>
+      <c r="C50" s="34" t="inlineStr">
         <is>
           <t>1964</t>
         </is>
       </c>
-      <c r="D49" s="35" t="inlineStr">
+      <c r="D50" s="35" t="inlineStr">
         <is>
           <t>Fabienne BRUGÈRE</t>
         </is>
       </c>
-      <c r="E49" s="36" t="inlineStr">
+      <c r="E50" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fabienne_Brug%C3%A8re" title=" Wikipedia"&gt;Fabienne BRUGÈRE&lt;/a&gt; est une philosophe française   spécialisée en esthétique, philosophie morale et politique, ainsi qu'en théorie féministe. Elle intègre l'École normale supérieure de Fontenay-Saint-Cloud en 1987 et obtient l'agrégation de philosophie en 1991, après un séjour à l'université de Londres. Sa thèse de 1996 porte sur la théorie de l'art chez Shaftesbury et elle a rejoint Paris-VIII en 2014 pour une chaire en philosophie des arts modernes et contemporains. &lt;/p&gt; &lt;p&gt; Elle a été vice-présidente aux relations internationales à Bordeaux-Montaigne et présidente de l'Université Paris Lumières de 2019 à 2023. Elle a aussi présidé le Conseil de développement durable de Bordeaux Métropole et dirige des collections comme "Perspectives du care" aux éditions de l'ENS Lyon. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'esthétique anglo-américaine, &lt;a href="https://www.youtube.com/watch?v=PmXPfJIOCUw"  title="Fabienne Brugère - L'Éthique du Care par librairie mollat"&gt;l'éthique du care  &lt;/a&gt; (notamment son ouvrage "L’éthique du care" paru en 2011), le féminisme et la sociabilité politique. Parmi ses récents essais : Désaimer. Manuel d’un retour à la vie (2024), La vraie histoire de l’impressionnisme (2024) et On ne naît pas femme, on le devient (2019). Elle montre que le &lt;em&gt;care&lt;/em&gt;, le soin apporté aux autres, n’est pas une affaire privée réservée aux femmes, mais une question politique qui concerne toute la société et la manière dont elle traite les plus vulnérables. Avec Guillaume le Blanc, elle a aussi écrit sur l’hospitalité et l’accueil des étrangers dans &lt;em&gt;La Fin de l’hospitalité&lt;/em&gt; (2017). &lt;/p&gt; 
   &lt;audio controls title="Le désamour avec Fabienne Brugère par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-03.05.2024-ITEMA_23729943-2024F45096S0124-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
-      <c r="F49" s="34" t="inlineStr">
+      <c r="F50" s="34" t="inlineStr">
         <is>
           <t>JkVPQiVidJM</t>
         </is>
       </c>
-      <c r="G49" s="36" t="inlineStr">
+      <c r="G50" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">"Fabienne Brugère - Désaimer : manuel d'un retour à la vie" par Librairie Mollat</t>
         </is>
       </c>
-      <c r="H49" s="36" t="inlineStr">
+      <c r="H50" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/brugere-mini.webp</t>
         </is>
       </c>
-      <c r="I49" s="36" t="n"/>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="I50" s="36" t="n"/>
+      <c r="J50" s="27" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="K49" s="27" t="inlineStr">
+      <c r="K50" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Libéralisme ; Éthique de la sollicitude</t>
         </is>
       </c>
-      <c r="L49" s="27" t="inlineStr">
+      <c r="L50" s="27" t="inlineStr">
         <is>
           <t>philosophe française spécialisée en esthétique, philosophie morale et politique et théorie féministe.</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t xml:space="preserve">genre ; justice ; art</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="126.75" customHeight="1" s="28">
-      <c r="A50" s="34" t="n">
+    <row r="51" ht="126.75" customHeight="1" s="28">
+      <c r="A51" s="34" t="n">
         <v>1964</v>
       </c>
-      <c r="B50" s="34" t="n"/>
-      <c r="C50" s="34" t="inlineStr">
+      <c r="B51" s="34" t="n"/>
+      <c r="C51" s="34" t="inlineStr">
         <is>
           <t>1964</t>
         </is>
       </c>
-      <c r="D50" s="35" t="inlineStr">
+      <c r="D51" s="35" t="inlineStr">
         <is>
           <t>Thierry MÉNISSIER</t>
         </is>
       </c>
-      <c r="E50" s="39" t="inlineStr">
+      <c r="E51" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thierry_M%C3%A9nissier" title=" Wikipedia"&gt;Thierry MÉNISSIER&lt;/a&gt;  est un philosophe français surtout connu pour ses travaux en philosophie politique et en histoire des idées. Il enseigne à l’université Grenoble Alpes et ses recherches s’appuient beaucoup sur Machiavel et la pensée de la Renaissance. &lt;/p&gt; &lt;p&gt;Sa philosophie s’intéresse d’abord à  &lt;a href="https://www.youtube.com/watch?v=KM8r0dQVwvE" title="Technologie et socéité soutenable par Agence Urbanisme t"&gt;l’éthique publique &lt;/a&gt;  et à la vie démocratique. Il cherche à comprendre comment les sociétés peuvent se gouverner sans réduire la politique à des principes abstraits, mais en partant des situations concrètes et des rapports de pouvoir. &lt;/p&gt; &lt;p&gt;  Un autre axe important de sa pensée concerne l’innovation et les technologies contemporaines. Il ne voit pas l’innovation comme un simple progrès automatique, mais comme un phénomène ambivalent qui oblige à réfléchir à ses effets sur la liberté, la responsabilité, la démocratie et le sens du bien commun. &lt;/p&gt; &lt;p&gt; Il est le &lt;a href="https://www.tumultieordini.com/" title="Tumulti e ordini
 Le blog de Thierry Ménissier"&gt;philosophe de l’action&lt;/a&gt;, de la décision et des transformations du monde contemporain. Sa pensée cherche à construire une éthique capable d’accompagner les mutations politiques,  technologiques et sociales  sans perdre de vue la justice. Spécialiste reconnu de Machiavel, auquel il a consacré plusieurs livres, il retient de lui l’idée que la politique se joue dans les circonstances, les conflits et l’occasion, et non dans l’application de règles éternelles. À Grenoble, il a animé des recherches sur l’éthique de l’innovation et sur l’intelligence artificielle, en associant philosophes, ingénieurs et citoyens à la réflexion sur les technologies. &lt;/p&gt;  &lt;audio controls title="Intelligence artificielle : par delà le bien et le mal par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14312-30.03.2022-ITEMA_22979351-2022C26360S0089-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F50" s="34" t="inlineStr">
+      <c r="F51" s="34" t="inlineStr">
         <is>
           <t>2m_2MDcB7h8</t>
         </is>
       </c>
-      <c r="G50" s="36" t="inlineStr">
+      <c r="G51" s="36" t="inlineStr">
         <is>
           <t>"Une philosophie politique de la corruption" par MSH Alpes</t>
         </is>
       </c>
-      <c r="H50" s="36" t="inlineStr">
+      <c r="H51" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/tmenissier-mini.webp</t>
-        </is>
-      </c>
-      <c r="I50" s="36" t="n"/>
-      <c r="J50" s="27" t="inlineStr">
-        <is>
-          <t>politique</t>
-        </is>
-      </c>
-      <c r="K50" s="27" t="inlineStr">
-        <is>
-          <t>Libéralisme</t>
-        </is>
-      </c>
-      <c r="L50" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français connu pour ses travaux en philosophie politique et en histoire des idées.</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="147.75" customHeight="1" s="28">
-      <c r="A51" s="34" t="n">
-        <v>1966</v>
-      </c>
-      <c r="B51" s="34" t="n"/>
-      <c r="C51" s="34" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="D51" s="35" t="inlineStr">
-        <is>
-          <t>Judith REVEL</t>
-        </is>
-      </c>
-      <c r="E51" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Judith_Revel"  title=" Wikipedia"&gt;Judith REVEL&lt;/a&gt; (née en 1966) est une philosophe française, spécialiste de Michel Foucault et de la pensée française et italienne contemporaine. Professeure à l’université Paris-Nanterre, après avoir enseigné à Paris 1 Panthéon-Sorbonne, elle a été membre de l’Institut universitaire de France. Elle a aussi traduit en français plusieurs philosophes italiens, en particulier Toni Negri.&lt;/p&gt; &lt;p&gt;Elle est l’une des meilleures connaisseuses de l’œuvre de Foucault, à laquelle elle a consacré plusieurs livres, dont &lt;em&gt;Le Vocabulaire de Foucault&lt;/em&gt; et un &lt;em&gt;Dictionnaire Foucault&lt;/em&gt;, ainsi qu’une étude sur la manière dont Foucault pense le discontinu, la rupture plutôt que la continuité de l’histoire. Elle montre comment, chez lui, l’analyse des pouvoirs qui façonnent les individus, la discipline puis la biopolitique, débouche sur une réflexion sur la « subjectivation » : la manière dont les sujets peuvent se constituer eux-mêmes, résister et inventer d’autres façons de vivre. Elle a aussi confronté Foucault à Merleau-Ponty. Avec d’autres penseurs, elle a développé la notion de « commun », qui désigne ce qui n’appartient ni à l’État ni aux propriétaires privés, mais est produit et géré ensemble par une communauté, et qui offre une alternative au couple du public et du privé. Plus largement, elle s’interroge sur une &lt;a href="https://www.youtube.com/watch?v=Y6J6TIET13w&amp;t=15s"  title=" Judith Revel // Suis-je responsable de l'humanité ? par Philomonaco"&gt;philosophie du présent&lt;/a&gt; : comment penser l’actualité, les luttes sociales et les transformations du travail.&lt;/p&gt; &lt;p&gt;Son travail relie ainsi l’histoire de la philosophie, la politique et les débats contemporains sur la démocratie, l’hégémonie culturelle et les mouvements sociaux.&lt;/p&gt;  &lt;audio controls title="L'hégémonie culturelle : Gramsci pillé de tous côtés par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-21.04.2025-ITEMA_24109706-2025C48904S0111-NET_MFC_47597AB9-4778-4D51-A8A2-7A3D26AD6489-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F51" s="34" t="inlineStr">
-        <is>
-          <t>me9YXsmumHs</t>
-        </is>
-      </c>
-      <c r="G51" s="36" t="inlineStr">
-        <is>
-          <t>"JUDITH REVEL - Quotidiens fragiles et labiles : le mortel des communs" par Rencontres Orient Occident</t>
-        </is>
-      </c>
-      <c r="H51" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/revel-mini.webp</t>
         </is>
       </c>
       <c r="I51" s="36" t="n"/>
       <c r="J51" s="27" t="inlineStr">
         <is>
-          <t>politique ; epistemologie</t>
+          <t>politique</t>
         </is>
       </c>
       <c r="K51" s="27" t="inlineStr">
         <is>
-          <t>Post-structuralisme</t>
+          <t>Libéralisme</t>
         </is>
       </c>
       <c r="L51" s="27" t="inlineStr">
         <is>
-          <t>philosophe française spécialiste des pensées française &amp;amp; italienne contemporaines.</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français connu pour ses travaux en philosophie politique et en histoire des idées.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3842,11 +3836,11 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">continental ; critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="161.25" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="147.75" customHeight="1" s="28">
       <c r="A52" s="34" t="n">
         <v>1966</v>
       </c>
@@ -3858,10 +3852,77 @@
       </c>
       <c r="D52" s="35" t="inlineStr">
         <is>
+          <t>Judith REVEL</t>
+        </is>
+      </c>
+      <c r="E52" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Judith_Revel"  title=" Wikipedia"&gt;Judith REVEL&lt;/a&gt; (née en 1966) est une philosophe française, spécialiste de Michel Foucault et de la pensée française et italienne contemporaine. Professeure à l’université Paris-Nanterre, après avoir enseigné à Paris 1 Panthéon-Sorbonne, elle a été membre de l’Institut universitaire de France. Elle a aussi traduit en français plusieurs philosophes italiens, en particulier Toni Negri.&lt;/p&gt; &lt;p&gt;Elle est l’une des meilleures connaisseuses de l’œuvre de Foucault, à laquelle elle a consacré plusieurs livres, dont &lt;em&gt;Le Vocabulaire de Foucault&lt;/em&gt; et un &lt;em&gt;Dictionnaire Foucault&lt;/em&gt;, ainsi qu’une étude sur la manière dont Foucault pense le discontinu, la rupture plutôt que la continuité de l’histoire. Elle montre comment, chez lui, l’analyse des pouvoirs qui façonnent les individus, la discipline puis la biopolitique, débouche sur une réflexion sur la « subjectivation » : la manière dont les sujets peuvent se constituer eux-mêmes, résister et inventer d’autres façons de vivre. Elle a aussi confronté Foucault à Merleau-Ponty. Avec d’autres penseurs, elle a développé la notion de « commun », qui désigne ce qui n’appartient ni à l’État ni aux propriétaires privés, mais est produit et géré ensemble par une communauté, et qui offre une alternative au couple du public et du privé. Plus largement, elle s’interroge sur une &lt;a href="https://www.youtube.com/watch?v=Y6J6TIET13w&amp;t=15s"  title=" Judith Revel // Suis-je responsable de l'humanité ? par Philomonaco"&gt;philosophie du présent&lt;/a&gt; : comment penser l’actualité, les luttes sociales et les transformations du travail.&lt;/p&gt; &lt;p&gt;Son travail relie ainsi l’histoire de la philosophie, la politique et les débats contemporains sur la démocratie, l’hégémonie culturelle et les mouvements sociaux.&lt;/p&gt;  &lt;audio controls title="L'hégémonie culturelle : Gramsci pillé de tous côtés par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-21.04.2025-ITEMA_24109706-2025C48904S0111-NET_MFC_47597AB9-4778-4D51-A8A2-7A3D26AD6489-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F52" s="34" t="inlineStr">
+        <is>
+          <t>me9YXsmumHs</t>
+        </is>
+      </c>
+      <c r="G52" s="36" t="inlineStr">
+        <is>
+          <t>"JUDITH REVEL - Quotidiens fragiles et labiles : le mortel des communs" par Rencontres Orient Occident</t>
+        </is>
+      </c>
+      <c r="H52" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/revel-mini.webp</t>
+        </is>
+      </c>
+      <c r="I52" s="36" t="n"/>
+      <c r="J52" s="27" t="inlineStr">
+        <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K52" s="27" t="inlineStr">
+        <is>
+          <t>Post-structuralisme</t>
+        </is>
+      </c>
+      <c r="L52" s="27" t="inlineStr">
+        <is>
+          <t>philosophe française spécialiste des pensées française &amp;amp; italienne contemporaines.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">continental ; critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="161.25" customHeight="1" s="28">
+      <c r="A53" s="34" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B53" s="34" t="n"/>
+      <c r="C53" s="34" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="D53" s="35" t="inlineStr">
+        <is>
           <t>Guillaume LE-BLANC</t>
         </is>
       </c>
-      <c r="E52" s="36" t="inlineStr">
+      <c r="E53" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_Le_Blanc_(%C3%A9crivain_fran%C3%A7ais)"  title=" Wikipedia"&gt;Guillaume LE BLANC&lt;/a&gt;  est un philosophe français spécialiste de philosophie sociale et politique, connu pour ses travaux sur la précarité, l’invisibilité sociale et les vies ordinaires. Il est professeur de philosophie sociale et politique à l’université Paris Cité et membre senior de l’Institut universitaire de France depuis 2022. &lt;/p&gt; &lt;p&gt; Il propose une philosophie des vies ordinaires qui prend au sérieux les expériences de précarité et de marginalisation. La précarité n’est pas une condition naturelle, mais une situation socialement produite qui  &lt;a href="https://www.lavie.fr/idees/debats/guillaume-le-blanc-nous-avons-bascule-dans-lage-de-la-tristesse-detre-soi-98208.php" style=" title=" Guillaume Le Blanc :  Nous avons basculé dans l’âge de la tristesse d’être soi  par lavie.fr"&gt;empêche les individus &lt;/a&gt; de se constituer comme autonomes dans leur rapport aux normes. Il montre comment les chômeurs, les "surnuméraires" et les "sans-voix" inventent de nouveaux langages et formes de vie, que la philosophie doit traduire pour contribuer à une &lt;a href="https://www.youtube.com/watch?v=2wtaG_uD8pQ" title=" L'hospitalité comme leçon de fraternité ? par Guillaume Le Blanc  par Espace Ethique"&gt;"société décente" &lt;/a&gt; et à une critique sociale des normes. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : "Canguilhem et les normes" paru en 1999, Canguilhem et la vie humaine / La vie humaine. Anthropologie et biologie en 2002. " Les maladies de l’homme normal" paru en 2004, "Vies ordinaires, vies précaires" en 2007, "L’invisibilité sociale" en 2009, "Que faire de notre vulnérabilité ?" en 2011 et  "L’insurrection des vies minuscules" en  2013. &lt;/p&gt; &lt;p&gt; Il hérite de Canguilhem et Foucault pour analyser la normalité, la santé, le pouvoir et les dispositifs d’invisibilisation, tout en les prolongeant vers une philosophie sociale de la vulnérabilité.
 Il défend une idée de la philosophie comme contre-culture, capable d’amplifier les voix marginalisées, d’explorer la créativité des vies ordinaires et de questionner les évidences de la normalité sociales. &lt;/p&gt; 
@@ -3869,97 +3930,35 @@
 </t>
         </is>
       </c>
-      <c r="F52" s="34" t="inlineStr">
+      <c r="F53" s="34" t="inlineStr">
         <is>
           <t>rT2XTNwqbRs</t>
         </is>
       </c>
-      <c r="G52" s="36" t="inlineStr">
+      <c r="G53" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">"Guillaume le Blanc - Que faire de notre vulnérabilité ?" par Librairie Mollat</t>
         </is>
       </c>
-      <c r="H52" s="36" t="inlineStr">
+      <c r="H53" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/blanc-mini.webp</t>
-        </is>
-      </c>
-      <c r="I52" s="36" t="n"/>
-      <c r="J52" s="27" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="K52" s="27" t="inlineStr">
-        <is>
-          <t>Post-structuralisme</t>
-        </is>
-      </c>
-      <c r="L52" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français qui s'interroge sur les normes dans leur dimension vitale et sociale.</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="219.75" customHeight="1" s="28">
-      <c r="A53" s="34" t="n">
-        <v>1967</v>
-      </c>
-      <c r="B53" s="34" t="n"/>
-      <c r="C53" s="34" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="D53" s="35" t="inlineStr">
-        <is>
-          <t>Quentin MEILLASSOUX</t>
-        </is>
-      </c>
-      <c r="E53" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Quentin_Meillassoux"  title=" Wikipedia"&gt;Quentin MEILLASSOUX&lt;/a&gt; est un philosophe français du courant qu'on appelle le  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif" style="color:#88A1E9" title=" Speculative Realism par Wikipedia "&gt;"réalisme spéculatif"&lt;/a&gt;. Le point de départ majeur de sa philosophie est "Le corrélationnisme" qui, selon lui, est la thèse dominante depuis Kant, et qui affirme qu'il est impossible de connaître le monde tel qu'il est en soi, indépendamment de notre rapport à lui (la corrélation entre la pensée et l'être). Cette position rend impossible de penser un "absolu" et nous enferme dans un cercle où nous ne pouvons accéder qu'à ce qui est "pour nous". &lt;a href="https://www.youtube.com/watch?v=29_IhFEWtlc" title="corine-pelluchon"&gt;Il s'interroge &lt;/a&gt;  sur la capacité de la science à parler de réalités "ancestrales", ce qui semble contredire le corrélationnisme. &lt;/p&gt; &lt;p&gt; Face au corrélationnisme, il propose de postuler que la seule chose nécessaire est la &lt;a href="https://www.youtube.com/watch?v=5ECkL9MKDiI" title=" Quentin Meillassoux's "After Finitude" par Five Minute Philosophy "&gt; contingence absolue&lt;/a&gt;. Cela signifie que toutes les lois de la nature, toutes les entités existantes, sont radicalement contingentes et pourraient être différentes, ou même ne pas exister du tout. Il n'y a aucune raison ou fondement nécessaire à l'existence du monde tel qu'il est. Cette absence de raison ultime n'est pas un aveu d'ignorance, mais une vérité ontologique. C'est ce qu'il appelle le "principe de factualité". En affirmant cette contingence radicale, il s'inscrit dans une tradition matérialiste, mais une tradition qui se veut "spéculative" parce qu'elle cherche à penser l'absolu (l'absolu de la contingence) au-delà des limites imposées par le corrélationnisme. Il s'agit de s'affranchir de la dépendance de l'être vis-à-vis de la pensée. Sa pensée est notamment développée dans son ouvrage le plus célèbre,  &lt;a  href="https://fr.wikipedia.org/wiki/Apr%C3%A8s_la_finitude._Essai_sur_la_n%C3%A9cessit%C3%A9_de_la_contingence#:~:text=Quentin%20Meillassoux%20nomme%20cette%20philosophie,la%20pens%C3%A9e%20de%20l'absolu." title=" "Après la finitude. Essai sur la nécessité de la contingence" par Wikipedia "&gt;"Après la finitude. Essai sur la nécessité de la contingence"&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;  Dans sa thèse de doctorat "L'inexistence divine", il explore la possibilité d'un "dieu à venir". Pour lui, si Dieu n'existe pas actuellement, sa non-existence n'est pas une nécessité, mais une contingence. Ainsi, il n'est pas impossible qu'un jour un "Dieu" puisse émerger d'une manière ou d'une autre, à la suite d'un changement radical des lois physiques. &lt;/p&gt; &lt;p&gt; Dans son second livre "Le Nombre et la Sirène", il propose une lecture inédite du célèbre poème de Stéphane Mallarmé, "Un coup de dés jamais n'abolira le hasard". Il y développe une analyse détaillée, y découvrant  &lt;a href="https://www.youtube.com/watch?v=yKwqoW9PxVA" title=" Le code secret de Mallarmé enfin dévoilé?  par De Revolutionibus "&gt;un code numérique&lt;/a&gt;  qui, selon lui, serait intégré au texte par Mallarmé lui-même, en lien avec ses réflexions sur le hasard et la contingence.&lt;/p&gt; &lt;p&gt; En critiquant radicalement le corrélationnisme, il cherche à ouvrir la voie à une nouvelle forme de réalisme et de matérialisme, où la contingence est pensée non pas comme une limite de notre connaissance, mais comme une propriété fondamentale de l'être lui-même. &lt;/p&gt;   &lt;audio controls title="Quentin Meillassoux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-16.12.2011-ITEMA_20320127-2011C3403E0204-ITE_00047293_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F53" s="34" t="inlineStr">
-        <is>
-          <t>Ic8h23MNVWU</t>
-        </is>
-      </c>
-      <c r="G53" s="36" t="inlineStr">
-        <is>
-          <t>"Quentin Meillassoux : Principes du signe creux" par Ecole Normale superieure</t>
-        </is>
-      </c>
-      <c r="H53" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/meillassoux-mini.webp</t>
         </is>
       </c>
       <c r="I53" s="36" t="n"/>
       <c r="J53" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; epistemologie</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K53" s="27" t="inlineStr">
         <is>
-          <t>Nouveau réalisme</t>
+          <t>Post-structuralisme</t>
         </is>
       </c>
       <c r="L53" s="27" t="inlineStr">
         <is>
-          <t>philosophe français qui a contribué à la formation du réalisme spéculatif.</t>
+          <t>philosophe français qui s'interroge sur les normes dans leur dimension vitale et sociale.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3969,11 +3968,11 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="198" customHeight="1" s="28">
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="219.75" customHeight="1" s="28">
       <c r="A54" s="34" t="n">
         <v>1967</v>
       </c>
@@ -3985,48 +3984,43 @@
       </c>
       <c r="D54" s="35" t="inlineStr">
         <is>
-          <t>Corine PELLUCHON</t>
-        </is>
-      </c>
-      <c r="E54" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Corine_Pelluchon"  style="color:#6A142A"  title=" Wikipedia"&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href="https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s" title="NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco"&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &lt;p&gt;Manifeste animaliste. Politiser la cause animale ( 2017 ) Éthique de la considération ( 2018) Réparons le monde. Humains, animaux, nature (2020) Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=zpzzDqYhF-8" title="Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat"&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href="https://www.youtube.com/watch?v=tmk-UzN1j70"  title="Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media"&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title="Corine Pelluchon par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t>Quentin MEILLASSOUX</t>
+        </is>
+      </c>
+      <c r="E54" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Quentin_Meillassoux"  title=" Wikipedia"&gt;Quentin MEILLASSOUX&lt;/a&gt; est un philosophe français du courant qu'on appelle le  &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9alisme_sp%C3%A9culatif" style="color:#88A1E9" title=" Speculative Realism par Wikipedia "&gt;"réalisme spéculatif"&lt;/a&gt;. Le point de départ majeur de sa philosophie est "Le corrélationnisme" qui, selon lui, est la thèse dominante depuis Kant, et qui affirme qu'il est impossible de connaître le monde tel qu'il est en soi, indépendamment de notre rapport à lui (la corrélation entre la pensée et l'être). Cette position rend impossible de penser un "absolu" et nous enferme dans un cercle où nous ne pouvons accéder qu'à ce qui est "pour nous". &lt;a href="https://www.youtube.com/watch?v=29_IhFEWtlc" title="corine-pelluchon"&gt;Il s'interroge &lt;/a&gt;  sur la capacité de la science à parler de réalités "ancestrales", ce qui semble contredire le corrélationnisme. &lt;/p&gt; &lt;p&gt; Face au corrélationnisme, il propose de postuler que la seule chose nécessaire est la &lt;a href="https://www.youtube.com/watch?v=5ECkL9MKDiI" title=" Quentin Meillassoux's "After Finitude" par Five Minute Philosophy "&gt; contingence absolue&lt;/a&gt;. Cela signifie que toutes les lois de la nature, toutes les entités existantes, sont radicalement contingentes et pourraient être différentes, ou même ne pas exister du tout. Il n'y a aucune raison ou fondement nécessaire à l'existence du monde tel qu'il est. Cette absence de raison ultime n'est pas un aveu d'ignorance, mais une vérité ontologique. C'est ce qu'il appelle le "principe de factualité". En affirmant cette contingence radicale, il s'inscrit dans une tradition matérialiste, mais une tradition qui se veut "spéculative" parce qu'elle cherche à penser l'absolu (l'absolu de la contingence) au-delà des limites imposées par le corrélationnisme. Il s'agit de s'affranchir de la dépendance de l'être vis-à-vis de la pensée. Sa pensée est notamment développée dans son ouvrage le plus célèbre,  &lt;a  href="https://fr.wikipedia.org/wiki/Apr%C3%A8s_la_finitude._Essai_sur_la_n%C3%A9cessit%C3%A9_de_la_contingence#:~:text=Quentin%20Meillassoux%20nomme%20cette%20philosophie,la%20pens%C3%A9e%20de%20l'absolu." title=" "Après la finitude. Essai sur la nécessité de la contingence" par Wikipedia "&gt;"Après la finitude. Essai sur la nécessité de la contingence"&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;  Dans sa thèse de doctorat "L'inexistence divine", il explore la possibilité d'un "dieu à venir". Pour lui, si Dieu n'existe pas actuellement, sa non-existence n'est pas une nécessité, mais une contingence. Ainsi, il n'est pas impossible qu'un jour un "Dieu" puisse émerger d'une manière ou d'une autre, à la suite d'un changement radical des lois physiques. &lt;/p&gt; &lt;p&gt; Dans son second livre "Le Nombre et la Sirène", il propose une lecture inédite du célèbre poème de Stéphane Mallarmé, "Un coup de dés jamais n'abolira le hasard". Il y développe une analyse détaillée, y découvrant  &lt;a href="https://www.youtube.com/watch?v=yKwqoW9PxVA" title=" Le code secret de Mallarmé enfin dévoilé?  par De Revolutionibus "&gt;un code numérique&lt;/a&gt;  qui, selon lui, serait intégré au texte par Mallarmé lui-même, en lien avec ses réflexions sur le hasard et la contingence.&lt;/p&gt; &lt;p&gt; En critiquant radicalement le corrélationnisme, il cherche à ouvrir la voie à une nouvelle forme de réalisme et de matérialisme, où la contingence est pensée non pas comme une limite de notre connaissance, mais comme une propriété fondamentale de l'être lui-même. &lt;/p&gt;   &lt;audio controls title="Quentin Meillassoux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10080-16.12.2011-ITEMA_20320127-2011C3403E0204-ITE_00047293_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>_qZVJll1J2k</t>
+          <t>Ic8h23MNVWU</t>
         </is>
       </c>
       <c r="G54" s="36" t="inlineStr">
         <is>
-          <t>"Corine Pelluchon : réparer le monde des vivants" par La Grande Librairie</t>
+          <t>"Quentin Meillassoux : Principes du signe creux" par Ecole Normale superieure</t>
         </is>
       </c>
       <c r="H54" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/pelluchon-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/meillassoux-mini.webp</t>
         </is>
       </c>
       <c r="I54" s="36" t="n"/>
       <c r="J54" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K54" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phénoménologie ; Éthique de la sollicitude</t>
+          <t>Nouveau réalisme</t>
         </is>
       </c>
       <c r="L54" s="27" t="inlineStr">
         <is>
-          <t>philosophe française qui s'intéresse aux questions d'éthique et de philosophie morale et politique.</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français qui a contribué à la formation du réalisme spéculatif.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4036,11 +4030,11 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie ; justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="162" customHeight="1" s="28">
+          <t xml:space="preserve">reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="198" customHeight="1" s="28">
       <c r="A55" s="34" t="n">
         <v>1967</v>
       </c>
@@ -4052,43 +4046,48 @@
       </c>
       <c r="D55" s="35" t="inlineStr">
         <is>
-          <t>Denis MOREAU</t>
-        </is>
-      </c>
-      <c r="E55" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Denis_Moreau"  title=" Wikipedia"&gt;Denis MOREAU&lt;/a&gt; est un philosophe français spécialiste de la philosophie moderne et de la philosophie de la religion. . Docteur en philosophie (1996) et habilité à diriger des recherches (2008), il a été membre junior de l'Institut universitaire de France dès 2004. &lt;/p&gt; &lt;p&gt; Ses travaux portent principalement sur le XVIIe siècle, avec un focus sur Descartes, le cartésianisme, Malebranche et Spinoza. En philosophie de la religion, il explore le christianisme sous un angle rationaliste, s'inscrivant dans une tradition qu'il nomme "rationalisme chrétien" incluant Augustin, Thomas d'Aquin, Descartes ou encore Benoît XVI. Il aborde des thèmes comme le salut, le mariage, la résurrection et la foi, en articulant justification rationnelle et impact existentiel. &lt;/p&gt; &lt;p&gt; Il a publié plusieurs ouvrages marquants qui allient philosophie moderne, histoire de la philosophie et réflexion sur le christianisme rationalisé. Ses travaux les plus importants se divisent entre essais académiques sur le XVIIe siècle et livres grand public sur la foi. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=sglQGZawGWA&amp;list=PL2d4vA4vfs79mlFW_Mo0iP8anxf1F0XXG" title=" DESCARTES - Une expérience philosophique de la vérité, Denis Moreau par Editions M-Editer"&gt;Deux cartésiens&lt;/a&gt;. La polémique entre Descartes et Gassendi (2000), qui analyse les débats entre ces deux penseurs sur la connaissance et la méthode. &lt;/p&gt; &lt;p&gt;Mort où est ta victoire ? (2017), une réflexion sur la mort et la résurrection vue sous l'angle philosophique&lt;/p&gt; &lt;p&gt;Les voies du salut (2015), qui explore les conceptions chrétiennes du salut de manière accessible et rationnelle. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=AMv4Quma6t0"title=" Denis Moreau - Résurrections : traverser les nuits de nos vies par Librairie La Procure"&gt;Résurrections. Traverser les nuits de nos vies&lt;/a&gt; (2022), qui applique des thèmes chrétiens à l'existence contemporaine.&lt;/p&gt; &lt;p&gt;Comment peut-on être catholique ? (2019), un plaidoyer rationnel pour la foi catholique dans un monde sécularisé. &lt;/p&gt;  &lt;audio controls title=" Cogito ergo sum : Descartes l'a-t-il réellement écrit ainsi ? Entretien avec Denis Moreau par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-08.09.2023-ITEMA_23480427-2023F45096S0251-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Corine PELLUCHON</t>
+        </is>
+      </c>
+      <c r="E55" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Corine_Pelluchon"  style="color:#6A142A"  title=" Wikipedia"&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href="https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s" title="NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco"&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &lt;p&gt;Manifeste animaliste. Politiser la cause animale ( 2017 ) Éthique de la considération ( 2018) Réparons le monde. Humains, animaux, nature (2020) Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=zpzzDqYhF-8" title="Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat"&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href="https://www.youtube.com/watch?v=tmk-UzN1j70"  title="Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media"&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title="Corine Pelluchon par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>pMOSVwX5U6Y</t>
+          <t>_qZVJll1J2k</t>
         </is>
       </c>
       <c r="G55" s="36" t="inlineStr">
         <is>
-          <t>"Être CHRÉTIEN est LA MEILLEURE FAÇON de RÉUSSIR SA VIE !" : Denis Moreau, professeur de philosophie par Meditatio</t>
+          <t>"Corine Pelluchon : réparer le monde des vivants" par La Grande Librairie</t>
         </is>
       </c>
       <c r="H55" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/moreau-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/pelluchon-mini.webp</t>
         </is>
       </c>
       <c r="I55" s="36" t="n"/>
       <c r="J55" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; spiritualite</t>
+          <t>ethique ; politique</t>
         </is>
       </c>
       <c r="K55" s="27" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
+          <t xml:space="preserve">Phénoménologie ; Éthique de la sollicitude</t>
         </is>
       </c>
       <c r="L55" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste du cartésianisme et de la philosophie des religions.</t>
+          <t>philosophe française qui s'intéresse aux questions d'éthique et de philosophie morale et politique.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4098,11 +4097,11 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">sens</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="126.75" customHeight="1" s="28">
+          <t xml:space="preserve">ecologie ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="162" customHeight="1" s="28">
       <c r="A56" s="34" t="n">
         <v>1967</v>
       </c>
@@ -4114,43 +4113,43 @@
       </c>
       <c r="D56" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stéphane HABER</t>
+          <t>Denis MOREAU</t>
         </is>
       </c>
       <c r="E56" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/St%C3%A9phane_Haber" title=" Wikipedia"&gt;Stéphane HABER&lt;/a&gt;  est un philosophe français spécialiste de la philosophie sociale et politique, ainsi que de l'épistémologie des sciences humaines. Son doctorat obtenu en 1996 à l'université de Besançon portait sur les formes de connaissance du présent dans les sciences sociales, sous la direction de Robert Damien. &lt;/p&gt; &lt;p&gt; Professeur à l'université Paris Nanterre, il est directeur adjoint du laboratoire Sophiapol. Ses enseignements couvrent l'histoire et l'épistémologie des sciences humaines, la philosophie contemporaine et les problèmes de théorie sociale et politique.&lt;/p&gt; &lt;p&gt;  Ses livres incluent Les Sciences humaines (1995), Habermas et la sociologie (1998), Freud et la théorie sociale (2012), Penser le néocapitalisme (2013). Il a dirigé des ouvrages comme L’Action en philosophie contemporaine (2005) et contribué à des revues sur Marx, l'aliénation et le capitalisme. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur  &lt;a href="https://www.youtube.com/watch?v=ZxECyRcOzFY&amp;t=11s"  title=". Haber : Exploitation du travail, appropriation de la nature, crise climatique. par Penser la Transformation"&gt; les interactions philosophie&lt;/a&gt;/sciences sociales, les marxismes contemporains, le néocapitalisme, l'aliénation subjective et objective, ainsi que les pathologies sociales et la théorie critique. Dans &lt;em&gt;L’Aliénation&lt;/em&gt; (2007), il redonne vie à cette notion héritée de Hegel et de Marx : on est aliéné quand on ne se reconnaît plus dans sa propre vie, ses activités ou ses institutions. Il montre que l’idée reste utile pour décrire les souffrances sociales d’aujourd’hui. Dans &lt;em&gt;Penser le néocapitalisme&lt;/em&gt;, il analyse un capitalisme qui s’étend à toutes les dimensions de l’existence, et ses travaux récents relient l’exploitation du travail et celle de la nature.</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Denis_Moreau"  title=" Wikipedia"&gt;Denis MOREAU&lt;/a&gt; est un philosophe français spécialiste de la philosophie moderne et de la philosophie de la religion. . Docteur en philosophie (1996) et habilité à diriger des recherches (2008), il a été membre junior de l'Institut universitaire de France dès 2004. &lt;/p&gt; &lt;p&gt; Ses travaux portent principalement sur le XVIIe siècle, avec un focus sur Descartes, le cartésianisme, Malebranche et Spinoza. En philosophie de la religion, il explore le christianisme sous un angle rationaliste, s'inscrivant dans une tradition qu'il nomme "rationalisme chrétien" incluant Augustin, Thomas d'Aquin, Descartes ou encore Benoît XVI. Il aborde des thèmes comme le salut, le mariage, la résurrection et la foi, en articulant justification rationnelle et impact existentiel. &lt;/p&gt; &lt;p&gt; Il a publié plusieurs ouvrages marquants qui allient philosophie moderne, histoire de la philosophie et réflexion sur le christianisme rationalisé. Ses travaux les plus importants se divisent entre essais académiques sur le XVIIe siècle et livres grand public sur la foi. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=sglQGZawGWA&amp;list=PL2d4vA4vfs79mlFW_Mo0iP8anxf1F0XXG" title=" DESCARTES - Une expérience philosophique de la vérité, Denis Moreau par Editions M-Editer"&gt;Deux cartésiens&lt;/a&gt;. La polémique entre Descartes et Gassendi (2000), qui analyse les débats entre ces deux penseurs sur la connaissance et la méthode. &lt;/p&gt; &lt;p&gt;Mort où est ta victoire ? (2017), une réflexion sur la mort et la résurrection vue sous l'angle philosophique&lt;/p&gt; &lt;p&gt;Les voies du salut (2015), qui explore les conceptions chrétiennes du salut de manière accessible et rationnelle. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=AMv4Quma6t0"title=" Denis Moreau - Résurrections : traverser les nuits de nos vies par Librairie La Procure"&gt;Résurrections. Traverser les nuits de nos vies&lt;/a&gt; (2022), qui applique des thèmes chrétiens à l'existence contemporaine.&lt;/p&gt; &lt;p&gt;Comment peut-on être catholique ? (2019), un plaidoyer rationnel pour la foi catholique dans un monde sécularisé. &lt;/p&gt;  &lt;audio controls title=" Cogito ergo sum : Descartes l'a-t-il réellement écrit ainsi ? Entretien avec Denis Moreau par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-08.09.2023-ITEMA_23480427-2023F45096S0251-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>vnSkomfLExM</t>
+          <t>pMOSVwX5U6Y</t>
         </is>
       </c>
       <c r="G56" s="36" t="inlineStr">
         <is>
-          <t>"Stephane Haber" par Université de Namur</t>
+          <t>"Être CHRÉTIEN est LA MEILLEURE FAÇON de RÉUSSIR SA VIE !" : Denis Moreau, professeur de philosophie par Meditatio</t>
         </is>
       </c>
       <c r="H56" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/haber-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/moreau-mini.webp</t>
         </is>
       </c>
       <c r="I56" s="36" t="n"/>
       <c r="J56" s="27" t="inlineStr">
         <is>
-          <t>politique ; epistemologie</t>
+          <t>metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K56" s="27" t="inlineStr">
         <is>
-          <t>Théorie Critique</t>
+          <t>Spiritualisme</t>
         </is>
       </c>
       <c r="L56" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la philosophie sociale &amp;amp; politique.</t>
+          <t>philosophe français spécialiste du cartésianisme et de la philosophie des religions.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4160,11 +4159,11 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="150" customHeight="1" s="28">
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="126.75" customHeight="1" s="28">
       <c r="A57" s="34" t="n">
         <v>1967</v>
       </c>
@@ -4176,288 +4175,283 @@
       </c>
       <c r="D57" s="35" t="inlineStr">
         <is>
-          <t>Emmanuel RENAULT</t>
+          <t xml:space="preserve">Stéphane HABER</t>
         </is>
       </c>
       <c r="E57" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Renault"  title=" Wikipedia"&gt;Emmanuel RENAULT&lt;/a&gt; est un philosophe français, spécialisé en théorie critique, philosophie sociale et rapports entre reconnaissance, conflit et domination. Il est largement associé à une approche pragmatiste et pluraliste, cherchant à articuler Hegel, Marx, Honneth et le pragmatisme de Dewey dans une perspective interdisciplinaire. &lt;/p&gt; &lt;p&gt;  Il développe une approche qui croise les traditions marxistes et pragmatistes, et met l’accent sur les questions de travail, de justice, de  &lt;a href="https://www.nonfiction.fr/article-11867-abolir-lexploitation-entretien-avec-emmanuel-renault.htm" title="Abolir l'exploitation : entretien avec Emmanuel Renault. par nonfiction"&gt; souffrance sociale &lt;/a&gt; et de reconnaissance et il analyse comment les conflits sociaux, la reconnaissance et les formes de domination structurent l’injustice moderne.  Il s’inscrit dans une démarche qui remet en question les bases normatives de la justice politique en faveur d’une compréhension de l’injustice comme déni de reconnaissance et comme expérience de souffrance sociale. &lt;/p&gt; &lt;p&gt; Son travail est influent dans les débats sur la philosophie sociale en France et à l’étranger, et il participe à l’extension des cadres marxistes et pragmatistes dans la réflexion sur le travail,  &lt;a href="https://www.youtube.com/watch?v=6DriuHGugCA" title=" l'impensé de l'exploitation par Hors serie"&gt; l’exploitation &lt;/a&gt; et la justice sociale. Ses publications représentatives : "Le Mépris social" paru en  2000 : exploration des formes de mépris et des dynamiques sociales qui les sous-tendent. "Souffrances sociales" paru en 2008 : analyse des mécanismes de souffrance dans les sociétés contemporaines et leur lien avec la reconnaissance et la distribution des ressources. "Reconnaissance, conflit, domination"  en 2017 : thèse centrale sur la relation entre reconnaissance, conflit et domination, et leur rôle dans la configuration des inégalités. &lt;/p&gt;  &lt;audio controls title="Mépris social : comment sortir du dialogue de sourds?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-29.10.2015-ITEMA_20828700-2015C19327S0302-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/St%C3%A9phane_Haber" title=" Wikipedia"&gt;Stéphane HABER&lt;/a&gt;  est un philosophe français spécialiste de la philosophie sociale et politique, ainsi que de l'épistémologie des sciences humaines. Son doctorat obtenu en 1996 à l'université de Besançon portait sur les formes de connaissance du présent dans les sciences sociales, sous la direction de Robert Damien. &lt;/p&gt; &lt;p&gt; Professeur à l'université Paris Nanterre, il est directeur adjoint du laboratoire Sophiapol. Ses enseignements couvrent l'histoire et l'épistémologie des sciences humaines, la philosophie contemporaine et les problèmes de théorie sociale et politique.&lt;/p&gt; &lt;p&gt;  Ses livres incluent Les Sciences humaines (1995), Habermas et la sociologie (1998), Freud et la théorie sociale (2012), Penser le néocapitalisme (2013). Il a dirigé des ouvrages comme L’Action en philosophie contemporaine (2005) et contribué à des revues sur Marx, l'aliénation et le capitalisme. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur  &lt;a href="https://www.youtube.com/watch?v=ZxECyRcOzFY&amp;t=11s"  title=". Haber : Exploitation du travail, appropriation de la nature, crise climatique. par Penser la Transformation"&gt; les interactions philosophie&lt;/a&gt;/sciences sociales, les marxismes contemporains, le néocapitalisme, l'aliénation subjective et objective, ainsi que les pathologies sociales et la théorie critique. Dans &lt;em&gt;L’Aliénation&lt;/em&gt; (2007), il redonne vie à cette notion héritée de Hegel et de Marx : on est aliéné quand on ne se reconnaît plus dans sa propre vie, ses activités ou ses institutions. Il montre que l’idée reste utile pour décrire les souffrances sociales d’aujourd’hui. Dans &lt;em&gt;Penser le néocapitalisme&lt;/em&gt;, il analyse un capitalisme qui s’étend à toutes les dimensions de l’existence, et ses travaux récents relient l’exploitation du travail et celle de la nature.</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>fbovR0UFucs</t>
+          <t>vnSkomfLExM</t>
         </is>
       </c>
       <c r="G57" s="36" t="inlineStr">
         <is>
-          <t>"E. Renault : l'exploitation comme domination" par Penser la Transformation</t>
+          <t>"Stephane Haber" par Université de Namur</t>
         </is>
       </c>
       <c r="H57" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/renault-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/haber-mini.webp</t>
         </is>
       </c>
       <c r="I57" s="36" t="n"/>
       <c r="J57" s="27" t="inlineStr">
         <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K57" s="27" t="inlineStr">
+        <is>
+          <t>Théorie Critique</t>
+        </is>
+      </c>
+      <c r="L57" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français spécialiste de la philosophie sociale &amp;amp; politique.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="150" customHeight="1" s="28">
+      <c r="A58" s="34" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B58" s="34" t="n"/>
+      <c r="C58" s="34" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="D58" s="35" t="inlineStr">
+        <is>
+          <t>Emmanuel RENAULT</t>
+        </is>
+      </c>
+      <c r="E58" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Renault"  title=" Wikipedia"&gt;Emmanuel RENAULT&lt;/a&gt; est un philosophe français, spécialisé en théorie critique, philosophie sociale et rapports entre reconnaissance, conflit et domination. Il est largement associé à une approche pragmatiste et pluraliste, cherchant à articuler Hegel, Marx, Honneth et le pragmatisme de Dewey dans une perspective interdisciplinaire. &lt;/p&gt; &lt;p&gt;  Il développe une approche qui croise les traditions marxistes et pragmatistes, et met l’accent sur les questions de travail, de justice, de  &lt;a href="https://www.nonfiction.fr/article-11867-abolir-lexploitation-entretien-avec-emmanuel-renault.htm" title="Abolir l'exploitation : entretien avec Emmanuel Renault. par nonfiction"&gt; souffrance sociale &lt;/a&gt; et de reconnaissance et il analyse comment les conflits sociaux, la reconnaissance et les formes de domination structurent l’injustice moderne.  Il s’inscrit dans une démarche qui remet en question les bases normatives de la justice politique en faveur d’une compréhension de l’injustice comme déni de reconnaissance et comme expérience de souffrance sociale. &lt;/p&gt; &lt;p&gt; Son travail est influent dans les débats sur la philosophie sociale en France et à l’étranger, et il participe à l’extension des cadres marxistes et pragmatistes dans la réflexion sur le travail,  &lt;a href="https://www.youtube.com/watch?v=6DriuHGugCA" title=" l'impensé de l'exploitation par Hors serie"&gt; l’exploitation &lt;/a&gt; et la justice sociale. Ses publications représentatives : "Le Mépris social" paru en  2000 : exploration des formes de mépris et des dynamiques sociales qui les sous-tendent. "Souffrances sociales" paru en 2008 : analyse des mécanismes de souffrance dans les sociétés contemporaines et leur lien avec la reconnaissance et la distribution des ressources. "Reconnaissance, conflit, domination"  en 2017 : thèse centrale sur la relation entre reconnaissance, conflit et domination, et leur rôle dans la configuration des inégalités. &lt;/p&gt;  &lt;audio controls title="Mépris social : comment sortir du dialogue de sourds?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-29.10.2015-ITEMA_20828700-2015C19327S0302-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F58" s="34" t="inlineStr">
+        <is>
+          <t>fbovR0UFucs</t>
+        </is>
+      </c>
+      <c r="G58" s="36" t="inlineStr">
+        <is>
+          <t>"E. Renault : l'exploitation comme domination" par Penser la Transformation</t>
+        </is>
+      </c>
+      <c r="H58" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/renault-mini.webp</t>
+        </is>
+      </c>
+      <c r="I58" s="36" t="n"/>
+      <c r="J58" s="27" t="inlineStr">
+        <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K57" s="27" t="inlineStr">
+      <c r="K58" s="27" t="inlineStr">
         <is>
           <t>Marxisme ; Théorie Critique</t>
         </is>
       </c>
-      <c r="L57" s="27" t="inlineStr">
+      <c r="L58" s="27" t="inlineStr">
         <is>
           <t>philosophe français promoteur de la philosophie sociale en France &amp;amp; de l'épistémologie hégélienne.</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
+      <c r="N58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="150" customHeight="1" s="28">
-      <c r="A58" s="44" t="n">
+    <row r="59" ht="150" customHeight="1" s="28">
+      <c r="A59" s="44" t="n">
         <v>1967</v>
       </c>
-      <c r="B58" s="44" t="n"/>
-      <c r="C58" s="44" t="inlineStr">
+      <c r="B59" s="44" t="n"/>
+      <c r="C59" s="44" t="inlineStr">
         <is>
           <t>1967</t>
         </is>
       </c>
-      <c r="D58" s="45" t="inlineStr">
+      <c r="D59" s="45" t="inlineStr">
         <is>
           <t>Franck FISCHBACH</t>
         </is>
       </c>
-      <c r="E58" s="46" t="inlineStr">
+      <c r="E59" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Franck_Fischbach"  style="color:#6A142A"  title=" Wikipedia"&gt;Franck FISCHBACH&lt;/a&gt; est un philosophe franco-suisse  spécialiste de la philosophie allemande et de la philosophie sociale. Ses recherches portent sur l’idéalisme allemand (particulièrement Fichte, Hegel et Schelling), la réception de Marx et la philosophie sociale contemporaine. Il s’intéresse notamment à la reconnaissance, à l’aliénation, au travail, au socialisme, et à la &lt;a href="https://www.philomag.com/articles/franck-fischbach-le-capitalisme-fabrique-des-etres-qui-netant-plus-vraiment-sociaux-ne" style="color:#88A1E9" title=" Franck Fischbach : “Le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains” par philosophie magazine"&gt;critique du capitalisme&lt;/a&gt;. Il contribue activement à redonner à la philosophie sociale une légitimité intellectuelle en France. &lt;/p&gt; &lt;p&gt; Il relie la tradition de la théorie critique (Adorno, Honneth) et celle du matérialisme marxien pour repenser les conditions de la vie sociale et du « vivre ensemble ». Il analyse le capitalisme contemporain comme un processus de désocialisation et de perte du monde commun, considérant que "le capitalisme fabrique des êtres qui, n’étant plus vraiment sociaux, ne seront plus vraiment humains".​ &lt;/p&gt; &lt;p&gt; Il  a reçu le Prix des Rencontres philosophiques de Monaco pour &lt;a href="https://www.youtube.com/watch?v=i16BcDagxns&amp;t=73s" style="color:#88A1E9" title=" Franck Fischbach → Faire ensemble. Reconstruction sociale et sortie du capitalisme par Librairie Ombre Blanche"&gt;"Faire ensemble"&lt;/a&gt;, ouvrage dans lequel il propose une refondation du lien social et une sortie éthique du capitalisme et il est aujourd’hui reconnu comme l’un des penseurs français majeurs de la philosophie sociale, prolongeant la critique marxienne à la lumière des défis écologiques et politiques contemporains.​ &lt;/p&gt; Professeur à l’université de Strasbourg, il a publié un &lt;em&gt;Manifeste pour une philosophie sociale&lt;/em&gt; (2009), qui veut redonner à la philosophie la tâche de diagnostiquer les « pathologies » de la société. Dans &lt;em&gt;La Privation de monde&lt;/em&gt; (2011), il décrit l’aliénation contemporaine comme une perte de prise sur le temps, l’espace et le monde commun.    &lt;audio controls title=" Qu'est-ce que la philosophie sociale? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11188-25.03.2010-ITEMA_20221135-2010C14987S0084-NET_B0358179-5AB7-42B6-8D32-144EADE35F65_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F58" s="44" t="inlineStr">
+      <c r="F59" s="44" t="inlineStr">
         <is>
           <t>QetmJoRDpY0</t>
         </is>
       </c>
-      <c r="G58" s="47" t="inlineStr">
+      <c r="G59" s="47" t="inlineStr">
         <is>
           <t>Franck Fischbach, L’aliénation : un concept encore utile aujourd’hui ? par Departement Philosophie</t>
         </is>
       </c>
-      <c r="H58" s="47" t="inlineStr">
+      <c r="H59" s="47" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fischbach-mini.webp</t>
         </is>
       </c>
-      <c r="I58" s="47" t="n"/>
-      <c r="J58" s="48" t="inlineStr">
+      <c r="I59" s="47" t="n"/>
+      <c r="J59" s="48" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K58" s="48" t="inlineStr">
+      <c r="K59" s="48" t="inlineStr">
         <is>
           <t>Marxisme ; Théorie Critique</t>
         </is>
       </c>
-      <c r="L58" s="48" t="inlineStr">
+      <c r="L59" s="48" t="inlineStr">
         <is>
           <t>philosophe franco-suisse spécialiste de la philosophie sociale.</t>
         </is>
       </c>
-      <c r="M58" s="27" t="n"/>
-      <c r="N58" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
+      <c r="M59" s="27" t="n"/>
+      <c r="N59" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
         <is>
           <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="167.25" customHeight="1" s="28">
-      <c r="A59" s="34" t="n">
+    <row r="60" ht="167.25" customHeight="1" s="28">
+      <c r="A60" s="34" t="n">
         <v>1968</v>
       </c>
-      <c r="B59" s="34" t="n"/>
-      <c r="C59" s="34" t="n">
+      <c r="B60" s="34" t="n"/>
+      <c r="C60" s="34" t="n">
         <v>1968</v>
       </c>
-      <c r="D59" s="27" t="inlineStr">
+      <c r="D60" s="27" t="inlineStr">
         <is>
           <t>Camille FROIDEVAUX-METTERIE</t>
         </is>
       </c>
-      <c r="E59" s="36" t="inlineStr">
+      <c r="E60" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Camille_Froidevaux-Metterie"  title=" Wikipedia"&gt;Camille FROIDEVAUX-METTERIE&lt;/a&gt;  est une philosophe et professeure de science politique française, spécialisée dans les questions féministes et la condition féminine contemporaine. Agrégée de science politique et titulaire d’un doctorat de philosophie politique, elle enseigne notamment à l’Université de Reims Champagne-Ardenne et a contribué à renouveler la pensée féministe en France. &lt;/p&gt; &lt;p&gt; Sa philosophie repose sur une phénoménologie du corps des femmes, qu’elle considère comme le &lt;a href="https://www.youtube.com/watch?v=raJW9Ovmpvk" title=" Camille Fridevaux-Metterie un corps à soi par librairie molla"&gt; lieu central de l’expérience &lt;/a&gt; féminine et de l’oppression patriarcale. Elle analyse comment le corps féminin a historiquement été objectivé, contrôlé et réduit à un objet de désir ou de norme sociale, ce qui produit une aliénation profonde pour les femmes. &lt;/p&gt; &lt;p&gt; Elle développe une approche de féminisme incarné, qui cherche à &lt;a href="https://www.youtube.com/watch?v=3omfOctPy48" title=" Camille Fridevaux-Metterie réinventer l’amour par Barbara Carlotti"&gt; dépasser les clivages &lt;/a&gt; traditionnels entre universalisme et différentialisme. Selon elle, le corps n’est pas seulement un lieu d’aliénation, mais aussi une source potentielle d’émancipation : la réappropriation de son propre corps permet aux femmes de se libérer et de transformer les normes sociales. &lt;/p&gt; &lt;p&gt; Elle insiste sur l’importance de l’expérience vécue (le « vécu corporel »), notamment autour de la grossesse, de la vulnérabilité et de la sexualité, qu’elle traite comme des dimensions politiques et non plus seulement intimes. Dans Un si gros ventre (2023), par exemple, elle explore la grossesse comme expérience à la fois intime et socialement structurante. &lt;/p&gt; &lt;p&gt; Elle incarne un féminisme contemporain qui articule philosophie, sciences politiques et récit personnel. Inspirée par Simone de Beauvoir et Iris Marion Young, elle défend un féminisme pluriel, créatif et politiquement engageant, où la libération des femmes passe par la reconnaissance et la réappropriation de leur corporéité.  &lt;/p&gt; &lt;audio controls title="Histoire politique du féménisme avec Camille Froidevaux-Metterie  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-31.10.2025-ITEMA_24296659-2025F45096S0304-NET_MFI_7891A381-183D-44C4-B741-51A4BC4DD2C4-22-2af896bd1e7f8bcd4790879da0a18b3c.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F59" s="34" t="inlineStr">
+      <c r="F60" s="34" t="inlineStr">
         <is>
           <t>mprvC9XQUJk</t>
         </is>
       </c>
-      <c r="G59" s="36" t="inlineStr">
+      <c r="G60" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">Camille Froidevaux-Metterie philosophie du genre par Collège de France</t>
         </is>
       </c>
-      <c r="H59" s="37" t="inlineStr">
+      <c r="H60" s="37" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/cfmetterie-mini.webp</t>
         </is>
       </c>
-      <c r="I59" s="36" t="n"/>
-      <c r="J59" s="27" t="inlineStr">
+      <c r="I60" s="36" t="n"/>
+      <c r="J60" s="27" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="K59" s="27" t="inlineStr">
+      <c r="K60" s="27" t="inlineStr">
         <is>
           <t>Phénoménologie ; Féminisme</t>
         </is>
       </c>
-      <c r="L59" s="49" t="inlineStr">
+      <c r="L60" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">philosophe féministe française connue pour ses travaux sur le corps des femmes et les transformations du féminisme.
 </t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
+      <c r="N60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t xml:space="preserve">genre</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="123.75" customHeight="1" s="28">
-      <c r="A60" s="34" t="n">
+    <row r="61" ht="123.75" customHeight="1" s="28">
+      <c r="A61" s="34" t="n">
         <v>1969</v>
       </c>
-      <c r="B60" s="34" t="n"/>
-      <c r="C60" s="34" t="inlineStr">
+      <c r="B61" s="34" t="n"/>
+      <c r="C61" s="34" t="inlineStr">
         <is>
           <t>1969</t>
         </is>
       </c>
-      <c r="D60" s="35" t="inlineStr">
+      <c r="D61" s="35" t="inlineStr">
         <is>
           <t>Laurence DEVILLAIRS</t>
         </is>
       </c>
-      <c r="E60" s="39" t="inlineStr">
+      <c r="E61" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://www.philomag.com/philosophes/laurence-devillairs"  title=" Wikipedia"&gt;Laurence DEVILLAIRS&lt;/a&gt;  est une philosophe française, spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle. Elle enseigne à l’université Paris 1 Panthéon-Sorbonne et s’adresse aussi à un large public à travers des essais et des interventions. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse beaucoup à la morale concrète : le bien, le mal, &lt;a href="https://www.youtube.com/watch?v=a5YnPWx7Xw8" title="laurence Devillairs : Eloge de la gentillesse par Brut"&gt; la gentillesse, &lt;/a&gt; le courage, la justice. Elle refuse une vision trop abstraite de l’éthique et cherche plutôt à montrer comment on devient une &lt;a href="https://www.youtube.com/watch?v=T0U2ro8b9Io" title="laurence Devillairs : a quoi reconnaître quelqu’un de bien par TV Monde"&gt; personne meilleure &lt;/a&gt; dans la vie quotidienne. &lt;/p&gt; &lt;p&gt; Elle réfléchit aussi au politique, mais d’une manière très humaine : comment vivre ensemble, comment &lt;a href="https://www.youtube.com/watch?v=p9AaVfIoIPg" title="laurence Devillairs : le pouvoir par Fabrice Midal"&gt; penser le pouvoir, &lt;/a&gt; comment garder une place pour l’utopie et l’espérance sans perdre le sens du réel. Chez elle, le politique n’est pas seulement affaire de règles, mais aussi de désir de transformation. &lt;/p&gt; &lt;p&gt; Sa philosophie défend une forme de fermeté douce : être bon ne veut pas dire être faible, et la gentillesse peut être un choix éthique fort. Son travail cherche à rendre la philosophie utile pour mieux vivre, mieux juger et mieux agir. Lectrice de Descartes, elle retient de lui le goût de la clarté et de la générosité, cette juste estime de soi qui consiste à bien user de sa liberté. Dans &lt;em&gt;Être quelqu’un de bien&lt;/em&gt; (2019), elle montre que la bonté n’est pas une naïveté, mais une forme de courage, et qu’elle se joue d’abord dans les gestes ordinaires, l’attention, la parole donnée, le refus de l’humiliation. &lt;/p&gt;  &lt;audio controls title="Laurence Devillairs : le désir de vengeance est une libération  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.04.2026-ITEMA_24449483-2026F22640S0095-NET_MFI_BFCBC71B-F523-4D4D-9C0D-E455E058A13C-22-23fd728f6afa552353ce5d4ded4690c9.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F60" s="34" t="inlineStr">
+      <c r="F61" s="34" t="inlineStr">
         <is>
           <t>ebQxk90j0NQ</t>
         </is>
       </c>
-      <c r="G60" s="36" t="inlineStr">
+      <c r="G61" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">"Laurence Devillairs - La splendeur du monde : aller à la rencontre de la beauté" par Librairie Mollat</t>
         </is>
       </c>
-      <c r="H60" s="36" t="inlineStr">
+      <c r="H61" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/devillairs-mini.webp</t>
-        </is>
-      </c>
-      <c r="I60" s="36" t="n"/>
-      <c r="J60" s="27" t="inlineStr">
-        <is>
-          <t>ethique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="K60" s="27" t="inlineStr">
-        <is>
-          <t>Spiritualisme</t>
-        </is>
-      </c>
-      <c r="L60" s="27" t="inlineStr">
-        <is>
-          <t>philosophe française spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sens</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="126.75" customHeight="1" s="28">
-      <c r="A61" s="34" t="n">
-        <v>1969</v>
-      </c>
-      <c r="B61" s="34" t="n"/>
-      <c r="C61" s="34" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="D61" s="35" t="inlineStr">
-        <is>
-          <t>Vincent DELECROIX</t>
-        </is>
-      </c>
-      <c r="E61" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Delecroix"  title=" Wikipedia"&gt;Vincent DELECROIX&lt;/a&gt; (né en 1969) est un philosophe et romancier français, spécialiste de Kierkegaard et de la philosophie de la religion. Agrégé de philosophie, il est directeur d’études à l’École pratique des hautes études (EPHE), où il enseigne la philosophie de la religion, et il a dirigé l’édition et la traduction de plusieurs œuvres de Kierkegaard.&lt;/p&gt; &lt;p&gt;Son travail interroge la manière dont la foi peut encore exister dans un monde moderne où les certitudes absolues &lt;a href="https://www.youtube.com/watch?v=2ZHOpP5GMwI" title="Vincent DELECROIX,la nécessité d’apprendre par TV5 monde"&gt;se sont affaiblies&lt;/a&gt;. À la suite de Kierkegaard, il ne traite pas la religion comme un héritage figé ou un ensemble de dogmes, mais comme une expérience intérieure, fragile et exigeante, où l’individu est engagé tout entier. La vérité, dans ce domaine, n’est pas un savoir objectif que l’on possède, mais une manière d’exister. Il réfléchit aussi aux rapports entre religion et politique, et à la façon dont les espérances religieuses se transforment dans les idéologies modernes. Un autre axe important de sa pensée est la révolte. Dans &lt;em&gt;Tombeau d’Achille&lt;/em&gt;, il médite sur la colère du héros d’Homère ; dans &lt;em&gt;Non ! De l’esprit de révolte&lt;/em&gt;, il réfléchit au refus et à la parole &lt;a href="https://www.youtube.com/watch?v=OiUgp6wLpCA" title="Vincent DELECROIX il faut sortir du oui non par France Culture"&gt;qui dit non&lt;/a&gt;, non comme de simples réactions d’humeur, mais comme des actes qui révèlent une exigence morale : refuser l’inacceptable, c’est affirmer qu’il existe quelque chose qui vaut.&lt;/p&gt; &lt;p&gt;Romancier, il a publié plusieurs livres où la fiction devient une autre manière de philosopher. Sa pensée cherche comment l’être humain peut garder une voix et une exigence spirituelle dans un monde désorienté.&lt;/p&gt;  &lt;audio controls title="Vincent DELECROIX  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F61" s="34" t="inlineStr">
-        <is>
-          <t>sVWokXyL1YE</t>
-        </is>
-      </c>
-      <c r="G61" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Vincent Delecroix - Naufrage" par Librairie Mollat</t>
-        </is>
-      </c>
-      <c r="H61" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/vdelecroix-mini.webp</t>
         </is>
       </c>
       <c r="I61" s="36" t="n"/>
@@ -4468,12 +4462,17 @@
       </c>
       <c r="K61" s="27" t="inlineStr">
         <is>
-          <t>Existentialisme</t>
-        </is>
-      </c>
-      <c r="L61" s="42" t="inlineStr">
-        <is>
-          <t>philosophe et écrivain français, spécialiste de Kierkegaard et de philosophie de la religion.</t>
+          <t>Spiritualisme</t>
+        </is>
+      </c>
+      <c r="L61" s="27" t="inlineStr">
+        <is>
+          <t>philosophe française spécialiste de Descartes, de Pascal et plus largement du XVIIe siècle.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4487,22 +4486,84 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="147.75" customHeight="1" s="28">
+    <row r="62" ht="126.75" customHeight="1" s="28">
       <c r="A62" s="34" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B62" s="34" t="n"/>
       <c r="C62" s="34" t="inlineStr">
         <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="D62" s="35" t="inlineStr">
+        <is>
+          <t>Vincent DELECROIX</t>
+        </is>
+      </c>
+      <c r="E62" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Delecroix"  title=" Wikipedia"&gt;Vincent DELECROIX&lt;/a&gt; (né en 1969) est un philosophe et romancier français, spécialiste de Kierkegaard et de la philosophie de la religion. Agrégé de philosophie, il est directeur d’études à l’École pratique des hautes études (EPHE), où il enseigne la philosophie de la religion, et il a dirigé l’édition et la traduction de plusieurs œuvres de Kierkegaard.&lt;/p&gt; &lt;p&gt;Son travail interroge la manière dont la foi peut encore exister dans un monde moderne où les certitudes absolues &lt;a href="https://www.youtube.com/watch?v=2ZHOpP5GMwI" title="Vincent DELECROIX,la nécessité d’apprendre par TV5 monde"&gt;se sont affaiblies&lt;/a&gt;. À la suite de Kierkegaard, il ne traite pas la religion comme un héritage figé ou un ensemble de dogmes, mais comme une expérience intérieure, fragile et exigeante, où l’individu est engagé tout entier. La vérité, dans ce domaine, n’est pas un savoir objectif que l’on possède, mais une manière d’exister. Il réfléchit aussi aux rapports entre religion et politique, et à la façon dont les espérances religieuses se transforment dans les idéologies modernes. Un autre axe important de sa pensée est la révolte. Dans &lt;em&gt;Tombeau d’Achille&lt;/em&gt;, il médite sur la colère du héros d’Homère ; dans &lt;em&gt;Non ! De l’esprit de révolte&lt;/em&gt;, il réfléchit au refus et à la parole &lt;a href="https://www.youtube.com/watch?v=OiUgp6wLpCA" title="Vincent DELECROIX il faut sortir du oui non par France Culture"&gt;qui dit non&lt;/a&gt;, non comme de simples réactions d’humeur, mais comme des actes qui révèlent une exigence morale : refuser l’inacceptable, c’est affirmer qu’il existe quelque chose qui vaut.&lt;/p&gt; &lt;p&gt;Romancier, il a publié plusieurs livres où la fiction devient une autre manière de philosopher. Sa pensée cherche comment l’être humain peut garder une voix et une exigence spirituelle dans un monde désorienté.&lt;/p&gt;  &lt;audio controls title="Vincent DELECROIX  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F62" s="34" t="inlineStr">
+        <is>
+          <t>sVWokXyL1YE</t>
+        </is>
+      </c>
+      <c r="G62" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Vincent Delecroix - Naufrage" par Librairie Mollat</t>
+        </is>
+      </c>
+      <c r="H62" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/vdelecroix-mini.webp</t>
+        </is>
+      </c>
+      <c r="I62" s="36" t="n"/>
+      <c r="J62" s="27" t="inlineStr">
+        <is>
+          <t>ethique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K62" s="27" t="inlineStr">
+        <is>
+          <t>Existentialisme</t>
+        </is>
+      </c>
+      <c r="L62" s="42" t="inlineStr">
+        <is>
+          <t>philosophe et écrivain français, spécialiste de Kierkegaard et de philosophie de la religion.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sens</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="147.75" customHeight="1" s="28">
+      <c r="A63" s="34" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B63" s="34" t="n"/>
+      <c r="C63" s="34" t="inlineStr">
+        <is>
           <t>1970</t>
         </is>
       </c>
-      <c r="D62" s="35" t="inlineStr">
+      <c r="D63" s="35" t="inlineStr">
         <is>
           <t>Jean Claude MONOD</t>
         </is>
       </c>
-      <c r="E62" s="36" t="inlineStr">
+      <c r="E63" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Claude_Monod"  title=" Wikipedia"&gt;Jean Claude MONOD&lt;/a&gt; est un philosophe français  contemporain, spécialiste de philosophie politique et de philosophie allemande des XIXe et XXe siècles, en particulier de la question de la sécularisation et des rapports entre religion, modernité et démocratie. Ancien élève de l’École normale supérieure, chercheur au CNRS aux Archives Husserl, il a aussi publié &lt;em&gt;Qu’est-ce qu’un chef en démocratie ?&lt;/em&gt; (2012), sur le charisme politique. &lt;/p&gt; &lt;p&gt;  Un axe central de sa réflexion est de comprendre la modernité sans la réduire à une simple transposition de catégories religieuses, et de penser  &lt;a href="https://www.youtube.com/watch?v=E111pSvCT8g"  title="
 Jean-Claude Monod - L'art de ne pas être trop gouverné par librairie mollat"&gt;le théologico-politique&lt;/a&gt;  aujourd’hui. Il s’intéresse aussi aux formes contemporaines du pouvoir (crises de l’État libéral, charisme politique, crises de gouvernementalité, néolibéralisme autoritaire) et aux tensions entre démocratie, vérité et fake news. &lt;/p&gt; &lt;p&gt; Dans son ouvrage : &lt;a href="https://www.gregoiredetours.fr/thematiques/religions/jean-claude-monod-secularisation-et-laicite/"  title="
@@ -4510,259 +4571,259 @@
   &lt;audio controls title="L'intellectuel peut-il encore exister au XXIe siècle ?  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/25951-29.11.2025-ITEMA_24326903-2025C54596S0333-NET_MFC_C2F18604-F792-44E5-803E-E62225C653B4-25-bf7dbc88816a940ebe2dc58d15ae6341.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F62" s="34" t="inlineStr">
+      <c r="F63" s="34" t="inlineStr">
         <is>
           <t>v6zl6a4K1Sw</t>
         </is>
       </c>
-      <c r="G62" s="36" t="inlineStr">
+      <c r="G63" s="36" t="inlineStr">
         <is>
           <t>"Gouverner sans dominer, ou le difficile héritage du libéralisme" par France Culture</t>
         </is>
       </c>
-      <c r="H62" s="36" t="inlineStr">
+      <c r="H63" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/monod-mini.webp</t>
         </is>
       </c>
-      <c r="I62" s="36" t="n"/>
-      <c r="J62" s="27" t="inlineStr">
+      <c r="I63" s="36" t="n"/>
+      <c r="J63" s="27" t="inlineStr">
         <is>
           <t>politique ; epistemologie</t>
         </is>
       </c>
-      <c r="K62" s="27" t="inlineStr">
+      <c r="K63" s="27" t="inlineStr">
         <is>
           <t>Herméneutique ; Phénoménologie</t>
         </is>
       </c>
-      <c r="L62" s="27" t="inlineStr">
+      <c r="L63" s="27" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de philosophie allemande contemporaine et de philosophie politique.</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
+      <c r="N63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="116.25" customHeight="1" s="28">
-      <c r="A63" s="34" t="n">
+    <row r="64" ht="116.25" customHeight="1" s="28">
+      <c r="A64" s="34" t="n">
         <v>1970</v>
       </c>
-      <c r="B63" s="34" t="n"/>
-      <c r="C63" s="34" t="inlineStr">
+      <c r="B64" s="34" t="n"/>
+      <c r="C64" s="34" t="inlineStr">
         <is>
           <t>1970</t>
         </is>
       </c>
-      <c r="D63" s="35" t="inlineStr">
+      <c r="D64" s="35" t="inlineStr">
         <is>
           <t>Edouard MEHL</t>
         </is>
       </c>
-      <c r="E63" s="38" t="inlineStr">
+      <c r="E64" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Mehl"  title=" Wikipedia"&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href="https://www.youtube.com/watch?v=NT0n7tKNb3w" title="qu’est ce que la verité par Le forum Veritas"&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; Il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. Il a notamment étudié le jeune Descartes lors de son séjour en Allemagne, en 1619-1620, au moment de ses célèbres songes et de la naissance de sa méthode, ainsi que ses rapports avec Kepler et les savants de son temps. Il montre que la métaphysique cartésienne est inséparable d’un projet de physique et de cosmologie, qui vise à rendre le monde visible et intelligible tout entier. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F63" s="34" t="inlineStr">
+      <c r="F64" s="34" t="inlineStr">
         <is>
           <t>aBav8Q81MeQ</t>
         </is>
       </c>
-      <c r="G63" s="36" t="inlineStr">
+      <c r="G64" s="36" t="inlineStr">
         <is>
           <t>"Pourquoi méditer ? — Edouard Mehl" par Andrea Cirla</t>
         </is>
       </c>
-      <c r="H63" s="36" t="inlineStr">
+      <c r="H64" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/emehl-mini.webp</t>
         </is>
       </c>
-      <c r="I63" s="36" t="n"/>
-      <c r="J63" s="27" t="inlineStr">
+      <c r="I64" s="36" t="n"/>
+      <c r="J64" s="27" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="K63" s="27" t="inlineStr">
+      <c r="K64" s="27" t="inlineStr">
         <is>
           <t>Idéalisme</t>
         </is>
       </c>
-      <c r="L63" s="27" t="inlineStr">
+      <c r="L64" s="27" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de la philosophie moderne et de l’histoire des sciences.</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
+      <c r="N64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t xml:space="preserve">reel</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="142.5" customHeight="1" s="28">
-      <c r="A64" s="34" t="n">
+    <row r="65" ht="142.5" customHeight="1" s="28">
+      <c r="A65" s="34" t="n">
         <v>1971</v>
       </c>
-      <c r="B64" s="34" t="n"/>
-      <c r="C64" s="34" t="inlineStr">
+      <c r="B65" s="34" t="n"/>
+      <c r="C65" s="34" t="inlineStr">
         <is>
           <t>1971</t>
         </is>
       </c>
-      <c r="D64" s="35" t="inlineStr">
+      <c r="D65" s="35" t="inlineStr">
         <is>
           <t>Barbara STIEGLER</t>
         </is>
       </c>
-      <c r="E64" s="37" t="inlineStr">
+      <c r="E65" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barbara_Stiegler" title=" Wikipedia"&gt;Barbara STIEGLER&lt;/a&gt; (née en 1971) est une philosophe française, spécialiste de Nietzsche et de philosophie politique, connue pour sa critique du néolibéralisme. Fille du philosophe Bernard Stiegler, agrégée de philosophie, elle est professeure à l’université Bordeaux-Montaigne, où elle a dirigé le master « Soin, éthique et santé ».&lt;/p&gt; &lt;p&gt;Ses premiers travaux portent sur Nietzsche et la biologie de son temps. Dans &lt;em&gt;Nietzsche et la biologie&lt;/em&gt; (2001) et &lt;em&gt;Nietzsche et la critique de la chair&lt;/em&gt; (2005), elle montre que la pensée de Nietzsche dialogue avec les sciences du vivant, et que le corps et la vie y sont des notions centrales. Elle se tourne ensuite vers la philosophie politique. Dans &lt;a href="https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/" title="Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit"&gt;&lt;em&gt;« Il faut s’adapter »&lt;/em&gt;&lt;/a&gt; (2019), elle remonte aux origines du &lt;a href="https://www.youtube.com/watch?v=oQQ4xqRvYTk" style="color:#88A1E9" title="LA LENTE AGONIE DU NÉOLIBÉRALISME  par 
 TheSwissBox Conversation"&gt;néolibéralisme&lt;/a&gt; : au début du XXe siècle, le journaliste américain Walter Lippmann, inspiré par une lecture de la théorie de l’évolution, soutenait que les peuples, en retard sur un monde qui change trop vite, devaient être adaptés par des experts au nouvel environnement mondialisé. Contre lui, le philosophe John Dewey défendait une démocratie fondée sur l’intelligence collective et la participation des citoyens. Barbara Stiegler montre que ce débat oublié éclaire nos sociétés, où l’injonction à s’adapter s’impose à l’école, au travail et dans la santé. Elle a ensuite appliqué ces analyses aux mouvements sociaux, dans &lt;em&gt;Du cap aux grèves&lt;/em&gt; (2020), puis à la crise de la covid, dans &lt;em&gt;De la démocratie en pandémie&lt;/em&gt; (2021).&lt;/p&gt; &lt;p&gt;Engagée dans le débat public, elle plaide pour une démocratie plus participative et pour une autre conception de la santé publique.&lt;/p&gt;  &lt;audio controls title="La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F64" s="34" t="inlineStr">
+      <c r="F65" s="34" t="inlineStr">
         <is>
           <t>bm6KyWYpaQU</t>
         </is>
       </c>
-      <c r="G64" s="36" t="inlineStr">
+      <c r="G65" s="36" t="inlineStr">
         <is>
           <t>"Barbara Stiegler - Les meilleurs moments de QG" par QG TV</t>
         </is>
       </c>
-      <c r="H64" s="37" t="inlineStr">
+      <c r="H65" s="37" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bastiegler-mini.webp</t>
         </is>
       </c>
-      <c r="I64" s="36" t="n"/>
-      <c r="J64" s="27" t="inlineStr">
+      <c r="I65" s="36" t="n"/>
+      <c r="J65" s="27" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K64" s="27" t="inlineStr">
+      <c r="K65" s="27" t="inlineStr">
         <is>
           <t>Théorie Critique</t>
         </is>
       </c>
-      <c r="L64" s="27" t="inlineStr">
+      <c r="L65" s="27" t="inlineStr">
         <is>
           <t>philosophe française spécialiste de Nietzsche, de philosophie politique &amp;amp; critique du néolibéralisme.</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="131.25" customHeight="1" s="28">
-      <c r="A65" s="34" t="n">
+    <row r="66" ht="131.25" customHeight="1" s="28">
+      <c r="A66" s="34" t="n">
         <v>1972</v>
       </c>
-      <c r="B65" s="34" t="n"/>
-      <c r="C65" s="34" t="inlineStr">
+      <c r="B66" s="34" t="n"/>
+      <c r="C66" s="34" t="inlineStr">
         <is>
           <t>1972</t>
         </is>
       </c>
-      <c r="D65" s="35" t="inlineStr">
+      <c r="D66" s="35" t="inlineStr">
         <is>
           <t>Yves CUSSET</t>
         </is>
       </c>
-      <c r="E65" s="36" t="inlineStr">
+      <c r="E66" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yves_Cusset"  style="color:#6A142A"  title=" Wikipedia"&gt;Yves CUSSET&lt;/a&gt;  est un philosophe français agrégé et docteur en philosophie, qui allie une réflexion sérieuse sur la philosophie politique à un engagement théâtral et  &lt;a href="https://www.youtube.com/watch?v=uJLmpAgqiWY" style="color:#88A1E9" title="Yves Cusset, Petit manuel d'engagement politique à l'usage des mammifères doués de raison.... par Yves Cusset"&gt;humoristique unique. &lt;/a&gt;  Spécialiste de Habermas et Foucault, il explore les tensions entre raison discussionnelle et pouvoir, ainsi que les apories de l’accueil : comment concilier exigence éthique d’hospitalité et contraintes politiques. &lt;/p&gt; &lt;p&gt; Ses essais interrogent le "bien-mourir", critiquant les normes contemporaines de la mort apaisée, et défendent une politique de l’accueil face à la misère du monde.  Il théorise l’humour comme "bonne humeur pour mourir", un outil philosophique qui désarme les idées fixes et favorise la pensée sans intimidation. Il crée des solos comme Rien ne sert d’exister, Tractatus philo-comicus ou La Philosophie enseignée à ma chouette, joués au festival d’Avignon et ailleurs, mêlant rire, absurdité et métaphysique. &lt;/p&gt; &lt;p&gt; Militant discret, il use de l’humour politique pour dénoncer clichés  &lt;a href="https://www.youtube.com/watch?v=QwVPt_PQE-Q" style="color:#88A1E9" title="Yves Cusset : 100 façons de ne pas accueillir un migrant par TV5Monde"&gt;anti-migrants &lt;/a&gt; ou dérives du "développement personnel".  Son genre hybride, l’"humour philosophique", vise à émerveiller par le rire, suscitant la réflexion sans complexer, comme il l’explique dans Le Monde. Ses premiers travaux portent sur Habermas, dont il présente l’« éthique de la discussion » : une norme n’est valable que si tous ceux qu’elle concerne pourraient l’accepter au terme d’une discussion libre. Il en tire une exigence démocratique, mais aussi une attention à ceux qui n’ont pas la parole. Pour lui, le rire n’est pas une fuite hors de la pensée : il oblige à prendre de la distance avec soi-même et avec les certitudes. &lt;/p&gt; 
   &lt;audio controls title="L'amour avec Yves Cusset par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-07.06.2024-ITEMA_23765968-2024F45096S0159-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F65" s="34" t="inlineStr">
+      <c r="F66" s="34" t="inlineStr">
         <is>
           <t>3vE-JUIYaPs</t>
         </is>
       </c>
-      <c r="G65" s="36" t="inlineStr">
+      <c r="G66" s="36" t="inlineStr">
         <is>
           <t>"Réussir sa vie du premier coup", Yves Cusset, extrait par Yves Cusset</t>
         </is>
       </c>
-      <c r="H65" s="36" t="inlineStr">
+      <c r="H66" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/cusset-mini.webp</t>
         </is>
       </c>
-      <c r="I65" s="36" t="n"/>
-      <c r="J65" s="27" t="inlineStr">
+      <c r="I66" s="36" t="n"/>
+      <c r="J66" s="27" t="inlineStr">
         <is>
           <t>ethique</t>
         </is>
       </c>
-      <c r="K65" s="27" t="inlineStr">
+      <c r="K66" s="27" t="inlineStr">
         <is>
           <t>Existentialisme</t>
         </is>
       </c>
-      <c r="L65" s="27" t="inlineStr">
+      <c r="L66" s="27" t="inlineStr">
         <is>
           <t>philosophe français connu pour ses relations avec l'institution de l'être-en-commun.</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
+      <c r="N66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
         <is>
           <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="174.75" customHeight="1" s="28">
-      <c r="A66" s="34" t="n">
+    <row r="67" ht="174.75" customHeight="1" s="28">
+      <c r="A67" s="34" t="n">
         <v>1973</v>
       </c>
-      <c r="B66" s="34" t="n"/>
-      <c r="C66" s="34" t="inlineStr">
+      <c r="B67" s="34" t="n"/>
+      <c r="C67" s="34" t="inlineStr">
         <is>
           <t>1973</t>
         </is>
       </c>
-      <c r="D66" s="35" t="inlineStr">
+      <c r="D67" s="35" t="inlineStr">
         <is>
           <t>Eric SADIN</t>
         </is>
       </c>
-      <c r="E66" s="37" t="inlineStr">
+      <c r="E67" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89ric_Sadin"  title=" Wikipedia"&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href="https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur" style="color:#88A1E9"   title=" Éric SADIN contre ChatGPT par Senseur"&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;
 Sadin s'est fait connaître grâce à son livre "La société de l'anticipation " publié en 2011, dans lequel il examine l'émergence de la société de la surveillance et des technologies de prévision qui cherchent à anticiper les comportements et les désirs des individus. Il y aborde notamment les thèmes de la surveillance généralisée, de la collecte de données personnelles et des risques de manipulation. &lt;/p&gt; &lt;p&gt;
@@ -4770,97 +4831,35 @@
 Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre "La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique" publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href="https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008"  title="Dataïsme par lebigdata"&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title="Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F66" s="34" t="inlineStr">
+      <c r="F67" s="34" t="inlineStr">
         <is>
           <t>DfLKeExecZc</t>
         </is>
       </c>
-      <c r="G66" s="36" t="inlineStr">
+      <c r="G67" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">"Pourquoi ChatGPT accélère la marchandisation de nos existences" par Le Figaro</t>
         </is>
       </c>
-      <c r="H66" s="36" t="inlineStr">
+      <c r="H67" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/sadin-mini.webp</t>
-        </is>
-      </c>
-      <c r="I66" s="36" t="n"/>
-      <c r="J66" s="27" t="inlineStr">
-        <is>
-          <t>politique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K66" s="27" t="inlineStr">
-        <is>
-          <t>Post Modernisme</t>
-        </is>
-      </c>
-      <c r="L66" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français critique des enjeux liés à la technologie et du Dataïsme.</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">esprit-ia</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="154.5" customHeight="1" s="28">
-      <c r="A67" s="34" t="n">
-        <v>1973</v>
-      </c>
-      <c r="B67" s="34" t="n"/>
-      <c r="C67" s="34" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="D67" s="35" t="inlineStr">
-        <is>
-          <t>Aurélien BARRAU</t>
-        </is>
-      </c>
-      <c r="E67" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau" title=" Wikipedia"&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href="https://www.youtube.com/watch?v=PNMZHr3L_Ws" title=" Vivons nous dans un multivers par Aurelien Barrau"&gt; concept de multivers&lt;/a&gt;, et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage "Chaos multiples" et "De la vérité dans les sciences"  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé "Météorites". &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de "sauver le climat" plutôt "qu’agir pour la vie". &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  "habiter la science en poète" en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href="https://www.youtube.com/watch?v=94IxSYo5wtM" title="Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter"&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href="https://www.youtube.com/watch?v=g3Z_LsXD7DU" title=" L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac"&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un "faire monde" éthique et conscient. &lt;/p&gt;   &lt;audio controls title=" Aurelien BARRAU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F67" s="34" t="inlineStr">
-        <is>
-          <t>NXHzt-dnNZY</t>
-        </is>
-      </c>
-      <c r="G67" s="36" t="inlineStr">
-        <is>
-          <t>"SORTIR DE NOS ADDICTIONS" par LIMIT</t>
-        </is>
-      </c>
-      <c r="H67" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/barrau-mini.webp</t>
         </is>
       </c>
       <c r="I67" s="36" t="n"/>
       <c r="J67" s="27" t="inlineStr">
         <is>
-          <t>metaphysique ; epistemologie</t>
+          <t>politique ; epistemologie</t>
         </is>
       </c>
       <c r="K67" s="27" t="inlineStr">
         <is>
-          <t>Réalisme</t>
+          <t>Post Modernisme</t>
         </is>
       </c>
       <c r="L67" s="27" t="inlineStr">
         <is>
-          <t>philosophe et astrophysicien français nous invitant à repenser notre rapport au vivant.</t>
+          <t>philosophe français critique des enjeux liés à la technologie et du Dataïsme.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4870,11 +4869,11 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie ; reel</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="168.75" customHeight="1" s="28">
+          <t xml:space="preserve">esprit-ia</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="154.5" customHeight="1" s="28">
       <c r="A68" s="34" t="n">
         <v>1973</v>
       </c>
@@ -4886,169 +4885,169 @@
       </c>
       <c r="D68" s="35" t="inlineStr">
         <is>
+          <t>Aurélien BARRAU</t>
+        </is>
+      </c>
+      <c r="E68" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau" title=" Wikipedia"&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href="https://www.youtube.com/watch?v=PNMZHr3L_Ws" title=" Vivons nous dans un multivers par Aurelien Barrau"&gt; concept de multivers&lt;/a&gt;, et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage "Chaos multiples" et "De la vérité dans les sciences"  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé "Météorites". &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de "sauver le climat" plutôt "qu’agir pour la vie". &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  "habiter la science en poète" en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href="https://www.youtube.com/watch?v=94IxSYo5wtM" title="Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter"&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href="https://www.youtube.com/watch?v=g3Z_LsXD7DU" title=" L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac"&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un "faire monde" éthique et conscient. &lt;/p&gt;   &lt;audio controls title=" Aurelien BARRAU par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F68" s="34" t="inlineStr">
+        <is>
+          <t>NXHzt-dnNZY</t>
+        </is>
+      </c>
+      <c r="G68" s="36" t="inlineStr">
+        <is>
+          <t>"SORTIR DE NOS ADDICTIONS" par LIMIT</t>
+        </is>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/barrau-mini.webp</t>
+        </is>
+      </c>
+      <c r="I68" s="36" t="n"/>
+      <c r="J68" s="27" t="inlineStr">
+        <is>
+          <t>metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K68" s="27" t="inlineStr">
+        <is>
+          <t>Réalisme</t>
+        </is>
+      </c>
+      <c r="L68" s="27" t="inlineStr">
+        <is>
+          <t>philosophe et astrophysicien français nous invitant à repenser notre rapport au vivant.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie ; reel</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="168.75" customHeight="1" s="28">
+      <c r="A69" s="34" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B69" s="34" t="n"/>
+      <c r="C69" s="34" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="D69" s="35" t="inlineStr">
+        <is>
           <t>Charles PÉPIN</t>
         </is>
       </c>
-      <c r="E68" s="37" t="inlineStr">
+      <c r="E69" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin" title=" Wikipedia"&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href="https://charlespepin.fr/"  title=" Site officiel Charles Pépin "&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href="https://www.youtube.com/watch?v=WExeoL6qVmc" title=" Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori"&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href="https://www.youtube.com/watch?v=orOxuIHT_vc" title="Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal"&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt;"Les Vertus de l’échec" publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt;"La Confiance en soi " paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt;"La Rencontre"  en 2021 et "Vivre avec son passé" en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href="https://www.youtube.com/watch?v=M09YmUzDwO8" title=" Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs"&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt;   &lt;audio controls title=" La philosophie selon Charles Pépin par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F68" s="34" t="inlineStr">
+      <c r="F69" s="34" t="inlineStr">
         <is>
           <t>EvUMFrTWzsQ</t>
         </is>
       </c>
-      <c r="G68" s="36" t="inlineStr">
+      <c r="G69" s="36" t="inlineStr">
         <is>
           <t>"Mieux vivre grâce la philosophie pratique ! avec le philosophe Charles Pépin" par Métamorphose, éveille ta conscience</t>
         </is>
       </c>
-      <c r="H68" s="36" t="inlineStr">
+      <c r="H69" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/pepin-mini.webp</t>
         </is>
       </c>
-      <c r="I68" s="36" t="n"/>
-      <c r="J68" s="27" t="inlineStr">
+      <c r="I69" s="36" t="n"/>
+      <c r="J69" s="27" t="inlineStr">
         <is>
           <t>ethique</t>
         </is>
       </c>
-      <c r="K68" s="27" t="inlineStr">
+      <c r="K69" s="27" t="inlineStr">
         <is>
           <t>Humanisme</t>
         </is>
       </c>
-      <c r="L68" s="27" t="inlineStr">
+      <c r="L69" s="27" t="inlineStr">
         <is>
           <t>philosophe français qui fait de la philosophie une force de vie quotidienne.</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t xml:space="preserve">sens</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="146.25" customHeight="1" s="28">
-      <c r="A69" s="34" t="n">
+    <row r="70" ht="146.25" customHeight="1" s="28">
+      <c r="A70" s="34" t="n">
         <v>1973</v>
       </c>
-      <c r="B69" s="34" t="n"/>
-      <c r="C69" s="34" t="inlineStr">
+      <c r="B70" s="34" t="n"/>
+      <c r="C70" s="34" t="inlineStr">
         <is>
           <t>1973</t>
         </is>
       </c>
-      <c r="D69" s="35" t="inlineStr">
+      <c r="D70" s="35" t="inlineStr">
         <is>
           <t>Mehdi BELHAJ KACEM</t>
         </is>
       </c>
-      <c r="E69" s="36" t="inlineStr">
+      <c r="E70" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mehdi_Belhaj_Kacem"   title=" Wikipedia"&gt;Mehdi BELHAJ KACEM&lt;/a&gt;   est un philosophe, écrivain et acteur franco-tunisien, autodidacte radical et figure controversée de la pensée contemporaine, passé par les milieux militants et   &lt;a href="https://blogs.mediapart.fr/olivier-rachet/blog/130525/le-manifeste-conspirationniste-de-mehdi-belhaj-kacem" title="Le manifeste conspirationniste de Mehdi Belhaj Kacempar par mediapart"&gt;littéraires underground &lt;/a&gt; avant de forger une œuvre philosophique exigeante et iconoclaste. Après des expériences communautaires militantes, il découvre Alain Badiou comme maître à penser initial. &lt;/p&gt; &lt;p&gt; Il développe une pensée du nihilisme héritée de Heidegger, Nietzsche et Schürmann, centrée sur le "pléonectique" (désir insatiable de puissance et de transcendance) et une ontologie de l’Histoire comme &lt;a href="https://www.youtube.com/watch?v=YTOzn7dta7k" title="Mehdi Belhaj Kacem : "Un nouveau totalitarisme est en train de se mettre en place" par France Soir"&gt;tragédie irréductible. &lt;/a&gt;  Dans cette période, il écrit ces deux ouvrages :  "L’Antéforme" en 1997 et "Esthétique du chaos" en 2000. Son projet majeur, "L’Esprit du nihilisme" (cinq tomes, 2009-2015), pose Hegel comme "parenthèse" entre Kant et Badiou, avant de rompre violemment avec ce dernier dans "Après Badiou" paru en  2011, accusé d’archaïsme politique et moral. &lt;/p&gt; &lt;p&gt; Positionné à la marge des institutions, il incarne une radicalité post-moderne qui refuse les compromis, liant esthétique, politique et métaphysique dans une critique du présent. Il explore la "sexuation" (être et genre comme inexistant fondamental) et la transgression comme seule voie face au néant. &lt;/p&gt; Né en 1973, il publie très jeune des romans avant de se tourner vers la philosophie. Son œuvre, abondante et difficile, cherche à penser le mal et la démesure humaine, ce désir d’avoir toujours plus qu’il appelle « pléonexie », comme le fond de l’histoire. Ses prises de position récentes, notamment pendant la crise sanitaire, ont suscité de vives critiques. 
  &lt;audio controls title="Le bel âge de Mehdi Belhaj Kacem par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13937-24.01.2017-ITEMA_21206998-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F69" s="34" t="inlineStr">
+      <c r="F70" s="34" t="inlineStr">
         <is>
           <t>0DgQg3UK08E</t>
         </is>
       </c>
-      <c r="G69" s="36" t="inlineStr">
+      <c r="G70" s="36" t="inlineStr">
         <is>
           <t>"MEHDI BELHAJ KACEM - ÊTRE ET SEXUATION" par Nicolas CHOPIN-DESPRES</t>
         </is>
       </c>
-      <c r="H69" s="36" t="inlineStr">
+      <c r="H70" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/kacem-mini.webp</t>
-        </is>
-      </c>
-      <c r="I69" s="36" t="n"/>
-      <c r="J69" s="27" t="inlineStr">
-        <is>
-          <t>metaphysique ; esthetique</t>
-        </is>
-      </c>
-      <c r="K69" s="27" t="inlineStr">
-        <is>
-          <t>Post-structuralisme</t>
-        </is>
-      </c>
-      <c r="L69" s="27" t="inlineStr">
-        <is>
-          <t>philosophe franco-tunisien auteur du Système du pléonectique.</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">continental ; art</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="192" customHeight="1" s="28">
-      <c r="A70" s="34" t="n">
-        <v>1974</v>
-      </c>
-      <c r="B70" s="34" t="n"/>
-      <c r="C70" s="34" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="D70" s="35" t="inlineStr">
-        <is>
-          <t>Michaël FOESSEL</t>
-        </is>
-      </c>
-      <c r="E70" s="37" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel"  title=" Wikipedia"&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un "philosophe de la liberté". Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que "être de gauche" signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage "La privation de l’intime" paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href="https://www.youtube.com/watch?v=HcDfUGypNvA" style="color:#88A1E9" title="Michaël Fœssel - Récidive, 1938 par Librairie mollat"&gt;"Récidive. 1938"&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme "laboratoire" pour comprendre les fragilités  &lt;a href="https://www.youtube.com/watch?v=wdeS7SFEz7Y"  title="Démocratie illibérale par Michaël Foessel par France Culture"&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 "Quartier rouge. Le plaisir et la gauche", il interroge le rapport de  &lt;a href="https://www.youtube.com/watch?v=MDubXJZox34" title="Michaël Foessel : "La question du plaisir est aujourd'hui centrale en politique" par France Inter"&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment "Vers la paix perpétuelle" et "La religion dans les limites de la simple raison", tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title="La gauche : état des lieux  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F70" s="34" t="inlineStr">
-        <is>
-          <t>qejnQu7Cubs</t>
-        </is>
-      </c>
-      <c r="G70" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Qui êtes-vous Michaël Fœssel ?" par ABC Penser</t>
-        </is>
-      </c>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/foessel-mini.webp</t>
         </is>
       </c>
       <c r="I70" s="36" t="n"/>
       <c r="J70" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>metaphysique ; esthetique</t>
         </is>
       </c>
       <c r="K70" s="27" t="inlineStr">
         <is>
-          <t>Phénoménologie</t>
+          <t>Post-structuralisme</t>
         </is>
       </c>
       <c r="L70" s="27" t="inlineStr">
         <is>
-          <t>philosophe français spécialiste de la philosophie politique &amp;amp; philosophie allemande.</t>
+          <t>philosophe franco-tunisien auteur du Système du pléonectique.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5058,11 +5057,11 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="141" customHeight="1" s="28">
+          <t xml:space="preserve">continental ; art</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="192" customHeight="1" s="28">
       <c r="A71" s="34" t="n">
         <v>1974</v>
       </c>
@@ -5074,48 +5073,43 @@
       </c>
       <c r="D71" s="35" t="inlineStr">
         <is>
-          <t>Cynthia FLEURY</t>
-        </is>
-      </c>
-      <c r="E71" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cynthia_Fleury"  style="color:#6A142A"  title=" Wikipedia"&gt;Cynthia FLEURY&lt;/a&gt;  est une philosophe française connue pour son travail sur la démocratie, la vulnérabilité et l’éthique du soin. Elle  s’intéresse aux "outils de la &lt;a href="https://www.youtube.com/watch?v=rlmteYHuBsc" style="color:#88A1E9" title="DÉMOCRATIE, Cynthia Fleury (ABC Penser) "&gt;régulation démocratique" &lt;/a&gt; et au principe d’individuation en État social de droit, c’est‑à‑dire à la manière dont un État permet à chacun de devenir un sujet autonome tout en restant inséré dans le collectif. &lt;/p&gt; &lt;p&gt; Elle insiste sur l’importance d’un État social qui ne vise pas seulement la croissance économique, mais l’émancipation et l’autonomie des individus, notamment via les biens communs comme la santé et l’éducation et défend l’idée que la démocratie se joue aussi dans la façon dont nous prenons soin des plus vulnérables, à la fois sur le plan institutionnel et dans les relations ordinaires. &lt;/p&gt; &lt;p&gt;Pour elle, la vulnérabilité n’est pas l’inverse de l’autonomie, mais ce qui la traverse et la rend possible, à condition que la société permette de rendre les épreuves vécues "réversibles".&lt;/p&gt; &lt;p&gt;  Elle insiste sur l’éthique du soin : l’éthique n’est pas un "supplément d’âme" mais une condition pour éviter l’épuisement des soignants et mieux soigner les patients dans des institutions très gestionnaires. &lt;/p&gt; &lt;p&gt;Elle  défend un humanisme renouvelé et affirme l’urgence de remettre l’humanisme au cœur du système, face à l’hyper‑compétition, à la productivité sans fin et à l’aliénation qu’elles produisent. Sa réflexion propose une articulation entre transformation personnelle (travailler sa  &lt;a href="https://www.youtube.com/watch?v=8raeMytwQ8U" style="color:#88A1E9" title="Conférence de Cynthia Fleury sur la vulnérabilité  par  Faculté de Santé Sorbonne"&gt;propre vulnérabilité, &lt;/a&gt;  son courage, sa responsabilité) et transformation sociale (institutions plus justes, protection des biens communs, attention à la dignité de tous). &lt;/p&gt;   &lt;audio controls title="Cynthia Fleury : comment refaire société ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22259-09.07.2024-ITEMA_23798171-2024F44116S0191-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Michaël FOESSEL</t>
+        </is>
+      </c>
+      <c r="E71" s="37" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel"  title=" Wikipedia"&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un "philosophe de la liberté". Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que "être de gauche" signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage "La privation de l’intime" paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href="https://www.youtube.com/watch?v=HcDfUGypNvA" style="color:#88A1E9" title="Michaël Fœssel - Récidive, 1938 par Librairie mollat"&gt;"Récidive. 1938"&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme "laboratoire" pour comprendre les fragilités  &lt;a href="https://www.youtube.com/watch?v=wdeS7SFEz7Y"  title="Démocratie illibérale par Michaël Foessel par France Culture"&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 "Quartier rouge. Le plaisir et la gauche", il interroge le rapport de  &lt;a href="https://www.youtube.com/watch?v=MDubXJZox34" title="Michaël Foessel : "La question du plaisir est aujourd'hui centrale en politique" par France Inter"&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment "Vers la paix perpétuelle" et "La religion dans les limites de la simple raison", tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title="La gauche : état des lieux  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>cwm4rm9brZE</t>
+          <t>qejnQu7Cubs</t>
         </is>
       </c>
       <c r="G71" s="36" t="inlineStr">
         <is>
-          <t>" le témoignage de Cynthia Fleury, psychologue" par Ville de Saint-Médard-en-Jalles</t>
+          <t xml:space="preserve">"Qui êtes-vous Michaël Fœssel ?" par ABC Penser</t>
         </is>
       </c>
       <c r="H71" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/fleury-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/foessel-mini.webp</t>
         </is>
       </c>
       <c r="I71" s="36" t="n"/>
       <c r="J71" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K71" s="27" t="inlineStr">
         <is>
-          <t>Herméneutique</t>
+          <t>Phénoménologie</t>
         </is>
       </c>
       <c r="L71" s="27" t="inlineStr">
         <is>
-          <t>philosophe et psychanalyste française auteure d'une thèse sur "la métaphysique de l'imagination".</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t>philosophe français spécialiste de la philosophie politique &amp;amp; philosophie allemande.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5129,7 +5123,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="132.75" customHeight="1" s="28">
+    <row r="72" ht="141" customHeight="1" s="28">
       <c r="A72" s="34" t="n">
         <v>1974</v>
       </c>
@@ -5141,43 +5135,43 @@
       </c>
       <c r="D72" s="35" t="inlineStr">
         <is>
-          <t>Elsa DORLIN</t>
+          <t>Cynthia FLEURY</t>
         </is>
       </c>
       <c r="E72" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Elsa_Dorlin"  title=" Wikipedia"&gt;Elsa DORLIN&lt;/a&gt;  est une philosophe française  professeure de philosophie politique contemporaine à l’université Toulouse Jean Jaurès, spécialiste des épistémologies féministes, des intersections race/genre et de la violence politique. Invitée à Berkeley et chercheuse associée à Columbia, elle a dirigé des programmes comme ANR “Biosex” sur les sciences biomédicales et la différence sexuelle/raciale. &lt;/p&gt; &lt;p&gt; Ses travaux croisent Foucault, Judith Butler, Frantz Fanon et les traditions matérialistes africaines-américaines pour analyser les imbrications de domination (genre, race, classe) via une généalogie des discours médicaux, coloniaux et biopolitiques. Elle explore  &lt;a href="https://www.youtube.com/watch?v=04iiLbmn65w" title="Elsa Dorlin, pour un féminisme qui révolutionne la société par Centre d'Action Laïque. Libres, ensemble"&gt;l’historicité du sexe &lt;/a&gt; comme construction médicale et politique, critiquant l’assignation binaire et l’hétérosexualité reproductive comme outils de contrôle. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"La Matrice de la race" paru en 2006 : généalogie coloniale et sexuelle de la nation française via la médecine et "Sexe, genre et sexualités" en 2008 : introduction aux théories féministes, queer et post-coloniales. -"Une philosophie de la violence"  en 2017 : histoire politique de l’autodéfense des minorités opprimées. &lt;/p&gt; &lt;p&gt; Elle défend une "analytique de la domination" intersectionnelle, où race et genre sont co-constitutifs via biopouvoirs historiques, et une phénoménologie fanonienne des corps opprimés qui légitime la   &lt;a href="https://www.youtube.com/watch?v=Qh0FHzFxZns" title="Se défendre, une philosophie de la violence - Elsa Dorlinr par lundimatin"&gt;violence défensive &lt;/a&gt; comme praxis émancipatrice. &lt;/p&gt; &lt;audio controls title="Se défendre avec Elsa Dorlin par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-03.05.2021-ITEMA_22654753-2021F26101S0123-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;                                                                                                                                                                                                                                       </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cynthia_Fleury"  style="color:#6A142A"  title=" Wikipedia"&gt;Cynthia FLEURY&lt;/a&gt;  est une philosophe française connue pour son travail sur la démocratie, la vulnérabilité et l’éthique du soin. Elle  s’intéresse aux "outils de la &lt;a href="https://www.youtube.com/watch?v=rlmteYHuBsc" style="color:#88A1E9" title="DÉMOCRATIE, Cynthia Fleury (ABC Penser) "&gt;régulation démocratique" &lt;/a&gt; et au principe d’individuation en État social de droit, c’est‑à‑dire à la manière dont un État permet à chacun de devenir un sujet autonome tout en restant inséré dans le collectif. &lt;/p&gt; &lt;p&gt; Elle insiste sur l’importance d’un État social qui ne vise pas seulement la croissance économique, mais l’émancipation et l’autonomie des individus, notamment via les biens communs comme la santé et l’éducation et défend l’idée que la démocratie se joue aussi dans la façon dont nous prenons soin des plus vulnérables, à la fois sur le plan institutionnel et dans les relations ordinaires. &lt;/p&gt; &lt;p&gt;Pour elle, la vulnérabilité n’est pas l’inverse de l’autonomie, mais ce qui la traverse et la rend possible, à condition que la société permette de rendre les épreuves vécues "réversibles".&lt;/p&gt; &lt;p&gt;  Elle insiste sur l’éthique du soin : l’éthique n’est pas un "supplément d’âme" mais une condition pour éviter l’épuisement des soignants et mieux soigner les patients dans des institutions très gestionnaires. &lt;/p&gt; &lt;p&gt;Elle  défend un humanisme renouvelé et affirme l’urgence de remettre l’humanisme au cœur du système, face à l’hyper‑compétition, à la productivité sans fin et à l’aliénation qu’elles produisent. Sa réflexion propose une articulation entre transformation personnelle (travailler sa  &lt;a href="https://www.youtube.com/watch?v=8raeMytwQ8U" style="color:#88A1E9" title="Conférence de Cynthia Fleury sur la vulnérabilité  par  Faculté de Santé Sorbonne"&gt;propre vulnérabilité, &lt;/a&gt;  son courage, sa responsabilité) et transformation sociale (institutions plus justes, protection des biens communs, attention à la dignité de tous). &lt;/p&gt;   &lt;audio controls title="Cynthia Fleury : comment refaire société ? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22259-09.07.2024-ITEMA_23798171-2024F44116S0191-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>tGPA-Nv1OBc</t>
+          <t>cwm4rm9brZE</t>
         </is>
       </c>
       <c r="G72" s="36" t="inlineStr">
         <is>
-          <t>"Mouvements sociaux : violence ou autodéfense  ? " par France 24</t>
+          <t>" le témoignage de Cynthia Fleury, psychologue" par Ville de Saint-Médard-en-Jalles</t>
         </is>
       </c>
       <c r="H72" s="36" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/dorlin-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/fleury-mini.webp</t>
         </is>
       </c>
       <c r="I72" s="36" t="n"/>
       <c r="J72" s="27" t="inlineStr">
         <is>
-          <t>politique ; ethique</t>
+          <t>ethique ; politique</t>
         </is>
       </c>
       <c r="K72" s="27" t="inlineStr">
         <is>
-          <t>Post-structuralisme</t>
+          <t>Herméneutique</t>
         </is>
       </c>
       <c r="L72" s="27" t="inlineStr">
         <is>
-          <t>philosophe française spécialiste des épistémologies féministes &amp;amp; des intersections race/genre.</t>
+          <t>philosophe et psychanalyste française auteure d'une thèse sur "la métaphysique de l'imagination".</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5192,11 +5186,11 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre ; critique</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="173.25" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="132.75" customHeight="1" s="28">
       <c r="A73" s="34" t="n">
         <v>1974</v>
       </c>
@@ -5208,691 +5202,696 @@
       </c>
       <c r="D73" s="35" t="inlineStr">
         <is>
+          <t>Elsa DORLIN</t>
+        </is>
+      </c>
+      <c r="E73" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Elsa_Dorlin"  title=" Wikipedia"&gt;Elsa DORLIN&lt;/a&gt;  est une philosophe française  professeure de philosophie politique contemporaine à l’université Toulouse Jean Jaurès, spécialiste des épistémologies féministes, des intersections race/genre et de la violence politique. Invitée à Berkeley et chercheuse associée à Columbia, elle a dirigé des programmes comme ANR “Biosex” sur les sciences biomédicales et la différence sexuelle/raciale. &lt;/p&gt; &lt;p&gt; Ses travaux croisent Foucault, Judith Butler, Frantz Fanon et les traditions matérialistes africaines-américaines pour analyser les imbrications de domination (genre, race, classe) via une généalogie des discours médicaux, coloniaux et biopolitiques. Elle explore  &lt;a href="https://www.youtube.com/watch?v=04iiLbmn65w" title="Elsa Dorlin, pour un féminisme qui révolutionne la société par Centre d'Action Laïque. Libres, ensemble"&gt;l’historicité du sexe &lt;/a&gt; comme construction médicale et politique, critiquant l’assignation binaire et l’hétérosexualité reproductive comme outils de contrôle. &lt;/p&gt; &lt;p&gt; Ses principaux ouvrages sont : -"La Matrice de la race" paru en 2006 : généalogie coloniale et sexuelle de la nation française via la médecine et "Sexe, genre et sexualités" en 2008 : introduction aux théories féministes, queer et post-coloniales. -"Une philosophie de la violence"  en 2017 : histoire politique de l’autodéfense des minorités opprimées. &lt;/p&gt; &lt;p&gt; Elle défend une "analytique de la domination" intersectionnelle, où race et genre sont co-constitutifs via biopouvoirs historiques, et une phénoménologie fanonienne des corps opprimés qui légitime la   &lt;a href="https://www.youtube.com/watch?v=Qh0FHzFxZns" title="Se défendre, une philosophie de la violence - Elsa Dorlinr par lundimatin"&gt;violence défensive &lt;/a&gt; comme praxis émancipatrice. &lt;/p&gt; &lt;audio controls title="Se défendre avec Elsa Dorlin par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16174-03.05.2021-ITEMA_22654753-2021F26101S0123-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="F73" s="34" t="inlineStr">
+        <is>
+          <t>tGPA-Nv1OBc</t>
+        </is>
+      </c>
+      <c r="G73" s="36" t="inlineStr">
+        <is>
+          <t>"Mouvements sociaux : violence ou autodéfense  ? " par France 24</t>
+        </is>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/dorlin-mini.webp</t>
+        </is>
+      </c>
+      <c r="I73" s="36" t="n"/>
+      <c r="J73" s="27" t="inlineStr">
+        <is>
+          <t>politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K73" s="27" t="inlineStr">
+        <is>
+          <t>Post-structuralisme</t>
+        </is>
+      </c>
+      <c r="L73" s="27" t="inlineStr">
+        <is>
+          <t>philosophe française spécialiste des épistémologies féministes &amp;amp; des intersections race/genre.</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">genre ; critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="173.25" customHeight="1" s="28">
+      <c r="A74" s="34" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B74" s="34" t="n"/>
+      <c r="C74" s="34" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="D74" s="35" t="inlineStr">
+        <is>
           <t>Claire MARIN</t>
         </is>
       </c>
-      <c r="E73" s="50" t="inlineStr">
+      <c r="E74" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claire_Marin"  title=" Wikipedia"&gt;Claire MARIN&lt;/a&gt;  est une philosophe et écrivaine française professeure agrégée de philosophie en classes préparatives aux grandes écoles et membre associée de l'École normale supérieure. Normalienne, elle enseigne des auteurs comme Deleuze ou Bergson tout en menant une œuvre accessible et sensible, mêlant philosophie, littérature et expérience intime. Ses essais,  &lt;a href="https://www.youtube.com/watch?v=189nLvJBfJc" title="Claire MARIN par LCP"&gt;best-sellers récents &lt;/a&gt; comme Rupture(s) (2021) et Être à sa place (2022), explorent les épreuves existentielles sans céder au développement personnel simpliste, en s'appuyant sur un corpus philosophique et littéraire vaste. &lt;/p&gt; &lt;p&gt; Elle excelle à philosophier l'intime : ruptures amoureuses, deuil, maladie, identité plurielle, en les reliant à des penseurs comme Pascal, Hume ou le courant du care (qu'elle étudie au Séminaire international d’études sur le soin à l’ENS). La rupture y est à double visage – blessure irrémédiable mais aussi transformation radicale, plaisir de la dispersion du "moi" fragmenté. Elle rejette l'unité illusoire du sujet pour une existence mouvante, ancrée dans le vécu concret et la narration poétique. &lt;/p&gt; &lt;p&gt; Ses &lt;a href="https://www.youtube.com/watch?v=3L7BK5JN8FM" title="Claire MARIN par Librairie mollat"&gt;réflexions récentes &lt;/a&gt; insistent sur le "vivant" comme mouvement patient, empathique et sensible, contre les abstractions métaphysiques : éducation au rythme biologique, altérité bienveillante, douceur face à la souffrance. Influencée par Bergson, elle reconnecte discours philosophiques au corps et à l'émotion, critiquant le mépris académique pour le care. Philosophe "psylosophe" post-Covid, elle rend la pensée romanesque, ciselant des chapitres incisifs comme des "disserts intimistes".&lt;/p&gt; &lt;p&gt; Enseignante engagée, elle vulgarise la philosophie pour lycéens via des ouvrages thématiques (bonheur, identité, nature/culture), sans manuel rigide mais avec un "pas de côté" concret. Romancière primée (prix Jean-Bernard en 2008), elle mêle esthétique poétique et réflexion sociétale, dialoguant avec la modernité (feminine, technique). Son style narratif transforme la philo en journal existentiel, touchant un large public féminin surtout. &lt;/p&gt; &lt;audio controls title="La philosophie de Claire MARIN par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13942-19.09.2022-ITEMA_23138788-2022F29830S0262-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
 </t>
         </is>
       </c>
-      <c r="F73" s="34" t="inlineStr">
+      <c r="F74" s="34" t="inlineStr">
         <is>
           <t>fe6vbibY2CY</t>
         </is>
       </c>
-      <c r="G73" s="36" t="inlineStr">
+      <c r="G74" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">"Les débuts - Claire Marin" par Librairie Mollat</t>
         </is>
       </c>
-      <c r="H73" s="36" t="inlineStr">
+      <c r="H74" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/cmarin-mini.webp</t>
         </is>
       </c>
-      <c r="I73" s="36" t="n"/>
-      <c r="J73" s="27" t="inlineStr">
+      <c r="I74" s="36" t="n"/>
+      <c r="J74" s="27" t="inlineStr">
         <is>
           <t>ethique</t>
         </is>
       </c>
-      <c r="K73" s="27" t="inlineStr">
+      <c r="K74" s="27" t="inlineStr">
         <is>
           <t>Phénoménologie</t>
         </is>
       </c>
-      <c r="L73" s="27" t="inlineStr">
+      <c r="L74" s="27" t="inlineStr">
         <is>
           <t>philosophe française au style narratif qui transforme la philo en journal existentiel.</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t xml:space="preserve">continental</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="162" customHeight="1" s="28">
-      <c r="A74" s="34" t="n">
+    <row r="75" ht="162" customHeight="1" s="28">
+      <c r="A75" s="34" t="n">
         <v>1974</v>
       </c>
-      <c r="B74" s="34" t="n"/>
-      <c r="C74" s="34" t="inlineStr">
+      <c r="B75" s="34" t="n"/>
+      <c r="C75" s="34" t="inlineStr">
         <is>
           <t>1974</t>
         </is>
       </c>
-      <c r="D74" s="35" t="inlineStr">
+      <c r="D75" s="35" t="inlineStr">
         <is>
           <t>Camille RIQUIER</t>
         </is>
       </c>
-      <c r="E74" s="39" t="inlineStr">
+      <c r="E75" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Camille_Riquier"  title=" Wikipedia"&gt;Camille RIQUIER&lt;/a&gt;  est un philosophe français, spécialiste de la philosophie française du XXe siècle, agrégé de philosophie (2000) et docteur de l'université Paris-Sorbonne (thèse sur « Temps et méthode chez Bergson »). Doyen de la faculté de philosophie de l'Institut catholique de Paris, il est membre de la rédaction des revues Esprit, Philosophie et Alter, et contribue à Libération. Lauréat du prix La Bruyère de l'Académie française en 2010 pour Archéologie de Bergson, il allie rigueur académique et  &lt;a href="https://www.youtube.com/watch?v=URFYj-EZAMc" title="Camille Riquier l’audace du rêve à l’action par TEDx Talks"&gt;réflexion contemporaine &lt;/a&gt; sur foi, temps et existentialisme.&lt;/p&gt; &lt;p&gt; Spécialiste de Bergson, il en propose une "archéologie" dans son ouvrage éponyme, révélant comment le temps bergsonien (durée intuitive) dépasse la métaphysique classique pour une méthode généalogique du changement. Il souligne l'intuition comme outil anti-scientiste, reliant Bergson à Péguy et Sartre : chez Bergson, le temps n'est pas spatialisé mais vivant, fondant une  &lt;a href="https://www.youtube.com/watch?v=dAFK_Quxcms" title="Camille Riquier lire ou quand l’oeil écoute par Banquetdelagrasse"&gt;métaphysique de l'intérieur.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Dans Philosophie de Péguy ou les mémoires d'un imbécile, il  explore la pensée péguyste comme anti-intellectualisme charnel : l'"imbécile" (figure bergsonienne) incarne la mémoire résistante à l'abstraction républicaine. Péguy y réconcilie mystique et révolution, foi et raison, contre le progressisme abstrait ; il y voit une philosophie de la répétition créatrice, proche du corps et de l'histoire vécue. &lt;/p&gt; &lt;p&gt; Ses travaux récents sur Sartre (Métamorphoses de Descartes : Le secret de Sartre, Gallimard, 2022) déconstruisent l'existentialisme sartrien comme héritage cartésien transformé : liberté absolue masquant un vide ontologique. Nous ne savons plus croire diagnostique un nihilisme post-moderne où la crédulité remplace la foi raisonnée, appelant à une "foi des autres" sociale et dubitative face à la désorientation spirituelle. &lt;/p&gt; &lt;audio controls title="Camille RIQUIER, philosophe de la croyance  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-28.08.2020-ITEMA_22411316-2020C12410E0368-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
 </t>
         </is>
       </c>
-      <c r="F74" s="34" t="inlineStr">
+      <c r="F75" s="34" t="inlineStr">
         <is>
           <t>6IVqKs2fQWE</t>
         </is>
       </c>
-      <c r="G74" s="36" t="inlineStr">
+      <c r="G75" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">"Philosophie ou spiritualités : avons-nous besoin d'un supplément d'âme ?" par Le Point</t>
         </is>
       </c>
-      <c r="H74" s="36" t="inlineStr">
+      <c r="H75" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/criquier-mini.webp</t>
         </is>
       </c>
-      <c r="I74" s="36" t="n"/>
-      <c r="J74" s="27" t="inlineStr">
+      <c r="I75" s="36" t="n"/>
+      <c r="J75" s="27" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="K74" s="27" t="inlineStr">
+      <c r="K75" s="27" t="inlineStr">
         <is>
           <t>Spiritualisme ; Réalisme</t>
         </is>
       </c>
-      <c r="L74" s="27" t="inlineStr">
+      <c r="L75" s="27" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de la philosophie française du XXe siècle.</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t xml:space="preserve">continental</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="144.75" customHeight="1" s="28">
-      <c r="A75" s="34" t="n">
+    <row r="76" ht="144.75" customHeight="1" s="28">
+      <c r="A76" s="34" t="n">
         <v>1975</v>
       </c>
-      <c r="B75" s="34" t="n"/>
-      <c r="C75" s="34" t="inlineStr">
+      <c r="B76" s="34" t="n"/>
+      <c r="C76" s="34" t="inlineStr">
         <is>
           <t>1975</t>
         </is>
       </c>
-      <c r="D75" s="35" t="inlineStr">
+      <c r="D76" s="35" t="inlineStr">
         <is>
           <t>Vincent CITOT</t>
         </is>
       </c>
-      <c r="E75" s="37" t="inlineStr">
+      <c r="E76" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vincent_Citot"  title=" Wikipedia"&gt;Vincent CITOT&lt;/a&gt; est un philosophe  français, directeur de la revue Le Philosophoire et auteur de travaux sur la philosophie générale, les rapports entre philosophie et science, ainsi que sur la modernité et l’histoire des idées.   &lt;a href="http://www.vincentcitot.com" title="Vincent CITOT"&gt;Son parcours &lt;/a&gt; mêle aussi l’écriture et la photographie, ce qui lui donne une pratique intellectuelle assez large. &lt;/p&gt; &lt;p&gt; Sa philosophie insiste d’abord sur l’exigence de penser contre les évidences, les dogmes et le conformisme. Chez lui, philosopher n’est pas simplement enchaîner des idées, mais faire un effort critique, une vigilance de l’esprit qui commence par le doute et la mise à distance des fausses certitudes. Cette dimension critique fait de la réflexion une forme d’ascèse intellectuelle, au service de la liberté. &lt;/p&gt; &lt;p&gt; Il défend aussi une conception exigeante mais non réductrice de la philosophie : elle n’est pas une science au sens strict, mais elle dialogue avec la science tout en gardant sa propre portée de sagesse, de valeurs et de pratique existentielle. Dans cette perspective, la philosophie doit examiner ses limites, ses présupposés et ses méthodes, sans se prendre pour un savoir absolu. Il accorde également une grande place à l’universalisme, notamment dans les questions existentielles, qu’il juge plus stables et plus universelles que les cadres purement historiques ou culturels. &lt;/p&gt; &lt;p&gt; Enfin, son ouvrage Histoire mondiale de la philosophie élargit le regard au-delà du seul modèle grec : il propose de penser la philosophie comme une forme de pensée qui cherche à se justifier par divers moyens, dans plusieurs civilisations et au sein de cycles intellectuels plus vastes. Cela fait de lui  &lt;a href="https://www.les-philosophes.fr/agora/vincent-citot.html" title="Vincent CITOT par lesphiulosophes,fr"&gt;un philosophe du comparatisme &lt;/a&gt;  et de la pluralité des traditions, attentif à la modernité, à la liberté individuelle et à la diversité des formes de rationalité. &lt;/p&gt; &lt;audio controls title="Histoire mondiale de la philosophie avec Vincent CITOT  par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/22676-14.10.2022-ITEMA_23166024-2022F45096S0287-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;    
 </t>
         </is>
       </c>
-      <c r="F75" s="34" t="inlineStr">
+      <c r="F76" s="34" t="inlineStr">
         <is>
           <t>Gt0gT_ORLYs</t>
         </is>
       </c>
-      <c r="G75" s="36" t="inlineStr">
+      <c r="G76" s="36" t="inlineStr">
         <is>
           <t>"Vincent Citot Exposition Montrond les bains" par Dominique Dozolme</t>
         </is>
       </c>
-      <c r="H75" s="36" t="inlineStr">
+      <c r="H76" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/vcitot-mini.webp</t>
         </is>
       </c>
-      <c r="I75" s="36" t="n"/>
-      <c r="J75" s="27" t="inlineStr">
+      <c r="I76" s="36" t="n"/>
+      <c r="J76" s="27" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="K75" s="27" t="inlineStr">
+      <c r="K76" s="27" t="inlineStr">
         <is>
           <t>Constructivisme</t>
         </is>
       </c>
-      <c r="L75" s="27" t="inlineStr">
+      <c r="L76" s="27" t="inlineStr">
         <is>
           <t>philosophe français penseur contre les évidences, les dogmes et le conformisme.</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t xml:space="preserve">continental</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="146.25" customHeight="1" s="28">
-      <c r="A76" s="34" t="n">
+    <row r="77" ht="146.25" customHeight="1" s="28">
+      <c r="A77" s="34" t="n">
         <v>1977</v>
       </c>
-      <c r="B76" s="34" t="n"/>
-      <c r="C76" s="34" t="inlineStr">
+      <c r="B77" s="34" t="n"/>
+      <c r="C77" s="34" t="inlineStr">
         <is>
           <t>1977</t>
         </is>
       </c>
-      <c r="D76" s="35" t="inlineStr">
+      <c r="D77" s="35" t="inlineStr">
         <is>
           <t>Séverine KODJO-GRANDVAUX</t>
         </is>
       </c>
-      <c r="E76" s="36" t="inlineStr">
+      <c r="E77" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A9verine_Kodjo-Grandvaux"  title=" Wikipedia"&gt;Séverine KODJO-GRANDVAUX&lt;/a&gt; est une philosophe, journaliste, programmatrice littéraire et  &lt;a href="https://www.jeuneafrique.com/auteurs/s-kodjo-grandvaux/"  title="Ses dernières publications par jeuneafrique"&gt;éditrice française &lt;/a&gt; principalement reconnue pour ses travaux sur les philosophies africaines contemporaines et les études postcoloniales. Elle occupe une position de chercheure associée au Laboratoire des logiques contemporaines de la philosophie à l’Université Paris 8, et elle est impliquée dans des initiatives autour des humanités africaines et des échanges intellectuels entre l’Afrique et le monde francophone. Née à Besançon en 1977, elle a consacré sa thèse (2006) à l’idée de « philosophie africaine » chez Jean-Godefroy Bidima, Souleymane Bachir Diagne, Henry Odera Oruka et Kwasi Wiredu. Journaliste pour &lt;em&gt;Le Monde&lt;/em&gt;, elle dirige aussi la collection « Essais » des éditions Jimsaan. &lt;/p&gt; &lt;p&gt; En 2013, elle publie &lt;a href="https://www.youtube.com/watch?v=w8pfqdnej-o" title="African Philosophies I Lecture by philosopher Séverine Kodjo-Grandvaux par Radboud Reflects"&gt;"Philosophies africaines", &lt;/a&gt; ouvrage qui est considéré comme une référence majeure dans le domaine et qui analyse en profondeur les courants et les enjeux de la philosophie africaine contemporaine. Elle publie ensuite  &lt;a href="https://www.youtube.com/watch?v=AJAz1OmcVbI" title=""Devenir Vivants" avec Séverine Kodjo-Grandvaux. Extrait du podcast Afrotopiques par Génération Afrotopia"&gt;"Devenir vivants" &lt;/a&gt; et "Droit et colonisation"  — œuvre collective sur les rapports entre droit et colonialisme, témoignant d’un engagement dans les études postcoloniales et juridiques. &lt;/p&gt; &lt;p&gt; Ce qui la distingue dans le paysage philosophique français, c'est sa capacité à faire dialoguer les philosophies africaines avec les enjeux contemporains globaux, notamment écologiques et postcoloniaux. Elle contribue à décentrer la pensée philosophique de son eurocentrisme traditionnel tout en proposant des outils conceptuels originaux pour penser notre relation au vivant et au cosmos.&lt;/p&gt;
    &lt;audio controls title="Philosophie Africaine par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12016-15.04.2013-ITEMA_20470144-2013C18044S0105-NET_FC_590A75DA-F57B-40F9-88DF-1D448D87542C-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F76" s="34" t="inlineStr">
+      <c r="F77" s="34" t="inlineStr">
         <is>
           <t>NDaTcUJ5XmY</t>
         </is>
       </c>
-      <c r="G76" s="36" t="inlineStr">
+      <c r="G77" s="36" t="inlineStr">
         <is>
           <t>"Séverine Kodjo-Grandvaux : De la domination à la résonance" par AFD</t>
         </is>
       </c>
-      <c r="H76" s="36" t="inlineStr">
+      <c r="H77" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/grandvaux-mini.webp</t>
         </is>
       </c>
-      <c r="I76" s="36" t="n"/>
-      <c r="J76" s="27" t="inlineStr">
+      <c r="I77" s="36" t="n"/>
+      <c r="J77" s="27" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K76" s="27" t="inlineStr">
+      <c r="K77" s="27" t="inlineStr">
         <is>
           <t>Tiers-mondisme ; Pan-africanisme</t>
         </is>
       </c>
-      <c r="L76" s="27" t="inlineStr">
+      <c r="L77" s="27" t="inlineStr">
         <is>
           <t>philosophe française spécialiste des philosophies africaines.</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">sud;femme</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
         <is>
           <t xml:space="preserve">decolonial</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="147.75" customHeight="1" s="28">
-      <c r="A77" s="34" t="n">
+    <row r="78" ht="147.75" customHeight="1" s="28">
+      <c r="A78" s="34" t="n">
         <v>1977</v>
       </c>
-      <c r="B77" s="34" t="n"/>
-      <c r="C77" s="34" t="inlineStr">
+      <c r="B78" s="34" t="n"/>
+      <c r="C78" s="34" t="inlineStr">
         <is>
           <t>1977</t>
         </is>
       </c>
-      <c r="D77" s="35" t="inlineStr">
+      <c r="D78" s="35" t="inlineStr">
         <is>
           <t>Maxime ROVÈRE</t>
         </is>
       </c>
-      <c r="E77" s="36" t="inlineStr">
+      <c r="E78" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maxime_Rov%C3%A8re"  title=" Wikipedia"&gt;Maxime ROVÈRE&lt;/a&gt;  est un philosophe, écrivain et traducteur français, spécialiste de Spinoza et créateur d’une -&lt;a href="https://www.youtube.com/watch?v=A_4XSOHakEY" title="À l'école des interactions - Maxime Rovere par Revue Esprit"&gt;"philosophie interactionnelle" &lt;/a&gt; qui met l’accent sur les relations humaines dynamiques plutôt que sur des systèmes abstraits. Chercheur associé à l’IHRIM et Fellow au Netherlands Institute for Advanced Study, il mêle recherche universitaire, traductions et écrits grand public. &lt;/p&gt; &lt;p&gt; Ses travaux sur Spinoza insistent sur des "méthodes pour exister" plutôt qu’un système rigide : la théorie des trois genres de connaissance (expérience, raison, intuition) comme outils pratiques de vérification, et une intelligence partagée plutôt que solitaire. Ses différents écrits sont "Le Clan Spinoza" paru en 2017 qui retrace la vie du philosophe et de son entourage comme invention collective de la liberté ; il a retraduit  "l’Éthique" en 2021 avec un millier de notes contextualisées. &lt;/p&gt; &lt;p&gt; Sa pensée originale, inspirée de l’interactionnisme symbolique (Goffman) et étendue à la métaphysique, voit les relations comme circulations multiples et incontrôlables d’attention, d’affects et de tensions. &lt;/p&gt; &lt;p&gt;  Ses ouvrages : &lt;a href="https://www.youtube.com/watch?v=oApu_IVn7p4"  title="Maxime Rovere - Se vouloir du bien et se faire du mal : philosophie de la dispute par librairie mollat"&gt;"Se vouloir du bien et se faire du mal" &lt;/a&gt; paru en 2021 : philosophie des disputes comme opportunités éthiques. "Que faire des cons ?"  best-seller de 2019 : guide argotique pour naviguer les conflits sans violence et &lt;a href="https://www.youtube.com/watch?v=2IGKNQB4bRo" title="Maxime Rovere : "Parler avec sa mère" "est un défi exigeant" par France Inter"&gt;"Parler avec sa mère"  &lt;/a&gt; paru en 2025 est une réflexion cosmique et pythagoricienne sur les liens familiaux. &lt;/p&gt; &lt;audio controls title="Maxime Rovere nous donne les clés de l'amour infini par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/24295-10.05.2024-ITEMA_23737128-2024F51733S0089-27.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
-      <c r="F77" s="34" t="inlineStr">
+      <c r="F78" s="34" t="inlineStr">
         <is>
           <t>ZamutZpubdY</t>
         </is>
       </c>
-      <c r="G77" s="36" t="inlineStr">
+      <c r="G78" s="36" t="inlineStr">
         <is>
           <t>"Que faire des cons ? | Maxime Rovere | TEDxTours" par TEDx Talks</t>
         </is>
       </c>
-      <c r="H77" s="36" t="inlineStr">
+      <c r="H78" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rovere-mini.webp</t>
         </is>
       </c>
-      <c r="I77" s="36" t="n"/>
-      <c r="J77" s="27" t="inlineStr">
+      <c r="I78" s="36" t="n"/>
+      <c r="J78" s="27" t="inlineStr">
         <is>
           <t>ethique ; epistemologie</t>
         </is>
       </c>
-      <c r="K77" s="27" t="inlineStr">
+      <c r="K78" s="27" t="inlineStr">
         <is>
           <t>Rationalisme</t>
         </is>
       </c>
-      <c r="L77" s="27" t="inlineStr">
+      <c r="L78" s="27" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de Spinoza et créateur d'une "philosophie interactionnelle".</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
         <is>
           <t xml:space="preserve">continental</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="180.55" customHeight="1" s="28">
-      <c r="A78" s="34" t="n">
+    <row r="79" ht="180.55" customHeight="1" s="28">
+      <c r="A79" s="34" t="n">
         <v>1978</v>
       </c>
-      <c r="B78" s="34" t="n"/>
-      <c r="C78" s="34" t="inlineStr">
+      <c r="B79" s="34" t="n"/>
+      <c r="C79" s="34" t="inlineStr">
         <is>
           <t>1978</t>
         </is>
       </c>
-      <c r="D78" s="35" t="inlineStr">
+      <c r="D79" s="35" t="inlineStr">
         <is>
           <t>Jean-Baptiste JEANGENE VILMER</t>
         </is>
       </c>
-      <c r="E78" s="37" t="inlineStr">
+      <c r="E79" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Baptiste_Jeang%C3%A8ne_Vilmer"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean-Baptiste JEANGENE VILMER&lt;/a&gt;  est un philosophe, politologue et juriste français spécialiste de l’éthique de la guerre, du droit international et des relations internationales, et également diplomate (ambassadeur de France au Vanuatu depuis 2022). Il est formé dans trois disciplines : philosophie (licence, master, doctorat), droit (licence, LLM, postdoctorat) et science politique (doctorat). &lt;/p&gt; &lt;p&gt; Sa thèse porte sur "l’intervention militaire justifiée par des raisons humanitaires", à la croisée de philosophie politique, droit international et théorie des relations internationales. Il défend en théorie des relations internationales un "réalisme libéral" inspiré de Raymond Aron, Stanley Hoffmann et Pierre Hassner : reconnaissance du tragique et des &lt;a href="https://www.youtube.com/watch?v=4EECHNFvt4Q"  title=" J-B. Jeangène Vilmer - Synthèse par Institut Guerre et Paix"&gt;rapports de force, &lt;/a&gt;  mais attachée au droit international, aux droits humains et aux institutions. &lt;/p&gt; &lt;p&gt; Il se situe à l’intersection de philosophie morale, droit international et stratégie : penser les guerres et interventions non seulement en termes juridiques ou militaires, mais surtout en termes de responsabilité morale (tuer, laisser mourir, protéger). Son &lt;a href="https://www.jbjv.com/IMG/pdf/JB_Jeangene_Vilmer_2013_-_Pour_un_realisme_liberal_en_relations_internationales.pdf"  title="Pour un réalisme libéral en relations internationales par jbjv"&gt;"réalisme libéral" &lt;/a&gt; refuse à la fois le cynisme réaliste pur et l’idéalisme naïf, il cherche des critères prudents mais exigeants pour juger les interventions, la justice pénale, ou la responsabilité des États. &lt;/p&gt; &lt;p&gt; Il insiste sur les dilemmes : parfois, intervenir violemment peut sauver des vies, mais peut aussi aggraver le conflit ; parfois, poursuivre les criminels peut fragiliser la paix. Sa pensée explore ces tensions plutôt que de proposer des solutions simplistes. &lt;/p&gt; 
   &lt;audio controls title="Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
-      <c r="F78" s="34" t="inlineStr">
+      <c r="F79" s="34" t="inlineStr">
         <is>
           <t>v_czW-Qh8sg</t>
         </is>
       </c>
-      <c r="G78" s="36" t="inlineStr">
+      <c r="G79" s="36" t="inlineStr">
         <is>
           <t>"Le changement climatique au Vanuatu et l'action de la France (Jean-Baptiste Jeangène Vilmer)" par ambassade fr</t>
         </is>
       </c>
-      <c r="H78" s="36" t="inlineStr">
+      <c r="H79" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/vilmer-mini.webp</t>
         </is>
       </c>
-      <c r="I78" s="36" t="n"/>
-      <c r="J78" s="27" t="inlineStr">
+      <c r="I79" s="36" t="n"/>
+      <c r="J79" s="27" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="K78" s="27" t="inlineStr">
+      <c r="K79" s="27" t="inlineStr">
         <is>
           <t>Analytique</t>
         </is>
       </c>
-      <c r="L78" s="27" t="inlineStr">
+      <c r="L79" s="27" t="inlineStr">
         <is>
           <t>philosophe français spécialiste de l'éthique de la guerre &amp;amp; du droit international.</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t xml:space="preserve">justice</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="283.55" customHeight="1" s="28">
-      <c r="A79" s="34" t="n">
+    <row r="80" ht="283.55" customHeight="1" s="28">
+      <c r="A80" s="34" t="n">
         <v>1978</v>
       </c>
-      <c r="B79" s="34" t="n"/>
-      <c r="C79" s="34" t="n">
+      <c r="B80" s="34" t="n"/>
+      <c r="C80" s="34" t="n">
         <v>1978</v>
       </c>
-      <c r="D79" s="27" t="inlineStr">
+      <c r="D80" s="27" t="inlineStr">
         <is>
           <t>Nadia Yala KISUKIDI</t>
         </is>
       </c>
-      <c r="E79" s="38" t="inlineStr">
+      <c r="E80" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nadia_Yala_Kisukidi"  title=" Wikipedia"&gt;Nadia Yala KISUKIDI&lt;/a&gt;  est une philosophe et écrivaine franco-congolaise née à Bruxelles, professeure à l’université Paris 8, connue pour ses travaux sur Bergson, la philosophie Africaine, le féminisme noir et les effets coloniaux dans la pensée occidentale. Sa philosophie part d’un constat simple : les grands corpus philosophiques ont longtemps été enseignés comme s’ils étaient universels, alors qu’ils reflètent souvent une histoire située, européenne et coloniale. &lt;/p&gt; &lt;p&gt; Elle est d’abord reconnue comme spécialiste de Bergson. Dans son livre Bergson ou l’humanité créatrice, elle relit Bergson à partir de la création, du mouvement et de l’invention de soi, en montrant que la philosophie peut penser la vie comme puissance de transformation plutôt que comme identité figée. &lt;/p&gt; &lt;p&gt; Un autre axe central de son travail est la critique de la « bibliothèque coloniale » : elle montre comment l’idée d’Afrique et l’idée de « Noir » ont été fabriquées dans &lt;a href="https://www.youtube.com/watch?v=smUx6yKHTF4"  title="NY Kisikidi une nouvelle pensée des mondes noirs par RFI"&gt;des cadres intellectuels &lt;/a&gt;  marqués par la domination européenne. Son approche ne consiste pas seulement à dénoncer ces héritages, mais à déplacer le centre du regard pour faire place à des pensées africaines, diasporiques et non occidentales. &lt;/p&gt; &lt;p&gt; Elle développe aussi une réflexion féministe et politique, notamment avec Djamila Ribeiro dans Dialogue transatlantique, où elle met en relation les expériences des femmes noires, les diasporas africaines et les formes contemporaines de résistance. Chez elle, le féminisme n’est pas séparé de la question raciale : il sert à &lt;a href="https://www.youtube.com/watch?v=ECngo81h5v0"  title="NY Kisikidi défendre les vies humaines par Campus AFD par RFI"&gt;penser des solidarités, &lt;/a&gt; des voix minorées et des alliances intellectuelles entre continents. &lt;/p&gt; &lt;p&gt; Sa philosophie vise une forme d’universel décentré : non pas un universel abstrait imposé d’en haut, mais un universel construit à partir des conflits, des pluralités et des expériences historiques concrètes. En ce sens, elle propose une philosophie de la relation, de la circulation et de la restitution, où l’on comprend le monde en écoutant les marges autant que les centres. &lt;/p&gt;  &lt;audio controls title="Nadia Yala Kisukidi le mouvement anti raciste par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-13.06.2020-ITEMA_22360573-3-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
-      <c r="F79" s="34" t="inlineStr">
+      <c r="F80" s="34" t="inlineStr">
         <is>
           <t>C6RlugxFljU</t>
         </is>
       </c>
-      <c r="G79" s="36" t="inlineStr">
+      <c r="G80" s="36" t="inlineStr">
         <is>
           <t>Nadia Yala Kisukidi décolonisation et philosophie par TV5 Monde</t>
         </is>
       </c>
-      <c r="H79" s="37" t="inlineStr">
+      <c r="H80" s="37" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/nykisukidi-mini.webp</t>
-        </is>
-      </c>
-      <c r="I79" s="36" t="n"/>
-      <c r="J79" s="27" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="K79" s="27" t="inlineStr">
-        <is>
-          <t>Tiers-mondisme</t>
-        </is>
-      </c>
-      <c r="L79" s="27" t="inlineStr">
-        <is>
-          <t>philosophe française spécialiste de la pensée de Bergson et des études postcoloniales.</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud;femme</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">decolonial</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="395.5" customHeight="1" s="28">
-      <c r="A80" s="34" t="n">
-        <v>1979</v>
-      </c>
-      <c r="B80" s="34" t="n"/>
-      <c r="C80" s="34" t="n">
-        <v>1979</v>
-      </c>
-      <c r="D80" s="27" t="inlineStr">
-        <is>
-          <t>Julia DE-FUNÈS</t>
-        </is>
-      </c>
-      <c r="E80" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julia_de_Fun%C3%A8s"  title=" Wikipedia"&gt;Julia DE-FUNÈS&lt;/a&gt; est une philosophe, essayiste et conférencière française, également spécialiste des ressources humaines et du monde de l’entreprise. Après avoir travaillé plusieurs années comme chasseuse de têtes, elle a créé en 2010 un cabinet de conseil mobilisant la philosophie dans les organisations. Elle a ensuite soutenu en 2017 une thèse consacrée au passage de l’identité personnelle à l’authenticité, à travers les notions de représentation et de mimétisme. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=OaDbpC3azdQ"  title="julia de Funès, philosophe par 21 News"&gt; Sa démarche consiste &lt;/a&gt;  à faire sortir la philosophie du cadre purement universitaire pour la confronter aux situations ordinaires : travail, management, bonheur, relations professionnelles ou développement personnel. Elle considère la philosophie comme un exercice de mise à distance, destiné à interroger les évidences et à examiner le sens réel des mots que nous employons. Dans cette perspective, philosopher revient à ne pas accepter mécaniquement les discours dominants, les slogans ou les habitudes de pensée. &lt;/p&gt; &lt;p&gt; Une de ses principales critiques vise l’entreprise contemporaine et la multiplication des procédures, des indicateurs et des discours managériaux. Dans Socrate au pays des process ou La Vie de bureau, elle dénonce ce qu’elle perçoit comme une perte de sens : les salariés peuvent être soumis à des injonctions contradictoires et à un langage abstrait qui transforme parfois l’être humain en simple fonction. Elle oppose à cette logique la nécessité de retrouver du jugement, de l’autonomie et une réflexion véritable sur les finalités du travail. &lt;/p&gt; &lt;p&gt; Elle critique également le développement personnel lorsqu’il promet le bonheur, la réussite ou la confiance en soi au moyen de recettes standardisées. Dans &lt;a href="https://www.youtube.com/watch?v=dV5r46P6yUU"  title="le développement personnel est la plus grosse arnaque par Clique Tv"&gt;Le Développement (im)personnel&lt;/a&gt;, elle soutient que certaines formes de psychologie positive peuvent transformer des problèmes sociaux ou professionnels en responsabilités purement individuelles : si l’on échoue, ce serait parce que l’on n’est pas assez motivé ou « positif ». Sa critique ne consiste donc pas à refuser toute recherche de bien-être, mais à dénoncer les méthodes qui imposent une conformité sous l’apparence de l’épanouissement. &lt;/p&gt; &lt;p&gt; Sa philosophie peut être caractérisée par trois exigences : l’esprit critique, le discernement et l’authenticité. Elle invite chacun à se méfier des formules toutes faites, à ne pas confondre adaptation sociale et vérité personnelle, et à rechercher un rapport plus lucide à soi-même et aux autres. Son originalité tient ainsi à la rencontre entre la tradition philosophique — notamment Socrate, Aristote ou Kant — et les problèmes très concrets de la vie professionnelle et sociale. &lt;/p&gt;  &lt;audio controls title="Un nouvel ordre identitaire avec Julia Dez Funès par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.11.2022-ITEMA_23186791-2022F30378S0309-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
-        </is>
-      </c>
-      <c r="F80" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IbHSzVzGVIM</t>
-        </is>
-      </c>
-      <c r="G80" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Julia de Funès, libre de douter" par Public Sénat</t>
-        </is>
-      </c>
-      <c r="H80" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/jdfunes-mini.webp</t>
         </is>
       </c>
       <c r="I80" s="36" t="n"/>
       <c r="J80" s="27" t="inlineStr">
         <is>
+          <t>politique ; ethique</t>
+        </is>
+      </c>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Tiers-mondisme</t>
+        </is>
+      </c>
+      <c r="L80" s="27" t="inlineStr">
+        <is>
+          <t>philosophe française spécialiste de la pensée de Bergson et des études postcoloniales.</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud;femme</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decolonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="395.5" customHeight="1" s="28">
+      <c r="A81" s="34" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B81" s="34" t="n"/>
+      <c r="C81" s="34" t="n">
+        <v>1979</v>
+      </c>
+      <c r="D81" s="27" t="inlineStr">
+        <is>
+          <t>Julia DE-FUNÈS</t>
+        </is>
+      </c>
+      <c r="E81" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julia_de_Fun%C3%A8s"  title=" Wikipedia"&gt;Julia DE-FUNÈS&lt;/a&gt; est une philosophe, essayiste et conférencière française, également spécialiste des ressources humaines et du monde de l’entreprise. Après avoir travaillé plusieurs années comme chasseuse de têtes, elle a créé en 2010 un cabinet de conseil mobilisant la philosophie dans les organisations. Elle a ensuite soutenu en 2017 une thèse consacrée au passage de l’identité personnelle à l’authenticité, à travers les notions de représentation et de mimétisme. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=OaDbpC3azdQ"  title="julia de Funès, philosophe par 21 News"&gt; Sa démarche consiste &lt;/a&gt;  à faire sortir la philosophie du cadre purement universitaire pour la confronter aux situations ordinaires : travail, management, bonheur, relations professionnelles ou développement personnel. Elle considère la philosophie comme un exercice de mise à distance, destiné à interroger les évidences et à examiner le sens réel des mots que nous employons. Dans cette perspective, philosopher revient à ne pas accepter mécaniquement les discours dominants, les slogans ou les habitudes de pensée. &lt;/p&gt; &lt;p&gt; Une de ses principales critiques vise l’entreprise contemporaine et la multiplication des procédures, des indicateurs et des discours managériaux. Dans Socrate au pays des process ou La Vie de bureau, elle dénonce ce qu’elle perçoit comme une perte de sens : les salariés peuvent être soumis à des injonctions contradictoires et à un langage abstrait qui transforme parfois l’être humain en simple fonction. Elle oppose à cette logique la nécessité de retrouver du jugement, de l’autonomie et une réflexion véritable sur les finalités du travail. &lt;/p&gt; &lt;p&gt; Elle critique également le développement personnel lorsqu’il promet le bonheur, la réussite ou la confiance en soi au moyen de recettes standardisées. Dans &lt;a href="https://www.youtube.com/watch?v=dV5r46P6yUU"  title="le développement personnel est la plus grosse arnaque par Clique Tv"&gt;Le Développement (im)personnel&lt;/a&gt;, elle soutient que certaines formes de psychologie positive peuvent transformer des problèmes sociaux ou professionnels en responsabilités purement individuelles : si l’on échoue, ce serait parce que l’on n’est pas assez motivé ou « positif ». Sa critique ne consiste donc pas à refuser toute recherche de bien-être, mais à dénoncer les méthodes qui imposent une conformité sous l’apparence de l’épanouissement. &lt;/p&gt; &lt;p&gt; Sa philosophie peut être caractérisée par trois exigences : l’esprit critique, le discernement et l’authenticité. Elle invite chacun à se méfier des formules toutes faites, à ne pas confondre adaptation sociale et vérité personnelle, et à rechercher un rapport plus lucide à soi-même et aux autres. Son originalité tient ainsi à la rencontre entre la tradition philosophique — notamment Socrate, Aristote ou Kant — et les problèmes très concrets de la vie professionnelle et sociale. &lt;/p&gt;  &lt;audio controls title="Un nouvel ordre identitaire avec Julia Dez Funès par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/23134-05.11.2022-ITEMA_23186791-2022F30378S0309-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+        </is>
+      </c>
+      <c r="F81" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IbHSzVzGVIM</t>
+        </is>
+      </c>
+      <c r="G81" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Julia de Funès, libre de douter" par Public Sénat</t>
+        </is>
+      </c>
+      <c r="H81" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/jdfunes-mini.webp</t>
+        </is>
+      </c>
+      <c r="I81" s="36" t="n"/>
+      <c r="J81" s="27" t="inlineStr">
+        <is>
           <t>ethique</t>
         </is>
       </c>
-      <c r="K80" s="27" t="inlineStr">
+      <c r="K81" s="27" t="inlineStr">
         <is>
           <t>Humanisme</t>
         </is>
       </c>
-      <c r="L80" s="42" t="inlineStr">
+      <c r="L81" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe, essayiste et conférencière française, spécialiste des ressources humaines et du monde de l’entreprise.</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t xml:space="preserve">critique</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="145.5" customHeight="1" s="28">
-      <c r="A81" s="34" t="n">
+    <row r="82" ht="145.5" customHeight="1" s="28">
+      <c r="A82" s="34" t="n">
         <v>1981</v>
       </c>
-      <c r="B81" s="34" t="n"/>
-      <c r="C81" s="34" t="inlineStr">
+      <c r="B82" s="34" t="n"/>
+      <c r="C82" s="34" t="inlineStr">
         <is>
           <t>1981</t>
         </is>
       </c>
-      <c r="D81" s="35" t="inlineStr">
+      <c r="D82" s="35" t="inlineStr">
         <is>
           <t>Tristan GARCIA</t>
         </is>
       </c>
-      <c r="E81" s="37" t="inlineStr">
+      <c r="E82" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tristan_Garcia" title=" Wikipedia"&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. Ancien élève de l’École normale supérieure, il enseigne la philosophie à l’université Jean-Moulin-Lyon-3. &lt;/p&gt; &lt;p&gt; Son œuvre majeure "Forme et objet. Un traité des choses" paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie "plate" qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans "Nous" ou "La Vie intense" paru en 2016, il explore l’appartenance à des collectifs variables "nous humains", "nous animaux" et critique l’obsession moderne pour  &lt;a href="https://www.youtube.com/watch?v=JTLVzryyyEg" title="Tristan Garcia, INTENSITÉ par abc penser"&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. Son roman &lt;em&gt;7&lt;/em&gt; reçoit en 2016 le prix du Livre Inter. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (&lt;em&gt;La Meilleure Part des hommes&lt;/em&gt;, sur les années sida, prix de Flore 2008) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href="https://www.youtube.com/watch?v=K_wxi5xTYz8" title="Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace"&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; 
    &lt;audio controls title="Tristan Garcia, "La vie intense : une obsession moderne" par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
  </t>
         </is>
       </c>
-      <c r="F81" s="34" t="inlineStr">
+      <c r="F82" s="34" t="inlineStr">
         <is>
           <t>CNhfmBxUwdc</t>
         </is>
       </c>
-      <c r="G81" s="36" t="inlineStr">
+      <c r="G82" s="36" t="inlineStr">
         <is>
           <t>"Ecriture inclusive : cinq minutes qui élèvent le débat, par Tristan Garcia" par Le nouvel Obs</t>
         </is>
       </c>
-      <c r="H81" s="36" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/garcia-mini.webp</t>
         </is>
       </c>
-      <c r="I81" s="36" t="n"/>
-      <c r="J81" s="27" t="inlineStr">
+      <c r="I82" s="36" t="n"/>
+      <c r="J82" s="27" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="K81" s="27" t="inlineStr">
+      <c r="K82" s="27" t="inlineStr">
         <is>
           <t>Nouveau réalisme</t>
         </is>
       </c>
-      <c r="L81" s="27" t="inlineStr">
+      <c r="L82" s="27" t="inlineStr">
         <is>
           <t>philosophe &amp;amp; romancier français figure montante d'une métaphysique contemporaine ambitieuse.</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t xml:space="preserve">reel</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="202.5" customHeight="1" s="28">
-      <c r="A82" s="34" t="n">
+    <row r="83" ht="202.5" customHeight="1" s="28">
+      <c r="A83" s="34" t="n">
         <v>1982</v>
       </c>
-      <c r="B82" s="34" t="n"/>
-      <c r="C82" s="34" t="inlineStr">
+      <c r="B83" s="34" t="n"/>
+      <c r="C83" s="34" t="inlineStr">
         <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="D82" s="35" t="inlineStr">
+      <c r="D83" s="35" t="inlineStr">
         <is>
           <t>Gaspard KOENIG</t>
         </is>
       </c>
-      <c r="E82" s="36" t="inlineStr">
+      <c r="E83" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gaspard_Koenig" title=" Wikipedia"&gt;Gaspard KOENIG&lt;/a&gt;  est un philosophe français connu pour défendre un libéralisme classique moderne axé sur la liberté individuelle et la réduction des normes administratives. Il étudie initialement Gilles Deleuze avant de découvrir le libéralisme lors d'un séjour à l'université Columbia à New York. Il enseigne comme ATER à Lille-III et travaille comme plume pour Christine Lagarde au ministère de l'Économie, puis à la BERD à Londres. &lt;/p&gt; &lt;p&gt; Fondateur en 2013 du &lt;a href="https://www.youtube.com/watch?v=XmM1deHK-Eo"  title="Génération libre : le think tank, "start-up intellectuelle" par BFM Business"&gt;"think tank Génération Libre", &lt;/a&gt; classé parmi les meilleurs think tanks européens, il en est président et promeut des idées comme le revenu universel (LIBER), la légalisation du cannabis, la propriété des données personnelles et la subsidiarité ascendante. En 2021, il lance le mouvement politique Simple pour  &lt;a href="https://www.youtube.com/watch?v=r6p0dZlUoLQ"  title="Gaspard Koenig : Simplifions radicalement notre administration ! par Contribuables Associés"&gt;diviser par cent les normes &lt;/a&gt; réglementaires ; candidat à la présidentielle 2022, il récolte 107 parrainages. Il se présente aussi aux législatives partielles en 2018. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.gaspardkoenig.com/" title="gaspard koenig - site personnel"&gt;Auteur  d'une quinzaine d'essais &lt;/a&gt; et romans, dont Humus (finaliste Goncourt 2023, prix Interallié), Agrophilosophie (2024) et Time to Philo, il redéfinit la liberté comme "pouvoir sur soi", inspiré par Montaigne, les stoïciens et David Graeber. Ses réflexions touchent l'IA, l'agroécologie, l'éthique et l'économie. Dans &lt;em&gt;La Fin de l’individu&lt;/em&gt; (2019) il s’inquiète de voir les algorithmes décider à notre place et réduire notre capacité de choisir. Avec &lt;em&gt;Humus&lt;/em&gt;, roman sur deux jeunes agronomes et la vie des vers de terre, puis &lt;em&gt;Agrophilosophie&lt;/em&gt;, il s’intéresse aux sols et à l’agriculture, et cherche à concilier la liberté individuelle avec le respect des équilibres naturels. &lt;/p&gt; 
   &lt;audio controls title="Gaspard Koenig, un philosophe en liberté par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/16740-30.09.2023-ITEMA_23504378-2023C49326S0273-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   
 </t>
         </is>
       </c>
-      <c r="F82" s="34" t="inlineStr">
+      <c r="F83" s="34" t="inlineStr">
         <is>
           <t>4BW1Ch1Dw6I</t>
         </is>
       </c>
-      <c r="G82" s="36" t="inlineStr">
+      <c r="G83" s="36" t="inlineStr">
         <is>
           <t>Gaspard Koenig : "Les panthéonisations sont une façon pour l'État de nationaliser les talents" par France Inter</t>
         </is>
       </c>
-      <c r="H82" s="36" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/koenig-mini.webp</t>
-        </is>
-      </c>
-      <c r="I82" s="36" t="n"/>
-      <c r="J82" s="27" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="K82" s="27" t="inlineStr">
-        <is>
-          <t>Libéralisme</t>
-        </is>
-      </c>
-      <c r="L82" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français défenseur du libéralisme classique moderne axé sur la liberté individuelle.</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="124.5" customHeight="1" s="28">
-      <c r="A83" s="34" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B83" s="34" t="n"/>
-      <c r="C83" s="34" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="D83" s="35" t="inlineStr">
-        <is>
-          <t>Pierre CHARBONNIER</t>
-        </is>
-      </c>
-      <c r="E83" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Charbonnier_(philosophe)"  title=" Wikipedia"&gt;Pierre CHARBONNIER&lt;/a&gt; est un philosophe français spécialiste de philosophie politique et de philosophie de l'environnement et de l'écologie. &lt;a href="https://laviedesidees.fr/_Charbonnier-Pierre_" title="ÉCOPO - Pierre Charbonnier par College de France"&gt;Ses travaux&lt;/a&gt; portent sur l'histoire des sciences sociales et de la pensée politique, en particulier sur la manière dont elles abordent la relation entre nature et société et s'intéresse aux systèmes de pensée et d'encadrement du milieu naturel, aux crises politiques et écologiques, et à la place de l'écologie dans le processus de démocratisation. &lt;/p&gt; &lt;p&gt; Son livre &lt;a href="https://www.youtube.com/watch?v=6s54KzHUmRU" title="ÉCOPO - Pierre Charbonnier, Abondance et liberté par Game Of Hearth"&gt;"Abondance et liberté"&lt;/a&gt; : Une histoire environnementale des idées politiques a rencontré un certain succès médiatique et explore l'histoire des idées politiques à travers le prisme des enjeux environnementaux. Il y analyse comment nos conceptions de la liberté et de l'abondance sont historiquement liées à notre rapport à la nature. &lt;/p&gt; &lt;p&gt; Plus récent, son ouvrage   &lt;a href="https://www.youtube.com/watch?v=HslDCTZNq2M"  title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt;"Vers l'écologie de guerre"&lt;/a&gt; : Une histoire environnementale de la paix, il propose une relecture de l'histoire des relations internationales et des conflits à travers le prisme des enjeux écologiques. Chercheur au CNRS, rattaché à Sciences Po, il montre que la démocratie libérale moderne s’est construite sur une promesse d’abondance rendue possible par l’exploitation de la terre, puis du charbon et du pétrole. La crise climatique oblige donc à repenser ce que nous entendons par liberté, sans renoncer à l’idéal d’émancipation. Il invite ainsi à faire de l’écologie une question centrale de la philosophie politique. &lt;/p&gt;  &lt;audio controls title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25343-29.08.2024-ITEMA_23842702-2024C53458S0242-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F83" s="34" t="inlineStr">
-        <is>
-          <t>GGLZjIzYDnE</t>
-        </is>
-      </c>
-      <c r="G83" s="36" t="inlineStr">
-        <is>
-          <t>"Le philosophe Pierre Charbonnier: "Beaucoup de choses qui nous semblaient aller de soi ne vont plus"" par France Inter</t>
-        </is>
-      </c>
-      <c r="H83" s="36" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/charbonnier-mini.webp</t>
         </is>
       </c>
       <c r="I83" s="36" t="n"/>
       <c r="J83" s="27" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="K83" s="27" t="inlineStr">
         <is>
-          <t>Ecologisme</t>
+          <t>Libéralisme</t>
         </is>
       </c>
       <c r="L83" s="27" t="inlineStr">
         <is>
-          <t>philosophe français principalement orienté sur l'environnement.</t>
+          <t>philosophe français défenseur du libéralisme classique moderne axé sur la liberté individuelle.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -5902,11 +5901,11 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecologie ; justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="167.25" customHeight="1" s="28">
+          <t xml:space="preserve">justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="124.5" customHeight="1" s="28">
       <c r="A84" s="34" t="n">
         <v>1983</v>
       </c>
@@ -5918,88 +5917,90 @@
       </c>
       <c r="D84" s="35" t="inlineStr">
         <is>
+          <t>Pierre CHARBONNIER</t>
+        </is>
+      </c>
+      <c r="E84" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Charbonnier_(philosophe)"  title=" Wikipedia"&gt;Pierre CHARBONNIER&lt;/a&gt; est un philosophe français spécialiste de philosophie politique et de philosophie de l'environnement et de l'écologie. &lt;a href="https://laviedesidees.fr/_Charbonnier-Pierre_" title="ÉCOPO - Pierre Charbonnier par College de France"&gt;Ses travaux&lt;/a&gt; portent sur l'histoire des sciences sociales et de la pensée politique, en particulier sur la manière dont elles abordent la relation entre nature et société et s'intéresse aux systèmes de pensée et d'encadrement du milieu naturel, aux crises politiques et écologiques, et à la place de l'écologie dans le processus de démocratisation. &lt;/p&gt; &lt;p&gt; Son livre &lt;a href="https://www.youtube.com/watch?v=6s54KzHUmRU" title="ÉCOPO - Pierre Charbonnier, Abondance et liberté par Game Of Hearth"&gt;"Abondance et liberté"&lt;/a&gt; : Une histoire environnementale des idées politiques a rencontré un certain succès médiatique et explore l'histoire des idées politiques à travers le prisme des enjeux environnementaux. Il y analyse comment nos conceptions de la liberté et de l'abondance sont historiquement liées à notre rapport à la nature. &lt;/p&gt; &lt;p&gt; Plus récent, son ouvrage   &lt;a href="https://www.youtube.com/watch?v=HslDCTZNq2M"  title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt;"Vers l'écologie de guerre"&lt;/a&gt; : Une histoire environnementale de la paix, il propose une relecture de l'histoire des relations internationales et des conflits à travers le prisme des enjeux écologiques. Chercheur au CNRS, rattaché à Sciences Po, il montre que la démocratie libérale moderne s’est construite sur une promesse d’abondance rendue possible par l’exploitation de la terre, puis du charbon et du pétrole. La crise climatique oblige donc à repenser ce que nous entendons par liberté, sans renoncer à l’idéal d’émancipation. Il invite ainsi à faire de l’écologie une question centrale de la philosophie politique. &lt;/p&gt;  &lt;audio controls title="L'écologie de guerre selon Pierre Charbonnier par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/25343-29.08.2024-ITEMA_23842702-2024C53458S0242-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F84" s="34" t="inlineStr">
+        <is>
+          <t>GGLZjIzYDnE</t>
+        </is>
+      </c>
+      <c r="G84" s="36" t="inlineStr">
+        <is>
+          <t>"Le philosophe Pierre Charbonnier: "Beaucoup de choses qui nous semblaient aller de soi ne vont plus"" par France Inter</t>
+        </is>
+      </c>
+      <c r="H84" s="36" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/charbonnier-mini.webp</t>
+        </is>
+      </c>
+      <c r="I84" s="36" t="n"/>
+      <c r="J84" s="27" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>Ecologisme</t>
+        </is>
+      </c>
+      <c r="L84" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français principalement orienté sur l'environnement.</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie ; justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="167.25" customHeight="1" s="28">
+      <c r="A85" s="34" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B85" s="34" t="n"/>
+      <c r="C85" s="34" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="D85" s="35" t="inlineStr">
+        <is>
           <t>Baptiste MORIZOT</t>
         </is>
       </c>
-      <c r="E84" s="38" t="inlineStr">
+      <c r="E85" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baptiste_Morizot"  title=" Wikipedia"&gt;Baptiste MORIZOT&lt;/a&gt;  est un philosophe français,  maître de conférences à l'université d'Aix-Marseille, dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle. Son approche se distingue par une pratique de terrain ancrée dans l'expérience, notamment le pistage des grands prédateurs comme les loups, ce qui lui permet de nourrir sa pensée philosophique par une observation directe et sensible du vivant.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve l'idée que la crise écologique contemporaine est avant tout une « crise de la sensibilité » et de nos relations avec le reste du monde vivant. Il soutient que la pensée moderne, marquée par un dualisme qui sépare strictement l'humain de la nature, nous a &lt;a href="https://www.youtube.com/watch?v=bAnXnPnnHCk" title="Baptiste Morizot, meme penseur on est un animal par France Inter"&gt;rendus aveugles et sourds &lt;/a&gt; aux autres espèces, qu'il préfère considérer comme d'autres « manières d'être vivant » plutôt que comme des êtres inférieurs. &lt;/p&gt; &lt;p&gt; Il propose ainsi de remplacer le modèle classique de la « maîtrise de la nature » par une « diplomatie des interdépendances ». Cette approche invite les humains à se concevoir comme des partenaires au sein d'un réseau complexe d'interdépendances, où il s'agit de tisser des alliances concrètes, de prêter attention aux signaux émis par les autres espèces et d'apprendre à cohabiter avec elles dans un esprit de respect et de responsabilité partagée. &lt;/p&gt; &lt;p&gt; Son travail, qui mêle récit, enquête éthologique et essai théorique, cherche à réenchanter &lt;a href="https://www.youtube.com/watch?v=uQZcktq_W3E" title="Baptiste Morizot, remet l’humain à sa place par La Grande Librairie"&gt;notre rapport au monde &lt;/a&gt; en réactivant nos capacités d'attention et d'intelligence sensible. En invitant à une forme de sagesse pragmatique et ancrée, il s'efforce de refonder notre culture environnementale, non pas pour dominer ou sanctuariser la nature, mais pour s'ajuster avec humilité à la diversité des formes de vie qui partagent la Terre avec nous. &lt;/p&gt;  &lt;audio controls title="Liberté, dignité, habitalité avec baptiste MORIZOT par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/18558-25.04.2026-ITEMA_24488881-2026F30378S0115-NET_MFI_D6CADDF4-ADD5-4D3F-AA1D-625272E9CD3C-22-b98aedea0426383b486dc3819cb77a8e.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F84" s="34" t="inlineStr">
+      <c r="F85" s="34" t="inlineStr">
         <is>
           <t>k8yRIzRzKPw</t>
         </is>
       </c>
-      <c r="G84" s="36" t="inlineStr">
+      <c r="G85" s="36" t="inlineStr">
         <is>
           <t>"Masterclass philosophique sur le vivant et la nature" par Ethique et tac</t>
         </is>
       </c>
-      <c r="H84" s="36" t="inlineStr">
+      <c r="H85" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bmorizot-mini.webp</t>
-        </is>
-      </c>
-      <c r="I84" s="36" t="n"/>
-      <c r="J84" s="27" t="inlineStr">
-        <is>
-          <t>ethique</t>
-        </is>
-      </c>
-      <c r="K84" s="27" t="inlineStr">
-        <is>
-          <t>Ecologisme</t>
-        </is>
-      </c>
-      <c r="L84" s="27" t="inlineStr">
-        <is>
-          <t>philosophe français dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle.</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ecologie</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="237.75" customHeight="1" s="28">
-      <c r="A85" s="34" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B85" s="34" t="n"/>
-      <c r="C85" s="34" t="n">
-        <v>1985</v>
-      </c>
-      <c r="D85" s="35" t="inlineStr">
-        <is>
-          <t>Yann DALL-AGLIO</t>
-        </is>
-      </c>
-      <c r="E85" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;(Son année de naissance n’étant pas connu, il est positionné ici de façon approximative)&lt;/p&gt; &lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Yann_Dall%27Aglio" title=" Wikipedia"&gt;Yamm DALL-AGLIO&lt;/a&gt; est un philosophe et essayiste français, agrégé de philosophie, qui s’est fait connaître par une manière accessible, humoristique et volontiers provocatrice de traiter les problèmes existentiels contemporains. Il a notamment enseigné la philosophie et s’est adressé à un large public à travers ses livres, ses conférences et une intervention TEDx consacrée à l’amour moderne. Son œuvre se situe ainsi à la croisée de la philosophie, de la satire sociale et de la vulgarisation. &lt;/p&gt; &lt;p&gt; Dans Une Rolex à 50 ans : A-t-on le droit de rater sa vie ?, il part d’une formule célèbre de Jacques Séguéla pour interroger l’idée selon laquelle  &lt;a href="https://www.youtube.com/watch?v=nxjf1wb5Rz4" title="reussir sa vie par Vers soi"&gt;la réussite se mesurerait &lt;/a&gt;  à la richesse, au prestige ou aux signes extérieurs de succès. Il montre que « réussir sa vie » n’a rien d’une norme objective : chacun donne un contenu différent au bonheur, à l’accomplissement ou à la réussite. La possession d’une Rolex devient alors le symbole d’une société qui confond la valeur d’une existence avec sa visibilité sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie défend donc le droit à une « vie de traviole », c’est-à-dire une existence qui ne suit pas nécessairement les modèles dominants de la performance, de la productivité et de la consommation. Il ne s’agit pas de glorifier l’échec ou la passivité, mais de refuser l’obligation de transformer sa vie en projet rentable et parfaitement maîtrisé. Dans cette perspective, l’erreur, l’errance, la simplicité et même certaines impasses peuvent avoir une valeur existentielle : une vie n’est pas ratée simplement parce qu’elle ne ressemble pas aux critères sociaux de la réussite. &lt;/p&gt; &lt;p&gt; Dans JTM. L’amour est-il has been ?, il applique cette réflexion au domaine amoureux. Il définit l’amour comme le désir d’être désiré et analyse les difficultés que l’individualisme, la logique de la performance, les rencontres virtuelles et les réseaux sociaux introduisent dans les relations. Puisque chacun cherche à être reconnu comme désirable, la relation amoureuse peut prendre la forme d’un véritable « marché des désirs », où l’on négocie sans cesse sa valeur aux yeux d’autrui. Il ne conclut toutefois pas à la disparition de l’amour : il plaide plutôt pour la tendresse, l’humour, la vulnérabilité et le droit à la maladresse. &lt;/p&gt; &lt;p&gt; Son style est inséparable de sa démarche philosophique : il préfère l’ironie au ton professoral et les exemples ordinaires aux abstractions isolées. Dans Vies, sentences et doctrines des sages imaginaires, il invente même de faux penseurs pour parodier les biographies et les doctrines philosophiques, tout en proposant une réflexion amusée sur notre besoin de fabriquer des autorités et des systèmes. Sa philosophie peut ainsi être comprise comme un scepticisme bienveillant : elle se méfie des recettes du bonheur, des normes de réussite et des discours trop sérieux, mais elle conserve une confiance dans l’amour, la liberté et la possibilité de vivre autrement. &lt;/p&gt;  &lt;audio controls title="L'amour est il ‘has been’?  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14034-12.02.2012-ITEMA_20344223-2012F4034S0043-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
-        </is>
-      </c>
-      <c r="F85" s="34" t="inlineStr">
-        <is>
-          <t>dJgiYBdD2VA</t>
-        </is>
-      </c>
-      <c r="G85" s="36" t="inlineStr">
-        <is>
-          <t>L’amour – vous le faites mal par TED</t>
-        </is>
-      </c>
-      <c r="H85" s="37" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/ydallaglio-mini.webp</t>
         </is>
       </c>
       <c r="I85" s="36" t="n"/>
@@ -6010,205 +6011,214 @@
       </c>
       <c r="K85" s="27" t="inlineStr">
         <is>
+          <t>Ecologisme</t>
+        </is>
+      </c>
+      <c r="L85" s="27" t="inlineStr">
+        <is>
+          <t>philosophe français dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle.</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ecologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="237.75" customHeight="1" s="28">
+      <c r="A86" s="34" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B86" s="34" t="n"/>
+      <c r="C86" s="34" t="n">
+        <v>1985</v>
+      </c>
+      <c r="D86" s="35" t="inlineStr">
+        <is>
+          <t>Yann DALL-AGLIO</t>
+        </is>
+      </c>
+      <c r="E86" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;(Son année de naissance n’étant pas connu, il est positionné ici de façon approximative)&lt;/p&gt; &lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Yann_Dall%27Aglio" title=" Wikipedia"&gt;Yamm DALL-AGLIO&lt;/a&gt; est un philosophe et essayiste français, agrégé de philosophie, qui s’est fait connaître par une manière accessible, humoristique et volontiers provocatrice de traiter les problèmes existentiels contemporains. Il a notamment enseigné la philosophie et s’est adressé à un large public à travers ses livres, ses conférences et une intervention TEDx consacrée à l’amour moderne. Son œuvre se situe ainsi à la croisée de la philosophie, de la satire sociale et de la vulgarisation. &lt;/p&gt; &lt;p&gt; Dans Une Rolex à 50 ans : A-t-on le droit de rater sa vie ?, il part d’une formule célèbre de Jacques Séguéla pour interroger l’idée selon laquelle  &lt;a href="https://www.youtube.com/watch?v=nxjf1wb5Rz4" title="reussir sa vie par Vers soi"&gt;la réussite se mesurerait &lt;/a&gt;  à la richesse, au prestige ou aux signes extérieurs de succès. Il montre que « réussir sa vie » n’a rien d’une norme objective : chacun donne un contenu différent au bonheur, à l’accomplissement ou à la réussite. La possession d’une Rolex devient alors le symbole d’une société qui confond la valeur d’une existence avec sa visibilité sociale. &lt;/p&gt; &lt;p&gt; Sa philosophie défend donc le droit à une « vie de traviole », c’est-à-dire une existence qui ne suit pas nécessairement les modèles dominants de la performance, de la productivité et de la consommation. Il ne s’agit pas de glorifier l’échec ou la passivité, mais de refuser l’obligation de transformer sa vie en projet rentable et parfaitement maîtrisé. Dans cette perspective, l’erreur, l’errance, la simplicité et même certaines impasses peuvent avoir une valeur existentielle : une vie n’est pas ratée simplement parce qu’elle ne ressemble pas aux critères sociaux de la réussite. &lt;/p&gt; &lt;p&gt; Dans JTM. L’amour est-il has been ?, il applique cette réflexion au domaine amoureux. Il définit l’amour comme le désir d’être désiré et analyse les difficultés que l’individualisme, la logique de la performance, les rencontres virtuelles et les réseaux sociaux introduisent dans les relations. Puisque chacun cherche à être reconnu comme désirable, la relation amoureuse peut prendre la forme d’un véritable « marché des désirs », où l’on négocie sans cesse sa valeur aux yeux d’autrui. Il ne conclut toutefois pas à la disparition de l’amour : il plaide plutôt pour la tendresse, l’humour, la vulnérabilité et le droit à la maladresse. &lt;/p&gt; &lt;p&gt; Son style est inséparable de sa démarche philosophique : il préfère l’ironie au ton professoral et les exemples ordinaires aux abstractions isolées. Dans Vies, sentences et doctrines des sages imaginaires, il invente même de faux penseurs pour parodier les biographies et les doctrines philosophiques, tout en proposant une réflexion amusée sur notre besoin de fabriquer des autorités et des systèmes. Sa philosophie peut ainsi être comprise comme un scepticisme bienveillant : elle se méfie des recettes du bonheur, des normes de réussite et des discours trop sérieux, mais elle conserve une confiance dans l’amour, la liberté et la possibilité de vivre autrement. &lt;/p&gt;  &lt;audio controls title="L'amour est il ‘has been’?  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14034-12.02.2012-ITEMA_20344223-2012F4034S0043-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
+      </c>
+      <c r="F86" s="34" t="inlineStr">
+        <is>
+          <t>dJgiYBdD2VA</t>
+        </is>
+      </c>
+      <c r="G86" s="36" t="inlineStr">
+        <is>
+          <t>L’amour – vous le faites mal par TED</t>
+        </is>
+      </c>
+      <c r="H86" s="37" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/ydallaglio-mini.webp</t>
+        </is>
+      </c>
+      <c r="I86" s="36" t="n"/>
+      <c r="J86" s="27" t="inlineStr">
+        <is>
+          <t>ethique</t>
+        </is>
+      </c>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
           <t>Existentialisme</t>
         </is>
       </c>
-      <c r="L85" s="42" t="inlineStr">
+      <c r="L86" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe et essayiste français, drôle et provocateur, qui traite des problèmes existentiels contemporains.</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t xml:space="preserve">sens</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="115.5" customHeight="1" s="28">
-      <c r="A86" s="34" t="n">
+    <row r="87" ht="115.5" customHeight="1" s="28">
+      <c r="A87" s="34" t="n">
         <v>1987</v>
       </c>
-      <c r="B86" s="34" t="n"/>
-      <c r="C86" s="34" t="inlineStr">
+      <c r="B87" s="34" t="n"/>
+      <c r="C87" s="34" t="inlineStr">
         <is>
           <t>1987</t>
         </is>
       </c>
-      <c r="D86" s="35" t="inlineStr">
+      <c r="D87" s="35" t="inlineStr">
         <is>
           <t>Norman AJARI</t>
         </is>
       </c>
-      <c r="E86" s="37" t="inlineStr">
+      <c r="E87" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Norman_Ajari"  title=" Wikipedia"&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href="https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari"  title="Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse"&gt;"études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href="https://www.youtube.com/watch?v=IMUBi9oi2WM" title="Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche"&gt;"colonialité de l’être" &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href="https://www.youtube.com/watch?v=ECSmpOXY8kg" title="NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS"&gt;"La Dignité ou la mort", &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de "philosophe militant" : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. Né en 1987, formé à l’université de Toulouse, il enseigne aux États-Unis, à l’université Villanova. Dans &lt;em&gt;La Dignité ou la mort. Éthique et politique de la race&lt;/em&gt; (2019), il soutient que l’expérience noire moderne, de l’esclavage aux violences policières, ne peut être comprise par les catégories habituelles de la philosophie morale, et qu’elle appelle une éthique de la dignité face à la mort sociale. Il a aussi fait connaître en France les débats du courant « afro-pessimiste » américain. &lt;/p&gt; &lt;audio controls title="où commence et où finit le racisme? par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F86" s="34" t="inlineStr">
+      <c r="F87" s="34" t="inlineStr">
         <is>
           <t>8xfdl8Hmbik</t>
         </is>
       </c>
-      <c r="G86" s="36" t="inlineStr">
+      <c r="G87" s="36" t="inlineStr">
         <is>
           <t>"Le racisme dans la loi et dans les faits - Norman Ajari" par A gauche</t>
         </is>
       </c>
-      <c r="H86" s="36" t="inlineStr">
+      <c r="H87" s="36" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/ajari-mini.webp</t>
         </is>
       </c>
-      <c r="I86" s="36" t="n"/>
-      <c r="J86" s="27" t="inlineStr">
+      <c r="I87" s="36" t="n"/>
+      <c r="J87" s="27" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="K86" s="27" t="inlineStr">
+      <c r="K87" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiers-mondisme ; Pensée décoloniale</t>
         </is>
       </c>
-      <c r="L86" s="27" t="inlineStr">
+      <c r="L87" s="27" t="inlineStr">
         <is>
           <t>philosophe franco-américain spécialiste des études noires francophones &amp;amp; décoloniales.</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t xml:space="preserve">decolonial</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="219.75" customHeight="1" s="28">
-      <c r="A87" s="26" t="n">
+    <row r="88" ht="219.75" customHeight="1" s="28">
+      <c r="A88" s="26" t="n">
         <v>1988</v>
       </c>
-      <c r="C87" s="26" t="n">
+      <c r="C88" s="26" t="n">
         <v>1988</v>
       </c>
-      <c r="D87" s="26" t="inlineStr">
+      <c r="D88" s="26" t="inlineStr">
         <is>
           <t>Marylin MAESO</t>
         </is>
       </c>
-      <c r="E87" s="43" t="inlineStr">
+      <c r="E88" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marylin_Maeso"  title=" Wikipedia"&gt;Marylin MAESO&lt;/a&gt; est une philosophe  et enseignante française, agrégée de philosophie et ancienne élève de l'École normale supérieure. Spécialiste reconnue de  &lt;a href="https://www.youtube.com/watch?v=UtgptKTW288" title="l’étranger de Camus, une philosophe de l’absurde par France Inter"&gt;l’œuvre d’Albert Camus, &lt;/a&gt; elle consacre une grande partie de ses recherches à la philosophie politique contemporaine, à la question de l’humanisme et aux dynamiques de la déshumanisation dans nos sociétés modernes. &lt;/p&gt;&lt;p&gt; Son travail intellectuel est profondément marqué par une lecture renouvelée de Camus, qu'elle mobilise pour analyser les enjeux éthiques de notre époque. Dans La Petite &lt;a href="https://www.youtube.com/watch?v=YQqfp9iA5ME" title="nous sommes nous habitués à l’inhumain par marianne"&gt;Fabrique de l'inhumain, &lt;/a&gt; elle s'appuie sur le roman La Peste pour explorer comment l'inhumanité s'insinue dans le quotidien, souvent de manière insidieuse, plutôt que par de grands événements spectaculaires. Elle cherche ainsi à éveiller la vigilance citoyenne face aux processus de banalisation du mal. &lt;/p&gt; &lt;p&gt; Parallèlement à ses recherches, Marylin Maeso défend une éthique du débat public fondée sur la nuance et le dialogue. Dans Les Conspirateurs du silence, elle critique les polémiques stériles et les clivages idéologiques qui empêchent la compréhension mutuelle, plaidant pour un exercice de la pensée qui permette de maintenir un lien social malgré les désaccords. Son engagement se traduit également par des actions concrètes, notamment à travers l'association Tête-à-texte, qu'elle a créée pour promouvoir la lecture et la réflexion comme leviers d'émancipation et de citoyenneté. &lt;/p&gt; &lt;p&gt;  Sa philosophie se veut une « philosophie de terrain » et de transmission, portée par un souci constant de réhabiliter l'humanisme face aux idéologies qui cloisonnent et déshumanisent. En privilégiant la lecture des textes classiques comme guides pour penser les crises actuelles, elle s'efforce de fournir aux citoyens des outils critiques pour naviguer dans un monde complexe tout en préservant leur capacité de jugement et d'empathie.  &lt;/p&gt;  &lt;audio controls title=" Camus, vivre malgré tout par France Culture"&gt; &lt;source  src="https://media.radiofrance-podcast.net/podcast09/10467-30.10.2023-ITEMA_23535378-2023C48904S0303-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;
 </t>
         </is>
       </c>
-      <c r="F87" s="26" t="inlineStr">
+      <c r="F88" s="26" t="inlineStr">
         <is>
           <t>6VIxXg4eTqw</t>
         </is>
       </c>
-      <c r="G87" s="27" t="inlineStr">
+      <c r="G88" s="27" t="inlineStr">
         <is>
           <t>Marylin Maeso : L ‘antisémitisme est une peste par France 24</t>
         </is>
       </c>
-      <c r="H87" s="27" t="inlineStr">
+      <c r="H88" s="27" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mmaeso-mini.webp</t>
         </is>
       </c>
-      <c r="J87" s="27" t="inlineStr">
+      <c r="J88" s="27" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="K87" s="27" t="inlineStr">
+      <c r="K88" s="27" t="inlineStr">
         <is>
           <t>Libéralisme</t>
         </is>
       </c>
-      <c r="L87" s="27" t="inlineStr">
+      <c r="L88" s="27" t="inlineStr">
         <is>
           <t>philosophe politique française, de l’humanisme aux dynamiques de la déshumanisation.</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">femme</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
         <is>
           <t xml:space="preserve">justice</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="219.75" customHeight="1" s="28">
-      <c r="A88" s="26">
-        <v>1950</v>
-      </c>
-      <c r="C88" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1950</t>
-        </is>
-      </c>
-      <c r="D88" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jean-Michel BESNIER</t>
-        </is>
-      </c>
-      <c r="E88" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean-Michel_Besnier" title=" Wikipedia"&gt;Jean-Michel BESNIER&lt;/a&gt; est un philosophe français. Né à Caen en 1950, agrégé de philosophie et docteur en sciences politiques, il enseigne à l’université de technologie de Compiègne de 1988 à 2001, puis à la Sorbonne, dont il est professeur émérite. Ses premiers livres portent sur l’histoire de la philosophie moderne et contemporaine, dont il publie une grande synthèse en 1993, et sur la figure de l’intellectuel, partagé entre la révolte et l’engagement, de Georges Bataille à Maurice Blanchot.&lt;/p&gt; &lt;p&gt;Il se consacre ensuite à l’impact des sciences et des techniques sur nos représentations et nos imaginaires. Dans &lt;em&gt;Demain les posthumains&lt;/em&gt; (2009), il analyse le &lt;a href="https://fr.wikipedia.org/wiki/Transhumanisme" title=" Wikipedia"&gt;transhumanisme&lt;/a&gt;, qui promet de dépasser la condition humaine grâce aux biotechnologies, aux nanotechnologies et à l’intelligence artificielle. Il y voit moins un progrès qu’une fatigue d’être soi, un désir de se débarrasser de la fragilité, de l’incertitude et de la mort, qui sont pourtant ce qui fait notre humanité.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Homme simplifié&lt;/em&gt; (2012), il décrit le « syndrome de la touche étoile » : à force de dialoguer avec des machines, nous simplifions notre langage et nos relations pour nous adapter à elles, au lieu de les rendre plus humaines. Il débat publiquement avec les partisans du transhumanisme, comme Laurent Alexandre, avec qui il publie &lt;em&gt;Les robots font-ils l’amour ?&lt;/em&gt; (2016). Il a siégé dans plusieurs comités d’éthique de la recherche, notamment celui du CNRS, et dirigé le secteur « sciences et société » du ministère de la Recherche de 2008 à 2011.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H88" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/besnier-mini.webp</t>
-        </is>
-      </c>
-      <c r="J88" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="K88" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Humanisme</t>
-        </is>
-      </c>
-      <c r="L88" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe français des techniques, critique du transhumanisme et de « l’homme simplifié ».</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="O88"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">esprit-ia</t>
         </is>
       </c>
     </row>
@@ -6229,34 +6239,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" display="https://www.laphilo.fr/pho/rpdroit-mini.webp" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philippe_Descola&quot;   title=&quot; Wikipedia&quot;&gt;Philippe DESCOLA&lt;/a&gt; est un anthropologue français spécialiste de l’Amazonie, il a consacré une partie importante de ses recherches aux Achuar, un peuple &lt;a href=&quot;https://www.youtube.com/watch?v=d4VRtkRg-_o&quot;   title=&quot;Etudier les Jivaros Achaur d’amazonie par RFI&quot;&gt; jivaro de Haute-Amazonie.&lt;/a&gt;  Ses travaux cherchent principalement à comprendre comment les différentes sociétés établissent des relations avec les animaux, les plantes, les objets, les esprits et leur environnement. &lt;/p&gt; &lt;p&gt;  Son œuvre la plus connue est Par-delà nature et culture, publiée en 2005. Dans ce livre, il critique la séparation entre la nature et la culture, séparation qui lui paraît caractéristique de la pensée occidentale moderne. Selon lui, cette distinction n’est pas universelle : toutes les sociétés ne considèrent pas les humains comme appartenant à un domaine culturel séparé d’une nature extérieure et objective. Il propose donc d’étudier différentes manières de composer le monde et d’identifier les êtres qui l’habitent. &lt;/p&gt; &lt;p&gt; Pour effectuer cette comparaison, il distingue quatre grandes ontologies : l’animisme, le totémisme, l’analogisme et le naturalisme. L’animisme reconnaît une intériorité semblable aux humains et aux non-humains, mais des corps différents ; le naturalisme, caractéristique des sociétés occidentales modernes, suppose au contraire une même nature physique, mais une intériorité principalement attribuée aux humains. Le totémisme établit une continuité entre certains humains et certains non-humains, tandis que l’analogisme conçoit le monde comme une multiplicité d’êtres différents reliés par des correspondances. &lt;/p&gt; &lt;p&gt; Il ne présente pas ces quatre ontologies comme des étapes successives de l’évolution de l’humanité. Il ne dit pas non plus qu’une société entière correspond toujours parfaitement à un seul modèle. Il s’agit plutôt de grands schèmes permettant de comparer les façons dont les sociétés organisent leurs rapports avec les existants. Son originalité consiste donc à prendre au sérieux les conceptions non occidentales du monde, sans les interpréter automatiquement comme des croyances irrationnelles ou comme des versions incomplètes de la science moderne. &lt;/p&gt; &lt;p&gt; Sa pensée dépasse ainsi l’anthropologie proprement dite et rejoint la philosophie, l’écologie et la réflexion sur la crise environnementale. En montrant que &lt;a href=&quot;https://www.youtube.com/watch?v=fV2VqJhxuEE&quot;   title=&quot;la nature n’existe pas par blast, le souflle de l’info&quot;&gt; la nature n’est pas partout &lt;/a&gt; conçue comme une réalité extérieure exploitable, il invite à repenser la place de l’être humain dans le monde. Parmi ses autres ouvrages importants figurent La Nature domestique, Les Lances du crépuscule, L’Écologie des autres, La Composition des mondes et Les Formes du visible. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Nous sommes les hotes de la terre par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/26684-21.05.2026-ITEMA_24520316-2026F49008S0141-NET_MFI_7313D6B1-DF3B-42D0-AD80-7A8884697517-27-c968a5478f57024ca66b57343b59f5c9.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" display="https://www.laphilo.fr/pho/pdescola-mini.webp" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Jullien&quot;  title=&quot; Wikipedia&quot;&gt;François JULLIEN&lt;/a&gt; est un philosophe français, à la fois helléniste et sinologue, connu pour avoir construit un dialogue suivi entre la pensée européenne (surtout grecque) et la pensée chinoise. Il séjourne longuement en Asie (notamment à Tokyo) et soutient deux thèses, l’une sur l’écrivain chinois Lu Xun, l’autre sur l’interprétation poétique dans la tradition chinoise, ce qui fonde son approche de  &lt;a href=&quot;https://www.berlol.net/foire/fle98ju.htm&quot;  title=&quot;le détour d'un grec par la chine par berlol.net&quot;&gt;l’altérité culturelle.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Son projet central consiste à &quot;dépayser&quot; la pensée européenne en la confrontant à la Chine, afin de faire apparaître les présupposés cachés de la philosophie occidentale. Il insiste sur le fait que la rencontre des pensées ne doit pas viser l’exotisme, mais ouvrir un espace &quot;entre&quot; les cultures où se travaille un véritable commun, différent de l’uniforme qu’on confond trop vite avec l’universel. &lt;/p&gt; &lt;p&gt; Il travaille la notion d’&quot;écart&quot; : au lieu de chercher ce qui est semblable entre les cultures, il valorise leurs écarts comme lieu de réflexion et de création conceptuelle. De cet écart naît un &quot;entre&quot; : un espace de tension fécond où se construit le commun, sans effacer les différences. Il propose aussi un déplacement majeur : passer de la pensée de l’&quot;être&quot; à une pensée du &quot;vivre&quot;, plus attentive aux processus, aux transformations et à l’expérience concrète de l’existence. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme le &quot;Traité de l’efficacité&quot;, il oppose la manière occidentale d’agir à une logique chinoise de l’efficience, qui mise sur les tendances de la situation et les transformations continues. L’idée est moins de choisir un camp que de se servir de cet  &lt;a href=&quot;https://www.youtube.com/watch?v=RAgmn0mbUnQ&quot;  title=&quot;François Jullien, entrer dans la pensée chinoise par deodaTV&quot;&gt;écart Chine/Europe &lt;/a&gt; pour repenser nos pratiques de l’action, de la stratégie et de la décision dans le monde contemporain. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;L’art de « décoïncider » selon François Jullien  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13957-13.02.2021-ITEMA_22573157-2021C22785S0044.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Olivier_Abel&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Olivier ABEL&lt;/a&gt;  est un philosophe français spécialiste en éthique et philosophie morale, influencé par Paul Ricœur, Emmanuel Levinas et la tradition protestante. Il soutient en 1983 une thèse sur la rêverie chez Gaston Bachelard sous la direction de Ricœur, puis une habilitation en 2000 sur le temps éthique entre courage et pardon. &lt;/p&gt; &lt;p&gt; Créateur du Fonds Ricœur à Paris, doyen de la Faculté protestante de Paris, il a présidé la Commission d'éthique de la &lt;a href=&quot;https://www.lavie.fr/idees/histoire/olivier-abel-avec-le-catholicisme-leffort-fait-partie-du-chemin-pour-acceder-a-la-grace-100952.php&quot;  title=&quot;Olivier Abel : Avec le catholicisme, l’effort fait partie du chemin pour accéder à la grâce par la Vie&quot;&gt;Fédération protestante &lt;/a&gt;  de France et est membre de l'Académie de Nîmes depuis 2018. Il est aussi membre du Comité consultatif national d'éthique et contribue à des revues comme Esprit. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'éthique interrogative, le pardon, la conversation, l'Europe et les penseurs protestants comme Calvin ou Bayle. Parmi ses ouvrages : L’éthique interrogative (2000), Le pardon, briser la dette et l’oubli (1991), Le vertige de l’Europe (2019),  &lt;a href=&quot;https://www.youtube.com/watch?v=G1_ynk7E7LQ&quot; title=&quot;Olivier Abel, philosophe : Le signe de l’humiliation, c’est cette parole rentrée par FRANCE 24&quot;&gt;De l’humiliation &lt;/a&gt; (récent) et La naissance, qu’est-ce que ça change. Il explore la fugacité des liens humains et une critique du sujet délié. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Le témoin du vendredi : Olivier Abel, la civilisation européenne par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/11739-12.04.2019-ITEMA_22034063-2019F17009S0102-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pascal_Engel&quot;   title=&quot; Wikipedia&quot;&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent &quot;La Norme du vrai&quot; paru en 1989 sur la philosophie de la logique, &lt;a href=&quot;https://www.youtube.com/watch?v=ivsIBYFN6DI&quot; title=&quot;*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos&quot;&gt; &quot;Va savoir&quot;&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et &quot;Les vices du savoir&quot; en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il l défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Faut-il faire la morale aux intellectuels ?  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J.G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime un séminaire sur les décolonisations avec l'Université de Louvain-la-Neuve. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href=&quot;https://www.youtube.com/watch?v=vEQWmSo67B4&quot; style=&quot;color:#88A1E9&quot; title=&quot;Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches&quot;&gt;&quot;Ce sont d'autres gens&quot; &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la &quot;qualité de la vie&quot; sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href=&quot;https://www.youtube.com/watch?v=ZDpbSRrWIhU&quot; title=&quot;Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées&quot;&gt;&quot;autre monde&quot; &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Sandra_Laugier&quot; title=&quot; Wikipedia&quot;&gt;Sandra LAUGIER&lt;/a&gt;  est une philosophe française, professeure à l’université Paris 1 Panthéon-Sorbonne, membre de l’Institut Universitaire de France et spécialiste de philosophie du langage, de philosophie morale et de philosophie politique. Elle a aussi beaucoup travaillé sur Stanley Cavell, qu’elle a traduit en français, ainsi que sur Emerson, Thoreau et le perfectionnisme moral. &lt;/p&gt; &lt;p&gt; Sa philosophie accorde une place centrale à l’ordinaire : les gestes, les paroles, les liens quotidiens et les formes de vie concrètes sont pour elle des lieux essentiels de la pensée. Elle défend l’idée qu’il faut partir de l’expérience vécue plutôt que de grands systèmes abstraits, ce qui l’a conduite à développer une éthique du care, une réflexion sur le langage ordinaire et une attention aux formes discrètes de la vie commune. &lt;/p&gt; &lt;p&gt; Sur le plan politique, elle s’intéresse aux formes contemporaines de démocratie, à &lt;a href=&quot;https://www.youtube.com/watch?v=nlM-aPBIRdg&quot; title=&quot;Sandra Laugier : reconnaître nos dépendances par France Inter&quot;&gt;la désobéissance civile &lt;/a&gt; et aux mouvements horizontaux comme Nuit debout. Elle y voit une manière de repenser le politique à partir de l’expression des personnes, du souci du commun et de l’égalité effective des droits, plutôt que d’un modèle hiérarchique classique. Cette perspective la conduit à défendre une démocratie plus attentive aux voix singulières et aux pratiques collectives concrètes. &lt;/p&gt; &lt;p&gt; Elle a aussi élargi la philosophie à la culture populaire, notamment &lt;a href=&quot;https://www.youtube.com/watch?v=Rjd2XEvkqWc&quot; title=&quot;Sandra Laugier : nos vies en séries par librairie mollat&quot;&gt;aux séries télévisées, &lt;/a&gt; qu’elle considère comme un laboratoire d’expériences morales et politiques. Dans des ouvrages récents, elle montre que les séries peuvent aider à penser nos manières de vivre, nos attachements et nos conflits, en révélant des aspects très actuels de la sensibilité démocratique. &lt;/p&gt;  &lt;audio controls title=&quot;L’éthique animale avec Florence Burgat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" display="https://www.laphilo.fr/pho/slaugier-mini.webp" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon&quot;  title=&quot; Wikipedia&quot;&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href=&quot;https://www.youtube.com/watch?v=xOKttB1HgSk&quot;  title=&quot;Marc Crépon sur la violence  par France Inter &quot;&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href=&quot;https://www.youtube.com/watch?v=kwFC9MSSWcg&quot;  title=&quot;Marc Crépon : l’épreuve de la haine   par Librairie mollat &quot;&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; On peut dire qu’il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste.  &lt;/p&gt; &lt;audio controls title=&quot;Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Audi&quot;  title=&quot; Wikipedia&quot;&gt;Paul AUDI&lt;/a&gt;  est un philosophe et écrivain français né à Beyrouth, au Liban, et ancien élève de l'École normale supérieure. Agrégé de philosophie et docteur en philosophie, il a soutenu une thèse sur Jean-Jacques Rousseau publiée en 1997. Après avoir enseigné à l'université de Paris-XII, il s'est éloigné du champ universitaire pour s'orienter vers l'édition, et aujourd'hui il est professeur invité dans diverses institutions en France et à l'étranger. Il est auteur de plus d'une trentaine d'ouvrages et membre de l'équipe de recherches PHILéPOL à l'université Paris Descartes. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre principalement sur les relations entre l'éthique et l'esthétique en Occident durant les Temps Modernes. Son œuvre explore ces liens à travers des &lt;a href=&quot;https://www.youtube.com/watch?v=3GRhkvYGMs0&quot;  title=&quot;Paul Audi contrat social par le nouvel Obs&quot;&gt;lectures de Rousseau, &lt;/a&gt;  Nietzsche, Lacan, Schopenhauer et Georges Bataille. Il est considéré comme un philosophe atypique, commençant à être reconnu hors de France. Sa pensée conjugue la vie du corps et la création artistique, l'éthique et la passion, avec un souci d'ancrer la pensée dans la vie physique. &lt;/p&gt; &lt;p&gt; L'idée centrale de sa philosophie est que l'acte de création et le comportement éthique ne forment qu'un seul et même geste, qui naît de la vie elle-même et finalement l'excède. Il nomme cette fusion « esth/éthique », considérant que l'éthique et l'esthétique dans l'acte de créer se confondent ou sont le recto et verso d'une même « explication avec la vie ». Pour lui, créer revient à « s'expliquer avec la vie », à faire de l'énigme que nous sommes une bribe d'un discours neuf. &lt;/p&gt; &lt;p&gt; L'éthique, selon lui, consiste d'abord en un travail sur soi, où « c'est moi-même qui suis la tâche ». La philosophie ne s'accomplit qu'au sein d'un corps à corps avec ce qui, en nous-mêmes, nous dépasse — non pas le monde ou un dehors, mais ce qui nous situe sur le  &lt;a href=&quot;https://www.youtube.com/watch?v=FJsDRUR9bYQ&quot;  title=&quot;Paul Audi il faut le nuance par France Inter&quot;&gt;« plan de la vie », &lt;/a&gt; qui ne recouvre ni le champ social ni l'espace politique. Cette éthique de la création, qu'il dénomme « esthéthique », n'est pas un code de règles mais une posture existentielle, une manière de se situer face au monde. &lt;/p&gt; &lt;p&gt; Il  s'intéresse également aux conditions permettant à l'être humain d'accéder à sa propre humanité, et interroge profondément la question de l'identité. Dans son ouvrage Troublante identité (2022), il parle pour la première fois de lui-même et de ce qui le hante, résistant à toute réduction de son être à sa provenance libanaise. Il désire en finir avec les clôtures identitaires et trouve son émancipation dans une conception juive d'une identité ouverte, toujours à construire, guidée par un impératif de justice à venir. Son dernier essai Le Vrai du beau (2026) transforme la contemplation d'un tableau en expérience de vérité, éclaircissant ce qui se joue en nous face à un tableau. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;la verité picturale existe t’elle ?  Par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/26657-24.04.2026-ITEMA_24487813-2026F45096S0114-NET_MFI_F40118A5-5297-4676-86E9-2E9A248FB2F7-27-03023a67ff6f93208a5f302d7d3b8771.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" display="https://www.laphilo.fr/pho/paudi-mini.webp" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" display="https://www.laphilo.fr/pho/cmichon-mini.webp" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Corine_Pelluchon&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href=&quot;https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s&quot; title=&quot;NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco&quot;&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &#10;&lt;p&gt; - Manifeste animaliste. Politiser la cause animale ( 2017 )  - Éthique de la considération ( 2018) - Réparons le monde. Humains, animaux, nature (2020)  &#10; - Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &#10;&lt;p&gt; -   &lt;a href=&quot;https://www.youtube.com/watch?v=zpzzDqYhF-8&quot; title=&quot;Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat&quot;&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href=&quot;https://www.youtube.com/watch?v=tmk-UzN1j70&quot;  title=&quot;Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media&quot;&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title=&quot;Corine Pelluchon par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" display="https://www.laphilo.fr/pho/cfmetterie-mini.webp" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vincent_Delecroix&quot;  title=&quot; Wikipedia&quot;&gt;Vincent DELECROIX&lt;/a&gt;  est un philosophe français spécialiste de Kierkegaard et de la philosophie de la religion. Il enseigne à l’EPHE, où il travaille sur la vérité, la croyance et les liens entre religion et pensée contemporaine. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse d’abord à la manière dont la foi peut exister dans un monde moderne où les certitudes absolues se  &lt;a href=&quot;https://www.youtube.com/watch?v=2ZHOpP5GMwI&quot; title=&quot;Vincent DELECROIX,la nécessité d’apprendre par TV5 monde&quot;&gt;sont affaiblies. &lt;/a&gt; Il ne traite pas la religion comme un simple héritage figé, mais comme une expérience intérieure, fragile et exigeante.  &lt;/p&gt; &lt;p&gt; Un autre axe important chez lui est la révolte. À travers des livres comme Tombeau d’Achille et Non ! De l’esprit de révolte, il réfléchit à la colère, au refus et à la parole &lt;a href=&quot;https://www.youtube.com/watch?v=OiUgp6wLpCA&quot; title=&quot;Vincent DELECROIX il faut sortir du oui non par France Culture&quot;&gt;qui dit non, &lt;/a&gt; non comme de simples réactions, mais comme des forces qui révèlent une vérité humaine et morale. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il  est un philosophe de la tension entre vérité, foi et révolte. Sa pensée cherche à comprendre comment l’être humain peut garder une voix, une conscience et une exigence spirituelle dans un monde désorienté. &lt;/p&gt;  &lt;audio controls title=&quot;Vincent DELECROIX  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89douard_Mehl&quot;  title=&quot; Wikipedia&quot;&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href=&quot;https://www.youtube.com/watch?v=NT0n7tKNb3w&quot; title=&quot;qu’est ce que la verité par Le forum Veritas&quot;&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. &lt;/p&gt; &#10;&#10;" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Barbara_Stiegler&quot; title=&quot; Wikipedia&quot;&gt;Barbara STEIGLER&lt;/a&gt;  est une philosophe française, fille du philosophe Bernard Stiegler, spécialiste de Nietzsche, de philosophie politique et critique du néolibéralisme. Agrégée de philosophie, elle soutient sa thèse en 2003 à Paris-Sorbonne sous la direction de Jean-Luc Marion sur Nietzsche et la biologie. Maître de conférences puis professeure à l'université Bordeaux-Montaigne depuis 2006, elle y dirige le master  &lt;a href=&quot;https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf&quot; title=&quot;Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne&quot;&gt;&quot;Soin, éthique et santé&quot;. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Engagée politiquement, elle analyse les Gilets Jaunes dans &quot;Du cap aux grèves&quot; paru en 2021 et critique l’adaptationnisme comme fondement du néolibéralisme, opposant une intelligence collective à l’élitisme technocratique. &lt;/p&gt; &lt;p&gt; Ses ouvrages sur Nietzsche explorent le corps et la vie (Nietzsche et la biologie, 2001 ; Nietzsche et la critique de la chair, 2005 ; Nietzsche et la vie, 2021). &lt;/p&gt; &lt;p&gt;  Elle étend ses recherches au politique avec  &lt;a href=&quot;https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/&quot; title=&quot;Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit&quot;&gt;&quot;Il faut s’adapter&quot; &lt;/a&gt; paru en  2019, dénonçant les racines évolutionnistes (Spencer, Lippmann) du &lt;a href=&quot;https://www.youtube.com/watch?v=oQQ4xqRvYTk&quot; style=&quot;color:#88A1E9&quot; title=&quot;LA LENTE AGONIE DU NÉOLIBÉRALISME  par &#10;TheSwissBox Conversation&quot;&gt;néolibéralisme &lt;/a&gt; face au pragmatisme démocratique de Dewey. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" display="https://www.laphilo.fr/pho/bastiegler-mini.webp" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89ric_Sadin&quot;  title=&quot; Wikipedia&quot;&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href=&quot;https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur&quot; style=&quot;color:#88A1E9&quot;   title=&quot; Éric SADIN contre ChatGPT par Senseur&quot;&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;&#10;Sadin s'est fait connaître grâce à son livre &quot;La société de l'anticipation &quot; publié en 2011, dans lequel il examine l'émergence de la société de la surveillance et des technologies de prévision qui cherchent à anticiper les comportements et les désirs des individus. Il y aborde notamment les thèmes de la surveillance généralisée, de la collecte de données personnelles et des risques de manipulation. &lt;/p&gt; &lt;p&gt;&#10;Dans son ouvrage &lt;a href=&quot;https://christian-biales.fr/wp-content/uploads/2020/12/Sadin.pdf&quot;  title=&quot;Extrait du livre par Christian Bialès&quot;&gt; &quot;L'Ère de l'individu tyran : la fin d'un monde commun&quot;&lt;/a&gt; paru en 2013, Sadin explore les conséquences de la numérisation de la société sur les notions de vie privée, de liberté individuelle et de démocratie. Il met en garde contre le pouvoir croissant des grandes plateformes technologiques et la manière dont elles peuvent influencer et contrôler nos comportements et nos choix. &lt;/p&gt; &lt;p&gt;&#10;Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre &quot;La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique&quot; publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href=&quot;https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008&quot;  title=&quot;Dataïsme par lebigdata&quot;&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title=&quot;Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau&quot; title=&quot; Wikipedia&quot;&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href=&quot;https://www.youtube.com/watch?v=PNMZHr3L_Ws&quot; title=&quot; Vivons nous dans un multivers par Aurelien Barrau&quot;&gt; concept de multivers&lt;/a&gt; , et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage &quot;Chaos multiples&quot; et &quot;De la vérité dans les sciences&quot;  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé &quot;Météorites&quot;. &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de &quot;sauver le climat&quot; plutôt &quot;qu’agir pour la vie&quot;. &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  &quot;habiter la science en poète&quot; en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href=&quot;https://www.youtube.com/watch?v=94IxSYo5wtM&quot; title=&quot;Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter&quot;&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href=&quot;https://www.youtube.com/watch?v=g3Z_LsXD7DU&quot; title=&quot; L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac&quot;&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un &quot;faire monde&quot; éthique et conscient. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Aurelien BARRAU par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin&quot; title=&quot; Wikipedia&quot;&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href=&quot;https://charlespepin.fr/&quot;  title=&quot; Site officiel Charles Pépin &quot;&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href=&quot;https://www.youtube.com/watch?v=WExeoL6qVmc&quot; title=&quot; Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori&quot;&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href=&quot;https://www.youtube.com/watch?v=orOxuIHT_vc&quot; title=&quot;Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal&quot;&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt; - &quot;Les Vertus de l’échec&quot; publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt; - &quot;La Confiance en soi &quot; paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt; - &quot;La Rencontre&quot;  en 2021 et &quot;Vivre avec son passé&quot; en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href=&quot;https://www.youtube.com/watch?v=M09YmUzDwO8&quot; title=&quot; Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs&quot;&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; La philosophie selon Charles Pépin par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel&quot;  title=&quot; Wikipedia&quot;&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un &quot;philosophe de la liberté&quot;. Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que &quot;être de gauche&quot; signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;La privation de l’intime&quot; paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href=&quot;https://www.youtube.com/watch?v=HcDfUGypNvA&quot; style=&quot;color:#88A1E9&quot; title=&quot;Michaël Fœssel - Récidive, 1938 par Librairie mollat&quot;&gt;&quot;Récidive. 1938&quot;&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme &quot;laboratoire&quot; pour comprendre les fragilités  &lt;a href=&quot;https://www.youtube.com/watch?v=wdeS7SFEz7Y&quot;  title=&quot;Démocratie illibérale par Michaël Foessel par France Culture&quot;&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 &quot;Quartier rouge. Le plaisir et la gauche&quot;, il interroge le rapport de  &lt;a href=&quot;https://www.youtube.com/watch?v=MDubXJZox34&quot; title=&quot;Michaël Foessel : &quot;La question du plaisir est aujourd'hui centrale en politique&quot; par France Inter&quot;&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment &quot;Vers la paix perpétuelle&quot; et &quot;La religion dans les limites de la simple raison&quot;, tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title=&quot;La gauche : état des lieux  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Baptiste_Jeang%C3%A8ne_Vilmer&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Baptiste JEANGENE VILMER&lt;/a&gt;  est un philosophe, politologue et juriste français spécialiste de l’éthique de la guerre, du droit international et des relations internationales, et également diplomate (ambassadeur de France au Vanuatu depuis 2022). Il est formé dans trois disciplines : philosophie (licence, master, doctorat), droit (licence, LLM, postdoctorat) et science politique (doctorat). &lt;/p&gt; &lt;p&gt; Sa thèse porte sur &quot;l’intervention militaire justifiée par des raisons humanitaires&quot;, à la croisée de philosophie politique, droit international et théorie des relations internationales. Il défend en théorie des relations internationales un &quot;réalisme libéral&quot; inspiré de Raymond Aron, Stanley Hoffmann et Pierre Hassner : reconnaissance du tragique et des &lt;a href=&quot;https://www.youtube.com/watch?v=4EECHNFvt4Q&quot;  title=&quot; J-B. Jeangène Vilmer - Synthèse par Institut Guerre et Paix&quot;&gt;rapports de force, &lt;/a&gt;  mais attachée au droit international, aux droits humains et aux institutions. &lt;/p&gt; &lt;p&gt; Il se situe à l’intersection de philosophie morale, droit international et stratégie : penser les guerres et interventions non seulement en termes juridiques ou militaires, mais surtout en termes de responsabilité morale (tuer, laisser mourir, protéger). Son &lt;a href=&quot;https://www.jbjv.com/IMG/pdf/JB_Jeangene_Vilmer_2013_-_Pour_un_realisme_liberal_en_relations_internationales.pdf&quot;  title=&quot;Pour un réalisme libéral en relations internationales par jbjv&quot;&gt;&quot;réalisme libéral&quot; &lt;/a&gt; refuse à la fois le cynisme réaliste pur et l’idéalisme naïf, il cherche des critères prudents mais exigeants pour juger les interventions, la justice pénale, ou la responsabilité des États. &lt;/p&gt; &lt;p&gt; Il insiste sur les dilemmes : parfois, intervenir violemment peut sauver des vies, mais peut aussi aggraver le conflit ; parfois, poursuivre les criminels peut fragiliser la paix. Sa pensée explore ces tensions plutôt que de proposer des solutions simplistes. &lt;/p&gt; &#10;&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   &#10;" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" display="https://www.laphilo.fr/pho/nykisukidi-mini.webp" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" display="https://www.laphilo.fr/pho/jdfunes-mini.webp" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tristan_Garcia&quot; title=&quot; Wikipedia&quot;&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. &lt;/p&gt; &lt;p&gt; Son œuvre majeure &quot;Forme et objet. Un traité des choses&quot; paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie &quot;plate&quot; qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans &quot;Nous&quot; ou &quot;La Vie intense&quot; paru en 2016, il explore l’appartenance à des collectifs variables &quot;nous humains&quot;, &quot;nous animaux&quot; et critique l’obsession moderne pour  &lt;a href=&quot;https://www.youtube.com/watch?v=JTLVzryyyEg&quot; title=&quot;Tristan Garcia, INTENSITÉ par abc penser&quot;&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (La Meilleure part des hommes, sur le sida) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href=&quot;https://www.youtube.com/watch?v=K_wxi5xTYz8&quot; title=&quot;Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace&quot;&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; &#10; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Tristan Garcia, &quot;La vie intense : une obsession moderne&quot; par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10; " r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Baptiste_Morizot&quot;  title=&quot; Wikipedia&quot;&gt;Baptiste MORIZOT&lt;/a&gt;  est un philosophe français,  maître de conférences à l'université d'Aix-Marseille, dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle. Son approche se distingue par une pratique de terrain ancrée dans l'expérience, notamment le pistage des grands prédateurs comme les loups, ce qui lui permet de nourrir sa pensée philosophique par une observation directe et sensible du vivant.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve l'idée que la crise écologique contemporaine est avant tout une « crise de la sensibilité » et de nos relations avec le reste du monde vivant. Il soutient que la pensée moderne, marquée par un dualisme qui sépare strictement l'humain de la nature, nous a &lt;a href=&quot;https://www.youtube.com/watch?v=bAnXnPnnHCk&quot; title=&quot;Baptiste Morizot, meme penseur on est un animal par France Inter&quot;&gt;rendus aveugles et sourds &lt;/a&gt; aux autres espèces, qu'il préfère considérer comme d'autres « manières d'être vivant » plutôt que comme des êtres inférieurs. &lt;/p&gt; &lt;p&gt; Il propose ainsi de remplacer le modèle classique de la « maîtrise de la nature » par une « diplomatie des interdépendances ». Cette approche invite les humains à se concevoir comme des partenaires au sein d'un réseau complexe d'interdépendances, où il s'agit de tisser des alliances concrètes, de prêter attention aux signaux émis par les autres espèces et d'apprendre à cohabiter avec elles dans un esprit de respect et de responsabilité partagée. &lt;/p&gt; &lt;p&gt; Son travail, qui mêle récit, enquête éthologique et essai théorique, cherche à réenchanter &lt;a href=&quot;https://www.youtube.com/watch?v=uQZcktq_W3E&quot; title=&quot;Baptiste Morizot, remet l’humain à sa place par La Grande Librairie&quot;&gt;notre rapport au monde &lt;/a&gt; en réactivant nos capacités d'attention et d'intelligence sensible. En invitant à une forme de sagesse pragmatique et ancrée, il s'efforce de refonder notre culture environnementale, non pas pour dominer ou sanctuariser la nature, mais pour s'ajuster avec humilité à la diversité des formes de vie qui partagent la Terre avec nous. &lt;/p&gt;  &lt;audio controls title=&quot;Liberté, dignité, habitalité avec baptiste MORIZOT par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18558-25.04.2026-ITEMA_24488881-2026F30378S0115-NET_MFI_D6CADDF4-ADD5-4D3F-AA1D-625272E9CD3C-22-b98aedea0426383b486dc3819cb77a8e.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" display="https://www.laphilo.fr/pho/ydallaglio-mini.webp" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Norman_Ajari&quot;  title=&quot; Wikipedia&quot;&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href=&quot;https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari&quot;  title=&quot;Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse&quot;&gt;&quot;études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href=&quot;https://www.youtube.com/watch?v=IMUBi9oi2WM&quot; title=&quot;Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche&quot;&gt;&quot;colonialité de l’être&quot; &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=ECSmpOXY8kg&quot; title=&quot;NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS&quot;&gt;&quot;La Dignité ou la mort&quot;, &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de &quot;philosophe militant&quot; : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. &lt;/p&gt; &lt;audio controls title=&quot;où commence et où finit le racisme? par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" display="https://www.laphilo.fr/pho/mmaeso-mini.webp" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Jullien&quot;  title=&quot; Wikipedia&quot;&gt;François JULLIEN&lt;/a&gt; est un philosophe français, à la fois helléniste et sinologue, connu pour avoir construit un dialogue suivi entre la pensée européenne (surtout grecque) et la pensée chinoise. Il séjourne longuement en Asie (notamment à Tokyo) et soutient deux thèses, l’une sur l’écrivain chinois Lu Xun, l’autre sur l’interprétation poétique dans la tradition chinoise, ce qui fonde son approche de  &lt;a href=&quot;https://www.berlol.net/foire/fle98ju.htm&quot;  title=&quot;le détour d'un grec par la chine par berlol.net&quot;&gt;l’altérité culturelle.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Son projet central consiste à &quot;dépayser&quot; la pensée européenne en la confrontant à la Chine, afin de faire apparaître les présupposés cachés de la philosophie occidentale. Il insiste sur le fait que la rencontre des pensées ne doit pas viser l’exotisme, mais ouvrir un espace &quot;entre&quot; les cultures où se travaille un véritable commun, différent de l’uniforme qu’on confond trop vite avec l’universel. &lt;/p&gt; &lt;p&gt; Il travaille la notion d’&quot;écart&quot; : au lieu de chercher ce qui est semblable entre les cultures, il valorise leurs écarts comme lieu de réflexion et de création conceptuelle. De cet écart naît un &quot;entre&quot; : un espace de tension fécond où se construit le commun, sans effacer les différences. Il propose aussi un déplacement majeur : passer de la pensée de l’&quot;être&quot; à une pensée du &quot;vivre&quot;, plus attentive aux processus, aux transformations et à l’expérience concrète de l’existence. &lt;/p&gt; &lt;p&gt; Dans des ouvrages comme le &quot;Traité de l’efficacité&quot;, il oppose la manière occidentale d’agir à une logique chinoise de l’efficience, qui mise sur les tendances de la situation et les transformations continues. L’idée est moins de choisir un camp que de se servir de cet  &lt;a href=&quot;https://www.youtube.com/watch?v=RAgmn0mbUnQ&quot;  title=&quot;François Jullien, entrer dans la pensée chinoise par deodaTV&quot;&gt;écart Chine/Europe &lt;/a&gt; pour repenser nos pratiques de l’action, de la stratégie et de la décision dans le monde contemporain. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;L’art de « décoïncider » selon François Jullien  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13957-13.02.2021-ITEMA_22573157-2021C22785S0044.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Olivier_Abel&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Olivier ABEL&lt;/a&gt;  est un philosophe français spécialiste en éthique et philosophie morale, influencé par Paul Ricœur, Emmanuel Levinas et la tradition protestante. Il soutient en 1983 une thèse sur la rêverie chez Gaston Bachelard sous la direction de Ricœur, puis une habilitation en 2000 sur le temps éthique entre courage et pardon. &lt;/p&gt; &lt;p&gt; Créateur du Fonds Ricœur à Paris, doyen de la Faculté protestante de Paris, il a présidé la Commission d'éthique de la &lt;a href=&quot;https://www.lavie.fr/idees/histoire/olivier-abel-avec-le-catholicisme-leffort-fait-partie-du-chemin-pour-acceder-a-la-grace-100952.php&quot;  title=&quot;Olivier Abel : Avec le catholicisme, l’effort fait partie du chemin pour accéder à la grâce par la Vie&quot;&gt;Fédération protestante &lt;/a&gt;  de France et est membre de l'Académie de Nîmes depuis 2018. Il est aussi membre du Comité consultatif national d'éthique et contribue à des revues comme Esprit. &lt;/p&gt; &lt;p&gt; Ses recherches portent sur l'éthique interrogative, le pardon, la conversation, l'Europe et les penseurs protestants comme Calvin ou Bayle. Parmi ses ouvrages : L’éthique interrogative (2000), Le pardon, briser la dette et l’oubli (1991), Le vertige de l’Europe (2019),  &lt;a href=&quot;https://www.youtube.com/watch?v=G1_ynk7E7LQ&quot; title=&quot;Olivier Abel, philosophe : Le signe de l’humiliation, c’est cette parole rentrée par FRANCE 24&quot;&gt;De l’humiliation &lt;/a&gt; (récent) et La naissance, qu’est-ce que ça change. Il explore la fugacité des liens humains et une critique du sujet délié. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Le témoin du vendredi : Olivier Abel, la civilisation européenne par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/11739-12.04.2019-ITEMA_22034063-2019F17009S0102-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pascal_Engel&quot;   title=&quot; Wikipedia&quot;&gt;Pascal ENGEL&lt;/a&gt; est un philosophe français spécialiste de la philosophie analytique, de l'épistémologie et de la philosophie du langage. Ancien élève de l'École normale supérieure et agrégé de philosophie, il a étudié aux universités de Paris IV et Paris I sous l'influence de Jacques Bouveresse et Gilles-Gaston Granger. Sa thèse de doctorat d'État (1990) portait sur la philosophie du langage de Donald Davidson. &lt;/p&gt; &lt;p&gt; Directeur d'études à l'École des hautes études en sciences sociales (EHESS) depuis 2012 et professeur honoraire à l'Université de Genève, il a enseigné à Grenoble, Caen et la Sorbonne. Il a présidé la Société de philosophie analytique et édité la revue Dialectica. &lt;/p&gt; &lt;p&gt; Ses livres incluent &quot;La Norme du vrai&quot; paru en 1989 sur la philosophie de la logique, &lt;a href=&quot;https://www.youtube.com/watch?v=ivsIBYFN6DI&quot; title=&quot;*Concevoir l'épistémologie de la psychologie, lecture d'un ouvrage de Pascal Engel par Laboratoire de talos&quot;&gt; &quot;Va savoir&quot;&lt;/a&gt; en 2007 défendant le réalisme épistémologique, et &quot;Les vices du savoir&quot; en 2019 sur l'éthique de la croyance. Il a dialogué avec Richard Rorty sur la vérité et exploré les normes épistémiques. Il l défend un réalisme minimal sur la vérité, une épistémologie normative et distingue croyance d'acceptation. Ses travaux critiquent le relativisme et le pragmatisme, appliquant ces idées à l'esprit, la connaissance et les vices intellectuels. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Faut-il faire la morale aux intellectuels ?  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.06.2019-ITEMA_22085369-3.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Christophe_Goddard&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Christophe GODDARD&lt;/a&gt; est un philosophe français, professeur à l'Université Toulouse 2. Ses travaux initiaux portaient sur l'idéalisme allemand, notamment J.G. Fichte dont il a traduit des textes, et la philosophie française du XXe siècle comme Deleuze et Maldiney. &lt;/p&gt; &lt;p&gt; Il a présidé l'Internationale Fichte Gesellschaft de 2006 à 2012 et coordonné le projet Erasmus Mundus EuroPhilosophie jusqu'en 2023. Depuis 2016, il anime un séminaire sur les décolonisations avec l'Université de Louvain-la-Neuve. &lt;/p&gt; &lt;p&gt; Depuis une décennie, il se consacre à la critique décoloniale de la philosophie européenne moderne, mobilisant philosophie africaine contemporaine et contre-anthropologies amazoniennes. Dans  &lt;a href=&quot;https://www.youtube.com/watch?v=vEQWmSo67B4&quot; style=&quot;color:#88A1E9&quot; title=&quot;Jean-Christophe Goddard : Ce sont d’autres gens par Librairie Ombres Blanches&quot;&gt;&quot;Ce sont d'autres gens&quot; &lt;/a&gt; paru en  2024, il valorise les savoirs non-blancs oraux pour questionner le modèle anthropologique colonial européen. &lt;/p&gt; &lt;p&gt; Il critique l'eurocentrisme philosophique qui efface l'altérité et impose une épistémologie coloniale, proposant à la place un perspectivisme indigène qui questionne la &quot;qualité de la vie&quot; sous le capitalisme extractiviste. Cette approche vise à penser un &lt;a href=&quot;https://www.youtube.com/watch?v=ZDpbSRrWIhU&quot; title=&quot;Jean-Christophe Goddard - La Manufacture d'idées 2024 par La Manufacture d'idées&quot;&gt;&quot;autre monde&quot; &lt;/a&gt; en restituant la puissance des savoirs subalternes contre le génocide continu et l'héritage colonial, sans essentialiser les cultures non blanches ni inverser simplement l'ethnocentrisme européen. &lt;/p&gt;  &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Le XIXème siècle à travers les âges 5/5 : Fichte et la nation allemande par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/14114-30.09.2014-ITEMA_20675216-2011C12410E0182-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Sandra_Laugier&quot; title=&quot; Wikipedia&quot;&gt;Sandra LAUGIER&lt;/a&gt;  est une philosophe française, professeure à l’université Paris 1 Panthéon-Sorbonne, membre de l’Institut Universitaire de France et spécialiste de philosophie du langage, de philosophie morale et de philosophie politique. Elle a aussi beaucoup travaillé sur Stanley Cavell, qu’elle a traduit en français, ainsi que sur Emerson, Thoreau et le perfectionnisme moral. &lt;/p&gt; &lt;p&gt; Sa philosophie accorde une place centrale à l’ordinaire : les gestes, les paroles, les liens quotidiens et les formes de vie concrètes sont pour elle des lieux essentiels de la pensée. Elle défend l’idée qu’il faut partir de l’expérience vécue plutôt que de grands systèmes abstraits, ce qui l’a conduite à développer une éthique du care, une réflexion sur le langage ordinaire et une attention aux formes discrètes de la vie commune. &lt;/p&gt; &lt;p&gt; Sur le plan politique, elle s’intéresse aux formes contemporaines de démocratie, à &lt;a href=&quot;https://www.youtube.com/watch?v=nlM-aPBIRdg&quot; title=&quot;Sandra Laugier : reconnaître nos dépendances par France Inter&quot;&gt;la désobéissance civile &lt;/a&gt; et aux mouvements horizontaux comme Nuit debout. Elle y voit une manière de repenser le politique à partir de l’expression des personnes, du souci du commun et de l’égalité effective des droits, plutôt que d’un modèle hiérarchique classique. Cette perspective la conduit à défendre une démocratie plus attentive aux voix singulières et aux pratiques collectives concrètes. &lt;/p&gt; &lt;p&gt; Elle a aussi élargi la philosophie à la culture populaire, notamment &lt;a href=&quot;https://www.youtube.com/watch?v=Rjd2XEvkqWc&quot; title=&quot;Sandra Laugier : nos vies en séries par librairie mollat&quot;&gt;aux séries télévisées, &lt;/a&gt; qu’elle considère comme un laboratoire d’expériences morales et politiques. Dans des ouvrages récents, elle montre que les séries peuvent aider à penser nos manières de vivre, nos attachements et nos conflits, en révélant des aspects très actuels de la sensibilité démocratique. &lt;/p&gt;  &lt;audio controls title=&quot;L’éthique animale avec Florence Burgat par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10201-30.05.2013-ITEMA_20485436-2013C10593E0019-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" display="https://www.laphilo.fr/pho/slaugier-mini.webp" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marc_Cr%C3%A9pon&quot;  title=&quot; Wikipedia&quot;&gt;Marc CRÉPON&lt;/a&gt;  est un philosophe français connu pour ses travaux au CNRS et à l’École normale supérieure. Son travail porte surtout sur la philosophie morale et politique, avec une attention constante  &lt;a href=&quot;https://www.youtube.com/watch?v=xOKttB1HgSk&quot;  title=&quot;Marc Crépon sur la violence  par France Inter &quot;&gt;à la violence, &lt;/a&gt; aux langues et aux formes de communauté. &lt;/p&gt; &lt;p&gt; Sa philosophie part d’une idée simple mais forte : la violence n’est jamais seulement un fait extérieur, elle transforme aussi notre rapport aux autres. Il montre comment elle détruit la confiance, réduit l’autre à un objet et s’inscrit parfois jusque dans le langage lui-même. &lt;/p&gt; &lt;p&gt; Il réfléchit aussi à la responsabilité envers autrui, en particulier envers les vies fragiles, oubliées ou rendues invisibles. Chez lui, penser le politique, ce n’est pas seulement parler d’institutions, mais défendre une manière de vivre ensemble qui résiste aux  &lt;a href=&quot;https://www.youtube.com/watch?v=kwFC9MSSWcg&quot;  title=&quot;Marc Crépon : l’épreuve de la haine   par Librairie mollat &quot;&gt;logiques de haine, &lt;/a&gt; de frontières fermées et de repli identitaire. &lt;/p&gt; &lt;p&gt; On peut dire qu’il est un philosophe de l’attention à l’autre, de la critique de la violence et de la défense de la vie commune. Sa pensée cherche moins à donner des réponses toutes faites qu’à ouvrir un espace pour la confiance, la critique et la révolte juste.  &lt;/p&gt; &lt;audio controls title=&quot;Marc Crepon, philosophe: on ne peut pas faire des différences ,, par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-21.02.2026-ITEMA_24416884-2026F22640S0052-NET_MFI_3748F374-A8B8-4CF7-B610-67B228C70EE1-22-e3cc0b367fe43af54dde46f562c53722.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Audi&quot;  title=&quot; Wikipedia&quot;&gt;Paul AUDI&lt;/a&gt;  est un philosophe et écrivain français né à Beyrouth, au Liban, et ancien élève de l'École normale supérieure. Agrégé de philosophie et docteur en philosophie, il a soutenu une thèse sur Jean-Jacques Rousseau publiée en 1997. Après avoir enseigné à l'université de Paris-XII, il s'est éloigné du champ universitaire pour s'orienter vers l'édition, et aujourd'hui il est professeur invité dans diverses institutions en France et à l'étranger. Il est auteur de plus d'une trentaine d'ouvrages et membre de l'équipe de recherches PHILéPOL à l'université Paris Descartes. &lt;/p&gt; &lt;p&gt; Sa philosophie se centre principalement sur les relations entre l'éthique et l'esthétique en Occident durant les Temps Modernes. Son œuvre explore ces liens à travers des &lt;a href=&quot;https://www.youtube.com/watch?v=3GRhkvYGMs0&quot;  title=&quot;Paul Audi contrat social par le nouvel Obs&quot;&gt;lectures de Rousseau, &lt;/a&gt;  Nietzsche, Lacan, Schopenhauer et Georges Bataille. Il est considéré comme un philosophe atypique, commençant à être reconnu hors de France. Sa pensée conjugue la vie du corps et la création artistique, l'éthique et la passion, avec un souci d'ancrer la pensée dans la vie physique. &lt;/p&gt; &lt;p&gt; L'idée centrale de sa philosophie est que l'acte de création et le comportement éthique ne forment qu'un seul et même geste, qui naît de la vie elle-même et finalement l'excède. Il nomme cette fusion « esth/éthique », considérant que l'éthique et l'esthétique dans l'acte de créer se confondent ou sont le recto et verso d'une même « explication avec la vie ». Pour lui, créer revient à « s'expliquer avec la vie », à faire de l'énigme que nous sommes une bribe d'un discours neuf. &lt;/p&gt; &lt;p&gt; L'éthique, selon lui, consiste d'abord en un travail sur soi, où « c'est moi-même qui suis la tâche ». La philosophie ne s'accomplit qu'au sein d'un corps à corps avec ce qui, en nous-mêmes, nous dépasse — non pas le monde ou un dehors, mais ce qui nous situe sur le  &lt;a href=&quot;https://www.youtube.com/watch?v=FJsDRUR9bYQ&quot;  title=&quot;Paul Audi il faut le nuance par France Inter&quot;&gt;« plan de la vie », &lt;/a&gt; qui ne recouvre ni le champ social ni l'espace politique. Cette éthique de la création, qu'il dénomme « esthéthique », n'est pas un code de règles mais une posture existentielle, une manière de se situer face au monde. &lt;/p&gt; &lt;p&gt; Il  s'intéresse également aux conditions permettant à l'être humain d'accéder à sa propre humanité, et interroge profondément la question de l'identité. Dans son ouvrage Troublante identité (2022), il parle pour la première fois de lui-même et de ce qui le hante, résistant à toute réduction de son être à sa provenance libanaise. Il désire en finir avec les clôtures identitaires et trouve son émancipation dans une conception juive d'une identité ouverte, toujours à construire, guidée par un impératif de justice à venir. Son dernier essai Le Vrai du beau (2026) transforme la contemplation d'un tableau en expérience de vérité, éclaircissant ce qui se joue en nous face à un tableau. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;la verité picturale existe t’elle ?  Par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/26657-24.04.2026-ITEMA_24487813-2026F45096S0114-NET_MFI_F40118A5-5297-4676-86E9-2E9A248FB2F7-27-03023a67ff6f93208a5f302d7d3b8771.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;&#10;" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" display="https://www.laphilo.fr/pho/paudi-mini.webp" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" display="https://www.laphilo.fr/pho/cmichon-mini.webp" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Corine_Pelluchon&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Corine PELLUCHON&lt;/a&gt; est une philosophe française reconnue pour ses travaux en philosophie politique et en éthique appliquée, notamment dans les domaines médical, environnemental et animal. Son œuvre interroge la condition humaine à travers les concepts de corporéité, de vulnérabilité, de dépendance à l'égard des autres et de la nature.​ &lt;/p&gt; &lt;p&gt; Elle renouvelle  &lt;a href=&quot;https://www.youtube.com/watch?v=r5c00JRkJy0&amp;t=60s&quot; title=&quot;NOUVELLES LUMIÈRES avec Corine Pelluchon // Qu'est-ce qui nous arrive ? par Philomonaco&quot;&gt;l’héritage des Lumières&lt;/a&gt;  en intégrant les défis du monde moderne : crises écologiques, nouvelles pratiques médicales, biotechnologies et défense de la cause animale et s’élève contre la déshumanisation contemporaine et veut promouvoir un monde habitable, juste envers les humains et les non-humains. Sa réflexion s’inspire de la phénoménologie (Merleau-Ponty), de la pensée de Levinas, et vise à articuler éthique, politique et soin du vivant. Elle développe une phénoménologie de la corporéité, mettant l’accent sur la vulnérabilité et notre cohabitation avec tous les vivants. Elle défend une éthique de la vulnérabilité, qui intègre le corps, l’affectif et le spirituel à la réflexion philosophique. &lt;/p&gt; &lt;p&gt; Son œuvre compte une quinzaine de livres traduits en plusieurs langues, parmi lesquels : &lt;/p&gt; &#10;&lt;p&gt; - Manifeste animaliste. Politiser la cause animale ( 2017 )  - Éthique de la considération ( 2018) - Réparons le monde. Humains, animaux, nature (2020)  &#10; - Les Lumières à l’âge du vivant (2021) &lt;/p&gt; &#10;&lt;p&gt; -   &lt;a href=&quot;https://www.youtube.com/watch?v=zpzzDqYhF-8&quot; title=&quot;Corine Pelluchon - L'être et la mer : pour un existentialisme écologique par librairie mollat&quot;&gt;L’être et la mer&lt;/a&gt;. Pour un existentialisme écologique (PUF, 2024) &lt;/p&gt; &lt;p&gt; Elle agit dans le domaine public pour transformer la société et ses modèles de production et de vie. Elle a reçu de nombreux prix, dont le Prix Günther Anders de la pensée critique en Allemagne en 2020 pour l’ensemble de ses travaux.​ En somme, sa philosophie pose la question de l’habitation du monde et du soin du vivant, en invitant à la transformation de soi et des structures collectives pour bâtir un monde plus juste et plus habitable et où  &lt;a href=&quot;https://www.youtube.com/watch?v=tmk-UzN1j70&quot;  title=&quot;Extrême-droite, autoritarisme, illibéralisme : pourquoi la démocratie a besoin du féminin par La Vie Media&quot;&gt;le féminin&lt;/a&gt; a toute sa place. &lt;/p&gt; &lt;audio controls title=&quot;Corine Pelluchon par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/16174-30.01.2023-ITEMA_23272268-2023F26101S0030-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" display="https://www.laphilo.fr/pho/cfmetterie-mini.webp" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vincent_Delecroix&quot;  title=&quot; Wikipedia&quot;&gt;Vincent DELECROIX&lt;/a&gt;  est un philosophe français spécialiste de Kierkegaard et de la philosophie de la religion. Il enseigne à l’EPHE, où il travaille sur la vérité, la croyance et les liens entre religion et pensée contemporaine. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse d’abord à la manière dont la foi peut exister dans un monde moderne où les certitudes absolues se  &lt;a href=&quot;https://www.youtube.com/watch?v=2ZHOpP5GMwI&quot; title=&quot;Vincent DELECROIX,la nécessité d’apprendre par TV5 monde&quot;&gt;sont affaiblies. &lt;/a&gt; Il ne traite pas la religion comme un simple héritage figé, mais comme une expérience intérieure, fragile et exigeante.  &lt;/p&gt; &lt;p&gt; Un autre axe important chez lui est la révolte. À travers des livres comme Tombeau d’Achille et Non ! De l’esprit de révolte, il réfléchit à la colère, au refus et à la parole &lt;a href=&quot;https://www.youtube.com/watch?v=OiUgp6wLpCA&quot; title=&quot;Vincent DELECROIX il faut sortir du oui non par France Culture&quot;&gt;qui dit non, &lt;/a&gt; non comme de simples réactions, mais comme des forces qui révèlent une vérité humaine et morale. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il  est un philosophe de la tension entre vérité, foi et révolte. Sa pensée cherche à comprendre comment l’être humain peut garder une voix, une conscience et une exigence spirituelle dans un monde désorienté. &lt;/p&gt;  &lt;audio controls title=&quot;Vincent DELECROIX  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-20.02.2026-ITEMA_24415905-2026C53456S0051-NET_MFC_3DAF1756-008D-498F-B71D-CC3C30449F83-21-69aa794b4a96b37fd3a9e6f0abf4f125.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89douard_Mehl&quot;  title=&quot; Wikipedia&quot;&gt;Edouard MEHL&lt;/a&gt;  est un philosophe français  professeur à l’université de Strasbourg, spécialiste de Descartes, de la philosophie moderne et de l’histoire des sciences. Son travail a été reconnu par le prix Moron de l’Académie française pour son livre sur Descartes et la cosmologie. &lt;/p&gt; &lt;p&gt; Sa philosophie s’intéresse surtout à la manière dont Descartes reconstruit le savoir au moment de la révolution scientifique. Il montre que la pensée cartésienne ne se limite  &lt;a href=&quot;https://www.youtube.com/watch?v=NT0n7tKNb3w&quot; title=&quot;qu’est ce que la verité par Le forum Veritas&quot;&gt;pas à la méthode : &lt;/a&gt; elle repense aussi la matière, le mouvement, la lumière, le ciel et la place du monde dans la connaissance. &lt;/p&gt; &lt;p&gt; Un autre aspect important de son travail est la relation entre philosophie et sciences. Il étudie comment les idées cosmologiques, de Copernic à Newton, transforment la métaphysique et la théorie de la connaissance, et comment la modernité philosophique naît de ces bouleversements. &lt;/p&gt; &lt;p&gt; On peut donc dire qu’il est un philosophe de la genèse de la modernité : il cherche à comprendre comment la pensée moderne s’est construite en dialogue avec les sciences, la cosmologie et Descartes. Sa philosophie éclaire à la fois l’histoire des idées et les grandes questions sur le monde, la liberté et la connaissance. &lt;/p&gt; &#10;&#10;" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Barbara_Stiegler&quot; title=&quot; Wikipedia&quot;&gt;Barbara STEIGLER&lt;/a&gt;  est une philosophe française, fille du philosophe Bernard Stiegler, spécialiste de Nietzsche, de philosophie politique et critique du néolibéralisme. Agrégée de philosophie, elle soutient sa thèse en 2003 à Paris-Sorbonne sous la direction de Jean-Luc Marion sur Nietzsche et la biologie. Maître de conférences puis professeure à l'université Bordeaux-Montaigne depuis 2006, elle y dirige le master  &lt;a href=&quot;https://www.u-bordeaux-montaigne.fr/_resource/ODF-Documents/Plaquettes-com/2016-2021/HUM/HUM_Masters/master-soin-ethique-sante-u-bordeaux-montaigne.pdf&quot; title=&quot;Barbara Stiegler - Soin, éthique et santé - Philosophie par Bordeaux Montaigne&quot;&gt;&quot;Soin, éthique et santé&quot;. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Engagée politiquement, elle analyse les Gilets Jaunes dans &quot;Du cap aux grèves&quot; paru en 2021 et critique l’adaptationnisme comme fondement du néolibéralisme, opposant une intelligence collective à l’élitisme technocratique. &lt;/p&gt; &lt;p&gt; Ses ouvrages sur Nietzsche explorent le corps et la vie (Nietzsche et la biologie, 2001 ; Nietzsche et la critique de la chair, 2005 ; Nietzsche et la vie, 2021). &lt;/p&gt; &lt;p&gt;  Elle étend ses recherches au politique avec  &lt;a href=&quot;https://www.erudit.org/fr/revues/philoso/2019-v46-n1-philoso04752/1062026ar/&quot; title=&quot;Barbara Stiegler, -Il faut s’adapter-. Sur un nouvel impératif politique par Erudit&quot;&gt;&quot;Il faut s’adapter&quot; &lt;/a&gt; paru en  2019, dénonçant les racines évolutionnistes (Spencer, Lippmann) du &lt;a href=&quot;https://www.youtube.com/watch?v=oQQ4xqRvYTk&quot; style=&quot;color:#88A1E9&quot; title=&quot;LA LENTE AGONIE DU NÉOLIBÉRALISME  par &#10;TheSwissBox Conversation&quot;&gt;néolibéralisme &lt;/a&gt; face au pragmatisme démocratique de Dewey. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;La démocratie avec Barbara Stiegler et Christophe Pébarthe par France Inter&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/22676-15.11.2024-ITEMA_23926359-2024F45096S0320-NET_MFI_8A61717A-715A-470C-8A6C-AB4BC63A33B5-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   " r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" display="https://www.laphilo.fr/pho/bastiegler-mini.webp" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89ric_Sadin&quot;  title=&quot; Wikipedia&quot;&gt;Eric SADIN&lt;/a&gt; est un écrivain et philosophe français connu pour ses travaux sur les enjeux liés à la technologie, à la surveillance et à &lt;a href=&quot;https://www.youtube.com/watch?v=_hGI2Wewrn8&amp;ab_channel=Senseur&quot; style=&quot;color:#88A1E9&quot;   title=&quot; Éric SADIN contre ChatGPT par Senseur&quot;&gt; l'intelligence artificielle&lt;/a&gt; et de ce fait aux implications sociales, culturelles et politiques des ces développements technologiques. &lt;/p&gt; &lt;p&gt;&#10;Sadin s'est fait connaître grâce à son livre &quot;La société de l'anticipation &quot; publié en 2011, dans lequel il examine l'émergence de la société de la surveillance et des technologies de prévision qui cherchent à anticiper les comportements et les désirs des individus. Il y aborde notamment les thèmes de la surveillance généralisée, de la collecte de données personnelles et des risques de manipulation. &lt;/p&gt; &lt;p&gt;&#10;Dans son ouvrage &lt;a href=&quot;https://christian-biales.fr/wp-content/uploads/2020/12/Sadin.pdf&quot;  title=&quot;Extrait du livre par Christian Bialès&quot;&gt; &quot;L'Ère de l'individu tyran : la fin d'un monde commun&quot;&lt;/a&gt; paru en 2013, Sadin explore les conséquences de la numérisation de la société sur les notions de vie privée, de liberté individuelle et de démocratie. Il met en garde contre le pouvoir croissant des grandes plateformes technologiques et la manière dont elles peuvent influencer et contrôler nos comportements et nos choix. &lt;/p&gt; &lt;p&gt;&#10;Il soulève également des questions sur l'impact de l'intelligence artificielle sur la société dans son livre &quot;La Silicolonisation du monde : L'irrésistible expansion du libéralisme numérique&quot; publié en 2016. Il examine comment les algorithmes et l'automatisation peuvent affecter les domaines du travail, de la santé, de l'éducation et de la politique, remettant en question les fondements de la démocratie et de &lt;a href=&quot;https://www.lebigdata.fr/dataisme-big-data-fin-libre-arbitre-3008&quot;  title=&quot;Dataïsme par lebigdata&quot;&gt; l'autonomie humaine&lt;/a&gt;. &lt;/p&gt;  &lt;audio controls title=&quot;Incidence et risque des nouveaux usages de l’intelligence artificielle - de quoi Chat GPT est-il le nom ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/19489-05.02.2023-ITEMA_23278863-2023C33085S0036-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Aur%C3%A9lien_Barrau&quot; title=&quot; Wikipedia&quot;&gt;Aurélien BARRAU&lt;/a&gt; est un philosophe et astrophysicien français, à la fois érudit et engagé. Reconnu pour ses contributions scientifiques en cosmologie, physique des astroparticules, trous noirs, gravité quantique à boucles, hypothèses sur la matière noire et comportement de l’univers à ses débuts. &lt;/p&gt; &lt;p&gt; Il collabore avec Jean-Luc Nancy pour explorer le &lt;a href=&quot;https://www.youtube.com/watch?v=PNMZHr3L_Ws&quot; title=&quot; Vivons nous dans un multivers par Aurelien Barrau&quot;&gt; concept de multivers&lt;/a&gt; , et travaille sur la métaphysique de la vérité, en lien avec Derrida et Goodman — notamment dans l’ouvrage &quot;Chaos multiples&quot; et &quot;De la vérité dans les sciences&quot;  où il critique un scientisme naïf tout en évitant un relativisme total. Il tisse des ponts entre sciences et arts, collaborant avec des plasticiens, cinéastes, des revues littéraires et a publié un recueil poétique intitulé &quot;Météorites&quot;. &lt;/p&gt; &lt;p&gt; Il est une voix écologique forte, il a lancé la tribune « Le plus grand défi de l’histoire de l’humanité » en 2018, relayée par 200 personnalités pour appeler à une action immédiate contre la crise climatique. Il va jusqu’à évoquer la nécessité d’une révolution politique, poétique et philosophique pour surmonter l’inertie face à l’effondrement écologique, dénonçant l’opposition stérile entre nature et culture, ou l’idée de &quot;sauver le climat&quot; plutôt &quot;qu’agir pour la vie&quot;. &lt;/p&gt; &lt;p&gt; Dans L’Hypothèse K, il appelle à  &quot;habiter la science en poète&quot; en questionnant la dépendance de la science à la technique, il invite à une suspension conceptuelle où arts et philosophie viennent éclairer des défis que la science seule ne peut résoudre. &lt;/p&gt; &lt;p&gt;Il fait partie de ceux qui déconstruisent les frontières entre disciplines — science, poésie, philosophie, art, politique — pour  &lt;a href=&quot;https://www.youtube.com/watch?v=94IxSYo5wtM&quot; title=&quot;Pour une révolution politique, poétique et philosophique avec l'astrophysicien Aurélien Barrau par France Inter&quot;&gt;  proposer une pensée &lt;/a&gt; profondément humaniste et interdisciplinaire. Il invite à repenser notre rapport au vivant,   &lt;a href=&quot;https://www.youtube.com/watch?v=g3Z_LsXD7DU&quot; title=&quot; L'intelligence artificielle vue par Aurélien Barrau par Ethique et tac&quot;&gt;  machines et progrès&lt;/a&gt;  compris, au nom d’un &quot;faire monde&quot; éthique et conscient. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; Aurelien BARRAU par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15273-25.11.2023-ITEMA_23563513-2023F30378S0329-22.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_P%C3%A9pin&quot; title=&quot; Wikipedia&quot;&gt;Charles PÉPIN&lt;/a&gt;  est un philosophe, écrivain et conférencier français, connu pour une &lt;a href=&quot;https://charlespepin.fr/&quot;  title=&quot; Site officiel Charles Pépin &quot;&gt;“philosophie pratique”&lt;/a&gt; qui articule concepts classiques et enjeux de &lt;a href=&quot;https://www.youtube.com/watch?v=WExeoL6qVmc&quot; title=&quot; Argent, famille, religion, carrière… On décloisonne tout | avec Charles Pépin par A Priori&quot;&gt;la vie quotidienne&lt;/a&gt; (échec, confiance, rencontre, mémoire). Il a popularisé la réflexion philosophique auprès d’un large public à travers des essais à succès, des bandes dessinées et des interventions médiatiques. Il  relie philosophie, psychologie et expériences de terrain pour proposer des repères opérants dans l’action sans renoncer à l’exigence conceptuelle.  &lt;a href=&quot;https://www.youtube.com/watch?v=orOxuIHT_vc&quot; title=&quot;Les clés d’un philosophe inspiré pour mieux vivre - Dialogue avec Charles Pépin par Dialogues par Fabrice Midal&quot;&gt;Sa démarche&lt;/a&gt; conjugue traditions philosophiques et approches cliniques récentes, notamment sur la mémoire et le changement, afin d’éclairer des questions comme la force intérieure, l’intuition, l’ambition et la joie. &lt;/p&gt; &lt;p&gt; - &quot;Les Vertus de l’échec&quot; publié en 2016 est un  plaidoyé pour transformer l’échec en apprentissage, mobilisant Stoïciens, psychanalyse et épistémologie pour montrer comment l’épreuve aiguise lucidité et désir. L’ouvrage a reçu le prix Elina et Louis Pauwels en 2017.​ &lt;/p&gt; &lt;p&gt; - &quot;La Confiance en soi &quot; paru en 2018 ou l'exploration des trois appuis de la confiance (en l’autre, en ses capacités, en la vie), nourrie par Emerson, Nietzsche, Bergson et des perspectives psychologiques contemporaines.​ &lt;/p&gt; &lt;p&gt; - &quot;La Rencontre&quot;  en 2021 et &quot;Vivre avec son passé&quot; en 2023 sont des reflexions sur l’événement de la rencontre et sur la mémoire, intégrant Bergson et des apports récents en neurosciences pour penser la “reconsolidation” des souvenirs.​ &lt;/p&gt; &lt;p&gt; Outre ses livres, il donne des conférences grand public et en entreprise sur  &lt;a href=&quot;https://www.youtube.com/watch?v=M09YmUzDwO8&quot; title=&quot; Que cache votre besoin de reconnaissance ? Avec le philosophe Charles Pépinpar Les Lueurs&quot;&gt;des sujets&lt;/a&gt; comme l’échec, la confiance, l’intuition et le leadership, prolongeant l’idée d’une philosophie utile au quotidien.&lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot; La philosophie selon Charles Pépin par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13904-30.11.2025-ITEMA_24327388-2025F22640S0334-NET_MFI_277E9352-959D-4527-9C9A-04BCD1F71B24-27-7c6a9522ebe5f90bdb42baadc1dfdafe.m4a&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;&#10;" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Micha%C3%ABl_F%C5%93ssel&quot;  title=&quot; Wikipedia&quot;&gt;Michaël FOESSEL&lt;/a&gt; est un philosophe français spécialiste de Kant, de la philosophie allemande et de la philosophie politique, souvent présenté comme un &quot;philosophe de la liberté&quot;. Militant communiste dans sa jeunesse, il se situe aujourd’hui clairement dans une tradition de gauche, même s’il insiste sur le fait que &quot;être de gauche&quot; signifie d’abord ne pas accepter comme évidentes les inégalités et les dénis de liberté.&lt;/p&gt; &lt;p&gt; Dans son ouvrage &quot;La privation de l’intime&quot; paru en 2008, il analyse la manière dont les sociétés libérales modernes exposent, marchandisent ou politisent l’intimité, au point de la priver de sa fonction de refuge et de ressource subjective. Il montre que cette érosion de l’intime a des conséquences politiques directes, en fragilisant les sujets et en rendant plus difficile une véritable autonomie. Il sort ensuite &lt;a href=&quot;https://www.youtube.com/watch?v=HcDfUGypNvA&quot; style=&quot;color:#88A1E9&quot; title=&quot;Michaël Fœssel - Récidive, 1938 par Librairie mollat&quot;&gt;&quot;Récidive. 1938&quot;&lt;/a&gt;  paru en 2019 ou il propose un parallèle réfléchi entre la France de 1938 et la situation politique actuelle, pour montrer comment un État de droit affaibli, la montée des discours autoritaires et la banalisation des injustices peuvent préparer des basculements graves sans qu’il y ait encore dictature ouverte. Ce n’est pas une répétition mécanique de l’histoire, mais une manière de se servir de 1938 comme &quot;laboratoire&quot; pour comprendre les fragilités  &lt;a href=&quot;https://www.youtube.com/watch?v=wdeS7SFEz7Y&quot;  title=&quot;Démocratie illibérale par Michaël Foessel par France Culture&quot;&gt;de la démocratie&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus récent paru en 2022 &quot;Quartier rouge. Le plaisir et la gauche&quot;, il interroge le rapport de  &lt;a href=&quot;https://www.youtube.com/watch?v=MDubXJZox34&quot; title=&quot;Michaël Foessel : &quot;La question du plaisir est aujourd'hui centrale en politique&quot; par France Inter&quot;&gt;la gauche au plaisir&lt;/a&gt;, à la joie, au désir, en critiquant l’idée que l’émancipation passerait seulement par la dénonciation ou la culpabilisation. Il cherche à penser une politique de gauche qui n’abandonne ni la justice sociale ni la dimension sensible et joyeuse de l’existence. &lt;/p&gt; &lt;p&gt; Spécialiste reconnu de Kant, il a commenté notamment &quot;Vers la paix perpétuelle&quot; et &quot;La religion dans les limites de la simple raison&quot;, tout en travaillant sur le problème du mal et de la raison pratique. Son travail reprend l’exigence kantienne de l’universalité et du cosmopolitisme, mais il la confronte aux enjeux actuels (migration, crise écologique, populismes), pour voir comment la raison peut encore orienter une politique démocratique au XXIᵉ siècle. &lt;/p&gt;  &lt;audio controls title=&quot;La gauche : état des lieux  par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-27.09.2025-ITEMA_24260856-2025C3397E0035-ITE_00153507_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Baptiste_Jeang%C3%A8ne_Vilmer&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Jean-Baptiste JEANGENE VILMER&lt;/a&gt;  est un philosophe, politologue et juriste français spécialiste de l’éthique de la guerre, du droit international et des relations internationales, et également diplomate (ambassadeur de France au Vanuatu depuis 2022). Il est formé dans trois disciplines : philosophie (licence, master, doctorat), droit (licence, LLM, postdoctorat) et science politique (doctorat). &lt;/p&gt; &lt;p&gt; Sa thèse porte sur &quot;l’intervention militaire justifiée par des raisons humanitaires&quot;, à la croisée de philosophie politique, droit international et théorie des relations internationales. Il défend en théorie des relations internationales un &quot;réalisme libéral&quot; inspiré de Raymond Aron, Stanley Hoffmann et Pierre Hassner : reconnaissance du tragique et des &lt;a href=&quot;https://www.youtube.com/watch?v=4EECHNFvt4Q&quot;  title=&quot; J-B. Jeangène Vilmer - Synthèse par Institut Guerre et Paix&quot;&gt;rapports de force, &lt;/a&gt;  mais attachée au droit international, aux droits humains et aux institutions. &lt;/p&gt; &lt;p&gt; Il se situe à l’intersection de philosophie morale, droit international et stratégie : penser les guerres et interventions non seulement en termes juridiques ou militaires, mais surtout en termes de responsabilité morale (tuer, laisser mourir, protéger). Son &lt;a href=&quot;https://www.jbjv.com/IMG/pdf/JB_Jeangene_Vilmer_2013_-_Pour_un_realisme_liberal_en_relations_internationales.pdf&quot;  title=&quot;Pour un réalisme libéral en relations internationales par jbjv&quot;&gt;&quot;réalisme libéral&quot; &lt;/a&gt; refuse à la fois le cynisme réaliste pur et l’idéalisme naïf, il cherche des critères prudents mais exigeants pour juger les interventions, la justice pénale, ou la responsabilité des États. &lt;/p&gt; &lt;p&gt; Il insiste sur les dilemmes : parfois, intervenir violemment peut sauver des vies, mais peut aussi aggraver le conflit ; parfois, poursuivre les criminels peut fragiliser la paix. Sa pensée explore ces tensions plutôt que de proposer des solutions simplistes. &lt;/p&gt; &#10;&lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Les métamorphoses de la guerre avec Jean-Baptiste Jeangène Vilmer par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/12360-22.02.2018-ITEMA_21595551-2018C19327S0053-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;   &#10;" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" display="https://www.laphilo.fr/pho/nykisukidi-mini.webp" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" display="https://www.laphilo.fr/pho/jdfunes-mini.webp" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tristan_Garcia&quot; title=&quot; Wikipedia&quot;&gt;Tristan GARCIA&lt;/a&gt;  est un philosophe et romancier français  figure montante d’une métaphysique contemporaine ambitieuse. Il soutient en 2008 une thèse de doctorat à Paris-Sorbonne sous la direction de Sandra Laugier (après un passage avec Alain Badiou), avant de se consacrer à l’enseignement et à une œuvre hybride mêlant philosophie, romans et essais. &lt;/p&gt; &lt;p&gt; Son œuvre majeure &quot;Forme et objet. Un traité des choses&quot; paru en 2011, propose une métaphysique systématique qui rejette les hiérarchies traditionnelles (sujet/objet) pour penser le monde comme un flux continu de choses indifférenciées, où tout niveau de réalité est également réel. Influencé par le réalisme spéculatif (Quentin Meillassoux, Graham Harman), il vise une ontologie &quot;plate&quot; qui inclut humains, animaux, objets et abstractions sans privilège anthropocentrique, tout en tenant compte des critiques post-modernes. &lt;/p&gt; &lt;p&gt; Dans &quot;Nous&quot; ou &quot;La Vie intense&quot; paru en 2016, il explore l’appartenance à des collectifs variables &quot;nous humains&quot;, &quot;nous animaux&quot; et critique l’obsession moderne pour  &lt;a href=&quot;https://www.youtube.com/watch?v=JTLVzryyyEg&quot; title=&quot;Tristan Garcia, INTENSITÉ par abc penser&quot;&gt;l’intensité vitale, &lt;/a&gt;  prônant une éthique de l’élargissement des perspectives. &lt;/p&gt; &lt;p&gt; Romancier polyvalent, il passe du réalisme social (La Meilleure part des hommes, sur le sida) à la science-fiction éthique  en passant par des fables animales toujours au service d’une  &lt;a href=&quot;https://www.youtube.com/watch?v=K_wxi5xTYz8&quot; title=&quot;Conférence de Tristan Garcia « Le réel n’a pas besoin de nous » par Banquedelagrace&quot;&gt;réflexion totalisante &lt;/a&gt; non hégémonique. &lt;/p&gt; &#10; &lt;p&gt;&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;audio controls title=&quot;Tristan Garcia, &quot;La vie intense : une obsession moderne&quot; par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-13.05.2016-ITEMA_20984234-2016C12410S0134-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10; " r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Baptiste_Morizot&quot;  title=&quot; Wikipedia&quot;&gt;Baptiste MORIZOT&lt;/a&gt;  est un philosophe français,  maître de conférences à l'université d'Aix-Marseille, dont l'œuvre occupe une place centrale dans la réflexion écologique actuelle. Son approche se distingue par une pratique de terrain ancrée dans l'expérience, notamment le pistage des grands prédateurs comme les loups, ce qui lui permet de nourrir sa pensée philosophique par une observation directe et sensible du vivant.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve l'idée que la crise écologique contemporaine est avant tout une « crise de la sensibilité » et de nos relations avec le reste du monde vivant. Il soutient que la pensée moderne, marquée par un dualisme qui sépare strictement l'humain de la nature, nous a &lt;a href=&quot;https://www.youtube.com/watch?v=bAnXnPnnHCk&quot; title=&quot;Baptiste Morizot, meme penseur on est un animal par France Inter&quot;&gt;rendus aveugles et sourds &lt;/a&gt; aux autres espèces, qu'il préfère considérer comme d'autres « manières d'être vivant » plutôt que comme des êtres inférieurs. &lt;/p&gt; &lt;p&gt; Il propose ainsi de remplacer le modèle classique de la « maîtrise de la nature » par une « diplomatie des interdépendances ». Cette approche invite les humains à se concevoir comme des partenaires au sein d'un réseau complexe d'interdépendances, où il s'agit de tisser des alliances concrètes, de prêter attention aux signaux émis par les autres espèces et d'apprendre à cohabiter avec elles dans un esprit de respect et de responsabilité partagée. &lt;/p&gt; &lt;p&gt; Son travail, qui mêle récit, enquête éthologique et essai théorique, cherche à réenchanter &lt;a href=&quot;https://www.youtube.com/watch?v=uQZcktq_W3E&quot; title=&quot;Baptiste Morizot, remet l’humain à sa place par La Grande Librairie&quot;&gt;notre rapport au monde &lt;/a&gt; en réactivant nos capacités d'attention et d'intelligence sensible. En invitant à une forme de sagesse pragmatique et ancrée, il s'efforce de refonder notre culture environnementale, non pas pour dominer ou sanctuariser la nature, mais pour s'ajuster avec humilité à la diversité des formes de vie qui partagent la Terre avec nous. &lt;/p&gt;  &lt;audio controls title=&quot;Liberté, dignité, habitalité avec baptiste MORIZOT par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/18558-25.04.2026-ITEMA_24488881-2026F30378S0115-NET_MFI_D6CADDF4-ADD5-4D3F-AA1D-625272E9CD3C-22-b98aedea0426383b486dc3819cb77a8e.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" display="https://www.laphilo.fr/pho/ydallaglio-mini.webp" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Norman_Ajari&quot;  title=&quot; Wikipedia&quot;&gt;Norman AJARI&lt;/a&gt;  est un philosophe franco-américain spécialiste des &lt;a href=&quot;https://www.laconverse.com/articles/les-grandes-converses-philosophie-decoloniale-et-racisme-anti-noir-avec-norman-ajari&quot;  title=&quot;Les Grandes Converses : Philosophie décoloniale et racisme anti-noir avec Norman Ajari par La converse&quot;&gt;&quot;études décoloniales &lt;/a&gt; et des études noires francophones, qui travaille au croisement de la philosophie sociale et politique, de la théorie critique de la race et de l’héritage de Frantz Fanon. Il participe à de nombreux colloques internationaux et a développé un important travail de conférences publiques en France et à l’étranger. &lt;/p&gt; &lt;p&gt; Il  travaille sur la  &lt;a href=&quot;https://www.youtube.com/watch?v=IMUBi9oi2WM&quot; title=&quot;Norman Ajari atomise la gauche blanche et le Marxisme occidental par A gauche&quot;&gt;&quot;colonialité de l’être&quot; &lt;/a&gt; et montre comment les structures coloniales continuent d’organiser la subjectivité, les corps et les hiérarchies raciales dans les sociétés contemporaines. Dans son ouvrage  &lt;a href=&quot;https://www.youtube.com/watch?v=ECSmpOXY8kg&quot; title=&quot;NORMAN AJARI - LA DIGNITE OU LA MORT par POUR PRESS&quot;&gt;&quot;La Dignité ou la mort&quot;, &lt;/a&gt;  il articule éthique, politique et race en montrant que la dignité noire est constamment conditionnée par des dispositifs de violence policière, pénale, économique et symbolique. &lt;/p&gt; &lt;p&gt; Il  assume une position de &quot;philosophe militant&quot; : la production théorique, pour lui, doit rester liée aux pratiques de lutte, et établir une parole en tant qu’intellectuel noir implique nécessairement la polémique et la confrontation avec l’ordre existant. &lt;/p&gt; &lt;audio controls title=&quot;où commence et où finit le racisme? par France Culture&quot;&gt; &lt;source  src=&quot;https://media.radiofrance-podcast.net/podcast09/13397-02.09.2023-ITEMA_23473922-2023C3397E0033-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;&#10;" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" display="https://www.laphilo.fr/pho/mmaeso-mini.webp" r:id="rId41"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
